--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2113" uniqueCount="2113">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2114" uniqueCount="2114">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">10.7068347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4860239028931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1916122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91192054748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93645191192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.225959777832</t>
+    <t xml:space="preserve">10.4860258102417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.191611289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91191959381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93645286560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2259607315063</t>
   </si>
   <si>
     <t xml:space="preserve">10.000244140625</t>
@@ -68,28 +68,28 @@
     <t xml:space="preserve">9.617506980896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33290672302246</t>
+    <t xml:space="preserve">9.33290481567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.15135097503662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37706756591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85693836212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25930309295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53899574279785</t>
+    <t xml:space="preserve">9.37706851959229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85693740844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25930118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53899478912354</t>
   </si>
   <si>
     <t xml:space="preserve">9.4899263381958</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50955390930176</t>
+    <t xml:space="preserve">9.50955486297607</t>
   </si>
   <si>
     <t xml:space="preserve">9.40160179138184</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">9.43595123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84712409973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99433040618896</t>
+    <t xml:space="preserve">8.84712314605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99433135986328</t>
   </si>
   <si>
     <t xml:space="preserve">8.79805469512939</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">8.05711364746094</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86574697494507</t>
+    <t xml:space="preserve">7.86574649810791</t>
   </si>
   <si>
     <t xml:space="preserve">8.32699394226074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61058855056763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67928409576416</t>
+    <t xml:space="preserve">7.61058759689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67928504943848</t>
   </si>
   <si>
     <t xml:space="preserve">8.10127639770508</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87065124511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53799057006836</t>
+    <t xml:space="preserve">7.8706521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53798961639404</t>
   </si>
   <si>
     <t xml:space="preserve">8.78333473205566</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">8.46929359436035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61649990081787</t>
+    <t xml:space="preserve">8.61649894714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.50364112854004</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">8.21413516998291</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69010353088379</t>
+    <t xml:space="preserve">8.69010257720947</t>
   </si>
   <si>
     <t xml:space="preserve">8.71954441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29365158081055</t>
+    <t xml:space="preserve">9.29365253448486</t>
   </si>
   <si>
     <t xml:space="preserve">9.30837154388428</t>
@@ -173,52 +173,52 @@
     <t xml:space="preserve">9.22004795074463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41141700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48011302947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77943420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66166877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79415416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77452754974365</t>
+    <t xml:space="preserve">9.41141510009766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4801139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77943325042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79415512084961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77452564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.68620204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64694595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72545719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2357749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3044710159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8383150100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56843662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98552322387695</t>
+    <t xml:space="preserve">9.64694786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72545623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2357740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3044700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83831596374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56843757629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98552227020264</t>
   </si>
   <si>
     <t xml:space="preserve">9.93154525756836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74508476257324</t>
+    <t xml:space="preserve">9.74508380889893</t>
   </si>
   <si>
     <t xml:space="preserve">10.3780727386475</t>
@@ -227,40 +227,40 @@
     <t xml:space="preserve">10.5449075698853</t>
   </si>
   <si>
-    <t xml:space="preserve">10.436957359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5547227859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.505654335022</t>
+    <t xml:space="preserve">10.4369554519653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5547218322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5056524276733</t>
   </si>
   <si>
     <t xml:space="preserve">10.5498151779175</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5007457733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5694427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.417329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4811182022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7411842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8442287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7853469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5988826751709</t>
+    <t xml:space="preserve">10.5007467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5694417953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173288345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4811191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7411832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8442277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.785346031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5988855361938</t>
   </si>
   <si>
     <t xml:space="preserve">10.2406806945801</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">10.2897500991821</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73036479949951</t>
+    <t xml:space="preserve">9.73036289215088</t>
   </si>
   <si>
     <t xml:space="preserve">9.57334327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43104553222656</t>
+    <t xml:space="preserve">9.43104362487793</t>
   </si>
   <si>
     <t xml:space="preserve">9.40650939941406</t>
@@ -284,133 +284,133 @@
     <t xml:space="preserve">9.19060611724854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08265590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35253429412842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47029876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27892971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30346393585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14644527435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52970123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79665470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190118789673</t>
+    <t xml:space="preserve">9.08265495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3525333404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47029781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27893161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30346488952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14644432067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52970218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79665374755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1190128326416</t>
   </si>
   <si>
     <t xml:space="preserve">9.89235496520996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95279693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492328643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84702396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.766432762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42896366119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42392730712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5246639251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54984951019287</t>
+    <t xml:space="preserve">9.95279598236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492338180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84702205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76643371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42896461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42392826080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52466583251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54984855651855</t>
   </si>
   <si>
     <t xml:space="preserve">9.39370632171631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82957935333252</t>
+    <t xml:space="preserve">8.82958126068115</t>
   </si>
   <si>
     <t xml:space="preserve">8.4820384979248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28560352325439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46189117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53744316101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68351268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39874267578125</t>
+    <t xml:space="preserve">8.28560161590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46189212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53744506835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68351173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39874362945557</t>
   </si>
   <si>
     <t xml:space="preserve">9.5045166015625</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81680011749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46459627151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540702819824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49985599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34875011444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43941307067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20268154144287</t>
+    <t xml:space="preserve">9.81680107116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46459722518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540798187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49985504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3487491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43941259384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.2026801109314</t>
   </si>
   <si>
     <t xml:space="preserve">6.87025022506714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50256061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6284818649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86017608642578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02135515213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38904428482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20771789550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44948720932007</t>
+    <t xml:space="preserve">6.50256109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62848138809204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86017560958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02135419845581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38904571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20771884918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44948577880859</t>
   </si>
   <si>
     <t xml:space="preserve">7.66607141494751</t>
@@ -419,43 +419,43 @@
     <t xml:space="preserve">7.5250391960144</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64592361450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79702949523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71140384674072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94309616088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81717586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94813394546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08179712295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92565536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71410799026489</t>
+    <t xml:space="preserve">7.64592409133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79702997207642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71140241622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94309568405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8171763420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94813203811646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08179807662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92565441131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71410894393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.78966045379639</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90047025680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22786569595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27823448181152</t>
+    <t xml:space="preserve">6.90047073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22786521911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27823495864868</t>
   </si>
   <si>
     <t xml:space="preserve">7.32860326766968</t>
@@ -464,91 +464,91 @@
     <t xml:space="preserve">7.31852865219116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39911890029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15734958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94580316543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764566421509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80477094650269</t>
+    <t xml:space="preserve">7.39911794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15735006332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94580268859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80477142333984</t>
   </si>
   <si>
     <t xml:space="preserve">7.02639102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08683395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04150199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85010147094727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86521339416504</t>
+    <t xml:space="preserve">7.08683443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04150295257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85010242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86521291732788</t>
   </si>
   <si>
     <t xml:space="preserve">6.93069219589233</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22282791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31349277496338</t>
+    <t xml:space="preserve">7.22282934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31349182128906</t>
   </si>
   <si>
     <t xml:space="preserve">7.23290252685547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29838132858276</t>
+    <t xml:space="preserve">7.29838085174561</t>
   </si>
   <si>
     <t xml:space="preserve">6.98106050491333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01128053665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53781843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79973316192627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68388652801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73929214477539</t>
+    <t xml:space="preserve">7.01128149032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53781890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7997350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68388557434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73929357528687</t>
   </si>
   <si>
     <t xml:space="preserve">6.94076490402222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90550756454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66877698898315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46226596832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57307720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67381381988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59826040267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87528657913208</t>
+    <t xml:space="preserve">6.90550804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66877746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4622654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57307577133179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6738133430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5982608795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87528705596924</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624465942383</t>
@@ -557,145 +557,145 @@
     <t xml:space="preserve">7.15231275558472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30341815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62577676773071</t>
+    <t xml:space="preserve">7.30341768264771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6257758140564</t>
   </si>
   <si>
     <t xml:space="preserve">7.66103410720825</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57037019729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45452308654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53511333465576</t>
+    <t xml:space="preserve">7.57037115097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45452404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53511238098145</t>
   </si>
   <si>
     <t xml:space="preserve">7.44444990158081</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5955548286438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72147655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.605628490448</t>
+    <t xml:space="preserve">7.59555530548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72147703170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60562753677368</t>
   </si>
   <si>
     <t xml:space="preserve">7.70636558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48474407196045</t>
+    <t xml:space="preserve">7.48474550247192</t>
   </si>
   <si>
     <t xml:space="preserve">7.3638596534729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26312351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.132164478302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17246055603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69629096984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91791439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35611915588379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38634014129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51729774475098</t>
+    <t xml:space="preserve">7.26312303543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13216590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17245960235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69629192352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91791248321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35611629486084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38633918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51729583740234</t>
   </si>
   <si>
     <t xml:space="preserve">8.45181751251221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20501232147217</t>
+    <t xml:space="preserve">8.20501327514648</t>
   </si>
   <si>
     <t xml:space="preserve">8.04887104034424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820713043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93132162094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71623420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73236656188965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.6355767250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64095544815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45813179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44199991226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57105255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68935060501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62482261657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79689264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20018100738525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43139839172363</t>
+    <t xml:space="preserve">7.9582085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93132305145264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71623516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73236799240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63557767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64095497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45813035964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44200038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57105207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68934869766235</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62482309341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79689359664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20018196105957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43140029907227</t>
   </si>
   <si>
     <t xml:space="preserve">8.61960029602051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54432010650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46903896331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58733749389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70025634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54969692230225</t>
+    <t xml:space="preserve">8.54432106018066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46903800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58733558654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70025730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54969596862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.60346794128418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53356456756592</t>
+    <t xml:space="preserve">8.53356552124023</t>
   </si>
   <si>
     <t xml:space="preserve">8.5980920791626</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">8.51743412017822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5281867980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67874908447266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11429882049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15731716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20033359527588</t>
+    <t xml:space="preserve">8.52818775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67875003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11429977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15731525421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20033264160156</t>
   </si>
   <si>
     <t xml:space="preserve">9.17882537841797</t>
@@ -725,34 +725,34 @@
     <t xml:space="preserve">9.05515003204346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33476448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13043117523193</t>
+    <t xml:space="preserve">9.33476257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13043022155762</t>
   </si>
   <si>
     <t xml:space="preserve">9.44768333435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38315868377686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41004371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4584379196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45306015014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37240314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2379732131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32938671112061</t>
+    <t xml:space="preserve">9.38315582275391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41004276275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45843887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4530611038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37240219116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23797416687012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32938575744629</t>
   </si>
   <si>
     <t xml:space="preserve">9.46919250488281</t>
@@ -764,46 +764,46 @@
     <t xml:space="preserve">8.92609786987305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09278964996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07128143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76478481292725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16806983947754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25948143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28636837005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24335193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26485824584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23259735107422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24872779846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96373844146729</t>
+    <t xml:space="preserve">9.0927906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07128238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76478290557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16807079315186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25948238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28637027740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2433500289917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26485919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2325963973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24872875213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96373748779297</t>
   </si>
   <si>
     <t xml:space="preserve">8.495924949646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59271430969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52280902862549</t>
+    <t xml:space="preserve">8.59271335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5228099822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.66799449920654</t>
@@ -815,55 +815,55 @@
     <t xml:space="preserve">8.71101188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70563316345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63573169708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53894138336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50130081176758</t>
+    <t xml:space="preserve">8.70563411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6357307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53894233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50130176544189</t>
   </si>
   <si>
     <t xml:space="preserve">8.28621482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33460807800293</t>
+    <t xml:space="preserve">8.33460998535156</t>
   </si>
   <si>
     <t xml:space="preserve">8.43677616119385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47441673278809</t>
+    <t xml:space="preserve">8.47441577911377</t>
   </si>
   <si>
     <t xml:space="preserve">8.62497615814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56582927703857</t>
+    <t xml:space="preserve">8.56582832336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.47979259490967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66261768341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61422348022461</t>
+    <t xml:space="preserve">8.66261672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61422157287598</t>
   </si>
   <si>
     <t xml:space="preserve">8.78091526031494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77016067504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79166984558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18420314788818</t>
+    <t xml:space="preserve">8.77016162872314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79166889190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1842041015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.04977321624756</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">9.14118480682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16269397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30250072479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13580799102783</t>
+    <t xml:space="preserve">9.16269302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30249977111816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1358060836792</t>
   </si>
   <si>
     <t xml:space="preserve">9.14656162261963</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">9.7165412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97464561462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0553026199341</t>
+    <t xml:space="preserve">9.97464656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0553035736084</t>
   </si>
   <si>
     <t xml:space="preserve">10.2435035705566</t>
@@ -923,16 +923,16 @@
     <t xml:space="preserve">10.3994426727295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4101963043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1305847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036987304688</t>
+    <t xml:space="preserve">10.4101972579956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349161148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1305837631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036977767944</t>
   </si>
   <si>
     <t xml:space="preserve">10.3295383453369</t>
@@ -941,34 +941,34 @@
     <t xml:space="preserve">10.425971031189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5507659912109</t>
+    <t xml:space="preserve">10.5507650375366</t>
   </si>
   <si>
     <t xml:space="preserve">10.6074905395508</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5847997665405</t>
+    <t xml:space="preserve">10.5848007202148</t>
   </si>
   <si>
     <t xml:space="preserve">10.4770231246948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2728147506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3408842086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2160902023315</t>
+    <t xml:space="preserve">10.2387800216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2728157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3408832550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2160911560059</t>
   </si>
   <si>
     <t xml:space="preserve">10.0856237411499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9041051864624</t>
+    <t xml:space="preserve">9.90410614013672</t>
   </si>
   <si>
     <t xml:space="preserve">10.2898321151733</t>
@@ -986,22 +986,22 @@
     <t xml:space="preserve">9.94381237030029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1707096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1366748809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0629329681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1990718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3522272109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104167938232</t>
+    <t xml:space="preserve">10.1707105636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1366758346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0629348754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1990728378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3522281646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104158401489</t>
   </si>
   <si>
     <t xml:space="preserve">10.1933994293213</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">9.95515823364258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.148021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2444515228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2217626571655</t>
+    <t xml:space="preserve">10.1480197906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2444505691528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841596603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2217617034912</t>
   </si>
   <si>
     <t xml:space="preserve">10.0912971496582</t>
@@ -1028,55 +1028,55 @@
     <t xml:space="preserve">10.1593656539917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5450925827026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.408953666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3181953430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2955045700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3692455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4316425323486</t>
+    <t xml:space="preserve">10.5450916290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4089546203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3181943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2955055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3692464828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4316434860229</t>
   </si>
   <si>
     <t xml:space="preserve">10.397608757019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7152671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6415252685547</t>
+    <t xml:space="preserve">10.7152662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6415243148804</t>
   </si>
   <si>
     <t xml:space="preserve">10.7436285018921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7209367752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6698865890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.777663230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7039213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6585426330566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.539421081543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3068494796753</t>
+    <t xml:space="preserve">10.7209386825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.669885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7776641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7039203643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.658540725708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5394201278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3068504333496</t>
   </si>
   <si>
     <t xml:space="preserve">10.7095947265625</t>
@@ -1097,16 +1097,16 @@
     <t xml:space="preserve">10.2784872055054</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0289001464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0969696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0345706939697</t>
+    <t xml:space="preserve">10.0288991928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.040244102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0969686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.034571647644</t>
   </si>
   <si>
     <t xml:space="preserve">9.98351955413818</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">9.98919296264648</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2274351119995</t>
+    <t xml:space="preserve">10.2274360656738</t>
   </si>
   <si>
     <t xml:space="preserve">10.2557983398438</t>
@@ -1130,22 +1130,22 @@
     <t xml:space="preserve">10.511058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4146270751953</t>
+    <t xml:space="preserve">10.414626121521</t>
   </si>
   <si>
     <t xml:space="preserve">10.3635740280151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3805923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4600048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.516731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3465576171875</t>
+    <t xml:space="preserve">10.3805913925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4600057601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5167303085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3465566635132</t>
   </si>
   <si>
     <t xml:space="preserve">9.84738063812256</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">9.86439800262451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7282600402832</t>
+    <t xml:space="preserve">9.72825908660889</t>
   </si>
   <si>
     <t xml:space="preserve">9.67720794677734</t>
@@ -1163,13 +1163,13 @@
     <t xml:space="preserve">9.66018962860107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48434448242188</t>
+    <t xml:space="preserve">9.48434352874756</t>
   </si>
   <si>
     <t xml:space="preserve">9.688551902771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58644866943359</t>
+    <t xml:space="preserve">9.58644771575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.71124172210693</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">9.6204833984375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73393058776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78498363494873</t>
+    <t xml:space="preserve">9.73393154144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78498458862305</t>
   </si>
   <si>
     <t xml:space="preserve">9.79632949829102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89843273162842</t>
+    <t xml:space="preserve">9.89843463897705</t>
   </si>
   <si>
     <t xml:space="preserve">9.16101360321045</t>
@@ -1202,43 +1202,43 @@
     <t xml:space="preserve">8.95113277435303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9908390045166</t>
+    <t xml:space="preserve">8.99084091186523</t>
   </si>
   <si>
     <t xml:space="preserve">8.76961421966553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75259685516357</t>
+    <t xml:space="preserve">8.75259780883789</t>
   </si>
   <si>
     <t xml:space="preserve">8.86604595184326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85470008850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05891036987305</t>
+    <t xml:space="preserve">8.85470104217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05891132354736</t>
   </si>
   <si>
     <t xml:space="preserve">9.24042797088623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2517728805542</t>
+    <t xml:space="preserve">9.25177383422852</t>
   </si>
   <si>
     <t xml:space="preserve">9.10996246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09294414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98516750335693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07592678070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13265228271484</t>
+    <t xml:space="preserve">9.09294319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98516845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.075927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13265132904053</t>
   </si>
   <si>
     <t xml:space="preserve">9.05323696136475</t>
@@ -1256,31 +1256,31 @@
     <t xml:space="preserve">8.79230403900146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79797554016113</t>
+    <t xml:space="preserve">8.79797744750977</t>
   </si>
   <si>
     <t xml:space="preserve">8.9681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00218486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07025527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9965124130249</t>
+    <t xml:space="preserve">9.00218391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0702543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99651336669922</t>
   </si>
   <si>
     <t xml:space="preserve">9.01920223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92277050018311</t>
+    <t xml:space="preserve">8.92277145385742</t>
   </si>
   <si>
     <t xml:space="preserve">9.04189205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03054714202881</t>
+    <t xml:space="preserve">9.03054809570312</t>
   </si>
   <si>
     <t xml:space="preserve">9.01353073120117</t>
@@ -1292,13 +1292,13 @@
     <t xml:space="preserve">9.03621959686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13832473754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97382354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12697792053223</t>
+    <t xml:space="preserve">9.1383228302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97382259368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12697887420654</t>
   </si>
   <si>
     <t xml:space="preserve">9.16668701171875</t>
@@ -1313,10 +1313,10 @@
     <t xml:space="preserve">9.38223934173584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34253215789795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46732616424561</t>
+    <t xml:space="preserve">9.34253311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46732521057129</t>
   </si>
   <si>
     <t xml:space="preserve">10.6755599975586</t>
@@ -1331,19 +1331,19 @@
     <t xml:space="preserve">10.5961446762085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7549724578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7379570007324</t>
+    <t xml:space="preserve">10.7549743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7379550933838</t>
   </si>
   <si>
     <t xml:space="preserve">10.7606449127197</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6613779067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4543323516846</t>
+    <t xml:space="preserve">10.661376953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4543333053589</t>
   </si>
   <si>
     <t xml:space="preserve">10.403281211853</t>
@@ -1352,25 +1352,25 @@
     <t xml:space="preserve">10.4429874420166</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3777561187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0742788314819</t>
+    <t xml:space="preserve">10.3777551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0742797851562</t>
   </si>
   <si>
     <t xml:space="preserve">10.1338396072388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0941324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98635673522949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1565284729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962375640869</t>
+    <t xml:space="preserve">10.0941314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98635578155518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.156530380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.196234703064</t>
   </si>
   <si>
     <t xml:space="preserve">10.2359437942505</t>
@@ -1382,28 +1382,28 @@
     <t xml:space="preserve">10.2416172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2501249313354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132530212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1678733825684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90694046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92963123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1877279281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2302703857422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0203886032104</t>
+    <t xml:space="preserve">10.2501258850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132539749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1678743362427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90694141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9296293258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1877269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2302713394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0203895568848</t>
   </si>
   <si>
     <t xml:space="preserve">10.1905641555786</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">10.0317344665527</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9778470993042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81618404388428</t>
+    <t xml:space="preserve">9.97784805297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81618213653564</t>
   </si>
   <si>
     <t xml:space="preserve">9.88708782196045</t>
@@ -1433,10 +1433,10 @@
     <t xml:space="preserve">9.97501087188721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0657711029053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1395111083984</t>
+    <t xml:space="preserve">10.065770149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1395120620728</t>
   </si>
   <si>
     <t xml:space="preserve">10.0005369186401</t>
@@ -1445,7 +1445,7 @@
     <t xml:space="preserve">10.0686063766479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73676872253418</t>
+    <t xml:space="preserve">9.73676776885986</t>
   </si>
   <si>
     <t xml:space="preserve">9.83603572845459</t>
@@ -1454,28 +1454,28 @@
     <t xml:space="preserve">9.89276027679443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86723518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8275260925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77931118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83319854736328</t>
+    <t xml:space="preserve">9.86723327636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82752704620361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77931022644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8331995010376</t>
   </si>
   <si>
     <t xml:space="preserve">9.94948577880859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0714416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93814182281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71407699584961</t>
+    <t xml:space="preserve">10.0714426040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93814086914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71407794952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.42761993408203</t>
@@ -1493,19 +1493,19 @@
     <t xml:space="preserve">9.24326419830322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20072174072266</t>
+    <t xml:space="preserve">9.20072269439697</t>
   </si>
   <si>
     <t xml:space="preserve">9.29274559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51369762420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39841747283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47206783294678</t>
+    <t xml:space="preserve">9.51369667053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39841842651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47206878662109</t>
   </si>
   <si>
     <t xml:space="preserve">9.4400463104248</t>
@@ -1517,13 +1517,13 @@
     <t xml:space="preserve">8.98533535003662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02696418762207</t>
+    <t xml:space="preserve">9.02696514129639</t>
   </si>
   <si>
     <t xml:space="preserve">8.89887619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34398078918457</t>
+    <t xml:space="preserve">9.34397983551025</t>
   </si>
   <si>
     <t xml:space="preserve">9.31836223602295</t>
@@ -1532,25 +1532,25 @@
     <t xml:space="preserve">8.93730449676514</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92129230499268</t>
+    <t xml:space="preserve">8.92129135131836</t>
   </si>
   <si>
     <t xml:space="preserve">8.93410110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64590358734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83803558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7547779083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72275638580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71635246276855</t>
+    <t xml:space="preserve">8.64590263366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83803462982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75477886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72275543212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71635150909424</t>
   </si>
   <si>
     <t xml:space="preserve">8.64270210266113</t>
@@ -1559,58 +1559,58 @@
     <t xml:space="preserve">8.82842922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8060131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83163070678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66511631011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73556613922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51781558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56904983520508</t>
+    <t xml:space="preserve">8.80601406097412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83162975311279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66511726379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73556518554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51781463623047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899745941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56905269622803</t>
   </si>
   <si>
     <t xml:space="preserve">8.45697498321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39613342285156</t>
+    <t xml:space="preserve">8.39613437652588</t>
   </si>
   <si>
     <t xml:space="preserve">8.51141166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53062629699707</t>
+    <t xml:space="preserve">8.53062534332275</t>
   </si>
   <si>
     <t xml:space="preserve">8.53703022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54343414306641</t>
+    <t xml:space="preserve">8.54343318939209</t>
   </si>
   <si>
     <t xml:space="preserve">8.71315002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40573978424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36411190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3320894241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42175197601318</t>
+    <t xml:space="preserve">8.40573883056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36411094665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33209037780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42175102233887</t>
   </si>
   <si>
     <t xml:space="preserve">8.58506202697754</t>
@@ -1619,31 +1619,31 @@
     <t xml:space="preserve">8.57225322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46017551422119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46658134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58186054229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4409646987915</t>
+    <t xml:space="preserve">8.46017742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46658229827881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58186149597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44096374511719</t>
   </si>
   <si>
     <t xml:space="preserve">9.09420967102051</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01735877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05578327178955</t>
+    <t xml:space="preserve">9.01735782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05578422546387</t>
   </si>
   <si>
     <t xml:space="preserve">9.19988250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18707370758057</t>
+    <t xml:space="preserve">9.18707180023193</t>
   </si>
   <si>
     <t xml:space="preserve">8.91808986663818</t>
@@ -1652,16 +1652,16 @@
     <t xml:space="preserve">8.87646198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03657150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18387222290039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15505218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15184879302979</t>
+    <t xml:space="preserve">9.03657054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18387126922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15505123138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1518497467041</t>
   </si>
   <si>
     <t xml:space="preserve">9.23510551452637</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">9.1262321472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26072311401367</t>
+    <t xml:space="preserve">9.2607250213623</t>
   </si>
   <si>
     <t xml:space="preserve">9.254319190979</t>
@@ -1685,7 +1685,7 @@
     <t xml:space="preserve">9.20948886871338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22549915313721</t>
+    <t xml:space="preserve">9.22550010681152</t>
   </si>
   <si>
     <t xml:space="preserve">9.10701942443848</t>
@@ -1694,19 +1694,19 @@
     <t xml:space="preserve">8.92769718170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76758670806885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65871143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68112850189209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72595882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61708450317383</t>
+    <t xml:space="preserve">8.76758766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65871334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68112659454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72595977783203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61708545684814</t>
   </si>
   <si>
     <t xml:space="preserve">8.7803955078125</t>
@@ -1715,7 +1715,7 @@
     <t xml:space="preserve">8.82202434539795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77719402313232</t>
+    <t xml:space="preserve">8.77719306945801</t>
   </si>
   <si>
     <t xml:space="preserve">8.78359699249268</t>
@@ -1742,10 +1742,10 @@
     <t xml:space="preserve">8.22321510314941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29366397857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53382778167725</t>
+    <t xml:space="preserve">8.29366302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53382873535156</t>
   </si>
   <si>
     <t xml:space="preserve">8.48259258270264</t>
@@ -1754,46 +1754,46 @@
     <t xml:space="preserve">8.40253734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14956569671631</t>
+    <t xml:space="preserve">8.14956474304199</t>
   </si>
   <si>
     <t xml:space="preserve">8.06630802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07271099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77490901947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74929237365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67884349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87417602539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73007822036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53474426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42266988754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25295305252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21772861480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0800347328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11205577850342</t>
+    <t xml:space="preserve">8.07271194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77490997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74929141998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67884397506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87417697906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73007869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53474521636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42266845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25295209884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21772909164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08003520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11205673217773</t>
   </si>
   <si>
     <t xml:space="preserve">6.84947681427002</t>
@@ -1802,10 +1802,10 @@
     <t xml:space="preserve">6.97115993499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04160833358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03520393371582</t>
+    <t xml:space="preserve">7.04160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03520441055298</t>
   </si>
   <si>
     <t xml:space="preserve">7.04801273345947</t>
@@ -1814,19 +1814,19 @@
     <t xml:space="preserve">6.94234085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95194673538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00958681106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13126802444458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97436094284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83026456832886</t>
+    <t xml:space="preserve">6.95194721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00958633422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13126945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97436189651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83026361465454</t>
   </si>
   <si>
     <t xml:space="preserve">6.95514965057373</t>
@@ -1835,103 +1835,103 @@
     <t xml:space="preserve">6.8014440536499</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7662205696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8590841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62852621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70537853240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74700593948364</t>
+    <t xml:space="preserve">6.76622009277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85908460617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6285252571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70537900924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74700689315796</t>
   </si>
   <si>
     <t xml:space="preserve">6.86548757553101</t>
   </si>
   <si>
-    <t xml:space="preserve">7.16329097747803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09604597091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06722593307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02239513397217</t>
+    <t xml:space="preserve">7.16329145431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09604549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06722640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02239561080933</t>
   </si>
   <si>
     <t xml:space="preserve">7.23053693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05761909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80464506149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89110469818115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71818733215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7374005317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95835113525391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01278972625732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88790369033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45881032943726</t>
+    <t xml:space="preserve">7.05761957168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80464649200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89110565185547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71818780899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73740100860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95835208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01278924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88790321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45880937576294</t>
   </si>
   <si>
     <t xml:space="preserve">6.39796876907349</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15204191207886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15844440460205</t>
+    <t xml:space="preserve">6.15204095840454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15844488143921</t>
   </si>
   <si>
     <t xml:space="preserve">5.96375179290771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10593032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10721015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39925003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64453601837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63172817230225</t>
+    <t xml:space="preserve">6.10592937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10721111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39925050735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64453649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6317286491394</t>
   </si>
   <si>
     <t xml:space="preserve">6.59010028839111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50043916702271</t>
+    <t xml:space="preserve">6.50043964385986</t>
   </si>
   <si>
     <t xml:space="preserve">6.60290861129761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5965051651001</t>
+    <t xml:space="preserve">6.59650325775146</t>
   </si>
   <si>
     <t xml:space="preserve">6.41718101501465</t>
@@ -1940,82 +1940,82 @@
     <t xml:space="preserve">6.52285432815552</t>
   </si>
   <si>
-    <t xml:space="preserve">6.42038440704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47802305221558</t>
+    <t xml:space="preserve">6.42038488388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47802400588989</t>
   </si>
   <si>
     <t xml:space="preserve">6.44600200653076</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32624053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2673192024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74380493164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09924840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30738973617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19851493835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08964109420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11846113204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15368461608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15688753128052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17930269241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04481077194214</t>
+    <t xml:space="preserve">6.32624006271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26732015609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74380588531494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09924745559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30739068984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19851589202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08964157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11846017837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15368509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15688705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17930126190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0448112487793</t>
   </si>
   <si>
     <t xml:space="preserve">6.99357557296753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27216625213623</t>
+    <t xml:space="preserve">7.27216672897339</t>
   </si>
   <si>
     <t xml:space="preserve">7.44828605651855</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75889873504639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57637357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72687578201294</t>
+    <t xml:space="preserve">7.75889825820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57637214660645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72687673568726</t>
   </si>
   <si>
     <t xml:space="preserve">7.83895301818848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82614374160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8453574180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89979410171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9126033782959</t>
+    <t xml:space="preserve">7.82614421844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84535598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8997950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91260290145874</t>
   </si>
   <si>
     <t xml:space="preserve">7.98305082321167</t>
@@ -2024,7 +2024,7 @@
     <t xml:space="preserve">7.88058090209961</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91900873184204</t>
+    <t xml:space="preserve">7.91900730133057</t>
   </si>
   <si>
     <t xml:space="preserve">8.23282146453857</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">8.12074565887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26164150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47298622131348</t>
+    <t xml:space="preserve">8.26164245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47298717498779</t>
   </si>
   <si>
     <t xml:space="preserve">8.46337890625</t>
@@ -2045,49 +2045,49 @@
     <t xml:space="preserve">8.84764194488525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9116849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2639274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3311710357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53291034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6770076751709</t>
+    <t xml:space="preserve">8.91168594360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26392650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33117198944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53291130065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67700862884521</t>
   </si>
   <si>
     <t xml:space="preserve">9.51049423217773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42083263397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32796859741211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40482330322266</t>
+    <t xml:space="preserve">9.42083358764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32796955108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40482234954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.47847270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55212306976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57133674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77627658843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81470108032227</t>
+    <t xml:space="preserve">9.55212211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5713357925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70262432098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77627563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81470203399658</t>
   </si>
   <si>
     <t xml:space="preserve">10.083685874939</t>
@@ -2096,19 +2096,19 @@
     <t xml:space="preserve">10.0356531143188</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1413240432739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2149753570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1957626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2694129943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2790203094482</t>
+    <t xml:space="preserve">10.1413249969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.21497631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.195761680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2694120407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2790193557739</t>
   </si>
   <si>
     <t xml:space="preserve">10.5608129501343</t>
@@ -2117,7 +2117,7 @@
     <t xml:space="preserve">10.849009513855</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8682222366333</t>
+    <t xml:space="preserve">10.868221282959</t>
   </si>
   <si>
     <t xml:space="preserve">10.8874340057373</t>
@@ -2129,22 +2129,22 @@
     <t xml:space="preserve">11.0603513717651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.281304359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2909097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5118608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5278730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.495849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3773679733276</t>
+    <t xml:space="preserve">11.2813034057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2909088134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5118618011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4958505630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.377368927002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3261337280273</t>
@@ -2162,16 +2162,16 @@
     <t xml:space="preserve">10.5992374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0219268798828</t>
+    <t xml:space="preserve">11.0219249725342</t>
   </si>
   <si>
     <t xml:space="preserve">11.1404075622559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1141204833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7917680740356</t>
+    <t xml:space="preserve">11.1141195297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7917671203613</t>
   </si>
   <si>
     <t xml:space="preserve">10.7882652282715</t>
@@ -2198,22 +2198,22 @@
     <t xml:space="preserve">10.423867225647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3678073883057</t>
+    <t xml:space="preserve">10.3678064346313</t>
   </si>
   <si>
     <t xml:space="preserve">10.7322034835815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7742500305176</t>
+    <t xml:space="preserve">10.7742490768433</t>
   </si>
   <si>
     <t xml:space="preserve">10.4448900222778</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5079584121704</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5149660110474</t>
+    <t xml:space="preserve">10.5079593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.514967918396</t>
   </si>
   <si>
     <t xml:space="preserve">10.6305932998657</t>
@@ -2222,10 +2222,10 @@
     <t xml:space="preserve">10.8127918243408</t>
   </si>
   <si>
-    <t xml:space="preserve">11.128134727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1877012252808</t>
+    <t xml:space="preserve">11.1281356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1877002716064</t>
   </si>
   <si>
     <t xml:space="preserve">11.3523807525635</t>
@@ -2237,13 +2237,13 @@
     <t xml:space="preserve">11.6151666641235</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7553195953369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7342967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429136276245</t>
+    <t xml:space="preserve">11.7553186416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7342977523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429145812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7097682952881</t>
@@ -2252,10 +2252,10 @@
     <t xml:space="preserve">11.6291809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8639373779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9059839248657</t>
+    <t xml:space="preserve">11.863938331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9059829711914</t>
   </si>
   <si>
     <t xml:space="preserve">11.9199981689453</t>
@@ -2267,7 +2267,7 @@
     <t xml:space="preserve">12.2318382263184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.22483253479</t>
+    <t xml:space="preserve">12.2248315811157</t>
   </si>
   <si>
     <t xml:space="preserve">12.2984113693237</t>
@@ -2279,49 +2279,49 @@
     <t xml:space="preserve">12.3159303665161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2773885726929</t>
+    <t xml:space="preserve">12.2773895263672</t>
   </si>
   <si>
     <t xml:space="preserve">12.4175405502319</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684892654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1267242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0391283035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464183807373</t>
+    <t xml:space="preserve">12.3684873580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1267251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0391292572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464193344116</t>
   </si>
   <si>
     <t xml:space="preserve">12.0636558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">12.140739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1232194900513</t>
+    <t xml:space="preserve">12.1407403945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1232204437256</t>
   </si>
   <si>
     <t xml:space="preserve">12.1092052459717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0321216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8779535293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760608673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6887474060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4680051803589</t>
+    <t xml:space="preserve">12.0321207046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8779544830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760599136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6887454986572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4680070877075</t>
   </si>
   <si>
     <t xml:space="preserve">11.4890298843384</t>
@@ -2330,10 +2330,10 @@
     <t xml:space="preserve">11.4820213317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6782350540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2472658157349</t>
+    <t xml:space="preserve">11.6782360076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2472639083862</t>
   </si>
   <si>
     <t xml:space="preserve">11.0370359420776</t>
@@ -2342,49 +2342,49 @@
     <t xml:space="preserve">11.1001043319702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7216920852661</t>
+    <t xml:space="preserve">10.7216911315918</t>
   </si>
   <si>
     <t xml:space="preserve">10.9284181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1561651229858</t>
+    <t xml:space="preserve">11.1561660766602</t>
   </si>
   <si>
     <t xml:space="preserve">11.496036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4469814300537</t>
+    <t xml:space="preserve">11.446982383728</t>
   </si>
   <si>
     <t xml:space="preserve">11.184196472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.324348449707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.275297164917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.061562538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4049367904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2297458648682</t>
+    <t xml:space="preserve">11.3243494033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2752962112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615634918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4049377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2297449111938</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119453430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4995393753052</t>
+    <t xml:space="preserve">11.4995403289795</t>
   </si>
   <si>
     <t xml:space="preserve">11.7903575897217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814573287964</t>
+    <t xml:space="preserve">11.8814563751221</t>
   </si>
   <si>
     <t xml:space="preserve">11.8288993835449</t>
@@ -2402,19 +2402,19 @@
     <t xml:space="preserve">11.8113803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970836639404</t>
+    <t xml:space="preserve">11.9970846176147</t>
   </si>
   <si>
     <t xml:space="preserve">11.9410219192505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9690523147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0671586990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703800201416</t>
+    <t xml:space="preserve">11.969051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.06715965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703819274902</t>
   </si>
   <si>
     <t xml:space="preserve">12.2738847732544</t>
@@ -2426,10 +2426,10 @@
     <t xml:space="preserve">12.0951900482178</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9725542068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0146017074585</t>
+    <t xml:space="preserve">11.9725551605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0146026611328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0741662979126</t>
@@ -2438,7 +2438,7 @@
     <t xml:space="preserve">11.9865713119507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6011505126953</t>
+    <t xml:space="preserve">11.6011514663696</t>
   </si>
   <si>
     <t xml:space="preserve">11.552098274231</t>
@@ -2453,10 +2453,10 @@
     <t xml:space="preserve">11.4259605407715</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5380830764771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6852436065674</t>
+    <t xml:space="preserve">11.5380821228027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6852426528931</t>
   </si>
   <si>
     <t xml:space="preserve">11.7693347930908</t>
@@ -2465,34 +2465,34 @@
     <t xml:space="preserve">11.7027626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9480285644531</t>
+    <t xml:space="preserve">11.9480295181274</t>
   </si>
   <si>
     <t xml:space="preserve">12.0846796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2108144760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7539100646973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9641380310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7188692092896</t>
+    <t xml:space="preserve">12.2108163833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7539091110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9641370773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7188711166382</t>
   </si>
   <si>
     <t xml:space="preserve">12.7889471054077</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7959537506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9886636734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1743669509888</t>
+    <t xml:space="preserve">12.7959547042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9886627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1743659973145</t>
   </si>
   <si>
     <t xml:space="preserve">12.9080762863159</t>
@@ -2501,37 +2501,37 @@
     <t xml:space="preserve">13.0412216186523</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2094049453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6649017333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8996553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.365665435791</t>
+    <t xml:space="preserve">13.2094039916992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6648998260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8996562957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007043838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3656663894653</t>
   </si>
   <si>
     <t xml:space="preserve">14.6389636993408</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0173768997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1365070343018</t>
+    <t xml:space="preserve">15.0173778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1365060806274</t>
   </si>
   <si>
     <t xml:space="preserve">15.5289354324341</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9493951797485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181415557861</t>
+    <t xml:space="preserve">15.9493942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181406021118</t>
   </si>
   <si>
     <t xml:space="preserve">15.9213619232178</t>
@@ -2540,13 +2540,13 @@
     <t xml:space="preserve">16.1035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9914388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1245861053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4118995666504</t>
+    <t xml:space="preserve">15.9914398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.124584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4118976593018</t>
   </si>
   <si>
     <t xml:space="preserve">16.5940971374512</t>
@@ -2555,19 +2555,19 @@
     <t xml:space="preserve">16.5100040435791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2086753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0475006103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8863229751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.486888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8232545852661</t>
+    <t xml:space="preserve">16.2086734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0474987030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.886323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4868879318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8232555389404</t>
   </si>
   <si>
     <t xml:space="preserve">15.7531785964966</t>
@@ -2579,67 +2579,67 @@
     <t xml:space="preserve">15.1575298309326</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3817749023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2626466751099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.297682762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0804452896118</t>
+    <t xml:space="preserve">15.3817739486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2626447677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2976808547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0804462432861</t>
   </si>
   <si>
     <t xml:space="preserve">15.2836656570435</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2205982208252</t>
+    <t xml:space="preserve">15.2205963134766</t>
   </si>
   <si>
     <t xml:space="preserve">15.0944604873657</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0664291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0454072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8562021255493</t>
+    <t xml:space="preserve">15.0664300918579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0454063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8562040328979</t>
   </si>
   <si>
     <t xml:space="preserve">14.9122629165649</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1715431213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8702154159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721090316772</t>
+    <t xml:space="preserve">15.1715440750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8702163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721099853516</t>
   </si>
   <si>
     <t xml:space="preserve">15.353741645813</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5029945373535</t>
+    <t xml:space="preserve">16.5029964447021</t>
   </si>
   <si>
     <t xml:space="preserve">16.5800800323486</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4189014434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7062187194824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8043270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6221237182617</t>
+    <t xml:space="preserve">16.4189052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7062168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8043231964111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.622127532959</t>
   </si>
   <si>
     <t xml:space="preserve">16.5660648345947</t>
@@ -2648,13 +2648,13 @@
     <t xml:space="preserve">16.9865226745605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0075492858887</t>
+    <t xml:space="preserve">17.0075454711914</t>
   </si>
   <si>
     <t xml:space="preserve">16.5380363464355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0545063018799</t>
+    <t xml:space="preserve">16.0545082092285</t>
   </si>
   <si>
     <t xml:space="preserve">16.3978824615479</t>
@@ -2663,28 +2663,28 @@
     <t xml:space="preserve">16.4959907531738</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0685253143311</t>
+    <t xml:space="preserve">16.0685234069824</t>
   </si>
   <si>
     <t xml:space="preserve">15.5499582290649</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5709800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.033483505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9423837661743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1666297912598</t>
+    <t xml:space="preserve">15.5709791183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0334854125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9423847198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1666316986084</t>
   </si>
   <si>
     <t xml:space="preserve">16.6431484222412</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3908729553223</t>
+    <t xml:space="preserve">16.3908748626709</t>
   </si>
   <si>
     <t xml:space="preserve">16.762279510498</t>
@@ -2696,16 +2696,16 @@
     <t xml:space="preserve">16.671178817749</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272396087646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.951488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6130266189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5198354721069</t>
+    <t xml:space="preserve">16.7272434234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9514865875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6130247116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5198335647583</t>
   </si>
   <si>
     <t xml:space="preserve">14.3516502380371</t>
@@ -2717,43 +2717,43 @@
     <t xml:space="preserve">13.7910394668579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4546718597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0272064208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9956712722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3474645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7202825546265</t>
+    <t xml:space="preserve">13.4546728134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0272054672241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9956731796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.347466468811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7202816009521</t>
   </si>
   <si>
     <t xml:space="preserve">10.3327674865723</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68806457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81069850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25149726867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51988220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4442081451416</t>
+    <t xml:space="preserve">9.68806552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81069946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25149822235107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51988124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44420909881592</t>
   </si>
   <si>
     <t xml:space="preserve">8.02024555206299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70490217208862</t>
+    <t xml:space="preserve">7.70490121841431</t>
   </si>
   <si>
     <t xml:space="preserve">7.77497911453247</t>
@@ -2762,25 +2762,25 @@
     <t xml:space="preserve">7.49817705154419</t>
   </si>
   <si>
-    <t xml:space="preserve">7.59978675842285</t>
+    <t xml:space="preserve">7.59978818893433</t>
   </si>
   <si>
     <t xml:space="preserve">8.28653621673584</t>
   </si>
   <si>
-    <t xml:space="preserve">9.06088066101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69507217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05037021636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87167453765869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23607158660889</t>
+    <t xml:space="preserve">9.06088161468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69507312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05036926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87167549133301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2360725402832</t>
   </si>
   <si>
     <t xml:space="preserve">8.87517833709717</t>
@@ -2789,13 +2789,13 @@
     <t xml:space="preserve">9.07489585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68246746063232</t>
+    <t xml:space="preserve">8.68246841430664</t>
   </si>
   <si>
     <t xml:space="preserve">9.0223388671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48834800720215</t>
+    <t xml:space="preserve">9.48834705352783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1680889129639</t>
@@ -2804,10 +2804,10 @@
     <t xml:space="preserve">10.2381649017334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87727069854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29914093017578</t>
+    <t xml:space="preserve">9.87727165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2991418838501</t>
   </si>
   <si>
     <t xml:space="preserve">9.4463005065918</t>
@@ -2816,13 +2816,13 @@
     <t xml:space="preserve">9.51637840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58995914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2535924911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33417987823486</t>
+    <t xml:space="preserve">9.58995819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25359058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33417797088623</t>
   </si>
   <si>
     <t xml:space="preserve">9.49535465240479</t>
@@ -2834,22 +2834,22 @@
     <t xml:space="preserve">10.3713102340698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8162956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2122278213501</t>
+    <t xml:space="preserve">10.816294670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2122268676758</t>
   </si>
   <si>
     <t xml:space="preserve">10.8793640136719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7602348327637</t>
+    <t xml:space="preserve">10.760232925415</t>
   </si>
   <si>
     <t xml:space="preserve">10.8618450164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5324859619141</t>
+    <t xml:space="preserve">10.5324869155884</t>
   </si>
   <si>
     <t xml:space="preserve">10.6025619506836</t>
@@ -2861,16 +2861,16 @@
     <t xml:space="preserve">10.5394945144653</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4133548736572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0058336257935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4649343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.765435218811</t>
+    <t xml:space="preserve">10.4133558273315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0058355331421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4649333953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7654342651367</t>
   </si>
   <si>
     <t xml:space="preserve">10.6414775848389</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">10.769190788269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8743667602539</t>
+    <t xml:space="preserve">10.8743658065796</t>
   </si>
   <si>
     <t xml:space="preserve">10.9757843017578</t>
@@ -2888,7 +2888,7 @@
     <t xml:space="preserve">10.9720277786255</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3589239120483</t>
+    <t xml:space="preserve">11.358922958374</t>
   </si>
   <si>
     <t xml:space="preserve">11.1936473846436</t>
@@ -2897,52 +2897,52 @@
     <t xml:space="preserve">11.3251171112061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5204429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7984046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0913934707642</t>
+    <t xml:space="preserve">11.5204420089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7984037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0913925170898</t>
   </si>
   <si>
     <t xml:space="preserve">12.6923952102661</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9966497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4407243728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3956508636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6481552124023</t>
+    <t xml:space="preserve">12.9966506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4407253265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3956499099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.648154258728</t>
   </si>
   <si>
     <t xml:space="preserve">11.6105918884277</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5166864395142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7721109390259</t>
+    <t xml:space="preserve">11.5166854858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7721099853516</t>
   </si>
   <si>
     <t xml:space="preserve">11.6669359207153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5091724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7157678604126</t>
+    <t xml:space="preserve">11.5091733932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7157669067383</t>
   </si>
   <si>
     <t xml:space="preserve">11.5730295181274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8284559249878</t>
+    <t xml:space="preserve">11.8284549713135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2687730789185</t>
@@ -2954,37 +2954,37 @@
     <t xml:space="preserve">11.2011594772339</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4791240692139</t>
+    <t xml:space="preserve">11.4791231155396</t>
   </si>
   <si>
     <t xml:space="preserve">11.4265356063843</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3664350509644</t>
+    <t xml:space="preserve">11.3664360046387</t>
   </si>
   <si>
     <t xml:space="preserve">11.663179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5429782867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7796239852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7608432769775</t>
+    <t xml:space="preserve">11.5429792404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7796249389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7608423233032</t>
   </si>
   <si>
     <t xml:space="preserve">11.4753665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6706914901733</t>
+    <t xml:space="preserve">11.6706924438477</t>
   </si>
   <si>
     <t xml:space="preserve">11.8585042953491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8434820175171</t>
+    <t xml:space="preserve">11.8434801101685</t>
   </si>
   <si>
     <t xml:space="preserve">12.3580884933472</t>
@@ -2993,7 +2993,7 @@
     <t xml:space="preserve">12.3205242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8013257980347</t>
+    <t xml:space="preserve">12.801326751709</t>
   </si>
   <si>
     <t xml:space="preserve">12.6999073028564</t>
@@ -3002,7 +3002,7 @@
     <t xml:space="preserve">12.7337131500244</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8351306915283</t>
+    <t xml:space="preserve">12.8351316452026</t>
   </si>
   <si>
     <t xml:space="preserve">12.5684375762939</t>
@@ -3011,7 +3011,7 @@
     <t xml:space="preserve">12.6097564697266</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3731126785278</t>
+    <t xml:space="preserve">12.3731117248535</t>
   </si>
   <si>
     <t xml:space="preserve">12.4369697570801</t>
@@ -3020,16 +3020,16 @@
     <t xml:space="preserve">12.0763683319092</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0575857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3693571090698</t>
+    <t xml:space="preserve">12.0575866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3693561553955</t>
   </si>
   <si>
     <t xml:space="preserve">12.3505754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4745311737061</t>
+    <t xml:space="preserve">12.4745321273804</t>
   </si>
   <si>
     <t xml:space="preserve">12.493311882019</t>
@@ -3038,31 +3038,31 @@
     <t xml:space="preserve">12.470775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8276214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938146591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6585893630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5984888076782</t>
+    <t xml:space="preserve">12.8276195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938137054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6585884094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5984878540039</t>
   </si>
   <si>
     <t xml:space="preserve">12.4557495117188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5158500671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3468179702759</t>
+    <t xml:space="preserve">12.5158491134644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3468189239502</t>
   </si>
   <si>
     <t xml:space="preserve">12.21910572052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6661005020142</t>
+    <t xml:space="preserve">12.6661014556885</t>
   </si>
   <si>
     <t xml:space="preserve">12.6247825622559</t>
@@ -3071,7 +3071,7 @@
     <t xml:space="preserve">12.508337020874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3881368637085</t>
+    <t xml:space="preserve">12.3881378173828</t>
   </si>
   <si>
     <t xml:space="preserve">12.1740312576294</t>
@@ -3080,28 +3080,28 @@
     <t xml:space="preserve">12.0650997161865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.264181137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9749488830566</t>
+    <t xml:space="preserve">12.2641820907593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.974949836731</t>
   </si>
   <si>
     <t xml:space="preserve">12.1552495956421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8847990036011</t>
+    <t xml:space="preserve">11.8847999572754</t>
   </si>
   <si>
     <t xml:space="preserve">12.0688562393188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1101751327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.207839012146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3843812942505</t>
+    <t xml:space="preserve">12.1101760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2078371047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3843822479248</t>
   </si>
   <si>
     <t xml:space="preserve">12.5120944976807</t>
@@ -3119,16 +3119,16 @@
     <t xml:space="preserve">11.8322114944458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8096752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6181049346924</t>
+    <t xml:space="preserve">11.8096742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6181039810181</t>
   </si>
   <si>
     <t xml:space="preserve">11.3326292037964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7645978927612</t>
+    <t xml:space="preserve">11.7645988464355</t>
   </si>
   <si>
     <t xml:space="preserve">11.5993232727051</t>
@@ -3143,76 +3143,76 @@
     <t xml:space="preserve">11.3626794815063</t>
   </si>
   <si>
-    <t xml:space="preserve">11.712010383606</t>
+    <t xml:space="preserve">11.7120113372803</t>
   </si>
   <si>
     <t xml:space="preserve">11.8772869110107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8359670639038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9524116516113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2003240585327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2904748916626</t>
+    <t xml:space="preserve">11.8359680175781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.952410697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.200325012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2904758453369</t>
   </si>
   <si>
     <t xml:space="preserve">12.1139316558838</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4031629562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.944899559021</t>
+    <t xml:space="preserve">12.4031620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9448986053467</t>
   </si>
   <si>
     <t xml:space="preserve">12.0989055633545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1514921188354</t>
+    <t xml:space="preserve">12.1514940261841</t>
   </si>
   <si>
     <t xml:space="preserve">12.0801248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7007427215576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5241985321045</t>
+    <t xml:space="preserve">11.7007436752319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5241994857788</t>
   </si>
   <si>
     <t xml:space="preserve">10.8255348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6452350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8893909454346</t>
+    <t xml:space="preserve">10.6452341079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8893918991089</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499914169312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.64439868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8209428787231</t>
+    <t xml:space="preserve">11.6443996429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8209419250488</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275363922119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8885555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5834636688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4332122802734</t>
+    <t xml:space="preserve">11.8885545730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5834617614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4332113265991</t>
   </si>
   <si>
     <t xml:space="preserve">12.4106750488281</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">13.1393890380859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2070007324219</t>
+    <t xml:space="preserve">13.2070016860962</t>
   </si>
   <si>
     <t xml:space="preserve">13.5600900650024</t>
@@ -3245,73 +3245,73 @@
     <t xml:space="preserve">13.3797903060913</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2746143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5375509262085</t>
+    <t xml:space="preserve">13.2746162414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5375528335571</t>
   </si>
   <si>
     <t xml:space="preserve">13.1882209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2896404266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2295408248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619272232056</t>
+    <t xml:space="preserve">13.2821264266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2896394729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2295398712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619253158569</t>
   </si>
   <si>
     <t xml:space="preserve">12.9327945709229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1731939315796</t>
+    <t xml:space="preserve">13.1731948852539</t>
   </si>
   <si>
     <t xml:space="preserve">13.1919765472412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1957340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0154342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.82386302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3272008895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361343383789</t>
+    <t xml:space="preserve">13.1957321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0154323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8238639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3272018432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361333847046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4962339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4323768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3497409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3384695053101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1994886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4135971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4248647689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.39857006073</t>
+    <t xml:space="preserve">13.4323759078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.349739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3384704589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1994895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4135961532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4248666763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3985710144043</t>
   </si>
   <si>
     <t xml:space="preserve">13.391058921814</t>
@@ -3320,61 +3320,61 @@
     <t xml:space="preserve">13.6802892684937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.209921836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9582538604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8305406570435</t>
+    <t xml:space="preserve">14.2099227905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9582529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8305397033691</t>
   </si>
   <si>
     <t xml:space="preserve">13.89439868927</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8380546569824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.931960105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7328786849976</t>
+    <t xml:space="preserve">13.8380527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9319591522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7328767776489</t>
   </si>
   <si>
     <t xml:space="preserve">13.4398899078369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4060831069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1093416213989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3009071350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.04172706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887208938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676021575928</t>
+    <t xml:space="preserve">13.4060821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3009080886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0417261123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887218475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676012039185</t>
   </si>
   <si>
     <t xml:space="preserve">13.7216081619263</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3526601791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5855503082275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0550813674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0926418304443</t>
+    <t xml:space="preserve">14.3526592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5855484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0550804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.092643737793</t>
   </si>
   <si>
     <t xml:space="preserve">15.0250291824341</t>
@@ -3383,13 +3383,13 @@
     <t xml:space="preserve">15.1978187561035</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8447303771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7207736968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9198551177979</t>
+    <t xml:space="preserve">14.8447284698486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7207717895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9198560714722</t>
   </si>
   <si>
     <t xml:space="preserve">14.8221921920776</t>
@@ -3401,22 +3401,22 @@
     <t xml:space="preserve">14.6005725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4315414428711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2812929153442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9499063491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7846298217773</t>
+    <t xml:space="preserve">14.4315404891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2812919616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9499053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7846307754517</t>
   </si>
   <si>
     <t xml:space="preserve">14.7095060348511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6644306182861</t>
+    <t xml:space="preserve">14.6644287109375</t>
   </si>
   <si>
     <t xml:space="preserve">14.4240303039551</t>
@@ -3425,70 +3425,70 @@
     <t xml:space="preserve">14.7958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7620916366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9123439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6606712341309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4090042114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1948986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1197719573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2024097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2775344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3226118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202709197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714399337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2925605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4653463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7470674514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5930595397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8898038864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8484859466553</t>
+    <t xml:space="preserve">14.7620906829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9123430252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6606740951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4090051651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1948976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1197738647461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.202410697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.277533531189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3226108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2925596237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4653482437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7470655441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5930614471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8898057937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8484869003296</t>
   </si>
   <si>
     <t xml:space="preserve">15.2504053115845</t>
   </si>
   <si>
-    <t xml:space="preserve">15.100154876709</t>
+    <t xml:space="preserve">15.1001558303833</t>
   </si>
   <si>
     <t xml:space="preserve">15.1151819229126</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0701055526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827917098999</t>
+    <t xml:space="preserve">15.0701065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827936172485</t>
   </si>
   <si>
     <t xml:space="preserve">14.7245292663574</t>
@@ -3497,10 +3497,10 @@
     <t xml:space="preserve">14.7508230209351</t>
   </si>
   <si>
-    <t xml:space="preserve">14.814679145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8184366226196</t>
+    <t xml:space="preserve">14.8146810531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.818434715271</t>
   </si>
   <si>
     <t xml:space="preserve">14.9837112426758</t>
@@ -3512,10 +3512,10 @@
     <t xml:space="preserve">14.792142868042</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9611740112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1602554321289</t>
+    <t xml:space="preserve">14.9611749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1602573394775</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724426269531</t>
@@ -3527,16 +3527,16 @@
     <t xml:space="preserve">15.1377182006836</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3555812835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2579183578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2804555892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2729434967041</t>
+    <t xml:space="preserve">15.355583190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2579193115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2804565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2729444503784</t>
   </si>
   <si>
     <t xml:space="preserve">15.7462310791016</t>
@@ -3545,22 +3545,22 @@
     <t xml:space="preserve">15.8664321899414</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8438949584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6410579681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6711072921753</t>
+    <t xml:space="preserve">15.8438968658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6410570144653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.708667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6711091995239</t>
   </si>
   <si>
     <t xml:space="preserve">16.1603355407715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0814266204834</t>
+    <t xml:space="preserve">16.081428527832</t>
   </si>
   <si>
     <t xml:space="preserve">15.8841571807861</t>
@@ -3569,10 +3569,10 @@
     <t xml:space="preserve">15.8999395370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.955174446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0419731140137</t>
+    <t xml:space="preserve">15.9551763534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0419750213623</t>
   </si>
   <si>
     <t xml:space="preserve">16.0025196075439</t>
@@ -3581,25 +3581,25 @@
     <t xml:space="preserve">16.0972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.144552230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4601860046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4522933959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.412841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3260402679443</t>
+    <t xml:space="preserve">16.1445560455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4601879119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4522953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4128398895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3260440826416</t>
   </si>
   <si>
     <t xml:space="preserve">16.3497142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9946298599243</t>
+    <t xml:space="preserve">15.99462890625</t>
   </si>
   <si>
     <t xml:space="preserve">16.1208820343018</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">16.0183010101318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9472827911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8762674331665</t>
+    <t xml:space="preserve">15.9472846984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8762683868408</t>
   </si>
   <si>
     <t xml:space="preserve">16.2392444610596</t>
@@ -3623,34 +3623,34 @@
     <t xml:space="preserve">16.2471351623535</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5312042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1287708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2155723571777</t>
+    <t xml:space="preserve">16.5312023162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1287746429443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2155704498291</t>
   </si>
   <si>
     <t xml:space="preserve">16.3023700714111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5943298339844</t>
+    <t xml:space="preserve">16.5943279266357</t>
   </si>
   <si>
     <t xml:space="preserve">16.5075302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4838581085205</t>
+    <t xml:space="preserve">16.4838562011719</t>
   </si>
   <si>
     <t xml:space="preserve">16.4444046020508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550239562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5233135223389</t>
+    <t xml:space="preserve">16.2550258636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5233154296875</t>
   </si>
   <si>
     <t xml:space="preserve">16.8073806762695</t>
@@ -3662,76 +3662,76 @@
     <t xml:space="preserve">17.5254421234131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3281726837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1940307617188</t>
+    <t xml:space="preserve">17.3281707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1940288543701</t>
   </si>
   <si>
     <t xml:space="preserve">17.2492656707764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1387939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4702053070068</t>
+    <t xml:space="preserve">17.1387920379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4702072143555</t>
   </si>
   <si>
     <t xml:space="preserve">17.4938793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2808265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4070796966553</t>
+    <t xml:space="preserve">17.2808284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4070816040039</t>
   </si>
   <si>
     <t xml:space="preserve">17.5727882385254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9041996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9120903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1093597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1172523498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2592868804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3224124908447</t>
+    <t xml:space="preserve">17.9042015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9120922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1093616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1172485351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2592849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3224105834961</t>
   </si>
   <si>
     <t xml:space="preserve">18.2435035705566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4644470214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2513942718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2829570770264</t>
+    <t xml:space="preserve">18.4644451141357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.251392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.282958984375</t>
   </si>
   <si>
     <t xml:space="preserve">18.424991607666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3539772033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4407749176025</t>
+    <t xml:space="preserve">18.3539752960205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4407730102539</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906982421875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.669605255127</t>
+    <t xml:space="preserve">18.6696090698242</t>
   </si>
   <si>
     <t xml:space="preserve">18.748514175415</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">18.7642974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8037509918213</t>
+    <t xml:space="preserve">18.8037490844727</t>
   </si>
   <si>
     <t xml:space="preserve">18.7011699676514</t>
@@ -3752,7 +3752,7 @@
     <t xml:space="preserve">18.7406234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6459350585938</t>
+    <t xml:space="preserve">18.6459331512451</t>
   </si>
   <si>
     <t xml:space="preserve">18.7169513702393</t>
@@ -3764,13 +3764,13 @@
     <t xml:space="preserve">18.843204498291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8984394073486</t>
+    <t xml:space="preserve">18.8984413146973</t>
   </si>
   <si>
     <t xml:space="preserve">18.9536743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1903972625732</t>
+    <t xml:space="preserve">19.1903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">19.0878200531006</t>
@@ -3788,7 +3788,7 @@
     <t xml:space="preserve">19.2614154815674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1430549621582</t>
+    <t xml:space="preserve">19.1430530548096</t>
   </si>
   <si>
     <t xml:space="preserve">18.7327327728271</t>
@@ -3797,22 +3797,22 @@
     <t xml:space="preserve">18.5985889434814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6538238525391</t>
+    <t xml:space="preserve">18.7721881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6538257598877</t>
   </si>
   <si>
     <t xml:space="preserve">18.4013195037842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6222629547119</t>
+    <t xml:space="preserve">18.6222610473633</t>
   </si>
   <si>
     <t xml:space="preserve">18.2356128692627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1409225463867</t>
+    <t xml:space="preserve">18.1409244537354</t>
   </si>
   <si>
     <t xml:space="preserve">18.43288230896</t>
@@ -3821,37 +3821,37 @@
     <t xml:space="preserve">18.6380443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8353118896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7090587615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5375919342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4034519195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5297050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6007194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8374443054199</t>
+    <t xml:space="preserve">18.8353137969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7090606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5375938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.403450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5297031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6007213592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8374423980713</t>
   </si>
   <si>
     <t xml:space="preserve">19.6322822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6954097747803</t>
+    <t xml:space="preserve">19.6954078674316</t>
   </si>
   <si>
     <t xml:space="preserve">19.640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9952602386475</t>
+    <t xml:space="preserve">19.9952583312988</t>
   </si>
   <si>
     <t xml:space="preserve">20.066276550293</t>
@@ -3860,16 +3860,16 @@
     <t xml:space="preserve">20.1057300567627</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0504932403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0741691589355</t>
+    <t xml:space="preserve">20.0504951477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0741672515869</t>
   </si>
   <si>
     <t xml:space="preserve">20.0189323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2398738861084</t>
+    <t xml:space="preserve">20.239875793457</t>
   </si>
   <si>
     <t xml:space="preserve">20.9027004241943</t>
@@ -3884,7 +3884,7 @@
     <t xml:space="preserve">20.9421539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9816093444824</t>
+    <t xml:space="preserve">20.9816074371338</t>
   </si>
   <si>
     <t xml:space="preserve">20.6659774780273</t>
@@ -3896,7 +3896,7 @@
     <t xml:space="preserve">20.1372947692871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0820560455322</t>
+    <t xml:space="preserve">20.0820579528809</t>
   </si>
   <si>
     <t xml:space="preserve">19.1035995483398</t>
@@ -3905,31 +3905,31 @@
     <t xml:space="preserve">19.316650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3324356079102</t>
+    <t xml:space="preserve">19.3324317932129</t>
   </si>
   <si>
     <t xml:space="preserve">19.4744682312012</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3087615966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1746158599854</t>
+    <t xml:space="preserve">19.3087596893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.174617767334</t>
   </si>
   <si>
     <t xml:space="preserve">19.2377433776855</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2850875854492</t>
+    <t xml:space="preserve">19.2850894927979</t>
   </si>
   <si>
     <t xml:space="preserve">19.1272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.024694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8116397857666</t>
+    <t xml:space="preserve">19.0246925354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8116416931152</t>
   </si>
   <si>
     <t xml:space="preserve">19.0168018341064</t>
@@ -3944,10 +3944,10 @@
     <t xml:space="preserve">19.16672706604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3561038970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.411340713501</t>
+    <t xml:space="preserve">19.3561058044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4113426208496</t>
   </si>
   <si>
     <t xml:space="preserve">19.7269725799561</t>
@@ -3971,49 +3971,49 @@
     <t xml:space="preserve">20.0268211364746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8711376190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9342632293701</t>
+    <t xml:space="preserve">20.8711395263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9342651367188</t>
   </si>
   <si>
     <t xml:space="preserve">20.5791778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6817569732666</t>
+    <t xml:space="preserve">20.6817588806152</t>
   </si>
   <si>
     <t xml:space="preserve">20.3187808990479</t>
   </si>
   <si>
-    <t xml:space="preserve">19.884786605835</t>
+    <t xml:space="preserve">19.8847885131836</t>
   </si>
   <si>
     <t xml:space="preserve">18.2119407653809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2671737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3934268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0325813293457</t>
+    <t xml:space="preserve">18.2671756744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3934288024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.032585144043</t>
   </si>
   <si>
     <t xml:space="preserve">18.8747673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">18.33030128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7958583831787</t>
+    <t xml:space="preserve">18.3303031921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7958602905273</t>
   </si>
   <si>
     <t xml:space="preserve">18.3697566986084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3145217895508</t>
+    <t xml:space="preserve">18.3145198822021</t>
   </si>
   <si>
     <t xml:space="preserve">17.8095111846924</t>
@@ -4022,16 +4022,16 @@
     <t xml:space="preserve">17.7463836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9278717041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.641674041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1782455444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8862895965576</t>
+    <t xml:space="preserve">17.9278697967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416759490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1782474517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.886287689209</t>
   </si>
   <si>
     <t xml:space="preserve">16.6337833404541</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">15.4501657485962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.663215637207</t>
+    <t xml:space="preserve">15.6632165908813</t>
   </si>
   <si>
     <t xml:space="preserve">17.0756664276123</t>
@@ -4058,37 +4058,37 @@
     <t xml:space="preserve">15.8525953292847</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0441055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7915992736816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4759674072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8152694702148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7837085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4286212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7442531585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2413749694824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9415245056152</t>
+    <t xml:space="preserve">17.0441036224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.791597366333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4759654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8152713775635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7837066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4286231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.744255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2413730621338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9415225982666</t>
   </si>
   <si>
     <t xml:space="preserve">16.6732349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7600364685059</t>
+    <t xml:space="preserve">16.7600345611572</t>
   </si>
   <si>
     <t xml:space="preserve">16.3181533813477</t>
@@ -4097,16 +4097,16 @@
     <t xml:space="preserve">15.7579050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4107122421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815771102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9157209396362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8920478820801</t>
+    <t xml:space="preserve">15.4107103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815761566162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9157199859619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8920488357544</t>
   </si>
   <si>
     <t xml:space="preserve">15.8683776855469</t>
@@ -4115,25 +4115,25 @@
     <t xml:space="preserve">15.6277074813843</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7973604202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8289222717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.089319229126</t>
+    <t xml:space="preserve">15.7973585128784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539587020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8289232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0893173217773</t>
   </si>
   <si>
     <t xml:space="preserve">16.0735378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.176118850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9236125946045</t>
+    <t xml:space="preserve">16.1761169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9236135482788</t>
   </si>
   <si>
     <t xml:space="preserve">15.6395444869995</t>
@@ -4142,10 +4142,10 @@
     <t xml:space="preserve">15.5132913589478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9964437484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1660957336426</t>
+    <t xml:space="preserve">14.9964427947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1660966873169</t>
   </si>
   <si>
     <t xml:space="preserve">15.6868877410889</t>
@@ -4154,10 +4154,10 @@
     <t xml:space="preserve">15.7381782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7657947540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0261917114258</t>
+    <t xml:space="preserve">15.7657976150513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0261936187744</t>
   </si>
   <si>
     <t xml:space="preserve">15.8052501678467</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">16.7703304290771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305305480957</t>
+    <t xml:space="preserve">16.9305286407471</t>
   </si>
   <si>
     <t xml:space="preserve">16.8209209442139</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">14.4390106201172</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6287212371826</t>
+    <t xml:space="preserve">14.6287202835083</t>
   </si>
   <si>
     <t xml:space="preserve">14.9828443527222</t>
@@ -4223,28 +4223,28 @@
     <t xml:space="preserve">14.3715581893921</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4432249069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5064630508423</t>
+    <t xml:space="preserve">14.4432239532471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.506462097168</t>
   </si>
   <si>
     <t xml:space="preserve">14.2197895050049</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6750926971436</t>
+    <t xml:space="preserve">14.6750936508179</t>
   </si>
   <si>
     <t xml:space="preserve">14.5191087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4811658859253</t>
+    <t xml:space="preserve">14.4811668395996</t>
   </si>
   <si>
     <t xml:space="preserve">14.2745952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9837064743042</t>
+    <t xml:space="preserve">13.9837055206299</t>
   </si>
   <si>
     <t xml:space="preserve">13.8277225494385</t>
@@ -4259,10 +4259,10 @@
     <t xml:space="preserve">13.7771339416504</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1523370742798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3420486450195</t>
+    <t xml:space="preserve">14.1523380279541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3420476913452</t>
   </si>
   <si>
     <t xml:space="preserve">14.1354742050171</t>
@@ -4274,25 +4274,25 @@
     <t xml:space="preserve">14.1987113952637</t>
   </si>
   <si>
-    <t xml:space="preserve">13.621150970459</t>
+    <t xml:space="preserve">13.6211519241333</t>
   </si>
   <si>
     <t xml:space="preserve">13.6801719665527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8108606338501</t>
+    <t xml:space="preserve">13.8108596801758</t>
   </si>
   <si>
     <t xml:space="preserve">14.2493000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6928186416626</t>
+    <t xml:space="preserve">13.6928195953369</t>
   </si>
   <si>
     <t xml:space="preserve">13.7602710723877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7939977645874</t>
+    <t xml:space="preserve">13.7939987182617</t>
   </si>
   <si>
     <t xml:space="preserve">13.4609518051147</t>
@@ -4313,7 +4313,7 @@
     <t xml:space="preserve">14.4727363586426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5739145278931</t>
+    <t xml:space="preserve">14.5739154815674</t>
   </si>
   <si>
     <t xml:space="preserve">14.2577314376831</t>
@@ -4328,13 +4328,13 @@
     <t xml:space="preserve">14.4600887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5022459030151</t>
+    <t xml:space="preserve">14.5022468566895</t>
   </si>
   <si>
     <t xml:space="preserve">14.5654830932617</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6371517181396</t>
+    <t xml:space="preserve">14.6371507644653</t>
   </si>
   <si>
     <t xml:space="preserve">14.3757734298706</t>
@@ -4343,7 +4343,7 @@
     <t xml:space="preserve">14.4643068313599</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9794902801514</t>
+    <t xml:space="preserve">13.9794912338257</t>
   </si>
   <si>
     <t xml:space="preserve">13.7687034606934</t>
@@ -4352,10 +4352,10 @@
     <t xml:space="preserve">13.9541959762573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9415493011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8530187606812</t>
+    <t xml:space="preserve">13.9415502548218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8530178070068</t>
   </si>
   <si>
     <t xml:space="preserve">13.4651679992676</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">13.6380138397217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4356575012207</t>
+    <t xml:space="preserve">13.435658454895</t>
   </si>
   <si>
     <t xml:space="preserve">13.1447687149048</t>
@@ -4382,10 +4382,10 @@
     <t xml:space="preserve">13.4946775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5199718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1692018508911</t>
+    <t xml:space="preserve">13.5199728012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1692008972168</t>
   </si>
   <si>
     <t xml:space="preserve">14.0806703567505</t>
@@ -4397,16 +4397,16 @@
     <t xml:space="preserve">13.9162540435791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7644882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8572330474854</t>
+    <t xml:space="preserve">13.7644872665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8572340011597</t>
   </si>
   <si>
     <t xml:space="preserve">13.4735994338989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1321210861206</t>
+    <t xml:space="preserve">13.1321220397949</t>
   </si>
   <si>
     <t xml:space="preserve">12.7484865188599</t>
@@ -4415,7 +4415,7 @@
     <t xml:space="preserve">12.7527027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5334825515747</t>
+    <t xml:space="preserve">12.5334815979004</t>
   </si>
   <si>
     <t xml:space="preserve">12.4112253189087</t>
@@ -4424,13 +4424,13 @@
     <t xml:space="preserve">12.0065107345581</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3985767364502</t>
+    <t xml:space="preserve">12.3985776901245</t>
   </si>
   <si>
     <t xml:space="preserve">12.6009340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1532001495361</t>
+    <t xml:space="preserve">13.1532011032104</t>
   </si>
   <si>
     <t xml:space="preserve">12.9044704437256</t>
@@ -4439,7 +4439,7 @@
     <t xml:space="preserve">12.7231922149658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5039720535278</t>
+    <t xml:space="preserve">12.5039710998535</t>
   </si>
   <si>
     <t xml:space="preserve">12.5503454208374</t>
@@ -4457,13 +4457,13 @@
     <t xml:space="preserve">12.5292663574219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7948598861694</t>
+    <t xml:space="preserve">12.7948608398438</t>
   </si>
   <si>
     <t xml:space="preserve">12.8791751861572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8665285110474</t>
+    <t xml:space="preserve">12.8665294647217</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538808822632</t>
@@ -4475,13 +4475,13 @@
     <t xml:space="preserve">13.3007526397705</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6843862533569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.532618522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7897815704346</t>
+    <t xml:space="preserve">13.6843872070312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5326194763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7897806167603</t>
   </si>
   <si>
     <t xml:space="preserve">13.743408203125</t>
@@ -4502,13 +4502,13 @@
     <t xml:space="preserve">14.9449024200439</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0292186737061</t>
+    <t xml:space="preserve">15.0292177200317</t>
   </si>
   <si>
     <t xml:space="preserve">16.1885547637939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8588619232178</t>
+    <t xml:space="preserve">16.8588638305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.6860160827637</t>
@@ -4523,10 +4523,10 @@
     <t xml:space="preserve">16.799840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3740482330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4415016174316</t>
+    <t xml:space="preserve">16.3740501403809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.441499710083</t>
   </si>
   <si>
     <t xml:space="preserve">16.4035587310791</t>
@@ -4550,13 +4550,13 @@
     <t xml:space="preserve">16.6059150695801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5047378540039</t>
+    <t xml:space="preserve">16.5047359466553</t>
   </si>
   <si>
     <t xml:space="preserve">16.5089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155246734619</t>
+    <t xml:space="preserve">16.7155265808105</t>
   </si>
   <si>
     <t xml:space="preserve">16.9389610290527</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">16.7618980407715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0570049285889</t>
+    <t xml:space="preserve">17.0570030212402</t>
   </si>
   <si>
     <t xml:space="preserve">16.9558258056641</t>
@@ -4574,10 +4574,10 @@
     <t xml:space="preserve">16.2855167388916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2677898406982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2593612670898</t>
+    <t xml:space="preserve">17.2677917480469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2593593597412</t>
   </si>
   <si>
     <t xml:space="preserve">17.2340660095215</t>
@@ -4589,10 +4589,10 @@
     <t xml:space="preserve">17.3774013519287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4617156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6893692016602</t>
+    <t xml:space="preserve">17.4617176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6893672943115</t>
   </si>
   <si>
     <t xml:space="preserve">17.7146644592285</t>
@@ -4601,7 +4601,7 @@
     <t xml:space="preserve">17.8579998016357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6472129821777</t>
+    <t xml:space="preserve">17.6472110748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.8664302825928</t>
@@ -4613,13 +4613,13 @@
     <t xml:space="preserve">18.2542819976807</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9760417938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9676074981689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3807525634766</t>
+    <t xml:space="preserve">17.9760398864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9676094055176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3807544708252</t>
   </si>
   <si>
     <t xml:space="preserve">18.3891868591309</t>
@@ -4628,7 +4628,7 @@
     <t xml:space="preserve">18.8697834014893</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9035091400146</t>
+    <t xml:space="preserve">18.9035110473633</t>
   </si>
   <si>
     <t xml:space="preserve">18.9625301361084</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">19.1648864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8444900512695</t>
+    <t xml:space="preserve">18.8444881439209</t>
   </si>
   <si>
     <t xml:space="preserve">19.2239074707031</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">19.3841075897217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4431266784668</t>
+    <t xml:space="preserve">19.4431285858154</t>
   </si>
   <si>
     <t xml:space="preserve">19.3250885009766</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">19.5358753204346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0637111663818</t>
+    <t xml:space="preserve">19.0637092590332</t>
   </si>
   <si>
     <t xml:space="preserve">19.0890026092529</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">19.2070465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0552768707275</t>
+    <t xml:space="preserve">19.0552787780762</t>
   </si>
   <si>
     <t xml:space="preserve">18.9878253936768</t>
@@ -4715,7 +4715,7 @@
     <t xml:space="preserve">18.6168365478516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9456653594971</t>
+    <t xml:space="preserve">18.9456672668457</t>
   </si>
   <si>
     <t xml:space="preserve">18.9793949127197</t>
@@ -4724,7 +4724,7 @@
     <t xml:space="preserve">19.1058673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8950786590576</t>
+    <t xml:space="preserve">18.895076751709</t>
   </si>
   <si>
     <t xml:space="preserve">18.8023319244385</t>
@@ -4742,10 +4742,10 @@
     <t xml:space="preserve">16.9811191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2391452789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114936828613</t>
+    <t xml:space="preserve">16.239143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114917755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.4667949676514</t>
@@ -4757,10 +4757,10 @@
     <t xml:space="preserve">16.3782634735107</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1126708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1337509155273</t>
+    <t xml:space="preserve">16.1126728057861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1337490081787</t>
   </si>
   <si>
     <t xml:space="preserve">16.3487529754639</t>
@@ -4775,13 +4775,13 @@
     <t xml:space="preserve">16.546895980835</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3403224945068</t>
+    <t xml:space="preserve">16.3403205871582</t>
   </si>
   <si>
     <t xml:space="preserve">16.521598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.711311340332</t>
+    <t xml:space="preserve">16.7113094329834</t>
   </si>
   <si>
     <t xml:space="preserve">17.158182144165</t>
@@ -4802,13 +4802,13 @@
     <t xml:space="preserve">17.107593536377</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0148468017578</t>
+    <t xml:space="preserve">17.0148448944092</t>
   </si>
   <si>
     <t xml:space="preserve">17.0401401519775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0654335021973</t>
+    <t xml:space="preserve">17.0654354095459</t>
   </si>
   <si>
     <t xml:space="preserve">16.8124885559082</t>
@@ -4817,10 +4817,10 @@
     <t xml:space="preserve">16.5806217193604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9726886749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0822982788086</t>
+    <t xml:space="preserve">16.9726867675781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.08229637146</t>
   </si>
   <si>
     <t xml:space="preserve">16.8546466827393</t>
@@ -4832,10 +4832,10 @@
     <t xml:space="preserve">17.0738658905029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8504314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2509269714355</t>
+    <t xml:space="preserve">16.8504295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2509288787842</t>
   </si>
   <si>
     <t xml:space="preserve">17.4084911346436</t>
@@ -4844,10 +4844,10 @@
     <t xml:space="preserve">17.3769779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0168323516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8097496032715</t>
+    <t xml:space="preserve">17.0168342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8097515106201</t>
   </si>
   <si>
     <t xml:space="preserve">17.2014083862305</t>
@@ -4856,28 +4856,28 @@
     <t xml:space="preserve">17.1743984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0753593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7242164611816</t>
+    <t xml:space="preserve">17.0753574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7242183685303</t>
   </si>
   <si>
     <t xml:space="preserve">17.0213356018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.412992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4580097198486</t>
+    <t xml:space="preserve">17.4129943847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4580116271973</t>
   </si>
   <si>
     <t xml:space="preserve">17.647087097168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6425838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721771240234</t>
+    <t xml:space="preserve">17.6425857543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721790313721</t>
   </si>
   <si>
     <t xml:space="preserve">17.6020679473877</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">18.0162353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8496685028076</t>
+    <t xml:space="preserve">17.8496704101562</t>
   </si>
   <si>
     <t xml:space="preserve">17.8136539459229</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">17.4715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5750598907471</t>
+    <t xml:space="preserve">17.5750579833984</t>
   </si>
   <si>
     <t xml:space="preserve">17.786642074585</t>
@@ -4949,7 +4949,7 @@
     <t xml:space="preserve">17.8541698455811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9667167663574</t>
+    <t xml:space="preserve">17.9667148590088</t>
   </si>
   <si>
     <t xml:space="preserve">17.9036903381348</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">18.1602935791016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2863426208496</t>
+    <t xml:space="preserve">18.2863445281982</t>
   </si>
   <si>
     <t xml:space="preserve">18.2323226928711</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">18.2413272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1783027648926</t>
+    <t xml:space="preserve">18.1783008575439</t>
   </si>
   <si>
     <t xml:space="preserve">18.2683372497559</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">19.0066337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6284828186035</t>
+    <t xml:space="preserve">18.6284809112549</t>
   </si>
   <si>
     <t xml:space="preserve">18.6014709472656</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">18.6104755401611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7005100250244</t>
+    <t xml:space="preserve">18.700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">18.7365245819092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8895854949951</t>
+    <t xml:space="preserve">18.8895874023438</t>
   </si>
   <si>
     <t xml:space="preserve">18.7545318603516</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">18.8715782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5924682617188</t>
+    <t xml:space="preserve">18.5924663543701</t>
   </si>
   <si>
     <t xml:space="preserve">18.3403663635254</t>
@@ -5033,10 +5033,10 @@
     <t xml:space="preserve">18.5114345550537</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0426483154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1326847076416</t>
+    <t xml:space="preserve">19.0426464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.132682800293</t>
   </si>
   <si>
     <t xml:space="preserve">19.2497310638428</t>
@@ -5048,16 +5048,16 @@
     <t xml:space="preserve">19.1867046356201</t>
   </si>
   <si>
-    <t xml:space="preserve">19.08766746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9346046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9706172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0516529083252</t>
+    <t xml:space="preserve">19.0876655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.934606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9706192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0516510009766</t>
   </si>
   <si>
     <t xml:space="preserve">19.0246410369873</t>
@@ -5072,31 +5072,31 @@
     <t xml:space="preserve">19.1957092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8625774383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7905464172363</t>
+    <t xml:space="preserve">18.8625755310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.790548324585</t>
   </si>
   <si>
     <t xml:space="preserve">18.7815437316895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.853572845459</t>
+    <t xml:space="preserve">18.8535709381104</t>
   </si>
   <si>
     <t xml:space="preserve">18.619478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">18.259334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493671417236</t>
+    <t xml:space="preserve">18.2593326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3493690490723</t>
   </si>
   <si>
     <t xml:space="preserve">18.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3313617706299</t>
+    <t xml:space="preserve">18.3313636779785</t>
   </si>
   <si>
     <t xml:space="preserve">18.0702571868896</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">17.4670143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4805202484131</t>
+    <t xml:space="preserve">17.4805221557617</t>
   </si>
   <si>
     <t xml:space="preserve">17.6200752258301</t>
@@ -5126,13 +5126,13 @@
     <t xml:space="preserve">17.8991870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8901844024658</t>
+    <t xml:space="preserve">17.8901863098145</t>
   </si>
   <si>
     <t xml:space="preserve">18.1422863006592</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4304008483887</t>
+    <t xml:space="preserve">18.4304027557373</t>
   </si>
   <si>
     <t xml:space="preserve">18.4213981628418</t>
@@ -5147,10 +5147,10 @@
     <t xml:space="preserve">18.7725391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2047119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4388065338135</t>
+    <t xml:space="preserve">19.2047138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4388084411621</t>
   </si>
   <si>
     <t xml:space="preserve">19.6278820037842</t>
@@ -5162,19 +5162,19 @@
     <t xml:space="preserve">20.0510520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9069938659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8439693450928</t>
+    <t xml:space="preserve">19.9069957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8439712524414</t>
   </si>
   <si>
     <t xml:space="preserve">19.7899475097656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8979911804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.807954788208</t>
+    <t xml:space="preserve">19.8979930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8079566955566</t>
   </si>
   <si>
     <t xml:space="preserve">19.6729011535645</t>
@@ -5183,7 +5183,7 @@
     <t xml:space="preserve">19.9520130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0960693359375</t>
+    <t xml:space="preserve">20.0960712432861</t>
   </si>
   <si>
     <t xml:space="preserve">20.0690612792969</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">20.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5372467041016</t>
+    <t xml:space="preserve">20.5372486114502</t>
   </si>
   <si>
     <t xml:space="preserve">20.996431350708</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">21.2215213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2755451202393</t>
+    <t xml:space="preserve">21.2755432128906</t>
   </si>
   <si>
     <t xml:space="preserve">21.2935523986816</t>
@@ -5237,22 +5237,22 @@
     <t xml:space="preserve">21.7887516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9598197937012</t>
+    <t xml:space="preserve">21.9598178863525</t>
   </si>
   <si>
     <t xml:space="preserve">22.3199634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6717052459717</t>
+    <t xml:space="preserve">21.671703338623</t>
   </si>
   <si>
     <t xml:space="preserve">22.0948734283447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.265941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4190044403076</t>
+    <t xml:space="preserve">22.2659435272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.419002532959</t>
   </si>
   <si>
     <t xml:space="preserve">22.5090389251709</t>
@@ -5261,10 +5261,10 @@
     <t xml:space="preserve">22.5900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5630626678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9051990509033</t>
+    <t xml:space="preserve">22.563060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.905200958252</t>
   </si>
   <si>
     <t xml:space="preserve">22.797155380249</t>
@@ -5273,7 +5273,7 @@
     <t xml:space="preserve">23.0762672424316</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0222473144531</t>
+    <t xml:space="preserve">23.0222454071045</t>
   </si>
   <si>
     <t xml:space="preserve">23.3103618621826</t>
@@ -5288,10 +5288,10 @@
     <t xml:space="preserve">23.3193645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2293300628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4003963470459</t>
+    <t xml:space="preserve">23.2293281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4003982543945</t>
   </si>
   <si>
     <t xml:space="preserve">23.2563400268555</t>
@@ -5300,7 +5300,7 @@
     <t xml:space="preserve">23.6705074310303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5894737243652</t>
+    <t xml:space="preserve">23.5894756317139</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264472961426</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">23.8865947723389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.706521987915</t>
+    <t xml:space="preserve">23.7065200805664</t>
   </si>
   <si>
     <t xml:space="preserve">23.6975173950195</t>
@@ -5360,7 +5360,7 @@
     <t xml:space="preserve">21.6987152099609</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9148025512695</t>
+    <t xml:space="preserve">21.9148006439209</t>
   </si>
   <si>
     <t xml:space="preserve">22.5720653533936</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">22.3559799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3109607696533</t>
+    <t xml:space="preserve">22.310962677002</t>
   </si>
   <si>
     <t xml:space="preserve">22.1218852996826</t>
@@ -5384,19 +5384,19 @@
     <t xml:space="preserve">22.4550189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3289680480957</t>
+    <t xml:space="preserve">22.3289661407471</t>
   </si>
   <si>
     <t xml:space="preserve">22.6260871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6711044311523</t>
+    <t xml:space="preserve">22.671106338501</t>
   </si>
   <si>
     <t xml:space="preserve">21.608678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7977523803711</t>
+    <t xml:space="preserve">21.7977542877197</t>
   </si>
   <si>
     <t xml:space="preserve">21.968822479248</t>
@@ -5414,22 +5414,22 @@
     <t xml:space="preserve">21.5996742248535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7257251739502</t>
+    <t xml:space="preserve">21.7257232666016</t>
   </si>
   <si>
     <t xml:space="preserve">21.7527370452881</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6176815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8427715301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2749462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1038780212402</t>
+    <t xml:space="preserve">21.6176834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2749443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">22.1578998565674</t>
@@ -5438,16 +5438,16 @@
     <t xml:space="preserve">22.2839488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3019561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2569370269775</t>
+    <t xml:space="preserve">22.3019580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2569389343262</t>
   </si>
   <si>
     <t xml:space="preserve">22.7341289520264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.950216293335</t>
+    <t xml:space="preserve">22.9502182006836</t>
   </si>
   <si>
     <t xml:space="preserve">23.1843109130859</t>
@@ -5459,13 +5459,13 @@
     <t xml:space="preserve">23.0672645568848</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4364147186279</t>
+    <t xml:space="preserve">23.4364128112793</t>
   </si>
   <si>
     <t xml:space="preserve">23.5084419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.84157371521</t>
+    <t xml:space="preserve">23.8415756225586</t>
   </si>
   <si>
     <t xml:space="preserve">23.5945644378662</t>
@@ -6351,6 +6351,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.2200012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.5499992370605</t>
   </si>
 </sst>
 </file>
@@ -71325,7 +71328,7 @@
     </row>
     <row r="2487">
       <c r="A2487" s="1" t="n">
-        <v>45940.6500810185</v>
+        <v>45940.2916666667</v>
       </c>
       <c r="B2487" t="n">
         <v>727986</v>
@@ -71346,6 +71349,32 @@
         <v>2112</v>
       </c>
       <c r="H2487" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2488">
+      <c r="A2488" s="1" t="n">
+        <v>45943.6494328704</v>
+      </c>
+      <c r="B2488" t="n">
+        <v>404769</v>
+      </c>
+      <c r="C2488" t="n">
+        <v>32.7599983215332</v>
+      </c>
+      <c r="D2488" t="n">
+        <v>32.2799987792969</v>
+      </c>
+      <c r="E2488" t="n">
+        <v>32.2799987792969</v>
+      </c>
+      <c r="F2488" t="n">
+        <v>32.5499992370605</v>
+      </c>
+      <c r="G2488" t="s">
+        <v>2113</v>
+      </c>
+      <c r="H2488" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2114" uniqueCount="2114">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="2115">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,55 +44,55 @@
     <t xml:space="preserve">AZM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068347930908</t>
+    <t xml:space="preserve">10.7068357467651</t>
   </si>
   <si>
     <t xml:space="preserve">10.4860258102417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.191611289978</t>
+    <t xml:space="preserve">10.1916131973267</t>
   </si>
   <si>
     <t xml:space="preserve">9.91191959381104</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93645286560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2259607315063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.000244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.617506980896</t>
+    <t xml:space="preserve">9.9364538192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.225959777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0002431869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61750507354736</t>
   </si>
   <si>
     <t xml:space="preserve">9.33290481567383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15135097503662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37706851959229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85693740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25930118560791</t>
+    <t xml:space="preserve">9.1513500213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37706756591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85693836212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25930309295654</t>
   </si>
   <si>
     <t xml:space="preserve">9.53899478912354</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4899263381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50955486297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40160179138184</t>
+    <t xml:space="preserve">9.48992729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50955295562744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40160274505615</t>
   </si>
   <si>
     <t xml:space="preserve">9.12681770324707</t>
@@ -104,61 +104,61 @@
     <t xml:space="preserve">9.43595123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84712314605713</t>
+    <t xml:space="preserve">8.84712409973145</t>
   </si>
   <si>
     <t xml:space="preserve">8.99433135986328</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79805469512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05711364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86574649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32699394226074</t>
+    <t xml:space="preserve">8.79805564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05711460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86574459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32699298858643</t>
   </si>
   <si>
     <t xml:space="preserve">7.61058759689331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67928504943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10127639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8706521987915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53798961639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78333473205566</t>
+    <t xml:space="preserve">7.67928314208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10127735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87065315246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53799057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78333568572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.46929359436035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61649894714355</t>
+    <t xml:space="preserve">8.61650085449219</t>
   </si>
   <si>
     <t xml:space="preserve">8.50364112854004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21413516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69010257720947</t>
+    <t xml:space="preserve">8.21413612365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69010353088379</t>
   </si>
   <si>
     <t xml:space="preserve">8.71954441070557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29365253448486</t>
+    <t xml:space="preserve">9.29365158081055</t>
   </si>
   <si>
     <t xml:space="preserve">9.30837154388428</t>
@@ -167,28 +167,28 @@
     <t xml:space="preserve">9.47520637512207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09737491607666</t>
+    <t xml:space="preserve">9.09737682342529</t>
   </si>
   <si>
     <t xml:space="preserve">9.22004795074463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41141510009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4801139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77943325042725</t>
+    <t xml:space="preserve">9.41141700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48011302947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77943229675293</t>
   </si>
   <si>
     <t xml:space="preserve">9.6616678237915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79415512084961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77452564239502</t>
+    <t xml:space="preserve">9.79415416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77452659606934</t>
   </si>
   <si>
     <t xml:space="preserve">9.68620204925537</t>
@@ -197,19 +197,19 @@
     <t xml:space="preserve">9.64694786071777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72545623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2357740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3044700622559</t>
+    <t xml:space="preserve">9.7254581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2357749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3044691085815</t>
   </si>
   <si>
     <t xml:space="preserve">9.83831596374512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56843757629395</t>
+    <t xml:space="preserve">9.56843566894531</t>
   </si>
   <si>
     <t xml:space="preserve">9.98552227020264</t>
@@ -218,166 +218,166 @@
     <t xml:space="preserve">9.93154525756836</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74508380889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3780727386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449075698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4369554519653</t>
+    <t xml:space="preserve">9.74508476257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3780736923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4369564056396</t>
   </si>
   <si>
     <t xml:space="preserve">10.5547218322754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5056524276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5498151779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5007467269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5694417953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4173288345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4811191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7411832809448</t>
+    <t xml:space="preserve">10.5056533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5498142242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5007457733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5694408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4811182022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7411842346191</t>
   </si>
   <si>
     <t xml:space="preserve">10.8442277908325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.785346031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5988855361938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406806945801</t>
+    <t xml:space="preserve">10.7853450775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5988836288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406797409058</t>
   </si>
   <si>
     <t xml:space="preserve">10.2897500991821</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73036289215088</t>
+    <t xml:space="preserve">9.7303638458252</t>
   </si>
   <si>
     <t xml:space="preserve">9.57334327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43104362487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40650939941406</t>
+    <t xml:space="preserve">9.43104457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40650844573975</t>
   </si>
   <si>
     <t xml:space="preserve">9.19060611724854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08265495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3525333404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47029781341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27893161773682</t>
+    <t xml:space="preserve">9.08265590667725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35253238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47029876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27892971038818</t>
   </si>
   <si>
     <t xml:space="preserve">9.30346488952637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14644432067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52970218658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79665374755859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89235496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95279598236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84702205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76643371582031</t>
+    <t xml:space="preserve">9.14644336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52970314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79665470123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.119010925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89235401153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95279693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84702301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.766432762146</t>
   </si>
   <si>
     <t xml:space="preserve">9.42896461486816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42392826080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52466583251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54984855651855</t>
+    <t xml:space="preserve">9.42392730712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52466487884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54984951019287</t>
   </si>
   <si>
     <t xml:space="preserve">9.39370632171631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82958126068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4820384979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28560161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46189212799072</t>
+    <t xml:space="preserve">8.82958030700684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48203945159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28560256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46189117431641</t>
   </si>
   <si>
     <t xml:space="preserve">8.53744506835938</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68351173400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39874362945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5045166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81680107116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692943572998</t>
+    <t xml:space="preserve">8.68351268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39874267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50451850891113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81680011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692848205566</t>
   </si>
   <si>
     <t xml:space="preserve">7.46459722518921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57540798187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49985504150391</t>
+    <t xml:space="preserve">7.57540655136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49985551834106</t>
   </si>
   <si>
     <t xml:space="preserve">7.3487491607666</t>
@@ -386,154 +386,154 @@
     <t xml:space="preserve">7.43941259384155</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2026801109314</t>
+    <t xml:space="preserve">7.20268106460571</t>
   </si>
   <si>
     <t xml:space="preserve">6.87025022506714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50256109237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62848138809204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86017560958862</t>
+    <t xml:space="preserve">6.50256061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62848281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86017656326294</t>
   </si>
   <si>
     <t xml:space="preserve">7.02135419845581</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38904571533203</t>
+    <t xml:space="preserve">7.38904476165771</t>
   </si>
   <si>
     <t xml:space="preserve">7.20771884918213</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44948577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66607141494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5250391960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64592409133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79702997207642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71140241622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94309568405151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8171763420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94813203811646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08179807662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92565441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71410894393921</t>
+    <t xml:space="preserve">7.44948720932007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66607189178467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52503871917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64592313766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79702854156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71140193939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94309616088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81717538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94813299179077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08179664611816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92565584182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71410799026489</t>
   </si>
   <si>
     <t xml:space="preserve">6.78966045379639</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90047073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22786521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27823495864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32860326766968</t>
+    <t xml:space="preserve">6.90047025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22786569595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27823352813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32860422134399</t>
   </si>
   <si>
     <t xml:space="preserve">7.31852865219116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39911794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15735006332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94580268859863</t>
+    <t xml:space="preserve">7.39911842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15734910964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94580221176147</t>
   </si>
   <si>
     <t xml:space="preserve">7.19764471054077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80477142333984</t>
+    <t xml:space="preserve">6.80477094650269</t>
   </si>
   <si>
     <t xml:space="preserve">7.02639102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08683443069458</t>
+    <t xml:space="preserve">7.08683300018311</t>
   </si>
   <si>
     <t xml:space="preserve">7.04150295257568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85010242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86521291732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069219589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22282934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31349182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23290252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29838085174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98106050491333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01128149032593</t>
+    <t xml:space="preserve">6.8501033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8652138710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069267272949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22282886505127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31349229812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23290157318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29838228225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98106002807617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01128101348877</t>
   </si>
   <si>
     <t xml:space="preserve">6.53781890869141</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7997350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68388557434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73929357528687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94076490402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90550804138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66877746582031</t>
+    <t xml:space="preserve">6.79973411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68388700485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73929309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94076681137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90550708770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.668776512146</t>
   </si>
   <si>
     <t xml:space="preserve">6.4622654914856</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">6.6738133430481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5982608795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87528705596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00624465942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15231275558472</t>
+    <t xml:space="preserve">6.59825992584229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87528657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00624418258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15231323242188</t>
   </si>
   <si>
     <t xml:space="preserve">7.30341768264771</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6257758140564</t>
+    <t xml:space="preserve">7.62577629089355</t>
   </si>
   <si>
     <t xml:space="preserve">7.66103410720825</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">7.57037115097046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45452404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53511238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44444990158081</t>
+    <t xml:space="preserve">7.45452356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5351128578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44445037841797</t>
   </si>
   <si>
     <t xml:space="preserve">7.59555530548096</t>
@@ -584,31 +584,31 @@
     <t xml:space="preserve">7.72147703170776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60562753677368</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70636558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48474550247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3638596534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26312303543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13216590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17245960235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69629192352295</t>
+    <t xml:space="preserve">7.60562944412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70636606216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48474502563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36386013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26312446594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13216495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617099761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17246150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69629096984863</t>
   </si>
   <si>
     <t xml:space="preserve">7.91791248321533</t>
@@ -617,79 +617,79 @@
     <t xml:space="preserve">8.35611629486084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38633918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51729583740234</t>
+    <t xml:space="preserve">8.38633823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51729679107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.45181751251221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20501327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04887104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9582085609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93132305145264</t>
+    <t xml:space="preserve">8.20501232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04887199401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95820808410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93132352828979</t>
   </si>
   <si>
     <t xml:space="preserve">7.71623516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73236799240112</t>
+    <t xml:space="preserve">7.73236608505249</t>
   </si>
   <si>
     <t xml:space="preserve">7.63557767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64095497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45813035964966</t>
+    <t xml:space="preserve">7.64095592498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45813226699829</t>
   </si>
   <si>
     <t xml:space="preserve">7.44200038909912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57105207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68934869766235</t>
+    <t xml:space="preserve">7.57105302810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68934917449951</t>
   </si>
   <si>
     <t xml:space="preserve">7.62482309341431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79689359664917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20018196105957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43140029907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61960029602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54432106018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46903800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58733558654785</t>
+    <t xml:space="preserve">7.79689311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20018100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43139839172363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61959934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54432010650635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46903896331787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58733749389648</t>
   </si>
   <si>
     <t xml:space="preserve">8.70025730133057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54969596862793</t>
+    <t xml:space="preserve">8.54969692230225</t>
   </si>
   <si>
     <t xml:space="preserve">8.60346794128418</t>
@@ -698,34 +698,34 @@
     <t xml:space="preserve">8.53356552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5980920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51743412017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52818775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67875003814697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11429977416992</t>
+    <t xml:space="preserve">8.59809112548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51743316650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5281867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67874813079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11429882049561</t>
   </si>
   <si>
     <t xml:space="preserve">9.15731525421143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20033264160156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17882537841797</t>
+    <t xml:space="preserve">9.20033359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17882442474365</t>
   </si>
   <si>
     <t xml:space="preserve">9.05515003204346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33476257324219</t>
+    <t xml:space="preserve">9.3347635269165</t>
   </si>
   <si>
     <t xml:space="preserve">9.13043022155762</t>
@@ -734,34 +734,34 @@
     <t xml:space="preserve">9.44768333435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38315582275391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41004276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45843887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4530611038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37240219116211</t>
+    <t xml:space="preserve">9.38315677642822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41004371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4584379196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45306015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37240314483643</t>
   </si>
   <si>
     <t xml:space="preserve">9.23797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32938575744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46919250488281</t>
+    <t xml:space="preserve">9.32938671112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4691915512085</t>
   </si>
   <si>
     <t xml:space="preserve">9.44230556488037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92609786987305</t>
+    <t xml:space="preserve">8.92609977722168</t>
   </si>
   <si>
     <t xml:space="preserve">9.0927906036377</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">9.07128238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478290557861</t>
+    <t xml:space="preserve">8.76478481292725</t>
   </si>
   <si>
     <t xml:space="preserve">9.16807079315186</t>
@@ -779,10 +779,10 @@
     <t xml:space="preserve">9.25948238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28637027740479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2433500289917</t>
+    <t xml:space="preserve">9.28636932373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24335193634033</t>
   </si>
   <si>
     <t xml:space="preserve">9.26485919952393</t>
@@ -791,43 +791,43 @@
     <t xml:space="preserve">9.2325963973999</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24872875213623</t>
+    <t xml:space="preserve">9.24872779846191</t>
   </si>
   <si>
     <t xml:space="preserve">8.96373748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.495924949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59271335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5228099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66799449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73789691925049</t>
+    <t xml:space="preserve">8.49592590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59271430969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52281093597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66799354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7378978729248</t>
   </si>
   <si>
     <t xml:space="preserve">8.71101188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70563411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6357307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53894233703613</t>
+    <t xml:space="preserve">8.70563316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63573169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53894138336182</t>
   </si>
   <si>
     <t xml:space="preserve">8.50130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28621482849121</t>
+    <t xml:space="preserve">8.28621578216553</t>
   </si>
   <si>
     <t xml:space="preserve">8.33460998535156</t>
@@ -836,13 +836,13 @@
     <t xml:space="preserve">8.43677616119385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47441577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62497615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56582832336426</t>
+    <t xml:space="preserve">8.47441673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62497711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56582927703857</t>
   </si>
   <si>
     <t xml:space="preserve">8.47979259490967</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">8.66261672973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61422157287598</t>
+    <t xml:space="preserve">8.61422252655029</t>
   </si>
   <si>
     <t xml:space="preserve">8.78091526031494</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">8.77016162872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79166889190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1842041015625</t>
+    <t xml:space="preserve">8.79166793823242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18420314788818</t>
   </si>
   <si>
     <t xml:space="preserve">9.04977321624756</t>
@@ -878,34 +878,34 @@
     <t xml:space="preserve">9.30249977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1358060836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14656162261963</t>
+    <t xml:space="preserve">9.13580799102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14656257629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.20571041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62513065338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63050651550293</t>
+    <t xml:space="preserve">9.62513160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63050556182861</t>
   </si>
   <si>
     <t xml:space="preserve">9.60899829864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63588523864746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7165412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97464656829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0553035736084</t>
+    <t xml:space="preserve">9.63588619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71654033660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97464561462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0553026199341</t>
   </si>
   <si>
     <t xml:space="preserve">10.2435035705566</t>
@@ -914,19 +914,19 @@
     <t xml:space="preserve">10.4155731201172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3456707000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2327499389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3994426727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4101972579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349161148071</t>
+    <t xml:space="preserve">10.3456716537476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2327489852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3994436264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4101963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349170684814</t>
   </si>
   <si>
     <t xml:space="preserve">10.1305837631226</t>
@@ -941,31 +941,31 @@
     <t xml:space="preserve">10.425971031189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5507650375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6074905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5848007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4770231246948</t>
+    <t xml:space="preserve">10.5507669448853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6074895858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847988128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4770221710205</t>
   </si>
   <si>
     <t xml:space="preserve">10.2387800216675</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2728157043457</t>
+    <t xml:space="preserve">10.2728147506714</t>
   </si>
   <si>
     <t xml:space="preserve">10.3408832550049</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2160911560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0856237411499</t>
+    <t xml:space="preserve">10.2160902023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0856246948242</t>
   </si>
   <si>
     <t xml:space="preserve">9.90410614013672</t>
@@ -977,34 +977,34 @@
     <t xml:space="preserve">10.2614698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1083126068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0062093734741</t>
+    <t xml:space="preserve">10.1083135604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0062103271484</t>
   </si>
   <si>
     <t xml:space="preserve">9.94381237030029</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1707105636597</t>
+    <t xml:space="preserve">10.1707096099854</t>
   </si>
   <si>
     <t xml:space="preserve">10.1366758346558</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0629348754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1990728378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3522281646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104158401489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1933994293213</t>
+    <t xml:space="preserve">10.062933921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1990718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3522291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1934013366699</t>
   </si>
   <si>
     <t xml:space="preserve">9.95515823364258</t>
@@ -1013,22 +1013,22 @@
     <t xml:space="preserve">10.1480197906494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2444505691528</t>
+    <t xml:space="preserve">10.2444524765015</t>
   </si>
   <si>
     <t xml:space="preserve">10.2841596603394</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2217617034912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0912971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1593656539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5450916290283</t>
+    <t xml:space="preserve">10.2217626571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0912961959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1593647003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.545093536377</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089546203613</t>
@@ -1040,7 +1040,7 @@
     <t xml:space="preserve">10.2955055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3692464828491</t>
+    <t xml:space="preserve">10.3692445755005</t>
   </si>
   <si>
     <t xml:space="preserve">10.4316434860229</t>
@@ -1049,55 +1049,55 @@
     <t xml:space="preserve">10.397608757019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7152662277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6415243148804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7436285018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7209386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.669885635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7776641845703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7039203643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.658540725708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5394201278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3068504333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5564374923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4826955795288</t>
+    <t xml:space="preserve">10.7152671813965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.641526222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7436294555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7209377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6698865890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7776622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7039213180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6585416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5394191741943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3068494796753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095937728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5564365386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4826936721802</t>
   </si>
   <si>
     <t xml:space="preserve">10.3352117538452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2331075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2784872055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0288991928101</t>
+    <t xml:space="preserve">10.2331085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2784862518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0288982391357</t>
   </si>
   <si>
     <t xml:space="preserve">10.040244102478</t>
@@ -1106,43 +1106,43 @@
     <t xml:space="preserve">10.0969686508179</t>
   </si>
   <si>
-    <t xml:space="preserve">10.034571647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98351955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96082973480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98919296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2274360656738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2557983398438</t>
+    <t xml:space="preserve">10.0345706939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98351860046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96082878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98919200897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2274351119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2557973861694</t>
   </si>
   <si>
     <t xml:space="preserve">10.4940404891968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.511058807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.414626121521</t>
+    <t xml:space="preserve">10.5110578536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4146280288696</t>
   </si>
   <si>
     <t xml:space="preserve">10.3635740280151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3805913925171</t>
+    <t xml:space="preserve">10.3805923461914</t>
   </si>
   <si>
     <t xml:space="preserve">10.4600057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5167303085327</t>
+    <t xml:space="preserve">10.516731262207</t>
   </si>
   <si>
     <t xml:space="preserve">10.3465566635132</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">9.72825908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67720794677734</t>
+    <t xml:space="preserve">9.67720699310303</t>
   </si>
   <si>
     <t xml:space="preserve">9.66018962860107</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">9.48434352874756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.688551902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58644771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71124172210693</t>
+    <t xml:space="preserve">9.68855285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58644866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7112398147583</t>
   </si>
   <si>
     <t xml:space="preserve">9.67153453826904</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">9.61480903625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6204833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73393154144287</t>
+    <t xml:space="preserve">9.62048149108887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73393249511719</t>
   </si>
   <si>
     <t xml:space="preserve">9.78498458862305</t>
@@ -1193,13 +1193,13 @@
     <t xml:space="preserve">9.79632949829102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89843463897705</t>
+    <t xml:space="preserve">9.89843368530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.16101360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95113277435303</t>
+    <t xml:space="preserve">8.95113182067871</t>
   </si>
   <si>
     <t xml:space="preserve">8.99084091186523</t>
@@ -1211,31 +1211,31 @@
     <t xml:space="preserve">8.75259780883789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86604595184326</t>
+    <t xml:space="preserve">8.86604499816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.85470104217529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05891132354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24042797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25177383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10996246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09294319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98516845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.075927734375</t>
+    <t xml:space="preserve">9.05891036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24042892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2517728805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10996150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09294414520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98516654968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07592678070068</t>
   </si>
   <si>
     <t xml:space="preserve">9.13265132904053</t>
@@ -1244,10 +1244,10 @@
     <t xml:space="preserve">9.05323696136475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90008068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88306331634521</t>
+    <t xml:space="preserve">8.90008163452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88306427001953</t>
   </si>
   <si>
     <t xml:space="preserve">8.82633876800537</t>
@@ -1262,46 +1262,46 @@
     <t xml:space="preserve">8.9681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00218391418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0702543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99651336669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01920223236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92277145385742</t>
+    <t xml:space="preserve">9.0021858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07025527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99651145935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01920318603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92277050018311</t>
   </si>
   <si>
     <t xml:space="preserve">9.04189205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03054809570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01353073120117</t>
+    <t xml:space="preserve">9.03054714202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01352882385254</t>
   </si>
   <si>
     <t xml:space="preserve">9.04756450653076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03621959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1383228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97382259368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12697887420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16668701171875</t>
+    <t xml:space="preserve">9.03622055053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13832378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97382354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12697982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16668510437012</t>
   </si>
   <si>
     <t xml:space="preserve">9.19504833221436</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">9.37089443206787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38223934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34253311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46732521057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6755599975586</t>
+    <t xml:space="preserve">9.38223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34253215789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46732616424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6755590438843</t>
   </si>
   <si>
     <t xml:space="preserve">10.420298576355</t>
@@ -1331,70 +1331,70 @@
     <t xml:space="preserve">10.5961446762085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7549743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7379550933838</t>
+    <t xml:space="preserve">10.7549724578857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7379560470581</t>
   </si>
   <si>
     <t xml:space="preserve">10.7606449127197</t>
   </si>
   <si>
-    <t xml:space="preserve">10.661376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4543333053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.403281211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4429874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3777551651001</t>
+    <t xml:space="preserve">10.6613779067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4543323516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4429883956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3777570724487</t>
   </si>
   <si>
     <t xml:space="preserve">10.0742797851562</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1338396072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0941314697266</t>
+    <t xml:space="preserve">10.1338386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0941324234009</t>
   </si>
   <si>
     <t xml:space="preserve">9.98635578155518</t>
   </si>
   <si>
-    <t xml:space="preserve">10.156530380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.196234703064</t>
+    <t xml:space="preserve">10.1565294265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962356567383</t>
   </si>
   <si>
     <t xml:space="preserve">10.2359437942505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1622018814087</t>
+    <t xml:space="preserve">10.162202835083</t>
   </si>
   <si>
     <t xml:space="preserve">10.2416172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2501258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132539749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1678743362427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90694141387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9296293258667</t>
+    <t xml:space="preserve">10.2501249313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132530212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1678733825684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90694046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92963027954102</t>
   </si>
   <si>
     <t xml:space="preserve">10.1877269744873</t>
@@ -1403,7 +1403,7 @@
     <t xml:space="preserve">10.2302713394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0203895568848</t>
+    <t xml:space="preserve">10.0203905105591</t>
   </si>
   <si>
     <t xml:space="preserve">10.1905641555786</t>
@@ -1412,22 +1412,22 @@
     <t xml:space="preserve">10.1820554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0317344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97784805297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81618213653564</t>
+    <t xml:space="preserve">10.0317354202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9778470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81618309020996</t>
   </si>
   <si>
     <t xml:space="preserve">9.88708782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89559650421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81334590911865</t>
+    <t xml:space="preserve">9.89559555053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81334495544434</t>
   </si>
   <si>
     <t xml:space="preserve">9.97501087188721</t>
@@ -1436,49 +1436,49 @@
     <t xml:space="preserve">10.065770149231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395120620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0005369186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686063766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73676776885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83603572845459</t>
+    <t xml:space="preserve">10.1395111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0005359649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686054229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73676681518555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83603668212891</t>
   </si>
   <si>
     <t xml:space="preserve">9.89276027679443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86723327636719</t>
+    <t xml:space="preserve">9.8672342300415</t>
   </si>
   <si>
     <t xml:space="preserve">9.82752704620361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77931022644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8331995010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94948577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714426040649</t>
+    <t xml:space="preserve">9.77931118011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83320045471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94948482513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714435577393</t>
   </si>
   <si>
     <t xml:space="preserve">9.93814086914062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71407794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42761993408203</t>
+    <t xml:space="preserve">9.71407890319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42761898040771</t>
   </si>
   <si>
     <t xml:space="preserve">9.10145378112793</t>
@@ -1493,40 +1493,40 @@
     <t xml:space="preserve">9.24326419830322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20072269439697</t>
+    <t xml:space="preserve">9.20072174072266</t>
   </si>
   <si>
     <t xml:space="preserve">9.29274559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51369667053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39841842651367</t>
+    <t xml:space="preserve">9.51369762420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39841651916504</t>
   </si>
   <si>
     <t xml:space="preserve">9.47206878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4400463104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33757591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98533535003662</t>
+    <t xml:space="preserve">9.44004726409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33757495880127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98533630371094</t>
   </si>
   <si>
     <t xml:space="preserve">9.02696514129639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89887619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34397983551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31836223602295</t>
+    <t xml:space="preserve">8.89887714385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34398078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31836414337158</t>
   </si>
   <si>
     <t xml:space="preserve">8.93730449676514</t>
@@ -1535,76 +1535,76 @@
     <t xml:space="preserve">8.92129135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93410110473633</t>
+    <t xml:space="preserve">8.93410015106201</t>
   </si>
   <si>
     <t xml:space="preserve">8.64590263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83803462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75477886199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72275543212891</t>
+    <t xml:space="preserve">8.83803367614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7547779083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72275638580322</t>
   </si>
   <si>
     <t xml:space="preserve">8.71635150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64270210266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82842922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80601406097412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83162975311279</t>
+    <t xml:space="preserve">8.64270114898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82842826843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80601215362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83163070678711</t>
   </si>
   <si>
     <t xml:space="preserve">8.66511726379395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73556518554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51781463623047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56905269622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45697498321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.39613437652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51141166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53062534332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53703022003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54343318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71315002441406</t>
+    <t xml:space="preserve">8.73556613922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51781558990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56905174255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45697593688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.39613342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51141262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53062438964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53702926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54343414306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71314907073975</t>
   </si>
   <si>
     <t xml:space="preserve">8.40573883056641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36411094665527</t>
+    <t xml:space="preserve">8.36411190032959</t>
   </si>
   <si>
     <t xml:space="preserve">8.33209037780762</t>
@@ -1619,52 +1619,52 @@
     <t xml:space="preserve">8.57225322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46017742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46658229827881</t>
+    <t xml:space="preserve">8.46017646789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46658134460449</t>
   </si>
   <si>
     <t xml:space="preserve">8.58186149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44096374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09420967102051</t>
+    <t xml:space="preserve">8.4409646987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09421062469482</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05578422546387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19988250732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18707180023193</t>
+    <t xml:space="preserve">9.05578327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1998815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">8.91808986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87646198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03657054901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18387126922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15505123138428</t>
+    <t xml:space="preserve">8.87646102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03657150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18387031555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15505218505859</t>
   </si>
   <si>
     <t xml:space="preserve">9.1518497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23510551452637</t>
+    <t xml:space="preserve">9.23510646820068</t>
   </si>
   <si>
     <t xml:space="preserve">9.16465950012207</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">9.1262321472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2607250213623</t>
+    <t xml:space="preserve">9.26072311401367</t>
   </si>
   <si>
     <t xml:space="preserve">9.254319190979</t>
@@ -1682,31 +1682,31 @@
     <t xml:space="preserve">9.2062873840332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20948886871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22550010681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10701942443848</t>
+    <t xml:space="preserve">9.20948791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22549915313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10701847076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.92769718170166</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76758766174316</t>
+    <t xml:space="preserve">8.76758575439453</t>
   </si>
   <si>
     <t xml:space="preserve">8.65871334075928</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68112659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72595977783203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61708545684814</t>
+    <t xml:space="preserve">8.68112754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72595882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61708450317383</t>
   </si>
   <si>
     <t xml:space="preserve">8.7803955078125</t>
@@ -1715,16 +1715,16 @@
     <t xml:space="preserve">8.82202434539795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77719306945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78359699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95331382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97252655029297</t>
+    <t xml:space="preserve">8.77719497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78359794616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95331478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97252750396729</t>
   </si>
   <si>
     <t xml:space="preserve">8.9661226272583</t>
@@ -1736,22 +1736,22 @@
     <t xml:space="preserve">8.86045074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32568454742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22321510314941</t>
+    <t xml:space="preserve">8.32568550109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.2232141494751</t>
   </si>
   <si>
     <t xml:space="preserve">8.29366302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53382873535156</t>
+    <t xml:space="preserve">8.53382682800293</t>
   </si>
   <si>
     <t xml:space="preserve">8.48259258270264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40253734588623</t>
+    <t xml:space="preserve">8.40253829956055</t>
   </si>
   <si>
     <t xml:space="preserve">8.14956474304199</t>
@@ -1766,34 +1766,34 @@
     <t xml:space="preserve">7.77490997314453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74929141998291</t>
+    <t xml:space="preserve">7.74929189682007</t>
   </si>
   <si>
     <t xml:space="preserve">7.67884397506714</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87417697906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73007869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53474521636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42266845703125</t>
+    <t xml:space="preserve">7.87417650222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73007917404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53474473953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42266893386841</t>
   </si>
   <si>
     <t xml:space="preserve">7.25295209884644</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21772909164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08003520965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11205673217773</t>
+    <t xml:space="preserve">7.21772813796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08003568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11205625534058</t>
   </si>
   <si>
     <t xml:space="preserve">6.84947681427002</t>
@@ -1805,7 +1805,7 @@
     <t xml:space="preserve">7.04160737991333</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03520441055298</t>
+    <t xml:space="preserve">7.03520488739014</t>
   </si>
   <si>
     <t xml:space="preserve">7.04801273345947</t>
@@ -1814,46 +1814,46 @@
     <t xml:space="preserve">6.94234085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95194721221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00958633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13126945495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97436189651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83026361465454</t>
+    <t xml:space="preserve">6.95194673538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00958728790283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13126850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97436141967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83026456832886</t>
   </si>
   <si>
     <t xml:space="preserve">6.95514965057373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8014440536499</t>
+    <t xml:space="preserve">6.80144453048706</t>
   </si>
   <si>
     <t xml:space="preserve">6.76622009277344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.85908460617065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6285252571106</t>
+    <t xml:space="preserve">6.85908317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62852621078491</t>
   </si>
   <si>
     <t xml:space="preserve">6.70537900924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74700689315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86548757553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16329145431519</t>
+    <t xml:space="preserve">6.7470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86548805236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16329193115234</t>
   </si>
   <si>
     <t xml:space="preserve">7.09604549407959</t>
@@ -1862,16 +1862,16 @@
     <t xml:space="preserve">7.06722640991211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02239561080933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23053693771362</t>
+    <t xml:space="preserve">7.02239608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23053741455078</t>
   </si>
   <si>
     <t xml:space="preserve">7.05761957168579</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80464649200439</t>
+    <t xml:space="preserve">6.80464696884155</t>
   </si>
   <si>
     <t xml:space="preserve">6.89110565185547</t>
@@ -1889,13 +1889,13 @@
     <t xml:space="preserve">7.01278924942017</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88790321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45880937576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39796876907349</t>
+    <t xml:space="preserve">6.88790273666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45881080627441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39796924591064</t>
   </si>
   <si>
     <t xml:space="preserve">6.15204095840454</t>
@@ -1904,22 +1904,22 @@
     <t xml:space="preserve">6.15844488143921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96375179290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10592937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10721111297607</t>
+    <t xml:space="preserve">5.96375131607056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10592985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1072096824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.39925050735474</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64453649520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6317286491394</t>
+    <t xml:space="preserve">6.6445369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63172817230225</t>
   </si>
   <si>
     <t xml:space="preserve">6.59010028839111</t>
@@ -1931,97 +1931,97 @@
     <t xml:space="preserve">6.60290861129761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59650325775146</t>
+    <t xml:space="preserve">6.59650468826294</t>
   </si>
   <si>
     <t xml:space="preserve">6.41718101501465</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52285432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42038488388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47802400588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44600200653076</t>
+    <t xml:space="preserve">6.52285480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42038440704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47802305221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4460015296936</t>
   </si>
   <si>
     <t xml:space="preserve">6.32624006271362</t>
   </si>
   <si>
-    <t xml:space="preserve">6.26732015609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74380588531494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09924745559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30739068984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19851589202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08964157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11846017837524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15368509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15688705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17930126190186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0448112487793</t>
+    <t xml:space="preserve">6.26731967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74380540847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09924697875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3073902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19851493835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08964109420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11846113204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15368413925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15688610076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17930269241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04481077194214</t>
   </si>
   <si>
     <t xml:space="preserve">6.99357557296753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27216672897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44828605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75889825820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57637214660645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72687673568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83895301818848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82614421844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84535598754883</t>
+    <t xml:space="preserve">7.27216625213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4482855796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75889778137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57637357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72687530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.838951587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82614469528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8453574180603</t>
   </si>
   <si>
     <t xml:space="preserve">7.8997950553894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91260290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98305082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88058090209961</t>
+    <t xml:space="preserve">7.91260194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98305177688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88057994842529</t>
   </si>
   <si>
     <t xml:space="preserve">7.91900730133057</t>
@@ -2033,10 +2033,10 @@
     <t xml:space="preserve">8.12074565887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26164245605469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47298717498779</t>
+    <t xml:space="preserve">8.26164054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47298622131348</t>
   </si>
   <si>
     <t xml:space="preserve">8.46337890625</t>
@@ -2051,10 +2051,10 @@
     <t xml:space="preserve">9.26392650604248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33117198944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53291130065918</t>
+    <t xml:space="preserve">9.33117294311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53291034698486</t>
   </si>
   <si>
     <t xml:space="preserve">9.67700862884521</t>
@@ -2063,19 +2063,19 @@
     <t xml:space="preserve">9.51049423217773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42083358764648</t>
+    <t xml:space="preserve">9.42083263397217</t>
   </si>
   <si>
     <t xml:space="preserve">9.32796955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40482234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47847270965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55212211608887</t>
+    <t xml:space="preserve">9.40482330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47847175598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55212306976318</t>
   </si>
   <si>
     <t xml:space="preserve">9.5713357925415</t>
@@ -2084,22 +2084,22 @@
     <t xml:space="preserve">9.70262432098389</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77627563476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81470203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.083685874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0356531143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1413249969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.21497631073</t>
+    <t xml:space="preserve">9.77627658843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8147029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0836868286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0356521606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1413240432739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2149753570557</t>
   </si>
   <si>
     <t xml:space="preserve">10.195761680603</t>
@@ -2114,7 +2114,7 @@
     <t xml:space="preserve">10.5608129501343</t>
   </si>
   <si>
-    <t xml:space="preserve">10.849009513855</t>
+    <t xml:space="preserve">10.8490076065063</t>
   </si>
   <si>
     <t xml:space="preserve">10.868221282959</t>
@@ -2123,37 +2123,37 @@
     <t xml:space="preserve">10.8874340057373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0155220031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0603513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2813034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2909088134766</t>
+    <t xml:space="preserve">11.0155229568481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0603504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.281304359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2909107208252</t>
   </si>
   <si>
     <t xml:space="preserve">11.5118618011475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5278720855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4958505630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.377368927002</t>
+    <t xml:space="preserve">11.5278730392456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.495849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3773679733276</t>
   </si>
   <si>
     <t xml:space="preserve">11.3261337280273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4926471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8105812072754</t>
+    <t xml:space="preserve">11.4926462173462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8105802536011</t>
   </si>
   <si>
     <t xml:space="preserve">10.9899053573608</t>
@@ -2162,43 +2162,43 @@
     <t xml:space="preserve">10.5992374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0219249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1404075622559</t>
+    <t xml:space="preserve">11.0219268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1404085159302</t>
   </si>
   <si>
     <t xml:space="preserve">11.1141195297241</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7917671203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7882652282715</t>
+    <t xml:space="preserve">10.79176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882661819458</t>
   </si>
   <si>
     <t xml:space="preserve">10.4203634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5780353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3993406295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4273719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2872190475464</t>
+    <t xml:space="preserve">10.5780363082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3993396759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4273710250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2872180938721</t>
   </si>
   <si>
     <t xml:space="preserve">10.3888292312622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.423867225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3678064346313</t>
+    <t xml:space="preserve">10.4238662719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3678073883057</t>
   </si>
   <si>
     <t xml:space="preserve">10.7322034835815</t>
@@ -2213,19 +2213,19 @@
     <t xml:space="preserve">10.5079593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.514967918396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6305932998657</t>
+    <t xml:space="preserve">10.5149669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6305923461914</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127918243408</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1281356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1877002716064</t>
+    <t xml:space="preserve">11.1281366348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1877012252808</t>
   </si>
   <si>
     <t xml:space="preserve">11.3523807525635</t>
@@ -2240,16 +2240,16 @@
     <t xml:space="preserve">11.7553186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7342977523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429145812988</t>
+    <t xml:space="preserve">11.7342967987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429136276245</t>
   </si>
   <si>
     <t xml:space="preserve">11.7097682952881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6291809082031</t>
+    <t xml:space="preserve">11.6291818618774</t>
   </si>
   <si>
     <t xml:space="preserve">11.863938331604</t>
@@ -2261,7 +2261,7 @@
     <t xml:space="preserve">11.9199981689453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0496397018433</t>
+    <t xml:space="preserve">12.0496406555176</t>
   </si>
   <si>
     <t xml:space="preserve">12.2318382263184</t>
@@ -2279,52 +2279,52 @@
     <t xml:space="preserve">12.3159303665161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2773895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4175405502319</t>
+    <t xml:space="preserve">12.2773885726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4175415039062</t>
   </si>
   <si>
     <t xml:space="preserve">12.3684873580933</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1267251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0391292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464193344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636558532715</t>
+    <t xml:space="preserve">12.1267242431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0391283035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464183807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636548995972</t>
   </si>
   <si>
     <t xml:space="preserve">12.1407403945923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1232204437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1092052459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0321207046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8779544830322</t>
+    <t xml:space="preserve">12.1232194900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.109206199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0321226119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8779535293579</t>
   </si>
   <si>
     <t xml:space="preserve">11.9760599136353</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6887454986572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4680070877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4890298843384</t>
+    <t xml:space="preserve">11.6887474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4680061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4890289306641</t>
   </si>
   <si>
     <t xml:space="preserve">11.4820213317871</t>
@@ -2333,34 +2333,34 @@
     <t xml:space="preserve">11.6782360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2472639083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0370359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1001043319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7216911315918</t>
+    <t xml:space="preserve">11.2472648620605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0370349884033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1001052856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7216920852661</t>
   </si>
   <si>
     <t xml:space="preserve">10.9284181594849</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1561660766602</t>
+    <t xml:space="preserve">11.1561651229858</t>
   </si>
   <si>
     <t xml:space="preserve">11.496036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.446982383728</t>
+    <t xml:space="preserve">11.4469814300537</t>
   </si>
   <si>
     <t xml:space="preserve">11.184196472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3243494033813</t>
+    <t xml:space="preserve">11.324348449707</t>
   </si>
   <si>
     <t xml:space="preserve">11.2752962112427</t>
@@ -2369,10 +2369,10 @@
     <t xml:space="preserve">11.0615634918213</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4049377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2297449111938</t>
+    <t xml:space="preserve">11.4049367904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2297458648682</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119453430176</t>
@@ -2384,40 +2384,40 @@
     <t xml:space="preserve">11.7903575897217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814563751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8288993835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550361633301</t>
+    <t xml:space="preserve">11.8814573287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8288984298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550352096558</t>
   </si>
   <si>
     <t xml:space="preserve">11.6677236557007</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6712274551392</t>
+    <t xml:space="preserve">11.6712284088135</t>
   </si>
   <si>
     <t xml:space="preserve">11.8113803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970846176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9410219192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.969051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.06715965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2738847732544</t>
+    <t xml:space="preserve">11.9970836639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9410228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9690523147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0671586990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703809738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2738857269287</t>
   </si>
   <si>
     <t xml:space="preserve">12.1021976470947</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">11.9725551605225</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0146026611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741662979126</t>
+    <t xml:space="preserve">12.0146017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741672515869</t>
   </si>
   <si>
     <t xml:space="preserve">11.9865713119507</t>
@@ -2441,19 +2441,19 @@
     <t xml:space="preserve">11.6011514663696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.552098274231</t>
+    <t xml:space="preserve">11.5520992279053</t>
   </si>
   <si>
     <t xml:space="preserve">11.5485935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5941429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4259605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5380821228027</t>
+    <t xml:space="preserve">11.5941438674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4259595870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5380830764771</t>
   </si>
   <si>
     <t xml:space="preserve">11.6852426528931</t>
@@ -2465,64 +2465,64 @@
     <t xml:space="preserve">11.7027626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9480295181274</t>
+    <t xml:space="preserve">11.9480285644531</t>
   </si>
   <si>
     <t xml:space="preserve">12.0846796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2108163833618</t>
+    <t xml:space="preserve">12.2108154296875</t>
   </si>
   <si>
     <t xml:space="preserve">12.7539091110229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9641370773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7188711166382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7889471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7959547042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9886627197266</t>
+    <t xml:space="preserve">12.9641389846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7188692092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7889461517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.795952796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9886636734009</t>
   </si>
   <si>
     <t xml:space="preserve">13.1743659973145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9080762863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0412216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094039916992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6648998260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8996562957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007043838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3656663894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389636993408</t>
+    <t xml:space="preserve">12.9080772399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0412225723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094049453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6649017333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8996553421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007034301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.365665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389627456665</t>
   </si>
   <si>
     <t xml:space="preserve">15.0173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1365060806274</t>
+    <t xml:space="preserve">15.1365079879761</t>
   </si>
   <si>
     <t xml:space="preserve">15.5289354324341</t>
@@ -2531,7 +2531,7 @@
     <t xml:space="preserve">15.9493942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7181406021118</t>
+    <t xml:space="preserve">15.7181415557861</t>
   </si>
   <si>
     <t xml:space="preserve">15.9213619232178</t>
@@ -2540,7 +2540,7 @@
     <t xml:space="preserve">16.1035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9914398193359</t>
+    <t xml:space="preserve">15.9914379119873</t>
   </si>
   <si>
     <t xml:space="preserve">16.124584197998</t>
@@ -2549,55 +2549,55 @@
     <t xml:space="preserve">16.4118976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5940971374512</t>
+    <t xml:space="preserve">16.5940952301025</t>
   </si>
   <si>
     <t xml:space="preserve">16.5100040435791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2086734771729</t>
+    <t xml:space="preserve">16.2086753845215</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474987030029</t>
   </si>
   <si>
-    <t xml:space="preserve">15.886323928833</t>
+    <t xml:space="preserve">15.8863248825073</t>
   </si>
   <si>
     <t xml:space="preserve">15.4868879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8232555389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7531785964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251482009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1575298309326</t>
+    <t xml:space="preserve">15.8232536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7531776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251491546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1575307846069</t>
   </si>
   <si>
     <t xml:space="preserve">15.3817739486694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2626447677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2976808547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0804462432861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2836656570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2205963134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0944604873657</t>
+    <t xml:space="preserve">15.2626428604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2976818084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0804452896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2836675643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2205982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0944595336914</t>
   </si>
   <si>
     <t xml:space="preserve">15.0664300918579</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">15.0454063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8562040328979</t>
+    <t xml:space="preserve">14.856201171875</t>
   </si>
   <si>
     <t xml:space="preserve">14.9122629165649</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1715440750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8702163696289</t>
+    <t xml:space="preserve">15.1715431213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8702144622803</t>
   </si>
   <si>
     <t xml:space="preserve">14.7721099853516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.353741645813</t>
+    <t xml:space="preserve">15.3537425994873</t>
   </si>
   <si>
     <t xml:space="preserve">16.5029964447021</t>
@@ -2636,7 +2636,7 @@
     <t xml:space="preserve">16.7062168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8043231964111</t>
+    <t xml:space="preserve">16.8043251037598</t>
   </si>
   <si>
     <t xml:space="preserve">16.622127532959</t>
@@ -2648,10 +2648,10 @@
     <t xml:space="preserve">16.9865226745605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0075454711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5380363464355</t>
+    <t xml:space="preserve">17.00754737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5380344390869</t>
   </si>
   <si>
     <t xml:space="preserve">16.0545082092285</t>
@@ -2660,31 +2660,31 @@
     <t xml:space="preserve">16.3978824615479</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4959907531738</t>
+    <t xml:space="preserve">16.4959926605225</t>
   </si>
   <si>
     <t xml:space="preserve">16.0685234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5499582290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5709791183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0334854125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9423847198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1666316986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6431484222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3908748626709</t>
+    <t xml:space="preserve">15.5499572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5709781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.033483505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9423866271973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1666278839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6431503295898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3908729553223</t>
   </si>
   <si>
     <t xml:space="preserve">16.762279510498</t>
@@ -2696,73 +2696,73 @@
     <t xml:space="preserve">16.671178817749</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272434234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9514865875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6130247116089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5198335647583</t>
+    <t xml:space="preserve">16.7272415161133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.951488494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6130285263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5198345184326</t>
   </si>
   <si>
     <t xml:space="preserve">14.3516502380371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5478649139404</t>
+    <t xml:space="preserve">14.5478639602661</t>
   </si>
   <si>
     <t xml:space="preserve">13.7910394668579</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4546728134155</t>
+    <t xml:space="preserve">13.4546737670898</t>
   </si>
   <si>
     <t xml:space="preserve">13.0272054672241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9956731796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.347466468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7202816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3327674865723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68806552886963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81069946289062</t>
+    <t xml:space="preserve">12.9956712722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3474655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7202806472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3327684402466</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68806457519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81069850921631</t>
   </si>
   <si>
     <t xml:space="preserve">8.25149822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51988124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44420909881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02024555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70490121841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77497911453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49817705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59978818893433</t>
+    <t xml:space="preserve">9.51988220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4442081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0202465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70490217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77497863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49817752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59978771209717</t>
   </si>
   <si>
     <t xml:space="preserve">8.28653621673584</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">9.06088161468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69507312774658</t>
+    <t xml:space="preserve">9.69507217407227</t>
   </si>
   <si>
     <t xml:space="preserve">9.05036926269531</t>
@@ -2798,31 +2798,31 @@
     <t xml:space="preserve">9.48834705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1680889129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87727165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2991418838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51637840270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58995819091797</t>
+    <t xml:space="preserve">10.1680898666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381639480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87727069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29914093017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44630146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51637744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58995914459229</t>
   </si>
   <si>
     <t xml:space="preserve">9.25359058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33417797088623</t>
+    <t xml:space="preserve">9.33417987823486</t>
   </si>
   <si>
     <t xml:space="preserve">9.49535465240479</t>
@@ -2834,22 +2834,22 @@
     <t xml:space="preserve">10.3713102340698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.816294670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2122268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.760232925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8618450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5324869155884</t>
+    <t xml:space="preserve">10.8162956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2122278213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7602338790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8618459701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5324859619141</t>
   </si>
   <si>
     <t xml:space="preserve">10.6025619506836</t>
@@ -2858,19 +2858,19 @@
     <t xml:space="preserve">10.6095705032349</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5394945144653</t>
+    <t xml:space="preserve">10.539493560791</t>
   </si>
   <si>
     <t xml:space="preserve">10.4133558273315</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0058355331421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4649333953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7654342651367</t>
+    <t xml:space="preserve">11.0058345794678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4649343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7654333114624</t>
   </si>
   <si>
     <t xml:space="preserve">10.6414775848389</t>
@@ -2891,34 +2891,34 @@
     <t xml:space="preserve">11.358922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1936473846436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3251171112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5204420089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7984037399292</t>
+    <t xml:space="preserve">11.1936483383179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3251161575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5204429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7984056472778</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913925170898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6923952102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9966506958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4407253265381</t>
+    <t xml:space="preserve">12.6923961639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9966497421265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4407243728638</t>
   </si>
   <si>
     <t xml:space="preserve">12.3956499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.648154258728</t>
+    <t xml:space="preserve">11.6481552124023</t>
   </si>
   <si>
     <t xml:space="preserve">11.6105918884277</t>
@@ -2927,10 +2927,10 @@
     <t xml:space="preserve">11.5166854858398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7721099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6669359207153</t>
+    <t xml:space="preserve">11.7721109390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.666934967041</t>
   </si>
   <si>
     <t xml:space="preserve">11.5091733932495</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">11.5730295181274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8284549713135</t>
+    <t xml:space="preserve">11.8284559249878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2687730789185</t>
@@ -2957,31 +2957,31 @@
     <t xml:space="preserve">11.4791231155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4265356063843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3664360046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.663179397583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5429792404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7796249389648</t>
+    <t xml:space="preserve">11.4265365600586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3664350509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6631803512573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5429782867432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7796239852905</t>
   </si>
   <si>
     <t xml:space="preserve">11.7608423233032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4753665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6706924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8585042953491</t>
+    <t xml:space="preserve">11.4753675460815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6706914901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8585052490234</t>
   </si>
   <si>
     <t xml:space="preserve">11.8434801101685</t>
@@ -2993,19 +2993,19 @@
     <t xml:space="preserve">12.3205242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.801326751709</t>
+    <t xml:space="preserve">12.8013277053833</t>
   </si>
   <si>
     <t xml:space="preserve">12.6999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7337131500244</t>
+    <t xml:space="preserve">12.7337141036987</t>
   </si>
   <si>
     <t xml:space="preserve">12.8351316452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5684375762939</t>
+    <t xml:space="preserve">12.5684385299683</t>
   </si>
   <si>
     <t xml:space="preserve">12.6097564697266</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">12.3731117248535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4369697570801</t>
+    <t xml:space="preserve">12.4369688034058</t>
   </si>
   <si>
     <t xml:space="preserve">12.0763683319092</t>
@@ -3029,34 +3029,34 @@
     <t xml:space="preserve">12.3505754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4745321273804</t>
+    <t xml:space="preserve">12.4745311737061</t>
   </si>
   <si>
     <t xml:space="preserve">12.493311882019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.470775604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8276195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938137054443</t>
+    <t xml:space="preserve">12.4707746505737</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8276214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938146591187</t>
   </si>
   <si>
     <t xml:space="preserve">12.6585884094238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5984878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4557495117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5158491134644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3468189239502</t>
+    <t xml:space="preserve">12.5984888076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4557504653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5158500671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3468179702759</t>
   </si>
   <si>
     <t xml:space="preserve">12.21910572052</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">12.6661014556885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6247825622559</t>
+    <t xml:space="preserve">12.6247816085815</t>
   </si>
   <si>
     <t xml:space="preserve">12.508337020874</t>
@@ -3083,19 +3083,19 @@
     <t xml:space="preserve">12.2641820907593</t>
   </si>
   <si>
-    <t xml:space="preserve">11.974949836731</t>
+    <t xml:space="preserve">11.9749488830566</t>
   </si>
   <si>
     <t xml:space="preserve">12.1552495956421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8847999572754</t>
+    <t xml:space="preserve">11.8847990036011</t>
   </si>
   <si>
     <t xml:space="preserve">12.0688562393188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1101760864258</t>
+    <t xml:space="preserve">12.1101751327515</t>
   </si>
   <si>
     <t xml:space="preserve">12.2078371047974</t>
@@ -3107,10 +3107,10 @@
     <t xml:space="preserve">12.5120944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6285371780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4257001876831</t>
+    <t xml:space="preserve">12.6285381317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4257011413574</t>
   </si>
   <si>
     <t xml:space="preserve">11.8547487258911</t>
@@ -3122,16 +3122,16 @@
     <t xml:space="preserve">11.8096742630005</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6181039810181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3326292037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7645988464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5993232727051</t>
+    <t xml:space="preserve">11.6181049346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3326282501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7645998001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5993242263794</t>
   </si>
   <si>
     <t xml:space="preserve">11.5842990875244</t>
@@ -3146,7 +3146,7 @@
     <t xml:space="preserve">11.7120113372803</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8772869110107</t>
+    <t xml:space="preserve">11.8772859573364</t>
   </si>
   <si>
     <t xml:space="preserve">11.8359680175781</t>
@@ -3158,67 +3158,67 @@
     <t xml:space="preserve">12.200325012207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2904758453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1139316558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4031620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9448986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0989055633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1514940261841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0801248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7007436752319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5241994857788</t>
+    <t xml:space="preserve">12.2904748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1139307022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4031629562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.944899559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0989065170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1514921188354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0801239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7007417678833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5241985321045</t>
   </si>
   <si>
     <t xml:space="preserve">10.8255348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6452341079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8893918991089</t>
+    <t xml:space="preserve">10.6452350616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8893909454346</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499914169312</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6443996429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8209419250488</t>
+    <t xml:space="preserve">11.64439868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8209428787231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275363922119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8885545730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5834617614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4332113265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4106750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1393890380859</t>
+    <t xml:space="preserve">11.8885555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5834636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4332122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4106760025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1393899917603</t>
   </si>
   <si>
     <t xml:space="preserve">13.2070016860962</t>
@@ -3227,43 +3227,43 @@
     <t xml:space="preserve">13.5600900650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2370519638062</t>
+    <t xml:space="preserve">13.2370529174805</t>
   </si>
   <si>
     <t xml:space="preserve">13.2595891952515</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2220268249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6727781295776</t>
+    <t xml:space="preserve">13.2220277786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.672779083252</t>
   </si>
   <si>
     <t xml:space="preserve">13.3572521209717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3797903060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2746162414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5375528335571</t>
+    <t xml:space="preserve">13.379789352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2746133804321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5375518798828</t>
   </si>
   <si>
     <t xml:space="preserve">13.1882209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821264266968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2896394729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2295398712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619253158569</t>
+    <t xml:space="preserve">13.2821273803711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2896404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2295408248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619272232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.9327945709229</t>
@@ -3272,31 +3272,31 @@
     <t xml:space="preserve">13.1731948852539</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1919765472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1957321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0154323577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8238639831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3272018432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361333847046</t>
+    <t xml:space="preserve">13.1919775009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1957330703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0154333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.82386302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3272008895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361343383789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4962339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4323759078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.349739074707</t>
+    <t xml:space="preserve">13.4323768615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3497400283813</t>
   </si>
   <si>
     <t xml:space="preserve">13.3384704589844</t>
@@ -3308,10 +3308,10 @@
     <t xml:space="preserve">13.4135961532593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4248666763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3985710144043</t>
+    <t xml:space="preserve">13.4248657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.39857006073</t>
   </si>
   <si>
     <t xml:space="preserve">13.391058921814</t>
@@ -3326,28 +3326,28 @@
     <t xml:space="preserve">13.9582529067993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8305397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.89439868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8380527496338</t>
+    <t xml:space="preserve">13.8305406570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943977355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8380546569824</t>
   </si>
   <si>
     <t xml:space="preserve">13.9319591522217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7328767776489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4398899078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4060821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1093397140503</t>
+    <t xml:space="preserve">13.7328796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4398908615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4060831069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1093406677246</t>
   </si>
   <si>
     <t xml:space="preserve">13.3009080886841</t>
@@ -3356,7 +3356,7 @@
     <t xml:space="preserve">13.0417261123657</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4887218475342</t>
+    <t xml:space="preserve">13.4887208938599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5676012039185</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">13.7216081619263</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3526592254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5855484008789</t>
+    <t xml:space="preserve">14.3526611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5855493545532</t>
   </si>
   <si>
     <t xml:space="preserve">15.0550804138184</t>
@@ -3377,25 +3377,25 @@
     <t xml:space="preserve">15.092643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0250291824341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1978187561035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447284698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7207717895508</t>
+    <t xml:space="preserve">15.0250301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1978178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447303771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7207727432251</t>
   </si>
   <si>
     <t xml:space="preserve">14.9198560714722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8221921920776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5329599380493</t>
+    <t xml:space="preserve">14.8221912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5329608917236</t>
   </si>
   <si>
     <t xml:space="preserve">14.6005725860596</t>
@@ -3410,28 +3410,28 @@
     <t xml:space="preserve">14.9499053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7846307754517</t>
+    <t xml:space="preserve">14.784628868103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7095060348511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6644287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240303039551</t>
+    <t xml:space="preserve">14.6644296646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240293502808</t>
   </si>
   <si>
     <t xml:space="preserve">14.7958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7620906829834</t>
+    <t xml:space="preserve">14.762092590332</t>
   </si>
   <si>
     <t xml:space="preserve">14.9123430252075</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6606740951538</t>
+    <t xml:space="preserve">14.6606712341309</t>
   </si>
   <si>
     <t xml:space="preserve">14.4090051651001</t>
@@ -3440,64 +3440,64 @@
     <t xml:space="preserve">14.1948976516724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1197738647461</t>
+    <t xml:space="preserve">14.1197729110718</t>
   </si>
   <si>
     <t xml:space="preserve">14.202410697937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.277533531189</t>
+    <t xml:space="preserve">14.2775354385376</t>
   </si>
   <si>
     <t xml:space="preserve">14.3226108551025</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4202728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714408874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2925596237183</t>
+    <t xml:space="preserve">14.4202718734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714418411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2925605773926</t>
   </si>
   <si>
     <t xml:space="preserve">14.4653482437134</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7470655441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5930614471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8898057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8484869003296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2504053115845</t>
+    <t xml:space="preserve">14.7470674514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5930624008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8898048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8484859466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2504043579102</t>
   </si>
   <si>
     <t xml:space="preserve">15.1001558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1151819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0701065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7245292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7508230209351</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8146810531616</t>
+    <t xml:space="preserve">15.1151809692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0701055526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827907562256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7245283126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7508239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.814679145813</t>
   </si>
   <si>
     <t xml:space="preserve">14.818434715271</t>
@@ -3506,73 +3506,73 @@
     <t xml:space="preserve">14.9837112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0175180435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.792142868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9611749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1602573394775</t>
+    <t xml:space="preserve">15.0175189971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7921438217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9611740112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1602563858032</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.085129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1377182006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.355583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2579193115234</t>
+    <t xml:space="preserve">15.0851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1377191543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3555822372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2579183578491</t>
   </si>
   <si>
     <t xml:space="preserve">15.2804565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2729444503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8664321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8438968658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6410570144653</t>
+    <t xml:space="preserve">15.2729434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.86643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8438940048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.641056060791</t>
   </si>
   <si>
     <t xml:space="preserve">15.708667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6711091995239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1603355407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.081428527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8841571807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8999395370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9551763534546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0419750213623</t>
+    <t xml:space="preserve">15.671106338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1603336334229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0814266204834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8841562271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8999404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9551753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0419731140137</t>
   </si>
   <si>
     <t xml:space="preserve">16.0025196075439</t>
@@ -3581,25 +3581,25 @@
     <t xml:space="preserve">16.0972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1445560455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4601879119873</t>
+    <t xml:space="preserve">16.144552230835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4601860046387</t>
   </si>
   <si>
     <t xml:space="preserve">16.4522953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4128398895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3260440826416</t>
+    <t xml:space="preserve">16.412841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3260402679443</t>
   </si>
   <si>
     <t xml:space="preserve">16.3497142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.99462890625</t>
+    <t xml:space="preserve">15.9946298599243</t>
   </si>
   <si>
     <t xml:space="preserve">16.1208820343018</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">16.0183010101318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9472846984863</t>
+    <t xml:space="preserve">15.9472827911377</t>
   </si>
   <si>
     <t xml:space="preserve">15.8762683868408</t>
@@ -3620,13 +3620,13 @@
     <t xml:space="preserve">16.2392444610596</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2471351623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5312023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1287746429443</t>
+    <t xml:space="preserve">16.2471332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5312042236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1287727355957</t>
   </si>
   <si>
     <t xml:space="preserve">16.2155704498291</t>
@@ -3635,7 +3635,7 @@
     <t xml:space="preserve">16.3023700714111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5943279266357</t>
+    <t xml:space="preserve">16.5943298339844</t>
   </si>
   <si>
     <t xml:space="preserve">16.5075302124023</t>
@@ -3650,10 +3650,10 @@
     <t xml:space="preserve">16.2550258636475</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5233154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8073806762695</t>
+    <t xml:space="preserve">16.5233116149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8073787689209</t>
   </si>
   <si>
     <t xml:space="preserve">17.1624660491943</t>
@@ -3662,76 +3662,76 @@
     <t xml:space="preserve">17.5254421234131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3281707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1940288543701</t>
+    <t xml:space="preserve">17.3281726837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1940307617188</t>
   </si>
   <si>
     <t xml:space="preserve">17.2492656707764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1387920379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4702072143555</t>
+    <t xml:space="preserve">17.1387939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4702053070068</t>
   </si>
   <si>
     <t xml:space="preserve">17.4938793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2808284759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4070816040039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5727882385254</t>
+    <t xml:space="preserve">17.2808265686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4070796966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5727863311768</t>
   </si>
   <si>
     <t xml:space="preserve">17.9042015075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9120922088623</t>
+    <t xml:space="preserve">17.9120903015137</t>
   </si>
   <si>
     <t xml:space="preserve">18.1093616485596</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1172485351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2592849731445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3224105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2435035705566</t>
+    <t xml:space="preserve">18.1172504425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2592868804932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3224124908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2435054779053</t>
   </si>
   <si>
     <t xml:space="preserve">18.4644451141357</t>
   </si>
   <si>
-    <t xml:space="preserve">18.251392364502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.282958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.424991607666</t>
+    <t xml:space="preserve">18.2513942718506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2829570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4249935150146</t>
   </si>
   <si>
     <t xml:space="preserve">18.3539752960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4407730102539</t>
+    <t xml:space="preserve">18.4407749176025</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906982421875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6696090698242</t>
+    <t xml:space="preserve">18.6696071624756</t>
   </si>
   <si>
     <t xml:space="preserve">18.748514175415</t>
@@ -3746,43 +3746,43 @@
     <t xml:space="preserve">18.7011699676514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.756404876709</t>
+    <t xml:space="preserve">18.7564067840576</t>
   </si>
   <si>
     <t xml:space="preserve">18.7406234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6459331512451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7169513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5749187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.843204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8984413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9536743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1903991699219</t>
+    <t xml:space="preserve">18.6459312438965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7169494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5749206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8432025909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8984394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9536762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1903972625732</t>
   </si>
   <si>
     <t xml:space="preserve">19.0878200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5591354370117</t>
+    <t xml:space="preserve">18.5591373443604</t>
   </si>
   <si>
     <t xml:space="preserve">18.8589859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9378929138184</t>
+    <t xml:space="preserve">18.937894821167</t>
   </si>
   <si>
     <t xml:space="preserve">19.2614154815674</t>
@@ -3797,7 +3797,7 @@
     <t xml:space="preserve">18.5985889434814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721881866455</t>
+    <t xml:space="preserve">18.7721862792969</t>
   </si>
   <si>
     <t xml:space="preserve">18.6538257598877</t>
@@ -3812,7 +3812,7 @@
     <t xml:space="preserve">18.2356128692627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1409244537354</t>
+    <t xml:space="preserve">18.1409225463867</t>
   </si>
   <si>
     <t xml:space="preserve">18.43288230896</t>
@@ -3836,13 +3836,13 @@
     <t xml:space="preserve">19.5297031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6007213592529</t>
+    <t xml:space="preserve">19.6007194519043</t>
   </si>
   <si>
     <t xml:space="preserve">19.8374423980713</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6322822570801</t>
+    <t xml:space="preserve">19.6322803497314</t>
   </si>
   <si>
     <t xml:space="preserve">19.6954078674316</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">19.9952583312988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.066276550293</t>
+    <t xml:space="preserve">20.0662784576416</t>
   </si>
   <si>
     <t xml:space="preserve">20.1057300567627</t>
@@ -3866,10 +3866,10 @@
     <t xml:space="preserve">20.0741672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0189323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.239875793457</t>
+    <t xml:space="preserve">20.0189304351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2398738861084</t>
   </si>
   <si>
     <t xml:space="preserve">20.9027004241943</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">20.9816074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6659774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2162017822266</t>
+    <t xml:space="preserve">20.6659755706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2162036895752</t>
   </si>
   <si>
     <t xml:space="preserve">20.1372947692871</t>
@@ -3905,16 +3905,16 @@
     <t xml:space="preserve">19.316650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3324317932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4744682312012</t>
+    <t xml:space="preserve">19.3324337005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4744663238525</t>
   </si>
   <si>
     <t xml:space="preserve">19.3087596893311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.174617767334</t>
+    <t xml:space="preserve">19.1746158599854</t>
   </si>
   <si>
     <t xml:space="preserve">19.2377433776855</t>
@@ -3929,10 +3929,10 @@
     <t xml:space="preserve">19.0246925354004</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8116416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0168018341064</t>
+    <t xml:space="preserve">18.8116397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0168037414551</t>
   </si>
   <si>
     <t xml:space="preserve">18.7248420715332</t>
@@ -3947,13 +3947,13 @@
     <t xml:space="preserve">19.3561058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4113426208496</t>
+    <t xml:space="preserve">19.411340713501</t>
   </si>
   <si>
     <t xml:space="preserve">19.7269725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9005680084229</t>
+    <t xml:space="preserve">19.9005699157715</t>
   </si>
   <si>
     <t xml:space="preserve">19.9479160308838</t>
@@ -3965,7 +3965,7 @@
     <t xml:space="preserve">19.5770454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6165008544922</t>
+    <t xml:space="preserve">19.6165027618408</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268211364746</t>
@@ -3974,22 +3974,22 @@
     <t xml:space="preserve">20.8711395263672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9342651367188</t>
+    <t xml:space="preserve">20.9342632293701</t>
   </si>
   <si>
     <t xml:space="preserve">20.5791778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6817588806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3187808990479</t>
+    <t xml:space="preserve">20.6817569732666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3187828063965</t>
   </si>
   <si>
     <t xml:space="preserve">19.8847885131836</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2119407653809</t>
+    <t xml:space="preserve">18.2119426727295</t>
   </si>
   <si>
     <t xml:space="preserve">18.2671756744385</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">18.3934288024902</t>
   </si>
   <si>
-    <t xml:space="preserve">19.032585144043</t>
+    <t xml:space="preserve">19.0325832366943</t>
   </si>
   <si>
     <t xml:space="preserve">18.8747673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3303031921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7958602905273</t>
+    <t xml:space="preserve">18.33030128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7958583831787</t>
   </si>
   <si>
     <t xml:space="preserve">18.3697566986084</t>
@@ -4019,31 +4019,31 @@
     <t xml:space="preserve">17.8095111846924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7463836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9278697967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416759490967</t>
+    <t xml:space="preserve">17.7463855743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9278736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416721343994</t>
   </si>
   <si>
     <t xml:space="preserve">17.1782474517822</t>
   </si>
   <si>
-    <t xml:space="preserve">16.886287689209</t>
+    <t xml:space="preserve">16.8862895965576</t>
   </si>
   <si>
     <t xml:space="preserve">16.6337833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4028186798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4501657485962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6632165908813</t>
+    <t xml:space="preserve">15.4028205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4501647949219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.663215637207</t>
   </si>
   <si>
     <t xml:space="preserve">17.0756664276123</t>
@@ -4052,16 +4052,16 @@
     <t xml:space="preserve">15.1897687911987</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5093460083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8525953292847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0441036224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.791597366333</t>
+    <t xml:space="preserve">15.5093469619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8525943756104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0441055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7915992736816</t>
   </si>
   <si>
     <t xml:space="preserve">16.4759654998779</t>
@@ -4070,13 +4070,13 @@
     <t xml:space="preserve">16.8152713775635</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7837066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4286231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.744255065918</t>
+    <t xml:space="preserve">16.7837085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4286212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7442512512207</t>
   </si>
   <si>
     <t xml:space="preserve">17.2413730621338</t>
@@ -4088,7 +4088,7 @@
     <t xml:space="preserve">16.6732349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7600345611572</t>
+    <t xml:space="preserve">16.7600364685059</t>
   </si>
   <si>
     <t xml:space="preserve">16.3181533813477</t>
@@ -4097,13 +4097,13 @@
     <t xml:space="preserve">15.7579050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4107103347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815761566162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9157199859619</t>
+    <t xml:space="preserve">15.4107112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815771102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9157209396362</t>
   </si>
   <si>
     <t xml:space="preserve">15.8920488357544</t>
@@ -4112,58 +4112,58 @@
     <t xml:space="preserve">15.8683776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6277074813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7973585128784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539587020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8289232254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0893173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0735378265381</t>
+    <t xml:space="preserve">15.6277084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7973594665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8289213180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.089319229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0735397338867</t>
   </si>
   <si>
     <t xml:space="preserve">16.1761169433594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9236135482788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6395444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5132913589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964427947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1660966873169</t>
+    <t xml:space="preserve">15.9236125946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6395435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5132904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964447021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1660957336426</t>
   </si>
   <si>
     <t xml:space="preserve">15.6868877410889</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7381782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7657976150513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0261936187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8052501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4583625793457</t>
+    <t xml:space="preserve">15.7381792068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.765796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0261917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8052530288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4583644866943</t>
   </si>
   <si>
     <t xml:space="preserve">16.0873756408691</t>
@@ -4184,13 +4184,13 @@
     <t xml:space="preserve">16.8209209442139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5932674407959</t>
+    <t xml:space="preserve">16.5932693481445</t>
   </si>
   <si>
     <t xml:space="preserve">16.8082733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5595417022705</t>
+    <t xml:space="preserve">16.5595397949219</t>
   </si>
   <si>
     <t xml:space="preserve">16.871509552002</t>
@@ -4205,7 +4205,7 @@
     <t xml:space="preserve">16.2012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7298974990845</t>
+    <t xml:space="preserve">14.7298984527588</t>
   </si>
   <si>
     <t xml:space="preserve">14.4390106201172</t>
@@ -4214,16 +4214,16 @@
     <t xml:space="preserve">14.6287202835083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9828443527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2830266952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3715581893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4432239532471</t>
+    <t xml:space="preserve">14.9828453063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2830276489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3715591430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4432249069214</t>
   </si>
   <si>
     <t xml:space="preserve">14.506462097168</t>
@@ -4232,19 +4232,19 @@
     <t xml:space="preserve">14.2197895050049</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6750936508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5191087722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4811668395996</t>
+    <t xml:space="preserve">14.6750926971436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5191097259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4811658859253</t>
   </si>
   <si>
     <t xml:space="preserve">14.2745952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9837055206299</t>
+    <t xml:space="preserve">13.9837064743042</t>
   </si>
   <si>
     <t xml:space="preserve">13.8277225494385</t>
@@ -4253,13 +4253,13 @@
     <t xml:space="preserve">13.9289026260376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3724212646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7771339416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1523380279541</t>
+    <t xml:space="preserve">13.3724203109741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7771348953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1523370742798</t>
   </si>
   <si>
     <t xml:space="preserve">14.3420476913452</t>
@@ -4268,7 +4268,7 @@
     <t xml:space="preserve">14.1354742050171</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3546943664551</t>
+    <t xml:space="preserve">14.3546934127808</t>
   </si>
   <si>
     <t xml:space="preserve">14.1987113952637</t>
@@ -4277,7 +4277,7 @@
     <t xml:space="preserve">13.6211519241333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6801719665527</t>
+    <t xml:space="preserve">13.6801729202271</t>
   </si>
   <si>
     <t xml:space="preserve">13.8108596801758</t>
@@ -4286,22 +4286,22 @@
     <t xml:space="preserve">14.2493000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6928195953369</t>
+    <t xml:space="preserve">13.6928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">13.7602710723877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7939987182617</t>
+    <t xml:space="preserve">13.7939977645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.4609518051147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5494823455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3631267547607</t>
+    <t xml:space="preserve">13.5494832992554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3631258010864</t>
   </si>
   <si>
     <t xml:space="preserve">14.3926362991333</t>
@@ -4322,40 +4322,40 @@
     <t xml:space="preserve">14.2956733703613</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1944942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600887298584</t>
+    <t xml:space="preserve">14.1944952011108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600877761841</t>
   </si>
   <si>
     <t xml:space="preserve">14.5022468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5654830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6371507644653</t>
+    <t xml:space="preserve">14.565484046936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6371517181396</t>
   </si>
   <si>
     <t xml:space="preserve">14.3757734298706</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4643068313599</t>
+    <t xml:space="preserve">14.4643049240112</t>
   </si>
   <si>
     <t xml:space="preserve">13.9794912338257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7687034606934</t>
+    <t xml:space="preserve">13.768702507019</t>
   </si>
   <si>
     <t xml:space="preserve">13.9541959762573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9415502548218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8530178070068</t>
+    <t xml:space="preserve">13.9415493011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8530187606812</t>
   </si>
   <si>
     <t xml:space="preserve">13.4651679992676</t>
@@ -4364,13 +4364,13 @@
     <t xml:space="preserve">13.4483041763306</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6380138397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.435658454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1447687149048</t>
+    <t xml:space="preserve">13.6380128860474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4356575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1447696685791</t>
   </si>
   <si>
     <t xml:space="preserve">13.6295833587646</t>
@@ -4382,7 +4382,7 @@
     <t xml:space="preserve">13.4946775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5199728012085</t>
+    <t xml:space="preserve">13.5199718475342</t>
   </si>
   <si>
     <t xml:space="preserve">14.1692008972168</t>
@@ -4394,16 +4394,16 @@
     <t xml:space="preserve">14.0722389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9162540435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7644872665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8572340011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4735994338989</t>
+    <t xml:space="preserve">13.9162530899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7644882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8572330474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4735984802246</t>
   </si>
   <si>
     <t xml:space="preserve">13.1321220397949</t>
@@ -4421,10 +4421,10 @@
     <t xml:space="preserve">12.4112253189087</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0065107345581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3985776901245</t>
+    <t xml:space="preserve">12.0065116882324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3985767364502</t>
   </si>
   <si>
     <t xml:space="preserve">12.6009340286255</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">13.1532011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9044704437256</t>
+    <t xml:space="preserve">12.9044694900513</t>
   </si>
   <si>
     <t xml:space="preserve">12.7231922149658</t>
@@ -4442,16 +4442,16 @@
     <t xml:space="preserve">12.5039710998535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5503454208374</t>
+    <t xml:space="preserve">12.5503463745117</t>
   </si>
   <si>
     <t xml:space="preserve">12.4280881881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7324857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0908269882202</t>
+    <t xml:space="preserve">11.7324867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0908260345459</t>
   </si>
   <si>
     <t xml:space="preserve">12.5292663574219</t>
@@ -4463,13 +4463,13 @@
     <t xml:space="preserve">12.8791751861572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8665294647217</t>
+    <t xml:space="preserve">12.8665285110474</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538808822632</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8960390090942</t>
+    <t xml:space="preserve">12.8960380554199</t>
   </si>
   <si>
     <t xml:space="preserve">13.3007526397705</t>
@@ -4478,7 +4478,7 @@
     <t xml:space="preserve">13.6843872070312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5326194763184</t>
+    <t xml:space="preserve">13.532618522644</t>
   </si>
   <si>
     <t xml:space="preserve">13.7897806167603</t>
@@ -4490,25 +4490,25 @@
     <t xml:space="preserve">13.9963550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1101808547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3462629318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7214660644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9449024200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0292177200317</t>
+    <t xml:space="preserve">14.110179901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3462619781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7214670181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9449043273926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0292186737061</t>
   </si>
   <si>
     <t xml:space="preserve">16.1885547637939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8588638305664</t>
+    <t xml:space="preserve">16.8588619232178</t>
   </si>
   <si>
     <t xml:space="preserve">16.6860160827637</t>
@@ -4523,7 +4523,7 @@
     <t xml:space="preserve">16.799840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3740501403809</t>
+    <t xml:space="preserve">16.3740482330322</t>
   </si>
   <si>
     <t xml:space="preserve">16.441499710083</t>
@@ -4532,31 +4532,31 @@
     <t xml:space="preserve">16.4035587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3909111022949</t>
+    <t xml:space="preserve">16.3909130096436</t>
   </si>
   <si>
     <t xml:space="preserve">16.1801242828369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2349262237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3023777008057</t>
+    <t xml:space="preserve">16.2349281311035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993453979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3023796081543</t>
   </si>
   <si>
     <t xml:space="preserve">16.6059150695801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5047359466553</t>
+    <t xml:space="preserve">16.5047378540039</t>
   </si>
   <si>
     <t xml:space="preserve">16.5089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155265808105</t>
+    <t xml:space="preserve">16.7155246734619</t>
   </si>
   <si>
     <t xml:space="preserve">16.9389610290527</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">17.0570030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9558258056641</t>
+    <t xml:space="preserve">16.9558238983154</t>
   </si>
   <si>
     <t xml:space="preserve">16.2855167388916</t>
@@ -4589,13 +4589,13 @@
     <t xml:space="preserve">17.3774013519287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4617176055908</t>
+    <t xml:space="preserve">17.4617156982422</t>
   </si>
   <si>
     <t xml:space="preserve">17.6893672943115</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7146644592285</t>
+    <t xml:space="preserve">17.7146625518799</t>
   </si>
   <si>
     <t xml:space="preserve">17.8579998016357</t>
@@ -4616,13 +4616,13 @@
     <t xml:space="preserve">17.9760398864746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9676094055176</t>
+    <t xml:space="preserve">17.9676074981689</t>
   </si>
   <si>
     <t xml:space="preserve">18.3807544708252</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3891868591309</t>
+    <t xml:space="preserve">18.3891849517822</t>
   </si>
   <si>
     <t xml:space="preserve">18.8697834014893</t>
@@ -4637,10 +4637,10 @@
     <t xml:space="preserve">19.1901817321777</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1311626434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1648864746094</t>
+    <t xml:space="preserve">19.131160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.164888381958</t>
   </si>
   <si>
     <t xml:space="preserve">18.8444881439209</t>
@@ -4652,7 +4652,7 @@
     <t xml:space="preserve">19.375675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3588104248047</t>
+    <t xml:space="preserve">19.3588123321533</t>
   </si>
   <si>
     <t xml:space="preserve">19.3419494628906</t>
@@ -4661,22 +4661,22 @@
     <t xml:space="preserve">19.3841075897217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4431285858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3250885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2913589477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3166542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8141174316406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8984317779541</t>
+    <t xml:space="preserve">19.4431266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3250865936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2913608551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3166561126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.814115524292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8984336853027</t>
   </si>
   <si>
     <t xml:space="preserve">19.9405899047852</t>
@@ -4691,19 +4691,19 @@
     <t xml:space="preserve">19.8309783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1564540863037</t>
+    <t xml:space="preserve">19.1564559936523</t>
   </si>
   <si>
     <t xml:space="preserve">19.5358753204346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0637092590332</t>
+    <t xml:space="preserve">19.0637111663818</t>
   </si>
   <si>
     <t xml:space="preserve">19.0890026092529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2070465087891</t>
+    <t xml:space="preserve">19.2070446014404</t>
   </si>
   <si>
     <t xml:space="preserve">19.0552787780762</t>
@@ -4718,19 +4718,19 @@
     <t xml:space="preserve">18.9456672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9793949127197</t>
+    <t xml:space="preserve">18.9793930053711</t>
   </si>
   <si>
     <t xml:space="preserve">19.1058673858643</t>
   </si>
   <si>
-    <t xml:space="preserve">18.895076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8023319244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1952610015869</t>
+    <t xml:space="preserve">18.8950786590576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8023300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1952590942383</t>
   </si>
   <si>
     <t xml:space="preserve">17.6134834289551</t>
@@ -4739,13 +4739,13 @@
     <t xml:space="preserve">16.7745456695557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9811191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.239143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114917755127</t>
+    <t xml:space="preserve">16.9811172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2391452789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114936828613</t>
   </si>
   <si>
     <t xml:space="preserve">16.4667949676514</t>
@@ -4754,10 +4754,10 @@
     <t xml:space="preserve">16.9052352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3782634735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1126728057861</t>
+    <t xml:space="preserve">16.3782653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1126708984375</t>
   </si>
   <si>
     <t xml:space="preserve">16.1337490081787</t>
@@ -4772,7 +4772,7 @@
     <t xml:space="preserve">16.6101322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.546895980835</t>
+    <t xml:space="preserve">16.5468940734863</t>
   </si>
   <si>
     <t xml:space="preserve">16.3403205871582</t>
@@ -4787,10 +4787,10 @@
     <t xml:space="preserve">17.158182144165</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1244564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0232772827148</t>
+    <t xml:space="preserve">17.124454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0232791900635</t>
   </si>
   <si>
     <t xml:space="preserve">17.2003383636475</t>
@@ -4799,34 +4799,34 @@
     <t xml:space="preserve">17.2424983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.107593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0148448944092</t>
+    <t xml:space="preserve">17.1075916290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0148468017578</t>
   </si>
   <si>
     <t xml:space="preserve">17.0401401519775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0654354095459</t>
+    <t xml:space="preserve">17.0654335021973</t>
   </si>
   <si>
     <t xml:space="preserve">16.8124885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5806217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9726867675781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.08229637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8546466827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9895496368408</t>
+    <t xml:space="preserve">16.5806198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9726848602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0822982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8546447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9895515441895</t>
   </si>
   <si>
     <t xml:space="preserve">17.0738658905029</t>
@@ -4844,10 +4844,10 @@
     <t xml:space="preserve">17.3769779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0168342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8097515106201</t>
+    <t xml:space="preserve">17.0168323516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8097496032715</t>
   </si>
   <si>
     <t xml:space="preserve">17.2014083862305</t>
@@ -4856,28 +4856,28 @@
     <t xml:space="preserve">17.1743984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0753574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7242183685303</t>
+    <t xml:space="preserve">17.0753593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">17.0213356018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4129943847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4580116271973</t>
+    <t xml:space="preserve">17.412992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4580097198486</t>
   </si>
   <si>
     <t xml:space="preserve">17.647087097168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6425857543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721790313721</t>
+    <t xml:space="preserve">17.6425838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721771240234</t>
   </si>
   <si>
     <t xml:space="preserve">17.6020679473877</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">18.0162353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8496704101562</t>
+    <t xml:space="preserve">17.8496685028076</t>
   </si>
   <si>
     <t xml:space="preserve">17.8136539459229</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">17.4715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5750579833984</t>
+    <t xml:space="preserve">17.5750598907471</t>
   </si>
   <si>
     <t xml:space="preserve">17.786642074585</t>
@@ -4949,7 +4949,7 @@
     <t xml:space="preserve">17.8541698455811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9667148590088</t>
+    <t xml:space="preserve">17.9667167663574</t>
   </si>
   <si>
     <t xml:space="preserve">17.9036903381348</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">18.1602935791016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2863445281982</t>
+    <t xml:space="preserve">18.2863426208496</t>
   </si>
   <si>
     <t xml:space="preserve">18.2323226928711</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">18.2413272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1783008575439</t>
+    <t xml:space="preserve">18.1783027648926</t>
   </si>
   <si>
     <t xml:space="preserve">18.2683372497559</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">19.0066337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6284809112549</t>
+    <t xml:space="preserve">18.6284828186035</t>
   </si>
   <si>
     <t xml:space="preserve">18.6014709472656</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">18.6104755401611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.700511932373</t>
+    <t xml:space="preserve">18.7005100250244</t>
   </si>
   <si>
     <t xml:space="preserve">18.7365245819092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8895874023438</t>
+    <t xml:space="preserve">18.8895854949951</t>
   </si>
   <si>
     <t xml:space="preserve">18.7545318603516</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">18.8715782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5924663543701</t>
+    <t xml:space="preserve">18.5924682617188</t>
   </si>
   <si>
     <t xml:space="preserve">18.3403663635254</t>
@@ -5033,10 +5033,10 @@
     <t xml:space="preserve">18.5114345550537</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0426464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.132682800293</t>
+    <t xml:space="preserve">19.0426483154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1326847076416</t>
   </si>
   <si>
     <t xml:space="preserve">19.2497310638428</t>
@@ -5048,16 +5048,16 @@
     <t xml:space="preserve">19.1867046356201</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0876655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.934606552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9706192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0516510009766</t>
+    <t xml:space="preserve">19.08766746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9346046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9706172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0516529083252</t>
   </si>
   <si>
     <t xml:space="preserve">19.0246410369873</t>
@@ -5072,31 +5072,31 @@
     <t xml:space="preserve">19.1957092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8625755310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.790548324585</t>
+    <t xml:space="preserve">18.8625774383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7905464172363</t>
   </si>
   <si>
     <t xml:space="preserve">18.7815437316895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8535709381104</t>
+    <t xml:space="preserve">18.853572845459</t>
   </si>
   <si>
     <t xml:space="preserve">18.619478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2593326568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493690490723</t>
+    <t xml:space="preserve">18.259334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3493671417236</t>
   </si>
   <si>
     <t xml:space="preserve">18.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3313636779785</t>
+    <t xml:space="preserve">18.3313617706299</t>
   </si>
   <si>
     <t xml:space="preserve">18.0702571868896</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">17.4670143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4805221557617</t>
+    <t xml:space="preserve">17.4805202484131</t>
   </si>
   <si>
     <t xml:space="preserve">17.6200752258301</t>
@@ -5126,13 +5126,13 @@
     <t xml:space="preserve">17.8991870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8901863098145</t>
+    <t xml:space="preserve">17.8901844024658</t>
   </si>
   <si>
     <t xml:space="preserve">18.1422863006592</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4304027557373</t>
+    <t xml:space="preserve">18.4304008483887</t>
   </si>
   <si>
     <t xml:space="preserve">18.4213981628418</t>
@@ -5147,10 +5147,10 @@
     <t xml:space="preserve">18.7725391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2047138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4388084411621</t>
+    <t xml:space="preserve">19.2047119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4388065338135</t>
   </si>
   <si>
     <t xml:space="preserve">19.6278820037842</t>
@@ -5162,19 +5162,19 @@
     <t xml:space="preserve">20.0510520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9069957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8439712524414</t>
+    <t xml:space="preserve">19.9069938659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8439693450928</t>
   </si>
   <si>
     <t xml:space="preserve">19.7899475097656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8979930877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8079566955566</t>
+    <t xml:space="preserve">19.8979911804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.807954788208</t>
   </si>
   <si>
     <t xml:space="preserve">19.6729011535645</t>
@@ -5183,7 +5183,7 @@
     <t xml:space="preserve">19.9520130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0960712432861</t>
+    <t xml:space="preserve">20.0960693359375</t>
   </si>
   <si>
     <t xml:space="preserve">20.0690612792969</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">20.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5372486114502</t>
+    <t xml:space="preserve">20.5372467041016</t>
   </si>
   <si>
     <t xml:space="preserve">20.996431350708</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">21.2215213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2755432128906</t>
+    <t xml:space="preserve">21.2755451202393</t>
   </si>
   <si>
     <t xml:space="preserve">21.2935523986816</t>
@@ -5237,22 +5237,22 @@
     <t xml:space="preserve">21.7887516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9598178863525</t>
+    <t xml:space="preserve">21.9598197937012</t>
   </si>
   <si>
     <t xml:space="preserve">22.3199634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">21.671703338623</t>
+    <t xml:space="preserve">21.6717052459717</t>
   </si>
   <si>
     <t xml:space="preserve">22.0948734283447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2659435272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.419002532959</t>
+    <t xml:space="preserve">22.265941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4190044403076</t>
   </si>
   <si>
     <t xml:space="preserve">22.5090389251709</t>
@@ -5261,10 +5261,10 @@
     <t xml:space="preserve">22.5900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.563060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.905200958252</t>
+    <t xml:space="preserve">22.5630626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9051990509033</t>
   </si>
   <si>
     <t xml:space="preserve">22.797155380249</t>
@@ -5273,7 +5273,7 @@
     <t xml:space="preserve">23.0762672424316</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0222454071045</t>
+    <t xml:space="preserve">23.0222473144531</t>
   </si>
   <si>
     <t xml:space="preserve">23.3103618621826</t>
@@ -5288,10 +5288,10 @@
     <t xml:space="preserve">23.3193645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2293281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4003982543945</t>
+    <t xml:space="preserve">23.2293300628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4003963470459</t>
   </si>
   <si>
     <t xml:space="preserve">23.2563400268555</t>
@@ -5300,7 +5300,7 @@
     <t xml:space="preserve">23.6705074310303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5894756317139</t>
+    <t xml:space="preserve">23.5894737243652</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264472961426</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">23.8865947723389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7065200805664</t>
+    <t xml:space="preserve">23.706521987915</t>
   </si>
   <si>
     <t xml:space="preserve">23.6975173950195</t>
@@ -5360,7 +5360,7 @@
     <t xml:space="preserve">21.6987152099609</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9148006439209</t>
+    <t xml:space="preserve">21.9148025512695</t>
   </si>
   <si>
     <t xml:space="preserve">22.5720653533936</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">22.3559799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.310962677002</t>
+    <t xml:space="preserve">22.3109607696533</t>
   </si>
   <si>
     <t xml:space="preserve">22.1218852996826</t>
@@ -5384,19 +5384,19 @@
     <t xml:space="preserve">22.4550189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3289661407471</t>
+    <t xml:space="preserve">22.3289680480957</t>
   </si>
   <si>
     <t xml:space="preserve">22.6260871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.671106338501</t>
+    <t xml:space="preserve">22.6711044311523</t>
   </si>
   <si>
     <t xml:space="preserve">21.608678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7977542877197</t>
+    <t xml:space="preserve">21.7977523803711</t>
   </si>
   <si>
     <t xml:space="preserve">21.968822479248</t>
@@ -5414,22 +5414,22 @@
     <t xml:space="preserve">21.5996742248535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7257232666016</t>
+    <t xml:space="preserve">21.7257251739502</t>
   </si>
   <si>
     <t xml:space="preserve">21.7527370452881</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6176834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8427734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2749443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1038761138916</t>
+    <t xml:space="preserve">21.6176815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8427715301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2749462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1038780212402</t>
   </si>
   <si>
     <t xml:space="preserve">22.1578998565674</t>
@@ -5438,16 +5438,16 @@
     <t xml:space="preserve">22.2839488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3019580841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2569389343262</t>
+    <t xml:space="preserve">22.3019561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2569370269775</t>
   </si>
   <si>
     <t xml:space="preserve">22.7341289520264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9502182006836</t>
+    <t xml:space="preserve">22.950216293335</t>
   </si>
   <si>
     <t xml:space="preserve">23.1843109130859</t>
@@ -5459,13 +5459,13 @@
     <t xml:space="preserve">23.0672645568848</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4364128112793</t>
+    <t xml:space="preserve">23.4364147186279</t>
   </si>
   <si>
     <t xml:space="preserve">23.5084419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8415756225586</t>
+    <t xml:space="preserve">23.84157371521</t>
   </si>
   <si>
     <t xml:space="preserve">23.5945644378662</t>
@@ -6354,6 +6354,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.5499992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7200012207031</t>
   </si>
 </sst>
 </file>
@@ -71354,7 +71357,7 @@
     </row>
     <row r="2488">
       <c r="A2488" s="1" t="n">
-        <v>45943.6494328704</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2488" t="n">
         <v>404769</v>
@@ -71375,6 +71378,32 @@
         <v>2113</v>
       </c>
       <c r="H2488" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2489">
+      <c r="A2489" s="1" t="n">
+        <v>45944.6494675926</v>
+      </c>
+      <c r="B2489" t="n">
+        <v>435639</v>
+      </c>
+      <c r="C2489" t="n">
+        <v>32.8800010681152</v>
+      </c>
+      <c r="D2489" t="n">
+        <v>32.0099983215332</v>
+      </c>
+      <c r="E2489" t="n">
+        <v>32.2000007629395</v>
+      </c>
+      <c r="F2489" t="n">
+        <v>32.7200012207031</v>
+      </c>
+      <c r="G2489" t="s">
+        <v>2114</v>
+      </c>
+      <c r="H2489" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2115" uniqueCount="2115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2116" uniqueCount="2116">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,64 +44,64 @@
     <t xml:space="preserve">AZM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068357467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4860258102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1916131973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91191959381104</t>
+    <t xml:space="preserve">10.7068367004395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.486026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1916122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91191864013672</t>
   </si>
   <si>
     <t xml:space="preserve">9.9364538192749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.225959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0002431869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61750507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33290481567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1513500213623</t>
+    <t xml:space="preserve">10.225962638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.000244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61750793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33290672302246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15135097503662</t>
   </si>
   <si>
     <t xml:space="preserve">9.37706756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85693836212158</t>
+    <t xml:space="preserve">8.85693645477295</t>
   </si>
   <si>
     <t xml:space="preserve">9.25930309295654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53899478912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48992729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50955295562744</t>
+    <t xml:space="preserve">9.53899574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4899263381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50955390930176</t>
   </si>
   <si>
     <t xml:space="preserve">9.40160274505615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12681770324707</t>
+    <t xml:space="preserve">9.12681865692139</t>
   </si>
   <si>
     <t xml:space="preserve">9.49483489990234</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43595123291016</t>
+    <t xml:space="preserve">9.43595027923584</t>
   </si>
   <si>
     <t xml:space="preserve">8.84712409973145</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">8.05711460113525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86574459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32699298858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61058759689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67928314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10127735137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87065315246582</t>
+    <t xml:space="preserve">7.86574649810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32699394226074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61058664321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67928409576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10127639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8706521987915</t>
   </si>
   <si>
     <t xml:space="preserve">8.53799057006836</t>
@@ -143,52 +143,52 @@
     <t xml:space="preserve">8.46929359436035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61650085449219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50364112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21413612365723</t>
+    <t xml:space="preserve">8.61649990081787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50364017486572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21413516998291</t>
   </si>
   <si>
     <t xml:space="preserve">8.69010353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71954441070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29365158081055</t>
+    <t xml:space="preserve">8.71954345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29365253448486</t>
   </si>
   <si>
     <t xml:space="preserve">9.30837154388428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47520637512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09737682342529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22004795074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41141700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48011302947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77943229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6616678237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79415416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77452659606934</t>
+    <t xml:space="preserve">9.47520542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09737491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22004699707031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41141605377197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48011207580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77943420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66166877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79415225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77452564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.68620204925537</t>
@@ -197,34 +197,34 @@
     <t xml:space="preserve">9.64694786071777</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7254581451416</t>
+    <t xml:space="preserve">9.72545719146729</t>
   </si>
   <si>
     <t xml:space="preserve">10.2357749938965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3044691085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83831596374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56843566894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98552227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93154525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74508476257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3780736923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449085235596</t>
+    <t xml:space="preserve">10.3044700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8383150100708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56843662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98552322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93154716491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74508380889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3780727386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449075698853</t>
   </si>
   <si>
     <t xml:space="preserve">10.4369564056396</t>
@@ -236,16 +236,16 @@
     <t xml:space="preserve">10.5056533813477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5498142242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5007457733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5694408416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4173278808594</t>
+    <t xml:space="preserve">10.5498161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5007448196411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5694417953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173269271851</t>
   </si>
   <si>
     <t xml:space="preserve">10.4811182022095</t>
@@ -260,10 +260,10 @@
     <t xml:space="preserve">10.7853450775146</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5988836288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406797409058</t>
+    <t xml:space="preserve">10.5988826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406806945801</t>
   </si>
   <si>
     <t xml:space="preserve">10.2897500991821</t>
@@ -272,25 +272,25 @@
     <t xml:space="preserve">9.7303638458252</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57334327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43104457855225</t>
+    <t xml:space="preserve">9.57334423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43104362487793</t>
   </si>
   <si>
     <t xml:space="preserve">9.40650844573975</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19060611724854</t>
+    <t xml:space="preserve">9.19060707092285</t>
   </si>
   <si>
     <t xml:space="preserve">9.08265590667725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35253238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47029876708984</t>
+    <t xml:space="preserve">9.3525333404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47029685974121</t>
   </si>
   <si>
     <t xml:space="preserve">9.27892971038818</t>
@@ -299,73 +299,73 @@
     <t xml:space="preserve">9.30346488952637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14644336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52970314025879</t>
+    <t xml:space="preserve">9.14644527435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52970027923584</t>
   </si>
   <si>
     <t xml:space="preserve">9.79665470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.119010925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89235401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95279693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492319107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84702301025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.766432762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42896461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42392730712891</t>
+    <t xml:space="preserve">10.1190128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89235591888428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95279598236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84702205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76643371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42896366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42392921447754</t>
   </si>
   <si>
     <t xml:space="preserve">9.52466487884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54984951019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39370632171631</t>
+    <t xml:space="preserve">9.54984855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39370727539062</t>
   </si>
   <si>
     <t xml:space="preserve">8.82958030700684</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48203945159912</t>
+    <t xml:space="preserve">8.48203754425049</t>
   </si>
   <si>
     <t xml:space="preserve">8.28560256958008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46189117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53744506835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68351268768311</t>
+    <t xml:space="preserve">8.46189212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53744316101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68351173400879</t>
   </si>
   <si>
     <t xml:space="preserve">9.39874267578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50451850891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81680011749268</t>
+    <t xml:space="preserve">9.50451946258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81680202484131</t>
   </si>
   <si>
     <t xml:space="preserve">8.46692848205566</t>
@@ -374,70 +374,70 @@
     <t xml:space="preserve">7.46459722518921</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57540655136108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49985551834106</t>
+    <t xml:space="preserve">7.57540798187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49985408782959</t>
   </si>
   <si>
     <t xml:space="preserve">7.3487491607666</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43941259384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20268106460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87025022506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50256061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62848281860352</t>
+    <t xml:space="preserve">7.43941354751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20268201828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87025117874146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50256204605103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62848138809204</t>
   </si>
   <si>
     <t xml:space="preserve">6.86017656326294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02135419845581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38904476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20771884918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44948720932007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66607189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52503871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64592313766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79702854156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71140193939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94309616088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81717538833618</t>
+    <t xml:space="preserve">7.02135610580444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3890438079834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20771932601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44948673248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66607236862183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5250391960144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64592409133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7970290184021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71140241622925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94309711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8171763420105</t>
   </si>
   <si>
     <t xml:space="preserve">7.94813299179077</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08179664611816</t>
+    <t xml:space="preserve">7.08179712295532</t>
   </si>
   <si>
     <t xml:space="preserve">6.92565584182739</t>
@@ -446,31 +446,31 @@
     <t xml:space="preserve">6.71410799026489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78966045379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90047025680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22786569595337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27823352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32860422134399</t>
+    <t xml:space="preserve">6.7896614074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90047121047974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22786521911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27823400497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32860279083252</t>
   </si>
   <si>
     <t xml:space="preserve">7.31852865219116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39911842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15734910964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94580221176147</t>
+    <t xml:space="preserve">7.39911794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15735006332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94580268859863</t>
   </si>
   <si>
     <t xml:space="preserve">7.19764471054077</t>
@@ -479,61 +479,61 @@
     <t xml:space="preserve">6.80477094650269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02639102935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08683300018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04150295257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8501033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8652138710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22282886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31349229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23290157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29838228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98106002807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01128101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53781890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79973411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68388700485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73929309844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94076681137085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90550708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.668776512146</t>
+    <t xml:space="preserve">7.02639150619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08683347702026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04150342941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85010290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86521339416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069171905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22282934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31349182128906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23290205001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29838085174561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98105955123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01128196716309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53781938552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7997350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68388652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73929262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94076585769653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90550804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66877603530884</t>
   </si>
   <si>
     <t xml:space="preserve">6.4622654914856</t>
@@ -542,22 +542,22 @@
     <t xml:space="preserve">6.57307577133179</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6738133430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59825992584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87528657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00624418258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15231323242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30341768264771</t>
+    <t xml:space="preserve">6.67381238937378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59826135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87528610229492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00624513626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15231275558472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30341863632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.62577629089355</t>
@@ -569,109 +569,109 @@
     <t xml:space="preserve">7.57037115097046</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45452356338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5351128578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59555530548096</t>
+    <t xml:space="preserve">7.45452308654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53511238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44444894790649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59555435180664</t>
   </si>
   <si>
     <t xml:space="preserve">7.72147703170776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60562944412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70636606216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48474502563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36386013031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26312446594238</t>
+    <t xml:space="preserve">7.605628490448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70636510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48474454879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3638596534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26312494277954</t>
   </si>
   <si>
     <t xml:space="preserve">7.13216495513916</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99617099761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17246150970459</t>
+    <t xml:space="preserve">6.99617195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17245960235596</t>
   </si>
   <si>
     <t xml:space="preserve">7.69629096984863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91791248321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35611629486084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38633823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51729679107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45181751251221</t>
+    <t xml:space="preserve">7.91791343688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35611724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38633918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51729488372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45181846618652</t>
   </si>
   <si>
     <t xml:space="preserve">8.20501232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04887199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95820808410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93132352828979</t>
+    <t xml:space="preserve">8.04887104034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9582085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93132305145264</t>
   </si>
   <si>
     <t xml:space="preserve">7.71623516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73236608505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63557767868042</t>
+    <t xml:space="preserve">7.73236703872681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63557720184326</t>
   </si>
   <si>
     <t xml:space="preserve">7.64095592498779</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45813226699829</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44200038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57105302810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68934917449951</t>
+    <t xml:space="preserve">7.45813035964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4419994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57105207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68934965133667</t>
   </si>
   <si>
     <t xml:space="preserve">7.62482309341431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79689311981201</t>
+    <t xml:space="preserve">7.79689359664917</t>
   </si>
   <si>
     <t xml:space="preserve">8.20018100738525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43139839172363</t>
+    <t xml:space="preserve">8.43139934539795</t>
   </si>
   <si>
     <t xml:space="preserve">8.61959934234619</t>
@@ -680,25 +680,25 @@
     <t xml:space="preserve">8.54432010650635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46903896331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58733749389648</t>
+    <t xml:space="preserve">8.46903800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5873384475708</t>
   </si>
   <si>
     <t xml:space="preserve">8.70025730133057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54969692230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60346794128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53356552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59809112548828</t>
+    <t xml:space="preserve">8.54969596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60346698760986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53356456756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5980920791626</t>
   </si>
   <si>
     <t xml:space="preserve">8.51743316650391</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">8.5281867980957</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67874813079834</t>
+    <t xml:space="preserve">8.67874908447266</t>
   </si>
   <si>
     <t xml:space="preserve">9.11429882049561</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">9.15731525421143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20033359527588</t>
+    <t xml:space="preserve">9.20033264160156</t>
   </si>
   <si>
     <t xml:space="preserve">9.17882442474365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05515003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3347635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13043022155762</t>
+    <t xml:space="preserve">9.05514907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33476257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13043117523193</t>
   </si>
   <si>
     <t xml:space="preserve">9.44768333435059</t>
@@ -737,40 +737,40 @@
     <t xml:space="preserve">9.38315677642822</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41004371643066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4584379196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45306015014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37240314483643</t>
+    <t xml:space="preserve">9.41004467010498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45843887329102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4530611038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37240219116211</t>
   </si>
   <si>
     <t xml:space="preserve">9.23797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32938671112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4691915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44230556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92609977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0927906036377</t>
+    <t xml:space="preserve">9.32938575744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46919345855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44230461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92609786987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09278964996338</t>
   </si>
   <si>
     <t xml:space="preserve">9.07128238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478481292725</t>
+    <t xml:space="preserve">8.76478290557861</t>
   </si>
   <si>
     <t xml:space="preserve">9.16807079315186</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">9.25948238372803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.28636932373047</t>
+    <t xml:space="preserve">9.28636837005615</t>
   </si>
   <si>
     <t xml:space="preserve">9.24335193634033</t>
@@ -788,25 +788,25 @@
     <t xml:space="preserve">9.26485919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2325963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24872779846191</t>
+    <t xml:space="preserve">9.23259830474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24872875213623</t>
   </si>
   <si>
     <t xml:space="preserve">8.96373748779297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.49592590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59271430969238</t>
+    <t xml:space="preserve">8.495924949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59271335601807</t>
   </si>
   <si>
     <t xml:space="preserve">8.52281093597412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66799354553223</t>
+    <t xml:space="preserve">8.66799449920654</t>
   </si>
   <si>
     <t xml:space="preserve">8.7378978729248</t>
@@ -815,52 +815,52 @@
     <t xml:space="preserve">8.71101188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70563316345215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63573169708252</t>
+    <t xml:space="preserve">8.70563411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6357307434082</t>
   </si>
   <si>
     <t xml:space="preserve">8.53894138336182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50130176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28621578216553</t>
+    <t xml:space="preserve">8.50130271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28621482849121</t>
   </si>
   <si>
     <t xml:space="preserve">8.33460998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43677616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47441673278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62497711181641</t>
+    <t xml:space="preserve">8.43677520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47441577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62497615814209</t>
   </si>
   <si>
     <t xml:space="preserve">8.56582927703857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47979259490967</t>
+    <t xml:space="preserve">8.47979354858398</t>
   </si>
   <si>
     <t xml:space="preserve">8.66261672973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61422252655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78091526031494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77016162872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79166793823242</t>
+    <t xml:space="preserve">8.61422157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78091621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77016067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79166984558105</t>
   </si>
   <si>
     <t xml:space="preserve">9.18420314788818</t>
@@ -872,16 +872,16 @@
     <t xml:space="preserve">9.14118480682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16269302368164</t>
+    <t xml:space="preserve">9.16269397735596</t>
   </si>
   <si>
     <t xml:space="preserve">9.30249977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13580799102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14656257629395</t>
+    <t xml:space="preserve">9.13580703735352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14656162261963</t>
   </si>
   <si>
     <t xml:space="preserve">9.20571041107178</t>
@@ -893,19 +893,19 @@
     <t xml:space="preserve">9.63050556182861</t>
   </si>
   <si>
-    <t xml:space="preserve">9.60899829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63588619232178</t>
+    <t xml:space="preserve">9.60899639129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63588523864746</t>
   </si>
   <si>
     <t xml:space="preserve">9.71654033660889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97464561462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0553026199341</t>
+    <t xml:space="preserve">9.97464656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0553035736084</t>
   </si>
   <si>
     <t xml:space="preserve">10.2435035705566</t>
@@ -914,22 +914,22 @@
     <t xml:space="preserve">10.4155731201172</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3456716537476</t>
+    <t xml:space="preserve">10.3456707000732</t>
   </si>
   <si>
     <t xml:space="preserve">10.2327489852905</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3994436264038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4101963043213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1305837631226</t>
+    <t xml:space="preserve">10.3994407653809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.410195350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349161148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1305847167969</t>
   </si>
   <si>
     <t xml:space="preserve">10.1036977767944</t>
@@ -941,13 +941,13 @@
     <t xml:space="preserve">10.425971031189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5507669448853</t>
+    <t xml:space="preserve">10.5507659912109</t>
   </si>
   <si>
     <t xml:space="preserve">10.6074895858765</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5847988128662</t>
+    <t xml:space="preserve">10.5847997665405</t>
   </si>
   <si>
     <t xml:space="preserve">10.4770221710205</t>
@@ -956,19 +956,19 @@
     <t xml:space="preserve">10.2387800216675</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2728147506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3408832550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2160902023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0856246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90410614013672</t>
+    <t xml:space="preserve">10.27281665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3408842086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2160921096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0856227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9041051864624</t>
   </si>
   <si>
     <t xml:space="preserve">10.2898321151733</t>
@@ -980,67 +980,67 @@
     <t xml:space="preserve">10.1083135604858</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0062103271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94381237030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1707096099854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1366758346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.062933921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1990718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3522291183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1934013366699</t>
+    <t xml:space="preserve">10.0062093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94381332397461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1707105636597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1366748809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0629329681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1990728378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3522281646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1934003829956</t>
   </si>
   <si>
     <t xml:space="preserve">9.95515823364258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1480197906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2444524765015</t>
+    <t xml:space="preserve">10.1480207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2444515228271</t>
   </si>
   <si>
     <t xml:space="preserve">10.2841596603394</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2217626571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0912961959839</t>
+    <t xml:space="preserve">10.2217617034912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0912971496582</t>
   </si>
   <si>
     <t xml:space="preserve">10.1593647003174</t>
   </si>
   <si>
-    <t xml:space="preserve">10.545093536377</t>
+    <t xml:space="preserve">10.5450925827026</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089546203613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3181943893433</t>
+    <t xml:space="preserve">10.3181953430176</t>
   </si>
   <si>
     <t xml:space="preserve">10.2955055236816</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3692445755005</t>
+    <t xml:space="preserve">10.3692455291748</t>
   </si>
   <si>
     <t xml:space="preserve">10.4316434860229</t>
@@ -1052,19 +1052,19 @@
     <t xml:space="preserve">10.7152671813965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.641526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7436294555664</t>
+    <t xml:space="preserve">10.6415252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7436275482178</t>
   </si>
   <si>
     <t xml:space="preserve">10.7209377288818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6698865890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7776622772217</t>
+    <t xml:space="preserve">10.669885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7776641845703</t>
   </si>
   <si>
     <t xml:space="preserve">10.7039213180542</t>
@@ -1073,67 +1073,67 @@
     <t xml:space="preserve">10.6585416793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5394191741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3068494796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095937728882</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5564365386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4826936721802</t>
+    <t xml:space="preserve">10.5394201278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3068513870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5564374923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4826955795288</t>
   </si>
   <si>
     <t xml:space="preserve">10.3352117538452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2331085205078</t>
+    <t xml:space="preserve">10.2331075668335</t>
   </si>
   <si>
     <t xml:space="preserve">10.2784862518311</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0288982391357</t>
+    <t xml:space="preserve">10.0288991928101</t>
   </si>
   <si>
     <t xml:space="preserve">10.040244102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0969686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0345706939697</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98351860046387</t>
+    <t xml:space="preserve">10.0969696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.034571647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9835205078125</t>
   </si>
   <si>
     <t xml:space="preserve">9.96082878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98919200897217</t>
+    <t xml:space="preserve">9.98919296264648</t>
   </si>
   <si>
     <t xml:space="preserve">10.2274351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2557973861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4940404891968</t>
+    <t xml:space="preserve">10.2557964324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4940395355225</t>
   </si>
   <si>
     <t xml:space="preserve">10.5110578536987</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4146280288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3635740280151</t>
+    <t xml:space="preserve">10.414626121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3635730743408</t>
   </si>
   <si>
     <t xml:space="preserve">10.3805923461914</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">10.4600057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">10.516731262207</t>
+    <t xml:space="preserve">10.5167303085327</t>
   </si>
   <si>
     <t xml:space="preserve">10.3465566635132</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">9.84738063812256</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86439800262451</t>
+    <t xml:space="preserve">9.86439895629883</t>
   </si>
   <si>
     <t xml:space="preserve">9.72825908660889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67720699310303</t>
+    <t xml:space="preserve">9.67720794677734</t>
   </si>
   <si>
     <t xml:space="preserve">9.66018962860107</t>
@@ -1166,13 +1166,13 @@
     <t xml:space="preserve">9.48434352874756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68855285644531</t>
+    <t xml:space="preserve">9.688551902771</t>
   </si>
   <si>
     <t xml:space="preserve">9.58644866943359</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7112398147583</t>
+    <t xml:space="preserve">9.71124076843262</t>
   </si>
   <si>
     <t xml:space="preserve">9.67153453826904</t>
@@ -1181,58 +1181,58 @@
     <t xml:space="preserve">9.61480903625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62048149108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73393249511719</t>
+    <t xml:space="preserve">9.62048244476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73393058776855</t>
   </si>
   <si>
     <t xml:space="preserve">9.78498458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79632949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89843368530273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16101360321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95113182067871</t>
+    <t xml:space="preserve">9.7963285446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89843273162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16101455688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95113277435303</t>
   </si>
   <si>
     <t xml:space="preserve">8.99084091186523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76961421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75259780883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86604499816895</t>
+    <t xml:space="preserve">8.76961326599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75259685516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86604595184326</t>
   </si>
   <si>
     <t xml:space="preserve">8.85470104217529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05891036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24042892456055</t>
+    <t xml:space="preserve">9.05891132354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24042701721191</t>
   </si>
   <si>
     <t xml:space="preserve">9.2517728805542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10996150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09294414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98516654968262</t>
+    <t xml:space="preserve">9.10996246337891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09294319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98516845703125</t>
   </si>
   <si>
     <t xml:space="preserve">9.07592678070068</t>
@@ -1241,130 +1241,130 @@
     <t xml:space="preserve">9.13265132904053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05323696136475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90008163452148</t>
+    <t xml:space="preserve">9.05323791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90008068084717</t>
   </si>
   <si>
     <t xml:space="preserve">8.88306427001953</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82633876800537</t>
+    <t xml:space="preserve">8.82633781433105</t>
   </si>
   <si>
     <t xml:space="preserve">8.79230403900146</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79797744750977</t>
+    <t xml:space="preserve">8.79797649383545</t>
   </si>
   <si>
     <t xml:space="preserve">8.9681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0021858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07025527954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99651145935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01920318603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92277050018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04189205169678</t>
+    <t xml:space="preserve">9.00218391418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0702543258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9965124130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01920223236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92277145385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04189300537109</t>
   </si>
   <si>
     <t xml:space="preserve">9.03054714202881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01352882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04756450653076</t>
+    <t xml:space="preserve">9.01352977752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04756546020508</t>
   </si>
   <si>
     <t xml:space="preserve">9.03622055053711</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13832378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97382354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12697982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16668510437012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19504833221436</t>
+    <t xml:space="preserve">9.1383228302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97382259368896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12697887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16668701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19504737854004</t>
   </si>
   <si>
     <t xml:space="preserve">9.37089443206787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38223838806152</t>
+    <t xml:space="preserve">9.38223934173584</t>
   </si>
   <si>
     <t xml:space="preserve">9.34253215789795</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46732616424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6755590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.420298576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3919363021851</t>
+    <t xml:space="preserve">9.46732521057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6755599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3919353485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.5961446762085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7549724578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7379560470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7606449127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6613779067993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4543323516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032821655273</t>
+    <t xml:space="preserve">10.7549743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7379570007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.760645866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6613788604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4543333053589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032802581787</t>
   </si>
   <si>
     <t xml:space="preserve">10.4429883956909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3777570724487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0742797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1338386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0941324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98635578155518</t>
+    <t xml:space="preserve">10.3777551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0742788314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1338396072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0941333770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98635673522949</t>
   </si>
   <si>
     <t xml:space="preserve">10.1565294265747</t>
@@ -1373,61 +1373,61 @@
     <t xml:space="preserve">10.1962356567383</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2359437942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.162202835083</t>
+    <t xml:space="preserve">10.2359447479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1622009277344</t>
   </si>
   <si>
     <t xml:space="preserve">10.2416172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2501249313354</t>
+    <t xml:space="preserve">10.2501239776611</t>
   </si>
   <si>
     <t xml:space="preserve">10.2132530212402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1678733825684</t>
+    <t xml:space="preserve">10.1678743362427</t>
   </si>
   <si>
     <t xml:space="preserve">9.90694046020508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92963027954102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1877269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2302713394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0203905105591</t>
+    <t xml:space="preserve">9.9296293258667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1877279281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2302722930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0203895568848</t>
   </si>
   <si>
     <t xml:space="preserve">10.1905641555786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1820554733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0317354202271</t>
+    <t xml:space="preserve">10.182056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0317344665527</t>
   </si>
   <si>
     <t xml:space="preserve">9.9778470993042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81618309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88708782196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89559555053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81334495544434</t>
+    <t xml:space="preserve">9.81618213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88708686828613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89559745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81334590911865</t>
   </si>
   <si>
     <t xml:space="preserve">9.97501087188721</t>
@@ -1436,31 +1436,31 @@
     <t xml:space="preserve">10.065770149231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395111083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0005359649658</t>
+    <t xml:space="preserve">10.1395130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0005369186401</t>
   </si>
   <si>
     <t xml:space="preserve">10.0686054229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73676681518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83603668212891</t>
+    <t xml:space="preserve">9.73676776885986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83603572845459</t>
   </si>
   <si>
     <t xml:space="preserve">9.89276027679443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8672342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82752704620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77931118011475</t>
+    <t xml:space="preserve">9.86723327636719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8275260925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77931022644043</t>
   </si>
   <si>
     <t xml:space="preserve">9.83320045471191</t>
@@ -1469,22 +1469,22 @@
     <t xml:space="preserve">9.94948482513428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0714435577393</t>
+    <t xml:space="preserve">10.0714426040649</t>
   </si>
   <si>
     <t xml:space="preserve">9.93814086914062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71407890319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42761898040771</t>
+    <t xml:space="preserve">9.71407794952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42761993408203</t>
   </si>
   <si>
     <t xml:space="preserve">9.10145378112793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21773815155029</t>
+    <t xml:space="preserve">9.21773910522461</t>
   </si>
   <si>
     <t xml:space="preserve">9.12414264678955</t>
@@ -1493,40 +1493,40 @@
     <t xml:space="preserve">9.24326419830322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20072174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29274559020996</t>
+    <t xml:space="preserve">9.20072078704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29274463653564</t>
   </si>
   <si>
     <t xml:space="preserve">9.51369762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39841651916504</t>
+    <t xml:space="preserve">9.39841842651367</t>
   </si>
   <si>
     <t xml:space="preserve">9.47206878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44004726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33757495880127</t>
+    <t xml:space="preserve">9.4400463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3375768661499</t>
   </si>
   <si>
     <t xml:space="preserve">8.98533630371094</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02696514129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89887714385986</t>
+    <t xml:space="preserve">9.02696418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89887619018555</t>
   </si>
   <si>
     <t xml:space="preserve">9.34398078918457</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31836414337158</t>
+    <t xml:space="preserve">9.31836128234863</t>
   </si>
   <si>
     <t xml:space="preserve">8.93730449676514</t>
@@ -1535,19 +1535,19 @@
     <t xml:space="preserve">8.92129135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93410015106201</t>
+    <t xml:space="preserve">8.93410110473633</t>
   </si>
   <si>
     <t xml:space="preserve">8.64590263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83803367614746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7547779083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72275638580322</t>
+    <t xml:space="preserve">8.83803462982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75477886199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72275543212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.71635150909424</t>
@@ -1559,58 +1559,58 @@
     <t xml:space="preserve">8.82842826843262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80601215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83163070678711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66511726379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73556613922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51781558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899555206299</t>
+    <t xml:space="preserve">8.8060131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83162879943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66511821746826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73556518554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5178165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4889965057373</t>
   </si>
   <si>
     <t xml:space="preserve">8.56905174255371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45697593688965</t>
+    <t xml:space="preserve">8.45697402954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.39613342285156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51141262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53062438964844</t>
+    <t xml:space="preserve">8.5114107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53062534332275</t>
   </si>
   <si>
     <t xml:space="preserve">8.53702926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54343414306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71314907073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40573883056641</t>
+    <t xml:space="preserve">8.54343223571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71315002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40573978424072</t>
   </si>
   <si>
     <t xml:space="preserve">8.36411190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33209037780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42175102233887</t>
+    <t xml:space="preserve">8.3320894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42175197601318</t>
   </si>
   <si>
     <t xml:space="preserve">8.58506202697754</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">8.57225322723389</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46017646789551</t>
+    <t xml:space="preserve">8.46017742156982</t>
   </si>
   <si>
     <t xml:space="preserve">8.46658134460449</t>
@@ -1628,7 +1628,7 @@
     <t xml:space="preserve">8.58186149597168</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4409646987915</t>
+    <t xml:space="preserve">8.44096279144287</t>
   </si>
   <si>
     <t xml:space="preserve">9.09421062469482</t>
@@ -1640,31 +1640,31 @@
     <t xml:space="preserve">9.05578327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1998815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18707370758057</t>
+    <t xml:space="preserve">9.19988250732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18707275390625</t>
   </si>
   <si>
     <t xml:space="preserve">8.91808986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87646102905273</t>
+    <t xml:space="preserve">8.87646198272705</t>
   </si>
   <si>
     <t xml:space="preserve">9.03657150268555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18387031555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15505218505859</t>
+    <t xml:space="preserve">9.18387126922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15505123138428</t>
   </si>
   <si>
     <t xml:space="preserve">9.1518497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23510646820068</t>
+    <t xml:space="preserve">9.23510456085205</t>
   </si>
   <si>
     <t xml:space="preserve">9.16465950012207</t>
@@ -1673,16 +1673,16 @@
     <t xml:space="preserve">9.1262321472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26072311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.254319190979</t>
+    <t xml:space="preserve">9.2607250213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25432014465332</t>
   </si>
   <si>
     <t xml:space="preserve">9.2062873840332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20948791503906</t>
+    <t xml:space="preserve">9.20948886871338</t>
   </si>
   <si>
     <t xml:space="preserve">9.22549915313721</t>
@@ -1691,13 +1691,13 @@
     <t xml:space="preserve">9.10701847076416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92769718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76758575439453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.65871334075928</t>
+    <t xml:space="preserve">8.92769622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76758670806885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.65871238708496</t>
   </si>
   <si>
     <t xml:space="preserve">8.68112754821777</t>
@@ -1709,49 +1709,49 @@
     <t xml:space="preserve">8.61708450317383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7803955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82202434539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77719497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78359794616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95331478118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97252750396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9661226272583</t>
+    <t xml:space="preserve">8.78039455413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82202529907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77719402313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78359699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95331382751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97252655029297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96612167358398</t>
   </si>
   <si>
     <t xml:space="preserve">8.86685466766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86045074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32568550109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2232141494751</t>
+    <t xml:space="preserve">8.86044979095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32568454742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22321510314941</t>
   </si>
   <si>
     <t xml:space="preserve">8.29366302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53382682800293</t>
+    <t xml:space="preserve">8.53382778167725</t>
   </si>
   <si>
     <t xml:space="preserve">8.48259258270264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40253829956055</t>
+    <t xml:space="preserve">8.40253734588623</t>
   </si>
   <si>
     <t xml:space="preserve">8.14956474304199</t>
@@ -1760,40 +1760,40 @@
     <t xml:space="preserve">8.06630802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07271194458008</t>
+    <t xml:space="preserve">8.07271289825439</t>
   </si>
   <si>
     <t xml:space="preserve">7.77490997314453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74929189682007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67884397506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87417650222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73007917404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53474473953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42266893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25295209884644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21772813796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08003568649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11205625534058</t>
+    <t xml:space="preserve">7.74929141998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67884302139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87417602539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73007822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53474378585815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42266845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25295305252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21772909164429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0800347328186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11205673217773</t>
   </si>
   <si>
     <t xml:space="preserve">6.84947681427002</t>
@@ -1802,64 +1802,64 @@
     <t xml:space="preserve">6.97115993499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04160737991333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03520488739014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04801273345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94234085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95194673538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00958728790283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13126850128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97436141967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83026456832886</t>
+    <t xml:space="preserve">7.0416088104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03520345687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04801225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94234037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95194721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00958633422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13126945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97436189651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8302640914917</t>
   </si>
   <si>
     <t xml:space="preserve">6.95514965057373</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80144453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76622009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85908317565918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62852621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70537900924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7470064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86548805236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16329193115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09604549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06722640991211</t>
+    <t xml:space="preserve">6.8014440536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7662205696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85908460617065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62852573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70537853240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74700689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86548852920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16329145431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09604501724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06722688674927</t>
   </si>
   <si>
     <t xml:space="preserve">7.02239608764648</t>
@@ -1868,31 +1868,31 @@
     <t xml:space="preserve">7.23053741455078</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05761957168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80464696884155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89110565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71818780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73740100860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01278924942017</t>
+    <t xml:space="preserve">7.05762004852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80464601516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89110469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71818828582764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7374005317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95835113525391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01278877258301</t>
   </si>
   <si>
     <t xml:space="preserve">6.88790273666382</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45881080627441</t>
+    <t xml:space="preserve">6.45880937576294</t>
   </si>
   <si>
     <t xml:space="preserve">6.39796924591064</t>
@@ -1901,31 +1901,31 @@
     <t xml:space="preserve">6.15204095840454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15844488143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96375131607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10592985153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1072096824646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39925050735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6445369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63172817230225</t>
+    <t xml:space="preserve">6.15844535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96375226974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10592937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10721015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39924907684326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64453601837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63172769546509</t>
   </si>
   <si>
     <t xml:space="preserve">6.59010028839111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50043964385986</t>
+    <t xml:space="preserve">6.50043869018555</t>
   </si>
   <si>
     <t xml:space="preserve">6.60290861129761</t>
@@ -1934,163 +1934,163 @@
     <t xml:space="preserve">6.59650468826294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41718101501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52285480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42038440704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47802305221558</t>
+    <t xml:space="preserve">6.41718149185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52285432815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42038488388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47802400588989</t>
   </si>
   <si>
     <t xml:space="preserve">6.4460015296936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32624006271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26731967926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74380540847778</t>
+    <t xml:space="preserve">6.32624053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2673192024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74380588531494</t>
   </si>
   <si>
     <t xml:space="preserve">7.09924697875977</t>
   </si>
   <si>
-    <t xml:space="preserve">7.3073902130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19851493835449</t>
+    <t xml:space="preserve">7.30738973617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19851589202881</t>
   </si>
   <si>
     <t xml:space="preserve">7.08964109420776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11846113204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15368413925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15688610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17930269241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04481077194214</t>
+    <t xml:space="preserve">7.1184606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15368604660034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15688705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17930221557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04481029510498</t>
   </si>
   <si>
     <t xml:space="preserve">6.99357557296753</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27216625213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4482855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75889778137207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57637357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72687530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.838951587677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82614469528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8453574180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8997950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91260194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98305177688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88057994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91900730133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23282146453857</t>
+    <t xml:space="preserve">7.27216577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44828701019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75889825820923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57637310028076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72687673568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83895301818848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82614326477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84535646438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89979410171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91260290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98305082321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88058090209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91900825500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23282241821289</t>
   </si>
   <si>
     <t xml:space="preserve">8.12074565887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26164054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47298622131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84764194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91168594360352</t>
+    <t xml:space="preserve">8.26164245605469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47298526763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46337985992432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84764099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9116849899292</t>
   </si>
   <si>
     <t xml:space="preserve">9.26392650604248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33117294311523</t>
+    <t xml:space="preserve">9.3311710357666</t>
   </si>
   <si>
     <t xml:space="preserve">9.53291034698486</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67700862884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51049423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42083263397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32796955108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40482330322266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47847175598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55212306976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5713357925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70262432098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77627658843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8147029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0836868286133</t>
+    <t xml:space="preserve">9.6770076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51049327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42083168029785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32797050476074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40482234954834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47847270965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55212211608887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57133674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77627563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81470203399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.083685874939</t>
   </si>
   <si>
     <t xml:space="preserve">10.0356521606445</t>
@@ -2099,7 +2099,7 @@
     <t xml:space="preserve">10.1413240432739</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2149753570557</t>
+    <t xml:space="preserve">10.21497631073</t>
   </si>
   <si>
     <t xml:space="preserve">10.195761680603</t>
@@ -2108,85 +2108,85 @@
     <t xml:space="preserve">10.2694120407104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2790193557739</t>
+    <t xml:space="preserve">10.2790184020996</t>
   </si>
   <si>
     <t xml:space="preserve">10.5608129501343</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8490076065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.868221282959</t>
+    <t xml:space="preserve">10.849009513855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8682222366333</t>
   </si>
   <si>
     <t xml:space="preserve">10.8874340057373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0155229568481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0603504180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.281304359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2909107208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5118618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5278730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.495849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3773679733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3261337280273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4926462173462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8105802536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9899053573608</t>
+    <t xml:space="preserve">11.0155210494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0603523254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2813034057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2909097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5118608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4958505630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.377368927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.326132774353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4926481246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8105812072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9899044036865</t>
   </si>
   <si>
     <t xml:space="preserve">10.5992374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0219268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1404085159302</t>
+    <t xml:space="preserve">11.0219259262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1404075622559</t>
   </si>
   <si>
     <t xml:space="preserve">11.1141195297241</t>
   </si>
   <si>
-    <t xml:space="preserve">10.79176902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7882661819458</t>
+    <t xml:space="preserve">10.7917680740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882652282715</t>
   </si>
   <si>
     <t xml:space="preserve">10.4203634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5780363082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3993396759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4273710250854</t>
+    <t xml:space="preserve">10.5780353546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3993406295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4273719787598</t>
   </si>
   <si>
     <t xml:space="preserve">10.2872180938721</t>
@@ -2195,43 +2195,43 @@
     <t xml:space="preserve">10.3888292312622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4238662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3678073883057</t>
+    <t xml:space="preserve">10.423867225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3678064346313</t>
   </si>
   <si>
     <t xml:space="preserve">10.7322034835815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7742490768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4448900222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079593658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5149669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6305923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8127918243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1281366348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1877012252808</t>
+    <t xml:space="preserve">10.7742500305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4448909759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.507960319519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.514967918396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6305932998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8127927780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1281356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1877002716064</t>
   </si>
   <si>
     <t xml:space="preserve">11.3523807525635</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5731201171875</t>
+    <t xml:space="preserve">11.5731210708618</t>
   </si>
   <si>
     <t xml:space="preserve">11.6151666641235</t>
@@ -2240,10 +2240,10 @@
     <t xml:space="preserve">11.7553186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7342967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429136276245</t>
+    <t xml:space="preserve">11.7342977523804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429145812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7097682952881</t>
@@ -2255,16 +2255,16 @@
     <t xml:space="preserve">11.863938331604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9059829711914</t>
+    <t xml:space="preserve">11.9059820175171</t>
   </si>
   <si>
     <t xml:space="preserve">11.9199981689453</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0496406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2318382263184</t>
+    <t xml:space="preserve">12.0496397018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2318391799927</t>
   </si>
   <si>
     <t xml:space="preserve">12.2248315811157</t>
@@ -2276,55 +2276,55 @@
     <t xml:space="preserve">12.2143201828003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3159303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2773885726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4175415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3684873580933</t>
+    <t xml:space="preserve">12.3159313201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2773895263672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4175405502319</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3684864044189</t>
   </si>
   <si>
     <t xml:space="preserve">12.1267242431641</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0391283035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464183807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636548995972</t>
+    <t xml:space="preserve">12.0391292572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636568069458</t>
   </si>
   <si>
     <t xml:space="preserve">12.1407403945923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1232194900513</t>
+    <t xml:space="preserve">12.123218536377</t>
   </si>
   <si>
     <t xml:space="preserve">12.109206199646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0321226119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8779535293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760599136353</t>
+    <t xml:space="preserve">12.0321207046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8779525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760589599609</t>
   </si>
   <si>
     <t xml:space="preserve">11.6887474060059</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4680061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4890289306641</t>
+    <t xml:space="preserve">11.4680070877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4890298843384</t>
   </si>
   <si>
     <t xml:space="preserve">11.4820213317871</t>
@@ -2333,13 +2333,13 @@
     <t xml:space="preserve">11.6782360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2472648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0370349884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1001052856445</t>
+    <t xml:space="preserve">11.2472639083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0370359420776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1001043319702</t>
   </si>
   <si>
     <t xml:space="preserve">10.7216920852661</t>
@@ -2351,34 +2351,34 @@
     <t xml:space="preserve">11.1561651229858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.496036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4469814300537</t>
+    <t xml:space="preserve">11.4960374832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.446982383728</t>
   </si>
   <si>
     <t xml:space="preserve">11.184196472168</t>
   </si>
   <si>
-    <t xml:space="preserve">11.324348449707</t>
+    <t xml:space="preserve">11.3243503570557</t>
   </si>
   <si>
     <t xml:space="preserve">11.2752962112427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0615634918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4049367904663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2297458648682</t>
+    <t xml:space="preserve">11.061562538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4049377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2297449111938</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119453430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4995403289795</t>
+    <t xml:space="preserve">11.4995412826538</t>
   </si>
   <si>
     <t xml:space="preserve">11.7903575897217</t>
@@ -2387,10 +2387,10 @@
     <t xml:space="preserve">11.8814573287964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8288984298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550352096558</t>
+    <t xml:space="preserve">11.8289003372192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550361633301</t>
   </si>
   <si>
     <t xml:space="preserve">11.6677236557007</t>
@@ -2402,13 +2402,13 @@
     <t xml:space="preserve">11.8113803863525</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9970836639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9410228729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9690523147583</t>
+    <t xml:space="preserve">11.9970846176147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9410219192505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.969051361084</t>
   </si>
   <si>
     <t xml:space="preserve">12.0671586990356</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">12.2703809738159</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2738857269287</t>
+    <t xml:space="preserve">12.2738847732544</t>
   </si>
   <si>
     <t xml:space="preserve">12.1021976470947</t>
@@ -2429,10 +2429,10 @@
     <t xml:space="preserve">11.9725551605225</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0146017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741672515869</t>
+    <t xml:space="preserve">12.0146026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741662979126</t>
   </si>
   <si>
     <t xml:space="preserve">11.9865713119507</t>
@@ -2441,16 +2441,16 @@
     <t xml:space="preserve">11.6011514663696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5520992279053</t>
+    <t xml:space="preserve">11.552098274231</t>
   </si>
   <si>
     <t xml:space="preserve">11.5485935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5941438674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4259595870972</t>
+    <t xml:space="preserve">11.5941429138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4259605407715</t>
   </si>
   <si>
     <t xml:space="preserve">11.5380830764771</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">11.9480285644531</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0846796035767</t>
+    <t xml:space="preserve">12.0846786499023</t>
   </si>
   <si>
     <t xml:space="preserve">12.2108154296875</t>
@@ -2477,127 +2477,127 @@
     <t xml:space="preserve">12.7539091110229</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9641389846802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7188692092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7889461517334</t>
+    <t xml:space="preserve">12.9641380310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7188711166382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7889471054077</t>
   </si>
   <si>
     <t xml:space="preserve">12.795952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9886636734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1743659973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9080772399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0412225723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094049453735</t>
+    <t xml:space="preserve">12.9886627197266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1743679046631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9080762863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.041220664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094058990479</t>
   </si>
   <si>
     <t xml:space="preserve">13.6649017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8996553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.365665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389627456665</t>
+    <t xml:space="preserve">13.899658203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007024765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3656663894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389636993408</t>
   </si>
   <si>
     <t xml:space="preserve">15.0173778533936</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1365079879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5289354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9493942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181415557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9213619232178</t>
+    <t xml:space="preserve">15.1365060806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5289335250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9493923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181406021118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9213600158691</t>
   </si>
   <si>
     <t xml:space="preserve">16.1035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9914379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.124584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4118976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5940952301025</t>
+    <t xml:space="preserve">15.9914398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1245861053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4118957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5940971374512</t>
   </si>
   <si>
     <t xml:space="preserve">16.5100040435791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2086753845215</t>
+    <t xml:space="preserve">16.2086734771729</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474987030029</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8863248825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4868879318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8232536315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7531776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251491546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1575307846069</t>
+    <t xml:space="preserve">15.886323928833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4868898391724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8232555389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7531785964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251482009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1575298309326</t>
   </si>
   <si>
     <t xml:space="preserve">15.3817739486694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2626428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2976818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0804452896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2836675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2205982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0944595336914</t>
+    <t xml:space="preserve">15.2626447677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.297682762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0804462432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2836656570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2205963134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0944604873657</t>
   </si>
   <si>
     <t xml:space="preserve">15.0664300918579</t>
@@ -2606,22 +2606,22 @@
     <t xml:space="preserve">15.0454063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">14.856201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9122629165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1715431213379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8702144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3537425994873</t>
+    <t xml:space="preserve">14.8562021255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9122619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1715440750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8702163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721080780029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3537435531616</t>
   </si>
   <si>
     <t xml:space="preserve">16.5029964447021</t>
@@ -2630,13 +2630,13 @@
     <t xml:space="preserve">16.5800800323486</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4189052581787</t>
+    <t xml:space="preserve">16.4189033508301</t>
   </si>
   <si>
     <t xml:space="preserve">16.7062168121338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8043251037598</t>
+    <t xml:space="preserve">16.8043231964111</t>
   </si>
   <si>
     <t xml:space="preserve">16.622127532959</t>
@@ -2645,7 +2645,7 @@
     <t xml:space="preserve">16.5660648345947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9865226745605</t>
+    <t xml:space="preserve">16.9865245819092</t>
   </si>
   <si>
     <t xml:space="preserve">17.00754737854</t>
@@ -2660,31 +2660,31 @@
     <t xml:space="preserve">16.3978824615479</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4959926605225</t>
+    <t xml:space="preserve">16.4959907531738</t>
   </si>
   <si>
     <t xml:space="preserve">16.0685234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5499572753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5709781646729</t>
+    <t xml:space="preserve">15.5499563217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5709791183472</t>
   </si>
   <si>
     <t xml:space="preserve">16.033483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9423866271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1666278839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6431503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3908729553223</t>
+    <t xml:space="preserve">15.9423847198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1666316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6431484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3908748626709</t>
   </si>
   <si>
     <t xml:space="preserve">16.762279510498</t>
@@ -2696,73 +2696,73 @@
     <t xml:space="preserve">16.671178817749</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272415161133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.951488494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6130285263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5198345184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3516502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5478639602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7910394668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4546737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0272054672241</t>
+    <t xml:space="preserve">16.7272434234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9514865875244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6130247116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5198335647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3516511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5478649139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7910375595093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4546728134155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0272073745728</t>
   </si>
   <si>
     <t xml:space="preserve">12.9956712722778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3474655151367</t>
+    <t xml:space="preserve">12.347466468811</t>
   </si>
   <si>
     <t xml:space="preserve">11.7202806472778</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3327684402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68806457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81069850921631</t>
+    <t xml:space="preserve">10.3327674865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68806552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81069946289062</t>
   </si>
   <si>
     <t xml:space="preserve">8.25149822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51988220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4442081451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0202465057373</t>
+    <t xml:space="preserve">9.51988124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44420909881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02024555206299</t>
   </si>
   <si>
     <t xml:space="preserve">7.70490217208862</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77497863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49817752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59978771209717</t>
+    <t xml:space="preserve">7.77497816085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49817609786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59978818893433</t>
   </si>
   <si>
     <t xml:space="preserve">8.28653621673584</t>
@@ -2771,7 +2771,7 @@
     <t xml:space="preserve">9.06088161468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69507217407227</t>
+    <t xml:space="preserve">9.6950740814209</t>
   </si>
   <si>
     <t xml:space="preserve">9.05036926269531</t>
@@ -2798,31 +2798,31 @@
     <t xml:space="preserve">9.48834705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1680898666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381639480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87727069854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29914093017578</t>
+    <t xml:space="preserve">10.1680879592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87727165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2991418838501</t>
   </si>
   <si>
     <t xml:space="preserve">9.44630146026611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51637744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58995914459229</t>
+    <t xml:space="preserve">9.51637840270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58995819091797</t>
   </si>
   <si>
     <t xml:space="preserve">9.25359058380127</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33417987823486</t>
+    <t xml:space="preserve">9.33417892456055</t>
   </si>
   <si>
     <t xml:space="preserve">9.49535465240479</t>
@@ -2834,13 +2834,13 @@
     <t xml:space="preserve">10.3713102340698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8162956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2122278213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793649673462</t>
+    <t xml:space="preserve">10.816294670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2122268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793640136719</t>
   </si>
   <si>
     <t xml:space="preserve">10.7602338790894</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">10.4649343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7654333114624</t>
+    <t xml:space="preserve">10.7654342651367</t>
   </si>
   <si>
     <t xml:space="preserve">10.6414775848389</t>
@@ -2891,46 +2891,46 @@
     <t xml:space="preserve">11.358922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1936483383179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3251161575317</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5204429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7984056472778</t>
+    <t xml:space="preserve">11.1936464309692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3251171112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5204420089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7984046936035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913925170898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6923961639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9966497421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4407243728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3956499099731</t>
+    <t xml:space="preserve">12.6923952102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9966506958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4407253265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3956508636475</t>
   </si>
   <si>
     <t xml:space="preserve">11.6481552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6105918884277</t>
+    <t xml:space="preserve">11.6105928421021</t>
   </si>
   <si>
     <t xml:space="preserve">11.5166854858398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7721109390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.666934967041</t>
+    <t xml:space="preserve">11.7721099853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6669359207153</t>
   </si>
   <si>
     <t xml:space="preserve">11.5091733932495</t>
@@ -2942,7 +2942,7 @@
     <t xml:space="preserve">11.5730295181274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8284559249878</t>
+    <t xml:space="preserve">11.8284549713135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2687730789185</t>
@@ -2951,61 +2951,61 @@
     <t xml:space="preserve">11.4490728378296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2011594772339</t>
+    <t xml:space="preserve">11.2011604309082</t>
   </si>
   <si>
     <t xml:space="preserve">11.4791231155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4265365600586</t>
+    <t xml:space="preserve">11.4265356063843</t>
   </si>
   <si>
     <t xml:space="preserve">11.3664350509644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5429782867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7796239852905</t>
+    <t xml:space="preserve">11.663179397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5429792404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7796249389648</t>
   </si>
   <si>
     <t xml:space="preserve">11.7608423233032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4753675460815</t>
+    <t xml:space="preserve">11.4753665924072</t>
   </si>
   <si>
     <t xml:space="preserve">11.6706914901733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8585052490234</t>
+    <t xml:space="preserve">11.8585042953491</t>
   </si>
   <si>
     <t xml:space="preserve">11.8434801101685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3580884933472</t>
+    <t xml:space="preserve">12.3580875396729</t>
   </si>
   <si>
     <t xml:space="preserve">12.3205242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8013277053833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6999073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7337141036987</t>
+    <t xml:space="preserve">12.801326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6999082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337131500244</t>
   </si>
   <si>
     <t xml:space="preserve">12.8351316452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5684385299683</t>
+    <t xml:space="preserve">12.5684375762939</t>
   </si>
   <si>
     <t xml:space="preserve">12.6097564697266</t>
@@ -3014,7 +3014,7 @@
     <t xml:space="preserve">12.3731117248535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4369688034058</t>
+    <t xml:space="preserve">12.4369697570801</t>
   </si>
   <si>
     <t xml:space="preserve">12.0763683319092</t>
@@ -3023,13 +3023,13 @@
     <t xml:space="preserve">12.0575866699219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3693561553955</t>
+    <t xml:space="preserve">12.3693571090698</t>
   </si>
   <si>
     <t xml:space="preserve">12.3505754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4745311737061</t>
+    <t xml:space="preserve">12.4745321273804</t>
   </si>
   <si>
     <t xml:space="preserve">12.493311882019</t>
@@ -3038,34 +3038,34 @@
     <t xml:space="preserve">12.4707746505737</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8276214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938146591187</t>
+    <t xml:space="preserve">12.8276195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938137054443</t>
   </si>
   <si>
     <t xml:space="preserve">12.6585884094238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5984888076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4557504653931</t>
+    <t xml:space="preserve">12.5984878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4557495117188</t>
   </si>
   <si>
     <t xml:space="preserve">12.5158500671387</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3468179702759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.21910572052</t>
+    <t xml:space="preserve">12.3468189239502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2191066741943</t>
   </si>
   <si>
     <t xml:space="preserve">12.6661014556885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6247816085815</t>
+    <t xml:space="preserve">12.6247835159302</t>
   </si>
   <si>
     <t xml:space="preserve">12.508337020874</t>
@@ -3086,7 +3086,7 @@
     <t xml:space="preserve">11.9749488830566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1552495956421</t>
+    <t xml:space="preserve">12.1552505493164</t>
   </si>
   <si>
     <t xml:space="preserve">11.8847990036011</t>
@@ -3107,7 +3107,7 @@
     <t xml:space="preserve">12.5120944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6285381317139</t>
+    <t xml:space="preserve">12.6285371780396</t>
   </si>
   <si>
     <t xml:space="preserve">12.4257011413574</t>
@@ -3128,10 +3128,10 @@
     <t xml:space="preserve">11.3326282501221</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7645998001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5993242263794</t>
+    <t xml:space="preserve">11.7645978927612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5993232727051</t>
   </si>
   <si>
     <t xml:space="preserve">11.5842990875244</t>
@@ -3140,7 +3140,7 @@
     <t xml:space="preserve">11.4640989303589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3626794815063</t>
+    <t xml:space="preserve">11.3626804351807</t>
   </si>
   <si>
     <t xml:space="preserve">11.7120113372803</t>
@@ -3152,34 +3152,34 @@
     <t xml:space="preserve">11.8359680175781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.952410697937</t>
+    <t xml:space="preserve">11.9524116516113</t>
   </si>
   <si>
     <t xml:space="preserve">12.200325012207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2904748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1139307022095</t>
+    <t xml:space="preserve">12.2904758453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1139316558838</t>
   </si>
   <si>
     <t xml:space="preserve">12.4031629562378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.944899559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0989065170288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1514921188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0801239013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7007417678833</t>
+    <t xml:space="preserve">11.9448986053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0989055633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1514930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0801248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7007427215576</t>
   </si>
   <si>
     <t xml:space="preserve">11.5241985321045</t>
@@ -3188,10 +3188,10 @@
     <t xml:space="preserve">10.8255348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6452350616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8893909454346</t>
+    <t xml:space="preserve">10.6452341079712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8893918991089</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499914169312</t>
@@ -3200,22 +3200,22 @@
     <t xml:space="preserve">11.64439868927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8209428787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0275363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8885555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5834636688232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4332122802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4106760025024</t>
+    <t xml:space="preserve">11.8209419250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0275373458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8885545730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5834617614746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4332113265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4106750488281</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393899917603</t>
@@ -3230,25 +3230,25 @@
     <t xml:space="preserve">13.2370529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2595891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2220277786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.672779083252</t>
+    <t xml:space="preserve">13.2595882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2220268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6727781295776</t>
   </si>
   <si>
     <t xml:space="preserve">13.3572521209717</t>
   </si>
   <si>
-    <t xml:space="preserve">13.379789352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2746133804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5375518798828</t>
+    <t xml:space="preserve">13.3797883987427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2746152877808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5375528335571</t>
   </si>
   <si>
     <t xml:space="preserve">13.1882209777832</t>
@@ -3260,58 +3260,58 @@
     <t xml:space="preserve">13.2896404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2295408248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619272232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9327945709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1731948852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1919775009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1957330703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0154333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.82386302948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3272008895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361343383789</t>
+    <t xml:space="preserve">13.2295398712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9327955245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1731939315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1919755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1957340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0154323577881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8238639831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3272018432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361333847046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4962339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4323768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3497400283813</t>
+    <t xml:space="preserve">13.4323759078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.349739074707</t>
   </si>
   <si>
     <t xml:space="preserve">13.3384704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1994895935059</t>
+    <t xml:space="preserve">13.1994886398315</t>
   </si>
   <si>
     <t xml:space="preserve">13.4135961532593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4248657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.39857006073</t>
+    <t xml:space="preserve">13.4248666763306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3985691070557</t>
   </si>
   <si>
     <t xml:space="preserve">13.391058921814</t>
@@ -3320,43 +3320,43 @@
     <t xml:space="preserve">13.6802892684937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2099227905273</t>
+    <t xml:space="preserve">14.209924697876</t>
   </si>
   <si>
     <t xml:space="preserve">13.9582529067993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8305406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8380546569824</t>
+    <t xml:space="preserve">13.8305397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943967819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8380527496338</t>
   </si>
   <si>
     <t xml:space="preserve">13.9319591522217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7328796386719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4398908615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4060831069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1093406677246</t>
+    <t xml:space="preserve">13.7328767776489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4398899078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4060821533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1093397140503</t>
   </si>
   <si>
     <t xml:space="preserve">13.3009080886841</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0417261123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887208938599</t>
+    <t xml:space="preserve">13.04172706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887218475342</t>
   </si>
   <si>
     <t xml:space="preserve">13.5676012039185</t>
@@ -3365,10 +3365,10 @@
     <t xml:space="preserve">13.7216081619263</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3526611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5855493545532</t>
+    <t xml:space="preserve">14.3526592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5855484008789</t>
   </si>
   <si>
     <t xml:space="preserve">15.0550804138184</t>
@@ -3386,22 +3386,22 @@
     <t xml:space="preserve">14.8447303771973</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7207727432251</t>
+    <t xml:space="preserve">14.7207736968994</t>
   </si>
   <si>
     <t xml:space="preserve">14.9198560714722</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8221912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5329608917236</t>
+    <t xml:space="preserve">14.8221921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5329599380493</t>
   </si>
   <si>
     <t xml:space="preserve">14.6005725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4315404891968</t>
+    <t xml:space="preserve">14.4315423965454</t>
   </si>
   <si>
     <t xml:space="preserve">14.2812919616699</t>
@@ -3410,28 +3410,28 @@
     <t xml:space="preserve">14.9499053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.784628868103</t>
+    <t xml:space="preserve">14.7846307754517</t>
   </si>
   <si>
     <t xml:space="preserve">14.7095060348511</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6644296646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240293502808</t>
+    <t xml:space="preserve">14.6644287109375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240303039551</t>
   </si>
   <si>
     <t xml:space="preserve">14.7958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.762092590332</t>
+    <t xml:space="preserve">14.7620906829834</t>
   </si>
   <si>
     <t xml:space="preserve">14.9123430252075</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6606712341309</t>
+    <t xml:space="preserve">14.6606740951538</t>
   </si>
   <si>
     <t xml:space="preserve">14.4090051651001</t>
@@ -3440,7 +3440,7 @@
     <t xml:space="preserve">14.1948976516724</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1197729110718</t>
+    <t xml:space="preserve">14.1197719573975</t>
   </si>
   <si>
     <t xml:space="preserve">14.202410697937</t>
@@ -3452,124 +3452,124 @@
     <t xml:space="preserve">14.3226108551025</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4202718734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714418411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2925605773926</t>
+    <t xml:space="preserve">14.4202728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2925615310669</t>
   </si>
   <si>
     <t xml:space="preserve">14.4653482437134</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7470674514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5930624008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8898048400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8484859466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2504043579102</t>
+    <t xml:space="preserve">14.7470655441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5930614471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8898057937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8484869003296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2504053115845</t>
   </si>
   <si>
     <t xml:space="preserve">15.1001558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1151809692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0701055526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827907562256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7245283126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7508239746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.814679145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.818434715271</t>
+    <t xml:space="preserve">15.1151819229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0701065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827936172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7245311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7508249282837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8146810531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8184366226196</t>
   </si>
   <si>
     <t xml:space="preserve">14.9837112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0175189971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7921438217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9611740112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1602563858032</t>
+    <t xml:space="preserve">15.0175170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.792142868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9611749649048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1602554321289</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0851306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1377191543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3555822372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2579183578491</t>
+    <t xml:space="preserve">15.085129737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1377182006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3555812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2579174041748</t>
   </si>
   <si>
     <t xml:space="preserve">15.2804565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2729434967041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.86643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8438940048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.641056060791</t>
+    <t xml:space="preserve">15.2729425430298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8664321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8438949584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6410570144653</t>
   </si>
   <si>
     <t xml:space="preserve">15.708667755127</t>
   </si>
   <si>
-    <t xml:space="preserve">15.671106338501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1603336334229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0814266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8841562271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8999404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9551753997803</t>
+    <t xml:space="preserve">15.6711091995239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1603355407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.081428527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8841571807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8999395370483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9551763534546</t>
   </si>
   <si>
     <t xml:space="preserve">16.0419731140137</t>
@@ -3581,25 +3581,25 @@
     <t xml:space="preserve">16.0972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.144552230835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4601860046387</t>
+    <t xml:space="preserve">16.1445541381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4601879119873</t>
   </si>
   <si>
     <t xml:space="preserve">16.4522953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.412841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3260402679443</t>
+    <t xml:space="preserve">16.4128398895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3260440826416</t>
   </si>
   <si>
     <t xml:space="preserve">16.3497142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9946298599243</t>
+    <t xml:space="preserve">15.99462890625</t>
   </si>
   <si>
     <t xml:space="preserve">16.1208820343018</t>
@@ -3611,7 +3611,7 @@
     <t xml:space="preserve">16.0183010101318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9472827911377</t>
+    <t xml:space="preserve">15.9472846984863</t>
   </si>
   <si>
     <t xml:space="preserve">15.8762683868408</t>
@@ -3623,7 +3623,7 @@
     <t xml:space="preserve">16.2471332550049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5312042236328</t>
+    <t xml:space="preserve">16.5312023162842</t>
   </si>
   <si>
     <t xml:space="preserve">16.1287727355957</t>
@@ -3650,31 +3650,31 @@
     <t xml:space="preserve">16.2550258636475</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5233116149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8073787689209</t>
+    <t xml:space="preserve">16.5233135223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8073806762695</t>
   </si>
   <si>
     <t xml:space="preserve">17.1624660491943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5254421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3281726837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1940307617188</t>
+    <t xml:space="preserve">17.5254402160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3281707763672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1940288543701</t>
   </si>
   <si>
     <t xml:space="preserve">17.2492656707764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1387939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4702053070068</t>
+    <t xml:space="preserve">17.1387920379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4702072143555</t>
   </si>
   <si>
     <t xml:space="preserve">17.4938793182373</t>
@@ -3692,28 +3692,28 @@
     <t xml:space="preserve">17.9042015075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9120903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1093616485596</t>
+    <t xml:space="preserve">17.9120922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1093635559082</t>
   </si>
   <si>
     <t xml:space="preserve">18.1172504425049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2592868804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3224124908447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2435054779053</t>
+    <t xml:space="preserve">18.2592849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3224105834961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2435035705566</t>
   </si>
   <si>
     <t xml:space="preserve">18.4644451141357</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2513942718506</t>
+    <t xml:space="preserve">18.251392364502</t>
   </si>
   <si>
     <t xml:space="preserve">18.2829570770264</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">18.3539752960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4407749176025</t>
+    <t xml:space="preserve">18.4407730102539</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906982421875</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">18.6696071624756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.748514175415</t>
+    <t xml:space="preserve">18.7485160827637</t>
   </si>
   <si>
     <t xml:space="preserve">18.7642974853516</t>
@@ -3746,43 +3746,43 @@
     <t xml:space="preserve">18.7011699676514</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7564067840576</t>
+    <t xml:space="preserve">18.756404876709</t>
   </si>
   <si>
     <t xml:space="preserve">18.7406234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6459312438965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7169494628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5749206542969</t>
+    <t xml:space="preserve">18.6459331512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7169513702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5749187469482</t>
   </si>
   <si>
     <t xml:space="preserve">18.8432025909424</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8984394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9536762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1903972625732</t>
+    <t xml:space="preserve">18.8984413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9536743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">19.0878200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5591373443604</t>
+    <t xml:space="preserve">18.5591354370117</t>
   </si>
   <si>
     <t xml:space="preserve">18.8589859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.937894821167</t>
+    <t xml:space="preserve">18.9378929138184</t>
   </si>
   <si>
     <t xml:space="preserve">19.2614154815674</t>
@@ -3797,10 +3797,10 @@
     <t xml:space="preserve">18.5985889434814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6538257598877</t>
+    <t xml:space="preserve">18.7721881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6538238525391</t>
   </si>
   <si>
     <t xml:space="preserve">18.4013195037842</t>
@@ -3809,16 +3809,16 @@
     <t xml:space="preserve">18.6222610473633</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2356128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1409225463867</t>
+    <t xml:space="preserve">18.2356147766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1409244537354</t>
   </si>
   <si>
     <t xml:space="preserve">18.43288230896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6380443572998</t>
+    <t xml:space="preserve">18.6380424499512</t>
   </si>
   <si>
     <t xml:space="preserve">18.8353137969971</t>
@@ -3833,7 +3833,7 @@
     <t xml:space="preserve">19.403450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5297031402588</t>
+    <t xml:space="preserve">19.5297012329102</t>
   </si>
   <si>
     <t xml:space="preserve">19.6007194519043</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">19.8374423980713</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6322803497314</t>
+    <t xml:space="preserve">19.6322822570801</t>
   </si>
   <si>
     <t xml:space="preserve">19.6954078674316</t>
@@ -3851,10 +3851,10 @@
     <t xml:space="preserve">19.640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9952583312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0662784576416</t>
+    <t xml:space="preserve">19.9952602386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.066276550293</t>
   </si>
   <si>
     <t xml:space="preserve">20.1057300567627</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">20.0504951477051</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0741672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0189304351807</t>
+    <t xml:space="preserve">20.0741691589355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0189323425293</t>
   </si>
   <si>
     <t xml:space="preserve">20.2398738861084</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">20.9027004241943</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1788787841797</t>
+    <t xml:space="preserve">21.1788768768311</t>
   </si>
   <si>
     <t xml:space="preserve">21.1946582794189</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">20.9816074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6659755706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2162036895752</t>
+    <t xml:space="preserve">20.6659774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2161998748779</t>
   </si>
   <si>
     <t xml:space="preserve">20.1372947692871</t>
@@ -3902,13 +3902,13 @@
     <t xml:space="preserve">19.1035995483398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.316650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3324337005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4744663238525</t>
+    <t xml:space="preserve">19.3166522979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3324317932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4744701385498</t>
   </si>
   <si>
     <t xml:space="preserve">19.3087596893311</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">19.0246925354004</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8116397857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0168037414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7248420715332</t>
+    <t xml:space="preserve">18.8116416931152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0168018341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7248401641846</t>
   </si>
   <si>
     <t xml:space="preserve">18.9142208099365</t>
@@ -3953,19 +3953,19 @@
     <t xml:space="preserve">19.7269725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9005699157715</t>
+    <t xml:space="preserve">19.9005680084229</t>
   </si>
   <si>
     <t xml:space="preserve">19.9479160308838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3403244018555</t>
+    <t xml:space="preserve">19.3403224945068</t>
   </si>
   <si>
     <t xml:space="preserve">19.5770454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6165027618408</t>
+    <t xml:space="preserve">19.6165008544922</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268211364746</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">20.8711395263672</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9342632293701</t>
+    <t xml:space="preserve">20.9342651367188</t>
   </si>
   <si>
     <t xml:space="preserve">20.5791778564453</t>
@@ -3983,31 +3983,31 @@
     <t xml:space="preserve">20.6817569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3187828063965</t>
+    <t xml:space="preserve">20.3187789916992</t>
   </si>
   <si>
     <t xml:space="preserve">19.8847885131836</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2119426727295</t>
+    <t xml:space="preserve">18.2119407653809</t>
   </si>
   <si>
     <t xml:space="preserve">18.2671756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3934288024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0325832366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8747673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.33030128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7958583831787</t>
+    <t xml:space="preserve">18.3934307098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.032585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8747692108154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3303031921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7958602905273</t>
   </si>
   <si>
     <t xml:space="preserve">18.3697566986084</t>
@@ -4016,34 +4016,34 @@
     <t xml:space="preserve">18.3145198822021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8095111846924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7463855743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9278736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416721343994</t>
+    <t xml:space="preserve">17.8095092773438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7463836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9278697967529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.641674041748</t>
   </si>
   <si>
     <t xml:space="preserve">17.1782474517822</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8862895965576</t>
+    <t xml:space="preserve">16.8862857818604</t>
   </si>
   <si>
     <t xml:space="preserve">16.6337833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4028205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4501647949219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.663215637207</t>
+    <t xml:space="preserve">15.4028186798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4501657485962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6632165908813</t>
   </si>
   <si>
     <t xml:space="preserve">17.0756664276123</t>
@@ -4052,31 +4052,31 @@
     <t xml:space="preserve">15.1897687911987</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5093469619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8525943756104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0441055297852</t>
+    <t xml:space="preserve">15.5093460083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8525953292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0441036224365</t>
   </si>
   <si>
     <t xml:space="preserve">16.7915992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4759654998779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8152713775635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7837085723877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4286212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7442512512207</t>
+    <t xml:space="preserve">16.4759674072266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8152694702148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7837066650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4286231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.744255065918</t>
   </si>
   <si>
     <t xml:space="preserve">17.2413730621338</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">16.9415225982666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6732349395752</t>
+    <t xml:space="preserve">16.6732368469238</t>
   </si>
   <si>
     <t xml:space="preserve">16.7600364685059</t>
@@ -4097,73 +4097,73 @@
     <t xml:space="preserve">15.7579050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4107112884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815771102905</t>
+    <t xml:space="preserve">15.4107103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815780639648</t>
   </si>
   <si>
     <t xml:space="preserve">15.9157209396362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8920488357544</t>
+    <t xml:space="preserve">15.8920469284058</t>
   </si>
   <si>
     <t xml:space="preserve">15.8683776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6277084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7973594665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7539596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8289213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.089319229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0735397338867</t>
+    <t xml:space="preserve">15.6277074813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7973604202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7539587020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8289232254028</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0893173217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0735378265381</t>
   </si>
   <si>
     <t xml:space="preserve">16.1761169433594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9236125946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6395435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5132904052734</t>
+    <t xml:space="preserve">15.9236116409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6395444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5132913589478</t>
   </si>
   <si>
     <t xml:space="preserve">14.9964447021484</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1660957336426</t>
+    <t xml:space="preserve">15.1660947799683</t>
   </si>
   <si>
     <t xml:space="preserve">15.6868877410889</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7381792068481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.765796661377</t>
+    <t xml:space="preserve">15.7381782531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7657957077026</t>
   </si>
   <si>
     <t xml:space="preserve">16.0261917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8052530288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4583644866943</t>
+    <t xml:space="preserve">15.8052492141724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4583625793457</t>
   </si>
   <si>
     <t xml:space="preserve">16.0873756408691</t>
@@ -4184,13 +4184,13 @@
     <t xml:space="preserve">16.8209209442139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5932693481445</t>
+    <t xml:space="preserve">16.5932674407959</t>
   </si>
   <si>
     <t xml:space="preserve">16.8082733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5595397949219</t>
+    <t xml:space="preserve">16.5595417022705</t>
   </si>
   <si>
     <t xml:space="preserve">16.871509552002</t>
@@ -4205,40 +4205,40 @@
     <t xml:space="preserve">16.2012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7298984527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4390106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6287202835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9828453063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2830276489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3715591430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4432249069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.506462097168</t>
+    <t xml:space="preserve">14.7298974990845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4390096664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.628719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9828443527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2830257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3715581893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4432258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5064630508423</t>
   </si>
   <si>
     <t xml:space="preserve">14.2197895050049</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6750926971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5191097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4811658859253</t>
+    <t xml:space="preserve">14.6750946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5191087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4811668395996</t>
   </si>
   <si>
     <t xml:space="preserve">14.2745952606201</t>
@@ -4253,31 +4253,31 @@
     <t xml:space="preserve">13.9289026260376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3724203109741</t>
+    <t xml:space="preserve">13.3724212646484</t>
   </si>
   <si>
     <t xml:space="preserve">13.7771348953247</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1523370742798</t>
+    <t xml:space="preserve">14.1523380279541</t>
   </si>
   <si>
     <t xml:space="preserve">14.3420476913452</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1354742050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3546934127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1987113952637</t>
+    <t xml:space="preserve">14.1354732513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3546943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1987104415894</t>
   </si>
   <si>
     <t xml:space="preserve">13.6211519241333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6801729202271</t>
+    <t xml:space="preserve">13.6801719665527</t>
   </si>
   <si>
     <t xml:space="preserve">13.8108596801758</t>
@@ -4286,22 +4286,22 @@
     <t xml:space="preserve">14.2493000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6928186416626</t>
+    <t xml:space="preserve">13.6928195953369</t>
   </si>
   <si>
     <t xml:space="preserve">13.7602710723877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7939977645874</t>
+    <t xml:space="preserve">13.7939987182617</t>
   </si>
   <si>
     <t xml:space="preserve">13.4609518051147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5494832992554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3631258010864</t>
+    <t xml:space="preserve">13.5494823455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3631267547607</t>
   </si>
   <si>
     <t xml:space="preserve">14.3926362991333</t>
@@ -4313,40 +4313,40 @@
     <t xml:space="preserve">14.4727363586426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5739154815674</t>
+    <t xml:space="preserve">14.5739145278931</t>
   </si>
   <si>
     <t xml:space="preserve">14.2577314376831</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2956733703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1944952011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4600877761841</t>
+    <t xml:space="preserve">14.2956743240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1944942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4600887298584</t>
   </si>
   <si>
     <t xml:space="preserve">14.5022468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.565484046936</t>
+    <t xml:space="preserve">14.5654821395874</t>
   </si>
   <si>
     <t xml:space="preserve">14.6371517181396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3757734298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643049240112</t>
+    <t xml:space="preserve">14.3757724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643058776855</t>
   </si>
   <si>
     <t xml:space="preserve">13.9794912338257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.768702507019</t>
+    <t xml:space="preserve">13.7687034606934</t>
   </si>
   <si>
     <t xml:space="preserve">13.9541959762573</t>
@@ -4355,10 +4355,10 @@
     <t xml:space="preserve">13.9415493011475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8530187606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4651679992676</t>
+    <t xml:space="preserve">13.8530178070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4651670455933</t>
   </si>
   <si>
     <t xml:space="preserve">13.4483041763306</t>
@@ -4367,13 +4367,13 @@
     <t xml:space="preserve">13.6380128860474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4356575012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1447696685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6295833587646</t>
+    <t xml:space="preserve">13.435658454895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1447687149048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6295824050903</t>
   </si>
   <si>
     <t xml:space="preserve">13.4272260665894</t>
@@ -4382,31 +4382,31 @@
     <t xml:space="preserve">13.4946775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5199718475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1692008972168</t>
+    <t xml:space="preserve">13.5199728012085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1692018508911</t>
   </si>
   <si>
     <t xml:space="preserve">14.0806703567505</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0722389221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9162530899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7644882202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8572330474854</t>
+    <t xml:space="preserve">14.0722379684448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9162540435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7644872665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8572340011597</t>
   </si>
   <si>
     <t xml:space="preserve">13.4735984802246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1321220397949</t>
+    <t xml:space="preserve">13.1321210861206</t>
   </si>
   <si>
     <t xml:space="preserve">12.7484865188599</t>
@@ -4415,16 +4415,16 @@
     <t xml:space="preserve">12.7527027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5334815979004</t>
+    <t xml:space="preserve">12.5334825515747</t>
   </si>
   <si>
     <t xml:space="preserve">12.4112253189087</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0065116882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3985767364502</t>
+    <t xml:space="preserve">12.0065107345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3985776901245</t>
   </si>
   <si>
     <t xml:space="preserve">12.6009340286255</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">13.1532011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9044694900513</t>
+    <t xml:space="preserve">12.9044704437256</t>
   </si>
   <si>
     <t xml:space="preserve">12.7231922149658</t>
@@ -4442,16 +4442,16 @@
     <t xml:space="preserve">12.5039710998535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5503463745117</t>
+    <t xml:space="preserve">12.5503454208374</t>
   </si>
   <si>
     <t xml:space="preserve">12.4280881881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7324867248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0908260345459</t>
+    <t xml:space="preserve">11.7324857711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0908269882202</t>
   </si>
   <si>
     <t xml:space="preserve">12.5292663574219</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">12.8538808822632</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8960380554199</t>
+    <t xml:space="preserve">12.8960390090942</t>
   </si>
   <si>
     <t xml:space="preserve">13.3007526397705</t>
@@ -4478,37 +4478,37 @@
     <t xml:space="preserve">13.6843872070312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.532618522644</t>
+    <t xml:space="preserve">13.5326194763184</t>
   </si>
   <si>
     <t xml:space="preserve">13.7897806167603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.743408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9963550567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.110179901123</t>
+    <t xml:space="preserve">13.7434072494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9963541030884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1101808547974</t>
   </si>
   <si>
     <t xml:space="preserve">14.3462619781494</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7214670181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9449043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0292186737061</t>
+    <t xml:space="preserve">14.7214660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9449024200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0292177200317</t>
   </si>
   <si>
     <t xml:space="preserve">16.1885547637939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8588619232178</t>
+    <t xml:space="preserve">16.8588638305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.6860160827637</t>
@@ -4520,7 +4520,7 @@
     <t xml:space="preserve">16.8293514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.799840927124</t>
+    <t xml:space="preserve">16.7998390197754</t>
   </si>
   <si>
     <t xml:space="preserve">16.3740482330322</t>
@@ -4529,16 +4529,16 @@
     <t xml:space="preserve">16.441499710083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4035587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3909130096436</t>
+    <t xml:space="preserve">16.4035568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3909111022949</t>
   </si>
   <si>
     <t xml:space="preserve">16.1801242828369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2349281311035</t>
+    <t xml:space="preserve">16.2349262237549</t>
   </si>
   <si>
     <t xml:space="preserve">16.3993453979492</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">16.5089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155246734619</t>
+    <t xml:space="preserve">16.7155265808105</t>
   </si>
   <si>
     <t xml:space="preserve">16.9389610290527</t>
@@ -4565,10 +4565,10 @@
     <t xml:space="preserve">16.7618980407715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0570030212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9558238983154</t>
+    <t xml:space="preserve">17.0570011138916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9558258056641</t>
   </si>
   <si>
     <t xml:space="preserve">16.2855167388916</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">17.2593593597412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2340660095215</t>
+    <t xml:space="preserve">17.2340641021729</t>
   </si>
   <si>
     <t xml:space="preserve">17.5375995635986</t>
@@ -4589,13 +4589,13 @@
     <t xml:space="preserve">17.3774013519287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4617156982422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6893672943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7146625518799</t>
+    <t xml:space="preserve">17.4617176055908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6893692016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7146644592285</t>
   </si>
   <si>
     <t xml:space="preserve">17.8579998016357</t>
@@ -4607,7 +4607,7 @@
     <t xml:space="preserve">17.8664302825928</t>
   </si>
   <si>
-    <t xml:space="preserve">18.043493270874</t>
+    <t xml:space="preserve">18.0434913635254</t>
   </si>
   <si>
     <t xml:space="preserve">18.2542819976807</t>
@@ -4625,10 +4625,10 @@
     <t xml:space="preserve">18.3891849517822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8697834014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9035110473633</t>
+    <t xml:space="preserve">18.8697814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9035091400146</t>
   </si>
   <si>
     <t xml:space="preserve">18.9625301361084</t>
@@ -4637,16 +4637,16 @@
     <t xml:space="preserve">19.1901817321777</t>
   </si>
   <si>
-    <t xml:space="preserve">19.131160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.164888381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8444881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2239074707031</t>
+    <t xml:space="preserve">19.1311626434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1648864746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8444900512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2239093780518</t>
   </si>
   <si>
     <t xml:space="preserve">19.375675201416</t>
@@ -4661,49 +4661,49 @@
     <t xml:space="preserve">19.3841075897217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4431266784668</t>
+    <t xml:space="preserve">19.4431285858154</t>
   </si>
   <si>
     <t xml:space="preserve">19.3250865936279</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2913608551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3166561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.814115524292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8984336853027</t>
+    <t xml:space="preserve">19.2913589477539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3166542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8141174316406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8984317779541</t>
   </si>
   <si>
     <t xml:space="preserve">19.9405899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9321575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8899993896484</t>
+    <t xml:space="preserve">19.9321556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8900012969971</t>
   </si>
   <si>
     <t xml:space="preserve">19.8309783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1564559936523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5358753204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0637111663818</t>
+    <t xml:space="preserve">19.1564540863037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5358734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0637092590332</t>
   </si>
   <si>
     <t xml:space="preserve">19.0890026092529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2070446014404</t>
+    <t xml:space="preserve">19.2070465087891</t>
   </si>
   <si>
     <t xml:space="preserve">19.0552787780762</t>
@@ -4721,31 +4721,31 @@
     <t xml:space="preserve">18.9793930053711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1058673858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8950786590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8023300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1952590942383</t>
+    <t xml:space="preserve">19.1058654785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.895076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8023319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1952610015869</t>
   </si>
   <si>
     <t xml:space="preserve">17.6134834289551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7745456695557</t>
+    <t xml:space="preserve">16.7745475769043</t>
   </si>
   <si>
     <t xml:space="preserve">16.9811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2391452789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114936828613</t>
+    <t xml:space="preserve">16.239143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114917755127</t>
   </si>
   <si>
     <t xml:space="preserve">16.4667949676514</t>
@@ -4754,7 +4754,7 @@
     <t xml:space="preserve">16.9052352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3782653808594</t>
+    <t xml:space="preserve">16.3782634735107</t>
   </si>
   <si>
     <t xml:space="preserve">16.1126708984375</t>
@@ -4778,19 +4778,19 @@
     <t xml:space="preserve">16.3403205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.521598815918</t>
+    <t xml:space="preserve">16.5216007232666</t>
   </si>
   <si>
     <t xml:space="preserve">16.7113094329834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.158182144165</t>
+    <t xml:space="preserve">17.1581802368164</t>
   </si>
   <si>
     <t xml:space="preserve">17.124454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0232791900635</t>
+    <t xml:space="preserve">17.0232772827148</t>
   </si>
   <si>
     <t xml:space="preserve">17.2003383636475</t>
@@ -4802,22 +4802,22 @@
     <t xml:space="preserve">17.1075916290283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0148468017578</t>
+    <t xml:space="preserve">17.0148448944092</t>
   </si>
   <si>
     <t xml:space="preserve">17.0401401519775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0654335021973</t>
+    <t xml:space="preserve">17.0654354095459</t>
   </si>
   <si>
     <t xml:space="preserve">16.8124885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5806198120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9726848602295</t>
+    <t xml:space="preserve">16.5806217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9726867675781</t>
   </si>
   <si>
     <t xml:space="preserve">17.0822982788086</t>
@@ -4826,16 +4826,16 @@
     <t xml:space="preserve">16.8546447753906</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9895515441895</t>
+    <t xml:space="preserve">16.9895496368408</t>
   </si>
   <si>
     <t xml:space="preserve">17.0738658905029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8504295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2509288787842</t>
+    <t xml:space="preserve">16.8504314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2509269714355</t>
   </si>
   <si>
     <t xml:space="preserve">17.4084911346436</t>
@@ -4844,10 +4844,10 @@
     <t xml:space="preserve">17.3769779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0168323516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8097496032715</t>
+    <t xml:space="preserve">17.0168342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8097515106201</t>
   </si>
   <si>
     <t xml:space="preserve">17.2014083862305</t>
@@ -4856,28 +4856,28 @@
     <t xml:space="preserve">17.1743984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0753593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7242164611816</t>
+    <t xml:space="preserve">17.0753574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7242183685303</t>
   </si>
   <si>
     <t xml:space="preserve">17.0213356018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.412992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4580097198486</t>
+    <t xml:space="preserve">17.4129943847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4580116271973</t>
   </si>
   <si>
     <t xml:space="preserve">17.647087097168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6425838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721771240234</t>
+    <t xml:space="preserve">17.6425857543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721790313721</t>
   </si>
   <si>
     <t xml:space="preserve">17.6020679473877</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">18.0162353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8496685028076</t>
+    <t xml:space="preserve">17.8496704101562</t>
   </si>
   <si>
     <t xml:space="preserve">17.8136539459229</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">17.4715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5750598907471</t>
+    <t xml:space="preserve">17.5750579833984</t>
   </si>
   <si>
     <t xml:space="preserve">17.786642074585</t>
@@ -4949,7 +4949,7 @@
     <t xml:space="preserve">17.8541698455811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9667167663574</t>
+    <t xml:space="preserve">17.9667148590088</t>
   </si>
   <si>
     <t xml:space="preserve">17.9036903381348</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">18.1602935791016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2863426208496</t>
+    <t xml:space="preserve">18.2863445281982</t>
   </si>
   <si>
     <t xml:space="preserve">18.2323226928711</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">18.2413272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1783027648926</t>
+    <t xml:space="preserve">18.1783008575439</t>
   </si>
   <si>
     <t xml:space="preserve">18.2683372497559</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">19.0066337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6284828186035</t>
+    <t xml:space="preserve">18.6284809112549</t>
   </si>
   <si>
     <t xml:space="preserve">18.6014709472656</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">18.6104755401611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7005100250244</t>
+    <t xml:space="preserve">18.700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">18.7365245819092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8895854949951</t>
+    <t xml:space="preserve">18.8895874023438</t>
   </si>
   <si>
     <t xml:space="preserve">18.7545318603516</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">18.8715782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5924682617188</t>
+    <t xml:space="preserve">18.5924663543701</t>
   </si>
   <si>
     <t xml:space="preserve">18.3403663635254</t>
@@ -5033,10 +5033,10 @@
     <t xml:space="preserve">18.5114345550537</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0426483154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1326847076416</t>
+    <t xml:space="preserve">19.0426464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.132682800293</t>
   </si>
   <si>
     <t xml:space="preserve">19.2497310638428</t>
@@ -5048,16 +5048,16 @@
     <t xml:space="preserve">19.1867046356201</t>
   </si>
   <si>
-    <t xml:space="preserve">19.08766746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9346046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9706172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0516529083252</t>
+    <t xml:space="preserve">19.0876655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.934606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9706192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0516510009766</t>
   </si>
   <si>
     <t xml:space="preserve">19.0246410369873</t>
@@ -5072,31 +5072,31 @@
     <t xml:space="preserve">19.1957092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8625774383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7905464172363</t>
+    <t xml:space="preserve">18.8625755310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.790548324585</t>
   </si>
   <si>
     <t xml:space="preserve">18.7815437316895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.853572845459</t>
+    <t xml:space="preserve">18.8535709381104</t>
   </si>
   <si>
     <t xml:space="preserve">18.619478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">18.259334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493671417236</t>
+    <t xml:space="preserve">18.2593326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3493690490723</t>
   </si>
   <si>
     <t xml:space="preserve">18.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3313617706299</t>
+    <t xml:space="preserve">18.3313636779785</t>
   </si>
   <si>
     <t xml:space="preserve">18.0702571868896</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">17.4670143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4805202484131</t>
+    <t xml:space="preserve">17.4805221557617</t>
   </si>
   <si>
     <t xml:space="preserve">17.6200752258301</t>
@@ -5126,13 +5126,13 @@
     <t xml:space="preserve">17.8991870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8901844024658</t>
+    <t xml:space="preserve">17.8901863098145</t>
   </si>
   <si>
     <t xml:space="preserve">18.1422863006592</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4304008483887</t>
+    <t xml:space="preserve">18.4304027557373</t>
   </si>
   <si>
     <t xml:space="preserve">18.4213981628418</t>
@@ -5147,10 +5147,10 @@
     <t xml:space="preserve">18.7725391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2047119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4388065338135</t>
+    <t xml:space="preserve">19.2047138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4388084411621</t>
   </si>
   <si>
     <t xml:space="preserve">19.6278820037842</t>
@@ -5162,19 +5162,19 @@
     <t xml:space="preserve">20.0510520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9069938659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8439693450928</t>
+    <t xml:space="preserve">19.9069957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8439712524414</t>
   </si>
   <si>
     <t xml:space="preserve">19.7899475097656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8979911804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.807954788208</t>
+    <t xml:space="preserve">19.8979930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8079566955566</t>
   </si>
   <si>
     <t xml:space="preserve">19.6729011535645</t>
@@ -5183,7 +5183,7 @@
     <t xml:space="preserve">19.9520130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0960693359375</t>
+    <t xml:space="preserve">20.0960712432861</t>
   </si>
   <si>
     <t xml:space="preserve">20.0690612792969</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">20.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5372467041016</t>
+    <t xml:space="preserve">20.5372486114502</t>
   </si>
   <si>
     <t xml:space="preserve">20.996431350708</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">21.2215213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2755451202393</t>
+    <t xml:space="preserve">21.2755432128906</t>
   </si>
   <si>
     <t xml:space="preserve">21.2935523986816</t>
@@ -5237,22 +5237,22 @@
     <t xml:space="preserve">21.7887516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9598197937012</t>
+    <t xml:space="preserve">21.9598178863525</t>
   </si>
   <si>
     <t xml:space="preserve">22.3199634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6717052459717</t>
+    <t xml:space="preserve">21.671703338623</t>
   </si>
   <si>
     <t xml:space="preserve">22.0948734283447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.265941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4190044403076</t>
+    <t xml:space="preserve">22.2659435272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.419002532959</t>
   </si>
   <si>
     <t xml:space="preserve">22.5090389251709</t>
@@ -5261,10 +5261,10 @@
     <t xml:space="preserve">22.5900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5630626678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9051990509033</t>
+    <t xml:space="preserve">22.563060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.905200958252</t>
   </si>
   <si>
     <t xml:space="preserve">22.797155380249</t>
@@ -5273,7 +5273,7 @@
     <t xml:space="preserve">23.0762672424316</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0222473144531</t>
+    <t xml:space="preserve">23.0222454071045</t>
   </si>
   <si>
     <t xml:space="preserve">23.3103618621826</t>
@@ -5288,10 +5288,10 @@
     <t xml:space="preserve">23.3193645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2293300628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4003963470459</t>
+    <t xml:space="preserve">23.2293281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4003982543945</t>
   </si>
   <si>
     <t xml:space="preserve">23.2563400268555</t>
@@ -5300,7 +5300,7 @@
     <t xml:space="preserve">23.6705074310303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5894737243652</t>
+    <t xml:space="preserve">23.5894756317139</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264472961426</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">23.8865947723389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.706521987915</t>
+    <t xml:space="preserve">23.7065200805664</t>
   </si>
   <si>
     <t xml:space="preserve">23.6975173950195</t>
@@ -5360,7 +5360,7 @@
     <t xml:space="preserve">21.6987152099609</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9148025512695</t>
+    <t xml:space="preserve">21.9148006439209</t>
   </si>
   <si>
     <t xml:space="preserve">22.5720653533936</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">22.3559799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3109607696533</t>
+    <t xml:space="preserve">22.310962677002</t>
   </si>
   <si>
     <t xml:space="preserve">22.1218852996826</t>
@@ -5384,19 +5384,19 @@
     <t xml:space="preserve">22.4550189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3289680480957</t>
+    <t xml:space="preserve">22.3289661407471</t>
   </si>
   <si>
     <t xml:space="preserve">22.6260871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6711044311523</t>
+    <t xml:space="preserve">22.671106338501</t>
   </si>
   <si>
     <t xml:space="preserve">21.608678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7977523803711</t>
+    <t xml:space="preserve">21.7977542877197</t>
   </si>
   <si>
     <t xml:space="preserve">21.968822479248</t>
@@ -5414,22 +5414,22 @@
     <t xml:space="preserve">21.5996742248535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7257251739502</t>
+    <t xml:space="preserve">21.7257232666016</t>
   </si>
   <si>
     <t xml:space="preserve">21.7527370452881</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6176815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8427715301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2749462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1038780212402</t>
+    <t xml:space="preserve">21.6176834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2749443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">22.1578998565674</t>
@@ -5438,16 +5438,16 @@
     <t xml:space="preserve">22.2839488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3019561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2569370269775</t>
+    <t xml:space="preserve">22.3019580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2569389343262</t>
   </si>
   <si>
     <t xml:space="preserve">22.7341289520264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.950216293335</t>
+    <t xml:space="preserve">22.9502182006836</t>
   </si>
   <si>
     <t xml:space="preserve">23.1843109130859</t>
@@ -5459,13 +5459,13 @@
     <t xml:space="preserve">23.0672645568848</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4364147186279</t>
+    <t xml:space="preserve">23.4364128112793</t>
   </si>
   <si>
     <t xml:space="preserve">23.5084419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.84157371521</t>
+    <t xml:space="preserve">23.8415756225586</t>
   </si>
   <si>
     <t xml:space="preserve">23.5945644378662</t>
@@ -6357,6 +6357,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.7200012207031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.7900009155273</t>
   </si>
 </sst>
 </file>
@@ -71383,7 +71386,7 @@
     </row>
     <row r="2489">
       <c r="A2489" s="1" t="n">
-        <v>45944.6494675926</v>
+        <v>45944.2916666667</v>
       </c>
       <c r="B2489" t="n">
         <v>435639</v>
@@ -71404,6 +71407,32 @@
         <v>2114</v>
       </c>
       <c r="H2489" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2490">
+      <c r="A2490" s="1" t="n">
+        <v>45945.6495833333</v>
+      </c>
+      <c r="B2490" t="n">
+        <v>691458</v>
+      </c>
+      <c r="C2490" t="n">
+        <v>33.1800003051758</v>
+      </c>
+      <c r="D2490" t="n">
+        <v>32.6100006103516</v>
+      </c>
+      <c r="E2490" t="n">
+        <v>32.8199996948242</v>
+      </c>
+      <c r="F2490" t="n">
+        <v>32.7900009155273</v>
+      </c>
+      <c r="G2490" t="s">
+        <v>2115</v>
+      </c>
+      <c r="H2490" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2118" uniqueCount="2118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="2119">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,103 +38,103 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8295068740845</t>
+    <t xml:space="preserve">10.8295078277588</t>
   </si>
   <si>
     <t xml:space="preserve">AZM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068347930908</t>
+    <t xml:space="preserve">10.7068367004395</t>
   </si>
   <si>
     <t xml:space="preserve">10.4860248565674</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1916122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91191959381104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93645286560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2259616851807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0002431869507</t>
+    <t xml:space="preserve">10.191611289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91191864013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9364538192749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.225962638855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.000244140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.617506980896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33290672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1513500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37706851959229</t>
+    <t xml:space="preserve">9.33290481567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15135097503662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37706756591797</t>
   </si>
   <si>
     <t xml:space="preserve">8.85693740844727</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25930309295654</t>
+    <t xml:space="preserve">9.25930213928223</t>
   </si>
   <si>
     <t xml:space="preserve">9.53899574279785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4899263381958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50955581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40160179138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12681674957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49483299255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43595027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84712314605713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99433040618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79805564880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05711364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86574411392212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32699489593506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61058759689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67928409576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10127639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87065315246582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53799057006836</t>
+    <t xml:space="preserve">9.48992729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50955486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40160274505615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12681770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49483394622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43595123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84712505340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99433135986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79805469512939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05711460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86574649810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32699298858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61058712005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67928314208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10127544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8706521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53798961639404</t>
   </si>
   <si>
     <t xml:space="preserve">8.78333473205566</t>
@@ -143,22 +143,22 @@
     <t xml:space="preserve">8.46929359436035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61649894714355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50364017486572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21413516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69010353088379</t>
+    <t xml:space="preserve">8.61649799346924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50364112854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21413421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69010448455811</t>
   </si>
   <si>
     <t xml:space="preserve">8.71954536437988</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29365062713623</t>
+    <t xml:space="preserve">9.29365158081055</t>
   </si>
   <si>
     <t xml:space="preserve">9.30837154388428</t>
@@ -167,13 +167,13 @@
     <t xml:space="preserve">9.47520542144775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09737586975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22004795074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41141605377197</t>
+    <t xml:space="preserve">9.09737491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22004890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41141891479492</t>
   </si>
   <si>
     <t xml:space="preserve">9.48011207580566</t>
@@ -182,13 +182,13 @@
     <t xml:space="preserve">9.77943420410156</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66166687011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79415225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77452754974365</t>
+    <t xml:space="preserve">9.6616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79415416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77452659606934</t>
   </si>
   <si>
     <t xml:space="preserve">9.68620109558105</t>
@@ -197,34 +197,34 @@
     <t xml:space="preserve">9.64694690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72545623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2357730865479</t>
+    <t xml:space="preserve">9.72545719146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2357749938965</t>
   </si>
   <si>
     <t xml:space="preserve">10.3044700622559</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83831405639648</t>
+    <t xml:space="preserve">9.83831596374512</t>
   </si>
   <si>
     <t xml:space="preserve">9.56843566894531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98552131652832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93154621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74508476257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3780746459961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449104309082</t>
+    <t xml:space="preserve">9.98552417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93154716491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74508571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3780727386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449066162109</t>
   </si>
   <si>
     <t xml:space="preserve">10.4369554519653</t>
@@ -233,46 +233,46 @@
     <t xml:space="preserve">10.5547227859497</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5056533813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5498151779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5007467269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5694427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4173278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4811182022095</t>
+    <t xml:space="preserve">10.505654335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5498161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5007476806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5694437026978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173288345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4811191558838</t>
   </si>
   <si>
     <t xml:space="preserve">10.7411842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8442277908325</t>
+    <t xml:space="preserve">10.8442287445068</t>
   </si>
   <si>
     <t xml:space="preserve">10.7853441238403</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5988826751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2897520065308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7303638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57334327697754</t>
+    <t xml:space="preserve">10.5988845825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2897491455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73036479949951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57334232330322</t>
   </si>
   <si>
     <t xml:space="preserve">9.43104457855225</t>
@@ -287,19 +287,19 @@
     <t xml:space="preserve">9.08265590667725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.35253429412842</t>
+    <t xml:space="preserve">9.35253524780273</t>
   </si>
   <si>
     <t xml:space="preserve">9.47029781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27892875671387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30346298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14644432067871</t>
+    <t xml:space="preserve">9.27893161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30346488952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14644527435303</t>
   </si>
   <si>
     <t xml:space="preserve">9.52970218658447</t>
@@ -308,61 +308,61 @@
     <t xml:space="preserve">9.79665470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1190128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89235496520996</t>
+    <t xml:space="preserve">10.1190137863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89235591888428</t>
   </si>
   <si>
     <t xml:space="preserve">9.95279598236084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1492338180542</t>
+    <t xml:space="preserve">10.1492319107056</t>
   </si>
   <si>
     <t xml:space="preserve">9.84702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76643371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42896556854248</t>
+    <t xml:space="preserve">9.76643466949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42896461486816</t>
   </si>
   <si>
     <t xml:space="preserve">9.42392826080322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52466297149658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54984855651855</t>
+    <t xml:space="preserve">9.52466583251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54984951019287</t>
   </si>
   <si>
     <t xml:space="preserve">9.39370727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82958030700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48203945159912</t>
+    <t xml:space="preserve">8.82958126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4820384979248</t>
   </si>
   <si>
     <t xml:space="preserve">8.28560161590576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46189117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53744506835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68351268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39874458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50451755523682</t>
+    <t xml:space="preserve">8.46189022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53744316101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68351173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39874267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5045166015625</t>
   </si>
   <si>
     <t xml:space="preserve">9.81680011749268</t>
@@ -371,130 +371,130 @@
     <t xml:space="preserve">8.46692943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46459674835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540798187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49985456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3487491607666</t>
+    <t xml:space="preserve">7.46459722518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5754075050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49985504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34874963760376</t>
   </si>
   <si>
     <t xml:space="preserve">7.43941211700439</t>
   </si>
   <si>
-    <t xml:space="preserve">7.2026834487915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87024974822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50256156921387</t>
+    <t xml:space="preserve">7.20268249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8702507019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50256061553955</t>
   </si>
   <si>
     <t xml:space="preserve">6.6284818649292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86017513275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02135515213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38904523849487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20771884918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44948577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66607093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52504014968872</t>
+    <t xml:space="preserve">6.86017656326294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02135562896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38904571533203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20771837234497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44948673248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66606998443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5250391960144</t>
   </si>
   <si>
     <t xml:space="preserve">7.64592409133911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79702806472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71140241622925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9430980682373</t>
+    <t xml:space="preserve">7.79702949523926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71140289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94309711456299</t>
   </si>
   <si>
     <t xml:space="preserve">7.8171763420105</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94813394546509</t>
+    <t xml:space="preserve">7.9481348991394</t>
   </si>
   <si>
     <t xml:space="preserve">7.08179759979248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92565584182739</t>
+    <t xml:space="preserve">6.92565536499023</t>
   </si>
   <si>
     <t xml:space="preserve">6.71410846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78966045379639</t>
+    <t xml:space="preserve">6.7896614074707</t>
   </si>
   <si>
     <t xml:space="preserve">6.90047025680542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22786474227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27823352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32860326766968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31852865219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39911794662476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15735006332397</t>
+    <t xml:space="preserve">7.22786569595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27823400497437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32860279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31852769851685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39911842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15734958648682</t>
   </si>
   <si>
     <t xml:space="preserve">6.94580268859863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19764471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80477142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02639198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08683443069458</t>
+    <t xml:space="preserve">7.19764423370361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80477094650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02639245986938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08683490753174</t>
   </si>
   <si>
     <t xml:space="preserve">7.04150295257568</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8501033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86521339416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069171905518</t>
+    <t xml:space="preserve">6.85010242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86521244049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069124221802</t>
   </si>
   <si>
     <t xml:space="preserve">7.22282838821411</t>
@@ -503,25 +503,25 @@
     <t xml:space="preserve">7.31349182128906</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23290348052979</t>
+    <t xml:space="preserve">7.23290252685547</t>
   </si>
   <si>
     <t xml:space="preserve">7.29838085174561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98105955123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01128196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53781890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79973459243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68388700485229</t>
+    <t xml:space="preserve">6.98106098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01128149032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53781843185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7997350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68388652801514</t>
   </si>
   <si>
     <t xml:space="preserve">6.73929214477539</t>
@@ -530,133 +530,133 @@
     <t xml:space="preserve">6.94076490402222</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90550756454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66877746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4622654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5730767250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6738133430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5982608795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8752875328064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00624418258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15231275558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30341863632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62577724456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66103410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5703706741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45452404022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5351128578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59555530548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72147607803345</t>
+    <t xml:space="preserve">6.9055061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.668776512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46226644515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57307529449463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67381381988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59826040267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87528657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00624513626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15231227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30341815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62577486038208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66103363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57037019729614</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45452308654785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53511476516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44444942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5955548286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72147560119629</t>
   </si>
   <si>
     <t xml:space="preserve">7.60562801361084</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70636510848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48474550247192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3638596534729</t>
+    <t xml:space="preserve">7.70636606216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48474502563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36386013031006</t>
   </si>
   <si>
     <t xml:space="preserve">7.26312303543091</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13216638565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17246007919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69629287719727</t>
+    <t xml:space="preserve">7.13216590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17246103286743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69629192352295</t>
   </si>
   <si>
     <t xml:space="preserve">7.91791343688965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35611724853516</t>
+    <t xml:space="preserve">8.35611820220947</t>
   </si>
   <si>
     <t xml:space="preserve">8.38633918762207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51729583740234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45181751251221</t>
+    <t xml:space="preserve">8.51729774475098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45181655883789</t>
   </si>
   <si>
     <t xml:space="preserve">8.20501232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04887199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95820760726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93132209777832</t>
+    <t xml:space="preserve">8.04887104034424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95820808410645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93132162094116</t>
   </si>
   <si>
     <t xml:space="preserve">7.71623516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73236799240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63557720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64095497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45813131332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44200038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57105302810669</t>
+    <t xml:space="preserve">7.73236846923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63557767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64095449447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45813179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4419994354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57105255126953</t>
   </si>
   <si>
     <t xml:space="preserve">7.68935060501099</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">7.79689264297485</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20018100738525</t>
+    <t xml:space="preserve">8.20017910003662</t>
   </si>
   <si>
     <t xml:space="preserve">8.43139839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61959838867188</t>
+    <t xml:space="preserve">8.61960029602051</t>
   </si>
   <si>
     <t xml:space="preserve">8.54432106018066</t>
@@ -686,16 +686,16 @@
     <t xml:space="preserve">8.58733654022217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70025825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54969692230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6034688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53356456756592</t>
+    <t xml:space="preserve">8.70025730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54969787597656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60346984863281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53356552124023</t>
   </si>
   <si>
     <t xml:space="preserve">8.5980920791626</t>
@@ -704,25 +704,25 @@
     <t xml:space="preserve">8.51743316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52818584442139</t>
+    <t xml:space="preserve">8.52818775177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.67874908447266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11429977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15731525421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2003345489502</t>
+    <t xml:space="preserve">9.11429786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15731620788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20033359527588</t>
   </si>
   <si>
     <t xml:space="preserve">9.17882537841797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05515003204346</t>
+    <t xml:space="preserve">9.05515098571777</t>
   </si>
   <si>
     <t xml:space="preserve">9.3347635269165</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">9.13043022155762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44768238067627</t>
+    <t xml:space="preserve">9.44768333435059</t>
   </si>
   <si>
     <t xml:space="preserve">9.38315677642822</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">9.41004371643066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4584379196167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4530611038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37240314483643</t>
+    <t xml:space="preserve">9.45843696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45306015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37240219116211</t>
   </si>
   <si>
     <t xml:space="preserve">9.23797416687012</t>
@@ -755,22 +755,22 @@
     <t xml:space="preserve">9.32938575744629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4691915512085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44230461120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92609786987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09278869628906</t>
+    <t xml:space="preserve">9.46919345855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44230556488037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92609977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0927906036377</t>
   </si>
   <si>
     <t xml:space="preserve">9.07128238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76478290557861</t>
+    <t xml:space="preserve">8.76478385925293</t>
   </si>
   <si>
     <t xml:space="preserve">9.16807174682617</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">9.28636932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24335098266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26485919952393</t>
+    <t xml:space="preserve">9.24335193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26486015319824</t>
   </si>
   <si>
     <t xml:space="preserve">9.23259735107422</t>
@@ -794,16 +794,16 @@
     <t xml:space="preserve">9.24872875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96373844146729</t>
+    <t xml:space="preserve">8.96373653411865</t>
   </si>
   <si>
     <t xml:space="preserve">8.495924949646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59271430969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5228099822998</t>
+    <t xml:space="preserve">8.59271335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52280902862549</t>
   </si>
   <si>
     <t xml:space="preserve">8.66799449920654</t>
@@ -812,70 +812,70 @@
     <t xml:space="preserve">8.7378978729248</t>
   </si>
   <si>
-    <t xml:space="preserve">8.711012840271</t>
+    <t xml:space="preserve">8.71101093292236</t>
   </si>
   <si>
     <t xml:space="preserve">8.70563411712646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.63573169708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53894233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50130271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28621482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43677711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47441577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62497711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56582832336426</t>
+    <t xml:space="preserve">8.6357307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53894138336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50130176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28621578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33460903167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43677616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47441673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62497615814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56582736968994</t>
   </si>
   <si>
     <t xml:space="preserve">8.47979354858398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66261672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61422157287598</t>
+    <t xml:space="preserve">8.66261768341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61422348022461</t>
   </si>
   <si>
     <t xml:space="preserve">8.78091526031494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77016162872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79166793823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18420124053955</t>
+    <t xml:space="preserve">8.77015972137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79166984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18420219421387</t>
   </si>
   <si>
     <t xml:space="preserve">9.04977321624756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14118480682373</t>
+    <t xml:space="preserve">9.14118576049805</t>
   </si>
   <si>
     <t xml:space="preserve">9.16269302368164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30249977111816</t>
+    <t xml:space="preserve">9.30250072479248</t>
   </si>
   <si>
     <t xml:space="preserve">9.13580799102783</t>
@@ -890,7 +890,7 @@
     <t xml:space="preserve">9.62513065338135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63050651550293</t>
+    <t xml:space="preserve">9.63050746917725</t>
   </si>
   <si>
     <t xml:space="preserve">9.60899829864502</t>
@@ -902,10 +902,10 @@
     <t xml:space="preserve">9.7165412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97464752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0553045272827</t>
+    <t xml:space="preserve">9.97464561462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0553035736084</t>
   </si>
   <si>
     <t xml:space="preserve">10.2435035705566</t>
@@ -917,262 +917,262 @@
     <t xml:space="preserve">10.3456707000732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2327508926392</t>
+    <t xml:space="preserve">10.2327499389648</t>
   </si>
   <si>
     <t xml:space="preserve">10.3994426727295</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4101963043213</t>
+    <t xml:space="preserve">10.4101972579956</t>
   </si>
   <si>
     <t xml:space="preserve">10.3349170684814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1305837631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036977767944</t>
+    <t xml:space="preserve">10.1305847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3295373916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.425971031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6074905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847988128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4770231246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2387800216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2728157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3408851623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2160921096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0856246948242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90410614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898321151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2614698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083135604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0062103271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94381237030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1707096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1366748809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.062933921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.199070930481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3522291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104177474976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1933994293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95515727996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.148021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2444515228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2217626571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0912961959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.159366607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5450925827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4089555740356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3181953430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2955045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3692445755005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4316434860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3976097106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7152643203735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.641526222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7436294555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7209377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6698875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7776622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7039194107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6585416793823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5394201278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.306848526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095928192139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5564374923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4826965332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3352117538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2331066131592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2784872055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0288991928101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.040244102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0969696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.034571647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9835205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96082973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2274351119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2557973861694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4940404891968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5110569000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4146270751953</t>
   </si>
   <si>
     <t xml:space="preserve">10.3295392990112</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4259700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5507659912109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6074905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847997665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4770240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2728147506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3408842086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2160921096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0856246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9041051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2898321151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2614707946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083135604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0062093734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94381237030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.170711517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1366748809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0629348754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1990728378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3522291183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1934003829956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95515823364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1480207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2444515228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841596603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2217636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0912961959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1593647003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5450916290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.408953666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3181943893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2955055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3692455291748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4316434860229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3976078033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7152662277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6415252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7436285018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7209396362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6698846817017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.777663230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7039213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6585416793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5394201278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3068513870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.556435585022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4826955795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3352117538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2331066131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2784862518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0288982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402431488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0969686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.034571647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9835205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96082878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98919296264648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2274351119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2557973861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4940404891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5110578536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4146270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3295383453369</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.3635740280151</t>
   </si>
   <si>
     <t xml:space="preserve">10.3805913925171</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4600057601929</t>
+    <t xml:space="preserve">10.4600048065186</t>
   </si>
   <si>
     <t xml:space="preserve">10.5167303085327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3465566635132</t>
+    <t xml:space="preserve">10.3465576171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.84738159179688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86439895629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72825908660889</t>
+    <t xml:space="preserve">9.86439800262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7282600402832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67720699310303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66018962860107</t>
+    <t xml:space="preserve">9.66018867492676</t>
   </si>
   <si>
     <t xml:space="preserve">9.48434352874756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68855285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58644771575928</t>
+    <t xml:space="preserve">9.688551902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58644866943359</t>
   </si>
   <si>
     <t xml:space="preserve">9.71124172210693</t>
@@ -1184,19 +1184,19 @@
     <t xml:space="preserve">9.61480903625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.6204833984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73393154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78498458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79632949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89843368530273</t>
+    <t xml:space="preserve">9.62048244476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73393058776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78498363494873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7963285446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89843273162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.16101360321045</t>
@@ -1205,64 +1205,64 @@
     <t xml:space="preserve">8.95113372802734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99084091186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76961326599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75259780883789</t>
+    <t xml:space="preserve">8.99083995819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76961421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75259590148926</t>
   </si>
   <si>
     <t xml:space="preserve">8.86604595184326</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85470199584961</t>
+    <t xml:space="preserve">8.85470104217529</t>
   </si>
   <si>
     <t xml:space="preserve">9.05891036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24042701721191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25177383422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10996246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09294319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98516845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07592678070068</t>
+    <t xml:space="preserve">9.24042797088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2517728805542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10996150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09294509887695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98516750335693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.075927734375</t>
   </si>
   <si>
     <t xml:space="preserve">9.13265132904053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05323696136475</t>
+    <t xml:space="preserve">9.05323600769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.90008068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88306331634521</t>
+    <t xml:space="preserve">8.8830623626709</t>
   </si>
   <si>
     <t xml:space="preserve">8.82633876800537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79230308532715</t>
+    <t xml:space="preserve">8.79230403900146</t>
   </si>
   <si>
     <t xml:space="preserve">8.79797649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96815013885498</t>
+    <t xml:space="preserve">8.9681510925293</t>
   </si>
   <si>
     <t xml:space="preserve">9.00218486785889</t>
@@ -1283,31 +1283,31 @@
     <t xml:space="preserve">9.04189109802246</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03054809570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01352977752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04756355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03621864318848</t>
+    <t xml:space="preserve">9.03054714202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01353168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04756450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03621959686279</t>
   </si>
   <si>
     <t xml:space="preserve">9.13832378387451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97382354736328</t>
+    <t xml:space="preserve">8.97382259368896</t>
   </si>
   <si>
     <t xml:space="preserve">9.12697887420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16668701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19504833221436</t>
+    <t xml:space="preserve">9.16668605804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19504737854004</t>
   </si>
   <si>
     <t xml:space="preserve">9.37089538574219</t>
@@ -1316,7 +1316,7 @@
     <t xml:space="preserve">9.38224029541016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34253215789795</t>
+    <t xml:space="preserve">9.34253120422363</t>
   </si>
   <si>
     <t xml:space="preserve">9.46732616424561</t>
@@ -1325,64 +1325,64 @@
     <t xml:space="preserve">10.6755599975586</t>
   </si>
   <si>
-    <t xml:space="preserve">10.420298576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3919353485107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5961456298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7549715042114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7379550933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7606449127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.661376953125</t>
+    <t xml:space="preserve">10.4202995300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3919372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5961446762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7549743652344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7379579544067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.760645866394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6613779067993</t>
   </si>
   <si>
     <t xml:space="preserve">10.4543333053589</t>
   </si>
   <si>
-    <t xml:space="preserve">10.403281211853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4429883956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3777551651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0742797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1338376998901</t>
+    <t xml:space="preserve">10.4032821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4429874420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3777561187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0742788314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1338396072388</t>
   </si>
   <si>
     <t xml:space="preserve">10.0941324234009</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98635578155518</t>
+    <t xml:space="preserve">9.98635768890381</t>
   </si>
   <si>
     <t xml:space="preserve">10.1565284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962366104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2359447479248</t>
+    <t xml:space="preserve">10.1962356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2359437942505</t>
   </si>
   <si>
     <t xml:space="preserve">10.1622018814087</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2416162490845</t>
+    <t xml:space="preserve">10.2416172027588</t>
   </si>
   <si>
     <t xml:space="preserve">10.2501249313354</t>
@@ -1391,19 +1391,19 @@
     <t xml:space="preserve">10.2132530212402</t>
   </si>
   <si>
-    <t xml:space="preserve">10.167875289917</t>
+    <t xml:space="preserve">10.1678743362427</t>
   </si>
   <si>
     <t xml:space="preserve">9.90694046020508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9296293258667</t>
+    <t xml:space="preserve">9.92963027954102</t>
   </si>
   <si>
     <t xml:space="preserve">10.1877269744873</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2302722930908</t>
+    <t xml:space="preserve">10.2302703857422</t>
   </si>
   <si>
     <t xml:space="preserve">10.0203895568848</t>
@@ -1412,13 +1412,13 @@
     <t xml:space="preserve">10.1905641555786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.182056427002</t>
+    <t xml:space="preserve">10.1820554733276</t>
   </si>
   <si>
     <t xml:space="preserve">10.0317354202271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97784900665283</t>
+    <t xml:space="preserve">9.9778470993042</t>
   </si>
   <si>
     <t xml:space="preserve">9.81618213653564</t>
@@ -1427,34 +1427,34 @@
     <t xml:space="preserve">9.88708782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89559555053711</t>
+    <t xml:space="preserve">9.89559650421143</t>
   </si>
   <si>
     <t xml:space="preserve">9.81334590911865</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97500991821289</t>
+    <t xml:space="preserve">9.97501087188721</t>
   </si>
   <si>
     <t xml:space="preserve">10.065770149231</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395120620728</t>
+    <t xml:space="preserve">10.1395111083984</t>
   </si>
   <si>
     <t xml:space="preserve">10.0005369186401</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0686054229736</t>
+    <t xml:space="preserve">10.0686044692993</t>
   </si>
   <si>
     <t xml:space="preserve">9.73676681518555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83603477478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89276027679443</t>
+    <t xml:space="preserve">9.83603668212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89276123046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.86723518371582</t>
@@ -1469,10 +1469,10 @@
     <t xml:space="preserve">9.83320045471191</t>
   </si>
   <si>
-    <t xml:space="preserve">9.94948387145996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714426040649</t>
+    <t xml:space="preserve">9.94948482513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714406967163</t>
   </si>
   <si>
     <t xml:space="preserve">9.93814086914062</t>
@@ -1490,28 +1490,28 @@
     <t xml:space="preserve">9.21773815155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12414360046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24326419830322</t>
+    <t xml:space="preserve">9.12414264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24326610565186</t>
   </si>
   <si>
     <t xml:space="preserve">9.20072174072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29274559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51369571685791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39841842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47206783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4400463104248</t>
+    <t xml:space="preserve">9.29274463653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51369762420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39841747283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47206878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44004726409912</t>
   </si>
   <si>
     <t xml:space="preserve">9.3375768661499</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">9.02696514129639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89887619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34398078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31836318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93730449676514</t>
+    <t xml:space="preserve">8.89887523651123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34397983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31836223602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93730354309082</t>
   </si>
   <si>
     <t xml:space="preserve">8.92129135131836</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">8.93410110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64590358734131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83803462982178</t>
+    <t xml:space="preserve">8.64590454101562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83803558349609</t>
   </si>
   <si>
     <t xml:space="preserve">8.7547779083252</t>
@@ -1553,46 +1553,46 @@
     <t xml:space="preserve">8.72275638580322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71635150909424</t>
+    <t xml:space="preserve">8.71635246276855</t>
   </si>
   <si>
     <t xml:space="preserve">8.64270114898682</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8284273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8060131072998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83162975311279</t>
+    <t xml:space="preserve">8.82842826843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80601215362549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83163070678711</t>
   </si>
   <si>
     <t xml:space="preserve">8.66511726379395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73556518554688</t>
+    <t xml:space="preserve">8.73556613922119</t>
   </si>
   <si>
     <t xml:space="preserve">8.51781558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48899745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56905269622803</t>
+    <t xml:space="preserve">8.4889965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56904983520508</t>
   </si>
   <si>
     <t xml:space="preserve">8.45697498321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39613437652588</t>
+    <t xml:space="preserve">8.39613342285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.51141166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53062534332275</t>
+    <t xml:space="preserve">8.53062629699707</t>
   </si>
   <si>
     <t xml:space="preserve">8.53703022003174</t>
@@ -1601,31 +1601,31 @@
     <t xml:space="preserve">8.54343318939209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71315002441406</t>
+    <t xml:space="preserve">8.71314907073975</t>
   </si>
   <si>
     <t xml:space="preserve">8.40573978424072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36410999298096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33209037780762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.42175102233887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58506202697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57225513458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46017742156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46658229827881</t>
+    <t xml:space="preserve">8.36411190032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.3320894241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.42175197601318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58506107330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5722541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46017646789551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46658134460449</t>
   </si>
   <si>
     <t xml:space="preserve">8.58186149597168</t>
@@ -1634,34 +1634,34 @@
     <t xml:space="preserve">8.4409646987915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09420967102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01735687255859</t>
+    <t xml:space="preserve">9.09421062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01735782623291</t>
   </si>
   <si>
     <t xml:space="preserve">9.05578327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19988250732422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18707275390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91808891296387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87646102905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03657150268555</t>
+    <t xml:space="preserve">9.1998815536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18707370758057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91808986663818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87646198272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03657054901123</t>
   </si>
   <si>
     <t xml:space="preserve">9.18387126922607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15505218505859</t>
+    <t xml:space="preserve">9.15505027770996</t>
   </si>
   <si>
     <t xml:space="preserve">9.1518497467041</t>
@@ -1676,37 +1676,37 @@
     <t xml:space="preserve">9.1262321472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26072406768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25432014465332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2062873840332</t>
+    <t xml:space="preserve">9.26072216033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.254319190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20628643035889</t>
   </si>
   <si>
     <t xml:space="preserve">9.20948886871338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22550010681152</t>
+    <t xml:space="preserve">9.22549915313721</t>
   </si>
   <si>
     <t xml:space="preserve">9.10701942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92769622802734</t>
+    <t xml:space="preserve">8.92769813537598</t>
   </si>
   <si>
     <t xml:space="preserve">8.76758670806885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65871238708496</t>
+    <t xml:space="preserve">8.65871143341064</t>
   </si>
   <si>
     <t xml:space="preserve">8.68112754821777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72595882415771</t>
+    <t xml:space="preserve">8.72595691680908</t>
   </si>
   <si>
     <t xml:space="preserve">8.61708450317383</t>
@@ -1715,19 +1715,19 @@
     <t xml:space="preserve">8.7803955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82202339172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77719306945801</t>
+    <t xml:space="preserve">8.82202529907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77719402313232</t>
   </si>
   <si>
     <t xml:space="preserve">8.78359699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95331382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97252559661865</t>
+    <t xml:space="preserve">8.95331478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97252655029297</t>
   </si>
   <si>
     <t xml:space="preserve">8.9661226272583</t>
@@ -1736,115 +1736,115 @@
     <t xml:space="preserve">8.86685466766357</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86044979095459</t>
+    <t xml:space="preserve">8.86045074462891</t>
   </si>
   <si>
     <t xml:space="preserve">8.32568550109863</t>
   </si>
   <si>
-    <t xml:space="preserve">8.2232141494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29366397857666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53382873535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48259353637695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40253734588623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14956474304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06630706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07271289825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77490997314453</t>
+    <t xml:space="preserve">8.22321510314941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29366302490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53382682800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48259258270264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40253829956055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14956569671631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06630802154541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07271194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7749080657959</t>
   </si>
   <si>
     <t xml:space="preserve">7.74929141998291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67884302139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87417793273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73007869720459</t>
+    <t xml:space="preserve">7.67884397506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87417602539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73007822036743</t>
   </si>
   <si>
     <t xml:space="preserve">7.53474521636963</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42266893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25295305252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21772861480713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08003568649292</t>
+    <t xml:space="preserve">7.42266941070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25295352935791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21772813796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0800347328186</t>
   </si>
   <si>
     <t xml:space="preserve">7.11205673217773</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8494758605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97115993499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03520441055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04801225662231</t>
+    <t xml:space="preserve">6.84947681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97116041183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04160833358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03520393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04801177978516</t>
   </si>
   <si>
     <t xml:space="preserve">6.94234085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95194816589355</t>
+    <t xml:space="preserve">6.95194673538208</t>
   </si>
   <si>
     <t xml:space="preserve">7.00958633422852</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1312689781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97436237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8302640914917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95514917373657</t>
+    <t xml:space="preserve">7.13126850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97436141967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83026361465454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95514869689941</t>
   </si>
   <si>
     <t xml:space="preserve">6.80144500732422</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76621961593628</t>
+    <t xml:space="preserve">6.7662205696106</t>
   </si>
   <si>
     <t xml:space="preserve">6.8590841293335</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6285252571106</t>
+    <t xml:space="preserve">6.62852668762207</t>
   </si>
   <si>
     <t xml:space="preserve">6.70537853240967</t>
@@ -1862,19 +1862,19 @@
     <t xml:space="preserve">7.09604597091675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06722640991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02239513397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23053741455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05761909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80464601516724</t>
+    <t xml:space="preserve">7.06722688674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02239608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23053693771362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05762004852295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80464506149292</t>
   </si>
   <si>
     <t xml:space="preserve">6.89110565185547</t>
@@ -1883,37 +1883,37 @@
     <t xml:space="preserve">6.71818780899048</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73740100860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95835161209106</t>
+    <t xml:space="preserve">6.7374005317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95835113525391</t>
   </si>
   <si>
     <t xml:space="preserve">7.01278877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88790321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45881080627441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.3979697227478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15204095840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15844535827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96375179290771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10592937469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10721063613892</t>
+    <t xml:space="preserve">6.88790416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45881032943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39796829223633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1520414352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15844488143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96375226974487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10592985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10721015930176</t>
   </si>
   <si>
     <t xml:space="preserve">6.39925003051758</t>
@@ -1922,10 +1922,10 @@
     <t xml:space="preserve">6.64453649520874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6317286491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59010028839111</t>
+    <t xml:space="preserve">6.63172817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59010076522827</t>
   </si>
   <si>
     <t xml:space="preserve">6.50043916702271</t>
@@ -1934,46 +1934,46 @@
     <t xml:space="preserve">6.60290861129761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59650373458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41718101501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52285480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42038440704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47802352905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4460015296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32624006271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26731967926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74380540847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09924793243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30739068984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19851493835449</t>
+    <t xml:space="preserve">6.59650421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41718053817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52285385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42038488388062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47802305221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44600200653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32624101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26732015609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74380397796631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09924745559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30738973617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19851541519165</t>
   </si>
   <si>
     <t xml:space="preserve">7.08964109420776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11845970153809</t>
+    <t xml:space="preserve">7.11846113204956</t>
   </si>
   <si>
     <t xml:space="preserve">7.15368556976318</t>
@@ -1982,25 +1982,25 @@
     <t xml:space="preserve">7.15688705444336</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17930269241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04481077194214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99357604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27216672897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44828653335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75889825820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57637310028076</t>
+    <t xml:space="preserve">7.17930221557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04481029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99357557296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27216625213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44828462600708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75889873504639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5763726234436</t>
   </si>
   <si>
     <t xml:space="preserve">7.72687673568726</t>
@@ -2009,25 +2009,25 @@
     <t xml:space="preserve">7.83895301818848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82614421844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8453574180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89979410171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91260290145874</t>
+    <t xml:space="preserve">7.82614278793335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84535598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8997950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91260242462158</t>
   </si>
   <si>
     <t xml:space="preserve">7.98305082321167</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88058090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91900825500488</t>
+    <t xml:space="preserve">7.88057994842529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91900777816772</t>
   </si>
   <si>
     <t xml:space="preserve">8.23282146453857</t>
@@ -2036,34 +2036,34 @@
     <t xml:space="preserve">8.12074565887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26164150238037</t>
+    <t xml:space="preserve">8.26164054870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.47298622131348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46337795257568</t>
+    <t xml:space="preserve">8.46337890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.84764194488525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9116849899292</t>
+    <t xml:space="preserve">8.91168594360352</t>
   </si>
   <si>
     <t xml:space="preserve">9.2639274597168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33117198944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53291034698486</t>
+    <t xml:space="preserve">9.3311710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53290939331055</t>
   </si>
   <si>
     <t xml:space="preserve">9.67700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51049327850342</t>
+    <t xml:space="preserve">9.51049423217773</t>
   </si>
   <si>
     <t xml:space="preserve">9.42083263397217</t>
@@ -2072,67 +2072,67 @@
     <t xml:space="preserve">9.32796859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40482139587402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47847175598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55212116241455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5713357925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70262432098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77627563476562</t>
+    <t xml:space="preserve">9.40482330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47847366333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55212306976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57133674621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.70262622833252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77627658843994</t>
   </si>
   <si>
     <t xml:space="preserve">9.81470203399658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0836868286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0356521606445</t>
+    <t xml:space="preserve">10.083685874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0356531143188</t>
   </si>
   <si>
     <t xml:space="preserve">10.1413249969482</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2149753570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.195761680603</t>
+    <t xml:space="preserve">10.21497631073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1957626342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.2694120407104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2790184020996</t>
+    <t xml:space="preserve">10.2790203094482</t>
   </si>
   <si>
     <t xml:space="preserve">10.5608129501343</t>
   </si>
   <si>
-    <t xml:space="preserve">10.849009513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.868221282959</t>
+    <t xml:space="preserve">10.8490085601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8682222366333</t>
   </si>
   <si>
     <t xml:space="preserve">10.8874340057373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0155210494995</t>
+    <t xml:space="preserve">11.0155229568481</t>
   </si>
   <si>
     <t xml:space="preserve">11.0603523254395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2813053131104</t>
+    <t xml:space="preserve">11.281304359436</t>
   </si>
   <si>
     <t xml:space="preserve">11.2909097671509</t>
@@ -2144,10 +2144,10 @@
     <t xml:space="preserve">11.5278730392456</t>
   </si>
   <si>
-    <t xml:space="preserve">11.495849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3773679733276</t>
+    <t xml:space="preserve">11.4958515167236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3773698806763</t>
   </si>
   <si>
     <t xml:space="preserve">11.3261337280273</t>
@@ -2165,43 +2165,43 @@
     <t xml:space="preserve">10.5992374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0219249725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1404066085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1141204833984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7917680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7882652282715</t>
+    <t xml:space="preserve">11.0219259262085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1404075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1141195297241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7917671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882642745972</t>
   </si>
   <si>
     <t xml:space="preserve">10.4203634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5780363082886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3993406295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4273719787598</t>
+    <t xml:space="preserve">10.5780353546143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.399341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4273710250854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2872190475464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3888292312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.423867225647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.367805480957</t>
+    <t xml:space="preserve">10.3888282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4238681793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3678073883057</t>
   </si>
   <si>
     <t xml:space="preserve">10.7322034835815</t>
@@ -2216,7 +2216,7 @@
     <t xml:space="preserve">10.5079593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5149669647217</t>
+    <t xml:space="preserve">10.5149660110474</t>
   </si>
   <si>
     <t xml:space="preserve">10.6305932998657</t>
@@ -2231,13 +2231,13 @@
     <t xml:space="preserve">11.1876993179321</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3523807525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5731201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6151666641235</t>
+    <t xml:space="preserve">11.3523797988892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5731191635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6151676177979</t>
   </si>
   <si>
     <t xml:space="preserve">11.7553195953369</t>
@@ -2249,10 +2249,10 @@
     <t xml:space="preserve">11.8429145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7097692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6291818618774</t>
+    <t xml:space="preserve">11.7097673416138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6291799545288</t>
   </si>
   <si>
     <t xml:space="preserve">11.8639373779297</t>
@@ -2261,16 +2261,16 @@
     <t xml:space="preserve">11.9059829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9199991226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0496397018433</t>
+    <t xml:space="preserve">11.9200010299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0496406555176</t>
   </si>
   <si>
     <t xml:space="preserve">12.2318382263184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2248315811157</t>
+    <t xml:space="preserve">12.2248306274414</t>
   </si>
   <si>
     <t xml:space="preserve">12.2984113693237</t>
@@ -2279,22 +2279,22 @@
     <t xml:space="preserve">12.214319229126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3159303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2773895263672</t>
+    <t xml:space="preserve">12.3159313201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2773885726929</t>
   </si>
   <si>
     <t xml:space="preserve">12.4175415039062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684883117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1267242431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0391292572021</t>
+    <t xml:space="preserve">12.3684873580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1267251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0391283035278</t>
   </si>
   <si>
     <t xml:space="preserve">11.8464193344116</t>
@@ -2306,25 +2306,25 @@
     <t xml:space="preserve">12.1407403945923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1232194900513</t>
+    <t xml:space="preserve">12.1232204437256</t>
   </si>
   <si>
     <t xml:space="preserve">12.1092052459717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0321207046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8779544830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760599136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6887464523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4680061340332</t>
+    <t xml:space="preserve">12.0321216583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8779535293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760608673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6887474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4680051803589</t>
   </si>
   <si>
     <t xml:space="preserve">11.4890289306641</t>
@@ -2336,19 +2336,19 @@
     <t xml:space="preserve">11.6782360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2472639083862</t>
+    <t xml:space="preserve">11.2472648620605</t>
   </si>
   <si>
     <t xml:space="preserve">11.0370359420776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1001043319702</t>
+    <t xml:space="preserve">11.1001052856445</t>
   </si>
   <si>
     <t xml:space="preserve">10.7216920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9284181594849</t>
+    <t xml:space="preserve">10.9284172058105</t>
   </si>
   <si>
     <t xml:space="preserve">11.1561651229858</t>
@@ -2369,13 +2369,13 @@
     <t xml:space="preserve">11.2752962112427</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0615615844727</t>
+    <t xml:space="preserve">11.061562538147</t>
   </si>
   <si>
     <t xml:space="preserve">11.4049377441406</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2297449111938</t>
+    <t xml:space="preserve">11.2297458648682</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119443893433</t>
@@ -2384,7 +2384,7 @@
     <t xml:space="preserve">11.4995403289795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.790358543396</t>
+    <t xml:space="preserve">11.7903575897217</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814563751221</t>
@@ -2393,16 +2393,16 @@
     <t xml:space="preserve">11.8288993835449</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9550361633301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6677227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6712284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113794326782</t>
+    <t xml:space="preserve">11.9550371170044</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6677236557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6712293624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113803863525</t>
   </si>
   <si>
     <t xml:space="preserve">11.9970836639404</t>
@@ -2411,49 +2411,49 @@
     <t xml:space="preserve">11.9410219192505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9690532684326</t>
+    <t xml:space="preserve">11.9690523147583</t>
   </si>
   <si>
     <t xml:space="preserve">12.0671586990356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2703819274902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2738828659058</t>
+    <t xml:space="preserve">12.2703809738159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2738838195801</t>
   </si>
   <si>
     <t xml:space="preserve">12.1021976470947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0951890945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9725551605225</t>
+    <t xml:space="preserve">12.0951900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9725561141968</t>
   </si>
   <si>
     <t xml:space="preserve">12.0146017074585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0741653442383</t>
+    <t xml:space="preserve">12.0741662979126</t>
   </si>
   <si>
     <t xml:space="preserve">11.9865713119507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6011524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5520992279053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5485935211182</t>
+    <t xml:space="preserve">11.6011505126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.552098274231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5485944747925</t>
   </si>
   <si>
     <t xml:space="preserve">11.5941429138184</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4259605407715</t>
+    <t xml:space="preserve">11.4259595870972</t>
   </si>
   <si>
     <t xml:space="preserve">11.5380821228027</t>
@@ -2462,25 +2462,25 @@
     <t xml:space="preserve">11.6852426528931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7693347930908</t>
+    <t xml:space="preserve">11.7693338394165</t>
   </si>
   <si>
     <t xml:space="preserve">11.7027626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9480285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0846786499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2108154296875</t>
+    <t xml:space="preserve">11.9480295181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0846796035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2108144760132</t>
   </si>
   <si>
     <t xml:space="preserve">12.7539081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9641380310059</t>
+    <t xml:space="preserve">12.9641361236572</t>
   </si>
   <si>
     <t xml:space="preserve">12.7188701629639</t>
@@ -2489,88 +2489,88 @@
     <t xml:space="preserve">12.7889461517334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7959547042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9886636734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1743659973145</t>
+    <t xml:space="preserve">12.795952796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9886646270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1743650436401</t>
   </si>
   <si>
     <t xml:space="preserve">12.9080762863159</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0412216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094049453735</t>
+    <t xml:space="preserve">13.0412225723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094068527222</t>
   </si>
   <si>
     <t xml:space="preserve">13.6649026870728</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8996562957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007043838501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3656663894653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389627456665</t>
+    <t xml:space="preserve">13.8996572494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007034301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.365665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389636993408</t>
   </si>
   <si>
     <t xml:space="preserve">15.0173759460449</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1365070343018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5289335250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9493923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181425094604</t>
+    <t xml:space="preserve">15.1365060806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5289354324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9493932723999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181396484375</t>
   </si>
   <si>
     <t xml:space="preserve">15.9213619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1035594940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9914398193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.124584197998</t>
+    <t xml:space="preserve">16.1035614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9914388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1245861053467</t>
   </si>
   <si>
     <t xml:space="preserve">16.4118976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5940952301025</t>
+    <t xml:space="preserve">16.5940971374512</t>
   </si>
   <si>
     <t xml:space="preserve">16.5100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2086734771729</t>
+    <t xml:space="preserve">16.2086772918701</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474987030029</t>
   </si>
   <si>
-    <t xml:space="preserve">15.886323928833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4868879318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8232555389404</t>
+    <t xml:space="preserve">15.8863248825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4868869781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8232545852661</t>
   </si>
   <si>
     <t xml:space="preserve">15.7531785964966</t>
@@ -2579,25 +2579,25 @@
     <t xml:space="preserve">15.7251482009888</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1575298309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3817739486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2626447677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.297682762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0804471969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2836675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2205991744995</t>
+    <t xml:space="preserve">15.1575288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3817749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2626457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2976818084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0804452896118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2836666107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2205972671509</t>
   </si>
   <si>
     <t xml:space="preserve">15.0944604873657</t>
@@ -2606,40 +2606,40 @@
     <t xml:space="preserve">15.0664300918579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0454053878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.856201171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9122638702393</t>
+    <t xml:space="preserve">15.0454063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8562002182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9122610092163</t>
   </si>
   <si>
     <t xml:space="preserve">15.1715450286865</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8702154159546</t>
+    <t xml:space="preserve">14.8702163696289</t>
   </si>
   <si>
     <t xml:space="preserve">14.7721099853516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3537435531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5029964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5800800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4189071655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7062168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8043231964111</t>
+    <t xml:space="preserve">15.3537425994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5029945373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5800819396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4189052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7062187194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8043270111084</t>
   </si>
   <si>
     <t xml:space="preserve">16.6221256256104</t>
@@ -2651,37 +2651,37 @@
     <t xml:space="preserve">16.9865226745605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0075454711914</t>
+    <t xml:space="preserve">17.00754737854</t>
   </si>
   <si>
     <t xml:space="preserve">16.5380363464355</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0545082092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3978824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4959907531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0685214996338</t>
+    <t xml:space="preserve">16.0545063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3978805541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4959888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0685234069824</t>
   </si>
   <si>
     <t xml:space="preserve">15.5499582290649</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5709791183472</t>
+    <t xml:space="preserve">15.5709781646729</t>
   </si>
   <si>
     <t xml:space="preserve">16.033483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9423866271973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1666297912598</t>
+    <t xml:space="preserve">15.9423837661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1666278839111</t>
   </si>
   <si>
     <t xml:space="preserve">16.6431503295898</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">16.762279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7833023071289</t>
+    <t xml:space="preserve">16.7833042144775</t>
   </si>
   <si>
     <t xml:space="preserve">16.6711807250977</t>
@@ -2705,16 +2705,16 @@
     <t xml:space="preserve">16.9514865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6130266189575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5198335647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3516492843628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5478668212891</t>
+    <t xml:space="preserve">15.6130285263062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5198354721069</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3516521453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5478639602661</t>
   </si>
   <si>
     <t xml:space="preserve">13.7910404205322</t>
@@ -2729,28 +2729,28 @@
     <t xml:space="preserve">12.9956722259521</t>
   </si>
   <si>
-    <t xml:space="preserve">12.347466468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7202816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3327665328979</t>
+    <t xml:space="preserve">12.3474655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7202825546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3327674865723</t>
   </si>
   <si>
     <t xml:space="preserve">9.68806457519531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81069946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25149822235107</t>
+    <t xml:space="preserve">9.81069850921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25149726867676</t>
   </si>
   <si>
     <t xml:space="preserve">9.51988220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44420719146729</t>
+    <t xml:space="preserve">8.4442081451416</t>
   </si>
   <si>
     <t xml:space="preserve">8.02024555206299</t>
@@ -2762,25 +2762,25 @@
     <t xml:space="preserve">7.77497911453247</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49817705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59978818893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28653717041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06088066101074</t>
+    <t xml:space="preserve">7.49817657470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59978771209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28653621673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06088161468506</t>
   </si>
   <si>
     <t xml:space="preserve">9.69507312774658</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05036926269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87167453765869</t>
+    <t xml:space="preserve">9.05037021636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87167549133301</t>
   </si>
   <si>
     <t xml:space="preserve">9.2360725402832</t>
@@ -2792,40 +2792,40 @@
     <t xml:space="preserve">9.07489585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68246746063232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02233982086182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48834609985352</t>
+    <t xml:space="preserve">8.68246841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02233791351318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48834800720215</t>
   </si>
   <si>
     <t xml:space="preserve">10.1680889129639</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2381639480591</t>
+    <t xml:space="preserve">10.2381649017334</t>
   </si>
   <si>
     <t xml:space="preserve">9.87727165222168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29913997650146</t>
+    <t xml:space="preserve">9.29914093017578</t>
   </si>
   <si>
     <t xml:space="preserve">9.4463005065918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51637840270996</t>
+    <t xml:space="preserve">9.51637744903564</t>
   </si>
   <si>
     <t xml:space="preserve">9.58995914459229</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25359153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33417797088623</t>
+    <t xml:space="preserve">9.2535924911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33417892456055</t>
   </si>
   <si>
     <t xml:space="preserve">9.49535465240479</t>
@@ -2837,19 +2837,19 @@
     <t xml:space="preserve">10.3713102340698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8162965774536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2122268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793630599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.760232925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8618440628052</t>
+    <t xml:space="preserve">10.816294670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2122278213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793640136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7602338790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8618450164795</t>
   </si>
   <si>
     <t xml:space="preserve">10.5324859619141</t>
@@ -2870,7 +2870,7 @@
     <t xml:space="preserve">11.0058345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4649333953857</t>
+    <t xml:space="preserve">10.4649343490601</t>
   </si>
   <si>
     <t xml:space="preserve">10.7654342651367</t>
@@ -2879,7 +2879,7 @@
     <t xml:space="preserve">10.6414775848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.769190788269</t>
+    <t xml:space="preserve">10.7691898345947</t>
   </si>
   <si>
     <t xml:space="preserve">10.8743667602539</t>
@@ -2897,22 +2897,22 @@
     <t xml:space="preserve">11.1936473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3251171112061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5204420089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7984056472778</t>
+    <t xml:space="preserve">11.3251161575317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5204429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7984046936035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913925170898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6923952102661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9966497421265</t>
+    <t xml:space="preserve">12.6923961639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9966506958008</t>
   </si>
   <si>
     <t xml:space="preserve">12.4407243728638</t>
@@ -2924,7 +2924,7 @@
     <t xml:space="preserve">11.648154258728</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6105918884277</t>
+    <t xml:space="preserve">11.6105928421021</t>
   </si>
   <si>
     <t xml:space="preserve">11.5166854858398</t>
@@ -2933,130 +2933,130 @@
     <t xml:space="preserve">11.7721109390259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669359207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5091733932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7157669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5730304718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8284559249878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2687730789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4490728378296</t>
+    <t xml:space="preserve">11.6669368743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5091724395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7157678604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5730295181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8284549713135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2687721252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4490718841553</t>
   </si>
   <si>
     <t xml:space="preserve">11.2011604309082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4791240692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.42653465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3664350509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6631803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5429782867432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7796249389648</t>
+    <t xml:space="preserve">11.4791231155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4265356063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3664360046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.663179397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5429792404175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7796239852905</t>
   </si>
   <si>
     <t xml:space="preserve">11.7608423233032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4753656387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6706924438477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8585062026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8434810638428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3580894470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3205242156982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.801326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6999063491821</t>
+    <t xml:space="preserve">11.4753665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6706914901733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8585033416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8434820175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3580884933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3205251693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8013257980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6999073028564</t>
   </si>
   <si>
     <t xml:space="preserve">12.7337141036987</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8351316452026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5684385299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6097564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3731126785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4369688034058</t>
+    <t xml:space="preserve">12.835132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5684375762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6097555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3731117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4369697570801</t>
   </si>
   <si>
     <t xml:space="preserve">12.0763692855835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0575876235962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3693561553955</t>
+    <t xml:space="preserve">12.0575857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3693571090698</t>
   </si>
   <si>
     <t xml:space="preserve">12.3505744934082</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4745321273804</t>
+    <t xml:space="preserve">12.4745311737061</t>
   </si>
   <si>
     <t xml:space="preserve">12.493311882019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.470775604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8276205062866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.79381275177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6585884094238</t>
+    <t xml:space="preserve">12.4707765579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8276214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938146591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6585893630981</t>
   </si>
   <si>
     <t xml:space="preserve">12.5984888076782</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4557495117188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5158500671387</t>
+    <t xml:space="preserve">12.4557504653931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.515851020813</t>
   </si>
   <si>
     <t xml:space="preserve">12.3468179702759</t>
@@ -3065,7 +3065,7 @@
     <t xml:space="preserve">12.21910572052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6661005020142</t>
+    <t xml:space="preserve">12.6661014556885</t>
   </si>
   <si>
     <t xml:space="preserve">12.6247825622559</t>
@@ -3074,16 +3074,16 @@
     <t xml:space="preserve">12.5083379745483</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3881378173828</t>
+    <t xml:space="preserve">12.3881368637085</t>
   </si>
   <si>
     <t xml:space="preserve">12.1740312576294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0650987625122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2641820907593</t>
+    <t xml:space="preserve">12.0650997161865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.264181137085</t>
   </si>
   <si>
     <t xml:space="preserve">11.9749488830566</t>
@@ -3104,13 +3104,13 @@
     <t xml:space="preserve">12.2078371047974</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3843822479248</t>
+    <t xml:space="preserve">12.3843812942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.5120944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6285381317139</t>
+    <t xml:space="preserve">12.6285371780396</t>
   </si>
   <si>
     <t xml:space="preserve">12.4257011413574</t>
@@ -3119,28 +3119,28 @@
     <t xml:space="preserve">11.8547487258911</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8322105407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8096742630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6181058883667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3326282501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7645988464355</t>
+    <t xml:space="preserve">11.8322114944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8096752166748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6181039810181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3326292037964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7645978927612</t>
   </si>
   <si>
     <t xml:space="preserve">11.5993232727051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5842990875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4640998840332</t>
+    <t xml:space="preserve">11.5842981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4640989303589</t>
   </si>
   <si>
     <t xml:space="preserve">11.362678527832</t>
@@ -3152,7 +3152,7 @@
     <t xml:space="preserve">11.8772869110107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8359680175781</t>
+    <t xml:space="preserve">11.8359670639038</t>
   </si>
   <si>
     <t xml:space="preserve">11.9524116516113</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">12.2003240585327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2904758453369</t>
+    <t xml:space="preserve">12.2904748916626</t>
   </si>
   <si>
     <t xml:space="preserve">12.1139307022095</t>
@@ -3170,19 +3170,19 @@
     <t xml:space="preserve">12.4031629562378</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9448986053467</t>
+    <t xml:space="preserve">11.944899559021</t>
   </si>
   <si>
     <t xml:space="preserve">12.0989055633545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1514930725098</t>
+    <t xml:space="preserve">12.1514921188354</t>
   </si>
   <si>
     <t xml:space="preserve">12.0801248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7007427215576</t>
+    <t xml:space="preserve">11.7007436752319</t>
   </si>
   <si>
     <t xml:space="preserve">11.5241985321045</t>
@@ -3194,7 +3194,7 @@
     <t xml:space="preserve">10.6452341079712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8893909454346</t>
+    <t xml:space="preserve">10.8893899917603</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499914169312</t>
@@ -3209,22 +3209,22 @@
     <t xml:space="preserve">12.0275363922119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8885545730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5834627151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4332113265991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4106750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1393880844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2070016860962</t>
+    <t xml:space="preserve">11.8885555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5834636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4332122802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4106740951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1393871307373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2070007324219</t>
   </si>
   <si>
     <t xml:space="preserve">13.5600900650024</t>
@@ -3233,16 +3233,16 @@
     <t xml:space="preserve">13.2370519638062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2595901489258</t>
+    <t xml:space="preserve">13.2595891952515</t>
   </si>
   <si>
     <t xml:space="preserve">13.2220277786255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6727781295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3572521209717</t>
+    <t xml:space="preserve">13.6727771759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3572540283203</t>
   </si>
   <si>
     <t xml:space="preserve">13.3797903060913</t>
@@ -3251,58 +3251,58 @@
     <t xml:space="preserve">13.2746143341064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5375518798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882209777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821283340454</t>
+    <t xml:space="preserve">13.5375528335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1882219314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821264266968</t>
   </si>
   <si>
     <t xml:space="preserve">13.2896404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2295398712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619272232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9327936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1731948852539</t>
+    <t xml:space="preserve">13.2295389175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9327945709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1731939315796</t>
   </si>
   <si>
     <t xml:space="preserve">13.1919765472412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1957340240479</t>
+    <t xml:space="preserve">13.1957321166992</t>
   </si>
   <si>
     <t xml:space="preserve">13.0154333114624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.82386302948</t>
+    <t xml:space="preserve">12.8238620758057</t>
   </si>
   <si>
     <t xml:space="preserve">13.3272008895874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361343383789</t>
+    <t xml:space="preserve">13.4361333847046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4962339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4323768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3497409820557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3384695053101</t>
+    <t xml:space="preserve">13.4323759078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3497400283813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3384704589844</t>
   </si>
   <si>
     <t xml:space="preserve">13.1994886398315</t>
@@ -3317,10 +3317,10 @@
     <t xml:space="preserve">13.39857006073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3910579681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.680290222168</t>
+    <t xml:space="preserve">13.3910598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6802892684937</t>
   </si>
   <si>
     <t xml:space="preserve">14.2099227905273</t>
@@ -3329,19 +3329,19 @@
     <t xml:space="preserve">13.9582538604736</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8305416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.89439868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8380537033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9319591522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7328796386719</t>
+    <t xml:space="preserve">13.8305397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943967819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8380527496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.931960105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7328786849976</t>
   </si>
   <si>
     <t xml:space="preserve">13.4398899078369</t>
@@ -3350,61 +3350,61 @@
     <t xml:space="preserve">13.4060831069946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1093406677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3009080886841</t>
+    <t xml:space="preserve">13.1093397140503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3009090423584</t>
   </si>
   <si>
     <t xml:space="preserve">13.0417280197144</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4887208938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676012039185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.721607208252</t>
+    <t xml:space="preserve">13.4887199401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676021575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7216091156006</t>
   </si>
   <si>
     <t xml:space="preserve">14.3526601791382</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5855493545532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0550813674927</t>
+    <t xml:space="preserve">14.5855484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0550804138184</t>
   </si>
   <si>
     <t xml:space="preserve">15.092643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0250301361084</t>
+    <t xml:space="preserve">15.0250310897827</t>
   </si>
   <si>
     <t xml:space="preserve">15.1978178024292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8447294235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7207717895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9198560714722</t>
+    <t xml:space="preserve">14.8447303771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9198579788208</t>
   </si>
   <si>
     <t xml:space="preserve">14.8221912384033</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5329608917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6005716323853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315414428711</t>
+    <t xml:space="preserve">14.532958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6005725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4315404891968</t>
   </si>
   <si>
     <t xml:space="preserve">14.2812919616699</t>
@@ -3413,13 +3413,13 @@
     <t xml:space="preserve">14.9499044418335</t>
   </si>
   <si>
-    <t xml:space="preserve">14.784628868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7095060348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6644287109375</t>
+    <t xml:space="preserve">14.784631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7095041275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6644296646118</t>
   </si>
   <si>
     <t xml:space="preserve">14.4240303039551</t>
@@ -3431,130 +3431,130 @@
     <t xml:space="preserve">14.7620916366577</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9123420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6606721878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4090042114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1948976516724</t>
+    <t xml:space="preserve">14.9123439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6606731414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4090032577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1948986053467</t>
   </si>
   <si>
     <t xml:space="preserve">14.1197729110718</t>
   </si>
   <si>
-    <t xml:space="preserve">14.202410697937</t>
+    <t xml:space="preserve">14.2024097442627</t>
   </si>
   <si>
     <t xml:space="preserve">14.2775344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3226099014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714408874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2925605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4653482437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7470674514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5930604934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8898057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8484859466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2504053115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1001558303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1151809692383</t>
+    <t xml:space="preserve">14.3226108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202718734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714399337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2925586700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4653472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7470664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5930595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8898038864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.848484992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2504062652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.100154876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1151819229126</t>
   </si>
   <si>
     <t xml:space="preserve">15.0701055526733</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1827917098999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7245292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7508220672607</t>
+    <t xml:space="preserve">15.1827926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7245283126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.750825881958</t>
   </si>
   <si>
     <t xml:space="preserve">14.814679145813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.818434715271</t>
+    <t xml:space="preserve">14.8184366226196</t>
   </si>
   <si>
     <t xml:space="preserve">14.9837112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0175189971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.792142868042</t>
+    <t xml:space="preserve">15.0175161361694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7921419143677</t>
   </si>
   <si>
     <t xml:space="preserve">14.9611740112305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1602563858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724435806274</t>
+    <t xml:space="preserve">15.1602573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724426269531</t>
   </si>
   <si>
     <t xml:space="preserve">15.085129737854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1377182006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3555793762207</t>
+    <t xml:space="preserve">15.1377191543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3555812835693</t>
   </si>
   <si>
     <t xml:space="preserve">15.2579174041748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2804565429688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2729425430298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.86643409729</t>
+    <t xml:space="preserve">15.2804555892944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2729444503784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8664321899414</t>
   </si>
   <si>
     <t xml:space="preserve">15.8438949584961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6410551071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7086706161499</t>
+    <t xml:space="preserve">15.641056060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7086696624756</t>
   </si>
   <si>
     <t xml:space="preserve">15.6711072921753</t>
@@ -3566,10 +3566,10 @@
     <t xml:space="preserve">16.0814266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8841571807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8999395370483</t>
+    <t xml:space="preserve">15.8841552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.899941444397</t>
   </si>
   <si>
     <t xml:space="preserve">15.955174446106</t>
@@ -3590,7 +3590,7 @@
     <t xml:space="preserve">16.4601860046387</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4522933959961</t>
+    <t xml:space="preserve">16.4522953033447</t>
   </si>
   <si>
     <t xml:space="preserve">16.412841796875</t>
@@ -3623,16 +3623,16 @@
     <t xml:space="preserve">16.2392444610596</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2471351623535</t>
+    <t xml:space="preserve">16.2471332550049</t>
   </si>
   <si>
     <t xml:space="preserve">16.5312042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1287708282471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2155723571777</t>
+    <t xml:space="preserve">16.1287727355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2155704498291</t>
   </si>
   <si>
     <t xml:space="preserve">16.3023700714111</t>
@@ -3650,7 +3650,7 @@
     <t xml:space="preserve">16.4444046020508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550239562988</t>
+    <t xml:space="preserve">16.2550258636475</t>
   </si>
   <si>
     <t xml:space="preserve">16.5233135223389</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">17.3281726837158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1940307617188</t>
+    <t xml:space="preserve">17.1940288543701</t>
   </si>
   <si>
     <t xml:space="preserve">17.2492656707764</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">17.1387939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4702053070068</t>
+    <t xml:space="preserve">17.4702072143555</t>
   </si>
   <si>
     <t xml:space="preserve">17.4938793182373</t>
@@ -3692,7 +3692,7 @@
     <t xml:space="preserve">17.5727882385254</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9041996002197</t>
+    <t xml:space="preserve">17.9042015075684</t>
   </si>
   <si>
     <t xml:space="preserve">17.9120903015137</t>
@@ -3725,7 +3725,7 @@
     <t xml:space="preserve">18.424991607666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3539772033691</t>
+    <t xml:space="preserve">18.3539752960205</t>
   </si>
   <si>
     <t xml:space="preserve">18.4407749176025</t>
@@ -3734,7 +3734,7 @@
     <t xml:space="preserve">18.5906982421875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.669605255127</t>
+    <t xml:space="preserve">18.6696071624756</t>
   </si>
   <si>
     <t xml:space="preserve">18.748514175415</t>
@@ -3746,7 +3746,7 @@
     <t xml:space="preserve">18.8037509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7011699676514</t>
+    <t xml:space="preserve">18.701171875</t>
   </si>
   <si>
     <t xml:space="preserve">18.756404876709</t>
@@ -3755,10 +3755,10 @@
     <t xml:space="preserve">18.7406234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6459350585938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7169513702393</t>
+    <t xml:space="preserve">18.6459331512451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7169494628906</t>
   </si>
   <si>
     <t xml:space="preserve">18.5749187469482</t>
@@ -3770,16 +3770,16 @@
     <t xml:space="preserve">18.8984394073486</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9536743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1903972625732</t>
+    <t xml:space="preserve">18.9536762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">19.0878200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5591354370117</t>
+    <t xml:space="preserve">18.5591373443604</t>
   </si>
   <si>
     <t xml:space="preserve">18.8589859008789</t>
@@ -3833,28 +3833,28 @@
     <t xml:space="preserve">19.5375919342041</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4034519195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5297050476074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6007194519043</t>
+    <t xml:space="preserve">19.403450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5297031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6007175445557</t>
   </si>
   <si>
     <t xml:space="preserve">19.8374443054199</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6322822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6954097747803</t>
+    <t xml:space="preserve">19.6322803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6954078674316</t>
   </si>
   <si>
     <t xml:space="preserve">19.640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9952602386475</t>
+    <t xml:space="preserve">19.9952583312988</t>
   </si>
   <si>
     <t xml:space="preserve">20.066276550293</t>
@@ -3863,10 +3863,10 @@
     <t xml:space="preserve">20.1057300567627</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0504932403564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0741691589355</t>
+    <t xml:space="preserve">20.0504951477051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0741672515869</t>
   </si>
   <si>
     <t xml:space="preserve">20.0189323425293</t>
@@ -3887,7 +3887,7 @@
     <t xml:space="preserve">20.9421539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9816093444824</t>
+    <t xml:space="preserve">20.9816074371338</t>
   </si>
   <si>
     <t xml:space="preserve">20.6659774780273</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">20.1372947692871</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0820560455322</t>
+    <t xml:space="preserve">20.0820579528809</t>
   </si>
   <si>
     <t xml:space="preserve">19.1035995483398</t>
@@ -3908,22 +3908,22 @@
     <t xml:space="preserve">19.316650390625</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3324356079102</t>
+    <t xml:space="preserve">19.3324337005615</t>
   </si>
   <si>
     <t xml:space="preserve">19.4744682312012</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3087615966797</t>
+    <t xml:space="preserve">19.3087596893311</t>
   </si>
   <si>
     <t xml:space="preserve">19.1746158599854</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2377433776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2850875854492</t>
+    <t xml:space="preserve">19.2377414703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2850894927979</t>
   </si>
   <si>
     <t xml:space="preserve">19.1272716522217</t>
@@ -3947,7 +3947,7 @@
     <t xml:space="preserve">19.16672706604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3561038970947</t>
+    <t xml:space="preserve">19.3561058044434</t>
   </si>
   <si>
     <t xml:space="preserve">19.411340713501</t>
@@ -3983,10 +3983,10 @@
     <t xml:space="preserve">20.5791778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6817569732666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.3187808990479</t>
+    <t xml:space="preserve">20.6817588806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.3187828063965</t>
   </si>
   <si>
     <t xml:space="preserve">19.884786605835</t>
@@ -3995,19 +3995,19 @@
     <t xml:space="preserve">18.2119407653809</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2671737670898</t>
+    <t xml:space="preserve">18.2671756744385</t>
   </si>
   <si>
     <t xml:space="preserve">18.3934268951416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0325813293457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8747673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.33030128479</t>
+    <t xml:space="preserve">19.0325832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8747653961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3303031921387</t>
   </si>
   <si>
     <t xml:space="preserve">18.7958583831787</t>
@@ -4016,7 +4016,7 @@
     <t xml:space="preserve">18.3697566986084</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3145217895508</t>
+    <t xml:space="preserve">18.3145198822021</t>
   </si>
   <si>
     <t xml:space="preserve">17.8095111846924</t>
@@ -4031,7 +4031,7 @@
     <t xml:space="preserve">16.641674041748</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1782455444336</t>
+    <t xml:space="preserve">17.1782474517822</t>
   </si>
   <si>
     <t xml:space="preserve">16.8862895965576</t>
@@ -4040,10 +4040,10 @@
     <t xml:space="preserve">16.6337833404541</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4028186798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4501657485962</t>
+    <t xml:space="preserve">15.4028205871582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4501638412476</t>
   </si>
   <si>
     <t xml:space="preserve">15.663215637207</t>
@@ -4058,7 +4058,7 @@
     <t xml:space="preserve">15.5093460083008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8525953292847</t>
+    <t xml:space="preserve">15.852593421936</t>
   </si>
   <si>
     <t xml:space="preserve">17.0441055297852</t>
@@ -4070,7 +4070,7 @@
     <t xml:space="preserve">16.4759674072266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8152694702148</t>
+    <t xml:space="preserve">16.8152713775635</t>
   </si>
   <si>
     <t xml:space="preserve">16.7837085723877</t>
@@ -4085,7 +4085,7 @@
     <t xml:space="preserve">17.2413749694824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9415245056152</t>
+    <t xml:space="preserve">16.9415225982666</t>
   </si>
   <si>
     <t xml:space="preserve">16.6732349395752</t>
@@ -4100,16 +4100,16 @@
     <t xml:space="preserve">15.7579050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4107122421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815771102905</t>
+    <t xml:space="preserve">15.4107103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815780639648</t>
   </si>
   <si>
     <t xml:space="preserve">15.9157209396362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8920478820801</t>
+    <t xml:space="preserve">15.8920497894287</t>
   </si>
   <si>
     <t xml:space="preserve">15.8683776855469</t>
@@ -4133,10 +4133,10 @@
     <t xml:space="preserve">16.0735378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.176118850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9236125946045</t>
+    <t xml:space="preserve">16.1761169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9236106872559</t>
   </si>
   <si>
     <t xml:space="preserve">15.6395444869995</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">15.7381782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7657947540283</t>
+    <t xml:space="preserve">15.765796661377</t>
   </si>
   <si>
     <t xml:space="preserve">16.0261917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8052501678467</t>
+    <t xml:space="preserve">15.8052520751953</t>
   </si>
   <si>
     <t xml:space="preserve">16.4583625793457</t>
@@ -4187,13 +4187,13 @@
     <t xml:space="preserve">16.8209209442139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5932674407959</t>
+    <t xml:space="preserve">16.5932693481445</t>
   </si>
   <si>
     <t xml:space="preserve">16.8082733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5595417022705</t>
+    <t xml:space="preserve">16.5595397949219</t>
   </si>
   <si>
     <t xml:space="preserve">16.871509552002</t>
@@ -4202,43 +4202,43 @@
     <t xml:space="preserve">16.7366046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5342483520508</t>
+    <t xml:space="preserve">16.5342464447021</t>
   </si>
   <si>
     <t xml:space="preserve">16.2012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7298974990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4390106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6287212371826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9828443527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2830266952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3715581893921</t>
+    <t xml:space="preserve">14.7298984527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4390096664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6287202835083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9828453063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2830276489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3715591430664</t>
   </si>
   <si>
     <t xml:space="preserve">14.4432249069214</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5064630508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2197895050049</t>
+    <t xml:space="preserve">14.506462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2197904586792</t>
   </si>
   <si>
     <t xml:space="preserve">14.6750926971436</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5191087722778</t>
+    <t xml:space="preserve">14.5191097259521</t>
   </si>
   <si>
     <t xml:space="preserve">14.4811658859253</t>
@@ -4253,10 +4253,10 @@
     <t xml:space="preserve">13.8277225494385</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289026260376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3724212646484</t>
+    <t xml:space="preserve">13.9289016723633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3724203109741</t>
   </si>
   <si>
     <t xml:space="preserve">13.7771339416504</t>
@@ -4265,16 +4265,16 @@
     <t xml:space="preserve">14.1523370742798</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3420486450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1354742050171</t>
+    <t xml:space="preserve">14.3420476913452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1354732513428</t>
   </si>
   <si>
     <t xml:space="preserve">14.3546943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1987113952637</t>
+    <t xml:space="preserve">14.198712348938</t>
   </si>
   <si>
     <t xml:space="preserve">13.621150970459</t>
@@ -4283,7 +4283,7 @@
     <t xml:space="preserve">13.6801719665527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8108606338501</t>
+    <t xml:space="preserve">13.8108596801758</t>
   </si>
   <si>
     <t xml:space="preserve">14.2493000030518</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">13.6928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7602710723877</t>
+    <t xml:space="preserve">13.760272026062</t>
   </si>
   <si>
     <t xml:space="preserve">13.7939977645874</t>
@@ -4304,10 +4304,10 @@
     <t xml:space="preserve">13.5494823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3631267547607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3926362991333</t>
+    <t xml:space="preserve">14.3631258010864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3926372528076</t>
   </si>
   <si>
     <t xml:space="preserve">14.1312589645386</t>
@@ -4322,19 +4322,19 @@
     <t xml:space="preserve">14.2577314376831</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2956733703613</t>
+    <t xml:space="preserve">14.2956743240356</t>
   </si>
   <si>
     <t xml:space="preserve">14.1944942474365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4600887298584</t>
+    <t xml:space="preserve">14.4600877761841</t>
   </si>
   <si>
     <t xml:space="preserve">14.5022459030151</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5654830932617</t>
+    <t xml:space="preserve">14.565484046936</t>
   </si>
   <si>
     <t xml:space="preserve">14.6371517181396</t>
@@ -4343,19 +4343,19 @@
     <t xml:space="preserve">14.3757734298706</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4643068313599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9794902801514</t>
+    <t xml:space="preserve">14.4643049240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9794912338257</t>
   </si>
   <si>
     <t xml:space="preserve">13.7687034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9541959762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9415493011475</t>
+    <t xml:space="preserve">13.9541969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9415483474731</t>
   </si>
   <si>
     <t xml:space="preserve">13.8530187606812</t>
@@ -4367,7 +4367,7 @@
     <t xml:space="preserve">13.4483041763306</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6380138397217</t>
+    <t xml:space="preserve">13.6380128860474</t>
   </si>
   <si>
     <t xml:space="preserve">13.4356575012207</t>
@@ -4379,7 +4379,7 @@
     <t xml:space="preserve">13.6295833587646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4272260665894</t>
+    <t xml:space="preserve">13.427225112915</t>
   </si>
   <si>
     <t xml:space="preserve">13.4946775436401</t>
@@ -4403,13 +4403,13 @@
     <t xml:space="preserve">13.7644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8572330474854</t>
+    <t xml:space="preserve">13.8572340011597</t>
   </si>
   <si>
     <t xml:space="preserve">13.4735994338989</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1321210861206</t>
+    <t xml:space="preserve">13.1321220397949</t>
   </si>
   <si>
     <t xml:space="preserve">12.7484865188599</t>
@@ -4421,10 +4421,10 @@
     <t xml:space="preserve">12.5334825515747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4112253189087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0065107345581</t>
+    <t xml:space="preserve">12.411226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0065116882324</t>
   </si>
   <si>
     <t xml:space="preserve">12.3985767364502</t>
@@ -4433,7 +4433,7 @@
     <t xml:space="preserve">12.6009340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1532001495361</t>
+    <t xml:space="preserve">13.1532011032104</t>
   </si>
   <si>
     <t xml:space="preserve">12.9044704437256</t>
@@ -4454,7 +4454,7 @@
     <t xml:space="preserve">11.7324857711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0908269882202</t>
+    <t xml:space="preserve">12.0908260345459</t>
   </si>
   <si>
     <t xml:space="preserve">12.5292663574219</t>
@@ -4472,13 +4472,13 @@
     <t xml:space="preserve">12.8538808822632</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8960390090942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3007526397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6843862533569</t>
+    <t xml:space="preserve">12.8960380554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3007516860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6843872070312</t>
   </si>
   <si>
     <t xml:space="preserve">13.532618522644</t>
@@ -4496,13 +4496,13 @@
     <t xml:space="preserve">14.1101808547974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3462629318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7214660644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9449024200439</t>
+    <t xml:space="preserve">14.3462619781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7214670181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9449043273926</t>
   </si>
   <si>
     <t xml:space="preserve">15.0292186737061</t>
@@ -4526,7 +4526,7 @@
     <t xml:space="preserve">16.799840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3740482330322</t>
+    <t xml:space="preserve">16.3740463256836</t>
   </si>
   <si>
     <t xml:space="preserve">16.4415016174316</t>
@@ -4535,13 +4535,13 @@
     <t xml:space="preserve">16.4035587310791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3909111022949</t>
+    <t xml:space="preserve">16.3909130096436</t>
   </si>
   <si>
     <t xml:space="preserve">16.1801242828369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2349262237549</t>
+    <t xml:space="preserve">16.2349281311035</t>
   </si>
   <si>
     <t xml:space="preserve">16.3993434906006</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">16.7618980407715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0570049285889</t>
+    <t xml:space="preserve">17.0570030212402</t>
   </si>
   <si>
     <t xml:space="preserve">16.9558258056641</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">16.2855167388916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2677898406982</t>
+    <t xml:space="preserve">17.2677917480469</t>
   </si>
   <si>
     <t xml:space="preserve">17.2593612670898</t>
@@ -4598,7 +4598,7 @@
     <t xml:space="preserve">17.6893692016602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7146644592285</t>
+    <t xml:space="preserve">17.7146625518799</t>
   </si>
   <si>
     <t xml:space="preserve">17.8579998016357</t>
@@ -4616,7 +4616,7 @@
     <t xml:space="preserve">18.2542819976807</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9760417938232</t>
+    <t xml:space="preserve">17.9760398864746</t>
   </si>
   <si>
     <t xml:space="preserve">17.9676074981689</t>
@@ -4625,13 +4625,13 @@
     <t xml:space="preserve">18.3807525634766</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3891868591309</t>
+    <t xml:space="preserve">18.3891849517822</t>
   </si>
   <si>
     <t xml:space="preserve">18.8697834014893</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9035091400146</t>
+    <t xml:space="preserve">18.9035110473633</t>
   </si>
   <si>
     <t xml:space="preserve">18.9625301361084</t>
@@ -4646,7 +4646,7 @@
     <t xml:space="preserve">19.1648864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8444900512695</t>
+    <t xml:space="preserve">18.8444881439209</t>
   </si>
   <si>
     <t xml:space="preserve">19.2239074707031</t>
@@ -4655,7 +4655,7 @@
     <t xml:space="preserve">19.375675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3588104248047</t>
+    <t xml:space="preserve">19.3588123321533</t>
   </si>
   <si>
     <t xml:space="preserve">19.3419494628906</t>
@@ -4670,7 +4670,7 @@
     <t xml:space="preserve">19.3250885009766</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2913589477539</t>
+    <t xml:space="preserve">19.2913608551025</t>
   </si>
   <si>
     <t xml:space="preserve">19.3166542053223</t>
@@ -4679,7 +4679,7 @@
     <t xml:space="preserve">19.8141174316406</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8984317779541</t>
+    <t xml:space="preserve">19.8984336853027</t>
   </si>
   <si>
     <t xml:space="preserve">19.9405899047852</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">19.2070465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0552768707275</t>
+    <t xml:space="preserve">19.0552787780762</t>
   </si>
   <si>
     <t xml:space="preserve">18.9878253936768</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">18.6168365478516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9456653594971</t>
+    <t xml:space="preserve">18.9456672668457</t>
   </si>
   <si>
     <t xml:space="preserve">18.9793949127197</t>
@@ -4730,19 +4730,19 @@
     <t xml:space="preserve">18.8950786590576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8023319244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1952610015869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134834289551</t>
+    <t xml:space="preserve">18.8023300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1952590942383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134853363037</t>
   </si>
   <si>
     <t xml:space="preserve">16.7745456695557</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9811191558838</t>
+    <t xml:space="preserve">16.9811172485352</t>
   </si>
   <si>
     <t xml:space="preserve">16.2391452789307</t>
@@ -4751,52 +4751,52 @@
     <t xml:space="preserve">16.0114936828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4667949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9052352905273</t>
+    <t xml:space="preserve">16.466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9052333831787</t>
   </si>
   <si>
     <t xml:space="preserve">16.3782634735107</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1126708984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1337509155273</t>
+    <t xml:space="preserve">16.1126689910889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1337490081787</t>
   </si>
   <si>
     <t xml:space="preserve">16.3487529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6438579559326</t>
+    <t xml:space="preserve">16.643856048584</t>
   </si>
   <si>
     <t xml:space="preserve">16.6101322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.546895980835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3403224945068</t>
+    <t xml:space="preserve">16.5468940734863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3403205871582</t>
   </si>
   <si>
     <t xml:space="preserve">16.521598815918</t>
   </si>
   <si>
-    <t xml:space="preserve">16.711311340332</t>
+    <t xml:space="preserve">16.7113094329834</t>
   </si>
   <si>
     <t xml:space="preserve">17.158182144165</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1244564056396</t>
+    <t xml:space="preserve">17.124454498291</t>
   </si>
   <si>
     <t xml:space="preserve">17.0232772827148</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2003383636475</t>
+    <t xml:space="preserve">17.2003402709961</t>
   </si>
   <si>
     <t xml:space="preserve">17.2424983978271</t>
@@ -4814,13 +4814,13 @@
     <t xml:space="preserve">17.0654335021973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8124885559082</t>
+    <t xml:space="preserve">16.8124904632568</t>
   </si>
   <si>
     <t xml:space="preserve">16.5806217193604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9726886749268</t>
+    <t xml:space="preserve">16.9726867675781</t>
   </si>
   <si>
     <t xml:space="preserve">17.0822982788086</t>
@@ -6366,6 +6366,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.6500015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">31.9200000762939</t>
   </si>
 </sst>
 </file>
@@ -71444,7 +71447,7 @@
     </row>
     <row r="2491">
       <c r="A2491" s="1" t="n">
-        <v>45946.6502083333</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2491" t="n">
         <v>519131</v>
@@ -71465,6 +71468,32 @@
         <v>2117</v>
       </c>
       <c r="H2491" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2492">
+      <c r="A2492" s="1" t="n">
+        <v>45947.6494560185</v>
+      </c>
+      <c r="B2492" t="n">
+        <v>702042</v>
+      </c>
+      <c r="C2492" t="n">
+        <v>32.2900009155273</v>
+      </c>
+      <c r="D2492" t="n">
+        <v>31.4099998474121</v>
+      </c>
+      <c r="E2492" t="n">
+        <v>32.0999984741211</v>
+      </c>
+      <c r="F2492" t="n">
+        <v>31.9200000762939</v>
+      </c>
+      <c r="G2492" t="s">
+        <v>2118</v>
+      </c>
+      <c r="H2492" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2119" uniqueCount="2119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2120" uniqueCount="2120">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,49 +38,49 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8295078277588</t>
+    <t xml:space="preserve">10.8295068740845</t>
   </si>
   <si>
     <t xml:space="preserve">AZM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068367004395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4860248565674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.191611289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91191864013672</t>
+    <t xml:space="preserve">10.7068347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.486026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1916122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91191959381104</t>
   </si>
   <si>
     <t xml:space="preserve">9.9364538192749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.225962638855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.000244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.617506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33290481567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15135097503662</t>
+    <t xml:space="preserve">10.2259607315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0002431869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61750602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33290576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1513500213623</t>
   </si>
   <si>
     <t xml:space="preserve">9.37706756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85693740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25930213928223</t>
+    <t xml:space="preserve">8.85693836212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25930309295654</t>
   </si>
   <si>
     <t xml:space="preserve">9.53899574279785</t>
@@ -92,31 +92,31 @@
     <t xml:space="preserve">9.50955486297607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40160274505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12681770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49483394622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43595123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84712505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99433135986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79805469512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05711460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86574649810791</t>
+    <t xml:space="preserve">9.40160179138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12681579589844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49483489990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43595027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84712409973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99433040618896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79805660247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05711364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86574554443359</t>
   </si>
   <si>
     <t xml:space="preserve">8.32699298858643</t>
@@ -125,16 +125,16 @@
     <t xml:space="preserve">7.61058712005615</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67928314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10127544403076</t>
+    <t xml:space="preserve">7.67928409576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10127639770508</t>
   </si>
   <si>
     <t xml:space="preserve">7.8706521987915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53798961639404</t>
+    <t xml:space="preserve">8.53799057006836</t>
   </si>
   <si>
     <t xml:space="preserve">8.78333473205566</t>
@@ -143,7 +143,7 @@
     <t xml:space="preserve">8.46929359436035</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61649799346924</t>
+    <t xml:space="preserve">8.61649990081787</t>
   </si>
   <si>
     <t xml:space="preserve">8.50364112854004</t>
@@ -155,28 +155,28 @@
     <t xml:space="preserve">8.69010448455811</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71954536437988</t>
+    <t xml:space="preserve">8.71954441070557</t>
   </si>
   <si>
     <t xml:space="preserve">9.29365158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30837154388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47520542144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09737491607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22004890441895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41141891479492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48011207580566</t>
+    <t xml:space="preserve">9.30837059020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47520732879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09737586975098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22004795074463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41141700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4801139831543</t>
   </si>
   <si>
     <t xml:space="preserve">9.77943420410156</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">9.6616678237915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79415416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77452659606934</t>
+    <t xml:space="preserve">9.79415321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77452564239502</t>
   </si>
   <si>
     <t xml:space="preserve">9.68620109558105</t>
@@ -197,37 +197,37 @@
     <t xml:space="preserve">9.64694690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72545719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2357749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3044700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83831596374512</t>
+    <t xml:space="preserve">9.72545623779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2357740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3044710159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8383150100708</t>
   </si>
   <si>
     <t xml:space="preserve">9.56843566894531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98552417755127</t>
+    <t xml:space="preserve">9.98552322387695</t>
   </si>
   <si>
     <t xml:space="preserve">9.93154716491699</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74508571624756</t>
+    <t xml:space="preserve">9.74508476257324</t>
   </si>
   <si>
     <t xml:space="preserve">10.3780727386475</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5449066162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4369554519653</t>
+    <t xml:space="preserve">10.5449085235596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4369583129883</t>
   </si>
   <si>
     <t xml:space="preserve">10.5547227859497</t>
@@ -236,70 +236,70 @@
     <t xml:space="preserve">10.505654335022</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5498161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5007476806641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5694437026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4173288345337</t>
+    <t xml:space="preserve">10.5498142242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5007467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5694417953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173278808594</t>
   </si>
   <si>
     <t xml:space="preserve">10.4811191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7411842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8442287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7853441238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5988845825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406816482544</t>
+    <t xml:space="preserve">10.7411851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8442277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.785346031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5988836288452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406806945801</t>
   </si>
   <si>
     <t xml:space="preserve">10.2897491455078</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73036479949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57334232330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43104457855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40650939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19060611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08265590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35253524780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47029781341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27893161773682</t>
+    <t xml:space="preserve">9.73036575317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57334423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43104267120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40651035308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19060707092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08265495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35253429412842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47029972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27892971038818</t>
   </si>
   <si>
     <t xml:space="preserve">9.30346488952637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14644527435303</t>
+    <t xml:space="preserve">9.14644432067871</t>
   </si>
   <si>
     <t xml:space="preserve">9.52970218658447</t>
@@ -311,37 +311,37 @@
     <t xml:space="preserve">10.1190137863159</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89235591888428</t>
+    <t xml:space="preserve">9.89235401153564</t>
   </si>
   <si>
     <t xml:space="preserve">9.95279598236084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1492319107056</t>
+    <t xml:space="preserve">10.1492338180542</t>
   </si>
   <si>
     <t xml:space="preserve">9.84702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76643466949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42896461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42392826080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52466583251953</t>
+    <t xml:space="preserve">9.766432762146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42896366119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42392635345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5246639251709</t>
   </si>
   <si>
     <t xml:space="preserve">9.54984951019287</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39370727539062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82958126068115</t>
+    <t xml:space="preserve">9.39370536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82958030700684</t>
   </si>
   <si>
     <t xml:space="preserve">8.4820384979248</t>
@@ -350,106 +350,106 @@
     <t xml:space="preserve">8.28560161590576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46189022064209</t>
+    <t xml:space="preserve">8.46189212799072</t>
   </si>
   <si>
     <t xml:space="preserve">8.53744316101074</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68351173400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39874267578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5045166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81680011749268</t>
+    <t xml:space="preserve">8.68351364135742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39874362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50451755523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81680107116699</t>
   </si>
   <si>
     <t xml:space="preserve">8.46692943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46459722518921</t>
+    <t xml:space="preserve">7.46459770202637</t>
   </si>
   <si>
     <t xml:space="preserve">7.5754075050354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49985504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34874963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43941211700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20268249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8702507019043</t>
+    <t xml:space="preserve">7.49985551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34875059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43941259384155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20268154144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87024974822998</t>
   </si>
   <si>
     <t xml:space="preserve">6.50256061553955</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6284818649292</t>
+    <t xml:space="preserve">6.62848138809204</t>
   </si>
   <si>
     <t xml:space="preserve">6.86017656326294</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02135562896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38904571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20771837234497</t>
+    <t xml:space="preserve">7.02135515213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38904428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20771789550781</t>
   </si>
   <si>
     <t xml:space="preserve">7.44948673248291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66606998443604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5250391960144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64592409133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79702949523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71140289306641</t>
+    <t xml:space="preserve">7.66607141494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52503967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64592313766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79702854156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71140193939209</t>
   </si>
   <si>
     <t xml:space="preserve">7.94309711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8171763420105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9481348991394</t>
+    <t xml:space="preserve">7.81717681884766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94813394546509</t>
   </si>
   <si>
     <t xml:space="preserve">7.08179759979248</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92565536499023</t>
+    <t xml:space="preserve">6.92565584182739</t>
   </si>
   <si>
     <t xml:space="preserve">6.71410846710205</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7896614074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90047025680542</t>
+    <t xml:space="preserve">6.78966045379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90047121047974</t>
   </si>
   <si>
     <t xml:space="preserve">7.22786569595337</t>
@@ -458,97 +458,97 @@
     <t xml:space="preserve">7.27823400497437</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32860279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31852769851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39911842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15734958648682</t>
+    <t xml:space="preserve">7.32860326766968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31852912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39911937713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15735101699829</t>
   </si>
   <si>
     <t xml:space="preserve">6.94580268859863</t>
   </si>
   <si>
-    <t xml:space="preserve">7.19764423370361</t>
+    <t xml:space="preserve">7.19764471054077</t>
   </si>
   <si>
     <t xml:space="preserve">6.80477094650269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02639245986938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08683490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04150295257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85010242462158</t>
+    <t xml:space="preserve">7.02639293670654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08683443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8501033782959</t>
   </si>
   <si>
     <t xml:space="preserve">6.86521244049072</t>
   </si>
   <si>
-    <t xml:space="preserve">6.93069124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22282838821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31349182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23290252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29838085174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98106098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01128149032593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53781843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7997350692749</t>
+    <t xml:space="preserve">6.93069171905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22282934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31349229812622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23290348052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29838228225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98105955123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01128101348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53781795501709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79973459243774</t>
   </si>
   <si>
     <t xml:space="preserve">6.68388652801514</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73929214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94076490402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9055061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.668776512146</t>
+    <t xml:space="preserve">6.73929262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94076538085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90550804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66877746582031</t>
   </si>
   <si>
     <t xml:space="preserve">6.46226644515991</t>
   </si>
   <si>
-    <t xml:space="preserve">6.57307529449463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67381381988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59826040267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87528657913208</t>
+    <t xml:space="preserve">6.57307624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6738133430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59826135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87528705596924</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624513626099</t>
@@ -557,7 +557,7 @@
     <t xml:space="preserve">7.15231227874756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30341815948486</t>
+    <t xml:space="preserve">7.30341911315918</t>
   </si>
   <si>
     <t xml:space="preserve">7.62577486038208</t>
@@ -566,49 +566,49 @@
     <t xml:space="preserve">7.66103363037109</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57037019729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45452308654785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53511476516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44444942474365</t>
+    <t xml:space="preserve">7.5703706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45452356338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5351128578186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44444894790649</t>
   </si>
   <si>
     <t xml:space="preserve">7.5955548286438</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72147560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60562801361084</t>
+    <t xml:space="preserve">7.72147703170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.605628490448</t>
   </si>
   <si>
     <t xml:space="preserve">7.70636606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48474502563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36386013031006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26312303543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13216590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17246103286743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69629192352295</t>
+    <t xml:space="preserve">7.48474407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36386060714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26312398910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13216543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617052078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17246007919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69629240036011</t>
   </si>
   <si>
     <t xml:space="preserve">7.91791343688965</t>
@@ -617,13 +617,13 @@
     <t xml:space="preserve">8.35611820220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38633918762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51729774475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45181655883789</t>
+    <t xml:space="preserve">8.38633823394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51729679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45181846618652</t>
   </si>
   <si>
     <t xml:space="preserve">8.20501232147217</t>
@@ -632,109 +632,109 @@
     <t xml:space="preserve">8.04887104034424</t>
   </si>
   <si>
-    <t xml:space="preserve">7.95820808410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93132162094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71623516082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73236846923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63557767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64095449447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45813179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4419994354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57105255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68935060501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62482309341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79689264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20017910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43139839172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61960029602051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54432106018066</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46903800964355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58733654022217</t>
+    <t xml:space="preserve">7.9582085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93132209777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71623468399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73236751556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63557624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64095640182495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45813131332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44200086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57105207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68935012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62482404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79689359664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20018005371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43140029907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61959934234619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54431819915771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46903991699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58733749389648</t>
   </si>
   <si>
     <t xml:space="preserve">8.70025730133057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54969787597656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60346984863281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53356552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5980920791626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51743316650391</t>
+    <t xml:space="preserve">8.54969501495361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60346794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53356456756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59809112548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51743412017822</t>
   </si>
   <si>
     <t xml:space="preserve">8.52818775177002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67874908447266</t>
+    <t xml:space="preserve">8.67874813079834</t>
   </si>
   <si>
     <t xml:space="preserve">9.11429786682129</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15731620788574</t>
+    <t xml:space="preserve">9.15731811523438</t>
   </si>
   <si>
     <t xml:space="preserve">9.20033359527588</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17882537841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05515098571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3347635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13043022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44768333435059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38315677642822</t>
+    <t xml:space="preserve">9.17882442474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05514907836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33476257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13043117523193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44768238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38315773010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.41004371643066</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">9.45843696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45306015014648</t>
+    <t xml:space="preserve">9.4530611038208</t>
   </si>
   <si>
     <t xml:space="preserve">9.37240219116211</t>
@@ -752,28 +752,28 @@
     <t xml:space="preserve">9.23797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32938575744629</t>
+    <t xml:space="preserve">9.32938671112061</t>
   </si>
   <si>
     <t xml:space="preserve">9.46919345855713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44230556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92609977722168</t>
+    <t xml:space="preserve">9.44230461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92609882354736</t>
   </si>
   <si>
     <t xml:space="preserve">9.0927906036377</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07128238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76478385925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16807174682617</t>
+    <t xml:space="preserve">9.0712833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7647819519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16807079315186</t>
   </si>
   <si>
     <t xml:space="preserve">9.25948238372803</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">9.28636932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24335193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26486015319824</t>
+    <t xml:space="preserve">9.24335098266602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26485919952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.23259735107422</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">9.24872875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96373653411865</t>
+    <t xml:space="preserve">8.96373844146729</t>
   </si>
   <si>
     <t xml:space="preserve">8.495924949646</t>
@@ -803,34 +803,34 @@
     <t xml:space="preserve">8.59271335601807</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52280902862549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66799449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7378978729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71101093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70563411712646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6357307434082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53894138336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50130176544189</t>
+    <t xml:space="preserve">8.52281093597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66799354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73789691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71101188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70563507080078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63573169708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53894329071045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50130271911621</t>
   </si>
   <si>
     <t xml:space="preserve">8.28621578216553</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33460903167725</t>
+    <t xml:space="preserve">8.33460998535156</t>
   </si>
   <si>
     <t xml:space="preserve">8.43677616119385</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">8.62497615814209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56582736968994</t>
+    <t xml:space="preserve">8.56582832336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.47979354858398</t>
@@ -851,7 +851,7 @@
     <t xml:space="preserve">8.66261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61422348022461</t>
+    <t xml:space="preserve">8.61422157287598</t>
   </si>
   <si>
     <t xml:space="preserve">8.78091526031494</t>
@@ -869,31 +869,31 @@
     <t xml:space="preserve">9.04977321624756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14118576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16269302368164</t>
+    <t xml:space="preserve">9.14118671417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16269397735596</t>
   </si>
   <si>
     <t xml:space="preserve">9.30250072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13580799102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14656162261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20571041107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62513065338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63050746917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60899829864502</t>
+    <t xml:space="preserve">9.13580894470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14656257629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20570945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62513160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63050651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6089973449707</t>
   </si>
   <si>
     <t xml:space="preserve">9.63588523864746</t>
@@ -902,40 +902,40 @@
     <t xml:space="preserve">9.7165412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97464561462402</t>
+    <t xml:space="preserve">9.97464656829834</t>
   </si>
   <si>
     <t xml:space="preserve">10.0553035736084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2435035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4155731201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3456707000732</t>
+    <t xml:space="preserve">10.243504524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4155750274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3456716537476</t>
   </si>
   <si>
     <t xml:space="preserve">10.2327499389648</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3994426727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4101972579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1305847167969</t>
+    <t xml:space="preserve">10.3994436264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4101963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349151611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1305837631226</t>
   </si>
   <si>
     <t xml:space="preserve">10.1036987304688</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3295373916626</t>
+    <t xml:space="preserve">10.3295383453369</t>
   </si>
   <si>
     <t xml:space="preserve">10.425971031189</t>
@@ -950,22 +950,22 @@
     <t xml:space="preserve">10.5847988128662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4770231246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2387800216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2728157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3408851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2160921096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0856246948242</t>
+    <t xml:space="preserve">10.4770221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2387809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2728147506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3408842086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2160911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0856237411499</t>
   </si>
   <si>
     <t xml:space="preserve">9.90410614013672</t>
@@ -977,13 +977,13 @@
     <t xml:space="preserve">10.2614698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1083135604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0062103271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94381237030029</t>
+    <t xml:space="preserve">10.1083116531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0062093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94381332397461</t>
   </si>
   <si>
     <t xml:space="preserve">10.1707096099854</t>
@@ -995,13 +995,13 @@
     <t xml:space="preserve">10.062933921814</t>
   </si>
   <si>
-    <t xml:space="preserve">10.199070930481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3522291183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104177474976</t>
+    <t xml:space="preserve">10.1990728378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3522281646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104167938232</t>
   </si>
   <si>
     <t xml:space="preserve">10.1933994293213</t>
@@ -1010,94 +1010,94 @@
     <t xml:space="preserve">9.95515727996826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.148021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2444515228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841606140137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2217626571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0912961959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.159366607666</t>
+    <t xml:space="preserve">10.1480207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2444524765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841596603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2217636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0912971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1593647003174</t>
   </si>
   <si>
     <t xml:space="preserve">10.5450925827026</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4089555740356</t>
+    <t xml:space="preserve">10.4089546203613</t>
   </si>
   <si>
     <t xml:space="preserve">10.3181953430176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2955045700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3692445755005</t>
+    <t xml:space="preserve">10.2955055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3692474365234</t>
   </si>
   <si>
     <t xml:space="preserve">10.4316434860229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3976097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7152643203735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.641526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7436294555664</t>
+    <t xml:space="preserve">10.397608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7152662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6415252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7436285018921</t>
   </si>
   <si>
     <t xml:space="preserve">10.7209377288818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6698875427246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7776622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7039194107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6585416793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5394201278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.306848526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095928192139</t>
+    <t xml:space="preserve">10.6698865890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.777663230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7039213180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6585426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3068504333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095947265625</t>
   </si>
   <si>
     <t xml:space="preserve">10.5564374923706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4826965332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3352117538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2331066131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2784872055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0288991928101</t>
+    <t xml:space="preserve">10.4826946258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3352108001709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2331075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2784862518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0289001464844</t>
   </si>
   <si>
     <t xml:space="preserve">10.040244102478</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">10.034571647644</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9835205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96082973480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98919296264648</t>
+    <t xml:space="preserve">9.98351955413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96082878112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98919105529785</t>
   </si>
   <si>
     <t xml:space="preserve">10.2274351119995</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">10.2557973861694</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4940404891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5110569000244</t>
+    <t xml:space="preserve">10.4940395355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">10.4146270751953</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">10.3635740280151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3805913925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4600048065186</t>
+    <t xml:space="preserve">10.3805923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4600057601929</t>
   </si>
   <si>
     <t xml:space="preserve">10.5167303085327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3465576171875</t>
+    <t xml:space="preserve">10.3465566635132</t>
   </si>
   <si>
     <t xml:space="preserve">9.84738159179688</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">9.7282600402832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67720699310303</t>
+    <t xml:space="preserve">9.67720794677734</t>
   </si>
   <si>
     <t xml:space="preserve">9.66018867492676</t>
@@ -1184,43 +1184,43 @@
     <t xml:space="preserve">9.61480903625488</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62048244476318</t>
+    <t xml:space="preserve">9.62048149108887</t>
   </si>
   <si>
     <t xml:space="preserve">9.73393058776855</t>
   </si>
   <si>
-    <t xml:space="preserve">9.78498363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7963285446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89843273162842</t>
+    <t xml:space="preserve">9.78498458862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79632949829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89843368530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.16101360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95113372802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99083995819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76961421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75259590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86604595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85470104217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05891036987305</t>
+    <t xml:space="preserve">8.95113182067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99084091186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76961231231689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75259685516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86604499816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85470008850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05890941619873</t>
   </si>
   <si>
     <t xml:space="preserve">9.24042797088623</t>
@@ -1229,34 +1229,34 @@
     <t xml:space="preserve">9.2517728805542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10996150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09294509887695</t>
+    <t xml:space="preserve">9.10996055603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09294414520264</t>
   </si>
   <si>
     <t xml:space="preserve">8.98516750335693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.075927734375</t>
+    <t xml:space="preserve">9.07592678070068</t>
   </si>
   <si>
     <t xml:space="preserve">9.13265132904053</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05323600769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90008068084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8830623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82633876800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79230403900146</t>
+    <t xml:space="preserve">9.05323791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90008163452148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88306331634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.826340675354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79230308532715</t>
   </si>
   <si>
     <t xml:space="preserve">8.79797649383545</t>
@@ -1265,10 +1265,10 @@
     <t xml:space="preserve">8.9681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.00218486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07025527954102</t>
+    <t xml:space="preserve">9.0021858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0702543258667</t>
   </si>
   <si>
     <t xml:space="preserve">8.9965124130249</t>
@@ -1277,16 +1277,16 @@
     <t xml:space="preserve">9.01920223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92277050018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04189109802246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03054714202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01353168487549</t>
+    <t xml:space="preserve">8.92276954650879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04189205169678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03054809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01353073120117</t>
   </si>
   <si>
     <t xml:space="preserve">9.04756450653076</t>
@@ -1295,7 +1295,7 @@
     <t xml:space="preserve">9.03621959686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13832378387451</t>
+    <t xml:space="preserve">9.1383228302002</t>
   </si>
   <si>
     <t xml:space="preserve">8.97382259368896</t>
@@ -1304,25 +1304,25 @@
     <t xml:space="preserve">9.12697887420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16668605804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19504737854004</t>
+    <t xml:space="preserve">9.16668701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19504833221436</t>
   </si>
   <si>
     <t xml:space="preserve">9.37089538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38224029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34253120422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46732616424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6755599975586</t>
+    <t xml:space="preserve">9.38223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34253311157227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46732521057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6755590438843</t>
   </si>
   <si>
     <t xml:space="preserve">10.4202995300293</t>
@@ -1334,10 +1334,10 @@
     <t xml:space="preserve">10.5961446762085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7549743652344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7379579544067</t>
+    <t xml:space="preserve">10.7549734115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7379550933838</t>
   </si>
   <si>
     <t xml:space="preserve">10.760645866394</t>
@@ -1367,7 +1367,7 @@
     <t xml:space="preserve">10.0941324234009</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98635768890381</t>
+    <t xml:space="preserve">9.98635673522949</t>
   </si>
   <si>
     <t xml:space="preserve">10.1565284729004</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">10.1962356567383</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2359437942505</t>
+    <t xml:space="preserve">10.2359428405762</t>
   </si>
   <si>
     <t xml:space="preserve">10.1622018814087</t>
@@ -1400,10 +1400,10 @@
     <t xml:space="preserve">9.92963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2302703857422</t>
+    <t xml:space="preserve">10.1877279281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2302722930908</t>
   </si>
   <si>
     <t xml:space="preserve">10.0203895568848</t>
@@ -1415,10 +1415,10 @@
     <t xml:space="preserve">10.1820554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0317354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9778470993042</t>
+    <t xml:space="preserve">10.0317344665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97784614562988</t>
   </si>
   <si>
     <t xml:space="preserve">9.81618213653564</t>
@@ -1427,7 +1427,7 @@
     <t xml:space="preserve">9.88708782196045</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89559650421143</t>
+    <t xml:space="preserve">9.89559745788574</t>
   </si>
   <si>
     <t xml:space="preserve">9.81334590911865</t>
@@ -1436,25 +1436,25 @@
     <t xml:space="preserve">9.97501087188721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1395111083984</t>
+    <t xml:space="preserve">10.0657691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1395120620728</t>
   </si>
   <si>
     <t xml:space="preserve">10.0005369186401</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0686044692993</t>
+    <t xml:space="preserve">10.0686054229736</t>
   </si>
   <si>
     <t xml:space="preserve">9.73676681518555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83603668212891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89276123046875</t>
+    <t xml:space="preserve">9.83603572845459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89276027679443</t>
   </si>
   <si>
     <t xml:space="preserve">9.86723518371582</t>
@@ -1463,16 +1463,16 @@
     <t xml:space="preserve">9.8275260925293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77931118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83320045471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94948482513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714406967163</t>
+    <t xml:space="preserve">9.77931213378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8331995010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94948577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714416503906</t>
   </si>
   <si>
     <t xml:space="preserve">9.93814086914062</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">9.71407794952393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42761993408203</t>
+    <t xml:space="preserve">9.4276180267334</t>
   </si>
   <si>
     <t xml:space="preserve">9.10145378112793</t>
@@ -1493,25 +1493,25 @@
     <t xml:space="preserve">9.12414264678955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24326610565186</t>
+    <t xml:space="preserve">9.24326515197754</t>
   </si>
   <si>
     <t xml:space="preserve">9.20072174072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29274463653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51369762420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39841747283936</t>
+    <t xml:space="preserve">9.29274559020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51369667053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39841842651367</t>
   </si>
   <si>
     <t xml:space="preserve">9.47206878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44004726409912</t>
+    <t xml:space="preserve">9.4400463104248</t>
   </si>
   <si>
     <t xml:space="preserve">9.3375768661499</t>
@@ -1523,16 +1523,16 @@
     <t xml:space="preserve">9.02696514129639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89887523651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34397983551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31836223602295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93730354309082</t>
+    <t xml:space="preserve">8.89887619018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34398078918457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31836318969727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9373025894165</t>
   </si>
   <si>
     <t xml:space="preserve">8.92129135131836</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">8.93410110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64590454101562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83803558349609</t>
+    <t xml:space="preserve">8.64590263366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83803367614746</t>
   </si>
   <si>
     <t xml:space="preserve">8.7547779083252</t>
@@ -1553,7 +1553,7 @@
     <t xml:space="preserve">8.72275638580322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71635246276855</t>
+    <t xml:space="preserve">8.71635150909424</t>
   </si>
   <si>
     <t xml:space="preserve">8.64270114898682</t>
@@ -1562,10 +1562,10 @@
     <t xml:space="preserve">8.82842826843262</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80601215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83163070678711</t>
+    <t xml:space="preserve">8.8060131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83163166046143</t>
   </si>
   <si>
     <t xml:space="preserve">8.66511726379395</t>
@@ -1580,10 +1580,10 @@
     <t xml:space="preserve">8.4889965057373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56904983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45697498321533</t>
+    <t xml:space="preserve">8.56905174255371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45697593688965</t>
   </si>
   <si>
     <t xml:space="preserve">8.39613342285156</t>
@@ -1592,55 +1592,55 @@
     <t xml:space="preserve">8.51141166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53062629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53703022003174</t>
+    <t xml:space="preserve">8.53062534332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53702926635742</t>
   </si>
   <si>
     <t xml:space="preserve">8.54343318939209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71314907073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40573978424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36411190032959</t>
+    <t xml:space="preserve">8.71315002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40573883056641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36411094665527</t>
   </si>
   <si>
     <t xml:space="preserve">8.3320894241333</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42175197601318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58506107330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5722541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46017646789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46658134460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58186149597168</t>
+    <t xml:space="preserve">8.42175102233887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58506298065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57225322723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46017742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46658039093018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58186054229736</t>
   </si>
   <si>
     <t xml:space="preserve">8.4409646987915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09421062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01735782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05578327178955</t>
+    <t xml:space="preserve">9.09420967102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01735687255859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05578422546387</t>
   </si>
   <si>
     <t xml:space="preserve">9.1998815536499</t>
@@ -1652,34 +1652,34 @@
     <t xml:space="preserve">8.91808986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87646198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03657054901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18387126922607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15505027770996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1518497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.235107421875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16465950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1262321472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26072216033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.254319190979</t>
+    <t xml:space="preserve">8.87646102905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03657150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18387222290039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15505218505859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15184879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23510551452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16465854644775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12623119354248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26072406768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25432014465332</t>
   </si>
   <si>
     <t xml:space="preserve">9.20628643035889</t>
@@ -1691,31 +1691,31 @@
     <t xml:space="preserve">9.22549915313721</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10701942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92769813537598</t>
+    <t xml:space="preserve">9.10701847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92769622802734</t>
   </si>
   <si>
     <t xml:space="preserve">8.76758670806885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65871143341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68112754821777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72595691680908</t>
+    <t xml:space="preserve">8.65871238708496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68112850189209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72595882415771</t>
   </si>
   <si>
     <t xml:space="preserve">8.61708450317383</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7803955078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82202529907227</t>
+    <t xml:space="preserve">8.78039646148682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82202434539795</t>
   </si>
   <si>
     <t xml:space="preserve">8.77719402313232</t>
@@ -1724,10 +1724,10 @@
     <t xml:space="preserve">8.78359699249268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95331478118896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97252655029297</t>
+    <t xml:space="preserve">8.95331382751465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97252750396729</t>
   </si>
   <si>
     <t xml:space="preserve">8.9661226272583</t>
@@ -1739,25 +1739,25 @@
     <t xml:space="preserve">8.86045074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32568550109863</t>
+    <t xml:space="preserve">8.32568454742432</t>
   </si>
   <si>
     <t xml:space="preserve">8.22321510314941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29366302490234</t>
+    <t xml:space="preserve">8.29366207122803</t>
   </si>
   <si>
     <t xml:space="preserve">8.53382682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48259258270264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40253829956055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14956569671631</t>
+    <t xml:space="preserve">8.48259162902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40253734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14956474304199</t>
   </si>
   <si>
     <t xml:space="preserve">8.06630802154541</t>
@@ -1766,73 +1766,73 @@
     <t xml:space="preserve">8.07271194458008</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7749080657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74929141998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67884397506714</t>
+    <t xml:space="preserve">7.77490997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74929094314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67884302139282</t>
   </si>
   <si>
     <t xml:space="preserve">7.87417602539062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73007822036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53474521636963</t>
+    <t xml:space="preserve">7.73007774353027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53474473953247</t>
   </si>
   <si>
     <t xml:space="preserve">7.42266941070557</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25295352935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21772813796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0800347328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11205673217773</t>
+    <t xml:space="preserve">7.25295305252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21772861480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08003568649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11205577850342</t>
   </si>
   <si>
     <t xml:space="preserve">6.84947681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97116041183472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04160833358765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03520393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04801177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94234085083008</t>
+    <t xml:space="preserve">6.97115993499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04160785675049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03520441055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04801273345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94234037399292</t>
   </si>
   <si>
     <t xml:space="preserve">6.95194673538208</t>
   </si>
   <si>
-    <t xml:space="preserve">7.00958633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13126850128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97436141967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83026361465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95514869689941</t>
+    <t xml:space="preserve">7.00958585739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1312689781189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97436094284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83026313781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95514965057373</t>
   </si>
   <si>
     <t xml:space="preserve">6.80144500732422</t>
@@ -1841,19 +1841,19 @@
     <t xml:space="preserve">6.7662205696106</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8590841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62852668762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70537853240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7470064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86548805236816</t>
+    <t xml:space="preserve">6.85908365249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62852621078491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70537900924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74700689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86548852920532</t>
   </si>
   <si>
     <t xml:space="preserve">7.16329193115234</t>
@@ -1862,28 +1862,28 @@
     <t xml:space="preserve">7.09604597091675</t>
   </si>
   <si>
-    <t xml:space="preserve">7.06722688674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02239608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23053693771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05762004852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80464506149292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89110565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71818780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7374005317688</t>
+    <t xml:space="preserve">7.06722593307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02239513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23053646087646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05761909484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80464601516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89110517501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71818685531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73740100860596</t>
   </si>
   <si>
     <t xml:space="preserve">6.95835113525391</t>
@@ -1892,55 +1892,55 @@
     <t xml:space="preserve">7.01278877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88790416717529</t>
+    <t xml:space="preserve">6.88790321350098</t>
   </si>
   <si>
     <t xml:space="preserve">6.45881032943726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39796829223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1520414352417</t>
+    <t xml:space="preserve">6.39796876907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15204095840454</t>
   </si>
   <si>
     <t xml:space="preserve">6.15844488143921</t>
   </si>
   <si>
-    <t xml:space="preserve">5.96375226974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10592985153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10721015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39925003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64453649520874</t>
+    <t xml:space="preserve">5.96375179290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10592937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10721111297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39924955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6445369720459</t>
   </si>
   <si>
     <t xml:space="preserve">6.63172817230225</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59010076522827</t>
+    <t xml:space="preserve">6.59009981155396</t>
   </si>
   <si>
     <t xml:space="preserve">6.50043916702271</t>
   </si>
   <si>
-    <t xml:space="preserve">6.60290861129761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59650421142578</t>
+    <t xml:space="preserve">6.60290908813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59650468826294</t>
   </si>
   <si>
     <t xml:space="preserve">6.41718053817749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52285385131836</t>
+    <t xml:space="preserve">6.52285480499268</t>
   </si>
   <si>
     <t xml:space="preserve">6.42038488388062</t>
@@ -1949,91 +1949,91 @@
     <t xml:space="preserve">6.47802305221558</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44600200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32624101638794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26732015609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74380397796631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09924745559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30738973617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19851541519165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08964109420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11846113204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15368556976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15688705444336</t>
+    <t xml:space="preserve">6.4460015296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32624053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2673192024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74380493164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09924793243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3073902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19851493835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08964157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11846160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15368366241455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1568865776062</t>
   </si>
   <si>
     <t xml:space="preserve">7.17930221557617</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04481029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99357557296753</t>
+    <t xml:space="preserve">7.04481172561646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99357461929321</t>
   </si>
   <si>
     <t xml:space="preserve">7.27216625213623</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44828462600708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75889873504639</t>
+    <t xml:space="preserve">7.44828605651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75889825820923</t>
   </si>
   <si>
     <t xml:space="preserve">7.5763726234436</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72687673568726</t>
+    <t xml:space="preserve">7.7268762588501</t>
   </si>
   <si>
     <t xml:space="preserve">7.83895301818848</t>
   </si>
   <si>
-    <t xml:space="preserve">7.82614278793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84535598754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8997950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91260242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98305082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88057994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91900777816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23282146453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12074565887451</t>
+    <t xml:space="preserve">7.82614374160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84535789489746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89979410171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9126033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98305225372314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88058185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91900730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23282241821289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.12074661254883</t>
   </si>
   <si>
     <t xml:space="preserve">8.26164054870605</t>
@@ -2045,37 +2045,37 @@
     <t xml:space="preserve">8.46337890625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84764194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91168594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2639274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3311710357666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53290939331055</t>
+    <t xml:space="preserve">8.84764099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9116849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26392650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33117198944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53291034698486</t>
   </si>
   <si>
     <t xml:space="preserve">9.67700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51049423217773</t>
+    <t xml:space="preserve">9.51049327850342</t>
   </si>
   <si>
     <t xml:space="preserve">9.42083263397217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32796859741211</t>
+    <t xml:space="preserve">9.32797050476074</t>
   </si>
   <si>
     <t xml:space="preserve">9.40482330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47847366333008</t>
+    <t xml:space="preserve">9.47847270965576</t>
   </si>
   <si>
     <t xml:space="preserve">9.55212306976318</t>
@@ -2084,25 +2084,25 @@
     <t xml:space="preserve">9.57133674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70262622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77627658843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81470203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.083685874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0356531143188</t>
+    <t xml:space="preserve">9.70262432098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77627563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81470108032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0836877822876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0356521606445</t>
   </si>
   <si>
     <t xml:space="preserve">10.1413249969482</t>
   </si>
   <si>
-    <t xml:space="preserve">10.21497631073</t>
+    <t xml:space="preserve">10.2149753570557</t>
   </si>
   <si>
     <t xml:space="preserve">10.1957626342773</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">10.2694120407104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2790203094482</t>
+    <t xml:space="preserve">10.2790184020996</t>
   </si>
   <si>
     <t xml:space="preserve">10.5608129501343</t>
@@ -2120,19 +2120,19 @@
     <t xml:space="preserve">10.8490085601807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8682222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8874340057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0155229568481</t>
+    <t xml:space="preserve">10.868221282959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8874349594116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0155210494995</t>
   </si>
   <si>
     <t xml:space="preserve">11.0603523254395</t>
   </si>
   <si>
-    <t xml:space="preserve">11.281304359436</t>
+    <t xml:space="preserve">11.2813053131104</t>
   </si>
   <si>
     <t xml:space="preserve">11.2909097671509</t>
@@ -2141,13 +2141,13 @@
     <t xml:space="preserve">11.5118608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5278730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4958515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3773698806763</t>
+    <t xml:space="preserve">11.5278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4958505630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3773670196533</t>
   </si>
   <si>
     <t xml:space="preserve">11.3261337280273</t>
@@ -2156,25 +2156,25 @@
     <t xml:space="preserve">11.4926481246948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8105812072754</t>
+    <t xml:space="preserve">10.8105821609497</t>
   </si>
   <si>
     <t xml:space="preserve">10.9899053573608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5992374420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1404075622559</t>
+    <t xml:space="preserve">10.5992383956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1404085159302</t>
   </si>
   <si>
     <t xml:space="preserve">11.1141195297241</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7917671203613</t>
+    <t xml:space="preserve">10.7917680740356</t>
   </si>
   <si>
     <t xml:space="preserve">10.7882642745972</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">10.4203634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5780353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.399341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4273710250854</t>
+    <t xml:space="preserve">10.5780363082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3993406295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4273719787598</t>
   </si>
   <si>
     <t xml:space="preserve">10.2872190475464</t>
@@ -2198,7 +2198,7 @@
     <t xml:space="preserve">10.3888282775879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4238681793213</t>
+    <t xml:space="preserve">10.423867225647</t>
   </si>
   <si>
     <t xml:space="preserve">10.3678073883057</t>
@@ -2216,10 +2216,10 @@
     <t xml:space="preserve">10.5079593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5149660110474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6305932998657</t>
+    <t xml:space="preserve">10.514965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6305923461914</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127918243408</t>
@@ -2228,16 +2228,16 @@
     <t xml:space="preserve">11.128134727478</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1876993179321</t>
+    <t xml:space="preserve">11.1877002716064</t>
   </si>
   <si>
     <t xml:space="preserve">11.3523797988892</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5731191635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6151676177979</t>
+    <t xml:space="preserve">11.5731210708618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6151666641235</t>
   </si>
   <si>
     <t xml:space="preserve">11.7553195953369</t>
@@ -2246,25 +2246,25 @@
     <t xml:space="preserve">11.7342967987061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429145812988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7097673416138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6291799545288</t>
+    <t xml:space="preserve">11.8429136276245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7097692489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6291809082031</t>
   </si>
   <si>
     <t xml:space="preserve">11.8639373779297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9059829711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9200010299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0496406555176</t>
+    <t xml:space="preserve">11.9059839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0496397018433</t>
   </si>
   <si>
     <t xml:space="preserve">12.2318382263184</t>
@@ -2279,37 +2279,37 @@
     <t xml:space="preserve">12.214319229126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3159313201904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2773885726929</t>
+    <t xml:space="preserve">12.3159303665161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2773895263672</t>
   </si>
   <si>
     <t xml:space="preserve">12.4175415039062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684873580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1267251968384</t>
+    <t xml:space="preserve">12.3684883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1267242431641</t>
   </si>
   <si>
     <t xml:space="preserve">12.0391283035278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8464193344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636558532715</t>
+    <t xml:space="preserve">11.8464202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636548995972</t>
   </si>
   <si>
     <t xml:space="preserve">12.1407403945923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1232204437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1092052459717</t>
+    <t xml:space="preserve">12.1232194900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.109206199646</t>
   </si>
   <si>
     <t xml:space="preserve">12.0321216583252</t>
@@ -2318,10 +2318,10 @@
     <t xml:space="preserve">11.8779535293579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760608673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6887474060059</t>
+    <t xml:space="preserve">11.9760599136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6887464523315</t>
   </si>
   <si>
     <t xml:space="preserve">11.4680051803589</t>
@@ -2345,85 +2345,85 @@
     <t xml:space="preserve">11.1001052856445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7216920852661</t>
+    <t xml:space="preserve">10.7216930389404</t>
   </si>
   <si>
     <t xml:space="preserve">10.9284172058105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1561651229858</t>
+    <t xml:space="preserve">11.1561660766602</t>
   </si>
   <si>
     <t xml:space="preserve">11.4960374832153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.446982383728</t>
+    <t xml:space="preserve">11.4469814300537</t>
   </si>
   <si>
     <t xml:space="preserve">11.1841974258423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3243494033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2752962112427</t>
+    <t xml:space="preserve">11.3243503570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.275297164917</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4049377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2297458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4119443893433</t>
+    <t xml:space="preserve">11.4049367904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2297468185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4119453430176</t>
   </si>
   <si>
     <t xml:space="preserve">11.4995403289795</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7903575897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8814563751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8288993835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9550371170044</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6677236557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6712293624878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9970836639404</t>
+    <t xml:space="preserve">11.790358543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8814573287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8288984298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9550361633301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6677227020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6712284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113813400269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9970846176147</t>
   </si>
   <si>
     <t xml:space="preserve">11.9410219192505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9690523147583</t>
+    <t xml:space="preserve">11.969051361084</t>
   </si>
   <si>
     <t xml:space="preserve">12.0671586990356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2703809738159</t>
+    <t xml:space="preserve">12.2703819274902</t>
   </si>
   <si>
     <t xml:space="preserve">12.2738838195801</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1021976470947</t>
+    <t xml:space="preserve">12.102198600769</t>
   </si>
   <si>
     <t xml:space="preserve">12.0951900482178</t>
@@ -2432,7 +2432,7 @@
     <t xml:space="preserve">11.9725561141968</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0146017074585</t>
+    <t xml:space="preserve">12.0146026611328</t>
   </si>
   <si>
     <t xml:space="preserve">12.0741662979126</t>
@@ -2441,16 +2441,16 @@
     <t xml:space="preserve">11.9865713119507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6011505126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.552098274231</t>
+    <t xml:space="preserve">11.6011514663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5520973205566</t>
   </si>
   <si>
     <t xml:space="preserve">11.5485944747925</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5941429138184</t>
+    <t xml:space="preserve">11.5941438674927</t>
   </si>
   <si>
     <t xml:space="preserve">11.4259595870972</t>
@@ -2459,34 +2459,34 @@
     <t xml:space="preserve">11.5380821228027</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6852426528931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7693338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7027626037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9480295181274</t>
+    <t xml:space="preserve">11.6852436065674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7693357467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7027616500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9480285644531</t>
   </si>
   <si>
     <t xml:space="preserve">12.0846796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2108144760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7539081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9641361236572</t>
+    <t xml:space="preserve">12.2108154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7539091110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9641380310059</t>
   </si>
   <si>
     <t xml:space="preserve">12.7188701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7889461517334</t>
+    <t xml:space="preserve">12.788948059082</t>
   </si>
   <si>
     <t xml:space="preserve">12.795952796936</t>
@@ -2495,16 +2495,16 @@
     <t xml:space="preserve">12.9886646270752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1743650436401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9080762863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0412225723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094068527222</t>
+    <t xml:space="preserve">13.1743659973145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9080772399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.041220664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094049453735</t>
   </si>
   <si>
     <t xml:space="preserve">13.6649026870728</t>
@@ -2513,37 +2513,37 @@
     <t xml:space="preserve">13.8996572494507</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4007034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.365665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389636993408</t>
+    <t xml:space="preserve">14.4007043838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3656663894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389627456665</t>
   </si>
   <si>
     <t xml:space="preserve">15.0173759460449</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1365060806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5289354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9493932723999</t>
+    <t xml:space="preserve">15.1365070343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5289344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9493923187256</t>
   </si>
   <si>
     <t xml:space="preserve">15.7181396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9213619232178</t>
+    <t xml:space="preserve">15.9213638305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.1035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9914388656616</t>
+    <t xml:space="preserve">15.9914398193359</t>
   </si>
   <si>
     <t xml:space="preserve">16.1245861053467</t>
@@ -2558,13 +2558,13 @@
     <t xml:space="preserve">16.5100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2086772918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0474987030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8863248825073</t>
+    <t xml:space="preserve">16.2086753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0475006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8863229751587</t>
   </si>
   <si>
     <t xml:space="preserve">15.4868869781494</t>
@@ -2576,16 +2576,16 @@
     <t xml:space="preserve">15.7531785964966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7251482009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1575288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3817749023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2626457214355</t>
+    <t xml:space="preserve">15.725152015686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.157527923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3817720413208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2626447677612</t>
   </si>
   <si>
     <t xml:space="preserve">15.2976818084717</t>
@@ -2594,67 +2594,67 @@
     <t xml:space="preserve">15.0804452896118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2836666107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2205972671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0944604873657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0664300918579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0454063415527</t>
+    <t xml:space="preserve">15.2836675643921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2205982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0944623947144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0664291381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0454082489014</t>
   </si>
   <si>
     <t xml:space="preserve">14.8562002182007</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9122610092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1715450286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8702163696289</t>
+    <t xml:space="preserve">14.9122638702393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1715440750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8702144622803</t>
   </si>
   <si>
     <t xml:space="preserve">14.7721099853516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3537425994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5029945373535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5800819396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4189052581787</t>
+    <t xml:space="preserve">15.353741645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5029964447021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5800800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4189033508301</t>
   </si>
   <si>
     <t xml:space="preserve">16.7062187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8043270111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6221256256104</t>
+    <t xml:space="preserve">16.8043251037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.622127532959</t>
   </si>
   <si>
     <t xml:space="preserve">16.5660648345947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9865226745605</t>
+    <t xml:space="preserve">16.9865245819092</t>
   </si>
   <si>
     <t xml:space="preserve">17.00754737854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5380363464355</t>
+    <t xml:space="preserve">16.5380344390869</t>
   </si>
   <si>
     <t xml:space="preserve">16.0545063018799</t>
@@ -2669,31 +2669,31 @@
     <t xml:space="preserve">16.0685234069824</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5499582290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5709781646729</t>
+    <t xml:space="preserve">15.5499572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5709800720215</t>
   </si>
   <si>
     <t xml:space="preserve">16.033483505249</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9423837661743</t>
+    <t xml:space="preserve">15.9423856735229</t>
   </si>
   <si>
     <t xml:space="preserve">16.1666278839111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6431503295898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3908729553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.762279510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7833042144775</t>
+    <t xml:space="preserve">16.6431484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3908748626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7622776031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7833003997803</t>
   </si>
   <si>
     <t xml:space="preserve">16.6711807250977</t>
@@ -2702,22 +2702,22 @@
     <t xml:space="preserve">16.7272415161133</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9514865875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6130285263062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5198354721069</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3516521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5478639602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7910404205322</t>
+    <t xml:space="preserve">16.9514846801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6130247116089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5198335647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3516511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5478668212891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7910385131836</t>
   </si>
   <si>
     <t xml:space="preserve">13.4546728134155</t>
@@ -2726,13 +2726,13 @@
     <t xml:space="preserve">13.0272054672241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9956722259521</t>
+    <t xml:space="preserve">12.9956703186035</t>
   </si>
   <si>
     <t xml:space="preserve">12.3474655151367</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7202825546265</t>
+    <t xml:space="preserve">11.7202816009521</t>
   </si>
   <si>
     <t xml:space="preserve">10.3327674865723</t>
@@ -2744,7 +2744,7 @@
     <t xml:space="preserve">9.81069850921631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25149726867676</t>
+    <t xml:space="preserve">8.25149822235107</t>
   </si>
   <si>
     <t xml:space="preserve">9.51988220214844</t>
@@ -2756,28 +2756,28 @@
     <t xml:space="preserve">8.02024555206299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70490217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77497911453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49817657470703</t>
+    <t xml:space="preserve">7.70490264892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77497863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49817752838135</t>
   </si>
   <si>
     <t xml:space="preserve">7.59978771209717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28653621673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06088161468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69507312774658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05037021636963</t>
+    <t xml:space="preserve">8.28653717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06088066101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69507217407227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05036926269531</t>
   </si>
   <si>
     <t xml:space="preserve">8.87167549133301</t>
@@ -2789,16 +2789,16 @@
     <t xml:space="preserve">8.87517833709717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07489585876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68246841430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02233791351318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48834800720215</t>
+    <t xml:space="preserve">9.07489681243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68246936798096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02233982086182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48834705352783</t>
   </si>
   <si>
     <t xml:space="preserve">10.1680889129639</t>
@@ -2807,10 +2807,10 @@
     <t xml:space="preserve">10.2381649017334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87727165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29914093017578</t>
+    <t xml:space="preserve">9.87727069854736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2991418838501</t>
   </si>
   <si>
     <t xml:space="preserve">9.4463005065918</t>
@@ -2819,10 +2819,10 @@
     <t xml:space="preserve">9.51637744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58995914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2535924911499</t>
+    <t xml:space="preserve">9.58995819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25359153747559</t>
   </si>
   <si>
     <t xml:space="preserve">9.33417892456055</t>
@@ -2837,10 +2837,10 @@
     <t xml:space="preserve">10.3713102340698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.816294670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2122278213501</t>
+    <t xml:space="preserve">10.8162956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2122259140015</t>
   </si>
   <si>
     <t xml:space="preserve">10.8793640136719</t>
@@ -2879,16 +2879,16 @@
     <t xml:space="preserve">10.6414775848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7691898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8743667602539</t>
+    <t xml:space="preserve">10.769190788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8743658065796</t>
   </si>
   <si>
     <t xml:space="preserve">10.9757843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9720287322998</t>
+    <t xml:space="preserve">10.9720277786255</t>
   </si>
   <si>
     <t xml:space="preserve">11.358922958374</t>
@@ -2900,31 +2900,31 @@
     <t xml:space="preserve">11.3251161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5204429626465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7984046936035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0913925170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6923961639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9966506958008</t>
+    <t xml:space="preserve">11.5204420089722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7984056472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0913915634155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6923952102661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9966497421265</t>
   </si>
   <si>
     <t xml:space="preserve">12.4407243728638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3956508636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.648154258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6105928421021</t>
+    <t xml:space="preserve">12.3956489562988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6481552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6105918884277</t>
   </si>
   <si>
     <t xml:space="preserve">11.5166854858398</t>
@@ -2933,31 +2933,31 @@
     <t xml:space="preserve">11.7721109390259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669368743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5091724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7157678604126</t>
+    <t xml:space="preserve">11.6669359207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5091733932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7157669067383</t>
   </si>
   <si>
     <t xml:space="preserve">11.5730295181274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8284549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2687721252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4490718841553</t>
+    <t xml:space="preserve">11.8284559249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2687740325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4490728378296</t>
   </si>
   <si>
     <t xml:space="preserve">11.2011604309082</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4791231155396</t>
+    <t xml:space="preserve">11.4791240692139</t>
   </si>
   <si>
     <t xml:space="preserve">11.4265356063843</t>
@@ -2975,31 +2975,31 @@
     <t xml:space="preserve">11.7796239852905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7608423233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4753665924072</t>
+    <t xml:space="preserve">11.7608413696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4753656387329</t>
   </si>
   <si>
     <t xml:space="preserve">11.6706914901733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8585033416748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8434820175171</t>
+    <t xml:space="preserve">11.8585052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8434810638428</t>
   </si>
   <si>
     <t xml:space="preserve">12.3580884933472</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3205251693726</t>
+    <t xml:space="preserve">12.3205242156982</t>
   </si>
   <si>
     <t xml:space="preserve">12.8013257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6999073028564</t>
+    <t xml:space="preserve">12.6999082565308</t>
   </si>
   <si>
     <t xml:space="preserve">12.7337141036987</t>
@@ -3008,82 +3008,82 @@
     <t xml:space="preserve">12.835132598877</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5684375762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6097555160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3731117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4369697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0763692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0575857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3693571090698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3505744934082</t>
+    <t xml:space="preserve">12.5684385299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6097564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3731126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4369688034058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0763683319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0575866699219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3693561553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3505754470825</t>
   </si>
   <si>
     <t xml:space="preserve">12.4745311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.493311882019</t>
+    <t xml:space="preserve">12.4933128356934</t>
   </si>
   <si>
     <t xml:space="preserve">12.4707765579224</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8276214599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938146591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6585893630981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5984888076782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4557504653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.515851020813</t>
+    <t xml:space="preserve">12.8276205062866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938137054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6585884094238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5984878540039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4557495117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5158500671387</t>
   </si>
   <si>
     <t xml:space="preserve">12.3468179702759</t>
   </si>
   <si>
-    <t xml:space="preserve">12.21910572052</t>
+    <t xml:space="preserve">12.2191066741943</t>
   </si>
   <si>
     <t xml:space="preserve">12.6661014556885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6247825622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5083379745483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3881368637085</t>
+    <t xml:space="preserve">12.6247816085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.508337020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3881378173828</t>
   </si>
   <si>
     <t xml:space="preserve">12.1740312576294</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0650997161865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.264181137085</t>
+    <t xml:space="preserve">12.0650987625122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2641820907593</t>
   </si>
   <si>
     <t xml:space="preserve">11.9749488830566</t>
@@ -3110,34 +3110,34 @@
     <t xml:space="preserve">12.5120944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6285371780396</t>
+    <t xml:space="preserve">12.6285381317139</t>
   </si>
   <si>
     <t xml:space="preserve">12.4257011413574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8547487258911</t>
+    <t xml:space="preserve">11.8547496795654</t>
   </si>
   <si>
     <t xml:space="preserve">11.8322114944458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8096752166748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6181039810181</t>
+    <t xml:space="preserve">11.8096742630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6181049346924</t>
   </si>
   <si>
     <t xml:space="preserve">11.3326292037964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7645978927612</t>
+    <t xml:space="preserve">11.7645998001099</t>
   </si>
   <si>
     <t xml:space="preserve">11.5993232727051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5842981338501</t>
+    <t xml:space="preserve">11.5842990875244</t>
   </si>
   <si>
     <t xml:space="preserve">11.4640989303589</t>
@@ -3146,13 +3146,13 @@
     <t xml:space="preserve">11.362678527832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7120113372803</t>
+    <t xml:space="preserve">11.712010383606</t>
   </si>
   <si>
     <t xml:space="preserve">11.8772869110107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8359670639038</t>
+    <t xml:space="preserve">11.8359680175781</t>
   </si>
   <si>
     <t xml:space="preserve">11.9524116516113</t>
@@ -3176,34 +3176,34 @@
     <t xml:space="preserve">12.0989055633545</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1514921188354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0801248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7007436752319</t>
+    <t xml:space="preserve">12.1514930725098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0801239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7007417678833</t>
   </si>
   <si>
     <t xml:space="preserve">11.5241985321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8255348205566</t>
+    <t xml:space="preserve">10.8255338668823</t>
   </si>
   <si>
     <t xml:space="preserve">10.6452341079712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8893899917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2499914169312</t>
+    <t xml:space="preserve">10.8893909454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2499923706055</t>
   </si>
   <si>
     <t xml:space="preserve">11.64439868927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8209419250488</t>
+    <t xml:space="preserve">11.8209428787231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275363922119</t>
@@ -3221,7 +3221,7 @@
     <t xml:space="preserve">12.4106740951538</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1393871307373</t>
+    <t xml:space="preserve">13.1393890380859</t>
   </si>
   <si>
     <t xml:space="preserve">13.2070007324219</t>
@@ -3233,16 +3233,16 @@
     <t xml:space="preserve">13.2370519638062</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2595891952515</t>
+    <t xml:space="preserve">13.2595901489258</t>
   </si>
   <si>
     <t xml:space="preserve">13.2220277786255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6727771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3572540283203</t>
+    <t xml:space="preserve">13.6727781295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3572521209717</t>
   </si>
   <si>
     <t xml:space="preserve">13.3797903060913</t>
@@ -3251,10 +3251,10 @@
     <t xml:space="preserve">13.2746143341064</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5375528335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882219314575</t>
+    <t xml:space="preserve">13.5375518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1882209777832</t>
   </si>
   <si>
     <t xml:space="preserve">13.2821264266968</t>
@@ -3263,10 +3263,10 @@
     <t xml:space="preserve">13.2896404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2295389175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619262695312</t>
+    <t xml:space="preserve">13.2295398712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619272232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.9327945709229</t>
@@ -3275,16 +3275,16 @@
     <t xml:space="preserve">13.1731939315796</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1919765472412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1957321166992</t>
+    <t xml:space="preserve">13.1919755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1957340240479</t>
   </si>
   <si>
     <t xml:space="preserve">13.0154333114624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8238620758057</t>
+    <t xml:space="preserve">12.82386302948</t>
   </si>
   <si>
     <t xml:space="preserve">13.3272008895874</t>
@@ -3293,22 +3293,22 @@
     <t xml:space="preserve">13.4361333847046</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4962339401245</t>
+    <t xml:space="preserve">13.4962348937988</t>
   </si>
   <si>
     <t xml:space="preserve">13.4323759078979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3497400283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3384704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1994886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4135971069336</t>
+    <t xml:space="preserve">13.3497409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3384695053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1994895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4135961532593</t>
   </si>
   <si>
     <t xml:space="preserve">13.4248657226562</t>
@@ -3317,7 +3317,7 @@
     <t xml:space="preserve">13.39857006073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3910598754883</t>
+    <t xml:space="preserve">13.391058921814</t>
   </si>
   <si>
     <t xml:space="preserve">13.6802892684937</t>
@@ -3326,19 +3326,19 @@
     <t xml:space="preserve">14.2099227905273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9582538604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8305397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943967819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8380527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.931960105896</t>
+    <t xml:space="preserve">13.9582548141479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8305406570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943977355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8380537033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9319581985474</t>
   </si>
   <si>
     <t xml:space="preserve">13.7328786849976</t>
@@ -3347,73 +3347,73 @@
     <t xml:space="preserve">13.4398899078369</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4060831069946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1093397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3009090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0417280197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887199401855</t>
+    <t xml:space="preserve">13.4060840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1093406677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3009080886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.04172706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887208938599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5676021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7216091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3526601791382</t>
+    <t xml:space="preserve">13.7216081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3526611328125</t>
   </si>
   <si>
     <t xml:space="preserve">14.5855484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0550804138184</t>
+    <t xml:space="preserve">15.0550813674927</t>
   </si>
   <si>
     <t xml:space="preserve">15.092643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0250310897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1978178024292</t>
+    <t xml:space="preserve">15.0250301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1978197097778</t>
   </si>
   <si>
     <t xml:space="preserve">14.8447303771973</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9198579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8221912384033</t>
+    <t xml:space="preserve">14.7207717895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9198570251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8221921920776</t>
   </si>
   <si>
     <t xml:space="preserve">14.532958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6005725860596</t>
+    <t xml:space="preserve">14.6005735397339</t>
   </si>
   <si>
     <t xml:space="preserve">14.4315404891968</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2812919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9499044418335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.784631729126</t>
+    <t xml:space="preserve">14.2812929153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9499053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.784628868103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7095041275024</t>
@@ -3422,46 +3422,46 @@
     <t xml:space="preserve">14.6644296646118</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4240303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7958993911743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7620916366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9123439788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6606731414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4090032577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1948986053467</t>
+    <t xml:space="preserve">14.4240293502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7959003448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.762092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9123420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6606721878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4090042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1948976516724</t>
   </si>
   <si>
     <t xml:space="preserve">14.1197729110718</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2024097442627</t>
+    <t xml:space="preserve">14.202410697937</t>
   </si>
   <si>
     <t xml:space="preserve">14.2775344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3226108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202718734741</t>
+    <t xml:space="preserve">14.3226099014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202728271484</t>
   </si>
   <si>
     <t xml:space="preserve">14.3714399337769</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2925586700439</t>
+    <t xml:space="preserve">14.2925605773926</t>
   </si>
   <si>
     <t xml:space="preserve">14.4653472900391</t>
@@ -3470,55 +3470,55 @@
     <t xml:space="preserve">14.7470664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5930595397949</t>
+    <t xml:space="preserve">14.5930604934692</t>
   </si>
   <si>
     <t xml:space="preserve">14.8898038864136</t>
   </si>
   <si>
-    <t xml:space="preserve">14.848484992981</t>
+    <t xml:space="preserve">14.8484869003296</t>
   </si>
   <si>
     <t xml:space="preserve">15.2504062652588</t>
   </si>
   <si>
-    <t xml:space="preserve">15.100154876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1151819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0701055526733</t>
+    <t xml:space="preserve">15.1001558303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1151809692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.070104598999</t>
   </si>
   <si>
     <t xml:space="preserve">15.1827926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7245283126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.750825881958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.814679145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8184366226196</t>
+    <t xml:space="preserve">14.7245302200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7508220672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8146800994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8184356689453</t>
   </si>
   <si>
     <t xml:space="preserve">14.9837112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0175161361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7921419143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9611740112305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1602573394775</t>
+    <t xml:space="preserve">15.0175170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7921438217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9611730575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1602554321289</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724426269531</t>
@@ -3527,28 +3527,28 @@
     <t xml:space="preserve">15.085129737854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1377191543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3555812835693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2579174041748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2804555892944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2729444503784</t>
+    <t xml:space="preserve">15.1377182006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.355580329895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2579183578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2804565429688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2729434967041</t>
   </si>
   <si>
     <t xml:space="preserve">15.7462310791016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8664321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8438949584961</t>
+    <t xml:space="preserve">15.86643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8438930511475</t>
   </si>
   <si>
     <t xml:space="preserve">15.641056060791</t>
@@ -3563,19 +3563,19 @@
     <t xml:space="preserve">16.1603355407715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0814266204834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8841552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.899941444397</t>
+    <t xml:space="preserve">16.081428527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8841571807861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8999395370483</t>
   </si>
   <si>
     <t xml:space="preserve">15.955174446106</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0419731140137</t>
+    <t xml:space="preserve">16.0419750213623</t>
   </si>
   <si>
     <t xml:space="preserve">16.0025196075439</t>
@@ -3584,7 +3584,7 @@
     <t xml:space="preserve">16.0972080230713</t>
   </si>
   <si>
-    <t xml:space="preserve">16.144552230835</t>
+    <t xml:space="preserve">16.1445541381836</t>
   </si>
   <si>
     <t xml:space="preserve">16.4601860046387</t>
@@ -3596,13 +3596,13 @@
     <t xml:space="preserve">16.412841796875</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3260402679443</t>
+    <t xml:space="preserve">16.3260440826416</t>
   </si>
   <si>
     <t xml:space="preserve">16.3497142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9946298599243</t>
+    <t xml:space="preserve">15.99462890625</t>
   </si>
   <si>
     <t xml:space="preserve">16.1208820343018</t>
@@ -3614,16 +3614,16 @@
     <t xml:space="preserve">16.0183010101318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9472827911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8762674331665</t>
+    <t xml:space="preserve">15.9472846984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8762683868408</t>
   </si>
   <si>
     <t xml:space="preserve">16.2392444610596</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2471332550049</t>
+    <t xml:space="preserve">16.2471351623535</t>
   </si>
   <si>
     <t xml:space="preserve">16.5312042236328</t>
@@ -3638,19 +3638,19 @@
     <t xml:space="preserve">16.3023700714111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5943298339844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5075302124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4838581085205</t>
+    <t xml:space="preserve">16.5943279266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.507532119751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4838562011719</t>
   </si>
   <si>
     <t xml:space="preserve">16.4444046020508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550258636475</t>
+    <t xml:space="preserve">16.2550239562988</t>
   </si>
   <si>
     <t xml:space="preserve">16.5233135223389</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">17.5254421234131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3281726837158</t>
+    <t xml:space="preserve">17.3281707763672</t>
   </si>
   <si>
     <t xml:space="preserve">17.1940288543701</t>
@@ -3674,16 +3674,16 @@
     <t xml:space="preserve">17.2492656707764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1387939453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4702072143555</t>
+    <t xml:space="preserve">17.1387920379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4702053070068</t>
   </si>
   <si>
     <t xml:space="preserve">17.4938793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2808265686035</t>
+    <t xml:space="preserve">17.2808284759521</t>
   </si>
   <si>
     <t xml:space="preserve">17.4070796966553</t>
@@ -3695,16 +3695,16 @@
     <t xml:space="preserve">17.9042015075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9120903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1093597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1172523498535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2592868804932</t>
+    <t xml:space="preserve">17.9120922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1093616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1172504425049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2592849731445</t>
   </si>
   <si>
     <t xml:space="preserve">18.3224124908447</t>
@@ -3713,13 +3713,13 @@
     <t xml:space="preserve">18.2435035705566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4644470214844</t>
+    <t xml:space="preserve">18.4644451141357</t>
   </si>
   <si>
     <t xml:space="preserve">18.2513942718506</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2829570770264</t>
+    <t xml:space="preserve">18.282958984375</t>
   </si>
   <si>
     <t xml:space="preserve">18.424991607666</t>
@@ -3728,7 +3728,7 @@
     <t xml:space="preserve">18.3539752960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4407749176025</t>
+    <t xml:space="preserve">18.4407730102539</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906982421875</t>
@@ -3737,19 +3737,19 @@
     <t xml:space="preserve">18.6696071624756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.748514175415</t>
+    <t xml:space="preserve">18.7485160827637</t>
   </si>
   <si>
     <t xml:space="preserve">18.7642974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8037509918213</t>
+    <t xml:space="preserve">18.8037490844727</t>
   </si>
   <si>
     <t xml:space="preserve">18.701171875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.756404876709</t>
+    <t xml:space="preserve">18.7564067840576</t>
   </si>
   <si>
     <t xml:space="preserve">18.7406234741211</t>
@@ -3758,7 +3758,7 @@
     <t xml:space="preserve">18.6459331512451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7169494628906</t>
+    <t xml:space="preserve">18.7169513702393</t>
   </si>
   <si>
     <t xml:space="preserve">18.5749187469482</t>
@@ -3773,19 +3773,19 @@
     <t xml:space="preserve">18.9536762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1903991699219</t>
+    <t xml:space="preserve">19.1903972625732</t>
   </si>
   <si>
     <t xml:space="preserve">19.0878200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5591373443604</t>
+    <t xml:space="preserve">18.5591354370117</t>
   </si>
   <si>
     <t xml:space="preserve">18.8589859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9378929138184</t>
+    <t xml:space="preserve">18.937894821167</t>
   </si>
   <si>
     <t xml:space="preserve">19.2614154815674</t>
@@ -3800,22 +3800,22 @@
     <t xml:space="preserve">18.5985889434814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721862792969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6538238525391</t>
+    <t xml:space="preserve">18.7721881866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6538257598877</t>
   </si>
   <si>
     <t xml:space="preserve">18.4013195037842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6222629547119</t>
+    <t xml:space="preserve">18.6222610473633</t>
   </si>
   <si>
     <t xml:space="preserve">18.2356128692627</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1409225463867</t>
+    <t xml:space="preserve">18.1409244537354</t>
   </si>
   <si>
     <t xml:space="preserve">18.43288230896</t>
@@ -3824,28 +3824,28 @@
     <t xml:space="preserve">18.6380443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8353118896484</t>
+    <t xml:space="preserve">18.8353137969971</t>
   </si>
   <si>
     <t xml:space="preserve">18.7090587615967</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5375919342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.403450012207</t>
+    <t xml:space="preserve">19.5375938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4034519195557</t>
   </si>
   <si>
     <t xml:space="preserve">19.5297031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6007175445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8374443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6322803497314</t>
+    <t xml:space="preserve">19.6007194519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8374423980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6322822570801</t>
   </si>
   <si>
     <t xml:space="preserve">19.6954078674316</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">19.9952583312988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.066276550293</t>
+    <t xml:space="preserve">20.0662784576416</t>
   </si>
   <si>
     <t xml:space="preserve">20.1057300567627</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">20.0504951477051</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0741672515869</t>
+    <t xml:space="preserve">20.0741691589355</t>
   </si>
   <si>
     <t xml:space="preserve">20.0189323425293</t>
@@ -3875,7 +3875,7 @@
     <t xml:space="preserve">20.2398738861084</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9027004241943</t>
+    <t xml:space="preserve">20.902702331543</t>
   </si>
   <si>
     <t xml:space="preserve">21.1788787841797</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">20.9816074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6659774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2162017822266</t>
+    <t xml:space="preserve">20.6659755706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2161998748779</t>
   </si>
   <si>
     <t xml:space="preserve">20.1372947692871</t>
@@ -3902,46 +3902,46 @@
     <t xml:space="preserve">20.0820579528809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1035995483398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.316650390625</t>
+    <t xml:space="preserve">19.1035976409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3166522979736</t>
   </si>
   <si>
     <t xml:space="preserve">19.3324337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4744682312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3087596893311</t>
+    <t xml:space="preserve">19.4744663238525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3087615966797</t>
   </si>
   <si>
     <t xml:space="preserve">19.1746158599854</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2377414703369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2850894927979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1272716522217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.024694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8116397857666</t>
+    <t xml:space="preserve">19.2377433776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2850875854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1272735595703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0246925354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8116416931152</t>
   </si>
   <si>
     <t xml:space="preserve">19.0168018341064</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7248420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9142208099365</t>
+    <t xml:space="preserve">18.7248401641846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9142189025879</t>
   </si>
   <si>
     <t xml:space="preserve">19.16672706604</t>
@@ -3950,7 +3950,7 @@
     <t xml:space="preserve">19.3561058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.411340713501</t>
+    <t xml:space="preserve">19.4113426208496</t>
   </si>
   <si>
     <t xml:space="preserve">19.7269725799561</t>
@@ -3968,7 +3968,7 @@
     <t xml:space="preserve">19.5770454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6165008544922</t>
+    <t xml:space="preserve">19.6165027618408</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268211364746</t>
@@ -3977,7 +3977,7 @@
     <t xml:space="preserve">20.8711376190186</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9342632293701</t>
+    <t xml:space="preserve">20.9342651367188</t>
   </si>
   <si>
     <t xml:space="preserve">20.5791778564453</t>
@@ -3986,10 +3986,10 @@
     <t xml:space="preserve">20.6817588806152</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3187828063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.884786605835</t>
+    <t xml:space="preserve">20.3187808990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8847885131836</t>
   </si>
   <si>
     <t xml:space="preserve">18.2119407653809</t>
@@ -3998,16 +3998,16 @@
     <t xml:space="preserve">18.2671756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3934268951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0325832366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8747653961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3303031921387</t>
+    <t xml:space="preserve">18.3934288024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.032585144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8747673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.33030128479</t>
   </si>
   <si>
     <t xml:space="preserve">18.7958583831787</t>
@@ -4022,7 +4022,7 @@
     <t xml:space="preserve">17.8095111846924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7463836669922</t>
+    <t xml:space="preserve">17.7463855743408</t>
   </si>
   <si>
     <t xml:space="preserve">17.9278717041016</t>
@@ -4046,10 +4046,10 @@
     <t xml:space="preserve">15.4501638412476</t>
   </si>
   <si>
-    <t xml:space="preserve">15.663215637207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0756664276123</t>
+    <t xml:space="preserve">15.6632165908813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0756683349609</t>
   </si>
   <si>
     <t xml:space="preserve">15.1897687911987</t>
@@ -4058,25 +4058,25 @@
     <t xml:space="preserve">15.5093460083008</t>
   </si>
   <si>
-    <t xml:space="preserve">15.852593421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0441055297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7915992736816</t>
+    <t xml:space="preserve">15.8525953292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0441036224365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7916011810303</t>
   </si>
   <si>
     <t xml:space="preserve">16.4759674072266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8152713775635</t>
+    <t xml:space="preserve">16.8152694702148</t>
   </si>
   <si>
     <t xml:space="preserve">16.7837085723877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4286212921143</t>
+    <t xml:space="preserve">16.4286231994629</t>
   </si>
   <si>
     <t xml:space="preserve">16.7442531585693</t>
@@ -4091,7 +4091,7 @@
     <t xml:space="preserve">16.6732349395752</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7600364685059</t>
+    <t xml:space="preserve">16.7600345611572</t>
   </si>
   <si>
     <t xml:space="preserve">16.3181533813477</t>
@@ -4100,7 +4100,7 @@
     <t xml:space="preserve">15.7579050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4107103347778</t>
+    <t xml:space="preserve">15.4107122421265</t>
   </si>
   <si>
     <t xml:space="preserve">15.7815780639648</t>
@@ -4109,7 +4109,7 @@
     <t xml:space="preserve">15.9157209396362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8920497894287</t>
+    <t xml:space="preserve">15.8920488357544</t>
   </si>
   <si>
     <t xml:space="preserve">15.8683776855469</t>
@@ -4121,34 +4121,34 @@
     <t xml:space="preserve">15.7973604202271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7539596557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8289222717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.089319229126</t>
+    <t xml:space="preserve">15.753960609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8289213180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0893173217773</t>
   </si>
   <si>
     <t xml:space="preserve">16.0735378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1761169433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9236106872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6395444869995</t>
+    <t xml:space="preserve">16.176118850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9236116409302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6395425796509</t>
   </si>
   <si>
     <t xml:space="preserve">15.5132913589478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9964437484741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1660957336426</t>
+    <t xml:space="preserve">14.9964427947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1660966873169</t>
   </si>
   <si>
     <t xml:space="preserve">15.6868877410889</t>
@@ -4157,13 +4157,13 @@
     <t xml:space="preserve">15.7381782531738</t>
   </si>
   <si>
-    <t xml:space="preserve">15.765796661377</t>
+    <t xml:space="preserve">15.7657976150513</t>
   </si>
   <si>
     <t xml:space="preserve">16.0261917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8052520751953</t>
+    <t xml:space="preserve">15.8052501678467</t>
   </si>
   <si>
     <t xml:space="preserve">16.4583625793457</t>
@@ -4181,19 +4181,19 @@
     <t xml:space="preserve">16.7703304290771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305305480957</t>
+    <t xml:space="preserve">16.9305286407471</t>
   </si>
   <si>
     <t xml:space="preserve">16.8209209442139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5932693481445</t>
+    <t xml:space="preserve">16.5932674407959</t>
   </si>
   <si>
     <t xml:space="preserve">16.8082733154297</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5595397949219</t>
+    <t xml:space="preserve">16.5595417022705</t>
   </si>
   <si>
     <t xml:space="preserve">16.871509552002</t>
@@ -4202,46 +4202,46 @@
     <t xml:space="preserve">16.7366046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5342464447021</t>
+    <t xml:space="preserve">16.5342483520508</t>
   </si>
   <si>
     <t xml:space="preserve">16.2012023925781</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7298984527588</t>
+    <t xml:space="preserve">14.7298974990845</t>
   </si>
   <si>
     <t xml:space="preserve">14.4390096664429</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6287202835083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9828453063965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2830276489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3715591430664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4432249069214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.506462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2197904586792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6750926971436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5191097259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4811658859253</t>
+    <t xml:space="preserve">14.628719329834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9828443527222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2830257415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3715581893921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4432258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5064630508423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2197895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6750946044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5191087722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4811668395996</t>
   </si>
   <si>
     <t xml:space="preserve">14.2745952606201</t>
@@ -4253,16 +4253,16 @@
     <t xml:space="preserve">13.8277225494385</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289016723633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3724203109741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7771339416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1523370742798</t>
+    <t xml:space="preserve">13.9289026260376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3724212646484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7771348953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1523380279541</t>
   </si>
   <si>
     <t xml:space="preserve">14.3420476913452</t>
@@ -4274,10 +4274,10 @@
     <t xml:space="preserve">14.3546943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">14.198712348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.621150970459</t>
+    <t xml:space="preserve">14.1987104415894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6211519241333</t>
   </si>
   <si>
     <t xml:space="preserve">13.6801719665527</t>
@@ -4289,13 +4289,13 @@
     <t xml:space="preserve">14.2493000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6928186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.760272026062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7939977645874</t>
+    <t xml:space="preserve">13.6928195953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7602710723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7939987182617</t>
   </si>
   <si>
     <t xml:space="preserve">13.4609518051147</t>
@@ -4304,10 +4304,10 @@
     <t xml:space="preserve">13.5494823455811</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3631258010864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3926372528076</t>
+    <t xml:space="preserve">14.3631267547607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3926362991333</t>
   </si>
   <si>
     <t xml:space="preserve">14.1312589645386</t>
@@ -4328,22 +4328,22 @@
     <t xml:space="preserve">14.1944942474365</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4600877761841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5022459030151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.565484046936</t>
+    <t xml:space="preserve">14.4600887298584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5022468566895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5654821395874</t>
   </si>
   <si>
     <t xml:space="preserve">14.6371517181396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3757734298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643049240112</t>
+    <t xml:space="preserve">14.3757724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643058776855</t>
   </si>
   <si>
     <t xml:space="preserve">13.9794912338257</t>
@@ -4352,16 +4352,16 @@
     <t xml:space="preserve">13.7687034606934</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9541969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9415483474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8530187606812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4651679992676</t>
+    <t xml:space="preserve">13.9541959762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9415493011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8530178070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4651670455933</t>
   </si>
   <si>
     <t xml:space="preserve">13.4483041763306</t>
@@ -4370,22 +4370,22 @@
     <t xml:space="preserve">13.6380128860474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4356575012207</t>
+    <t xml:space="preserve">13.435658454895</t>
   </si>
   <si>
     <t xml:space="preserve">13.1447687149048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6295833587646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.427225112915</t>
+    <t xml:space="preserve">13.6295824050903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4272260665894</t>
   </si>
   <si>
     <t xml:space="preserve">13.4946775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5199718475342</t>
+    <t xml:space="preserve">13.5199728012085</t>
   </si>
   <si>
     <t xml:space="preserve">14.1692018508911</t>
@@ -4394,22 +4394,22 @@
     <t xml:space="preserve">14.0806703567505</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0722389221191</t>
+    <t xml:space="preserve">14.0722379684448</t>
   </si>
   <si>
     <t xml:space="preserve">13.9162540435791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7644882202148</t>
+    <t xml:space="preserve">13.7644872665405</t>
   </si>
   <si>
     <t xml:space="preserve">13.8572340011597</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4735994338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1321220397949</t>
+    <t xml:space="preserve">13.4735984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1321210861206</t>
   </si>
   <si>
     <t xml:space="preserve">12.7484865188599</t>
@@ -4421,13 +4421,13 @@
     <t xml:space="preserve">12.5334825515747</t>
   </si>
   <si>
-    <t xml:space="preserve">12.411226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0065116882324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3985767364502</t>
+    <t xml:space="preserve">12.4112253189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0065107345581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3985776901245</t>
   </si>
   <si>
     <t xml:space="preserve">12.6009340286255</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">12.7231922149658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5039720535278</t>
+    <t xml:space="preserve">12.5039710998535</t>
   </si>
   <si>
     <t xml:space="preserve">12.5503454208374</t>
@@ -4454,13 +4454,13 @@
     <t xml:space="preserve">11.7324857711792</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0908260345459</t>
+    <t xml:space="preserve">12.0908269882202</t>
   </si>
   <si>
     <t xml:space="preserve">12.5292663574219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7948598861694</t>
+    <t xml:space="preserve">12.7948608398438</t>
   </si>
   <si>
     <t xml:space="preserve">12.8791751861572</t>
@@ -4472,25 +4472,25 @@
     <t xml:space="preserve">12.8538808822632</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8960380554199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3007516860962</t>
+    <t xml:space="preserve">12.8960390090942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3007526397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.6843872070312</t>
   </si>
   <si>
-    <t xml:space="preserve">13.532618522644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7897815704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.743408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9963550567627</t>
+    <t xml:space="preserve">13.5326194763184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7897806167603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7434072494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9963541030884</t>
   </si>
   <si>
     <t xml:space="preserve">14.1101808547974</t>
@@ -4499,19 +4499,19 @@
     <t xml:space="preserve">14.3462619781494</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7214670181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9449043273926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0292186737061</t>
+    <t xml:space="preserve">14.7214660644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9449024200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0292177200317</t>
   </si>
   <si>
     <t xml:space="preserve">16.1885547637939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8588619232178</t>
+    <t xml:space="preserve">16.8588638305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.6860160827637</t>
@@ -4523,31 +4523,31 @@
     <t xml:space="preserve">16.8293514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.799840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3740463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4415016174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4035587310791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3909130096436</t>
+    <t xml:space="preserve">16.7998390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3740482330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.441499710083</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4035568237305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3909111022949</t>
   </si>
   <si>
     <t xml:space="preserve">16.1801242828369</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2349281311035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3993434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3023777008057</t>
+    <t xml:space="preserve">16.2349262237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3993453979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3023796081543</t>
   </si>
   <si>
     <t xml:space="preserve">16.6059150695801</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">16.5089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155246734619</t>
+    <t xml:space="preserve">16.7155265808105</t>
   </si>
   <si>
     <t xml:space="preserve">16.9389610290527</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">16.7618980407715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0570030212402</t>
+    <t xml:space="preserve">17.0570011138916</t>
   </si>
   <si>
     <t xml:space="preserve">16.9558258056641</t>
@@ -4580,10 +4580,10 @@
     <t xml:space="preserve">17.2677917480469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2593612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2340660095215</t>
+    <t xml:space="preserve">17.2593593597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2340641021729</t>
   </si>
   <si>
     <t xml:space="preserve">17.5375995635986</t>
@@ -4592,25 +4592,25 @@
     <t xml:space="preserve">17.3774013519287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4617156982422</t>
+    <t xml:space="preserve">17.4617176055908</t>
   </si>
   <si>
     <t xml:space="preserve">17.6893692016602</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7146625518799</t>
+    <t xml:space="preserve">17.7146644592285</t>
   </si>
   <si>
     <t xml:space="preserve">17.8579998016357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6472129821777</t>
+    <t xml:space="preserve">17.6472110748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.8664302825928</t>
   </si>
   <si>
-    <t xml:space="preserve">18.043493270874</t>
+    <t xml:space="preserve">18.0434913635254</t>
   </si>
   <si>
     <t xml:space="preserve">18.2542819976807</t>
@@ -4622,16 +4622,16 @@
     <t xml:space="preserve">17.9676074981689</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3807525634766</t>
+    <t xml:space="preserve">18.3807544708252</t>
   </si>
   <si>
     <t xml:space="preserve">18.3891849517822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8697834014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9035110473633</t>
+    <t xml:space="preserve">18.8697814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9035091400146</t>
   </si>
   <si>
     <t xml:space="preserve">18.9625301361084</t>
@@ -4646,10 +4646,10 @@
     <t xml:space="preserve">19.1648864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8444881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2239074707031</t>
+    <t xml:space="preserve">18.8444900512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2239093780518</t>
   </si>
   <si>
     <t xml:space="preserve">19.375675201416</t>
@@ -4664,13 +4664,13 @@
     <t xml:space="preserve">19.3841075897217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4431266784668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3250885009766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2913608551025</t>
+    <t xml:space="preserve">19.4431285858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3250865936279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2913589477539</t>
   </si>
   <si>
     <t xml:space="preserve">19.3166542053223</t>
@@ -4679,16 +4679,16 @@
     <t xml:space="preserve">19.8141174316406</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8984336853027</t>
+    <t xml:space="preserve">19.8984317779541</t>
   </si>
   <si>
     <t xml:space="preserve">19.9405899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9321575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8899993896484</t>
+    <t xml:space="preserve">19.9321556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8900012969971</t>
   </si>
   <si>
     <t xml:space="preserve">19.8309783935547</t>
@@ -4697,10 +4697,10 @@
     <t xml:space="preserve">19.1564540863037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5358753204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0637111663818</t>
+    <t xml:space="preserve">19.5358734130859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0637092590332</t>
   </si>
   <si>
     <t xml:space="preserve">19.0890026092529</t>
@@ -4721,46 +4721,46 @@
     <t xml:space="preserve">18.9456672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9793949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1058673858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8950786590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8023300170898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1952590942383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.6134853363037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7745456695557</t>
+    <t xml:space="preserve">18.9793930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1058654785156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.895076751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8023319244385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1952610015869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.6134834289551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7745475769043</t>
   </si>
   <si>
     <t xml:space="preserve">16.9811172485352</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2391452789307</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114936828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9052333831787</t>
+    <t xml:space="preserve">16.239143371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114917755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4667949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9052352905273</t>
   </si>
   <si>
     <t xml:space="preserve">16.3782634735107</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1126689910889</t>
+    <t xml:space="preserve">16.1126708984375</t>
   </si>
   <si>
     <t xml:space="preserve">16.1337490081787</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">16.3487529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.643856048584</t>
+    <t xml:space="preserve">16.6438579559326</t>
   </si>
   <si>
     <t xml:space="preserve">16.6101322174072</t>
@@ -4781,13 +4781,13 @@
     <t xml:space="preserve">16.3403205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.521598815918</t>
+    <t xml:space="preserve">16.5216007232666</t>
   </si>
   <si>
     <t xml:space="preserve">16.7113094329834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.158182144165</t>
+    <t xml:space="preserve">17.1581802368164</t>
   </si>
   <si>
     <t xml:space="preserve">17.124454498291</t>
@@ -4796,25 +4796,25 @@
     <t xml:space="preserve">17.0232772827148</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2003402709961</t>
+    <t xml:space="preserve">17.2003383636475</t>
   </si>
   <si>
     <t xml:space="preserve">17.2424983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.107593536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0148468017578</t>
+    <t xml:space="preserve">17.1075916290283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0148448944092</t>
   </si>
   <si>
     <t xml:space="preserve">17.0401401519775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0654335021973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8124904632568</t>
+    <t xml:space="preserve">17.0654354095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8124885559082</t>
   </si>
   <si>
     <t xml:space="preserve">16.5806217193604</t>
@@ -4826,7 +4826,7 @@
     <t xml:space="preserve">17.0822982788086</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8546466827393</t>
+    <t xml:space="preserve">16.8546447753906</t>
   </si>
   <si>
     <t xml:space="preserve">16.9895496368408</t>
@@ -4847,10 +4847,10 @@
     <t xml:space="preserve">17.3769779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0168323516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8097496032715</t>
+    <t xml:space="preserve">17.0168342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8097515106201</t>
   </si>
   <si>
     <t xml:space="preserve">17.2014083862305</t>
@@ -4859,28 +4859,28 @@
     <t xml:space="preserve">17.1743984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0753593444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7242164611816</t>
+    <t xml:space="preserve">17.0753574371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7242183685303</t>
   </si>
   <si>
     <t xml:space="preserve">17.0213356018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.412992477417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4580097198486</t>
+    <t xml:space="preserve">17.4129943847656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4580116271973</t>
   </si>
   <si>
     <t xml:space="preserve">17.647087097168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6425838470459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721771240234</t>
+    <t xml:space="preserve">17.6425857543945</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721790313721</t>
   </si>
   <si>
     <t xml:space="preserve">17.6020679473877</t>
@@ -4901,7 +4901,7 @@
     <t xml:space="preserve">18.0162353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8496685028076</t>
+    <t xml:space="preserve">17.8496704101562</t>
   </si>
   <si>
     <t xml:space="preserve">17.8136539459229</t>
@@ -4925,7 +4925,7 @@
     <t xml:space="preserve">17.4715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5750598907471</t>
+    <t xml:space="preserve">17.5750579833984</t>
   </si>
   <si>
     <t xml:space="preserve">17.786642074585</t>
@@ -4952,7 +4952,7 @@
     <t xml:space="preserve">17.8541698455811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9667167663574</t>
+    <t xml:space="preserve">17.9667148590088</t>
   </si>
   <si>
     <t xml:space="preserve">17.9036903381348</t>
@@ -4964,7 +4964,7 @@
     <t xml:space="preserve">18.1602935791016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2863426208496</t>
+    <t xml:space="preserve">18.2863445281982</t>
   </si>
   <si>
     <t xml:space="preserve">18.2323226928711</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">18.2413272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1783027648926</t>
+    <t xml:space="preserve">18.1783008575439</t>
   </si>
   <si>
     <t xml:space="preserve">18.2683372497559</t>
@@ -4994,7 +4994,7 @@
     <t xml:space="preserve">19.0066337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6284828186035</t>
+    <t xml:space="preserve">18.6284809112549</t>
   </si>
   <si>
     <t xml:space="preserve">18.6014709472656</t>
@@ -5006,13 +5006,13 @@
     <t xml:space="preserve">18.6104755401611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7005100250244</t>
+    <t xml:space="preserve">18.700511932373</t>
   </si>
   <si>
     <t xml:space="preserve">18.7365245819092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8895854949951</t>
+    <t xml:space="preserve">18.8895874023438</t>
   </si>
   <si>
     <t xml:space="preserve">18.7545318603516</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">18.8715782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5924682617188</t>
+    <t xml:space="preserve">18.5924663543701</t>
   </si>
   <si>
     <t xml:space="preserve">18.3403663635254</t>
@@ -5036,10 +5036,10 @@
     <t xml:space="preserve">18.5114345550537</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0426483154297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1326847076416</t>
+    <t xml:space="preserve">19.0426464080811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.132682800293</t>
   </si>
   <si>
     <t xml:space="preserve">19.2497310638428</t>
@@ -5051,16 +5051,16 @@
     <t xml:space="preserve">19.1867046356201</t>
   </si>
   <si>
-    <t xml:space="preserve">19.08766746521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9346046447754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9706172943115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0516529083252</t>
+    <t xml:space="preserve">19.0876655578613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.934606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9706192016602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0516510009766</t>
   </si>
   <si>
     <t xml:space="preserve">19.0246410369873</t>
@@ -5075,31 +5075,31 @@
     <t xml:space="preserve">19.1957092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8625774383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7905464172363</t>
+    <t xml:space="preserve">18.8625755310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.790548324585</t>
   </si>
   <si>
     <t xml:space="preserve">18.7815437316895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.853572845459</t>
+    <t xml:space="preserve">18.8535709381104</t>
   </si>
   <si>
     <t xml:space="preserve">18.619478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">18.259334564209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493671417236</t>
+    <t xml:space="preserve">18.2593326568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3493690490723</t>
   </si>
   <si>
     <t xml:space="preserve">18.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3313617706299</t>
+    <t xml:space="preserve">18.3313636779785</t>
   </si>
   <si>
     <t xml:space="preserve">18.0702571868896</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">17.4670143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4805202484131</t>
+    <t xml:space="preserve">17.4805221557617</t>
   </si>
   <si>
     <t xml:space="preserve">17.6200752258301</t>
@@ -5129,13 +5129,13 @@
     <t xml:space="preserve">17.8991870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8901844024658</t>
+    <t xml:space="preserve">17.8901863098145</t>
   </si>
   <si>
     <t xml:space="preserve">18.1422863006592</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4304008483887</t>
+    <t xml:space="preserve">18.4304027557373</t>
   </si>
   <si>
     <t xml:space="preserve">18.4213981628418</t>
@@ -5150,10 +5150,10 @@
     <t xml:space="preserve">18.7725391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2047119140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4388065338135</t>
+    <t xml:space="preserve">19.2047138214111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4388084411621</t>
   </si>
   <si>
     <t xml:space="preserve">19.6278820037842</t>
@@ -5165,19 +5165,19 @@
     <t xml:space="preserve">20.0510520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9069938659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8439693450928</t>
+    <t xml:space="preserve">19.9069957733154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8439712524414</t>
   </si>
   <si>
     <t xml:space="preserve">19.7899475097656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8979911804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.807954788208</t>
+    <t xml:space="preserve">19.8979930877686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8079566955566</t>
   </si>
   <si>
     <t xml:space="preserve">19.6729011535645</t>
@@ -5186,7 +5186,7 @@
     <t xml:space="preserve">19.9520130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0960693359375</t>
+    <t xml:space="preserve">20.0960712432861</t>
   </si>
   <si>
     <t xml:space="preserve">20.0690612792969</t>
@@ -5204,7 +5204,7 @@
     <t xml:space="preserve">20.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5372467041016</t>
+    <t xml:space="preserve">20.5372486114502</t>
   </si>
   <si>
     <t xml:space="preserve">20.996431350708</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">21.2215213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2755451202393</t>
+    <t xml:space="preserve">21.2755432128906</t>
   </si>
   <si>
     <t xml:space="preserve">21.2935523986816</t>
@@ -5240,22 +5240,22 @@
     <t xml:space="preserve">21.7887516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9598197937012</t>
+    <t xml:space="preserve">21.9598178863525</t>
   </si>
   <si>
     <t xml:space="preserve">22.3199634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6717052459717</t>
+    <t xml:space="preserve">21.671703338623</t>
   </si>
   <si>
     <t xml:space="preserve">22.0948734283447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.265941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.4190044403076</t>
+    <t xml:space="preserve">22.2659435272217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.419002532959</t>
   </si>
   <si>
     <t xml:space="preserve">22.5090389251709</t>
@@ -5264,10 +5264,10 @@
     <t xml:space="preserve">22.5900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.5630626678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.9051990509033</t>
+    <t xml:space="preserve">22.563060760498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.905200958252</t>
   </si>
   <si>
     <t xml:space="preserve">22.797155380249</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">23.0762672424316</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0222473144531</t>
+    <t xml:space="preserve">23.0222454071045</t>
   </si>
   <si>
     <t xml:space="preserve">23.3103618621826</t>
@@ -5291,10 +5291,10 @@
     <t xml:space="preserve">23.3193645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2293300628662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4003963470459</t>
+    <t xml:space="preserve">23.2293281555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4003982543945</t>
   </si>
   <si>
     <t xml:space="preserve">23.2563400268555</t>
@@ -5303,7 +5303,7 @@
     <t xml:space="preserve">23.6705074310303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5894737243652</t>
+    <t xml:space="preserve">23.5894756317139</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264472961426</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">23.8865947723389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.706521987915</t>
+    <t xml:space="preserve">23.7065200805664</t>
   </si>
   <si>
     <t xml:space="preserve">23.6975173950195</t>
@@ -5363,7 +5363,7 @@
     <t xml:space="preserve">21.6987152099609</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9148025512695</t>
+    <t xml:space="preserve">21.9148006439209</t>
   </si>
   <si>
     <t xml:space="preserve">22.5720653533936</t>
@@ -5378,7 +5378,7 @@
     <t xml:space="preserve">22.3559799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3109607696533</t>
+    <t xml:space="preserve">22.310962677002</t>
   </si>
   <si>
     <t xml:space="preserve">22.1218852996826</t>
@@ -5387,19 +5387,19 @@
     <t xml:space="preserve">22.4550189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3289680480957</t>
+    <t xml:space="preserve">22.3289661407471</t>
   </si>
   <si>
     <t xml:space="preserve">22.6260871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.6711044311523</t>
+    <t xml:space="preserve">22.671106338501</t>
   </si>
   <si>
     <t xml:space="preserve">21.608678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7977523803711</t>
+    <t xml:space="preserve">21.7977542877197</t>
   </si>
   <si>
     <t xml:space="preserve">21.968822479248</t>
@@ -5417,22 +5417,22 @@
     <t xml:space="preserve">21.5996742248535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7257251739502</t>
+    <t xml:space="preserve">21.7257232666016</t>
   </si>
   <si>
     <t xml:space="preserve">21.7527370452881</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6176815032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8427715301514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2749462127686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1038780212402</t>
+    <t xml:space="preserve">21.6176834106445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8427734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2749443054199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1038761138916</t>
   </si>
   <si>
     <t xml:space="preserve">22.1578998565674</t>
@@ -5441,16 +5441,16 @@
     <t xml:space="preserve">22.2839488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3019561767578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2569370269775</t>
+    <t xml:space="preserve">22.3019580841064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2569389343262</t>
   </si>
   <si>
     <t xml:space="preserve">22.7341289520264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.950216293335</t>
+    <t xml:space="preserve">22.9502182006836</t>
   </si>
   <si>
     <t xml:space="preserve">23.1843109130859</t>
@@ -5462,13 +5462,13 @@
     <t xml:space="preserve">23.0672645568848</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4364147186279</t>
+    <t xml:space="preserve">23.4364128112793</t>
   </si>
   <si>
     <t xml:space="preserve">23.5084419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.84157371521</t>
+    <t xml:space="preserve">23.8415756225586</t>
   </si>
   <si>
     <t xml:space="preserve">23.5945644378662</t>
@@ -6369,6 +6369,9 @@
   </si>
   <si>
     <t xml:space="preserve">31.9200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.2799987792969</t>
   </si>
 </sst>
 </file>
@@ -71473,7 +71476,7 @@
     </row>
     <row r="2492">
       <c r="A2492" s="1" t="n">
-        <v>45947.6494560185</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2492" t="n">
         <v>702042</v>
@@ -71494,6 +71497,32 @@
         <v>2118</v>
       </c>
       <c r="H2492" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2493">
+      <c r="A2493" s="1" t="n">
+        <v>45950.6494328704</v>
+      </c>
+      <c r="B2493" t="n">
+        <v>477519</v>
+      </c>
+      <c r="C2493" t="n">
+        <v>32.3600006103516</v>
+      </c>
+      <c r="D2493" t="n">
+        <v>32.0299987792969</v>
+      </c>
+      <c r="E2493" t="n">
+        <v>32.2599983215332</v>
+      </c>
+      <c r="F2493" t="n">
+        <v>32.2799987792969</v>
+      </c>
+      <c r="G2493" t="s">
+        <v>2119</v>
+      </c>
+      <c r="H2493" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2122" uniqueCount="2122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="2123">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8295059204102</t>
+    <t xml:space="preserve">10.8295068740845</t>
   </si>
   <si>
     <t xml:space="preserve">AZM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4860258102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.191611289978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91191864013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93645286560059</t>
+    <t xml:space="preserve">10.7068338394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4860248565674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1916103363037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91191959381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9364538192749</t>
   </si>
   <si>
     <t xml:space="preserve">10.2259607315063</t>
   </si>
   <si>
-    <t xml:space="preserve">10.000244140625</t>
+    <t xml:space="preserve">10.0002431869507</t>
   </si>
   <si>
     <t xml:space="preserve">9.617506980896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33290672302246</t>
+    <t xml:space="preserve">9.33290576934814</t>
   </si>
   <si>
     <t xml:space="preserve">9.1513500213623</t>
@@ -80,70 +80,70 @@
     <t xml:space="preserve">8.85693836212158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25930309295654</t>
+    <t xml:space="preserve">9.25930213928223</t>
   </si>
   <si>
     <t xml:space="preserve">9.53899574279785</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4899263381958</t>
+    <t xml:space="preserve">9.48992824554443</t>
   </si>
   <si>
     <t xml:space="preserve">9.50955390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40160369873047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12681770324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49483394622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43595123291016</t>
+    <t xml:space="preserve">9.40160179138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12681674957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49483585357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43595027923584</t>
   </si>
   <si>
     <t xml:space="preserve">8.84712409973145</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99433040618896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79805564880371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05711555480957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86574697494507</t>
+    <t xml:space="preserve">8.99433135986328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79805374145508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05711460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86574554443359</t>
   </si>
   <si>
     <t xml:space="preserve">8.32699394226074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61058712005615</t>
+    <t xml:space="preserve">7.61058807373047</t>
   </si>
   <si>
     <t xml:space="preserve">7.67928409576416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10127544403076</t>
+    <t xml:space="preserve">8.10127639770508</t>
   </si>
   <si>
     <t xml:space="preserve">7.8706521987915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53798961639404</t>
+    <t xml:space="preserve">8.53799057006836</t>
   </si>
   <si>
     <t xml:space="preserve">8.78333377838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61649799346924</t>
+    <t xml:space="preserve">8.46929359436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61649990081787</t>
   </si>
   <si>
     <t xml:space="preserve">8.50364112854004</t>
@@ -155,37 +155,37 @@
     <t xml:space="preserve">8.69010353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71954536437988</t>
+    <t xml:space="preserve">8.71954441070557</t>
   </si>
   <si>
     <t xml:space="preserve">9.29365158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30837249755859</t>
+    <t xml:space="preserve">9.30837154388428</t>
   </si>
   <si>
     <t xml:space="preserve">9.47520637512207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09737586975098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22004985809326</t>
+    <t xml:space="preserve">9.09737396240234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22004795074463</t>
   </si>
   <si>
     <t xml:space="preserve">9.41141700744629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48011302947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77943420410156</t>
+    <t xml:space="preserve">9.4801139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77943325042725</t>
   </si>
   <si>
     <t xml:space="preserve">9.6616678237915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79415225982666</t>
+    <t xml:space="preserve">9.79415416717529</t>
   </si>
   <si>
     <t xml:space="preserve">9.77452754974365</t>
@@ -197,79 +197,79 @@
     <t xml:space="preserve">9.64694690704346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72545909881592</t>
+    <t xml:space="preserve">9.72545719146729</t>
   </si>
   <si>
     <t xml:space="preserve">10.2357740402222</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3044710159302</t>
+    <t xml:space="preserve">10.3044700622559</t>
   </si>
   <si>
     <t xml:space="preserve">9.8383150100708</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56843566894531</t>
+    <t xml:space="preserve">9.56843757629395</t>
   </si>
   <si>
     <t xml:space="preserve">9.98552322387695</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93154525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74508476257324</t>
+    <t xml:space="preserve">9.93154621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74508571624756</t>
   </si>
   <si>
     <t xml:space="preserve">10.3780736923218</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5449085235596</t>
+    <t xml:space="preserve">10.5449075698853</t>
   </si>
   <si>
     <t xml:space="preserve">10.4369564056396</t>
   </si>
   <si>
-    <t xml:space="preserve">10.554723739624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5056524276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5498142242432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5007457733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5694427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.417329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4811191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7411832809448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8442268371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7853469848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5988836288452</t>
+    <t xml:space="preserve">10.5547227859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5056533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5498161315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5007467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5694417953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173288345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4811172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7411851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8442277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7853441238403</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5988845825195</t>
   </si>
   <si>
     <t xml:space="preserve">10.2406816482544</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2897481918335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73036575317383</t>
+    <t xml:space="preserve">10.2897491455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73036479949951</t>
   </si>
   <si>
     <t xml:space="preserve">9.57334327697754</t>
@@ -281,22 +281,22 @@
     <t xml:space="preserve">9.40650939941406</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19060516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08265590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35253238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47030067443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27892971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30346393585205</t>
+    <t xml:space="preserve">9.19060611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08265495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3525333404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47029876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2789306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30346298217773</t>
   </si>
   <si>
     <t xml:space="preserve">9.14644432067871</t>
@@ -308,22 +308,22 @@
     <t xml:space="preserve">9.79665470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1190128326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89235496520996</t>
+    <t xml:space="preserve">10.1190137863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89235401153564</t>
   </si>
   <si>
     <t xml:space="preserve">9.95279598236084</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1492309570312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84702205657959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76643371582031</t>
+    <t xml:space="preserve">10.1492328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84702301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76643466949463</t>
   </si>
   <si>
     <t xml:space="preserve">9.42896366119385</t>
@@ -335,46 +335,46 @@
     <t xml:space="preserve">9.52466487884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54984951019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39370632171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82958126068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48203754425049</t>
+    <t xml:space="preserve">9.54984760284424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39370536804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82957935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4820384979248</t>
   </si>
   <si>
     <t xml:space="preserve">8.28560161590576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46189117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53744316101074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68351364135742</t>
+    <t xml:space="preserve">8.46189212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53744411468506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68351268768311</t>
   </si>
   <si>
     <t xml:space="preserve">9.39874267578125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50451850891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81680011749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46459722518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540655136108</t>
+    <t xml:space="preserve">9.50451755523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81680107116699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46459770202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540845870972</t>
   </si>
   <si>
     <t xml:space="preserve">7.49985599517822</t>
@@ -383,40 +383,40 @@
     <t xml:space="preserve">7.34874963760376</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43941211700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20268106460571</t>
+    <t xml:space="preserve">7.43941307067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20268154144287</t>
   </si>
   <si>
     <t xml:space="preserve">6.8702507019043</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50256109237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62848091125488</t>
+    <t xml:space="preserve">6.50256061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62848138809204</t>
   </si>
   <si>
     <t xml:space="preserve">6.86017608642578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02135562896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38904476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20771837234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44948577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66607093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5250391960144</t>
+    <t xml:space="preserve">7.02135515213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38904523849487</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20771789550781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44948673248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66607141494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52503967285156</t>
   </si>
   <si>
     <t xml:space="preserve">7.64592409133911</t>
@@ -428,103 +428,103 @@
     <t xml:space="preserve">7.71140289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94309616088867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81717586517334</t>
+    <t xml:space="preserve">7.94309711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81717491149902</t>
   </si>
   <si>
     <t xml:space="preserve">7.94813394546509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08179807662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92565536499023</t>
+    <t xml:space="preserve">7.08179759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92565584182739</t>
   </si>
   <si>
     <t xml:space="preserve">6.71410799026489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.78966093063354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90047073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22786712646484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27823400497437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32860279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.318528175354</t>
+    <t xml:space="preserve">6.78966045379639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90047168731689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22786569595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27823305130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32860231399536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31852912902832</t>
   </si>
   <si>
     <t xml:space="preserve">7.39911842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15734958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94580268859863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80477142333984</t>
+    <t xml:space="preserve">7.15734910964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94580316543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80476999282837</t>
   </si>
   <si>
     <t xml:space="preserve">7.02639102935791</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08683395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04150342941284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85010242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86521482467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069219589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22282886505127</t>
+    <t xml:space="preserve">7.0868353843689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85010290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86521291732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069171905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22282934188843</t>
   </si>
   <si>
     <t xml:space="preserve">7.31349229812622</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23290300369263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29838228225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98106098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01128196716309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53781890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79973411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68388605117798</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73929214477539</t>
+    <t xml:space="preserve">7.23290157318115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29838180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98106050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01128244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53781938552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79973363876343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68388652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73929309844971</t>
   </si>
   <si>
     <t xml:space="preserve">6.94076585769653</t>
@@ -536,19 +536,19 @@
     <t xml:space="preserve">6.66877698898315</t>
   </si>
   <si>
-    <t xml:space="preserve">6.4622654914856</t>
+    <t xml:space="preserve">6.46226644515991</t>
   </si>
   <si>
     <t xml:space="preserve">6.57307720184326</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67381381988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59825944900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87528800964355</t>
+    <t xml:space="preserve">6.6738133430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5982608795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8752875328064</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624418258667</t>
@@ -557,151 +557,151 @@
     <t xml:space="preserve">7.15231227874756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30341958999634</t>
+    <t xml:space="preserve">7.30341863632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.6257758140564</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66103267669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57037019729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45452308654785</t>
+    <t xml:space="preserve">7.66103363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57037162780762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45452356338501</t>
   </si>
   <si>
     <t xml:space="preserve">7.5351128578186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59555530548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72147655487061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60562896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70636606216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48474359512329</t>
+    <t xml:space="preserve">7.44444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5955548286438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72147560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.605628490448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70636510848999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48474502563477</t>
   </si>
   <si>
     <t xml:space="preserve">7.36386060714722</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26312351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13216590881348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617195129395</t>
+    <t xml:space="preserve">7.26312398910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13216543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617147445679</t>
   </si>
   <si>
     <t xml:space="preserve">7.17246103286743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69629192352295</t>
+    <t xml:space="preserve">7.69629240036011</t>
   </si>
   <si>
     <t xml:space="preserve">7.91791343688965</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35611820220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3863410949707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51729774475098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45181751251221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20501232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04887104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95820808410645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93132257461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71623706817627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73236751556396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63557767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64095449447632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45813179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44200038909912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57105255126953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68934869766235</t>
+    <t xml:space="preserve">8.35611724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38633918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51729679107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45181846618652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20501327514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04887008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9582085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93132209777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71623563766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73236846923828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63557720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64095497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45813226699829</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44199991226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57105112075806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68935012817383</t>
   </si>
   <si>
     <t xml:space="preserve">7.62482309341431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79689455032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.2001781463623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43139839172363</t>
+    <t xml:space="preserve">7.79689359664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20018100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43140029907227</t>
   </si>
   <si>
     <t xml:space="preserve">8.61959934234619</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54431819915771</t>
+    <t xml:space="preserve">8.54431915283203</t>
   </si>
   <si>
     <t xml:space="preserve">8.46903896331787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58733654022217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70025825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54969692230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6034688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53356456756592</t>
+    <t xml:space="preserve">8.5873384475708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70025730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54969596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60346794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53356552124023</t>
   </si>
   <si>
     <t xml:space="preserve">8.5980920791626</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51743412017822</t>
+    <t xml:space="preserve">8.51743316650391</t>
   </si>
   <si>
     <t xml:space="preserve">8.52818775177002</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">8.67874908447266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11429786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15731620788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2003345489502</t>
+    <t xml:space="preserve">9.11429882049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15731525421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20033359527588</t>
   </si>
   <si>
     <t xml:space="preserve">9.17882442474365</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05515003204346</t>
+    <t xml:space="preserve">9.05514907836914</t>
   </si>
   <si>
     <t xml:space="preserve">9.3347635269165</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">9.38315773010254</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41004276275635</t>
+    <t xml:space="preserve">9.41004371643066</t>
   </si>
   <si>
     <t xml:space="preserve">9.4584379196167</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45306015014648</t>
+    <t xml:space="preserve">9.4530611038208</t>
   </si>
   <si>
     <t xml:space="preserve">9.37240219116211</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">9.23797416687012</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32938575744629</t>
+    <t xml:space="preserve">9.32938480377197</t>
   </si>
   <si>
     <t xml:space="preserve">9.46919250488281</t>
@@ -761,31 +761,31 @@
     <t xml:space="preserve">9.44230461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92609882354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0927906036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07128238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76478290557861</t>
+    <t xml:space="preserve">8.92609977722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09279155731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0712833404541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7647819519043</t>
   </si>
   <si>
     <t xml:space="preserve">9.16807079315186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25948238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28636932373047</t>
+    <t xml:space="preserve">9.25948143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28637027740479</t>
   </si>
   <si>
     <t xml:space="preserve">9.24335098266602</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26486015319824</t>
+    <t xml:space="preserve">9.26485919952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.2325963973999</t>
@@ -800,22 +800,22 @@
     <t xml:space="preserve">8.495924949646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59271335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5228099822998</t>
+    <t xml:space="preserve">8.59271240234375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52280902862549</t>
   </si>
   <si>
     <t xml:space="preserve">8.66799449920654</t>
   </si>
   <si>
-    <t xml:space="preserve">8.7378978729248</t>
+    <t xml:space="preserve">8.73789596557617</t>
   </si>
   <si>
     <t xml:space="preserve">8.71101188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70563411712646</t>
+    <t xml:space="preserve">8.70563507080078</t>
   </si>
   <si>
     <t xml:space="preserve">8.63573169708252</t>
@@ -824,19 +824,19 @@
     <t xml:space="preserve">8.53894138336182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50130176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28621482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33460807800293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43677711486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47441577911377</t>
+    <t xml:space="preserve">8.50130271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28621578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33460998535156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43677616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47441673278809</t>
   </si>
   <si>
     <t xml:space="preserve">8.62497615814209</t>
@@ -845,13 +845,13 @@
     <t xml:space="preserve">8.56582832336426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47979259490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66261672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61422252655029</t>
+    <t xml:space="preserve">8.47979354858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66261768341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61422157287598</t>
   </si>
   <si>
     <t xml:space="preserve">8.78091526031494</t>
@@ -863,64 +863,64 @@
     <t xml:space="preserve">8.79166889190674</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18420314788818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04977226257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14118576049805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16269397735596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30250072479248</t>
+    <t xml:space="preserve">9.18420219421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04977321624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14118671417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16269302368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3025016784668</t>
   </si>
   <si>
     <t xml:space="preserve">9.13580799102783</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14656162261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20571136474609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62513160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63050556182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60899829864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63588523864746</t>
+    <t xml:space="preserve">9.14656257629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20571041107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62513065338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63050651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6089973449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63588428497314</t>
   </si>
   <si>
     <t xml:space="preserve">9.7165412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97464752197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0553035736084</t>
+    <t xml:space="preserve">9.97464656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0553045272827</t>
   </si>
   <si>
     <t xml:space="preserve">10.2435035705566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4155731201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3456697463989</t>
+    <t xml:space="preserve">10.4155740737915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3456707000732</t>
   </si>
   <si>
     <t xml:space="preserve">10.2327508926392</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3994426727295</t>
+    <t xml:space="preserve">10.3994436264038</t>
   </si>
   <si>
     <t xml:space="preserve">10.4101963043213</t>
@@ -929,13 +929,13 @@
     <t xml:space="preserve">10.3349161148071</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1305847167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3295373916626</t>
+    <t xml:space="preserve">10.1305837631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036996841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3295383453369</t>
   </si>
   <si>
     <t xml:space="preserve">10.425971031189</t>
@@ -950,37 +950,37 @@
     <t xml:space="preserve">10.5847988128662</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4770231246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2387809753418</t>
+    <t xml:space="preserve">10.4770221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2387800216675</t>
   </si>
   <si>
     <t xml:space="preserve">10.2728157043457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3408851623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2160921096802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0856246948242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90410614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2898330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2614698410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083145141602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0062103271484</t>
+    <t xml:space="preserve">10.3408842086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2160902023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0856237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9041051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898321151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2614707946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083116531372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0062093734741</t>
   </si>
   <si>
     <t xml:space="preserve">9.94381237030029</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">10.1707105636597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1366748809814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0629348754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1990718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3522272109985</t>
+    <t xml:space="preserve">10.1366758346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.062933921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1990728378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3522281646729</t>
   </si>
   <si>
     <t xml:space="preserve">10.2104167938232</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">9.95515823364258</t>
   </si>
   <si>
-    <t xml:space="preserve">10.148021697998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2444515228271</t>
+    <t xml:space="preserve">10.1480207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2444524765015</t>
   </si>
   <si>
     <t xml:space="preserve">10.2841596603394</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2217626571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0912971496582</t>
+    <t xml:space="preserve">10.2217636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0912981033325</t>
   </si>
   <si>
     <t xml:space="preserve">10.1593647003174</t>
@@ -1043,13 +1043,13 @@
     <t xml:space="preserve">10.3692464828491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4316444396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.397608757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7152662277222</t>
+    <t xml:space="preserve">10.4316434860229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3976078033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7152671813965</t>
   </si>
   <si>
     <t xml:space="preserve">10.641526222229</t>
@@ -1058,34 +1058,34 @@
     <t xml:space="preserve">10.7436294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7209367752075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.669885635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.777663230896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7039203643799</t>
+    <t xml:space="preserve">10.7209377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6698875427246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7776641845703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7039213180542</t>
   </si>
   <si>
     <t xml:space="preserve">10.6585426330566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.539421081543</t>
+    <t xml:space="preserve">10.5394201278687</t>
   </si>
   <si>
     <t xml:space="preserve">10.3068513870239</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7095947265625</t>
+    <t xml:space="preserve">10.7095937728882</t>
   </si>
   <si>
     <t xml:space="preserve">10.5564365386963</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4826955795288</t>
+    <t xml:space="preserve">10.4826946258545</t>
   </si>
   <si>
     <t xml:space="preserve">10.3352117538452</t>
@@ -1094,10 +1094,10 @@
     <t xml:space="preserve">10.2331085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2784862518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0289001464844</t>
+    <t xml:space="preserve">10.2784872055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0288991928101</t>
   </si>
   <si>
     <t xml:space="preserve">10.0402450561523</t>
@@ -1106,7 +1106,7 @@
     <t xml:space="preserve">10.0969696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.034571647644</t>
+    <t xml:space="preserve">10.0345706939697</t>
   </si>
   <si>
     <t xml:space="preserve">9.98351955413818</t>
@@ -1115,76 +1115,76 @@
     <t xml:space="preserve">9.96082878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98919296264648</t>
+    <t xml:space="preserve">9.98919200897217</t>
   </si>
   <si>
     <t xml:space="preserve">10.2274351119995</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2557964324951</t>
+    <t xml:space="preserve">10.2557973861694</t>
   </si>
   <si>
     <t xml:space="preserve">10.4940395355225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5110569000244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4146280288696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3295383453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3635740280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3805923461914</t>
+    <t xml:space="preserve">10.511058807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4146270751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3295392990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3635730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3805932998657</t>
   </si>
   <si>
     <t xml:space="preserve">10.4600057601929</t>
   </si>
   <si>
-    <t xml:space="preserve">10.516731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3465566635132</t>
+    <t xml:space="preserve">10.5167303085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3465576171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.84738159179688</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86439800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72825908660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67720699310303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66018962860107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48434352874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68855285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58644771575928</t>
+    <t xml:space="preserve">9.8643970489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7282600402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67720794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66018867492676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48434448242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.688551902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58644866943359</t>
   </si>
   <si>
     <t xml:space="preserve">9.71124076843262</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67153453826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6148099899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62048244476318</t>
+    <t xml:space="preserve">9.67153549194336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61480903625488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62048149108887</t>
   </si>
   <si>
     <t xml:space="preserve">9.73393058776855</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">9.78498458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7963285446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89843273162842</t>
+    <t xml:space="preserve">9.79632949829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89843368530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.16101360321045</t>
@@ -1208,13 +1208,13 @@
     <t xml:space="preserve">8.99083995819092</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76961421966553</t>
+    <t xml:space="preserve">8.76961326599121</t>
   </si>
   <si>
     <t xml:space="preserve">8.75259780883789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86604404449463</t>
+    <t xml:space="preserve">8.86604499816895</t>
   </si>
   <si>
     <t xml:space="preserve">8.85470104217529</t>
@@ -1223,7 +1223,7 @@
     <t xml:space="preserve">9.05891036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24042797088623</t>
+    <t xml:space="preserve">9.24042701721191</t>
   </si>
   <si>
     <t xml:space="preserve">9.2517728805542</t>
@@ -1235,7 +1235,7 @@
     <t xml:space="preserve">9.09294414520264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98516845703125</t>
+    <t xml:space="preserve">8.98516654968262</t>
   </si>
   <si>
     <t xml:space="preserve">9.07592678070068</t>
@@ -1250,10 +1250,10 @@
     <t xml:space="preserve">8.90008068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8830623626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82633876800537</t>
+    <t xml:space="preserve">8.88306331634521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82633972167969</t>
   </si>
   <si>
     <t xml:space="preserve">8.79230403900146</t>
@@ -1268,13 +1268,13 @@
     <t xml:space="preserve">9.00218486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07025623321533</t>
+    <t xml:space="preserve">9.0702543258667</t>
   </si>
   <si>
     <t xml:space="preserve">8.9965124130249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01920127868652</t>
+    <t xml:space="preserve">9.01920223236084</t>
   </si>
   <si>
     <t xml:space="preserve">8.92277050018311</t>
@@ -1283,58 +1283,58 @@
     <t xml:space="preserve">9.04189205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03054714202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01352977752686</t>
+    <t xml:space="preserve">9.03054618835449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01353073120117</t>
   </si>
   <si>
     <t xml:space="preserve">9.04756450653076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03622055053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13832473754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97382164001465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12697982788086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16668701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19504833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37089538574219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38223934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34253120422363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46732616424561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6755599975586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.420298576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3919363021851</t>
+    <t xml:space="preserve">9.03621959686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13832378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97382354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12697887420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16668605804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19504928588867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37089347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34253215789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46732521057129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6755590438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3919353485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.5961446762085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7549734115601</t>
+    <t xml:space="preserve">10.7549724578857</t>
   </si>
   <si>
     <t xml:space="preserve">10.7379550933838</t>
@@ -1346,37 +1346,37 @@
     <t xml:space="preserve">10.6613779067993</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4543333053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032821655273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4429883956909</t>
+    <t xml:space="preserve">10.4543323516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032831192017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4429874420166</t>
   </si>
   <si>
     <t xml:space="preserve">10.3777561187744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0742797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1338396072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0941314697266</t>
+    <t xml:space="preserve">10.0742788314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1338405609131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0941333770752</t>
   </si>
   <si>
     <t xml:space="preserve">9.98635673522949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1565284729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962366104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2359437942505</t>
+    <t xml:space="preserve">10.1565294265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2359447479248</t>
   </si>
   <si>
     <t xml:space="preserve">10.1622018814087</t>
@@ -1388,10 +1388,10 @@
     <t xml:space="preserve">10.2501249313354</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2132539749146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1678733825684</t>
+    <t xml:space="preserve">10.2132530212402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1678743362427</t>
   </si>
   <si>
     <t xml:space="preserve">9.90694046020508</t>
@@ -1400,13 +1400,13 @@
     <t xml:space="preserve">9.92963027954102</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877269744873</t>
+    <t xml:space="preserve">10.1877279281616</t>
   </si>
   <si>
     <t xml:space="preserve">10.2302713394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0203905105591</t>
+    <t xml:space="preserve">10.0203895568848</t>
   </si>
   <si>
     <t xml:space="preserve">10.1905641555786</t>
@@ -1421,19 +1421,19 @@
     <t xml:space="preserve">9.9778470993042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81618309020996</t>
+    <t xml:space="preserve">9.81618213653564</t>
   </si>
   <si>
     <t xml:space="preserve">9.88708686828613</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89559555053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81334590911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97500991821289</t>
+    <t xml:space="preserve">9.89559745788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81334686279297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97501087188721</t>
   </si>
   <si>
     <t xml:space="preserve">10.065770149231</t>
@@ -1442,10 +1442,10 @@
     <t xml:space="preserve">10.1395111083984</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0005369186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686054229736</t>
+    <t xml:space="preserve">10.0005359649658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686063766479</t>
   </si>
   <si>
     <t xml:space="preserve">9.73676776885986</t>
@@ -1457,28 +1457,28 @@
     <t xml:space="preserve">9.89276027679443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.86723518371582</t>
+    <t xml:space="preserve">9.86723613739014</t>
   </si>
   <si>
     <t xml:space="preserve">9.8275260925293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77931213378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8331995010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94948577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93814086914062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71407699584961</t>
+    <t xml:space="preserve">9.77931118011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83319854736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94948387145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714426040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93814182281494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71407794952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.42761898040771</t>
@@ -1487,22 +1487,22 @@
     <t xml:space="preserve">9.10145282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21773815155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12414264678955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24326419830322</t>
+    <t xml:space="preserve">9.21773719787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12414360046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24326515197754</t>
   </si>
   <si>
     <t xml:space="preserve">9.20072174072266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.29274559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51369762420654</t>
+    <t xml:space="preserve">9.29274463653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51369667053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.39841747283936</t>
@@ -1511,37 +1511,37 @@
     <t xml:space="preserve">9.47206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44004726409912</t>
+    <t xml:space="preserve">9.4400463104248</t>
   </si>
   <si>
     <t xml:space="preserve">9.3375768661499</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98533630371094</t>
+    <t xml:space="preserve">8.98533535003662</t>
   </si>
   <si>
     <t xml:space="preserve">9.02696418762207</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89887523651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34397983551025</t>
+    <t xml:space="preserve">8.89887619018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34398078918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.31836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93730354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92129039764404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93410110473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64590454101562</t>
+    <t xml:space="preserve">8.9373025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92129135131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93410015106201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64590358734131</t>
   </si>
   <si>
     <t xml:space="preserve">8.83803462982178</t>
@@ -1550,19 +1550,19 @@
     <t xml:space="preserve">8.7547779083252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72275638580322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71635150909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64270114898682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82842922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80601215362549</t>
+    <t xml:space="preserve">8.72275733947754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71635246276855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64270210266113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8284273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8060131072998</t>
   </si>
   <si>
     <t xml:space="preserve">8.83163070678711</t>
@@ -1577,10 +1577,10 @@
     <t xml:space="preserve">8.51781558990479</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48899745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56905078887939</t>
+    <t xml:space="preserve">8.4889965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56905174255371</t>
   </si>
   <si>
     <t xml:space="preserve">8.45697593688965</t>
@@ -1592,7 +1592,7 @@
     <t xml:space="preserve">8.51141166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53062629699707</t>
+    <t xml:space="preserve">8.53062534332275</t>
   </si>
   <si>
     <t xml:space="preserve">8.53703022003174</t>
@@ -1601,46 +1601,46 @@
     <t xml:space="preserve">8.54343414306641</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71315002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40573978424072</t>
+    <t xml:space="preserve">8.71314907073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40573883056641</t>
   </si>
   <si>
     <t xml:space="preserve">8.36411190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33209037780762</t>
+    <t xml:space="preserve">8.3320894241333</t>
   </si>
   <si>
     <t xml:space="preserve">8.42175197601318</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58506107330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5722541809082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46017742156982</t>
+    <t xml:space="preserve">8.58506202697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.57225322723389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46017646789551</t>
   </si>
   <si>
     <t xml:space="preserve">8.46658134460449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58186054229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4409646987915</t>
+    <t xml:space="preserve">8.58185958862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44096374511719</t>
   </si>
   <si>
     <t xml:space="preserve">9.09421062469482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01735877990723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05578327178955</t>
+    <t xml:space="preserve">9.01735782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05578231811523</t>
   </si>
   <si>
     <t xml:space="preserve">9.1998815536499</t>
@@ -1649,16 +1649,16 @@
     <t xml:space="preserve">9.18707370758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91808986663818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87646293640137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03657054901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18387222290039</t>
+    <t xml:space="preserve">8.9180908203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87646198272705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03657150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18387031555176</t>
   </si>
   <si>
     <t xml:space="preserve">9.15505218505859</t>
@@ -1667,70 +1667,70 @@
     <t xml:space="preserve">9.15184879302979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23510646820068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16465950012207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12623310089111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26072216033936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.254319190979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20628643035889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20948886871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22549915313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10701942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92769718170166</t>
+    <t xml:space="preserve">9.23510551452637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16465759277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1262321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26072311401367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25432014465332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2062873840332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2094898223877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22550010681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10701847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92769622802734</t>
   </si>
   <si>
     <t xml:space="preserve">8.76758670806885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65871238708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68112850189209</t>
+    <t xml:space="preserve">8.65871334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68112754821777</t>
   </si>
   <si>
     <t xml:space="preserve">8.72595882415771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61708450317383</t>
+    <t xml:space="preserve">8.61708354949951</t>
   </si>
   <si>
     <t xml:space="preserve">8.7803955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82202529907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77719402313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78359699249268</t>
+    <t xml:space="preserve">8.82202434539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77719306945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78359794616699</t>
   </si>
   <si>
     <t xml:space="preserve">8.95331382751465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97252655029297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9661226272583</t>
+    <t xml:space="preserve">8.97252750396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96612358093262</t>
   </si>
   <si>
     <t xml:space="preserve">8.86685466766357</t>
@@ -1739,37 +1739,37 @@
     <t xml:space="preserve">8.86045074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32568550109863</t>
+    <t xml:space="preserve">8.32568359375</t>
   </si>
   <si>
     <t xml:space="preserve">8.22321510314941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29366397857666</t>
+    <t xml:space="preserve">8.29366302490234</t>
   </si>
   <si>
     <t xml:space="preserve">8.53382682800293</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48259162902832</t>
+    <t xml:space="preserve">8.48259353637695</t>
   </si>
   <si>
     <t xml:space="preserve">8.40253734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14956569671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06630802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07271194458008</t>
+    <t xml:space="preserve">8.14956474304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06630706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07271289825439</t>
   </si>
   <si>
     <t xml:space="preserve">7.77490901947021</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74929141998291</t>
+    <t xml:space="preserve">7.74929189682007</t>
   </si>
   <si>
     <t xml:space="preserve">7.67884302139282</t>
@@ -1778,130 +1778,130 @@
     <t xml:space="preserve">7.87417602539062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73007917404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53474521636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42266941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25295257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21772909164429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08003616333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11205530166626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84947681427002</t>
+    <t xml:space="preserve">7.73007869720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53474473953247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42266988754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25295305252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21772861480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08003520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11205625534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84947729110718</t>
   </si>
   <si>
     <t xml:space="preserve">6.97115993499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04160785675049</t>
+    <t xml:space="preserve">7.0416088104248</t>
   </si>
   <si>
     <t xml:space="preserve">7.03520441055298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04801225662231</t>
+    <t xml:space="preserve">7.04801273345947</t>
   </si>
   <si>
     <t xml:space="preserve">6.94234085083008</t>
   </si>
   <si>
-    <t xml:space="preserve">6.9519476890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00958633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1312689781189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97436141967773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83026361465454</t>
+    <t xml:space="preserve">6.95194578170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00958585739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13126850128174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97436189651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83026456832886</t>
   </si>
   <si>
     <t xml:space="preserve">6.95515012741089</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80144453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76622104644775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85908317565918</t>
+    <t xml:space="preserve">6.80144500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7662205696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8590841293335</t>
   </si>
   <si>
     <t xml:space="preserve">6.62852573394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70537900924683</t>
+    <t xml:space="preserve">6.70537805557251</t>
   </si>
   <si>
     <t xml:space="preserve">6.74700736999512</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86548805236816</t>
+    <t xml:space="preserve">6.86548852920532</t>
   </si>
   <si>
     <t xml:space="preserve">7.16329193115234</t>
   </si>
   <si>
-    <t xml:space="preserve">7.09604549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06722640991211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02239465713501</t>
+    <t xml:space="preserve">7.09604501724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06722497940063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02239513397217</t>
   </si>
   <si>
     <t xml:space="preserve">7.23053693771362</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05761909484863</t>
+    <t xml:space="preserve">7.05761957168579</t>
   </si>
   <si>
     <t xml:space="preserve">6.80464601516724</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89110422134399</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71818733215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73740148544312</t>
+    <t xml:space="preserve">6.89110612869263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71818780899048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7374005317688</t>
   </si>
   <si>
     <t xml:space="preserve">6.95835161209106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01278924942017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88790369033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45881032943726</t>
+    <t xml:space="preserve">7.01278829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88790273666382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45881080627441</t>
   </si>
   <si>
     <t xml:space="preserve">6.39796924591064</t>
   </si>
   <si>
-    <t xml:space="preserve">6.1520414352417</t>
+    <t xml:space="preserve">6.15204191207886</t>
   </si>
   <si>
     <t xml:space="preserve">6.15844488143921</t>
@@ -1910,7 +1910,7 @@
     <t xml:space="preserve">5.96375179290771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10592937469482</t>
+    <t xml:space="preserve">6.10592985153198</t>
   </si>
   <si>
     <t xml:space="preserve">6.10721063613892</t>
@@ -1919,7 +1919,7 @@
     <t xml:space="preserve">6.39925003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.64453649520874</t>
+    <t xml:space="preserve">6.6445369720459</t>
   </si>
   <si>
     <t xml:space="preserve">6.6317286491394</t>
@@ -1934,40 +1934,40 @@
     <t xml:space="preserve">6.60290861129761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.5965051651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41718101501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52285480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42038488388062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47802305221558</t>
+    <t xml:space="preserve">6.59650421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41718149185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52285528182983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4203839302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47802257537842</t>
   </si>
   <si>
     <t xml:space="preserve">6.4460015296936</t>
   </si>
   <si>
-    <t xml:space="preserve">6.3262414932251</t>
+    <t xml:space="preserve">6.32624053955078</t>
   </si>
   <si>
     <t xml:space="preserve">6.26732015609741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74380445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09924793243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30738973617554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19851589202881</t>
+    <t xml:space="preserve">6.74380493164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09924697875977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3073902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19851541519165</t>
   </si>
   <si>
     <t xml:space="preserve">7.08964157104492</t>
@@ -1976,82 +1976,82 @@
     <t xml:space="preserve">7.11846208572388</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15368556976318</t>
+    <t xml:space="preserve">7.15368509292603</t>
   </si>
   <si>
     <t xml:space="preserve">7.1568865776062</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17930269241333</t>
+    <t xml:space="preserve">7.17930221557617</t>
   </si>
   <si>
     <t xml:space="preserve">7.04481029510498</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99357509613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27216529846191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44828653335571</t>
+    <t xml:space="preserve">6.99357604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27216625213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44828605651855</t>
   </si>
   <si>
     <t xml:space="preserve">7.75889778137207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5763726234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72687578201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83895206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82614469528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8453574180603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8997950553894</t>
+    <t xml:space="preserve">7.57637357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72687530517578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83895111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82614374160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84535694122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89979600906372</t>
   </si>
   <si>
     <t xml:space="preserve">7.9126033782959</t>
   </si>
   <si>
-    <t xml:space="preserve">7.98305177688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88058090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91900777816772</t>
+    <t xml:space="preserve">7.98305130004883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88058185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91900730133057</t>
   </si>
   <si>
     <t xml:space="preserve">8.23282146453857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1207447052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26164054870605</t>
+    <t xml:space="preserve">8.12074661254883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26164150238037</t>
   </si>
   <si>
     <t xml:space="preserve">8.47298526763916</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46337890625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84764099121094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91168689727783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2639274597168</t>
+    <t xml:space="preserve">8.46337795257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84764194488525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9116849899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26392555236816</t>
   </si>
   <si>
     <t xml:space="preserve">9.33117198944092</t>
@@ -2063,22 +2063,22 @@
     <t xml:space="preserve">9.67700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51049327850342</t>
+    <t xml:space="preserve">9.51049423217773</t>
   </si>
   <si>
     <t xml:space="preserve">9.42083263397217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32796859741211</t>
+    <t xml:space="preserve">9.32796955108643</t>
   </si>
   <si>
     <t xml:space="preserve">9.40482330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47847366333008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55212306976318</t>
+    <t xml:space="preserve">9.47847175598145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55212211608887</t>
   </si>
   <si>
     <t xml:space="preserve">9.57133674621582</t>
@@ -2090,85 +2090,85 @@
     <t xml:space="preserve">9.77627658843994</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81470108032227</t>
+    <t xml:space="preserve">9.81470203399658</t>
   </si>
   <si>
     <t xml:space="preserve">10.0836868286133</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0356531143188</t>
+    <t xml:space="preserve">10.0356521606445</t>
   </si>
   <si>
     <t xml:space="preserve">10.1413240432739</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2149753570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.195761680603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2694120407104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2790193557739</t>
+    <t xml:space="preserve">10.2149744033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1957626342773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2694129943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2790184020996</t>
   </si>
   <si>
     <t xml:space="preserve">10.5608129501343</t>
   </si>
   <si>
-    <t xml:space="preserve">10.849009513855</t>
+    <t xml:space="preserve">10.8490085601807</t>
   </si>
   <si>
     <t xml:space="preserve">10.868221282959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.887433052063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0155220031738</t>
+    <t xml:space="preserve">10.8874340057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0155210494995</t>
   </si>
   <si>
     <t xml:space="preserve">11.0603513717651</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2813053131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2909097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5118608474731</t>
+    <t xml:space="preserve">11.281304359436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2909107208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5118598937988</t>
   </si>
   <si>
     <t xml:space="preserve">11.5278720855713</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4958505630493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.377368927002</t>
+    <t xml:space="preserve">11.495849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3773679733276</t>
   </si>
   <si>
     <t xml:space="preserve">11.3261337280273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4926481246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8105812072754</t>
+    <t xml:space="preserve">11.4926471710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8105821609497</t>
   </si>
   <si>
     <t xml:space="preserve">10.9899053573608</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5992383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219259262085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1404085159302</t>
+    <t xml:space="preserve">10.5992393493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219268798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1404075622559</t>
   </si>
   <si>
     <t xml:space="preserve">11.1141204833984</t>
@@ -2177,16 +2177,16 @@
     <t xml:space="preserve">10.7917680740356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7882642745972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4203634262085</t>
+    <t xml:space="preserve">10.7882652282715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4203624725342</t>
   </si>
   <si>
     <t xml:space="preserve">10.5780353546143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3993406295776</t>
+    <t xml:space="preserve">10.3993396759033</t>
   </si>
   <si>
     <t xml:space="preserve">10.4273719787598</t>
@@ -2195,10 +2195,10 @@
     <t xml:space="preserve">10.2872190475464</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3888292312622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.423867225647</t>
+    <t xml:space="preserve">10.3888282775879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4238662719727</t>
   </si>
   <si>
     <t xml:space="preserve">10.3678073883057</t>
@@ -2210,7 +2210,7 @@
     <t xml:space="preserve">10.7742500305176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4448890686035</t>
+    <t xml:space="preserve">10.4448900222778</t>
   </si>
   <si>
     <t xml:space="preserve">10.5079593658447</t>
@@ -2219,7 +2219,7 @@
     <t xml:space="preserve">10.5149669647217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6305923461914</t>
+    <t xml:space="preserve">10.6305932998657</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127918243408</t>
@@ -2231,7 +2231,7 @@
     <t xml:space="preserve">11.1877012252808</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3523807525635</t>
+    <t xml:space="preserve">11.3523797988892</t>
   </si>
   <si>
     <t xml:space="preserve">11.5731201171875</t>
@@ -2243,25 +2243,25 @@
     <t xml:space="preserve">11.7553195953369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7342958450317</t>
+    <t xml:space="preserve">11.7342967987061</t>
   </si>
   <si>
     <t xml:space="preserve">11.8429136276245</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7097682952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6291809082031</t>
+    <t xml:space="preserve">11.7097692489624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6291818618774</t>
   </si>
   <si>
     <t xml:space="preserve">11.863938331604</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9059829711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9199991226196</t>
+    <t xml:space="preserve">11.9059839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9199981689453</t>
   </si>
   <si>
     <t xml:space="preserve">12.0496397018433</t>
@@ -2279,7 +2279,7 @@
     <t xml:space="preserve">12.2143201828003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3159303665161</t>
+    <t xml:space="preserve">12.3159313201904</t>
   </si>
   <si>
     <t xml:space="preserve">12.2773895263672</t>
@@ -2288,16 +2288,16 @@
     <t xml:space="preserve">12.4175415039062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684883117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1267242431641</t>
+    <t xml:space="preserve">12.3684873580933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1267251968384</t>
   </si>
   <si>
     <t xml:space="preserve">12.0391283035278</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8464183807373</t>
+    <t xml:space="preserve">11.8464193344116</t>
   </si>
   <si>
     <t xml:space="preserve">12.0636548995972</t>
@@ -2306,19 +2306,19 @@
     <t xml:space="preserve">12.1407403945923</t>
   </si>
   <si>
-    <t xml:space="preserve">12.123218536377</t>
+    <t xml:space="preserve">12.1232194900513</t>
   </si>
   <si>
     <t xml:space="preserve">12.109206199646</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0321216583252</t>
+    <t xml:space="preserve">12.0321226119995</t>
   </si>
   <si>
     <t xml:space="preserve">11.8779535293579</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9760608673096</t>
+    <t xml:space="preserve">11.9760599136353</t>
   </si>
   <si>
     <t xml:space="preserve">11.6887474060059</t>
@@ -2330,19 +2330,19 @@
     <t xml:space="preserve">11.4890289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4820222854614</t>
+    <t xml:space="preserve">11.4820213317871</t>
   </si>
   <si>
     <t xml:space="preserve">11.6782360076904</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2472658157349</t>
+    <t xml:space="preserve">11.2472648620605</t>
   </si>
   <si>
     <t xml:space="preserve">11.0370359420776</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1001043319702</t>
+    <t xml:space="preserve">11.1001052856445</t>
   </si>
   <si>
     <t xml:space="preserve">10.7216920852661</t>
@@ -2351,16 +2351,16 @@
     <t xml:space="preserve">10.9284172058105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1561651229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.496036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.446982383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.184196472168</t>
+    <t xml:space="preserve">11.1561660766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4960374832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4469814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1841974258423</t>
   </si>
   <si>
     <t xml:space="preserve">11.324348449707</t>
@@ -2381,7 +2381,7 @@
     <t xml:space="preserve">11.4119443893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4995403289795</t>
+    <t xml:space="preserve">11.4995412826538</t>
   </si>
   <si>
     <t xml:space="preserve">11.790358543396</t>
@@ -2390,31 +2390,31 @@
     <t xml:space="preserve">11.8814573287964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8288984298706</t>
+    <t xml:space="preserve">11.8288974761963</t>
   </si>
   <si>
     <t xml:space="preserve">11.9550361633301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6677236557007</t>
+    <t xml:space="preserve">11.6677227020264</t>
   </si>
   <si>
     <t xml:space="preserve">11.6712284088135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8113803863525</t>
+    <t xml:space="preserve">11.8113813400269</t>
   </si>
   <si>
     <t xml:space="preserve">11.9970836639404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9410228729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.969051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0671577453613</t>
+    <t xml:space="preserve">11.9410238265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9690523147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0671586990356</t>
   </si>
   <si>
     <t xml:space="preserve">12.2703809738159</t>
@@ -2423,13 +2423,13 @@
     <t xml:space="preserve">12.2738847732544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1021976470947</t>
+    <t xml:space="preserve">12.102198600769</t>
   </si>
   <si>
     <t xml:space="preserve">12.0951900482178</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9725551605225</t>
+    <t xml:space="preserve">11.9725561141968</t>
   </si>
   <si>
     <t xml:space="preserve">12.0146026611328</t>
@@ -2444,19 +2444,19 @@
     <t xml:space="preserve">11.6011514663696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5520992279053</t>
+    <t xml:space="preserve">11.552098274231</t>
   </si>
   <si>
     <t xml:space="preserve">11.5485935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5941429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4259595870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5380811691284</t>
+    <t xml:space="preserve">11.5941438674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4259605407715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5380821228027</t>
   </si>
   <si>
     <t xml:space="preserve">11.6852426528931</t>
@@ -2468,7 +2468,7 @@
     <t xml:space="preserve">11.7027616500854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9480285644531</t>
+    <t xml:space="preserve">11.9480276107788</t>
   </si>
   <si>
     <t xml:space="preserve">12.084680557251</t>
@@ -2477,13 +2477,13 @@
     <t xml:space="preserve">12.2108144760132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7539081573486</t>
+    <t xml:space="preserve">12.7539091110229</t>
   </si>
   <si>
     <t xml:space="preserve">12.9641389846802</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7188682556152</t>
+    <t xml:space="preserve">12.7188692092896</t>
   </si>
   <si>
     <t xml:space="preserve">12.7889471054077</t>
@@ -2492,7 +2492,7 @@
     <t xml:space="preserve">12.795952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9886636734009</t>
+    <t xml:space="preserve">12.9886646270752</t>
   </si>
   <si>
     <t xml:space="preserve">13.1743659973145</t>
@@ -2501,7 +2501,7 @@
     <t xml:space="preserve">12.9080781936646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0412225723267</t>
+    <t xml:space="preserve">13.0412216186523</t>
   </si>
   <si>
     <t xml:space="preserve">13.2094049453735</t>
@@ -2510,16 +2510,16 @@
     <t xml:space="preserve">13.6649017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8996562957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007034301758</t>
+    <t xml:space="preserve">13.8996572494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007024765015</t>
   </si>
   <si>
     <t xml:space="preserve">14.365665435791</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6389636993408</t>
+    <t xml:space="preserve">14.6389646530151</t>
   </si>
   <si>
     <t xml:space="preserve">15.0173778533936</t>
@@ -2528,28 +2528,28 @@
     <t xml:space="preserve">15.1365070343018</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5289354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9493932723999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181415557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9213638305664</t>
+    <t xml:space="preserve">15.5289344787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9493923187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9213619232178</t>
   </si>
   <si>
     <t xml:space="preserve">16.1035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9914388656616</t>
+    <t xml:space="preserve">15.9914398193359</t>
   </si>
   <si>
     <t xml:space="preserve">16.1245861053467</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4118995666504</t>
+    <t xml:space="preserve">16.4118976593018</t>
   </si>
   <si>
     <t xml:space="preserve">16.5940952301025</t>
@@ -2564,7 +2564,7 @@
     <t xml:space="preserve">16.0474987030029</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8863248825073</t>
+    <t xml:space="preserve">15.886326789856</t>
   </si>
   <si>
     <t xml:space="preserve">15.4868869781494</t>
@@ -2573,19 +2573,19 @@
     <t xml:space="preserve">15.8232545852661</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7531805038452</t>
+    <t xml:space="preserve">15.7531785964966</t>
   </si>
   <si>
     <t xml:space="preserve">15.7251482009888</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1575307846069</t>
+    <t xml:space="preserve">15.1575298309326</t>
   </si>
   <si>
     <t xml:space="preserve">15.3817739486694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2626438140869</t>
+    <t xml:space="preserve">15.2626447677612</t>
   </si>
   <si>
     <t xml:space="preserve">15.2976818084717</t>
@@ -2594,7 +2594,7 @@
     <t xml:space="preserve">15.0804452896118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2836666107178</t>
+    <t xml:space="preserve">15.2836656570435</t>
   </si>
   <si>
     <t xml:space="preserve">15.2205982208252</t>
@@ -2603,28 +2603,28 @@
     <t xml:space="preserve">15.0944604873657</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0664300918579</t>
+    <t xml:space="preserve">15.0664310455322</t>
   </si>
   <si>
     <t xml:space="preserve">15.0454063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8562021255493</t>
+    <t xml:space="preserve">14.856201171875</t>
   </si>
   <si>
     <t xml:space="preserve">14.9122629165649</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1715450286865</t>
+    <t xml:space="preserve">15.1715440750122</t>
   </si>
   <si>
     <t xml:space="preserve">14.8702144622803</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7721099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3537445068359</t>
+    <t xml:space="preserve">14.7721090316772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3537435531616</t>
   </si>
   <si>
     <t xml:space="preserve">16.5029945373535</t>
@@ -2633,10 +2633,10 @@
     <t xml:space="preserve">16.5800819396973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4189052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7062168121338</t>
+    <t xml:space="preserve">16.4189033508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7062187194824</t>
   </si>
   <si>
     <t xml:space="preserve">16.8043270111084</t>
@@ -2645,52 +2645,52 @@
     <t xml:space="preserve">16.6221256256104</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5660648345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9865226745605</t>
+    <t xml:space="preserve">16.5660667419434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9865245819092</t>
   </si>
   <si>
     <t xml:space="preserve">17.0075492858887</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5380344390869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0545063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3978824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4959888458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0685253143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499582290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5709781646729</t>
+    <t xml:space="preserve">16.5380325317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0545082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3978805541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4959907531738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0685234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5709800720215</t>
   </si>
   <si>
     <t xml:space="preserve">16.0334854125977</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9423837661743</t>
+    <t xml:space="preserve">15.9423856735229</t>
   </si>
   <si>
     <t xml:space="preserve">16.1666278839111</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6431484222412</t>
+    <t xml:space="preserve">16.6431503295898</t>
   </si>
   <si>
     <t xml:space="preserve">16.3908729553223</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7622776031494</t>
+    <t xml:space="preserve">16.762279510498</t>
   </si>
   <si>
     <t xml:space="preserve">16.7833023071289</t>
@@ -2708,7 +2708,7 @@
     <t xml:space="preserve">15.6130266189575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5198335647583</t>
+    <t xml:space="preserve">14.5198345184326</t>
   </si>
   <si>
     <t xml:space="preserve">14.3516502380371</t>
@@ -2717,7 +2717,7 @@
     <t xml:space="preserve">14.5478639602661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7910394668579</t>
+    <t xml:space="preserve">13.7910385131836</t>
   </si>
   <si>
     <t xml:space="preserve">13.4546728134155</t>
@@ -2729,7 +2729,7 @@
     <t xml:space="preserve">12.9956712722778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3474645614624</t>
+    <t xml:space="preserve">12.347466468811</t>
   </si>
   <si>
     <t xml:space="preserve">11.7202825546265</t>
@@ -2750,16 +2750,16 @@
     <t xml:space="preserve">9.51988220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4442081451416</t>
+    <t xml:space="preserve">8.44420909881592</t>
   </si>
   <si>
     <t xml:space="preserve">8.0202465057373</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70490312576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77497911453247</t>
+    <t xml:space="preserve">7.70490264892578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77497863769531</t>
   </si>
   <si>
     <t xml:space="preserve">7.49817657470703</t>
@@ -2768,7 +2768,7 @@
     <t xml:space="preserve">7.59978771209717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28653621673584</t>
+    <t xml:space="preserve">8.28653717041016</t>
   </si>
   <si>
     <t xml:space="preserve">9.06088161468506</t>
@@ -2783,7 +2783,7 @@
     <t xml:space="preserve">8.87167453765869</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2360725402832</t>
+    <t xml:space="preserve">9.23607158660889</t>
   </si>
   <si>
     <t xml:space="preserve">8.87517833709717</t>
@@ -2792,7 +2792,7 @@
     <t xml:space="preserve">9.07489585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68246841430664</t>
+    <t xml:space="preserve">8.68246936798096</t>
   </si>
   <si>
     <t xml:space="preserve">9.0223388671875</t>
@@ -2801,34 +2801,34 @@
     <t xml:space="preserve">9.48834705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1680898666382</t>
+    <t xml:space="preserve">10.1680889129639</t>
   </si>
   <si>
     <t xml:space="preserve">10.2381649017334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87727069854736</t>
+    <t xml:space="preserve">9.87727165222168</t>
   </si>
   <si>
     <t xml:space="preserve">9.29914093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44630146026611</t>
+    <t xml:space="preserve">9.4463005065918</t>
   </si>
   <si>
     <t xml:space="preserve">9.51637744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5899600982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2535924911499</t>
+    <t xml:space="preserve">9.58995914459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25359153747559</t>
   </si>
   <si>
     <t xml:space="preserve">9.33417892456055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49535465240479</t>
+    <t xml:space="preserve">9.4953556060791</t>
   </si>
   <si>
     <t xml:space="preserve">9.47433185577393</t>
@@ -2837,16 +2837,16 @@
     <t xml:space="preserve">10.3713102340698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.816294670105</t>
+    <t xml:space="preserve">10.8162956237793</t>
   </si>
   <si>
     <t xml:space="preserve">11.2122278213501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8793640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7602338790894</t>
+    <t xml:space="preserve">10.8793649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.760232925415</t>
   </si>
   <si>
     <t xml:space="preserve">10.8618450164795</t>
@@ -2861,10 +2861,10 @@
     <t xml:space="preserve">10.6095705032349</t>
   </si>
   <si>
-    <t xml:space="preserve">10.539493560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4133558273315</t>
+    <t xml:space="preserve">10.5394926071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4133567810059</t>
   </si>
   <si>
     <t xml:space="preserve">11.0058345794678</t>
@@ -2873,7 +2873,7 @@
     <t xml:space="preserve">10.4649343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7654342651367</t>
+    <t xml:space="preserve">10.7654333114624</t>
   </si>
   <si>
     <t xml:space="preserve">10.6414775848389</t>
@@ -2882,7 +2882,7 @@
     <t xml:space="preserve">10.769190788269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8743667602539</t>
+    <t xml:space="preserve">10.8743658065796</t>
   </si>
   <si>
     <t xml:space="preserve">10.9757843017578</t>
@@ -2894,7 +2894,7 @@
     <t xml:space="preserve">11.358922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1936473846436</t>
+    <t xml:space="preserve">11.1936483383179</t>
   </si>
   <si>
     <t xml:space="preserve">11.3251161575317</t>
@@ -2903,7 +2903,7 @@
     <t xml:space="preserve">11.5204429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7984046936035</t>
+    <t xml:space="preserve">11.7984056472778</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913925170898</t>
@@ -2936,13 +2936,13 @@
     <t xml:space="preserve">11.666934967041</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5091724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7157678604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5730304718018</t>
+    <t xml:space="preserve">11.5091733932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7157669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5730295181274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8284559249878</t>
@@ -2954,10 +2954,10 @@
     <t xml:space="preserve">11.4490728378296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2011604309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4791240692139</t>
+    <t xml:space="preserve">11.2011594772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4791231155396</t>
   </si>
   <si>
     <t xml:space="preserve">11.4265365600586</t>
@@ -2966,7 +2966,7 @@
     <t xml:space="preserve">11.3664350509644</t>
   </si>
   <si>
-    <t xml:space="preserve">11.663179397583</t>
+    <t xml:space="preserve">11.6631803512573</t>
   </si>
   <si>
     <t xml:space="preserve">11.5429782867432</t>
@@ -2984,31 +2984,31 @@
     <t xml:space="preserve">11.6706914901733</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8585042953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8434810638428</t>
+    <t xml:space="preserve">11.8585052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8434801101685</t>
   </si>
   <si>
     <t xml:space="preserve">12.3580884933472</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3205251693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.801326751709</t>
+    <t xml:space="preserve">12.3205242156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8013277053833</t>
   </si>
   <si>
     <t xml:space="preserve">12.6999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7337131500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8351306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5684375762939</t>
+    <t xml:space="preserve">12.7337141036987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8351316452026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5684385299683</t>
   </si>
   <si>
     <t xml:space="preserve">12.6097564697266</t>
@@ -3017,7 +3017,7 @@
     <t xml:space="preserve">12.3731117248535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4369697570801</t>
+    <t xml:space="preserve">12.4369688034058</t>
   </si>
   <si>
     <t xml:space="preserve">12.0763683319092</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">12.3693561553955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3505744934082</t>
+    <t xml:space="preserve">12.3505754470825</t>
   </si>
   <si>
     <t xml:space="preserve">12.4745311737061</t>
@@ -3038,7 +3038,7 @@
     <t xml:space="preserve">12.493311882019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.470775604248</t>
+    <t xml:space="preserve">12.4707746505737</t>
   </si>
   <si>
     <t xml:space="preserve">12.8276214599609</t>
@@ -3071,19 +3071,19 @@
     <t xml:space="preserve">12.6247816085815</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5083379745483</t>
+    <t xml:space="preserve">12.508337020874</t>
   </si>
   <si>
     <t xml:space="preserve">12.3881378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1740322113037</t>
+    <t xml:space="preserve">12.1740312576294</t>
   </si>
   <si>
     <t xml:space="preserve">12.0650997161865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.264181137085</t>
+    <t xml:space="preserve">12.2641820907593</t>
   </si>
   <si>
     <t xml:space="preserve">11.9749488830566</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">12.1552495956421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8847999572754</t>
+    <t xml:space="preserve">11.8847990036011</t>
   </si>
   <si>
     <t xml:space="preserve">12.0688562393188</t>
@@ -3110,40 +3110,40 @@
     <t xml:space="preserve">12.5120944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6285371780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4257001876831</t>
+    <t xml:space="preserve">12.6285381317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4257011413574</t>
   </si>
   <si>
     <t xml:space="preserve">11.8547487258911</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8322105407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8096752166748</t>
+    <t xml:space="preserve">11.8322114944458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8096742630005</t>
   </si>
   <si>
     <t xml:space="preserve">11.6181049346924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3326292037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7645988464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5993232727051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5842981338501</t>
+    <t xml:space="preserve">11.3326282501221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7645998001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5993242263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5842990875244</t>
   </si>
   <si>
     <t xml:space="preserve">11.4640989303589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.362678527832</t>
+    <t xml:space="preserve">11.3626794815063</t>
   </si>
   <si>
     <t xml:space="preserve">11.7120113372803</t>
@@ -3155,7 +3155,7 @@
     <t xml:space="preserve">11.8359680175781</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9524116516113</t>
+    <t xml:space="preserve">11.952410697937</t>
   </si>
   <si>
     <t xml:space="preserve">12.200325012207</t>
@@ -3167,22 +3167,22 @@
     <t xml:space="preserve">12.1139307022095</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4031639099121</t>
+    <t xml:space="preserve">12.4031629562378</t>
   </si>
   <si>
     <t xml:space="preserve">11.944899559021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0989055633545</t>
+    <t xml:space="preserve">12.0989065170288</t>
   </si>
   <si>
     <t xml:space="preserve">12.1514921188354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0801248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7007427215576</t>
+    <t xml:space="preserve">12.0801239013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7007417678833</t>
   </si>
   <si>
     <t xml:space="preserve">11.5241985321045</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">11.64439868927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8209419250488</t>
+    <t xml:space="preserve">11.8209428787231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275363922119</t>
@@ -3218,19 +3218,19 @@
     <t xml:space="preserve">12.4332122802734</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106750488281</t>
+    <t xml:space="preserve">12.4106760025024</t>
   </si>
   <si>
     <t xml:space="preserve">13.1393899917603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2070007324219</t>
+    <t xml:space="preserve">13.2070016860962</t>
   </si>
   <si>
     <t xml:space="preserve">13.5600900650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2370519638062</t>
+    <t xml:space="preserve">13.2370529174805</t>
   </si>
   <si>
     <t xml:space="preserve">13.2595891952515</t>
@@ -3239,7 +3239,7 @@
     <t xml:space="preserve">13.2220277786255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6727781295776</t>
+    <t xml:space="preserve">13.672779083252</t>
   </si>
   <si>
     <t xml:space="preserve">13.3572521209717</t>
@@ -3248,7 +3248,7 @@
     <t xml:space="preserve">13.379789352417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2746143341064</t>
+    <t xml:space="preserve">13.2746133804321</t>
   </si>
   <si>
     <t xml:space="preserve">13.5375518798828</t>
@@ -3272,10 +3272,10 @@
     <t xml:space="preserve">12.9327945709229</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1731939315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1919765472412</t>
+    <t xml:space="preserve">13.1731948852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1919775009155</t>
   </si>
   <si>
     <t xml:space="preserve">13.1957330703735</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">12.82386302948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3271999359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361333847046</t>
+    <t xml:space="preserve">13.3272008895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361343383789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4962339401245</t>
@@ -3299,16 +3299,16 @@
     <t xml:space="preserve">13.4323768615723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3497409820557</t>
+    <t xml:space="preserve">13.3497400283813</t>
   </si>
   <si>
     <t xml:space="preserve">13.3384704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1994886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4135971069336</t>
+    <t xml:space="preserve">13.1994895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4135961532593</t>
   </si>
   <si>
     <t xml:space="preserve">13.4248657226562</t>
@@ -3320,13 +3320,13 @@
     <t xml:space="preserve">13.391058921814</t>
   </si>
   <si>
-    <t xml:space="preserve">13.680290222168</t>
+    <t xml:space="preserve">13.6802892684937</t>
   </si>
   <si>
     <t xml:space="preserve">14.2099227905273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9582538604736</t>
+    <t xml:space="preserve">13.9582529067993</t>
   </si>
   <si>
     <t xml:space="preserve">13.8305406570435</t>
@@ -3341,10 +3341,10 @@
     <t xml:space="preserve">13.9319591522217</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7328786849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4398899078369</t>
+    <t xml:space="preserve">13.7328796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4398908615112</t>
   </si>
   <si>
     <t xml:space="preserve">13.4060831069946</t>
@@ -3353,16 +3353,16 @@
     <t xml:space="preserve">13.1093406677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3009071350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.04172706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887199401855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676021575928</t>
+    <t xml:space="preserve">13.3009080886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0417261123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887208938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676012039185</t>
   </si>
   <si>
     <t xml:space="preserve">13.7216081619263</t>
@@ -3371,16 +3371,16 @@
     <t xml:space="preserve">14.3526611328125</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5855503082275</t>
+    <t xml:space="preserve">14.5855493545532</t>
   </si>
   <si>
     <t xml:space="preserve">15.0550804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0926418304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0250291824341</t>
+    <t xml:space="preserve">15.092643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0250301361084</t>
   </si>
   <si>
     <t xml:space="preserve">15.1978178024292</t>
@@ -3413,7 +3413,7 @@
     <t xml:space="preserve">14.9499053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7846298217773</t>
+    <t xml:space="preserve">14.784628868103</t>
   </si>
   <si>
     <t xml:space="preserve">14.7095060348511</t>
@@ -3422,34 +3422,34 @@
     <t xml:space="preserve">14.6644296646118</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4240303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7958974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7620916366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9123439788818</t>
+    <t xml:space="preserve">14.4240293502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.762092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9123430252075</t>
   </si>
   <si>
     <t xml:space="preserve">14.6606712341309</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4090061187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1948986053467</t>
+    <t xml:space="preserve">14.4090051651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1948976516724</t>
   </si>
   <si>
     <t xml:space="preserve">14.1197729110718</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2024097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2775344848633</t>
+    <t xml:space="preserve">14.202410697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2775354385376</t>
   </si>
   <si>
     <t xml:space="preserve">14.3226108551025</t>
@@ -3458,34 +3458,34 @@
     <t xml:space="preserve">14.4202718734741</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3714408874512</t>
+    <t xml:space="preserve">14.3714418411255</t>
   </si>
   <si>
     <t xml:space="preserve">14.2925605773926</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4653472900391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7470684051514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5930614471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8898038864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8484869003296</t>
+    <t xml:space="preserve">14.4653482437134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7470674514771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5930624008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8898048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8484859466553</t>
   </si>
   <si>
     <t xml:space="preserve">15.2504043579102</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1001567840576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1151819229126</t>
+    <t xml:space="preserve">15.1001558303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1151809692383</t>
   </si>
   <si>
     <t xml:space="preserve">15.0701055526733</t>
@@ -3503,13 +3503,13 @@
     <t xml:space="preserve">14.814679145813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8184356689453</t>
+    <t xml:space="preserve">14.818434715271</t>
   </si>
   <si>
     <t xml:space="preserve">14.9837112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0175180435181</t>
+    <t xml:space="preserve">15.0175189971924</t>
   </si>
   <si>
     <t xml:space="preserve">14.7921438217163</t>
@@ -3518,61 +3518,61 @@
     <t xml:space="preserve">14.9611740112305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1602554321289</t>
+    <t xml:space="preserve">15.1602563858032</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.085129737854</t>
+    <t xml:space="preserve">15.0851306915283</t>
   </si>
   <si>
     <t xml:space="preserve">15.1377191543579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3555812835693</t>
+    <t xml:space="preserve">15.3555822372437</t>
   </si>
   <si>
     <t xml:space="preserve">15.2579183578491</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2804555892944</t>
+    <t xml:space="preserve">15.2804565429688</t>
   </si>
   <si>
     <t xml:space="preserve">15.2729434967041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7462310791016</t>
+    <t xml:space="preserve">15.7462329864502</t>
   </si>
   <si>
     <t xml:space="preserve">15.86643409729</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8438949584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6410579681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6711053848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1603355407715</t>
+    <t xml:space="preserve">15.8438940048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.641056060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.708667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.671106338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1603336334229</t>
   </si>
   <si>
     <t xml:space="preserve">16.0814266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8841552734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.899941444397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.955174446106</t>
+    <t xml:space="preserve">15.8841562271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8999404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9551753997803</t>
   </si>
   <si>
     <t xml:space="preserve">16.0419731140137</t>
@@ -3617,7 +3617,7 @@
     <t xml:space="preserve">15.9472827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8762674331665</t>
+    <t xml:space="preserve">15.8762683868408</t>
   </si>
   <si>
     <t xml:space="preserve">16.2392444610596</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">16.5075302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4838581085205</t>
+    <t xml:space="preserve">16.4838562011719</t>
   </si>
   <si>
     <t xml:space="preserve">16.4444046020508</t>
@@ -3653,10 +3653,10 @@
     <t xml:space="preserve">16.2550258636475</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5233135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8073806762695</t>
+    <t xml:space="preserve">16.5233116149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8073787689209</t>
   </si>
   <si>
     <t xml:space="preserve">17.1624660491943</t>
@@ -3668,7 +3668,7 @@
     <t xml:space="preserve">17.3281726837158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1940288543701</t>
+    <t xml:space="preserve">17.1940307617188</t>
   </si>
   <si>
     <t xml:space="preserve">17.2492656707764</t>
@@ -3677,7 +3677,7 @@
     <t xml:space="preserve">17.1387939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4702072143555</t>
+    <t xml:space="preserve">17.4702053070068</t>
   </si>
   <si>
     <t xml:space="preserve">17.4938793182373</t>
@@ -3689,7 +3689,7 @@
     <t xml:space="preserve">17.4070796966553</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5727882385254</t>
+    <t xml:space="preserve">17.5727863311768</t>
   </si>
   <si>
     <t xml:space="preserve">17.9042015075684</t>
@@ -3698,10 +3698,10 @@
     <t xml:space="preserve">17.9120903015137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1093597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1172523498535</t>
+    <t xml:space="preserve">18.1093616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1172504425049</t>
   </si>
   <si>
     <t xml:space="preserve">18.2592868804932</t>
@@ -3710,10 +3710,10 @@
     <t xml:space="preserve">18.3224124908447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2435035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4644470214844</t>
+    <t xml:space="preserve">18.2435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4644451141357</t>
   </si>
   <si>
     <t xml:space="preserve">18.2513942718506</t>
@@ -3722,7 +3722,7 @@
     <t xml:space="preserve">18.2829570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">18.424991607666</t>
+    <t xml:space="preserve">18.4249935150146</t>
   </si>
   <si>
     <t xml:space="preserve">18.3539752960205</t>
@@ -3743,28 +3743,28 @@
     <t xml:space="preserve">18.7642974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8037509918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.756404876709</t>
+    <t xml:space="preserve">18.8037490844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7011699676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7564067840576</t>
   </si>
   <si>
     <t xml:space="preserve">18.7406234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6459331512451</t>
+    <t xml:space="preserve">18.6459312438965</t>
   </si>
   <si>
     <t xml:space="preserve">18.7169494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5749187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.843204498291</t>
+    <t xml:space="preserve">18.5749206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8432025909424</t>
   </si>
   <si>
     <t xml:space="preserve">18.8984394073486</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">18.9536762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1903991699219</t>
+    <t xml:space="preserve">19.1903972625732</t>
   </si>
   <si>
     <t xml:space="preserve">19.0878200531006</t>
@@ -3785,13 +3785,13 @@
     <t xml:space="preserve">18.8589859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9378929138184</t>
+    <t xml:space="preserve">18.937894821167</t>
   </si>
   <si>
     <t xml:space="preserve">19.2614154815674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1430549621582</t>
+    <t xml:space="preserve">19.1430530548096</t>
   </si>
   <si>
     <t xml:space="preserve">18.7327327728271</t>
@@ -3803,13 +3803,13 @@
     <t xml:space="preserve">18.7721862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6538238525391</t>
+    <t xml:space="preserve">18.6538257598877</t>
   </si>
   <si>
     <t xml:space="preserve">18.4013195037842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6222629547119</t>
+    <t xml:space="preserve">18.6222610473633</t>
   </si>
   <si>
     <t xml:space="preserve">18.2356128692627</t>
@@ -3824,13 +3824,13 @@
     <t xml:space="preserve">18.6380443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8353118896484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7090587615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5375919342041</t>
+    <t xml:space="preserve">18.8353137969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7090606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5375938415527</t>
   </si>
   <si>
     <t xml:space="preserve">19.403450012207</t>
@@ -3839,10 +3839,10 @@
     <t xml:space="preserve">19.5297031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6007175445557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8374443054199</t>
+    <t xml:space="preserve">19.6007194519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8374423980713</t>
   </si>
   <si>
     <t xml:space="preserve">19.6322803497314</t>
@@ -3857,7 +3857,7 @@
     <t xml:space="preserve">19.9952583312988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.066276550293</t>
+    <t xml:space="preserve">20.0662784576416</t>
   </si>
   <si>
     <t xml:space="preserve">20.1057300567627</t>
@@ -3869,7 +3869,7 @@
     <t xml:space="preserve">20.0741672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0189323425293</t>
+    <t xml:space="preserve">20.0189304351807</t>
   </si>
   <si>
     <t xml:space="preserve">20.2398738861084</t>
@@ -3890,10 +3890,10 @@
     <t xml:space="preserve">20.9816074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6659774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2162017822266</t>
+    <t xml:space="preserve">20.6659755706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2162036895752</t>
   </si>
   <si>
     <t xml:space="preserve">20.1372947692871</t>
@@ -3911,7 +3911,7 @@
     <t xml:space="preserve">19.3324337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4744682312012</t>
+    <t xml:space="preserve">19.4744663238525</t>
   </si>
   <si>
     <t xml:space="preserve">19.3087596893311</t>
@@ -3920,7 +3920,7 @@
     <t xml:space="preserve">19.1746158599854</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2377414703369</t>
+    <t xml:space="preserve">19.2377433776855</t>
   </si>
   <si>
     <t xml:space="preserve">19.2850894927979</t>
@@ -3929,13 +3929,13 @@
     <t xml:space="preserve">19.1272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.024694442749</t>
+    <t xml:space="preserve">19.0246925354004</t>
   </si>
   <si>
     <t xml:space="preserve">18.8116397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0168018341064</t>
+    <t xml:space="preserve">19.0168037414551</t>
   </si>
   <si>
     <t xml:space="preserve">18.7248420715332</t>
@@ -3956,7 +3956,7 @@
     <t xml:space="preserve">19.7269725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9005680084229</t>
+    <t xml:space="preserve">19.9005699157715</t>
   </si>
   <si>
     <t xml:space="preserve">19.9479160308838</t>
@@ -3968,13 +3968,13 @@
     <t xml:space="preserve">19.5770454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6165008544922</t>
+    <t xml:space="preserve">19.6165027618408</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268211364746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8711376190186</t>
+    <t xml:space="preserve">20.8711395263672</t>
   </si>
   <si>
     <t xml:space="preserve">20.9342632293701</t>
@@ -3983,31 +3983,31 @@
     <t xml:space="preserve">20.5791778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6817588806152</t>
+    <t xml:space="preserve">20.6817569732666</t>
   </si>
   <si>
     <t xml:space="preserve">20.3187828063965</t>
   </si>
   <si>
-    <t xml:space="preserve">19.884786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2119407653809</t>
+    <t xml:space="preserve">19.8847885131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2119426727295</t>
   </si>
   <si>
     <t xml:space="preserve">18.2671756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3934268951416</t>
+    <t xml:space="preserve">18.3934288024902</t>
   </si>
   <si>
     <t xml:space="preserve">19.0325832366943</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8747653961182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3303031921387</t>
+    <t xml:space="preserve">18.8747673034668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.33030128479</t>
   </si>
   <si>
     <t xml:space="preserve">18.7958583831787</t>
@@ -4022,13 +4022,13 @@
     <t xml:space="preserve">17.8095111846924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7463836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9278717041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.641674041748</t>
+    <t xml:space="preserve">17.7463855743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9278736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416721343994</t>
   </si>
   <si>
     <t xml:space="preserve">17.1782474517822</t>
@@ -4043,7 +4043,7 @@
     <t xml:space="preserve">15.4028205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4501638412476</t>
+    <t xml:space="preserve">15.4501647949219</t>
   </si>
   <si>
     <t xml:space="preserve">15.663215637207</t>
@@ -4055,10 +4055,10 @@
     <t xml:space="preserve">15.1897687911987</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5093460083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.852593421936</t>
+    <t xml:space="preserve">15.5093469619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8525943756104</t>
   </si>
   <si>
     <t xml:space="preserve">17.0441055297852</t>
@@ -4067,7 +4067,7 @@
     <t xml:space="preserve">16.7915992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4759674072266</t>
+    <t xml:space="preserve">16.4759654998779</t>
   </si>
   <si>
     <t xml:space="preserve">16.8152713775635</t>
@@ -4079,10 +4079,10 @@
     <t xml:space="preserve">16.4286212921143</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7442531585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2413749694824</t>
+    <t xml:space="preserve">16.7442512512207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2413730621338</t>
   </si>
   <si>
     <t xml:space="preserve">16.9415225982666</t>
@@ -4100,52 +4100,52 @@
     <t xml:space="preserve">15.7579050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4107103347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815780639648</t>
+    <t xml:space="preserve">15.4107112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815771102905</t>
   </si>
   <si>
     <t xml:space="preserve">15.9157209396362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8920497894287</t>
+    <t xml:space="preserve">15.8920488357544</t>
   </si>
   <si>
     <t xml:space="preserve">15.8683776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6277074813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7973604202271</t>
+    <t xml:space="preserve">15.6277084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7973594665527</t>
   </si>
   <si>
     <t xml:space="preserve">15.7539596557617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8289222717285</t>
+    <t xml:space="preserve">15.8289213180542</t>
   </si>
   <si>
     <t xml:space="preserve">16.089319229126</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0735378265381</t>
+    <t xml:space="preserve">16.0735397338867</t>
   </si>
   <si>
     <t xml:space="preserve">16.1761169433594</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9236106872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6395444869995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5132913589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964437484741</t>
+    <t xml:space="preserve">15.9236125946045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6395435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5132904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964447021484</t>
   </si>
   <si>
     <t xml:space="preserve">15.1660957336426</t>
@@ -4154,7 +4154,7 @@
     <t xml:space="preserve">15.6868877410889</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7381782531738</t>
+    <t xml:space="preserve">15.7381792068481</t>
   </si>
   <si>
     <t xml:space="preserve">15.765796661377</t>
@@ -4163,10 +4163,10 @@
     <t xml:space="preserve">16.0261917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8052520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4583625793457</t>
+    <t xml:space="preserve">15.8052530288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4583644866943</t>
   </si>
   <si>
     <t xml:space="preserve">16.0873756408691</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">16.7703304290771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305305480957</t>
+    <t xml:space="preserve">16.9305286407471</t>
   </si>
   <si>
     <t xml:space="preserve">16.8209209442139</t>
@@ -4202,7 +4202,7 @@
     <t xml:space="preserve">16.7366046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5342464447021</t>
+    <t xml:space="preserve">16.5342483520508</t>
   </si>
   <si>
     <t xml:space="preserve">16.2012023925781</t>
@@ -4211,7 +4211,7 @@
     <t xml:space="preserve">14.7298984527588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4390096664429</t>
+    <t xml:space="preserve">14.4390106201172</t>
   </si>
   <si>
     <t xml:space="preserve">14.6287202835083</t>
@@ -4232,7 +4232,7 @@
     <t xml:space="preserve">14.506462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2197904586792</t>
+    <t xml:space="preserve">14.2197895050049</t>
   </si>
   <si>
     <t xml:space="preserve">14.6750926971436</t>
@@ -4253,13 +4253,13 @@
     <t xml:space="preserve">13.8277225494385</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289016723633</t>
+    <t xml:space="preserve">13.9289026260376</t>
   </si>
   <si>
     <t xml:space="preserve">13.3724203109741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7771339416504</t>
+    <t xml:space="preserve">13.7771348953247</t>
   </si>
   <si>
     <t xml:space="preserve">14.1523370742798</t>
@@ -4268,19 +4268,19 @@
     <t xml:space="preserve">14.3420476913452</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1354732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3546943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.198712348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.621150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6801719665527</t>
+    <t xml:space="preserve">14.1354742050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3546934127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1987113952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6211519241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6801729202271</t>
   </si>
   <si>
     <t xml:space="preserve">13.8108596801758</t>
@@ -4292,7 +4292,7 @@
     <t xml:space="preserve">13.6928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.760272026062</t>
+    <t xml:space="preserve">13.7602710723877</t>
   </si>
   <si>
     <t xml:space="preserve">13.7939977645874</t>
@@ -4301,13 +4301,13 @@
     <t xml:space="preserve">13.4609518051147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5494823455811</t>
+    <t xml:space="preserve">13.5494832992554</t>
   </si>
   <si>
     <t xml:space="preserve">14.3631258010864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3926372528076</t>
+    <t xml:space="preserve">14.3926362991333</t>
   </si>
   <si>
     <t xml:space="preserve">14.1312589645386</t>
@@ -4316,22 +4316,22 @@
     <t xml:space="preserve">14.4727363586426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5739145278931</t>
+    <t xml:space="preserve">14.5739154815674</t>
   </si>
   <si>
     <t xml:space="preserve">14.2577314376831</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2956743240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1944942474365</t>
+    <t xml:space="preserve">14.2956733703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1944952011108</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600877761841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5022459030151</t>
+    <t xml:space="preserve">14.5022468566895</t>
   </si>
   <si>
     <t xml:space="preserve">14.565484046936</t>
@@ -4349,13 +4349,13 @@
     <t xml:space="preserve">13.9794912338257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7687034606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9541969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9415483474731</t>
+    <t xml:space="preserve">13.768702507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9541959762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9415493011475</t>
   </si>
   <si>
     <t xml:space="preserve">13.8530187606812</t>
@@ -4373,13 +4373,13 @@
     <t xml:space="preserve">13.4356575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1447687149048</t>
+    <t xml:space="preserve">13.1447696685791</t>
   </si>
   <si>
     <t xml:space="preserve">13.6295833587646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.427225112915</t>
+    <t xml:space="preserve">13.4272260665894</t>
   </si>
   <si>
     <t xml:space="preserve">13.4946775436401</t>
@@ -4388,7 +4388,7 @@
     <t xml:space="preserve">13.5199718475342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1692018508911</t>
+    <t xml:space="preserve">14.1692008972168</t>
   </si>
   <si>
     <t xml:space="preserve">14.0806703567505</t>
@@ -4397,16 +4397,16 @@
     <t xml:space="preserve">14.0722389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9162540435791</t>
+    <t xml:space="preserve">13.9162530899048</t>
   </si>
   <si>
     <t xml:space="preserve">13.7644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8572340011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4735994338989</t>
+    <t xml:space="preserve">13.8572330474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4735984802246</t>
   </si>
   <si>
     <t xml:space="preserve">13.1321220397949</t>
@@ -4418,10 +4418,10 @@
     <t xml:space="preserve">12.7527027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5334825515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.411226272583</t>
+    <t xml:space="preserve">12.5334815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4112253189087</t>
   </si>
   <si>
     <t xml:space="preserve">12.0065116882324</t>
@@ -4436,22 +4436,22 @@
     <t xml:space="preserve">13.1532011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9044704437256</t>
+    <t xml:space="preserve">12.9044694900513</t>
   </si>
   <si>
     <t xml:space="preserve">12.7231922149658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5039720535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5503454208374</t>
+    <t xml:space="preserve">12.5039710998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5503463745117</t>
   </si>
   <si>
     <t xml:space="preserve">12.4280881881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7324857711792</t>
+    <t xml:space="preserve">11.7324867248535</t>
   </si>
   <si>
     <t xml:space="preserve">12.0908260345459</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">12.5292663574219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7948598861694</t>
+    <t xml:space="preserve">12.7948608398438</t>
   </si>
   <si>
     <t xml:space="preserve">12.8791751861572</t>
@@ -4475,7 +4475,7 @@
     <t xml:space="preserve">12.8960380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3007516860962</t>
+    <t xml:space="preserve">13.3007526397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.6843872070312</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">13.532618522644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7897815704346</t>
+    <t xml:space="preserve">13.7897806167603</t>
   </si>
   <si>
     <t xml:space="preserve">13.743408203125</t>
@@ -4493,7 +4493,7 @@
     <t xml:space="preserve">13.9963550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1101808547974</t>
+    <t xml:space="preserve">14.110179901123</t>
   </si>
   <si>
     <t xml:space="preserve">14.3462619781494</t>
@@ -4526,10 +4526,10 @@
     <t xml:space="preserve">16.799840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3740463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4415016174316</t>
+    <t xml:space="preserve">16.3740482330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.441499710083</t>
   </si>
   <si>
     <t xml:space="preserve">16.4035587310791</t>
@@ -4544,10 +4544,10 @@
     <t xml:space="preserve">16.2349281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3993434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3023777008057</t>
+    <t xml:space="preserve">16.3993453979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3023796081543</t>
   </si>
   <si>
     <t xml:space="preserve">16.6059150695801</t>
@@ -4571,7 +4571,7 @@
     <t xml:space="preserve">17.0570030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9558258056641</t>
+    <t xml:space="preserve">16.9558238983154</t>
   </si>
   <si>
     <t xml:space="preserve">16.2855167388916</t>
@@ -4580,7 +4580,7 @@
     <t xml:space="preserve">17.2677917480469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2593612670898</t>
+    <t xml:space="preserve">17.2593593597412</t>
   </si>
   <si>
     <t xml:space="preserve">17.2340660095215</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">17.4617156982422</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6893692016602</t>
+    <t xml:space="preserve">17.6893672943115</t>
   </si>
   <si>
     <t xml:space="preserve">17.7146625518799</t>
@@ -4604,7 +4604,7 @@
     <t xml:space="preserve">17.8579998016357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6472129821777</t>
+    <t xml:space="preserve">17.6472110748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.8664302825928</t>
@@ -4622,7 +4622,7 @@
     <t xml:space="preserve">17.9676074981689</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3807525634766</t>
+    <t xml:space="preserve">18.3807544708252</t>
   </si>
   <si>
     <t xml:space="preserve">18.3891849517822</t>
@@ -4640,10 +4640,10 @@
     <t xml:space="preserve">19.1901817321777</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1311626434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1648864746094</t>
+    <t xml:space="preserve">19.131160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.164888381958</t>
   </si>
   <si>
     <t xml:space="preserve">18.8444881439209</t>
@@ -4667,16 +4667,16 @@
     <t xml:space="preserve">19.4431266784668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3250885009766</t>
+    <t xml:space="preserve">19.3250865936279</t>
   </si>
   <si>
     <t xml:space="preserve">19.2913608551025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3166542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8141174316406</t>
+    <t xml:space="preserve">19.3166561126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.814115524292</t>
   </si>
   <si>
     <t xml:space="preserve">19.8984336853027</t>
@@ -4694,7 +4694,7 @@
     <t xml:space="preserve">19.8309783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1564540863037</t>
+    <t xml:space="preserve">19.1564559936523</t>
   </si>
   <si>
     <t xml:space="preserve">19.5358753204346</t>
@@ -4706,7 +4706,7 @@
     <t xml:space="preserve">19.0890026092529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2070465087891</t>
+    <t xml:space="preserve">19.2070446014404</t>
   </si>
   <si>
     <t xml:space="preserve">19.0552787780762</t>
@@ -4721,7 +4721,7 @@
     <t xml:space="preserve">18.9456672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9793949127197</t>
+    <t xml:space="preserve">18.9793930053711</t>
   </si>
   <si>
     <t xml:space="preserve">19.1058673858643</t>
@@ -4736,7 +4736,7 @@
     <t xml:space="preserve">18.1952590942383</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6134853363037</t>
+    <t xml:space="preserve">17.6134834289551</t>
   </si>
   <si>
     <t xml:space="preserve">16.7745456695557</t>
@@ -4751,16 +4751,16 @@
     <t xml:space="preserve">16.0114936828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9052333831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782634735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1126689910889</t>
+    <t xml:space="preserve">16.4667949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9052352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1126708984375</t>
   </si>
   <si>
     <t xml:space="preserve">16.1337490081787</t>
@@ -4769,7 +4769,7 @@
     <t xml:space="preserve">16.3487529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.643856048584</t>
+    <t xml:space="preserve">16.6438579559326</t>
   </si>
   <si>
     <t xml:space="preserve">16.6101322174072</t>
@@ -4793,16 +4793,16 @@
     <t xml:space="preserve">17.124454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0232772827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2003402709961</t>
+    <t xml:space="preserve">17.0232791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2003383636475</t>
   </si>
   <si>
     <t xml:space="preserve">17.2424983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.107593536377</t>
+    <t xml:space="preserve">17.1075916290283</t>
   </si>
   <si>
     <t xml:space="preserve">17.0148468017578</t>
@@ -4814,31 +4814,31 @@
     <t xml:space="preserve">17.0654335021973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8124904632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5806217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9726867675781</t>
+    <t xml:space="preserve">16.8124885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5806198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9726848602295</t>
   </si>
   <si>
     <t xml:space="preserve">17.0822982788086</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8546466827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9895496368408</t>
+    <t xml:space="preserve">16.8546447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9895515441895</t>
   </si>
   <si>
     <t xml:space="preserve">17.0738658905029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8504314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2509269714355</t>
+    <t xml:space="preserve">16.8504295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2509288787842</t>
   </si>
   <si>
     <t xml:space="preserve">17.4084911346436</t>
@@ -6378,6 +6378,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.1199989318848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">32.3899993896484</t>
   </si>
 </sst>
 </file>
@@ -71560,7 +71563,7 @@
     </row>
     <row r="2495">
       <c r="A2495" s="1" t="n">
-        <v>45952.6493865741</v>
+        <v>45952.2916666667</v>
       </c>
       <c r="B2495" t="n">
         <v>365020</v>
@@ -71581,6 +71584,32 @@
         <v>2121</v>
       </c>
       <c r="H2495" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2496">
+      <c r="A2496" s="1" t="n">
+        <v>45953.6522106481</v>
+      </c>
+      <c r="B2496" t="n">
+        <v>447177</v>
+      </c>
+      <c r="C2496" t="n">
+        <v>32.6399993896484</v>
+      </c>
+      <c r="D2496" t="n">
+        <v>31.9500007629395</v>
+      </c>
+      <c r="E2496" t="n">
+        <v>32.1199989318848</v>
+      </c>
+      <c r="F2496" t="n">
+        <v>32.3899993896484</v>
+      </c>
+      <c r="G2496" t="s">
+        <v>2122</v>
+      </c>
+      <c r="H2496" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2123" uniqueCount="2123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="2124">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,46 +44,46 @@
     <t xml:space="preserve">AZM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4860258102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1916122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91191959381104</t>
+    <t xml:space="preserve">10.7068357467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.486026763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.191611289978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91192054748535</t>
   </si>
   <si>
     <t xml:space="preserve">9.9364538192749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.225959777832</t>
+    <t xml:space="preserve">10.2259607315063</t>
   </si>
   <si>
     <t xml:space="preserve">10.0002431869507</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61750602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33290576934814</t>
+    <t xml:space="preserve">9.61750507354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33290672302246</t>
   </si>
   <si>
     <t xml:space="preserve">9.1513500213623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37706756591797</t>
+    <t xml:space="preserve">9.37706661224365</t>
   </si>
   <si>
     <t xml:space="preserve">8.85693836212158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25930213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53899574279785</t>
+    <t xml:space="preserve">9.25930404663086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53899669647217</t>
   </si>
   <si>
     <t xml:space="preserve">9.48992824554443</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">9.50955390930176</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40160274505615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12681674957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49483585357666</t>
+    <t xml:space="preserve">9.40160369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12681770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49483394622803</t>
   </si>
   <si>
     <t xml:space="preserve">9.43595123291016</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">8.99433040618896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79805469512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05711460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86574649810791</t>
+    <t xml:space="preserve">8.79805564880371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05711364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86574554443359</t>
   </si>
   <si>
     <t xml:space="preserve">8.32699394226074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61058759689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67928314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10127735137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87065267562866</t>
+    <t xml:space="preserve">7.61058664321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67928409576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10127639770508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87065315246582</t>
   </si>
   <si>
     <t xml:space="preserve">8.53798961639404</t>
@@ -140,127 +140,127 @@
     <t xml:space="preserve">8.78333473205566</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46929359436035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61649990081787</t>
+    <t xml:space="preserve">8.46929264068604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61649799346924</t>
   </si>
   <si>
     <t xml:space="preserve">8.50364112854004</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21413612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69010448455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71954345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29365158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30837059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47520542144775</t>
+    <t xml:space="preserve">8.21413516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69010353088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71954536437988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29365062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30837249755859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47520637512207</t>
   </si>
   <si>
     <t xml:space="preserve">9.09737586975098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22004795074463</t>
+    <t xml:space="preserve">9.22004890441895</t>
   </si>
   <si>
     <t xml:space="preserve">9.41141605377197</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48011207580566</t>
+    <t xml:space="preserve">9.48011302947998</t>
   </si>
   <si>
     <t xml:space="preserve">9.77943325042725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66166877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79415321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77452564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68620300292969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64694690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7254581451416</t>
+    <t xml:space="preserve">9.66166687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79415416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7745246887207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68620204925537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64694786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.72545623779297</t>
   </si>
   <si>
     <t xml:space="preserve">10.2357749938965</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3044710159302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8383150100708</t>
+    <t xml:space="preserve">10.3044691085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83831691741943</t>
   </si>
   <si>
     <t xml:space="preserve">9.56843566894531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98552227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93154621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74508476257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3780736923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449085235596</t>
+    <t xml:space="preserve">9.98552417755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93154716491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74508571624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3780727386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449094772339</t>
   </si>
   <si>
     <t xml:space="preserve">10.436957359314</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5547227859497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.505654335022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5498161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5007457733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5694437026978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.417329788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4811191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7411823272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8442287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7853441238403</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5988836288452</t>
+    <t xml:space="preserve">10.5547218322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5056524276733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5498151779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5007467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5694417953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173288345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4811201095581</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7411842346191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8442277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.785346031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5988845825195</t>
   </si>
   <si>
     <t xml:space="preserve">10.2406806945801</t>
@@ -269,19 +269,19 @@
     <t xml:space="preserve">10.2897510528564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73036479949951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57334327697754</t>
+    <t xml:space="preserve">9.73036575317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57334518432617</t>
   </si>
   <si>
     <t xml:space="preserve">9.43104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40650939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19060611724854</t>
+    <t xml:space="preserve">9.40651035308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19060707092285</t>
   </si>
   <si>
     <t xml:space="preserve">9.08265495300293</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">9.3525333404541</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47029876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27892971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30346393585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14644336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52970123291016</t>
+    <t xml:space="preserve">9.47029781341553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27892875671387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30346584320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14644432067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52970218658447</t>
   </si>
   <si>
     <t xml:space="preserve">9.79665470123291</t>
@@ -314,73 +314,73 @@
     <t xml:space="preserve">9.89235496520996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95279693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492328643799</t>
+    <t xml:space="preserve">9.95279502868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492319107056</t>
   </si>
   <si>
     <t xml:space="preserve">9.84702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76643371582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42896461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42392921447754</t>
+    <t xml:space="preserve">9.76643466949463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42896556854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42392730712891</t>
   </si>
   <si>
     <t xml:space="preserve">9.5246639251709</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54984855651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39370632171631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82958126068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4820384979248</t>
+    <t xml:space="preserve">9.54984951019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39370727539062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82958221435547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48203945159912</t>
   </si>
   <si>
     <t xml:space="preserve">8.28560256958008</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46189117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53744506835938</t>
+    <t xml:space="preserve">8.46189212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53744411468506</t>
   </si>
   <si>
     <t xml:space="preserve">8.68351268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39874267578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5045166015625</t>
+    <t xml:space="preserve">9.39874362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50451850891113</t>
   </si>
   <si>
     <t xml:space="preserve">9.81680011749268</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46692752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46459674835205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540845870972</t>
+    <t xml:space="preserve">8.46692943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46459722518921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5754075050354</t>
   </si>
   <si>
     <t xml:space="preserve">7.49985551834106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.34875106811523</t>
+    <t xml:space="preserve">7.34875011444092</t>
   </si>
   <si>
     <t xml:space="preserve">7.43941259384155</t>
@@ -389,100 +389,100 @@
     <t xml:space="preserve">7.20268297195435</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8702507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50256109237671</t>
+    <t xml:space="preserve">6.87025022506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50256061553955</t>
   </si>
   <si>
     <t xml:space="preserve">6.6284818649292</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86017513275146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02135467529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3890438079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20771932601929</t>
+    <t xml:space="preserve">6.86017560958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02135562896729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38904428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20771837234497</t>
   </si>
   <si>
     <t xml:space="preserve">7.44948625564575</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66607141494751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52503871917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64592266082764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79702949523926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71140241622925</t>
+    <t xml:space="preserve">7.66607093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52503967285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64592313766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79703044891357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71140289306641</t>
   </si>
   <si>
     <t xml:space="preserve">7.94309711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81717586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94813442230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08179807662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92565488815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71410751342773</t>
+    <t xml:space="preserve">7.8171763420105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94813394546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08179712295532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92565584182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71410894393921</t>
   </si>
   <si>
     <t xml:space="preserve">6.78966093063354</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90047168731689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22786521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27823352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32860279083252</t>
+    <t xml:space="preserve">6.90047025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22786617279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27823495864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32860326766968</t>
   </si>
   <si>
     <t xml:space="preserve">7.31852865219116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39911842346191</t>
+    <t xml:space="preserve">7.39911890029907</t>
   </si>
   <si>
     <t xml:space="preserve">7.15735006332397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94580268859863</t>
+    <t xml:space="preserve">6.94580173492432</t>
   </si>
   <si>
     <t xml:space="preserve">7.19764518737793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80477142333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02639102935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08683347702026</t>
+    <t xml:space="preserve">6.804771900177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02639198303223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08683443069458</t>
   </si>
   <si>
     <t xml:space="preserve">7.04150342941284</t>
@@ -491,22 +491,22 @@
     <t xml:space="preserve">6.85010290145874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86521339416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069314956665</t>
+    <t xml:space="preserve">6.8652138710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069171905518</t>
   </si>
   <si>
     <t xml:space="preserve">7.22282838821411</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31349229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23290157318115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29838085174561</t>
+    <t xml:space="preserve">7.31349325180054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23290205001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29838037490845</t>
   </si>
   <si>
     <t xml:space="preserve">6.98106050491333</t>
@@ -515,40 +515,40 @@
     <t xml:space="preserve">7.01128101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53781938552856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79973411560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68388700485229</t>
+    <t xml:space="preserve">6.53781890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7997350692749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68388748168945</t>
   </si>
   <si>
     <t xml:space="preserve">6.73929262161255</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94076538085938</t>
+    <t xml:space="preserve">6.94076633453369</t>
   </si>
   <si>
     <t xml:space="preserve">6.90550851821899</t>
   </si>
   <si>
-    <t xml:space="preserve">6.668776512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4622654914856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57307577133179</t>
+    <t xml:space="preserve">6.66877746582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46226596832275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57307720184326</t>
   </si>
   <si>
     <t xml:space="preserve">6.6738133430481</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59826135635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87528705596924</t>
+    <t xml:space="preserve">6.59826040267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87528657913208</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624418258667</t>
@@ -557,25 +557,25 @@
     <t xml:space="preserve">7.15231275558472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30341815948486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62577629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66103363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57037019729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45452356338501</t>
+    <t xml:space="preserve">7.30341863632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62577724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66103410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57037115097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45452451705933</t>
   </si>
   <si>
     <t xml:space="preserve">7.5351128578186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44444990158081</t>
+    <t xml:space="preserve">7.44444847106934</t>
   </si>
   <si>
     <t xml:space="preserve">7.59555530548096</t>
@@ -584,64 +584,64 @@
     <t xml:space="preserve">7.72147607803345</t>
   </si>
   <si>
-    <t xml:space="preserve">7.60562896728516</t>
+    <t xml:space="preserve">7.605628490448</t>
   </si>
   <si>
     <t xml:space="preserve">7.70636510848999</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48474407196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36386060714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26312351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13216638565063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17246007919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69629335403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91791439056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35611820220947</t>
+    <t xml:space="preserve">7.48474502563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36385917663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26312303543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13216400146484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617052078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17246055603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69629096984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91791296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35611724853516</t>
   </si>
   <si>
     <t xml:space="preserve">8.38633823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51729869842529</t>
+    <t xml:space="preserve">8.51729679107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.45181751251221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20501232147217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04887008666992</t>
+    <t xml:space="preserve">8.20501327514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04887104034424</t>
   </si>
   <si>
     <t xml:space="preserve">7.95820808410645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93132305145264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71623611450195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73236751556396</t>
+    <t xml:space="preserve">7.93132162094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71623516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73236799240112</t>
   </si>
   <si>
     <t xml:space="preserve">7.6355767250061</t>
@@ -650,31 +650,31 @@
     <t xml:space="preserve">7.64095497131348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45813179016113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44199991226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57105302810669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68935060501099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62482261657715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79689264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20018005371094</t>
+    <t xml:space="preserve">7.45813083648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44200086593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57105207443237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68935108184814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62482309341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79689311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20018100738525</t>
   </si>
   <si>
     <t xml:space="preserve">8.43139839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61959838867188</t>
+    <t xml:space="preserve">8.61960029602051</t>
   </si>
   <si>
     <t xml:space="preserve">8.54432010650635</t>
@@ -686,10 +686,10 @@
     <t xml:space="preserve">8.58733654022217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70025825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54969596862793</t>
+    <t xml:space="preserve">8.70025730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54969692230225</t>
   </si>
   <si>
     <t xml:space="preserve">8.60346794128418</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">8.53356552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5980920791626</t>
+    <t xml:space="preserve">8.59809017181396</t>
   </si>
   <si>
     <t xml:space="preserve">8.51743412017822</t>
@@ -707,13 +707,13 @@
     <t xml:space="preserve">8.52818775177002</t>
   </si>
   <si>
-    <t xml:space="preserve">8.67874813079834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.11429977416992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15731525421143</t>
+    <t xml:space="preserve">8.67875003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.11429882049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15731716156006</t>
   </si>
   <si>
     <t xml:space="preserve">9.20033359527588</t>
@@ -722,52 +722,52 @@
     <t xml:space="preserve">9.17882537841797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05515098571777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33476448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13043117523193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4476842880249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38315868377686</t>
+    <t xml:space="preserve">9.05515003204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3347635269165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13043022155762</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44768238067627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38315677642822</t>
   </si>
   <si>
     <t xml:space="preserve">9.41004371643066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45843696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45306015014648</t>
+    <t xml:space="preserve">9.4584379196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4530611038208</t>
   </si>
   <si>
     <t xml:space="preserve">9.37240219116211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23797416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32938671112061</t>
+    <t xml:space="preserve">9.2379732131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32938575744629</t>
   </si>
   <si>
     <t xml:space="preserve">9.46919250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44230651855469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92609786987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09278964996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07128238677979</t>
+    <t xml:space="preserve">9.442307472229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92609882354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0927906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07128143310547</t>
   </si>
   <si>
     <t xml:space="preserve">8.76478290557861</t>
@@ -776,16 +776,16 @@
     <t xml:space="preserve">9.16807174682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25948238372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28636837005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24335098266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26486015319824</t>
+    <t xml:space="preserve">9.25948143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28636932373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24335193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26485919952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.23259735107422</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">9.24872875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96373844146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49592590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59271335601807</t>
+    <t xml:space="preserve">8.9637393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.495924949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59271430969238</t>
   </si>
   <si>
     <t xml:space="preserve">8.52281093597412</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">8.71101188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70563411712646</t>
+    <t xml:space="preserve">8.7056360244751</t>
   </si>
   <si>
     <t xml:space="preserve">8.63573169708252</t>
@@ -824,37 +824,37 @@
     <t xml:space="preserve">8.53894233703613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50130271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28621482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33460998535156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43677616119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4744176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62497711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56582832336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47979259490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66261672973633</t>
+    <t xml:space="preserve">8.50130176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28621578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33460903167725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43677520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47441577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62497615814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56582736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47979354858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66261577606201</t>
   </si>
   <si>
     <t xml:space="preserve">8.61422252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78091526031494</t>
+    <t xml:space="preserve">8.78091430664062</t>
   </si>
   <si>
     <t xml:space="preserve">8.77016067504883</t>
@@ -866,7 +866,7 @@
     <t xml:space="preserve">9.18420219421387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04977416992188</t>
+    <t xml:space="preserve">9.04977321624756</t>
   </si>
   <si>
     <t xml:space="preserve">9.14118480682373</t>
@@ -875,16 +875,16 @@
     <t xml:space="preserve">9.16269302368164</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30249977111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13580894470215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14656162261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20571041107178</t>
+    <t xml:space="preserve">9.30250072479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13580799102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14656352996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20570945739746</t>
   </si>
   <si>
     <t xml:space="preserve">9.62513065338135</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">9.60899829864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63588428497314</t>
+    <t xml:space="preserve">9.63588714599609</t>
   </si>
   <si>
     <t xml:space="preserve">9.7165412902832</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">9.97464656829834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0553045272827</t>
+    <t xml:space="preserve">10.0553035736084</t>
   </si>
   <si>
     <t xml:space="preserve">10.243504524231</t>
@@ -914,73 +914,73 @@
     <t xml:space="preserve">10.4155740737915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3456716537476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2327499389648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3994426727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4101972579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349161148071</t>
+    <t xml:space="preserve">10.3456697463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2327489852905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3994436264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4101963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349170684814</t>
   </si>
   <si>
     <t xml:space="preserve">10.1305828094482</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036968231201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3295392990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4259700775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5507650375366</t>
+    <t xml:space="preserve">10.1036996841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3295383453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4259719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5507669448853</t>
   </si>
   <si>
     <t xml:space="preserve">10.6074905395508</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5847997665405</t>
+    <t xml:space="preserve">10.5848007202148</t>
   </si>
   <si>
     <t xml:space="preserve">10.4770240783691</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2387800216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2728147506714</t>
+    <t xml:space="preserve">10.2387809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2728157043457</t>
   </si>
   <si>
     <t xml:space="preserve">10.3408842086792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2160911560059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0856237411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90410614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2898330688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2614698410034</t>
+    <t xml:space="preserve">10.2160902023315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0856227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9041051864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898321151733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2614707946777</t>
   </si>
   <si>
     <t xml:space="preserve">10.1083135604858</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0062103271484</t>
+    <t xml:space="preserve">10.0062093734741</t>
   </si>
   <si>
     <t xml:space="preserve">9.94381237030029</t>
@@ -992,7 +992,7 @@
     <t xml:space="preserve">10.1366758346558</t>
   </si>
   <si>
-    <t xml:space="preserve">10.062933921814</t>
+    <t xml:space="preserve">10.0629348754883</t>
   </si>
   <si>
     <t xml:space="preserve">10.1990728378296</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">10.2104167938232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.193398475647</t>
+    <t xml:space="preserve">10.1933994293213</t>
   </si>
   <si>
     <t xml:space="preserve">9.95515727996826</t>
@@ -1013,43 +1013,43 @@
     <t xml:space="preserve">10.1480197906494</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2444534301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841606140137</t>
+    <t xml:space="preserve">10.2444524765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841596603394</t>
   </si>
   <si>
     <t xml:space="preserve">10.2217626571655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0912971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1593656539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5450916290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4089546203613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3181953430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2955045700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3692455291748</t>
+    <t xml:space="preserve">10.0912961959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1593647003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.545093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4089527130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3181934356689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.295506477356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3692464828491</t>
   </si>
   <si>
     <t xml:space="preserve">10.4316434860229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.397608757019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7152662277222</t>
+    <t xml:space="preserve">10.3976078033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7152671813965</t>
   </si>
   <si>
     <t xml:space="preserve">10.641526222229</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">10.7209377288818</t>
   </si>
   <si>
-    <t xml:space="preserve">10.669885635376</t>
+    <t xml:space="preserve">10.6698865890503</t>
   </si>
   <si>
     <t xml:space="preserve">10.7776613235474</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7039213180542</t>
+    <t xml:space="preserve">10.7039222717285</t>
   </si>
   <si>
     <t xml:space="preserve">10.658540725708</t>
@@ -1082,7 +1082,7 @@
     <t xml:space="preserve">10.7095928192139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5564374923706</t>
+    <t xml:space="preserve">10.5564365386963</t>
   </si>
   <si>
     <t xml:space="preserve">10.4826955795288</t>
@@ -1091,28 +1091,28 @@
     <t xml:space="preserve">10.3352117538452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2331075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2784872055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0288991928101</t>
+    <t xml:space="preserve">10.2331085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2784852981567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0288982391357</t>
   </si>
   <si>
     <t xml:space="preserve">10.040244102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0969696044922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.034571647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98351955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96082973480225</t>
+    <t xml:space="preserve">10.0969686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0345706939697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9835205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96082878112793</t>
   </si>
   <si>
     <t xml:space="preserve">9.98919200897217</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">10.511058807373</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4146270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3635721206665</t>
+    <t xml:space="preserve">10.4146280288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3635740280151</t>
   </si>
   <si>
     <t xml:space="preserve">10.3805913925171</t>
@@ -1145,34 +1145,34 @@
     <t xml:space="preserve">10.5167303085327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3465576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84738254547119</t>
+    <t xml:space="preserve">10.3465566635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84738063812256</t>
   </si>
   <si>
     <t xml:space="preserve">9.86439895629883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7282600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67720890045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66018867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48434352874756</t>
+    <t xml:space="preserve">9.72825908660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67720794677734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66018962860107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48434448242188</t>
   </si>
   <si>
     <t xml:space="preserve">9.688551902771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58644866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71124076843262</t>
+    <t xml:space="preserve">9.58644771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71124172210693</t>
   </si>
   <si>
     <t xml:space="preserve">9.67153549194336</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">9.78498363494873</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7963285446167</t>
+    <t xml:space="preserve">9.79633045196533</t>
   </si>
   <si>
     <t xml:space="preserve">9.89843368530273</t>
@@ -1199,28 +1199,28 @@
     <t xml:space="preserve">9.16101360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95113182067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99083995819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76961421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75259780883789</t>
+    <t xml:space="preserve">8.95113277435303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99084091186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76961326599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75259685516357</t>
   </si>
   <si>
     <t xml:space="preserve">8.86604499816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85470104217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05890941619873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24042701721191</t>
+    <t xml:space="preserve">8.85470008850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05891036987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24042892456055</t>
   </si>
   <si>
     <t xml:space="preserve">9.2517728805542</t>
@@ -1229,28 +1229,28 @@
     <t xml:space="preserve">9.10996246337891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09294319152832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98516845703125</t>
+    <t xml:space="preserve">9.09294414520264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98516750335693</t>
   </si>
   <si>
     <t xml:space="preserve">9.07592678070068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13265228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05323505401611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.90008068084717</t>
+    <t xml:space="preserve">9.13265132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05323696136475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.90007972717285</t>
   </si>
   <si>
     <t xml:space="preserve">8.88306331634521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82633781433105</t>
+    <t xml:space="preserve">8.82633876800537</t>
   </si>
   <si>
     <t xml:space="preserve">8.79230403900146</t>
@@ -1262,10 +1262,10 @@
     <t xml:space="preserve">8.9681510925293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0021858215332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07025527954102</t>
+    <t xml:space="preserve">9.00218486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0702543258667</t>
   </si>
   <si>
     <t xml:space="preserve">8.9965124130249</t>
@@ -1283,19 +1283,19 @@
     <t xml:space="preserve">9.03054714202881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01353073120117</t>
+    <t xml:space="preserve">9.01352882385254</t>
   </si>
   <si>
     <t xml:space="preserve">9.04756450653076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03621959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13832378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97382354736328</t>
+    <t xml:space="preserve">9.03622055053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1383228302002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97382259368896</t>
   </si>
   <si>
     <t xml:space="preserve">9.12697887420654</t>
@@ -1304,73 +1304,73 @@
     <t xml:space="preserve">9.16668605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19504928588867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37089443206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38224029541016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34253311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46732711791992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.67555809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4202976226807</t>
+    <t xml:space="preserve">9.19504833221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37089538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34253120422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46732616424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6755590438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.420298576355</t>
   </si>
   <si>
     <t xml:space="preserve">10.3919372558594</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5961456298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7549724578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7379579544067</t>
+    <t xml:space="preserve">10.5961437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7549734115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7379560470581</t>
   </si>
   <si>
     <t xml:space="preserve">10.760645866394</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6613788604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4543323516846</t>
+    <t xml:space="preserve">10.6613779067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4543342590332</t>
   </si>
   <si>
     <t xml:space="preserve">10.4032821655273</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4429874420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3777542114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0742788314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1338386535645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0941324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98635578155518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1565275192261</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962375640869</t>
+    <t xml:space="preserve">10.4429883956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3777561187744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0742807388306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1338396072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0941314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98635673522949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1565284729004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962366104126</t>
   </si>
   <si>
     <t xml:space="preserve">10.2359447479248</t>
@@ -1385,28 +1385,28 @@
     <t xml:space="preserve">10.2501239776611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2132539749146</t>
+    <t xml:space="preserve">10.2132530212402</t>
   </si>
   <si>
     <t xml:space="preserve">10.167875289917</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90694141387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9296293258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1877269744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2302722930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0203905105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.19056224823</t>
+    <t xml:space="preserve">9.90694046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92963123321533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1877279281616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2302732467651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0203895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1905641555786</t>
   </si>
   <si>
     <t xml:space="preserve">10.182056427002</t>
@@ -1415,40 +1415,40 @@
     <t xml:space="preserve">10.0317354202271</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97784614562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81618309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88708686828613</t>
+    <t xml:space="preserve">9.97784805297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81618118286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88708877563477</t>
   </si>
   <si>
     <t xml:space="preserve">9.89559650421143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81334590911865</t>
+    <t xml:space="preserve">9.81334686279297</t>
   </si>
   <si>
     <t xml:space="preserve">9.97500991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065770149231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1395130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0005369186401</t>
+    <t xml:space="preserve">10.0657691955566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1395120620728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0005359649658</t>
   </si>
   <si>
     <t xml:space="preserve">10.0686054229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73676776885986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83603668212891</t>
+    <t xml:space="preserve">9.73676872253418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83603572845459</t>
   </si>
   <si>
     <t xml:space="preserve">9.89276027679443</t>
@@ -1469,7 +1469,7 @@
     <t xml:space="preserve">9.94948577880859</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0714416503906</t>
+    <t xml:space="preserve">10.0714426040649</t>
   </si>
   <si>
     <t xml:space="preserve">9.93814086914062</t>
@@ -1481,7 +1481,7 @@
     <t xml:space="preserve">9.42761898040771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10145282745361</t>
+    <t xml:space="preserve">9.10145378112793</t>
   </si>
   <si>
     <t xml:space="preserve">9.21773815155029</t>
@@ -1490,7 +1490,7 @@
     <t xml:space="preserve">9.12414264678955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24326419830322</t>
+    <t xml:space="preserve">9.24326515197754</t>
   </si>
   <si>
     <t xml:space="preserve">9.20072078704834</t>
@@ -1502,7 +1502,7 @@
     <t xml:space="preserve">9.51369762420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39841747283936</t>
+    <t xml:space="preserve">9.39841651916504</t>
   </si>
   <si>
     <t xml:space="preserve">9.47206783294678</t>
@@ -1511,34 +1511,34 @@
     <t xml:space="preserve">9.4400463104248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3375768661499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98533630371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02696323394775</t>
+    <t xml:space="preserve">9.33757591247559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98533535003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02696514129639</t>
   </si>
   <si>
     <t xml:space="preserve">8.89887619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34397983551025</t>
+    <t xml:space="preserve">9.34398078918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.31836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93730354309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92129039764404</t>
+    <t xml:space="preserve">8.9373025894165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92129135131836</t>
   </si>
   <si>
     <t xml:space="preserve">8.93410015106201</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64590454101562</t>
+    <t xml:space="preserve">8.64590358734131</t>
   </si>
   <si>
     <t xml:space="preserve">8.83803462982178</t>
@@ -1550,43 +1550,43 @@
     <t xml:space="preserve">8.72275638580322</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71635246276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64270305633545</t>
+    <t xml:space="preserve">8.71635150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64270210266113</t>
   </si>
   <si>
     <t xml:space="preserve">8.82842922210693</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80601215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83163166046143</t>
+    <t xml:space="preserve">8.8060131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83163070678711</t>
   </si>
   <si>
     <t xml:space="preserve">8.66511726379395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73556709289551</t>
+    <t xml:space="preserve">8.73556423187256</t>
   </si>
   <si>
     <t xml:space="preserve">8.5178165435791</t>
   </si>
   <si>
-    <t xml:space="preserve">8.4889965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56905174255371</t>
+    <t xml:space="preserve">8.48899745941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56905078887939</t>
   </si>
   <si>
     <t xml:space="preserve">8.45697498321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39613342285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51141262054443</t>
+    <t xml:space="preserve">8.39613246917725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51141166687012</t>
   </si>
   <si>
     <t xml:space="preserve">8.53062534332275</t>
@@ -1595,7 +1595,7 @@
     <t xml:space="preserve">8.53702926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54343223571777</t>
+    <t xml:space="preserve">8.54343318939209</t>
   </si>
   <si>
     <t xml:space="preserve">8.71314907073975</t>
@@ -1607,13 +1607,13 @@
     <t xml:space="preserve">8.36411190032959</t>
   </si>
   <si>
-    <t xml:space="preserve">8.3320894241333</t>
+    <t xml:space="preserve">8.33209037780762</t>
   </si>
   <si>
     <t xml:space="preserve">8.42175102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58506298065186</t>
+    <t xml:space="preserve">8.58506202697754</t>
   </si>
   <si>
     <t xml:space="preserve">8.57225322723389</t>
@@ -1622,49 +1622,49 @@
     <t xml:space="preserve">8.46017742156982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46658039093018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58185958862305</t>
+    <t xml:space="preserve">8.46658134460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58186149597168</t>
   </si>
   <si>
     <t xml:space="preserve">8.44096374511719</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09421062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01735877990723</t>
+    <t xml:space="preserve">9.09420967102051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01735782623291</t>
   </si>
   <si>
     <t xml:space="preserve">9.05578327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19988250732422</t>
+    <t xml:space="preserve">9.1998815536499</t>
   </si>
   <si>
     <t xml:space="preserve">9.18707466125488</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9180908203125</t>
+    <t xml:space="preserve">8.91808986663818</t>
   </si>
   <si>
     <t xml:space="preserve">8.87646198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03657150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18387126922607</t>
+    <t xml:space="preserve">9.03657054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18387031555176</t>
   </si>
   <si>
     <t xml:space="preserve">9.15505218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15184879302979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23510646820068</t>
+    <t xml:space="preserve">9.1518497467041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23510551452637</t>
   </si>
   <si>
     <t xml:space="preserve">9.16465854644775</t>
@@ -1676,37 +1676,37 @@
     <t xml:space="preserve">9.26072311401367</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25431823730469</t>
+    <t xml:space="preserve">9.254319190979</t>
   </si>
   <si>
     <t xml:space="preserve">9.20628643035889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20948791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22550010681152</t>
+    <t xml:space="preserve">9.20948886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22549915313721</t>
   </si>
   <si>
     <t xml:space="preserve">9.10701942443848</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92769622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76758766174316</t>
+    <t xml:space="preserve">8.92769718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76758670806885</t>
   </si>
   <si>
     <t xml:space="preserve">8.65871238708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68112659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7259578704834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61708450317383</t>
+    <t xml:space="preserve">8.68112754821777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.72595882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61708545684814</t>
   </si>
   <si>
     <t xml:space="preserve">8.78039646148682</t>
@@ -1718,13 +1718,13 @@
     <t xml:space="preserve">8.77719402313232</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78359699249268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95331382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97252655029297</t>
+    <t xml:space="preserve">8.78359889984131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95331478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97252750396729</t>
   </si>
   <si>
     <t xml:space="preserve">8.96612167358398</t>
@@ -1736,22 +1736,22 @@
     <t xml:space="preserve">8.86045074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32568454742432</t>
+    <t xml:space="preserve">8.32568550109863</t>
   </si>
   <si>
     <t xml:space="preserve">8.22321510314941</t>
   </si>
   <si>
-    <t xml:space="preserve">8.29366302490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53382682800293</t>
+    <t xml:space="preserve">8.29366397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53382778167725</t>
   </si>
   <si>
     <t xml:space="preserve">8.48259258270264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40253734588623</t>
+    <t xml:space="preserve">8.40253829956055</t>
   </si>
   <si>
     <t xml:space="preserve">8.14956474304199</t>
@@ -1760,61 +1760,61 @@
     <t xml:space="preserve">8.06630706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07271289825439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77490854263306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74929094314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67884397506714</t>
+    <t xml:space="preserve">8.07271099090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77491044998169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74929189682007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67884302139282</t>
   </si>
   <si>
     <t xml:space="preserve">7.87417650222778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73007869720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53474378585815</t>
+    <t xml:space="preserve">7.73007822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53474473953247</t>
   </si>
   <si>
     <t xml:space="preserve">7.42266893386841</t>
   </si>
   <si>
-    <t xml:space="preserve">7.25295352935791</t>
+    <t xml:space="preserve">7.25295305252075</t>
   </si>
   <si>
     <t xml:space="preserve">7.21772813796997</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08003425598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11205673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84947729110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9711594581604</t>
+    <t xml:space="preserve">7.08003520965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11205625534058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84947681427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97115993499756</t>
   </si>
   <si>
     <t xml:space="preserve">7.04160785675049</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03520441055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04801177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94234037399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95194721221924</t>
+    <t xml:space="preserve">7.03520393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04801273345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94234180450439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9519476890564</t>
   </si>
   <si>
     <t xml:space="preserve">7.00958681106567</t>
@@ -1823,67 +1823,67 @@
     <t xml:space="preserve">7.1312689781189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97436237335205</t>
+    <t xml:space="preserve">6.97436189651489</t>
   </si>
   <si>
     <t xml:space="preserve">6.83026361465454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95515012741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80144453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7662205696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85908365249634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62852573394775</t>
+    <t xml:space="preserve">6.95514917373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80144500732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76622009277344</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8590841293335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62852621078491</t>
   </si>
   <si>
     <t xml:space="preserve">6.70537900924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74700593948364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86548852920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1632924079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09604549407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06722593307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02239608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23053741455078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05761909484863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80464649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89110612869263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71818780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73740005493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95835113525391</t>
+    <t xml:space="preserve">6.7470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86548757553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16329145431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09604597091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06722545623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02239465713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23053789138794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05761957168579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80464553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89110517501831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71818685531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73740100860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95835161209106</t>
   </si>
   <si>
     <t xml:space="preserve">7.01278877258301</t>
@@ -1892,154 +1892,154 @@
     <t xml:space="preserve">6.88790369033813</t>
   </si>
   <si>
-    <t xml:space="preserve">6.45880937576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39796876907349</t>
+    <t xml:space="preserve">6.45881032943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39796924591064</t>
   </si>
   <si>
     <t xml:space="preserve">6.1520414352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15844535827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96375274658203</t>
+    <t xml:space="preserve">6.15844488143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96375226974487</t>
   </si>
   <si>
     <t xml:space="preserve">6.10592985153198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10721015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39925003051758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64453601837158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6317286491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59010076522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50043869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60290908813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59650421142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41718149185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52285432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4203839302063</t>
+    <t xml:space="preserve">6.10721063613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39925050735474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6445369720459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63172817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5900993347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50043916702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60290956497192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59650468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41718053817749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52285385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42038440704346</t>
   </si>
   <si>
     <t xml:space="preserve">6.47802305221558</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44600248336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32624053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2673192024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74380588531494</t>
+    <t xml:space="preserve">6.44600200653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32624006271362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26732015609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74380493164062</t>
   </si>
   <si>
     <t xml:space="preserve">7.09924745559692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30738973617554</t>
+    <t xml:space="preserve">7.30739068984985</t>
   </si>
   <si>
     <t xml:space="preserve">7.19851493835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08964157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11846113204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15368461608887</t>
+    <t xml:space="preserve">7.08964061737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11846160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15368556976318</t>
   </si>
   <si>
     <t xml:space="preserve">7.15688610076904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17930221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04481172561646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99357604980469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27216672897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4482855796814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75889682769775</t>
+    <t xml:space="preserve">7.17930126190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0448112487793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99357557296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27216577529907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44828748703003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75889778137207</t>
   </si>
   <si>
     <t xml:space="preserve">7.57637214660645</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72687530517578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83895254135132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82614421844482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84535646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8997950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9126033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98305130004883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88058090209961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91900825500488</t>
+    <t xml:space="preserve">7.7268762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83895349502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82614469528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8453574180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89979457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91260290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98305177688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88058137893677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91900634765625</t>
   </si>
   <si>
     <t xml:space="preserve">8.23282146453857</t>
   </si>
   <si>
-    <t xml:space="preserve">8.1207447052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.26164150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47298622131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46337795257568</t>
+    <t xml:space="preserve">8.12074565887451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.26164054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47298717498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46337890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.84764194488525</t>
@@ -2048,25 +2048,25 @@
     <t xml:space="preserve">8.91168594360352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2639274597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33117198944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53291034698486</t>
+    <t xml:space="preserve">9.26392650604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33117294311523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53290939331055</t>
   </si>
   <si>
     <t xml:space="preserve">9.67700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51049327850342</t>
+    <t xml:space="preserve">9.51049423217773</t>
   </si>
   <si>
     <t xml:space="preserve">9.42083263397217</t>
   </si>
   <si>
-    <t xml:space="preserve">9.32796955108643</t>
+    <t xml:space="preserve">9.32796859741211</t>
   </si>
   <si>
     <t xml:space="preserve">9.40482234954834</t>
@@ -2078,31 +2078,31 @@
     <t xml:space="preserve">9.55212211608887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57133674621582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.70262622833252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77627658843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81470203399658</t>
+    <t xml:space="preserve">9.57133483886719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7026252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77627563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8147029876709</t>
   </si>
   <si>
     <t xml:space="preserve">10.083685874939</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0356531143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1413259506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.21497631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.195761680603</t>
+    <t xml:space="preserve">10.0356521606445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1413249969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2149753570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1957626342773</t>
   </si>
   <si>
     <t xml:space="preserve">10.2694120407104</t>
@@ -2111,10 +2111,10 @@
     <t xml:space="preserve">10.2790193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5608129501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8490085601807</t>
+    <t xml:space="preserve">10.56081199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.849009513855</t>
   </si>
   <si>
     <t xml:space="preserve">10.868221282959</t>
@@ -2123,7 +2123,7 @@
     <t xml:space="preserve">10.8874340057373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0155210494995</t>
+    <t xml:space="preserve">11.0155220031738</t>
   </si>
   <si>
     <t xml:space="preserve">11.0603523254395</t>
@@ -2132,43 +2132,43 @@
     <t xml:space="preserve">11.281304359436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2909097671509</t>
+    <t xml:space="preserve">11.2909107208252</t>
   </si>
   <si>
     <t xml:space="preserve">11.5118608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5278730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4958515167236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3773698806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.326132774353</t>
+    <t xml:space="preserve">11.5278739929199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4958486557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3773679733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3261346817017</t>
   </si>
   <si>
     <t xml:space="preserve">11.4926471710205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8105812072754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9899044036865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5992383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219259262085</t>
+    <t xml:space="preserve">10.8105802536011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9899053573608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5992374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219268798828</t>
   </si>
   <si>
     <t xml:space="preserve">11.1404075622559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1141195297241</t>
+    <t xml:space="preserve">11.1141214370728</t>
   </si>
   <si>
     <t xml:space="preserve">10.7917680740356</t>
@@ -2180,13 +2180,13 @@
     <t xml:space="preserve">10.4203634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5780353546143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3993406295776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4273710250854</t>
+    <t xml:space="preserve">10.5780363082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3993396759033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4273719787598</t>
   </si>
   <si>
     <t xml:space="preserve">10.2872190475464</t>
@@ -2195,43 +2195,43 @@
     <t xml:space="preserve">10.3888282775879</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4238662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.367805480957</t>
+    <t xml:space="preserve">10.4238681793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3678064346313</t>
   </si>
   <si>
     <t xml:space="preserve">10.7322025299072</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7742500305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4448909759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079593658447</t>
+    <t xml:space="preserve">10.7742490768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4448900222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079584121704</t>
   </si>
   <si>
     <t xml:space="preserve">10.5149669647217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6305932998657</t>
+    <t xml:space="preserve">10.6305923461914</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127918243408</t>
   </si>
   <si>
-    <t xml:space="preserve">11.128134727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1876993179321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3523797988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5731191635132</t>
+    <t xml:space="preserve">11.1281356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1877012252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3523817062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5731201171875</t>
   </si>
   <si>
     <t xml:space="preserve">11.6151676177979</t>
@@ -2243,25 +2243,25 @@
     <t xml:space="preserve">11.7342967987061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429136276245</t>
+    <t xml:space="preserve">11.8429145812988</t>
   </si>
   <si>
     <t xml:space="preserve">11.7097692489624</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6291818618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8639373779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9059829711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9200000762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0496406555176</t>
+    <t xml:space="preserve">11.6291809082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.863938331604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9059839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9199991226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0496387481689</t>
   </si>
   <si>
     <t xml:space="preserve">12.2318382263184</t>
@@ -2270,28 +2270,28 @@
     <t xml:space="preserve">12.2248306274414</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2984094619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2143201828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3159303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2773876190186</t>
+    <t xml:space="preserve">12.2984113693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.214319229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3159313201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2773885726929</t>
   </si>
   <si>
     <t xml:space="preserve">12.4175415039062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684883117676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1267232894897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0391292572021</t>
+    <t xml:space="preserve">12.3684864044189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1267242431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0391283035278</t>
   </si>
   <si>
     <t xml:space="preserve">11.8464193344116</t>
@@ -2300,52 +2300,52 @@
     <t xml:space="preserve">12.0636558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">12.140739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1232194900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1092052459717</t>
+    <t xml:space="preserve">12.1407403945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1232204437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.109206199646</t>
   </si>
   <si>
     <t xml:space="preserve">12.0321207046509</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8779544830322</t>
+    <t xml:space="preserve">11.8779535293579</t>
   </si>
   <si>
     <t xml:space="preserve">11.9760608673096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6887464523315</t>
+    <t xml:space="preserve">11.6887474060059</t>
   </si>
   <si>
     <t xml:space="preserve">11.4680051803589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4890289306641</t>
+    <t xml:space="preserve">11.4890298843384</t>
   </si>
   <si>
     <t xml:space="preserve">11.4820213317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6782360076904</t>
+    <t xml:space="preserve">11.6782350540161</t>
   </si>
   <si>
     <t xml:space="preserve">11.2472648620605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0370349884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1001043319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7216911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9284162521362</t>
+    <t xml:space="preserve">11.037036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1001052856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7216920852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9284181594849</t>
   </si>
   <si>
     <t xml:space="preserve">11.1561660766602</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">11.496036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4469804763794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1841974258423</t>
+    <t xml:space="preserve">11.4469833374023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.184196472168</t>
   </si>
   <si>
     <t xml:space="preserve">11.3243494033813</t>
@@ -2366,10 +2366,10 @@
     <t xml:space="preserve">11.2752952575684</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0615615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4049377441406</t>
+    <t xml:space="preserve">11.061562538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4049367904663</t>
   </si>
   <si>
     <t xml:space="preserve">11.2297458648682</t>
@@ -2378,7 +2378,7 @@
     <t xml:space="preserve">11.4119453430176</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4995403289795</t>
+    <t xml:space="preserve">11.4995393753052</t>
   </si>
   <si>
     <t xml:space="preserve">11.790358543396</t>
@@ -2387,22 +2387,22 @@
     <t xml:space="preserve">11.8814573287964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8288993835449</t>
+    <t xml:space="preserve">11.8288984298706</t>
   </si>
   <si>
     <t xml:space="preserve">11.9550371170044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6677217483521</t>
+    <t xml:space="preserve">11.6677236557007</t>
   </si>
   <si>
     <t xml:space="preserve">11.6712274551392</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8113794326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9970827102661</t>
+    <t xml:space="preserve">11.8113803863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9970836639404</t>
   </si>
   <si>
     <t xml:space="preserve">11.9410219192505</t>
@@ -2417,7 +2417,7 @@
     <t xml:space="preserve">12.2703819274902</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2738838195801</t>
+    <t xml:space="preserve">12.2738847732544</t>
   </si>
   <si>
     <t xml:space="preserve">12.102198600769</t>
@@ -2426,16 +2426,16 @@
     <t xml:space="preserve">12.0951900482178</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9725561141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0146007537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9865713119507</t>
+    <t xml:space="preserve">11.9725551605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0146017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9865703582764</t>
   </si>
   <si>
     <t xml:space="preserve">11.6011514663696</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">11.5485935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5941438674927</t>
+    <t xml:space="preserve">11.5941429138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.4259605407715</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">11.6852426528931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7693347930908</t>
+    <t xml:space="preserve">11.7693338394165</t>
   </si>
   <si>
     <t xml:space="preserve">11.7027626037598</t>
@@ -2477,124 +2477,124 @@
     <t xml:space="preserve">12.7539072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9641370773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7188692092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7889471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.795952796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9886646270752</t>
+    <t xml:space="preserve">12.9641380310059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7188701629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7889461517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7959547042847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9886627197266</t>
   </si>
   <si>
     <t xml:space="preserve">13.1743659973145</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9080762863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0412225723267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094049453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6649026870728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.899658203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007024765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3656673431396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389636993408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0173768997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1365079879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5289344787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9493932723999</t>
+    <t xml:space="preserve">12.9080772399902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.041220664978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094058990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6649017333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8996562957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007034301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.365665435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389646530151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0173759460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1365041732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5289335250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9493942260742</t>
   </si>
   <si>
     <t xml:space="preserve">15.7181396484375</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9213609695435</t>
+    <t xml:space="preserve">15.9213619232178</t>
   </si>
   <si>
     <t xml:space="preserve">16.1035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9914388656616</t>
+    <t xml:space="preserve">15.9914379119873</t>
   </si>
   <si>
     <t xml:space="preserve">16.124584197998</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4118995666504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5940971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5100040435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2086753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0474987030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8863248825073</t>
+    <t xml:space="preserve">16.4118976593018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5940952301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5100021362305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2086734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0475006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.886326789856</t>
   </si>
   <si>
     <t xml:space="preserve">15.4868879318237</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7531795501709</t>
+    <t xml:space="preserve">15.8232555389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7531785964966</t>
   </si>
   <si>
     <t xml:space="preserve">15.7251491546631</t>
   </si>
   <si>
-    <t xml:space="preserve">15.157527923584</t>
+    <t xml:space="preserve">15.1575307846069</t>
   </si>
   <si>
     <t xml:space="preserve">15.3817739486694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2626447677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2976808547974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0804452896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2836666107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2205982208252</t>
+    <t xml:space="preserve">15.2626428604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2976818084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0804471969604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2836656570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2206001281738</t>
   </si>
   <si>
     <t xml:space="preserve">15.09446144104</t>
@@ -2603,37 +2603,37 @@
     <t xml:space="preserve">15.0664300918579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0454053878784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8562021255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9122638702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1715440750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8702154159546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721080780029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3537454605103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5029945373535</t>
+    <t xml:space="preserve">15.0454063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8562002182007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9122619628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1715431213379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8702163696289</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721071243286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3537425994873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5029964447021</t>
   </si>
   <si>
     <t xml:space="preserve">16.5800800323486</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4189033508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7062187194824</t>
+    <t xml:space="preserve">16.4189052581787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7062168121338</t>
   </si>
   <si>
     <t xml:space="preserve">16.8043251037598</t>
@@ -2645,46 +2645,46 @@
     <t xml:space="preserve">16.5660648345947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9865226745605</t>
+    <t xml:space="preserve">16.9865245819092</t>
   </si>
   <si>
     <t xml:space="preserve">17.00754737854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5380363464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0545101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3978805541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4959907531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0685234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499582290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5709810256958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0334854125977</t>
+    <t xml:space="preserve">16.5380382537842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0545082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3978843688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4959888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0685214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499591827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5709800720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.033483505249</t>
   </si>
   <si>
     <t xml:space="preserve">15.9423847198486</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1666278839111</t>
+    <t xml:space="preserve">16.1666297912598</t>
   </si>
   <si>
     <t xml:space="preserve">16.6431484222412</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3908729553223</t>
+    <t xml:space="preserve">16.3908748626709</t>
   </si>
   <si>
     <t xml:space="preserve">16.762279510498</t>
@@ -2693,7 +2693,7 @@
     <t xml:space="preserve">16.7833023071289</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6711807250977</t>
+    <t xml:space="preserve">16.671178817749</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272434234619</t>
@@ -2708,61 +2708,61 @@
     <t xml:space="preserve">14.5198335647583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3516502380371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5478630065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7910394668579</t>
+    <t xml:space="preserve">14.3516511917114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5478639602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7910404205322</t>
   </si>
   <si>
     <t xml:space="preserve">13.4546728134155</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0272054672241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9956712722778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.347466468811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7202825546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3327674865723</t>
+    <t xml:space="preserve">13.0272064208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9956722259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3474655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7202816009521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3327684402466</t>
   </si>
   <si>
     <t xml:space="preserve">9.68806457519531</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81069946289062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25149726867676</t>
+    <t xml:space="preserve">9.81069850921631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25149822235107</t>
   </si>
   <si>
     <t xml:space="preserve">9.51988124847412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44420909881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02024555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70490264892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77497911453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49817752838135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59978818893433</t>
+    <t xml:space="preserve">8.4442081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0202465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70490217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77497959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49817562103271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59978771209717</t>
   </si>
   <si>
     <t xml:space="preserve">8.28653717041016</t>
@@ -2771,34 +2771,34 @@
     <t xml:space="preserve">9.06088161468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69507217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05037021636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87167549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23607158660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.87517833709717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07489585876465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68246936798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02233982086182</t>
+    <t xml:space="preserve">9.69507312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05036926269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87167453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2360725402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.87517929077148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07489681243896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68246841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0223388671875</t>
   </si>
   <si>
     <t xml:space="preserve">9.48834705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1680879592896</t>
+    <t xml:space="preserve">10.1680898666382</t>
   </si>
   <si>
     <t xml:space="preserve">10.2381649017334</t>
@@ -2810,55 +2810,55 @@
     <t xml:space="preserve">9.29914093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44630146026611</t>
+    <t xml:space="preserve">9.4463005065918</t>
   </si>
   <si>
     <t xml:space="preserve">9.51637744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58995914459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25359058380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33417797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49535465240479</t>
+    <t xml:space="preserve">9.58995819091797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2535924911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33417892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4953556060791</t>
   </si>
   <si>
     <t xml:space="preserve">9.47433185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3713111877441</t>
+    <t xml:space="preserve">10.3713092803955</t>
   </si>
   <si>
     <t xml:space="preserve">10.8162956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2122259140015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793630599976</t>
+    <t xml:space="preserve">11.2122268676758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793640136719</t>
   </si>
   <si>
     <t xml:space="preserve">10.7602338790894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8618440628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5324840545654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6025619506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6095705032349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.539493560791</t>
+    <t xml:space="preserve">10.8618450164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5324859619141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6025629043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6095695495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5394926071167</t>
   </si>
   <si>
     <t xml:space="preserve">10.4133558273315</t>
@@ -2873,28 +2873,28 @@
     <t xml:space="preserve">10.7654342651367</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6414785385132</t>
+    <t xml:space="preserve">10.6414775848389</t>
   </si>
   <si>
     <t xml:space="preserve">10.7691898345947</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8743658065796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9757852554321</t>
+    <t xml:space="preserve">10.8743648529053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9757843017578</t>
   </si>
   <si>
     <t xml:space="preserve">10.9720287322998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.358922958374</t>
+    <t xml:space="preserve">11.3589220046997</t>
   </si>
   <si>
     <t xml:space="preserve">11.1936473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3251161575317</t>
+    <t xml:space="preserve">11.3251152038574</t>
   </si>
   <si>
     <t xml:space="preserve">11.5204429626465</t>
@@ -2912,40 +2912,40 @@
     <t xml:space="preserve">12.9966506958008</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4407243728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3956499099731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.648154258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6105928421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5166854858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7721109390259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6669368743896</t>
+    <t xml:space="preserve">12.4407262802124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3956508636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6481552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6105918884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5166864395142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7721118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.666934967041</t>
   </si>
   <si>
     <t xml:space="preserve">11.5091733932495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7157669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5730304718018</t>
+    <t xml:space="preserve">11.7157678604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5730295181274</t>
   </si>
   <si>
     <t xml:space="preserve">11.8284549713135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2687721252441</t>
+    <t xml:space="preserve">11.2687730789185</t>
   </si>
   <si>
     <t xml:space="preserve">11.4490728378296</t>
@@ -2960,7 +2960,7 @@
     <t xml:space="preserve">11.4265356063843</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3664350509644</t>
+    <t xml:space="preserve">11.3664360046387</t>
   </si>
   <si>
     <t xml:space="preserve">11.663179397583</t>
@@ -2975,16 +2975,16 @@
     <t xml:space="preserve">11.7608423233032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4753675460815</t>
+    <t xml:space="preserve">11.4753665924072</t>
   </si>
   <si>
     <t xml:space="preserve">11.6706924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8585042953491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8434810638428</t>
+    <t xml:space="preserve">11.8585052490234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8434801101685</t>
   </si>
   <si>
     <t xml:space="preserve">12.3580884933472</t>
@@ -2993,25 +2993,25 @@
     <t xml:space="preserve">12.3205242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8013257980347</t>
+    <t xml:space="preserve">12.801326751709</t>
   </si>
   <si>
     <t xml:space="preserve">12.6999073028564</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7337141036987</t>
+    <t xml:space="preserve">12.733715057373</t>
   </si>
   <si>
     <t xml:space="preserve">12.8351316452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5684375762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6097564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3731107711792</t>
+    <t xml:space="preserve">12.5684385299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6097555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3731117248535</t>
   </si>
   <si>
     <t xml:space="preserve">12.4369697570801</t>
@@ -3026,13 +3026,13 @@
     <t xml:space="preserve">12.3693561553955</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3505764007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4745311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4933128356934</t>
+    <t xml:space="preserve">12.3505754470825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4745321273804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.493311882019</t>
   </si>
   <si>
     <t xml:space="preserve">12.470775604248</t>
@@ -3041,16 +3041,16 @@
     <t xml:space="preserve">12.8276205062866</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7938146591187</t>
+    <t xml:space="preserve">12.7938137054443</t>
   </si>
   <si>
     <t xml:space="preserve">12.6585884094238</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5984878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4557495117188</t>
+    <t xml:space="preserve">12.5984888076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4557504653931</t>
   </si>
   <si>
     <t xml:space="preserve">12.5158500671387</t>
@@ -3059,16 +3059,16 @@
     <t xml:space="preserve">12.3468179702759</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2191047668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6661024093628</t>
+    <t xml:space="preserve">12.21910572052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6661014556885</t>
   </si>
   <si>
     <t xml:space="preserve">12.6247816085815</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5083360671997</t>
+    <t xml:space="preserve">12.508337020874</t>
   </si>
   <si>
     <t xml:space="preserve">12.3881378173828</t>
@@ -3080,13 +3080,13 @@
     <t xml:space="preserve">12.0650997161865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.264181137085</t>
+    <t xml:space="preserve">12.2641820907593</t>
   </si>
   <si>
     <t xml:space="preserve">11.9749488830566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1552505493164</t>
+    <t xml:space="preserve">12.1552486419678</t>
   </si>
   <si>
     <t xml:space="preserve">11.8847990036011</t>
@@ -3101,25 +3101,25 @@
     <t xml:space="preserve">12.2078371047974</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3843822479248</t>
+    <t xml:space="preserve">12.3843812942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.5120944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6285381317139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4257001876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8547487258911</t>
+    <t xml:space="preserve">12.6285390853882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4257011413574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8547477722168</t>
   </si>
   <si>
     <t xml:space="preserve">11.8322114944458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8096752166748</t>
+    <t xml:space="preserve">11.8096742630005</t>
   </si>
   <si>
     <t xml:space="preserve">11.6181049346924</t>
@@ -3137,13 +3137,13 @@
     <t xml:space="preserve">11.5842990875244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4640989303589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3626794815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7120122909546</t>
+    <t xml:space="preserve">11.4640979766846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3626804351807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7120113372803</t>
   </si>
   <si>
     <t xml:space="preserve">11.8772869110107</t>
@@ -3158,28 +3158,28 @@
     <t xml:space="preserve">12.200325012207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2904748916626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1139316558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4031629562378</t>
+    <t xml:space="preserve">12.2904758453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1139307022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4031620025635</t>
   </si>
   <si>
     <t xml:space="preserve">11.944899559021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0989055633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1514930725098</t>
+    <t xml:space="preserve">12.0989065170288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1514921188354</t>
   </si>
   <si>
     <t xml:space="preserve">12.0801248550415</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7007436752319</t>
+    <t xml:space="preserve">11.7007417678833</t>
   </si>
   <si>
     <t xml:space="preserve">11.5241985321045</t>
@@ -3188,55 +3188,55 @@
     <t xml:space="preserve">10.8255338668823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6452341079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8893909454346</t>
+    <t xml:space="preserve">10.6452350616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8893899917603</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499923706055</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6443977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8209419250488</t>
+    <t xml:space="preserve">11.64439868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8209428787231</t>
   </si>
   <si>
     <t xml:space="preserve">12.0275363922119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8885555267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5834627151489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4332122802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4106750488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1393871307373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2070007324219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5600900650024</t>
+    <t xml:space="preserve">11.8885545730591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5834636688232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4332113265991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4106760025024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1393890380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2070016860962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5600891113281</t>
   </si>
   <si>
     <t xml:space="preserve">13.2370529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2595891952515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2220277786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6727771759033</t>
+    <t xml:space="preserve">13.2595882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2220268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6727781295776</t>
   </si>
   <si>
     <t xml:space="preserve">13.357253074646</t>
@@ -3245,13 +3245,13 @@
     <t xml:space="preserve">13.379789352417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2746143341064</t>
+    <t xml:space="preserve">13.2746133804321</t>
   </si>
   <si>
     <t xml:space="preserve">13.5375537872314</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1882200241089</t>
+    <t xml:space="preserve">13.1882209777832</t>
   </si>
   <si>
     <t xml:space="preserve">13.2821273803711</t>
@@ -3260,16 +3260,16 @@
     <t xml:space="preserve">13.2896394729614</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2295389175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9327955245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1731948852539</t>
+    <t xml:space="preserve">13.2295398712158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619272232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9327936172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1731958389282</t>
   </si>
   <si>
     <t xml:space="preserve">13.1919765472412</t>
@@ -3278,25 +3278,25 @@
     <t xml:space="preserve">13.1957330703735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0154323577881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8238620758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3272008895874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361343383789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4962339401245</t>
+    <t xml:space="preserve">13.0154333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.82386302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3272018432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361333847046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4962348937988</t>
   </si>
   <si>
     <t xml:space="preserve">13.4323768615723</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3497400283813</t>
+    <t xml:space="preserve">13.3497409820557</t>
   </si>
   <si>
     <t xml:space="preserve">13.3384704589844</t>
@@ -3305,16 +3305,16 @@
     <t xml:space="preserve">13.1994886398315</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4135961532593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4248666763306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3985691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3910598754883</t>
+    <t xml:space="preserve">13.413595199585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4248657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3985710144043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.391058921814</t>
   </si>
   <si>
     <t xml:space="preserve">13.6802892684937</t>
@@ -3323,19 +3323,19 @@
     <t xml:space="preserve">14.2099227905273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9582538604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8305397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.89439868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8380527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9319591522217</t>
+    <t xml:space="preserve">13.958251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8305406570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943977355957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8380517959595</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.931960105896</t>
   </si>
   <si>
     <t xml:space="preserve">13.7328786849976</t>
@@ -3344,40 +3344,40 @@
     <t xml:space="preserve">13.4398889541626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4060840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1093397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3009090423584</t>
+    <t xml:space="preserve">13.4060831069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.109338760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3009071350098</t>
   </si>
   <si>
     <t xml:space="preserve">13.04172706604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4887218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676021575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7216081619263</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3526611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5855484008789</t>
+    <t xml:space="preserve">13.4887208938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676012039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7216091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3526592254639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5855474472046</t>
   </si>
   <si>
     <t xml:space="preserve">15.055082321167</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0926427841187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0250310897827</t>
+    <t xml:space="preserve">15.092643737793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.025032043457</t>
   </si>
   <si>
     <t xml:space="preserve">15.1978197097778</t>
@@ -3386,43 +3386,43 @@
     <t xml:space="preserve">14.8447303771973</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7207736968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9198560714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.822193145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5329599380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6005725860596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315404891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2812910079956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9499053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7846298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7095050811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6644306182861</t>
+    <t xml:space="preserve">14.7207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9198551177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8221921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5329608917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6005735397339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4315423965454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2812919616699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9499034881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.784631729126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7095041275024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6644296646118</t>
   </si>
   <si>
     <t xml:space="preserve">14.4240293502808</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7958993911743</t>
+    <t xml:space="preserve">14.7958984375</t>
   </si>
   <si>
     <t xml:space="preserve">14.7620916366577</t>
@@ -3437,7 +3437,7 @@
     <t xml:space="preserve">14.4090042114258</t>
   </si>
   <si>
-    <t xml:space="preserve">14.194899559021</t>
+    <t xml:space="preserve">14.1948976516724</t>
   </si>
   <si>
     <t xml:space="preserve">14.1197729110718</t>
@@ -3449,55 +3449,55 @@
     <t xml:space="preserve">14.2775354385376</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3226118087769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202718734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714408874512</t>
+    <t xml:space="preserve">14.3226099014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202747344971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714418411255</t>
   </si>
   <si>
     <t xml:space="preserve">14.2925596237183</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4653463363647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7470674514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5930604934692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8898048400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8484859466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2504062652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1001558303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1151819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0701055526733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7245292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7508249282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.814679145813</t>
+    <t xml:space="preserve">14.4653472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7470655441284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5930624008179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8898057937622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.848484992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2504043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1001539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1151809692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0701036453247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7245302200317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7508239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8146800994873</t>
   </si>
   <si>
     <t xml:space="preserve">14.8184366226196</t>
@@ -3506,49 +3506,49 @@
     <t xml:space="preserve">14.9837121963501</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0175161361694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7921419143677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9611749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1602554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.085129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1377182006836</t>
+    <t xml:space="preserve">15.0175189971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7921438217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9611730575562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1602563858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724435806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1377191543579</t>
   </si>
   <si>
     <t xml:space="preserve">15.3555822372437</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2579164505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2804536819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2729444503784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462301254272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8664321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8438940048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6410551071167</t>
+    <t xml:space="preserve">15.2579183578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2804546356201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2729434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8664302825928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8438959121704</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.641056060791</t>
   </si>
   <si>
     <t xml:space="preserve">15.7086696624756</t>
@@ -3563,22 +3563,22 @@
     <t xml:space="preserve">16.0814266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8841552734375</t>
+    <t xml:space="preserve">15.8841562271118</t>
   </si>
   <si>
     <t xml:space="preserve">15.8999404907227</t>
   </si>
   <si>
-    <t xml:space="preserve">15.955174446106</t>
+    <t xml:space="preserve">15.9551734924316</t>
   </si>
   <si>
     <t xml:space="preserve">16.0419731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0025196075439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0972080230713</t>
+    <t xml:space="preserve">16.0025215148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0972099304199</t>
   </si>
   <si>
     <t xml:space="preserve">16.1445541381836</t>
@@ -3599,13 +3599,13 @@
     <t xml:space="preserve">16.3497142791748</t>
   </si>
   <si>
-    <t xml:space="preserve">15.99462890625</t>
+    <t xml:space="preserve">15.9946298599243</t>
   </si>
   <si>
     <t xml:space="preserve">16.1208820343018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1919002532959</t>
+    <t xml:space="preserve">16.1918983459473</t>
   </si>
   <si>
     <t xml:space="preserve">16.0183010101318</t>
@@ -3614,19 +3614,19 @@
     <t xml:space="preserve">15.9472846984863</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8762674331665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2392425537109</t>
+    <t xml:space="preserve">15.8762683868408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2392444610596</t>
   </si>
   <si>
     <t xml:space="preserve">16.2471332550049</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5312023162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1287708282471</t>
+    <t xml:space="preserve">16.5312042236328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1287746429443</t>
   </si>
   <si>
     <t xml:space="preserve">16.2155704498291</t>
@@ -3638,7 +3638,7 @@
     <t xml:space="preserve">16.5943298339844</t>
   </si>
   <si>
-    <t xml:space="preserve">16.507532119751</t>
+    <t xml:space="preserve">16.5075302124023</t>
   </si>
   <si>
     <t xml:space="preserve">16.4838562011719</t>
@@ -3650,13 +3650,13 @@
     <t xml:space="preserve">16.2550258636475</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5233116149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8073787689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1624660491943</t>
+    <t xml:space="preserve">16.5233135223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8073806762695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1624641418457</t>
   </si>
   <si>
     <t xml:space="preserve">17.5254402160645</t>
@@ -3665,22 +3665,22 @@
     <t xml:space="preserve">17.3281726837158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1940307617188</t>
+    <t xml:space="preserve">17.1940288543701</t>
   </si>
   <si>
     <t xml:space="preserve">17.2492637634277</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1387920379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4702072143555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4938774108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2808265686035</t>
+    <t xml:space="preserve">17.1387939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4702053070068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4938793182373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2808284759521</t>
   </si>
   <si>
     <t xml:space="preserve">17.4070796966553</t>
@@ -3701,16 +3701,16 @@
     <t xml:space="preserve">18.1172504425049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2592849731445</t>
+    <t xml:space="preserve">18.2592868804932</t>
   </si>
   <si>
     <t xml:space="preserve">18.3224105834961</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2435035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4644451141357</t>
+    <t xml:space="preserve">18.2435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4644470214844</t>
   </si>
   <si>
     <t xml:space="preserve">18.2513942718506</t>
@@ -3719,19 +3719,19 @@
     <t xml:space="preserve">18.2829570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">18.424991607666</t>
+    <t xml:space="preserve">18.4249935150146</t>
   </si>
   <si>
     <t xml:space="preserve">18.3539752960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4407730102539</t>
+    <t xml:space="preserve">18.4407749176025</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906982421875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6696071624756</t>
+    <t xml:space="preserve">18.669605255127</t>
   </si>
   <si>
     <t xml:space="preserve">18.748514175415</t>
@@ -3740,7 +3740,7 @@
     <t xml:space="preserve">18.7642955780029</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8037490844727</t>
+    <t xml:space="preserve">18.8037509918213</t>
   </si>
   <si>
     <t xml:space="preserve">18.7011699676514</t>
@@ -3749,7 +3749,7 @@
     <t xml:space="preserve">18.7564067840576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7406253814697</t>
+    <t xml:space="preserve">18.7406234741211</t>
   </si>
   <si>
     <t xml:space="preserve">18.6459331512451</t>
@@ -3758,10 +3758,10 @@
     <t xml:space="preserve">18.7169513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5749187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8432006835938</t>
+    <t xml:space="preserve">18.5749168395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.843204498291</t>
   </si>
   <si>
     <t xml:space="preserve">18.8984413146973</t>
@@ -3782,19 +3782,19 @@
     <t xml:space="preserve">18.8589859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9378929138184</t>
+    <t xml:space="preserve">18.937894821167</t>
   </si>
   <si>
     <t xml:space="preserve">19.2614154815674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1430549621582</t>
+    <t xml:space="preserve">19.1430530548096</t>
   </si>
   <si>
     <t xml:space="preserve">18.7327327728271</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5985870361328</t>
+    <t xml:space="preserve">18.5985889434814</t>
   </si>
   <si>
     <t xml:space="preserve">18.7721881866455</t>
@@ -3806,13 +3806,13 @@
     <t xml:space="preserve">18.4013195037842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6222648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2356128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1409244537354</t>
+    <t xml:space="preserve">18.6222629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2356147766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1409225463867</t>
   </si>
   <si>
     <t xml:space="preserve">18.4328842163086</t>
@@ -3821,16 +3821,16 @@
     <t xml:space="preserve">18.6380443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8353137969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7090587615967</t>
+    <t xml:space="preserve">18.8353157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7090606689453</t>
   </si>
   <si>
     <t xml:space="preserve">19.5375938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4034481048584</t>
+    <t xml:space="preserve">19.403450012207</t>
   </si>
   <si>
     <t xml:space="preserve">19.5297012329102</t>
@@ -3842,7 +3842,7 @@
     <t xml:space="preserve">19.8374423980713</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6322822570801</t>
+    <t xml:space="preserve">19.6322803497314</t>
   </si>
   <si>
     <t xml:space="preserve">19.6954078674316</t>
@@ -3857,19 +3857,19 @@
     <t xml:space="preserve">20.066276550293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1057300567627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0504951477051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0741691589355</t>
+    <t xml:space="preserve">20.1057281494141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0504932403564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0741672515869</t>
   </si>
   <si>
     <t xml:space="preserve">20.0189323425293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2398719787598</t>
+    <t xml:space="preserve">20.2398738861084</t>
   </si>
   <si>
     <t xml:space="preserve">20.9027004241943</t>
@@ -3881,7 +3881,7 @@
     <t xml:space="preserve">21.1946601867676</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9421539306641</t>
+    <t xml:space="preserve">20.9421558380127</t>
   </si>
   <si>
     <t xml:space="preserve">20.9816074371338</t>
@@ -3893,13 +3893,13 @@
     <t xml:space="preserve">20.2162017822266</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1372928619385</t>
+    <t xml:space="preserve">20.1372947692871</t>
   </si>
   <si>
     <t xml:space="preserve">20.0820579528809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1036014556885</t>
+    <t xml:space="preserve">19.1035976409912</t>
   </si>
   <si>
     <t xml:space="preserve">19.316650390625</t>
@@ -3908,13 +3908,13 @@
     <t xml:space="preserve">19.3324337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4744701385498</t>
+    <t xml:space="preserve">19.4744663238525</t>
   </si>
   <si>
     <t xml:space="preserve">19.3087596893311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1746158599854</t>
+    <t xml:space="preserve">19.1746196746826</t>
   </si>
   <si>
     <t xml:space="preserve">19.2377433776855</t>
@@ -3929,7 +3929,7 @@
     <t xml:space="preserve">19.024694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8116397857666</t>
+    <t xml:space="preserve">18.8116416931152</t>
   </si>
   <si>
     <t xml:space="preserve">19.0168018341064</t>
@@ -3941,61 +3941,61 @@
     <t xml:space="preserve">18.9142208099365</t>
   </si>
   <si>
-    <t xml:space="preserve">19.16672706604</t>
+    <t xml:space="preserve">19.1667251586914</t>
   </si>
   <si>
     <t xml:space="preserve">19.3561058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.411340713501</t>
+    <t xml:space="preserve">19.4113426208496</t>
   </si>
   <si>
     <t xml:space="preserve">19.7269706726074</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9005680084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9479160308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3403244018555</t>
+    <t xml:space="preserve">19.9005699157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9479141235352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3403224945068</t>
   </si>
   <si>
     <t xml:space="preserve">19.5770473480225</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6165008544922</t>
+    <t xml:space="preserve">19.6165027618408</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268211364746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8711395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9342651367188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.5791759490967</t>
+    <t xml:space="preserve">20.8711376190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9342632293701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.5791778564453</t>
   </si>
   <si>
     <t xml:space="preserve">20.6817569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3187808990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.884786605835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2119407653809</t>
+    <t xml:space="preserve">20.3187828063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8847904205322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2119388580322</t>
   </si>
   <si>
     <t xml:space="preserve">18.2671756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3934288024902</t>
+    <t xml:space="preserve">18.3934268951416</t>
   </si>
   <si>
     <t xml:space="preserve">19.0325832366943</t>
@@ -4010,13 +4010,13 @@
     <t xml:space="preserve">18.7958583831787</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3697566986084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3145198822021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8095111846924</t>
+    <t xml:space="preserve">18.369758605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3145217895508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8095092773438</t>
   </si>
   <si>
     <t xml:space="preserve">17.7463836669922</t>
@@ -4025,43 +4025,43 @@
     <t xml:space="preserve">17.9278717041016</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6416721343994</t>
+    <t xml:space="preserve">16.641674041748</t>
   </si>
   <si>
     <t xml:space="preserve">17.1782474517822</t>
   </si>
   <si>
-    <t xml:space="preserve">16.886287689209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6337852478027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4028186798096</t>
+    <t xml:space="preserve">16.8862895965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6337814331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4028205871582</t>
   </si>
   <si>
     <t xml:space="preserve">15.4501647949219</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6632165908813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0756664276123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.189769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5093460083008</t>
+    <t xml:space="preserve">15.663215637207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0756683349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1897687911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5093450546265</t>
   </si>
   <si>
     <t xml:space="preserve">15.8525943756104</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0441036224365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7916011810303</t>
+    <t xml:space="preserve">17.0441055297852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.791597366333</t>
   </si>
   <si>
     <t xml:space="preserve">16.4759674072266</t>
@@ -4073,22 +4073,22 @@
     <t xml:space="preserve">16.7837085723877</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4286231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.744255065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2413749694824</t>
+    <t xml:space="preserve">16.4286212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7442531585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2413730621338</t>
   </si>
   <si>
     <t xml:space="preserve">16.9415225982666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6732368469238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7600383758545</t>
+    <t xml:space="preserve">16.6732387542725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7600345611572</t>
   </si>
   <si>
     <t xml:space="preserve">16.318151473999</t>
@@ -4097,31 +4097,31 @@
     <t xml:space="preserve">15.7579050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4107103347778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815771102905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9157218933105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8920469284058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8683757781982</t>
+    <t xml:space="preserve">15.4107112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815790176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9157209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8920478820801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8683776855469</t>
   </si>
   <si>
     <t xml:space="preserve">15.62770652771</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7973604202271</t>
+    <t xml:space="preserve">15.7973594665527</t>
   </si>
   <si>
     <t xml:space="preserve">15.7539596557617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8289232254028</t>
+    <t xml:space="preserve">15.8289213180542</t>
   </si>
   <si>
     <t xml:space="preserve">16.0893173217773</t>
@@ -4130,10 +4130,10 @@
     <t xml:space="preserve">16.0735378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1761169433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9236116409302</t>
+    <t xml:space="preserve">16.176118850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9236125946045</t>
   </si>
   <si>
     <t xml:space="preserve">15.6395435333252</t>
@@ -4145,25 +4145,25 @@
     <t xml:space="preserve">14.9964447021484</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1660947799683</t>
+    <t xml:space="preserve">15.1660976409912</t>
   </si>
   <si>
     <t xml:space="preserve">15.6868877410889</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7381782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7657947540283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0261936187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8052501678467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4583625793457</t>
+    <t xml:space="preserve">15.7381792068481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.765796661377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0261917114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.805251121521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4583644866943</t>
   </si>
   <si>
     <t xml:space="preserve">16.0873756408691</t>
@@ -4184,13 +4184,13 @@
     <t xml:space="preserve">16.8209209442139</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5932674407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8082714080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5595417022705</t>
+    <t xml:space="preserve">16.5932693481445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8082733154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5595397949219</t>
   </si>
   <si>
     <t xml:space="preserve">16.871509552002</t>
@@ -4202,37 +4202,37 @@
     <t xml:space="preserve">16.5342483520508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2012004852295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7298974990845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4390096664429</t>
+    <t xml:space="preserve">16.2012023925781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7298984527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4390106201172</t>
   </si>
   <si>
     <t xml:space="preserve">14.6287202835083</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9828443527222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2830257415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3715581893921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4432258605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5064630508423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2197885513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6750936508179</t>
+    <t xml:space="preserve">14.9828453063965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2830276489258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3715591430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4432249069214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.506462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2197895050049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6750926971436</t>
   </si>
   <si>
     <t xml:space="preserve">14.5191097259521</t>
@@ -4241,43 +4241,43 @@
     <t xml:space="preserve">14.4811658859253</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2745962142944</t>
+    <t xml:space="preserve">14.2745952606201</t>
   </si>
   <si>
     <t xml:space="preserve">13.9837064743042</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8277235031128</t>
+    <t xml:space="preserve">13.8277225494385</t>
   </si>
   <si>
     <t xml:space="preserve">13.9289026260376</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3724212646484</t>
+    <t xml:space="preserve">13.3724203109741</t>
   </si>
   <si>
     <t xml:space="preserve">13.7771348953247</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1523380279541</t>
+    <t xml:space="preserve">14.1523370742798</t>
   </si>
   <si>
     <t xml:space="preserve">14.3420476913452</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1354732513428</t>
+    <t xml:space="preserve">14.1354742050171</t>
   </si>
   <si>
     <t xml:space="preserve">14.3546934127808</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1987104415894</t>
+    <t xml:space="preserve">14.1987113952637</t>
   </si>
   <si>
     <t xml:space="preserve">13.6211519241333</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6801719665527</t>
+    <t xml:space="preserve">13.6801729202271</t>
   </si>
   <si>
     <t xml:space="preserve">13.8108596801758</t>
@@ -4286,7 +4286,7 @@
     <t xml:space="preserve">14.2493000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6928195953369</t>
+    <t xml:space="preserve">13.6928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">13.7602710723877</t>
@@ -4295,10 +4295,10 @@
     <t xml:space="preserve">13.7939977645874</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4609508514404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5494823455811</t>
+    <t xml:space="preserve">13.4609518051147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5494832992554</t>
   </si>
   <si>
     <t xml:space="preserve">14.3631258010864</t>
@@ -4313,13 +4313,13 @@
     <t xml:space="preserve">14.4727363586426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5739145278931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2577323913574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2956743240356</t>
+    <t xml:space="preserve">14.5739154815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2577314376831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2956733703613</t>
   </si>
   <si>
     <t xml:space="preserve">14.1944952011108</t>
@@ -4331,16 +4331,16 @@
     <t xml:space="preserve">14.5022468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5654821395874</t>
+    <t xml:space="preserve">14.565484046936</t>
   </si>
   <si>
     <t xml:space="preserve">14.6371517181396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3757724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643058776855</t>
+    <t xml:space="preserve">14.3757734298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643049240112</t>
   </si>
   <si>
     <t xml:space="preserve">13.9794912338257</t>
@@ -4355,10 +4355,10 @@
     <t xml:space="preserve">13.9415493011475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8530178070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4651670455933</t>
+    <t xml:space="preserve">13.8530187606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4651679992676</t>
   </si>
   <si>
     <t xml:space="preserve">13.4483041763306</t>
@@ -4367,10 +4367,10 @@
     <t xml:space="preserve">13.6380128860474</t>
   </si>
   <si>
-    <t xml:space="preserve">13.435658454895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1447687149048</t>
+    <t xml:space="preserve">13.4356575012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1447696685791</t>
   </si>
   <si>
     <t xml:space="preserve">13.6295833587646</t>
@@ -4382,22 +4382,22 @@
     <t xml:space="preserve">13.4946775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5199728012085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1692018508911</t>
+    <t xml:space="preserve">13.5199718475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1692008972168</t>
   </si>
   <si>
     <t xml:space="preserve">14.0806703567505</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0722379684448</t>
+    <t xml:space="preserve">14.0722389221191</t>
   </si>
   <si>
     <t xml:space="preserve">13.9162530899048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7644872665405</t>
+    <t xml:space="preserve">13.7644882202148</t>
   </si>
   <si>
     <t xml:space="preserve">13.8572330474854</t>
@@ -4424,10 +4424,10 @@
     <t xml:space="preserve">12.0065116882324</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3985776901245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6009349822998</t>
+    <t xml:space="preserve">12.3985767364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6009340286255</t>
   </si>
   <si>
     <t xml:space="preserve">13.1532011032104</t>
@@ -4436,25 +4436,25 @@
     <t xml:space="preserve">12.9044694900513</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7231912612915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5039720535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5503454208374</t>
+    <t xml:space="preserve">12.7231922149658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5039710998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5503463745117</t>
   </si>
   <si>
     <t xml:space="preserve">12.4280881881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7324857711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0908269882202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5292654037476</t>
+    <t xml:space="preserve">11.7324867248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0908260345459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5292663574219</t>
   </si>
   <si>
     <t xml:space="preserve">12.7948608398438</t>
@@ -4469,7 +4469,7 @@
     <t xml:space="preserve">12.8538808822632</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8960390090942</t>
+    <t xml:space="preserve">12.8960380554199</t>
   </si>
   <si>
     <t xml:space="preserve">13.3007526397705</t>
@@ -4484,7 +4484,7 @@
     <t xml:space="preserve">13.7897806167603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7434072494507</t>
+    <t xml:space="preserve">13.743408203125</t>
   </si>
   <si>
     <t xml:space="preserve">13.9963550567627</t>
@@ -4496,10 +4496,10 @@
     <t xml:space="preserve">14.3462619781494</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7214651107788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9449024200439</t>
+    <t xml:space="preserve">14.7214670181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9449043273926</t>
   </si>
   <si>
     <t xml:space="preserve">15.0292186737061</t>
@@ -4517,7 +4517,7 @@
     <t xml:space="preserve">16.8335666656494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8293495178223</t>
+    <t xml:space="preserve">16.8293514251709</t>
   </si>
   <si>
     <t xml:space="preserve">16.799840927124</t>
@@ -4535,13 +4535,13 @@
     <t xml:space="preserve">16.3909130096436</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1801223754883</t>
+    <t xml:space="preserve">16.1801242828369</t>
   </si>
   <si>
     <t xml:space="preserve">16.2349281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3993434906006</t>
+    <t xml:space="preserve">16.3993453979492</t>
   </si>
   <si>
     <t xml:space="preserve">16.3023796081543</t>
@@ -4556,7 +4556,7 @@
     <t xml:space="preserve">16.5089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155265808105</t>
+    <t xml:space="preserve">16.7155246734619</t>
   </si>
   <si>
     <t xml:space="preserve">16.9389610290527</t>
@@ -4565,7 +4565,7 @@
     <t xml:space="preserve">16.7618980407715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0570011138916</t>
+    <t xml:space="preserve">17.0570030212402</t>
   </si>
   <si>
     <t xml:space="preserve">16.9558238983154</t>
@@ -4577,22 +4577,22 @@
     <t xml:space="preserve">17.2677917480469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2593612670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2340641021729</t>
+    <t xml:space="preserve">17.2593593597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2340660095215</t>
   </si>
   <si>
     <t xml:space="preserve">17.5375995635986</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3774032592773</t>
+    <t xml:space="preserve">17.3774013519287</t>
   </si>
   <si>
     <t xml:space="preserve">17.4617156982422</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6893692016602</t>
+    <t xml:space="preserve">17.6893672943115</t>
   </si>
   <si>
     <t xml:space="preserve">17.7146625518799</t>
@@ -4601,13 +4601,13 @@
     <t xml:space="preserve">17.8579998016357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6472129821777</t>
+    <t xml:space="preserve">17.6472110748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.8664302825928</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0434913635254</t>
+    <t xml:space="preserve">18.043493270874</t>
   </si>
   <si>
     <t xml:space="preserve">18.2542819976807</t>
@@ -4625,7 +4625,7 @@
     <t xml:space="preserve">18.3891849517822</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8697814941406</t>
+    <t xml:space="preserve">18.8697834014893</t>
   </si>
   <si>
     <t xml:space="preserve">18.9035110473633</t>
@@ -4643,7 +4643,7 @@
     <t xml:space="preserve">19.164888381958</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8444900512695</t>
+    <t xml:space="preserve">18.8444881439209</t>
   </si>
   <si>
     <t xml:space="preserve">19.2239074707031</t>
@@ -4661,7 +4661,7 @@
     <t xml:space="preserve">19.3841075897217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4431285858154</t>
+    <t xml:space="preserve">19.4431266784668</t>
   </si>
   <si>
     <t xml:space="preserve">19.3250865936279</t>
@@ -4673,7 +4673,7 @@
     <t xml:space="preserve">19.3166561126709</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8141174316406</t>
+    <t xml:space="preserve">19.814115524292</t>
   </si>
   <si>
     <t xml:space="preserve">19.8984336853027</t>
@@ -4697,13 +4697,13 @@
     <t xml:space="preserve">19.5358753204346</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0637092590332</t>
+    <t xml:space="preserve">19.0637111663818</t>
   </si>
   <si>
     <t xml:space="preserve">19.0890026092529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2070465087891</t>
+    <t xml:space="preserve">19.2070446014404</t>
   </si>
   <si>
     <t xml:space="preserve">19.0552787780762</t>
@@ -4721,22 +4721,22 @@
     <t xml:space="preserve">18.9793930053711</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1058654785156</t>
+    <t xml:space="preserve">19.1058673858643</t>
   </si>
   <si>
     <t xml:space="preserve">18.8950786590576</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8023319244385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1952610015869</t>
+    <t xml:space="preserve">18.8023300170898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1952590942383</t>
   </si>
   <si>
     <t xml:space="preserve">17.6134834289551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7745475769043</t>
+    <t xml:space="preserve">16.7745456695557</t>
   </si>
   <si>
     <t xml:space="preserve">16.9811172485352</t>
@@ -4745,7 +4745,7 @@
     <t xml:space="preserve">16.2391452789307</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0114917755127</t>
+    <t xml:space="preserve">16.0114936828613</t>
   </si>
   <si>
     <t xml:space="preserve">16.4667949676514</t>
@@ -4754,13 +4754,13 @@
     <t xml:space="preserve">16.9052352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3782634735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1126728057861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1337509155273</t>
+    <t xml:space="preserve">16.3782653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1126708984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1337490081787</t>
   </si>
   <si>
     <t xml:space="preserve">16.3487529754639</t>
@@ -4778,7 +4778,7 @@
     <t xml:space="preserve">16.3403205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5216007232666</t>
+    <t xml:space="preserve">16.521598815918</t>
   </si>
   <si>
     <t xml:space="preserve">16.7113094329834</t>
@@ -4787,10 +4787,10 @@
     <t xml:space="preserve">17.158182144165</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1244564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0232772827148</t>
+    <t xml:space="preserve">17.124454498291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0232791900635</t>
   </si>
   <si>
     <t xml:space="preserve">17.2003383636475</t>
@@ -4802,7 +4802,7 @@
     <t xml:space="preserve">17.1075916290283</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0148448944092</t>
+    <t xml:space="preserve">17.0148468017578</t>
   </si>
   <si>
     <t xml:space="preserve">17.0401401519775</t>
@@ -4814,7 +4814,7 @@
     <t xml:space="preserve">16.8124885559082</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5806217193604</t>
+    <t xml:space="preserve">16.5806198120117</t>
   </si>
   <si>
     <t xml:space="preserve">16.9726848602295</t>
@@ -4844,10 +4844,10 @@
     <t xml:space="preserve">17.3769779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0168342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8097515106201</t>
+    <t xml:space="preserve">17.0168323516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8097496032715</t>
   </si>
   <si>
     <t xml:space="preserve">17.2014083862305</t>
@@ -4856,28 +4856,28 @@
     <t xml:space="preserve">17.1743984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0753574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7242183685303</t>
+    <t xml:space="preserve">17.0753593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">17.0213356018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4129943847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4580116271973</t>
+    <t xml:space="preserve">17.412992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4580097198486</t>
   </si>
   <si>
     <t xml:space="preserve">17.647087097168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6425857543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721790313721</t>
+    <t xml:space="preserve">17.6425838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721771240234</t>
   </si>
   <si>
     <t xml:space="preserve">17.6020679473877</t>
@@ -4898,7 +4898,7 @@
     <t xml:space="preserve">18.0162353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8496704101562</t>
+    <t xml:space="preserve">17.8496685028076</t>
   </si>
   <si>
     <t xml:space="preserve">17.8136539459229</t>
@@ -4922,7 +4922,7 @@
     <t xml:space="preserve">17.4715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5750579833984</t>
+    <t xml:space="preserve">17.5750598907471</t>
   </si>
   <si>
     <t xml:space="preserve">17.786642074585</t>
@@ -4949,7 +4949,7 @@
     <t xml:space="preserve">17.8541698455811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9667148590088</t>
+    <t xml:space="preserve">17.9667167663574</t>
   </si>
   <si>
     <t xml:space="preserve">17.9036903381348</t>
@@ -4961,7 +4961,7 @@
     <t xml:space="preserve">18.1602935791016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2863445281982</t>
+    <t xml:space="preserve">18.2863426208496</t>
   </si>
   <si>
     <t xml:space="preserve">18.2323226928711</t>
@@ -4970,7 +4970,7 @@
     <t xml:space="preserve">18.2413272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1783008575439</t>
+    <t xml:space="preserve">18.1783027648926</t>
   </si>
   <si>
     <t xml:space="preserve">18.2683372497559</t>
@@ -4991,7 +4991,7 @@
     <t xml:space="preserve">19.0066337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6284809112549</t>
+    <t xml:space="preserve">18.6284828186035</t>
   </si>
   <si>
     <t xml:space="preserve">18.6014709472656</t>
@@ -5003,13 +5003,13 @@
     <t xml:space="preserve">18.6104755401611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.700511932373</t>
+    <t xml:space="preserve">18.7005100250244</t>
   </si>
   <si>
     <t xml:space="preserve">18.7365245819092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8895874023438</t>
+    <t xml:space="preserve">18.8895854949951</t>
   </si>
   <si>
     <t xml:space="preserve">18.7545318603516</t>
@@ -5021,7 +5021,7 @@
     <t xml:space="preserve">18.8715782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5924663543701</t>
+    <t xml:space="preserve">18.5924682617188</t>
   </si>
   <si>
     <t xml:space="preserve">18.3403663635254</t>
@@ -5033,10 +5033,10 @@
     <t xml:space="preserve">18.5114345550537</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0426464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.132682800293</t>
+    <t xml:space="preserve">19.0426483154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1326847076416</t>
   </si>
   <si>
     <t xml:space="preserve">19.2497310638428</t>
@@ -5048,16 +5048,16 @@
     <t xml:space="preserve">19.1867046356201</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0876655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.934606552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9706192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0516510009766</t>
+    <t xml:space="preserve">19.08766746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9346046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9706172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0516529083252</t>
   </si>
   <si>
     <t xml:space="preserve">19.0246410369873</t>
@@ -5072,31 +5072,31 @@
     <t xml:space="preserve">19.1957092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8625755310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.790548324585</t>
+    <t xml:space="preserve">18.8625774383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7905464172363</t>
   </si>
   <si>
     <t xml:space="preserve">18.7815437316895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8535709381104</t>
+    <t xml:space="preserve">18.853572845459</t>
   </si>
   <si>
     <t xml:space="preserve">18.619478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2593326568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493690490723</t>
+    <t xml:space="preserve">18.259334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3493671417236</t>
   </si>
   <si>
     <t xml:space="preserve">18.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3313636779785</t>
+    <t xml:space="preserve">18.3313617706299</t>
   </si>
   <si>
     <t xml:space="preserve">18.0702571868896</t>
@@ -5117,7 +5117,7 @@
     <t xml:space="preserve">17.4670143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4805221557617</t>
+    <t xml:space="preserve">17.4805202484131</t>
   </si>
   <si>
     <t xml:space="preserve">17.6200752258301</t>
@@ -5126,13 +5126,13 @@
     <t xml:space="preserve">17.8991870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8901863098145</t>
+    <t xml:space="preserve">17.8901844024658</t>
   </si>
   <si>
     <t xml:space="preserve">18.1422863006592</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4304027557373</t>
+    <t xml:space="preserve">18.4304008483887</t>
   </si>
   <si>
     <t xml:space="preserve">18.4213981628418</t>
@@ -5147,10 +5147,10 @@
     <t xml:space="preserve">18.7725391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2047138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4388084411621</t>
+    <t xml:space="preserve">19.2047119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4388065338135</t>
   </si>
   <si>
     <t xml:space="preserve">19.6278820037842</t>
@@ -5162,19 +5162,19 @@
     <t xml:space="preserve">20.0510520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9069957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8439712524414</t>
+    <t xml:space="preserve">19.9069938659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8439693450928</t>
   </si>
   <si>
     <t xml:space="preserve">19.7899475097656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8979930877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8079566955566</t>
+    <t xml:space="preserve">19.8979911804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.807954788208</t>
   </si>
   <si>
     <t xml:space="preserve">19.6729011535645</t>
@@ -5183,7 +5183,7 @@
     <t xml:space="preserve">19.9520130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0960712432861</t>
+    <t xml:space="preserve">20.0960693359375</t>
   </si>
   <si>
     <t xml:space="preserve">20.0690612792969</t>
@@ -5201,7 +5201,7 @@
     <t xml:space="preserve">20.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5372486114502</t>
+    <t xml:space="preserve">20.5372467041016</t>
   </si>
   <si>
     <t xml:space="preserve">20.996431350708</t>
@@ -5216,7 +5216,7 @@
     <t xml:space="preserve">21.2215213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2755432128906</t>
+    <t xml:space="preserve">21.2755451202393</t>
   </si>
   <si>
     <t xml:space="preserve">21.2935523986816</t>
@@ -5237,22 +5237,22 @@
     <t xml:space="preserve">21.7887516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9598178863525</t>
+    <t xml:space="preserve">21.9598197937012</t>
   </si>
   <si>
     <t xml:space="preserve">22.3199634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">21.671703338623</t>
+    <t xml:space="preserve">21.6717052459717</t>
   </si>
   <si>
     <t xml:space="preserve">22.0948734283447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2659435272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.419002532959</t>
+    <t xml:space="preserve">22.265941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4190044403076</t>
   </si>
   <si>
     <t xml:space="preserve">22.5090389251709</t>
@@ -5261,10 +5261,10 @@
     <t xml:space="preserve">22.5900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.563060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.905200958252</t>
+    <t xml:space="preserve">22.5630626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9051990509033</t>
   </si>
   <si>
     <t xml:space="preserve">22.797155380249</t>
@@ -5273,7 +5273,7 @@
     <t xml:space="preserve">23.0762672424316</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0222454071045</t>
+    <t xml:space="preserve">23.0222473144531</t>
   </si>
   <si>
     <t xml:space="preserve">23.3103618621826</t>
@@ -5288,10 +5288,10 @@
     <t xml:space="preserve">23.3193645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2293281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4003982543945</t>
+    <t xml:space="preserve">23.2293300628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4003963470459</t>
   </si>
   <si>
     <t xml:space="preserve">23.2563400268555</t>
@@ -5300,7 +5300,7 @@
     <t xml:space="preserve">23.6705074310303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5894756317139</t>
+    <t xml:space="preserve">23.5894737243652</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264472961426</t>
@@ -5312,7 +5312,7 @@
     <t xml:space="preserve">23.8865947723389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7065200805664</t>
+    <t xml:space="preserve">23.706521987915</t>
   </si>
   <si>
     <t xml:space="preserve">23.6975173950195</t>
@@ -5360,7 +5360,7 @@
     <t xml:space="preserve">21.6987152099609</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9148006439209</t>
+    <t xml:space="preserve">21.9148025512695</t>
   </si>
   <si>
     <t xml:space="preserve">22.5720653533936</t>
@@ -5375,7 +5375,7 @@
     <t xml:space="preserve">22.3559799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.310962677002</t>
+    <t xml:space="preserve">22.3109607696533</t>
   </si>
   <si>
     <t xml:space="preserve">22.1218852996826</t>
@@ -5384,19 +5384,19 @@
     <t xml:space="preserve">22.4550189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3289661407471</t>
+    <t xml:space="preserve">22.3289680480957</t>
   </si>
   <si>
     <t xml:space="preserve">22.6260871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.671106338501</t>
+    <t xml:space="preserve">22.6711044311523</t>
   </si>
   <si>
     <t xml:space="preserve">21.608678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7977542877197</t>
+    <t xml:space="preserve">21.7977523803711</t>
   </si>
   <si>
     <t xml:space="preserve">21.968822479248</t>
@@ -5414,22 +5414,22 @@
     <t xml:space="preserve">21.5996742248535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7257232666016</t>
+    <t xml:space="preserve">21.7257251739502</t>
   </si>
   <si>
     <t xml:space="preserve">21.7527370452881</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6176834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8427734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2749443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1038761138916</t>
+    <t xml:space="preserve">21.6176815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8427715301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2749462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1038780212402</t>
   </si>
   <si>
     <t xml:space="preserve">22.1578998565674</t>
@@ -5438,16 +5438,16 @@
     <t xml:space="preserve">22.2839488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3019580841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2569389343262</t>
+    <t xml:space="preserve">22.3019561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2569370269775</t>
   </si>
   <si>
     <t xml:space="preserve">22.7341289520264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9502182006836</t>
+    <t xml:space="preserve">22.950216293335</t>
   </si>
   <si>
     <t xml:space="preserve">23.1843109130859</t>
@@ -5459,13 +5459,13 @@
     <t xml:space="preserve">23.0672645568848</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4364128112793</t>
+    <t xml:space="preserve">23.4364147186279</t>
   </si>
   <si>
     <t xml:space="preserve">23.5084419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8415756225586</t>
+    <t xml:space="preserve">23.84157371521</t>
   </si>
   <si>
     <t xml:space="preserve">23.5945644378662</t>
@@ -6381,6 +6381,9 @@
   </si>
   <si>
     <t xml:space="preserve">32.7000007629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.1800003051758</t>
   </si>
 </sst>
 </file>
@@ -71615,7 +71618,7 @@
     </row>
     <row r="2497">
       <c r="A2497" s="1" t="n">
-        <v>45954.6495833333</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2497" t="n">
         <v>325414</v>
@@ -71636,6 +71639,32 @@
         <v>2122</v>
       </c>
       <c r="H2497" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2498">
+      <c r="A2498" s="1" t="n">
+        <v>45957.6941666667</v>
+      </c>
+      <c r="B2498" t="n">
+        <v>550355</v>
+      </c>
+      <c r="C2498" t="n">
+        <v>33.25</v>
+      </c>
+      <c r="D2498" t="n">
+        <v>32.7999992370605</v>
+      </c>
+      <c r="E2498" t="n">
+        <v>32.7999992370605</v>
+      </c>
+      <c r="F2498" t="n">
+        <v>33.1800003051758</v>
+      </c>
+      <c r="G2498" t="s">
+        <v>2123</v>
+      </c>
+      <c r="H2498" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2124" uniqueCount="2124">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="2125">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8295068740845</t>
+    <t xml:space="preserve">10.8295078277588</t>
   </si>
   <si>
     <t xml:space="preserve">AZM.MI</t>
@@ -56,10 +56,10 @@
     <t xml:space="preserve">9.91192054748535</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9364538192749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2259607315063</t>
+    <t xml:space="preserve">9.93645286560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2259616851807</t>
   </si>
   <si>
     <t xml:space="preserve">10.0002431869507</t>
@@ -68,40 +68,40 @@
     <t xml:space="preserve">9.61750507354736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33290672302246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1513500213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37706661224365</t>
+    <t xml:space="preserve">9.33290386199951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15135192871094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37706756591797</t>
   </si>
   <si>
     <t xml:space="preserve">8.85693836212158</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25930404663086</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53899669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48992824554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50955390930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40160369873047</t>
+    <t xml:space="preserve">9.25930309295654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53899478912354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48992729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50955581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40160274505615</t>
   </si>
   <si>
     <t xml:space="preserve">9.12681770324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49483394622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43595123291016</t>
+    <t xml:space="preserve">9.49483489990234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43595218658447</t>
   </si>
   <si>
     <t xml:space="preserve">8.84712409973145</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">8.79805564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05711364746094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86574554443359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32699394226074</t>
+    <t xml:space="preserve">8.05711460113525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86574459075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32699298858643</t>
   </si>
   <si>
     <t xml:space="preserve">7.61058664321899</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">8.53798961639404</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78333473205566</t>
+    <t xml:space="preserve">8.78333377838135</t>
   </si>
   <si>
     <t xml:space="preserve">8.46929264068604</t>
@@ -146,13 +146,13 @@
     <t xml:space="preserve">8.61649799346924</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50364112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21413516998291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69010353088379</t>
+    <t xml:space="preserve">8.50364208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21413326263428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69010448455811</t>
   </si>
   <si>
     <t xml:space="preserve">8.71954536437988</t>
@@ -161,7 +161,7 @@
     <t xml:space="preserve">9.29365062713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30837249755859</t>
+    <t xml:space="preserve">9.30837154388428</t>
   </si>
   <si>
     <t xml:space="preserve">9.47520637512207</t>
@@ -173,67 +173,67 @@
     <t xml:space="preserve">9.22004890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41141605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48011302947998</t>
+    <t xml:space="preserve">9.41141796112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48011207580566</t>
   </si>
   <si>
     <t xml:space="preserve">9.77943325042725</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66166687011719</t>
+    <t xml:space="preserve">9.66166877746582</t>
   </si>
   <si>
     <t xml:space="preserve">9.79415416717529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7745246887207</t>
+    <t xml:space="preserve">9.77452850341797</t>
   </si>
   <si>
     <t xml:space="preserve">9.68620204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64694786071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72545623779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2357749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3044691085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83831691741943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56843566894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98552417755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93154716491699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74508571624756</t>
+    <t xml:space="preserve">9.64694690704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7254581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2357740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3044719696045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83831596374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56843662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98552227020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93154811859131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74508476257324</t>
   </si>
   <si>
     <t xml:space="preserve">10.3780727386475</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5449094772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.436957359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5547218322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5056524276733</t>
+    <t xml:space="preserve">10.5449075698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4369564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5547227859497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5056533813477</t>
   </si>
   <si>
     <t xml:space="preserve">10.5498151779175</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">10.5007467269897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5694417953491</t>
+    <t xml:space="preserve">10.5694427490234</t>
   </si>
   <si>
     <t xml:space="preserve">10.4173288345337</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4811201095581</t>
+    <t xml:space="preserve">10.4811191558838</t>
   </si>
   <si>
     <t xml:space="preserve">10.7411842346191</t>
@@ -257,43 +257,43 @@
     <t xml:space="preserve">10.8442277908325</t>
   </si>
   <si>
-    <t xml:space="preserve">10.785346031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5988845825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2897510528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73036575317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57334518432617</t>
+    <t xml:space="preserve">10.7853469848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5988826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406826019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2897520065308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7303638458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57334423065186</t>
   </si>
   <si>
     <t xml:space="preserve">9.43104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40651035308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19060707092285</t>
+    <t xml:space="preserve">9.40650844573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19060516357422</t>
   </si>
   <si>
     <t xml:space="preserve">9.08265495300293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3525333404541</t>
+    <t xml:space="preserve">9.35253429412842</t>
   </si>
   <si>
     <t xml:space="preserve">9.47029781341553</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27892875671387</t>
+    <t xml:space="preserve">9.27892971038818</t>
   </si>
   <si>
     <t xml:space="preserve">9.30346584320068</t>
@@ -302,22 +302,22 @@
     <t xml:space="preserve">9.14644432067871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52970218658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79665470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190118789673</t>
+    <t xml:space="preserve">9.52970314025879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79665565490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1190137863159</t>
   </si>
   <si>
     <t xml:space="preserve">9.89235496520996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95279502868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492319107056</t>
+    <t xml:space="preserve">9.95279693603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492309570312</t>
   </si>
   <si>
     <t xml:space="preserve">9.84702205657959</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">9.76643466949463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42896556854248</t>
+    <t xml:space="preserve">9.42896461486816</t>
   </si>
   <si>
     <t xml:space="preserve">9.42392730712891</t>
@@ -341,76 +341,76 @@
     <t xml:space="preserve">9.39370727539062</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82958221435547</t>
+    <t xml:space="preserve">8.82958126068115</t>
   </si>
   <si>
     <t xml:space="preserve">8.48203945159912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28560256958008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46189212799072</t>
+    <t xml:space="preserve">8.28560066223145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46189022064209</t>
   </si>
   <si>
     <t xml:space="preserve">8.53744411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68351268768311</t>
+    <t xml:space="preserve">8.68351173400879</t>
   </si>
   <si>
     <t xml:space="preserve">9.39874362945557</t>
   </si>
   <si>
-    <t xml:space="preserve">9.50451850891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81680011749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46459722518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5754075050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49985551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34875011444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43941259384155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20268297195435</t>
+    <t xml:space="preserve">9.50451755523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81680202484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692848205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46459770202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540655136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49985456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34875059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43941164016724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20268106460571</t>
   </si>
   <si>
     <t xml:space="preserve">6.87025022506714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50256061553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6284818649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86017560958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02135562896729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38904428482056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20771837234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44948625564575</t>
+    <t xml:space="preserve">6.50256109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62848234176636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86017608642578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02135515213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38904476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20771884918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44948530197144</t>
   </si>
   <si>
     <t xml:space="preserve">7.66607093811035</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">7.52503967285156</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64592313766479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79703044891357</t>
+    <t xml:space="preserve">7.64592218399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79702854156494</t>
   </si>
   <si>
     <t xml:space="preserve">7.71140289306641</t>
@@ -431,193 +431,193 @@
     <t xml:space="preserve">7.94309711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.8171763420105</t>
+    <t xml:space="preserve">7.81717538833618</t>
   </si>
   <si>
     <t xml:space="preserve">7.94813394546509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08179712295532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92565584182739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71410894393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78966093063354</t>
+    <t xml:space="preserve">7.0817985534668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92565679550171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71410846710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7896614074707</t>
   </si>
   <si>
     <t xml:space="preserve">6.90047025680542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22786617279053</t>
+    <t xml:space="preserve">7.22786426544189</t>
   </si>
   <si>
     <t xml:space="preserve">7.27823495864868</t>
   </si>
   <si>
-    <t xml:space="preserve">7.32860326766968</t>
+    <t xml:space="preserve">7.32860279083252</t>
   </si>
   <si>
     <t xml:space="preserve">7.31852865219116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.39911890029907</t>
+    <t xml:space="preserve">7.39911842346191</t>
   </si>
   <si>
     <t xml:space="preserve">7.15735006332397</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94580173492432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764518737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.804771900177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02639198303223</t>
+    <t xml:space="preserve">6.94580268859863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80477094650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02639245986938</t>
   </si>
   <si>
     <t xml:space="preserve">7.08683443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04150342941284</t>
+    <t xml:space="preserve">7.04150199890137</t>
   </si>
   <si>
     <t xml:space="preserve">6.85010290145874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8652138710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069171905518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22282838821411</t>
+    <t xml:space="preserve">6.86521244049072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069124221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22282981872559</t>
   </si>
   <si>
     <t xml:space="preserve">7.31349325180054</t>
   </si>
   <si>
-    <t xml:space="preserve">7.23290205001831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29838037490845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98106050491333</t>
+    <t xml:space="preserve">7.23290252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29838275909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98106002807617</t>
   </si>
   <si>
     <t xml:space="preserve">7.01128101348877</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53781890869141</t>
+    <t xml:space="preserve">6.53781843185425</t>
   </si>
   <si>
     <t xml:space="preserve">6.7997350692749</t>
   </si>
   <si>
-    <t xml:space="preserve">6.68388748168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73929262161255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94076633453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90550851821899</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66877746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46226596832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57307720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6738133430481</t>
+    <t xml:space="preserve">6.68388652801514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73929309844971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94076538085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90550708770752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66877603530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4622654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57307624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67381381988525</t>
   </si>
   <si>
     <t xml:space="preserve">6.59826040267944</t>
   </si>
   <si>
-    <t xml:space="preserve">6.87528657913208</t>
+    <t xml:space="preserve">6.8752875328064</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624418258667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15231275558472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30341863632202</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62577724456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66103410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57037115097046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45452451705933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5351128578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44444847106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59555530548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72147607803345</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.605628490448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70636510848999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48474502563477</t>
+    <t xml:space="preserve">7.15231227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30341911315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62577629089355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66103219985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57037210464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45452404022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53511333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59555435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72147703170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60562944412231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70636606216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48474454879761</t>
   </si>
   <si>
     <t xml:space="preserve">7.36385917663574</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26312303543091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13216400146484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617052078247</t>
+    <t xml:space="preserve">7.26312351226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13216543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617099761963</t>
   </si>
   <si>
     <t xml:space="preserve">7.17246055603027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69629096984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91791296005249</t>
+    <t xml:space="preserve">7.69629192352295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91791248321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.35611724853516</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38633823394775</t>
+    <t xml:space="preserve">8.38633918762207</t>
   </si>
   <si>
     <t xml:space="preserve">8.51729679107666</t>
@@ -626,40 +626,40 @@
     <t xml:space="preserve">8.45181751251221</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20501327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.04887104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95820808410645</t>
+    <t xml:space="preserve">8.20501232147217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.04887199401855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.95820713043213</t>
   </si>
   <si>
     <t xml:space="preserve">7.93132162094116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71623516082764</t>
+    <t xml:space="preserve">7.71623420715332</t>
   </si>
   <si>
     <t xml:space="preserve">7.73236799240112</t>
   </si>
   <si>
-    <t xml:space="preserve">7.6355767250061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64095497131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45813083648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44200086593628</t>
+    <t xml:space="preserve">7.63557767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64095401763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45813274383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4419994354248</t>
   </si>
   <si>
     <t xml:space="preserve">7.57105207443237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68935108184814</t>
+    <t xml:space="preserve">7.68934917449951</t>
   </si>
   <si>
     <t xml:space="preserve">7.62482309341431</t>
@@ -674,28 +674,28 @@
     <t xml:space="preserve">8.43139839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61960029602051</t>
+    <t xml:space="preserve">8.61959934234619</t>
   </si>
   <si>
     <t xml:space="preserve">8.54432010650635</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46903896331787</t>
+    <t xml:space="preserve">8.46903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">8.58733654022217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70025730133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54969692230225</t>
+    <t xml:space="preserve">8.70025634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54969596862793</t>
   </si>
   <si>
     <t xml:space="preserve">8.60346794128418</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53356552124023</t>
+    <t xml:space="preserve">8.53356456756592</t>
   </si>
   <si>
     <t xml:space="preserve">8.59809017181396</t>
@@ -704,19 +704,19 @@
     <t xml:space="preserve">8.51743412017822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52818775177002</t>
+    <t xml:space="preserve">8.5281867980957</t>
   </si>
   <si>
     <t xml:space="preserve">8.67875003814697</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11429882049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15731716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20033359527588</t>
+    <t xml:space="preserve">9.11429786682129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15731620788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2003345489502</t>
   </si>
   <si>
     <t xml:space="preserve">9.17882537841797</t>
@@ -725,13 +725,13 @@
     <t xml:space="preserve">9.05515003204346</t>
   </si>
   <si>
-    <t xml:space="preserve">9.3347635269165</t>
+    <t xml:space="preserve">9.33476448059082</t>
   </si>
   <si>
     <t xml:space="preserve">9.13043022155762</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44768238067627</t>
+    <t xml:space="preserve">9.44768333435059</t>
   </si>
   <si>
     <t xml:space="preserve">9.38315677642822</t>
@@ -740,13 +740,13 @@
     <t xml:space="preserve">9.41004371643066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4584379196167</t>
+    <t xml:space="preserve">9.45843696594238</t>
   </si>
   <si>
     <t xml:space="preserve">9.4530611038208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37240219116211</t>
+    <t xml:space="preserve">9.37240314483643</t>
   </si>
   <si>
     <t xml:space="preserve">9.2379732131958</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">9.46919250488281</t>
   </si>
   <si>
-    <t xml:space="preserve">9.442307472229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92609882354736</t>
+    <t xml:space="preserve">9.44230461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92609977722168</t>
   </si>
   <si>
     <t xml:space="preserve">9.0927906036377</t>
@@ -776,25 +776,25 @@
     <t xml:space="preserve">9.16807174682617</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25948143005371</t>
+    <t xml:space="preserve">9.25948238372803</t>
   </si>
   <si>
     <t xml:space="preserve">9.28636932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24335193634033</t>
+    <t xml:space="preserve">9.24335098266602</t>
   </si>
   <si>
     <t xml:space="preserve">9.26485919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23259735107422</t>
+    <t xml:space="preserve">9.2325963973999</t>
   </si>
   <si>
     <t xml:space="preserve">9.24872875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9637393951416</t>
+    <t xml:space="preserve">8.96373844146729</t>
   </si>
   <si>
     <t xml:space="preserve">8.495924949646</t>
@@ -803,7 +803,7 @@
     <t xml:space="preserve">8.59271430969238</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52281093597412</t>
+    <t xml:space="preserve">8.5228099822998</t>
   </si>
   <si>
     <t xml:space="preserve">8.66799449920654</t>
@@ -812,91 +812,91 @@
     <t xml:space="preserve">8.73789691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71101188659668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7056360244751</t>
+    <t xml:space="preserve">8.71101093292236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70563507080078</t>
   </si>
   <si>
     <t xml:space="preserve">8.63573169708252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53894233703613</t>
+    <t xml:space="preserve">8.53894138336182</t>
   </si>
   <si>
     <t xml:space="preserve">8.50130176544189</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28621578216553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33460903167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43677520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47441577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62497615814209</t>
+    <t xml:space="preserve">8.28621482849121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33461093902588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43677616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47441673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62497711181641</t>
   </si>
   <si>
     <t xml:space="preserve">8.56582736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47979354858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66261577606201</t>
+    <t xml:space="preserve">8.47979259490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66261672973633</t>
   </si>
   <si>
     <t xml:space="preserve">8.61422252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78091430664062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77016067504883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79166889190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18420219421387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04977321624756</t>
+    <t xml:space="preserve">8.78091621398926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77015972137451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79166984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18420124053955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04977416992188</t>
   </si>
   <si>
     <t xml:space="preserve">9.14118480682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16269302368164</t>
+    <t xml:space="preserve">9.16269397735596</t>
   </si>
   <si>
     <t xml:space="preserve">9.30250072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13580799102783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14656352996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20570945739746</t>
+    <t xml:space="preserve">9.13580894470215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14656162261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20571041107178</t>
   </si>
   <si>
     <t xml:space="preserve">9.62513065338135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63050746917725</t>
+    <t xml:space="preserve">9.63050651550293</t>
   </si>
   <si>
     <t xml:space="preserve">9.60899829864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63588714599609</t>
+    <t xml:space="preserve">9.63588619232178</t>
   </si>
   <si>
     <t xml:space="preserve">9.7165412902832</t>
@@ -905,55 +905,55 @@
     <t xml:space="preserve">9.97464656829834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0553035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.243504524231</t>
+    <t xml:space="preserve">10.0553045272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2435035705566</t>
   </si>
   <si>
     <t xml:space="preserve">10.4155740737915</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3456697463989</t>
+    <t xml:space="preserve">10.3456716537476</t>
   </si>
   <si>
     <t xml:space="preserve">10.2327489852905</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3994436264038</t>
+    <t xml:space="preserve">10.3994426727295</t>
   </si>
   <si>
     <t xml:space="preserve">10.4101963043213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3349170684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1305828094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036996841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3295383453369</t>
+    <t xml:space="preserve">10.3349180221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1305837631226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3295392990112</t>
   </si>
   <si>
     <t xml:space="preserve">10.4259719848633</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5507669448853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6074905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5848007202148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4770240783691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2387809753418</t>
+    <t xml:space="preserve">10.5507650375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6074895858765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847997665405</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4770231246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2387790679932</t>
   </si>
   <si>
     <t xml:space="preserve">10.2728157043457</t>
@@ -962,25 +962,25 @@
     <t xml:space="preserve">10.3408842086792</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2160902023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0856227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9041051864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2898321151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2614707946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083135604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0062093734741</t>
+    <t xml:space="preserve">10.2160921096802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0856237411499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90410614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898302078247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2614698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0062103271484</t>
   </si>
   <si>
     <t xml:space="preserve">9.94381237030029</t>
@@ -989,7 +989,7 @@
     <t xml:space="preserve">10.1707105636597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1366758346558</t>
+    <t xml:space="preserve">10.1366767883301</t>
   </si>
   <si>
     <t xml:space="preserve">10.0629348754883</t>
@@ -998,19 +998,19 @@
     <t xml:space="preserve">10.1990728378296</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3522291183472</t>
+    <t xml:space="preserve">10.3522281646729</t>
   </si>
   <si>
     <t xml:space="preserve">10.2104167938232</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1933994293213</t>
+    <t xml:space="preserve">10.1934003829956</t>
   </si>
   <si>
     <t xml:space="preserve">9.95515727996826</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1480197906494</t>
+    <t xml:space="preserve">10.1480207443237</t>
   </si>
   <si>
     <t xml:space="preserve">10.2444524765015</t>
@@ -1022,70 +1022,70 @@
     <t xml:space="preserve">10.2217626571655</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0912961959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1593647003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.545093536377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4089527130127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3181934356689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.295506477356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3692464828491</t>
+    <t xml:space="preserve">10.0912971496582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1593656539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5450925827026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4089546203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3181943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2955045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3692455291748</t>
   </si>
   <si>
     <t xml:space="preserve">10.4316434860229</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3976078033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7152671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.641526222229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7436285018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7209377288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6698865890503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7776613235474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7039222717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.658540725708</t>
+    <t xml:space="preserve">10.397608757019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7152662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6415252685547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7436294555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7209386825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.669885635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7776622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7039213180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6585416793823</t>
   </si>
   <si>
     <t xml:space="preserve">10.5394201278687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3068504333496</t>
+    <t xml:space="preserve">10.3068494796753</t>
   </si>
   <si>
     <t xml:space="preserve">10.7095928192139</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5564365386963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4826955795288</t>
+    <t xml:space="preserve">10.5564374923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4826974868774</t>
   </si>
   <si>
     <t xml:space="preserve">10.3352117538452</t>
@@ -1094,31 +1094,31 @@
     <t xml:space="preserve">10.2331085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2784852981567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0288982391357</t>
+    <t xml:space="preserve">10.2784862518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0288991928101</t>
   </si>
   <si>
     <t xml:space="preserve">10.040244102478</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0969686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0345706939697</t>
+    <t xml:space="preserve">10.0969696044922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.034571647644</t>
   </si>
   <si>
     <t xml:space="preserve">9.9835205078125</t>
   </si>
   <si>
-    <t xml:space="preserve">9.96082878112793</t>
+    <t xml:space="preserve">9.96082782745361</t>
   </si>
   <si>
     <t xml:space="preserve">9.98919200897217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2274351119995</t>
+    <t xml:space="preserve">10.2274341583252</t>
   </si>
   <si>
     <t xml:space="preserve">10.2557973861694</t>
@@ -1127,19 +1127,19 @@
     <t xml:space="preserve">10.4940404891968</t>
   </si>
   <si>
-    <t xml:space="preserve">10.511058807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4146280288696</t>
+    <t xml:space="preserve">10.5110578536987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4146270751953</t>
   </si>
   <si>
     <t xml:space="preserve">10.3635740280151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3805913925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4600057601929</t>
+    <t xml:space="preserve">10.3805904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4600048065186</t>
   </si>
   <si>
     <t xml:space="preserve">10.5167303085327</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">10.3465566635132</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84738063812256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86439895629883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72825908660889</t>
+    <t xml:space="preserve">9.84738159179688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86439800262451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7282600402832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67720794677734</t>
@@ -1163,22 +1163,22 @@
     <t xml:space="preserve">9.66018962860107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48434448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.688551902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58644771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71124172210693</t>
+    <t xml:space="preserve">9.48434352874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68855285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58644866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71124076843262</t>
   </si>
   <si>
     <t xml:space="preserve">9.67153549194336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61481094360352</t>
+    <t xml:space="preserve">9.61480903625488</t>
   </si>
   <si>
     <t xml:space="preserve">9.62048149108887</t>
@@ -1193,7 +1193,7 @@
     <t xml:space="preserve">9.79633045196533</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89843368530273</t>
+    <t xml:space="preserve">9.89843273162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.16101360321045</t>
@@ -1202,25 +1202,25 @@
     <t xml:space="preserve">8.95113277435303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99084091186523</t>
+    <t xml:space="preserve">8.9908390045166</t>
   </si>
   <si>
     <t xml:space="preserve">8.76961326599121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.75259685516357</t>
+    <t xml:space="preserve">8.75259780883789</t>
   </si>
   <si>
     <t xml:space="preserve">8.86604499816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85470008850098</t>
+    <t xml:space="preserve">8.85470104217529</t>
   </si>
   <si>
     <t xml:space="preserve">9.05891036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24042892456055</t>
+    <t xml:space="preserve">9.24042797088623</t>
   </si>
   <si>
     <t xml:space="preserve">9.2517728805542</t>
@@ -1244,22 +1244,22 @@
     <t xml:space="preserve">9.05323696136475</t>
   </si>
   <si>
-    <t xml:space="preserve">8.90007972717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.88306331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82633876800537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79230403900146</t>
+    <t xml:space="preserve">8.90008068084717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.88306427001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82633972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79230499267578</t>
   </si>
   <si>
     <t xml:space="preserve">8.79797649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9681510925293</t>
+    <t xml:space="preserve">8.96815013885498</t>
   </si>
   <si>
     <t xml:space="preserve">9.00218486785889</t>
@@ -1277,67 +1277,67 @@
     <t xml:space="preserve">8.92277050018311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04189109802246</t>
+    <t xml:space="preserve">9.04189205169678</t>
   </si>
   <si>
     <t xml:space="preserve">9.03054714202881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01352882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04756450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03622055053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1383228302002</t>
+    <t xml:space="preserve">9.01353073120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04756355285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03621959686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13832473754883</t>
   </si>
   <si>
     <t xml:space="preserve">8.97382259368896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12697887420654</t>
+    <t xml:space="preserve">9.12697792053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.16668605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19504833221436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37089538574219</t>
+    <t xml:space="preserve">9.19504737854004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37089443206787</t>
   </si>
   <si>
     <t xml:space="preserve">9.38223838806152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34253120422363</t>
+    <t xml:space="preserve">9.34253215789795</t>
   </si>
   <si>
     <t xml:space="preserve">9.46732616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6755590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.420298576355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3919372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5961437225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7549734115601</t>
+    <t xml:space="preserve">10.67555809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4202976226807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3919363021851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5961456298828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7549724578857</t>
   </si>
   <si>
     <t xml:space="preserve">10.7379560470581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.760645866394</t>
+    <t xml:space="preserve">10.7606449127197</t>
   </si>
   <si>
     <t xml:space="preserve">10.6613779067993</t>
@@ -1346,7 +1346,7 @@
     <t xml:space="preserve">10.4543342590332</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4032821655273</t>
+    <t xml:space="preserve">10.4032831192017</t>
   </si>
   <si>
     <t xml:space="preserve">10.4429883956909</t>
@@ -1355,31 +1355,31 @@
     <t xml:space="preserve">10.3777561187744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0742807388306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1338396072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0941314697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98635673522949</t>
+    <t xml:space="preserve">10.0742797851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1338376998901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0941324234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98635578155518</t>
   </si>
   <si>
     <t xml:space="preserve">10.1565284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962366104126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2359447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1622009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2416172027588</t>
+    <t xml:space="preserve">10.1962356567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2359437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1622018814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2416162490845</t>
   </si>
   <si>
     <t xml:space="preserve">10.2501239776611</t>
@@ -1400,7 +1400,7 @@
     <t xml:space="preserve">10.1877279281616</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2302732467651</t>
+    <t xml:space="preserve">10.2302722930908</t>
   </si>
   <si>
     <t xml:space="preserve">10.0203895568848</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">10.1905641555786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.182056427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0317354202271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97784805297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81618118286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88708877563477</t>
+    <t xml:space="preserve">10.1820554733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0317344665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9778470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81618213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88708782196045</t>
   </si>
   <si>
     <t xml:space="preserve">9.89559650421143</t>
@@ -1436,16 +1436,16 @@
     <t xml:space="preserve">10.0657691955566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1395120620728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0005359649658</t>
+    <t xml:space="preserve">10.1395130157471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0005369186401</t>
   </si>
   <si>
     <t xml:space="preserve">10.0686054229736</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73676872253418</t>
+    <t xml:space="preserve">9.73676776885986</t>
   </si>
   <si>
     <t xml:space="preserve">9.83603572845459</t>
@@ -1457,73 +1457,73 @@
     <t xml:space="preserve">9.8672342300415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8275260925293</t>
+    <t xml:space="preserve">9.82752704620361</t>
   </si>
   <si>
     <t xml:space="preserve">9.77931118011475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8331995010376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94948577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714426040649</t>
+    <t xml:space="preserve">9.83320045471191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94948387145996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714416503906</t>
   </si>
   <si>
     <t xml:space="preserve">9.93814086914062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71407699584961</t>
+    <t xml:space="preserve">9.71407794952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.42761898040771</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10145378112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21773815155029</t>
+    <t xml:space="preserve">9.10145282745361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21773910522461</t>
   </si>
   <si>
     <t xml:space="preserve">9.12414264678955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24326515197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20072078704834</t>
+    <t xml:space="preserve">9.24326419830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20072174072266</t>
   </si>
   <si>
     <t xml:space="preserve">9.29274559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51369762420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39841651916504</t>
+    <t xml:space="preserve">9.51369667053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39841747283936</t>
   </si>
   <si>
     <t xml:space="preserve">9.47206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4400463104248</t>
+    <t xml:space="preserve">9.44004726409912</t>
   </si>
   <si>
     <t xml:space="preserve">9.33757591247559</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98533535003662</t>
+    <t xml:space="preserve">8.9853343963623</t>
   </si>
   <si>
     <t xml:space="preserve">9.02696514129639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89887619018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34398078918457</t>
+    <t xml:space="preserve">8.89887714385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34397983551025</t>
   </si>
   <si>
     <t xml:space="preserve">9.31836318969727</t>
@@ -1535,7 +1535,7 @@
     <t xml:space="preserve">8.92129135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93410015106201</t>
+    <t xml:space="preserve">8.93410110473633</t>
   </si>
   <si>
     <t xml:space="preserve">8.64590358734131</t>
@@ -1556,10 +1556,10 @@
     <t xml:space="preserve">8.64270210266113</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82842922210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8060131072998</t>
+    <t xml:space="preserve">8.8284273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80601215362549</t>
   </si>
   <si>
     <t xml:space="preserve">8.83163070678711</t>
@@ -1583,7 +1583,7 @@
     <t xml:space="preserve">8.45697498321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39613246917725</t>
+    <t xml:space="preserve">8.39613342285156</t>
   </si>
   <si>
     <t xml:space="preserve">8.51141166687012</t>
@@ -1598,52 +1598,52 @@
     <t xml:space="preserve">8.54343318939209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71314907073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40573978424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36411190032959</t>
+    <t xml:space="preserve">8.71315002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40574073791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36411094665527</t>
   </si>
   <si>
     <t xml:space="preserve">8.33209037780762</t>
   </si>
   <si>
-    <t xml:space="preserve">8.42175102233887</t>
+    <t xml:space="preserve">8.42175197601318</t>
   </si>
   <si>
     <t xml:space="preserve">8.58506202697754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57225322723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46017742156982</t>
+    <t xml:space="preserve">8.5722541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46017646789551</t>
   </si>
   <si>
     <t xml:space="preserve">8.46658134460449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58186149597168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44096374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09420967102051</t>
+    <t xml:space="preserve">8.58186054229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44096565246582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09421062469482</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735782623291</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05578327178955</t>
+    <t xml:space="preserve">9.05578231811523</t>
   </si>
   <si>
     <t xml:space="preserve">9.1998815536499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18707466125488</t>
+    <t xml:space="preserve">9.18707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">8.91808986663818</t>
@@ -1652,10 +1652,10 @@
     <t xml:space="preserve">8.87646198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03657054901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18387031555176</t>
+    <t xml:space="preserve">9.03657150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18387126922607</t>
   </si>
   <si>
     <t xml:space="preserve">9.15505218505859</t>
@@ -1664,7 +1664,7 @@
     <t xml:space="preserve">9.1518497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23510551452637</t>
+    <t xml:space="preserve">9.23510456085205</t>
   </si>
   <si>
     <t xml:space="preserve">9.16465854644775</t>
@@ -1673,7 +1673,7 @@
     <t xml:space="preserve">9.1262321472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26072311401367</t>
+    <t xml:space="preserve">9.2607250213623</t>
   </si>
   <si>
     <t xml:space="preserve">9.254319190979</t>
@@ -1682,49 +1682,49 @@
     <t xml:space="preserve">9.20628643035889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20948886871338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22549915313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10701942443848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92769718170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76758670806885</t>
+    <t xml:space="preserve">9.20948791503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22550010681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10701847076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92769622802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76758766174316</t>
   </si>
   <si>
     <t xml:space="preserve">8.65871238708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68112754821777</t>
+    <t xml:space="preserve">8.68112659454346</t>
   </si>
   <si>
     <t xml:space="preserve">8.72595882415771</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61708545684814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78039646148682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82202434539795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77719402313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78359889984131</t>
+    <t xml:space="preserve">8.61708450317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7803955078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82202529907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77719497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78359794616699</t>
   </si>
   <si>
     <t xml:space="preserve">8.95331478118896</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97252750396729</t>
+    <t xml:space="preserve">8.97252655029297</t>
   </si>
   <si>
     <t xml:space="preserve">8.96612167358398</t>
@@ -1736,7 +1736,7 @@
     <t xml:space="preserve">8.86045074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32568550109863</t>
+    <t xml:space="preserve">8.32568454742432</t>
   </si>
   <si>
     <t xml:space="preserve">8.22321510314941</t>
@@ -1745,13 +1745,13 @@
     <t xml:space="preserve">8.29366397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53382778167725</t>
+    <t xml:space="preserve">8.53382682800293</t>
   </si>
   <si>
     <t xml:space="preserve">8.48259258270264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40253829956055</t>
+    <t xml:space="preserve">8.40253639221191</t>
   </si>
   <si>
     <t xml:space="preserve">8.14956474304199</t>
@@ -1760,13 +1760,13 @@
     <t xml:space="preserve">8.06630706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07271099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77491044998169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74929189682007</t>
+    <t xml:space="preserve">8.07271194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77490997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74929094314575</t>
   </si>
   <si>
     <t xml:space="preserve">7.67884302139282</t>
@@ -1775,16 +1775,16 @@
     <t xml:space="preserve">7.87417650222778</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73007822036743</t>
+    <t xml:space="preserve">7.73007917404175</t>
   </si>
   <si>
     <t xml:space="preserve">7.53474473953247</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42266893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25295305252075</t>
+    <t xml:space="preserve">7.42266988754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25295257568359</t>
   </si>
   <si>
     <t xml:space="preserve">7.21772813796997</t>
@@ -1793,115 +1793,115 @@
     <t xml:space="preserve">7.08003520965576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11205625534058</t>
+    <t xml:space="preserve">7.11205673217773</t>
   </si>
   <si>
     <t xml:space="preserve">6.84947681427002</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97115993499756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04160785675049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03520393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04801273345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94234180450439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9519476890564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00958681106567</t>
+    <t xml:space="preserve">6.97116041183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04160737991333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03520441055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04801225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94234037399292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95194625854492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0095853805542</t>
   </si>
   <si>
     <t xml:space="preserve">7.1312689781189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97436189651489</t>
+    <t xml:space="preserve">6.97436141967773</t>
   </si>
   <si>
     <t xml:space="preserve">6.83026361465454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95514917373657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80144500732422</t>
+    <t xml:space="preserve">6.95515012741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80144548416138</t>
   </si>
   <si>
     <t xml:space="preserve">6.76622009277344</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8590841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62852621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70537900924683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7470064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86548757553101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16329145431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09604597091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06722545623779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02239465713501</t>
+    <t xml:space="preserve">6.85908317565918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62852716445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70537853240967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74700736999512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86548805236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16329193115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09604501724243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06722593307495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02239608764648</t>
   </si>
   <si>
     <t xml:space="preserve">7.23053789138794</t>
   </si>
   <si>
-    <t xml:space="preserve">7.05761957168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80464553833008</t>
+    <t xml:space="preserve">7.05761909484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80464601516724</t>
   </si>
   <si>
     <t xml:space="preserve">6.89110517501831</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71818685531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73740100860596</t>
+    <t xml:space="preserve">6.71818876266479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7374005317688</t>
   </si>
   <si>
     <t xml:space="preserve">6.95835161209106</t>
   </si>
   <si>
-    <t xml:space="preserve">7.01278877258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88790369033813</t>
+    <t xml:space="preserve">7.01278924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88790416717529</t>
   </si>
   <si>
     <t xml:space="preserve">6.45881032943726</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39796924591064</t>
+    <t xml:space="preserve">6.39796876907349</t>
   </si>
   <si>
     <t xml:space="preserve">6.1520414352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15844488143921</t>
+    <t xml:space="preserve">6.15844535827637</t>
   </si>
   <si>
     <t xml:space="preserve">5.96375226974487</t>
@@ -1910,19 +1910,19 @@
     <t xml:space="preserve">6.10592985153198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10721063613892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39925050735474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6445369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63172817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5900993347168</t>
+    <t xml:space="preserve">6.10721015930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39924955368042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64453649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.63172769546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59010076522827</t>
   </si>
   <si>
     <t xml:space="preserve">6.50043916702271</t>
@@ -1931,115 +1931,115 @@
     <t xml:space="preserve">6.60290956497192</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59650468826294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41718053817749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52285385131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.42038440704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47802305221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44600200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32624006271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26732015609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74380493164062</t>
+    <t xml:space="preserve">6.59650325775146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41718196868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52285432815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4203839302063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47802400588989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44600105285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32624053955078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.2673192024231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74380540847778</t>
   </si>
   <si>
     <t xml:space="preserve">7.09924745559692</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30739068984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19851493835449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08964061737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11846160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15368556976318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15688610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17930126190186</t>
+    <t xml:space="preserve">7.30738973617554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19851589202881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08964157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11846113204956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15368509292603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15688800811768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17930173873901</t>
   </si>
   <si>
     <t xml:space="preserve">7.0448112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99357557296753</t>
+    <t xml:space="preserve">6.99357509613037</t>
   </si>
   <si>
     <t xml:space="preserve">7.27216577529907</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44828748703003</t>
+    <t xml:space="preserve">7.44828605651855</t>
   </si>
   <si>
     <t xml:space="preserve">7.75889778137207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57637214660645</t>
+    <t xml:space="preserve">7.57637310028076</t>
   </si>
   <si>
     <t xml:space="preserve">7.7268762588501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.83895349502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82614469528198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8453574180603</t>
+    <t xml:space="preserve">7.838951587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82614374160767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84535694122314</t>
   </si>
   <si>
     <t xml:space="preserve">7.89979457855225</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91260290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98305177688599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88058137893677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91900634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23282146453857</t>
+    <t xml:space="preserve">7.91260385513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98305082321167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88058042526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91900730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23282051086426</t>
   </si>
   <si>
     <t xml:space="preserve">8.12074565887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26164054870605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47298717498779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46337890625</t>
+    <t xml:space="preserve">8.26164150238037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47298622131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46337985992432</t>
   </si>
   <si>
     <t xml:space="preserve">8.84764194488525</t>
@@ -2051,16 +2051,16 @@
     <t xml:space="preserve">9.26392650604248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33117294311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53290939331055</t>
+    <t xml:space="preserve">9.33117198944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53291034698486</t>
   </si>
   <si>
     <t xml:space="preserve">9.67700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51049423217773</t>
+    <t xml:space="preserve">9.51049518585205</t>
   </si>
   <si>
     <t xml:space="preserve">9.42083263397217</t>
@@ -2069,16 +2069,16 @@
     <t xml:space="preserve">9.32796859741211</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40482234954834</t>
+    <t xml:space="preserve">9.40482330322266</t>
   </si>
   <si>
     <t xml:space="preserve">9.47847270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55212211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57133483886719</t>
+    <t xml:space="preserve">9.55212306976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57133674621582</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026252746582</t>
@@ -2090,22 +2090,22 @@
     <t xml:space="preserve">9.8147029876709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.083685874939</t>
+    <t xml:space="preserve">10.0836868286133</t>
   </si>
   <si>
     <t xml:space="preserve">10.0356521606445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1413249969482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2149753570557</t>
+    <t xml:space="preserve">10.1413259506226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2149744033813</t>
   </si>
   <si>
     <t xml:space="preserve">10.1957626342773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2694120407104</t>
+    <t xml:space="preserve">10.2694129943848</t>
   </si>
   <si>
     <t xml:space="preserve">10.2790193557739</t>
@@ -2114,43 +2114,43 @@
     <t xml:space="preserve">10.56081199646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.849009513855</t>
+    <t xml:space="preserve">10.8490076065063</t>
   </si>
   <si>
     <t xml:space="preserve">10.868221282959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8874340057373</t>
+    <t xml:space="preserve">10.8874349594116</t>
   </si>
   <si>
     <t xml:space="preserve">11.0155220031738</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0603523254395</t>
+    <t xml:space="preserve">11.0603513717651</t>
   </si>
   <si>
     <t xml:space="preserve">11.281304359436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2909107208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5118608474731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5278739929199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4958486557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3773679733276</t>
+    <t xml:space="preserve">11.2909097671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5118598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.495849609375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.377368927002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3261346817017</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4926471710205</t>
+    <t xml:space="preserve">11.4926481246948</t>
   </si>
   <si>
     <t xml:space="preserve">10.8105802536011</t>
@@ -2162,46 +2162,46 @@
     <t xml:space="preserve">10.5992374420166</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0219268798828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1404075622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1141214370728</t>
+    <t xml:space="preserve">11.0219249725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1404085159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1141204833984</t>
   </si>
   <si>
     <t xml:space="preserve">10.7917680740356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7882652282715</t>
+    <t xml:space="preserve">10.7882661819458</t>
   </si>
   <si>
     <t xml:space="preserve">10.4203634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5780363082886</t>
+    <t xml:space="preserve">10.5780353546143</t>
   </si>
   <si>
     <t xml:space="preserve">10.3993396759033</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4273719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2872190475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3888282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4238681793213</t>
+    <t xml:space="preserve">10.4273710250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2872180938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3888292312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4238662719727</t>
   </si>
   <si>
     <t xml:space="preserve">10.3678064346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7322025299072</t>
+    <t xml:space="preserve">10.7322034835815</t>
   </si>
   <si>
     <t xml:space="preserve">10.7742490768433</t>
@@ -2210,25 +2210,25 @@
     <t xml:space="preserve">10.4448900222778</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5079584121704</t>
+    <t xml:space="preserve">10.5079593658447</t>
   </si>
   <si>
     <t xml:space="preserve">10.5149669647217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6305923461914</t>
+    <t xml:space="preserve">10.6305932998657</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127918243408</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1281356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1877012252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3523817062378</t>
+    <t xml:space="preserve">11.128134727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1877002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3523807525635</t>
   </si>
   <si>
     <t xml:space="preserve">11.5731201171875</t>
@@ -2246,22 +2246,22 @@
     <t xml:space="preserve">11.8429145812988</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7097692489624</t>
+    <t xml:space="preserve">11.7097682952881</t>
   </si>
   <si>
     <t xml:space="preserve">11.6291809082031</t>
   </si>
   <si>
-    <t xml:space="preserve">11.863938331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9059839248657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9199991226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0496387481689</t>
+    <t xml:space="preserve">11.8639373779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9059820175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0496406555176</t>
   </si>
   <si>
     <t xml:space="preserve">12.2318382263184</t>
@@ -2276,7 +2276,7 @@
     <t xml:space="preserve">12.214319229126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3159313201904</t>
+    <t xml:space="preserve">12.3159303665161</t>
   </si>
   <si>
     <t xml:space="preserve">12.2773885726929</t>
@@ -2285,31 +2285,31 @@
     <t xml:space="preserve">12.4175415039062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684864044189</t>
+    <t xml:space="preserve">12.3684873580933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1267242431641</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0391283035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464193344116</t>
+    <t xml:space="preserve">12.0391292572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464202880859</t>
   </si>
   <si>
     <t xml:space="preserve">12.0636558532715</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1407403945923</t>
+    <t xml:space="preserve">12.1407384872437</t>
   </si>
   <si>
     <t xml:space="preserve">12.1232204437256</t>
   </si>
   <si>
-    <t xml:space="preserve">12.109206199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0321207046509</t>
+    <t xml:space="preserve">12.1092052459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0321216583252</t>
   </si>
   <si>
     <t xml:space="preserve">11.8779535293579</t>
@@ -2324,19 +2324,19 @@
     <t xml:space="preserve">11.4680051803589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4890298843384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820213317871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6782350540161</t>
+    <t xml:space="preserve">11.4890289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820203781128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6782360076904</t>
   </si>
   <si>
     <t xml:space="preserve">11.2472648620605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.037036895752</t>
+    <t xml:space="preserve">11.0370359420776</t>
   </si>
   <si>
     <t xml:space="preserve">11.1001052856445</t>
@@ -2345,16 +2345,16 @@
     <t xml:space="preserve">10.7216920852661</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9284181594849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1561660766602</t>
+    <t xml:space="preserve">10.9284172058105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1561651229858</t>
   </si>
   <si>
     <t xml:space="preserve">11.496036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4469833374023</t>
+    <t xml:space="preserve">11.4469814300537</t>
   </si>
   <si>
     <t xml:space="preserve">11.184196472168</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">11.3243494033813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2752952575684</t>
+    <t xml:space="preserve">11.2752962112427</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
@@ -2381,10 +2381,10 @@
     <t xml:space="preserve">11.4995393753052</t>
   </si>
   <si>
-    <t xml:space="preserve">11.790358543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8814573287964</t>
+    <t xml:space="preserve">11.7903575897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8814563751221</t>
   </si>
   <si>
     <t xml:space="preserve">11.8288984298706</t>
@@ -2393,16 +2393,16 @@
     <t xml:space="preserve">11.9550371170044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6677236557007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6712274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113803863525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9970836639404</t>
+    <t xml:space="preserve">11.6677227020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6712284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113794326782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9970846176147</t>
   </si>
   <si>
     <t xml:space="preserve">11.9410219192505</t>
@@ -2420,13 +2420,13 @@
     <t xml:space="preserve">12.2738847732544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.102198600769</t>
+    <t xml:space="preserve">12.1021976470947</t>
   </si>
   <si>
     <t xml:space="preserve">12.0951900482178</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9725551605225</t>
+    <t xml:space="preserve">11.9725561141968</t>
   </si>
   <si>
     <t xml:space="preserve">12.0146017074585</t>
@@ -2435,10 +2435,10 @@
     <t xml:space="preserve">12.0741672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9865703582764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6011514663696</t>
+    <t xml:space="preserve">11.9865713119507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6011524200439</t>
   </si>
   <si>
     <t xml:space="preserve">11.552098274231</t>
@@ -2447,94 +2447,94 @@
     <t xml:space="preserve">11.5485935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5941429138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4259605407715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5380821228027</t>
+    <t xml:space="preserve">11.5941438674927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4259595870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5380830764771</t>
   </si>
   <si>
     <t xml:space="preserve">11.6852426528931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7693338394165</t>
+    <t xml:space="preserve">11.7693347930908</t>
   </si>
   <si>
     <t xml:space="preserve">11.7027626037598</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9480285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0846796035767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2108154296875</t>
+    <t xml:space="preserve">11.9480295181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0846786499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2108144760132</t>
   </si>
   <si>
     <t xml:space="preserve">12.7539072036743</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9641380310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7188701629639</t>
+    <t xml:space="preserve">12.9641370773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7188692092896</t>
   </si>
   <si>
     <t xml:space="preserve">12.7889461517334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7959547042847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9886627197266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1743659973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9080772399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.041220664978</t>
+    <t xml:space="preserve">12.7959537506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9886636734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1743650436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9080781936646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0412216186523</t>
   </si>
   <si>
     <t xml:space="preserve">13.2094058990479</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6649017333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8996562957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.365665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389646530151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0173759460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1365041732788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5289335250854</t>
+    <t xml:space="preserve">13.6649007797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8996553421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007024765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3656663894653</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389636993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0173778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1365060806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5289325714111</t>
   </si>
   <si>
     <t xml:space="preserve">15.9493942260742</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7181396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9213619232178</t>
+    <t xml:space="preserve">15.7181415557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9213638305664</t>
   </si>
   <si>
     <t xml:space="preserve">16.1035614013672</t>
@@ -2543,25 +2543,25 @@
     <t xml:space="preserve">15.9914379119873</t>
   </si>
   <si>
-    <t xml:space="preserve">16.124584197998</t>
+    <t xml:space="preserve">16.1245861053467</t>
   </si>
   <si>
     <t xml:space="preserve">16.4118976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5940952301025</t>
+    <t xml:space="preserve">16.5940971374512</t>
   </si>
   <si>
     <t xml:space="preserve">16.5100021362305</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2086734771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0475006103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.886326789856</t>
+    <t xml:space="preserve">16.2086753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0474987030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8863248825073</t>
   </si>
   <si>
     <t xml:space="preserve">15.4868879318237</t>
@@ -2570,10 +2570,10 @@
     <t xml:space="preserve">15.8232555389404</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7531785964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251491546631</t>
+    <t xml:space="preserve">15.7531776428223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251501083374</t>
   </si>
   <si>
     <t xml:space="preserve">15.1575307846069</t>
@@ -2582,46 +2582,46 @@
     <t xml:space="preserve">15.3817739486694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2626428604126</t>
+    <t xml:space="preserve">15.2626447677612</t>
   </si>
   <si>
     <t xml:space="preserve">15.2976818084717</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0804471969604</t>
+    <t xml:space="preserve">15.0804452896118</t>
   </si>
   <si>
     <t xml:space="preserve">15.2836656570435</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2206001281738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.09446144104</t>
+    <t xml:space="preserve">15.2205982208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0944595336914</t>
   </si>
   <si>
     <t xml:space="preserve">15.0664300918579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0454063415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8562002182007</t>
+    <t xml:space="preserve">15.0454044342041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8561992645264</t>
   </si>
   <si>
     <t xml:space="preserve">14.9122619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1715431213379</t>
+    <t xml:space="preserve">15.1715450286865</t>
   </si>
   <si>
     <t xml:space="preserve">14.8702163696289</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7721071243286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3537425994873</t>
+    <t xml:space="preserve">14.7721099853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3537435531616</t>
   </si>
   <si>
     <t xml:space="preserve">16.5029964447021</t>
@@ -2645,31 +2645,31 @@
     <t xml:space="preserve">16.5660648345947</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9865245819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.00754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5380382537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0545082092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3978843688965</t>
+    <t xml:space="preserve">16.9865226745605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0075454711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5380344390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0545063018799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3978824615479</t>
   </si>
   <si>
     <t xml:space="preserve">16.4959888458252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0685214996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499591827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5709800720215</t>
+    <t xml:space="preserve">16.0685234069824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5709781646729</t>
   </si>
   <si>
     <t xml:space="preserve">16.033483505249</t>
@@ -2681,19 +2681,19 @@
     <t xml:space="preserve">16.1666297912598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6431484222412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3908748626709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.762279510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7833023071289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.671178817749</t>
+    <t xml:space="preserve">16.6431522369385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3908729553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7622776031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7833042144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6711807250977</t>
   </si>
   <si>
     <t xml:space="preserve">16.7272434234619</t>
@@ -2705,7 +2705,7 @@
     <t xml:space="preserve">15.6130266189575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5198335647583</t>
+    <t xml:space="preserve">14.5198345184326</t>
   </si>
   <si>
     <t xml:space="preserve">14.3516511917114</t>
@@ -2714,7 +2714,7 @@
     <t xml:space="preserve">14.5478639602661</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7910404205322</t>
+    <t xml:space="preserve">13.7910394668579</t>
   </si>
   <si>
     <t xml:space="preserve">13.4546728134155</t>
@@ -2723,10 +2723,10 @@
     <t xml:space="preserve">13.0272064208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9956722259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3474655151367</t>
+    <t xml:space="preserve">12.9956703186035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.347466468811</t>
   </si>
   <si>
     <t xml:space="preserve">11.7202816009521</t>
@@ -2735,7 +2735,7 @@
     <t xml:space="preserve">10.3327684402466</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68806457519531</t>
+    <t xml:space="preserve">9.688063621521</t>
   </si>
   <si>
     <t xml:space="preserve">9.81069850921631</t>
@@ -2744,22 +2744,22 @@
     <t xml:space="preserve">8.25149822235107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51988124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4442081451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0202465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70490217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77497959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49817562103271</t>
+    <t xml:space="preserve">9.51988220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44420909881592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02024555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70490312576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77497863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49817657470703</t>
   </si>
   <si>
     <t xml:space="preserve">7.59978771209717</t>
@@ -2771,25 +2771,25 @@
     <t xml:space="preserve">9.06088161468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69507312774658</t>
+    <t xml:space="preserve">9.69507217407227</t>
   </si>
   <si>
     <t xml:space="preserve">9.05036926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87167453765869</t>
+    <t xml:space="preserve">8.87167549133301</t>
   </si>
   <si>
     <t xml:space="preserve">9.2360725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87517929077148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07489681243896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68246841430664</t>
+    <t xml:space="preserve">8.87517833709717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07489585876465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68246936798096</t>
   </si>
   <si>
     <t xml:space="preserve">9.0223388671875</t>
@@ -2798,7 +2798,7 @@
     <t xml:space="preserve">9.48834705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1680898666382</t>
+    <t xml:space="preserve">10.1680879592896</t>
   </si>
   <si>
     <t xml:space="preserve">10.2381649017334</t>
@@ -2810,19 +2810,19 @@
     <t xml:space="preserve">9.29914093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4463005065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51637744903564</t>
+    <t xml:space="preserve">9.44630146026611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51637840270996</t>
   </si>
   <si>
     <t xml:space="preserve">9.58995819091797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2535924911499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33417892456055</t>
+    <t xml:space="preserve">9.25359153747559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33417797088623</t>
   </si>
   <si>
     <t xml:space="preserve">9.4953556060791</t>
@@ -2831,13 +2831,13 @@
     <t xml:space="preserve">9.47433185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3713092803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8162956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2122268676758</t>
+    <t xml:space="preserve">10.3713102340698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8162965774536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2122278213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.8793640136719</t>
@@ -2846,7 +2846,7 @@
     <t xml:space="preserve">10.7602338790894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8618450164795</t>
+    <t xml:space="preserve">10.8618459701538</t>
   </si>
   <si>
     <t xml:space="preserve">10.5324859619141</t>
@@ -2855,10 +2855,10 @@
     <t xml:space="preserve">10.6025629043579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6095695495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5394926071167</t>
+    <t xml:space="preserve">10.6095705032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.539493560791</t>
   </si>
   <si>
     <t xml:space="preserve">10.4133558273315</t>
@@ -2867,28 +2867,28 @@
     <t xml:space="preserve">11.0058345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4649333953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7654342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6414775848389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7691898345947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8743648529053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9757843017578</t>
+    <t xml:space="preserve">10.4649343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7654333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6414785385132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.769190788269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8743667602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9757852554321</t>
   </si>
   <si>
     <t xml:space="preserve">10.9720287322998</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3589220046997</t>
+    <t xml:space="preserve">11.358922958374</t>
   </si>
   <si>
     <t xml:space="preserve">11.1936473846436</t>
@@ -2906,37 +2906,37 @@
     <t xml:space="preserve">12.0913925170898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6923952102661</t>
+    <t xml:space="preserve">12.6923961639404</t>
   </si>
   <si>
     <t xml:space="preserve">12.9966506958008</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4407262802124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3956508636475</t>
+    <t xml:space="preserve">12.4407243728638</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3956499099731</t>
   </si>
   <si>
     <t xml:space="preserve">11.6481552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6105918884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5166864395142</t>
+    <t xml:space="preserve">11.6105928421021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5166854858398</t>
   </si>
   <si>
     <t xml:space="preserve">11.7721118927002</t>
   </si>
   <si>
-    <t xml:space="preserve">11.666934967041</t>
+    <t xml:space="preserve">11.6669359207153</t>
   </si>
   <si>
     <t xml:space="preserve">11.5091733932495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7157678604126</t>
+    <t xml:space="preserve">11.7157669067383</t>
   </si>
   <si>
     <t xml:space="preserve">11.5730295181274</t>
@@ -2960,19 +2960,19 @@
     <t xml:space="preserve">11.4265356063843</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3664360046387</t>
+    <t xml:space="preserve">11.366436958313</t>
   </si>
   <si>
     <t xml:space="preserve">11.663179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5429792404175</t>
+    <t xml:space="preserve">11.5429801940918</t>
   </si>
   <si>
     <t xml:space="preserve">11.7796239852905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7608423233032</t>
+    <t xml:space="preserve">11.7608413696289</t>
   </si>
   <si>
     <t xml:space="preserve">11.4753665924072</t>
@@ -2981,25 +2981,25 @@
     <t xml:space="preserve">11.6706924438477</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8585052490234</t>
+    <t xml:space="preserve">11.8585042953491</t>
   </si>
   <si>
     <t xml:space="preserve">11.8434801101685</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3580884933472</t>
+    <t xml:space="preserve">12.3580875396729</t>
   </si>
   <si>
     <t xml:space="preserve">12.3205242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.801326751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6999073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.733715057373</t>
+    <t xml:space="preserve">12.8013257980347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6999082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337141036987</t>
   </si>
   <si>
     <t xml:space="preserve">12.8351316452026</t>
@@ -3008,19 +3008,19 @@
     <t xml:space="preserve">12.5684385299683</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6097555160522</t>
+    <t xml:space="preserve">12.6097564697266</t>
   </si>
   <si>
     <t xml:space="preserve">12.3731117248535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4369697570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0763692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0575857162476</t>
+    <t xml:space="preserve">12.4369707107544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0763683319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0575866699219</t>
   </si>
   <si>
     <t xml:space="preserve">12.3693561553955</t>
@@ -3029,16 +3029,16 @@
     <t xml:space="preserve">12.3505754470825</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4745321273804</t>
+    <t xml:space="preserve">12.4745311737061</t>
   </si>
   <si>
     <t xml:space="preserve">12.493311882019</t>
   </si>
   <si>
-    <t xml:space="preserve">12.470775604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8276205062866</t>
+    <t xml:space="preserve">12.4707765579224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8276214599609</t>
   </si>
   <si>
     <t xml:space="preserve">12.7938137054443</t>
@@ -3053,52 +3053,52 @@
     <t xml:space="preserve">12.4557504653931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5158500671387</t>
+    <t xml:space="preserve">12.515851020813</t>
   </si>
   <si>
     <t xml:space="preserve">12.3468179702759</t>
   </si>
   <si>
-    <t xml:space="preserve">12.21910572052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6661014556885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6247816085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.508337020874</t>
+    <t xml:space="preserve">12.2191047668457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6661005020142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6247825622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5083360671997</t>
   </si>
   <si>
     <t xml:space="preserve">12.3881378173828</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1740312576294</t>
+    <t xml:space="preserve">12.1740303039551</t>
   </si>
   <si>
     <t xml:space="preserve">12.0650997161865</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2641820907593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9749488830566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1552486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8847990036011</t>
+    <t xml:space="preserve">12.264181137085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.974949836731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1552505493164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8847980499268</t>
   </si>
   <si>
     <t xml:space="preserve">12.0688562393188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1101751327515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2078371047974</t>
+    <t xml:space="preserve">12.1101760864258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2078380584717</t>
   </si>
   <si>
     <t xml:space="preserve">12.3843812942505</t>
@@ -3107,40 +3107,40 @@
     <t xml:space="preserve">12.5120944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6285390853882</t>
+    <t xml:space="preserve">12.6285371780396</t>
   </si>
   <si>
     <t xml:space="preserve">12.4257011413574</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8547477722168</t>
+    <t xml:space="preserve">11.8547487258911</t>
   </si>
   <si>
     <t xml:space="preserve">11.8322114944458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8096742630005</t>
+    <t xml:space="preserve">11.8096733093262</t>
   </si>
   <si>
     <t xml:space="preserve">11.6181049346924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3326292037964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7645988464355</t>
+    <t xml:space="preserve">11.3326301574707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7645978927612</t>
   </si>
   <si>
     <t xml:space="preserve">11.5993232727051</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5842990875244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4640979766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3626804351807</t>
+    <t xml:space="preserve">11.5842981338501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4640989303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3626794815063</t>
   </si>
   <si>
     <t xml:space="preserve">11.7120113372803</t>
@@ -3155,31 +3155,31 @@
     <t xml:space="preserve">11.9524116516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.200325012207</t>
+    <t xml:space="preserve">12.2003240585327</t>
   </si>
   <si>
     <t xml:space="preserve">12.2904758453369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1139307022095</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4031620025635</t>
+    <t xml:space="preserve">12.1139316558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4031629562378</t>
   </si>
   <si>
     <t xml:space="preserve">11.944899559021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0989065170288</t>
+    <t xml:space="preserve">12.0989055633545</t>
   </si>
   <si>
     <t xml:space="preserve">12.1514921188354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0801248550415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7007417678833</t>
+    <t xml:space="preserve">12.0801258087158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7007427215576</t>
   </si>
   <si>
     <t xml:space="preserve">11.5241985321045</t>
@@ -3188,13 +3188,13 @@
     <t xml:space="preserve">10.8255338668823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6452350616455</t>
+    <t xml:space="preserve">10.6452341079712</t>
   </si>
   <si>
     <t xml:space="preserve">10.8893899917603</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2499923706055</t>
+    <t xml:space="preserve">11.2499914169312</t>
   </si>
   <si>
     <t xml:space="preserve">11.64439868927</t>
@@ -3203,7 +3203,7 @@
     <t xml:space="preserve">11.8209428787231</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275363922119</t>
+    <t xml:space="preserve">12.0275373458862</t>
   </si>
   <si>
     <t xml:space="preserve">11.8885545730591</t>
@@ -3212,13 +3212,13 @@
     <t xml:space="preserve">12.5834636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4332113265991</t>
+    <t xml:space="preserve">12.4332122802734</t>
   </si>
   <si>
     <t xml:space="preserve">12.4106760025024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1393890380859</t>
+    <t xml:space="preserve">13.1393880844116</t>
   </si>
   <si>
     <t xml:space="preserve">13.2070016860962</t>
@@ -3230,13 +3230,13 @@
     <t xml:space="preserve">13.2370529174805</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2595882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2220268249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6727781295776</t>
+    <t xml:space="preserve">13.2595891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2220277786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6727771759033</t>
   </si>
   <si>
     <t xml:space="preserve">13.357253074646</t>
@@ -3254,31 +3254,31 @@
     <t xml:space="preserve">13.1882209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2896394729614</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2295398712158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619272232056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9327936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1731958389282</t>
+    <t xml:space="preserve">13.2821283340454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2896404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2295389175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9327945709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1731939315796</t>
   </si>
   <si>
     <t xml:space="preserve">13.1919765472412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1957330703735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0154333114624</t>
+    <t xml:space="preserve">13.1957321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0154323577881</t>
   </si>
   <si>
     <t xml:space="preserve">12.82386302948</t>
@@ -3287,70 +3287,70 @@
     <t xml:space="preserve">13.3272018432617</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361333847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4962348937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4323768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3497409820557</t>
+    <t xml:space="preserve">13.4361343383789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4962339401245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4323749542236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.349739074707</t>
   </si>
   <si>
     <t xml:space="preserve">13.3384704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1994886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.413595199585</t>
+    <t xml:space="preserve">13.1994895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4135961532593</t>
   </si>
   <si>
     <t xml:space="preserve">13.4248657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3985710144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.391058921814</t>
+    <t xml:space="preserve">13.3985691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3910608291626</t>
   </si>
   <si>
     <t xml:space="preserve">13.6802892684937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2099227905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.958251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8305406570435</t>
+    <t xml:space="preserve">14.2099237442017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9582538604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8305397033691</t>
   </si>
   <si>
     <t xml:space="preserve">13.8943977355957</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8380517959595</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.931960105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7328786849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4398889541626</t>
+    <t xml:space="preserve">13.8380537033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9319581985474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7328796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4398899078369</t>
   </si>
   <si>
     <t xml:space="preserve">13.4060831069946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.109338760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3009071350098</t>
+    <t xml:space="preserve">13.1093406677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3009090423584</t>
   </si>
   <si>
     <t xml:space="preserve">13.04172706604</t>
@@ -3365,43 +3365,43 @@
     <t xml:space="preserve">13.7216091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3526592254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5855474472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.055082321167</t>
+    <t xml:space="preserve">14.3526611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5855484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0550804138184</t>
   </si>
   <si>
     <t xml:space="preserve">15.092643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.025032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1978197097778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447303771973</t>
+    <t xml:space="preserve">15.0250301361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1978178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447294235229</t>
   </si>
   <si>
     <t xml:space="preserve">14.7207727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9198551177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8221921920776</t>
+    <t xml:space="preserve">14.9198570251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.822193145752</t>
   </si>
   <si>
     <t xml:space="preserve">14.5329608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6005735397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315423965454</t>
+    <t xml:space="preserve">14.6005706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4315404891968</t>
   </si>
   <si>
     <t xml:space="preserve">14.2812919616699</t>
@@ -3410,10 +3410,10 @@
     <t xml:space="preserve">14.9499034881592</t>
   </si>
   <si>
-    <t xml:space="preserve">14.784631729126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7095041275024</t>
+    <t xml:space="preserve">14.7846298217773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7095050811768</t>
   </si>
   <si>
     <t xml:space="preserve">14.6644296646118</t>
@@ -3425,40 +3425,40 @@
     <t xml:space="preserve">14.7958984375</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7620916366577</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9123420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6606731414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4090042114258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1948976516724</t>
+    <t xml:space="preserve">14.7620935440063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9123439788818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6606740951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4090032577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.194899559021</t>
   </si>
   <si>
     <t xml:space="preserve">14.1197729110718</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2024097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2775354385376</t>
+    <t xml:space="preserve">14.202410697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.277533531189</t>
   </si>
   <si>
     <t xml:space="preserve">14.3226099014282</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4202747344971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714418411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2925596237183</t>
+    <t xml:space="preserve">14.4202728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2925577163696</t>
   </si>
   <si>
     <t xml:space="preserve">14.4653472900391</t>
@@ -3467,49 +3467,49 @@
     <t xml:space="preserve">14.7470655441284</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5930624008179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8898057937622</t>
+    <t xml:space="preserve">14.5930614471436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8898048400879</t>
   </si>
   <si>
     <t xml:space="preserve">14.848484992981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2504043579102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1001539230347</t>
+    <t xml:space="preserve">15.2504053115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1001558303833</t>
   </si>
   <si>
     <t xml:space="preserve">15.1151809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0701036453247</t>
+    <t xml:space="preserve">15.070107460022</t>
   </si>
   <si>
     <t xml:space="preserve">15.1827926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7245302200317</t>
+    <t xml:space="preserve">14.7245292663574</t>
   </si>
   <si>
     <t xml:space="preserve">14.7508239746094</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8146800994873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8184366226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9837121963501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0175189971924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7921438217163</t>
+    <t xml:space="preserve">14.814679145813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8184385299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9837112426758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0175170898438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.792142868042</t>
   </si>
   <si>
     <t xml:space="preserve">14.9611730575562</t>
@@ -3518,7 +3518,7 @@
     <t xml:space="preserve">15.1602563858032</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9724435806274</t>
+    <t xml:space="preserve">14.9724426269531</t>
   </si>
   <si>
     <t xml:space="preserve">15.0851306915283</t>
@@ -3530,31 +3530,31 @@
     <t xml:space="preserve">15.3555822372437</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2579183578491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2804546356201</t>
+    <t xml:space="preserve">15.2579164505005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2804565429688</t>
   </si>
   <si>
     <t xml:space="preserve">15.2729434967041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7462310791016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8664302825928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8438959121704</t>
+    <t xml:space="preserve">15.7462329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8664321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8438940048218</t>
   </si>
   <si>
     <t xml:space="preserve">15.641056060791</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6711082458496</t>
+    <t xml:space="preserve">15.708667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.671106338501</t>
   </si>
   <si>
     <t xml:space="preserve">16.1603355407715</t>
@@ -6384,6 +6384,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.1800003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.4000015258789</t>
   </si>
 </sst>
 </file>
@@ -71644,7 +71647,7 @@
     </row>
     <row r="2498">
       <c r="A2498" s="1" t="n">
-        <v>45957.6941666667</v>
+        <v>45957.3333333333</v>
       </c>
       <c r="B2498" t="n">
         <v>550355</v>
@@ -71665,6 +71668,32 @@
         <v>2123</v>
       </c>
       <c r="H2498" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2499">
+      <c r="A2499" s="1" t="n">
+        <v>45958.6941898148</v>
+      </c>
+      <c r="B2499" t="n">
+        <v>2400779</v>
+      </c>
+      <c r="C2499" t="n">
+        <v>34.689998626709</v>
+      </c>
+      <c r="D2499" t="n">
+        <v>32.8300018310547</v>
+      </c>
+      <c r="E2499" t="n">
+        <v>33.0699996948242</v>
+      </c>
+      <c r="F2499" t="n">
+        <v>34.4000015258789</v>
+      </c>
+      <c r="G2499" t="s">
+        <v>2124</v>
+      </c>
+      <c r="H2499" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2125" uniqueCount="2125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2126" uniqueCount="2126">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8295078277588</t>
+    <t xml:space="preserve">10.8295068740845</t>
   </si>
   <si>
     <t xml:space="preserve">AZM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068357467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.486026763916</t>
+    <t xml:space="preserve">10.7068347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4860258102417</t>
   </si>
   <si>
     <t xml:space="preserve">10.191611289978</t>
   </si>
   <si>
-    <t xml:space="preserve">9.91192054748535</t>
+    <t xml:space="preserve">9.91191864013672</t>
   </si>
   <si>
     <t xml:space="preserve">9.93645286560059</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">10.2259616851807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0002431869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61750507354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33290386199951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15135192871094</t>
+    <t xml:space="preserve">10.000244140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61750602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33290576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15135097503662</t>
   </si>
   <si>
     <t xml:space="preserve">9.37706756591797</t>
@@ -83,55 +83,55 @@
     <t xml:space="preserve">9.25930309295654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53899478912354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48992729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50955581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40160274505615</t>
+    <t xml:space="preserve">9.53899574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48992824554443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50955486297607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40160369873047</t>
   </si>
   <si>
     <t xml:space="preserve">9.12681770324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49483489990234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43595218658447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84712409973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99433040618896</t>
+    <t xml:space="preserve">9.49483394622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43595123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84712505340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99433135986328</t>
   </si>
   <si>
     <t xml:space="preserve">8.79805564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05711460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86574459075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32699298858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61058664321899</t>
+    <t xml:space="preserve">8.05711364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86574697494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32699489593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61058902740479</t>
   </si>
   <si>
     <t xml:space="preserve">7.67928409576416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.10127639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87065315246582</t>
+    <t xml:space="preserve">8.10127544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8706521987915</t>
   </si>
   <si>
     <t xml:space="preserve">8.53798961639404</t>
@@ -140,28 +140,28 @@
     <t xml:space="preserve">8.78333377838135</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46929264068604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61649799346924</t>
+    <t xml:space="preserve">8.46929359436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61649990081787</t>
   </si>
   <si>
     <t xml:space="preserve">8.50364208221436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21413326263428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69010448455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71954536437988</t>
+    <t xml:space="preserve">8.21413421630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69010353088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71954441070557</t>
   </si>
   <si>
     <t xml:space="preserve">9.29365062713623</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30837154388428</t>
+    <t xml:space="preserve">9.30837249755859</t>
   </si>
   <si>
     <t xml:space="preserve">9.47520637512207</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">9.09737586975098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22004890441895</t>
+    <t xml:space="preserve">9.22004699707031</t>
   </si>
   <si>
     <t xml:space="preserve">9.41141796112061</t>
@@ -179,55 +179,55 @@
     <t xml:space="preserve">9.48011207580566</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77943325042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66166877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79415416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77452850341797</t>
+    <t xml:space="preserve">9.77943420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79415321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77452659606934</t>
   </si>
   <si>
     <t xml:space="preserve">9.68620204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64694690704346</t>
+    <t xml:space="preserve">9.64694786071777</t>
   </si>
   <si>
     <t xml:space="preserve">9.7254581451416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3044719696045</t>
+    <t xml:space="preserve">10.2357749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3044710159302</t>
   </si>
   <si>
     <t xml:space="preserve">9.83831596374512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56843662261963</t>
+    <t xml:space="preserve">9.56843566894531</t>
   </si>
   <si>
     <t xml:space="preserve">9.98552227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93154811859131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74508476257324</t>
+    <t xml:space="preserve">9.93154525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74508380889893</t>
   </si>
   <si>
     <t xml:space="preserve">10.3780727386475</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5449075698853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4369564056396</t>
+    <t xml:space="preserve">10.5449066162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.436957359314</t>
   </si>
   <si>
     <t xml:space="preserve">10.5547227859497</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">10.5056533813477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5498151779175</t>
+    <t xml:space="preserve">10.5498161315918</t>
   </si>
   <si>
     <t xml:space="preserve">10.5007467269897</t>
@@ -245,28 +245,28 @@
     <t xml:space="preserve">10.5694427490234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4173288345337</t>
+    <t xml:space="preserve">10.4173269271851</t>
   </si>
   <si>
     <t xml:space="preserve">10.4811191558838</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7411842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8442277908325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7853469848633</t>
+    <t xml:space="preserve">10.7411832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8442287445068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7853441238403</t>
   </si>
   <si>
     <t xml:space="preserve">10.5988826751709</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2406826019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2897520065308</t>
+    <t xml:space="preserve">10.2406806945801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2897500991821</t>
   </si>
   <si>
     <t xml:space="preserve">9.7303638458252</t>
@@ -278,52 +278,52 @@
     <t xml:space="preserve">9.43104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40650844573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19060516357422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08265495300293</t>
+    <t xml:space="preserve">9.40650939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19060611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08265590667725</t>
   </si>
   <si>
     <t xml:space="preserve">9.35253429412842</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47029781341553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27892971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30346584320068</t>
+    <t xml:space="preserve">9.47029876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2789306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30346393585205</t>
   </si>
   <si>
     <t xml:space="preserve">9.14644432067871</t>
   </si>
   <si>
-    <t xml:space="preserve">9.52970314025879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79665565490723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190137863159</t>
+    <t xml:space="preserve">9.52970218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79665470123291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.119010925293</t>
   </si>
   <si>
     <t xml:space="preserve">9.89235496520996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95279693603516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492309570312</t>
+    <t xml:space="preserve">9.95279598236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492319107056</t>
   </si>
   <si>
     <t xml:space="preserve">9.84702205657959</t>
   </si>
   <si>
-    <t xml:space="preserve">9.76643466949463</t>
+    <t xml:space="preserve">9.766432762146</t>
   </si>
   <si>
     <t xml:space="preserve">9.42896461486816</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">9.42392730712891</t>
   </si>
   <si>
-    <t xml:space="preserve">9.5246639251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54984951019287</t>
+    <t xml:space="preserve">9.52466583251953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54984855651855</t>
   </si>
   <si>
     <t xml:space="preserve">9.39370727539062</t>
@@ -347,121 +347,121 @@
     <t xml:space="preserve">8.48203945159912</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28560066223145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46189022064209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53744411468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68351173400879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39874362945557</t>
+    <t xml:space="preserve">8.28560256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46189212799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53744316101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68351268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39874172210693</t>
   </si>
   <si>
     <t xml:space="preserve">9.50451755523682</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81680202484131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46459770202637</t>
+    <t xml:space="preserve">9.81680011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692943572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46459627151489</t>
   </si>
   <si>
     <t xml:space="preserve">7.57540655136108</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49985456466675</t>
+    <t xml:space="preserve">7.49985599517822</t>
   </si>
   <si>
     <t xml:space="preserve">7.34875059127808</t>
   </si>
   <si>
-    <t xml:space="preserve">7.43941164016724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20268106460571</t>
+    <t xml:space="preserve">7.43941211700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20268201828003</t>
   </si>
   <si>
     <t xml:space="preserve">6.87025022506714</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50256109237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62848234176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86017608642578</t>
+    <t xml:space="preserve">6.50256013870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62848281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86017656326294</t>
   </si>
   <si>
     <t xml:space="preserve">7.02135515213013</t>
   </si>
   <si>
-    <t xml:space="preserve">7.38904476165771</t>
+    <t xml:space="preserve">7.38904571533203</t>
   </si>
   <si>
     <t xml:space="preserve">7.20771884918213</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44948530197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66607093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52503967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64592218399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79702854156494</t>
+    <t xml:space="preserve">7.44948577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66606998443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52504014968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64592409133911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79702949523926</t>
   </si>
   <si>
     <t xml:space="preserve">7.71140289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">7.94309711456299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81717538833618</t>
+    <t xml:space="preserve">7.94309616088867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8171763420105</t>
   </si>
   <si>
     <t xml:space="preserve">7.94813394546509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0817985534668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92565679550171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71410846710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7896614074707</t>
+    <t xml:space="preserve">7.08179807662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92565536499023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71410799026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.78966045379639</t>
   </si>
   <si>
     <t xml:space="preserve">6.90047025680542</t>
   </si>
   <si>
-    <t xml:space="preserve">7.22786426544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27823495864868</t>
+    <t xml:space="preserve">7.22786474227905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27823400497437</t>
   </si>
   <si>
     <t xml:space="preserve">7.32860279083252</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31852865219116</t>
+    <t xml:space="preserve">7.318528175354</t>
   </si>
   <si>
     <t xml:space="preserve">7.39911842346191</t>
@@ -476,64 +476,64 @@
     <t xml:space="preserve">7.19764471054077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80477094650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02639245986938</t>
+    <t xml:space="preserve">6.80477142333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02639198303223</t>
   </si>
   <si>
     <t xml:space="preserve">7.08683443069458</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04150199890137</t>
+    <t xml:space="preserve">7.04150342941284</t>
   </si>
   <si>
     <t xml:space="preserve">6.85010290145874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86521244049072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069124221802</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22282981872559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31349325180054</t>
+    <t xml:space="preserve">6.86521434783936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069171905518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22282838821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31349229812622</t>
   </si>
   <si>
     <t xml:space="preserve">7.23290252685547</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29838275909424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98106002807617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01128101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53781843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7997350692749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68388652801514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73929309844971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94076538085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90550708770752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.66877603530884</t>
+    <t xml:space="preserve">7.29838228225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98106050491333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01128149032593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53781938552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79973411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68388605117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73929119110107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94076633453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90550851821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66877746582031</t>
   </si>
   <si>
     <t xml:space="preserve">6.4622654914856</t>
@@ -545,91 +545,91 @@
     <t xml:space="preserve">6.67381381988525</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59826040267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8752875328064</t>
+    <t xml:space="preserve">6.59826183319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87528705596924</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624418258667</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15231227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30341911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62577629089355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66103219985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57037210464478</t>
+    <t xml:space="preserve">7.15231323242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30341815948486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.6257758140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66103267669678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57037019729614</t>
   </si>
   <si>
     <t xml:space="preserve">7.45452404022217</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53511333465576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44444990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59555435180664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72147703170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60562944412231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70636606216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48474454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36385917663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26312351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13216543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617099761963</t>
+    <t xml:space="preserve">7.53511190414429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44444942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59555530548096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72147560119629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60562992095947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70636558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48474407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36386013031006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26312303543091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13216590881348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617195129395</t>
   </si>
   <si>
     <t xml:space="preserve">7.17246055603027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.69629192352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91791248321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35611724853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38633918762207</t>
+    <t xml:space="preserve">7.69629096984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91791343688965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35611820220947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38633823394775</t>
   </si>
   <si>
     <t xml:space="preserve">8.51729679107666</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45181751251221</t>
+    <t xml:space="preserve">8.45181655883789</t>
   </si>
   <si>
     <t xml:space="preserve">8.20501232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04887199401855</t>
+    <t xml:space="preserve">8.04887104034424</t>
   </si>
   <si>
     <t xml:space="preserve">7.95820713043213</t>
@@ -638,58 +638,58 @@
     <t xml:space="preserve">7.93132162094116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71623420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73236799240112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63557767868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64095401763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45813274383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.4419994354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57105207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68934917449951</t>
+    <t xml:space="preserve">7.71623516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73236751556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63557815551758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64095449447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45813179016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44200038909912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57105255126953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68934965133667</t>
   </si>
   <si>
     <t xml:space="preserve">7.62482309341431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79689311981201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20018100738525</t>
+    <t xml:space="preserve">7.79689359664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20017910003662</t>
   </si>
   <si>
     <t xml:space="preserve">8.43139839172363</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61959934234619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54432010650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46903991699219</t>
+    <t xml:space="preserve">8.61960029602051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54431915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46903800964355</t>
   </si>
   <si>
     <t xml:space="preserve">8.58733654022217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70025634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54969596862793</t>
+    <t xml:space="preserve">8.70025825500488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54969692230225</t>
   </si>
   <si>
     <t xml:space="preserve">8.60346794128418</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">8.53356456756592</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59809017181396</t>
+    <t xml:space="preserve">8.5980920791626</t>
   </si>
   <si>
     <t xml:space="preserve">8.51743412017822</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5281867980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67875003814697</t>
+    <t xml:space="preserve">8.52818775177002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67874908447266</t>
   </si>
   <si>
     <t xml:space="preserve">9.11429786682129</t>
@@ -719,13 +719,13 @@
     <t xml:space="preserve">9.2003345489502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.17882537841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05515003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33476448059082</t>
+    <t xml:space="preserve">9.17882347106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05515098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3347635269165</t>
   </si>
   <si>
     <t xml:space="preserve">9.13043022155762</t>
@@ -734,22 +734,22 @@
     <t xml:space="preserve">9.44768333435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38315677642822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41004371643066</t>
+    <t xml:space="preserve">9.38315773010254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41004276275635</t>
   </si>
   <si>
     <t xml:space="preserve">9.45843696594238</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4530611038208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37240314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2379732131958</t>
+    <t xml:space="preserve">9.45306015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37240219116211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.32938575744629</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">9.44230461120605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92609977722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0927906036377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07128143310547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76478290557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16807174682617</t>
+    <t xml:space="preserve">8.92609691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09278964996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07128238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76478385925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16807079315186</t>
   </si>
   <si>
     <t xml:space="preserve">9.25948238372803</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">9.28636932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24335098266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26485919952393</t>
+    <t xml:space="preserve">9.24335193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26486015319824</t>
   </si>
   <si>
     <t xml:space="preserve">9.2325963973999</t>
@@ -800,22 +800,22 @@
     <t xml:space="preserve">8.495924949646</t>
   </si>
   <si>
-    <t xml:space="preserve">8.59271430969238</t>
+    <t xml:space="preserve">8.59271335601807</t>
   </si>
   <si>
     <t xml:space="preserve">8.5228099822998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66799449920654</t>
+    <t xml:space="preserve">8.66799354553223</t>
   </si>
   <si>
     <t xml:space="preserve">8.73789691925049</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71101093292236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70563507080078</t>
+    <t xml:space="preserve">8.71101188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70563316345215</t>
   </si>
   <si>
     <t xml:space="preserve">8.63573169708252</t>
@@ -824,79 +824,79 @@
     <t xml:space="preserve">8.53894138336182</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50130176544189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28621482849121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.33461093902588</t>
+    <t xml:space="preserve">8.50130271911621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28621578216553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33460903167725</t>
   </si>
   <si>
     <t xml:space="preserve">8.43677616119385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47441673278809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62497711181641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56582736968994</t>
+    <t xml:space="preserve">8.47441577911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62497615814209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56582832336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.47979259490967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66261672973633</t>
+    <t xml:space="preserve">8.66261768341064</t>
   </si>
   <si>
     <t xml:space="preserve">8.61422252655029</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78091621398926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77015972137451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79166984558105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18420124053955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04977416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14118480682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16269397735596</t>
+    <t xml:space="preserve">8.78091526031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77016067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79166889190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18420219421387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04977226257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14118671417236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16269302368164</t>
   </si>
   <si>
     <t xml:space="preserve">9.30250072479248</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13580894470215</t>
+    <t xml:space="preserve">9.13580703735352</t>
   </si>
   <si>
     <t xml:space="preserve">9.14656162261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20571041107178</t>
+    <t xml:space="preserve">9.20570945739746</t>
   </si>
   <si>
     <t xml:space="preserve">9.62513065338135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63050651550293</t>
+    <t xml:space="preserve">9.63050556182861</t>
   </si>
   <si>
     <t xml:space="preserve">9.60899829864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63588619232178</t>
+    <t xml:space="preserve">9.63588523864746</t>
   </si>
   <si>
     <t xml:space="preserve">9.7165412902832</t>
@@ -911,13 +911,13 @@
     <t xml:space="preserve">10.2435035705566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4155740737915</t>
+    <t xml:space="preserve">10.4155731201172</t>
   </si>
   <si>
     <t xml:space="preserve">10.3456716537476</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2327489852905</t>
+    <t xml:space="preserve">10.2327508926392</t>
   </si>
   <si>
     <t xml:space="preserve">10.3994426727295</t>
@@ -926,43 +926,43 @@
     <t xml:space="preserve">10.4101963043213</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3349180221558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1305837631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036977767944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3295392990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4259719848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5507650375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6074895858765</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847997665405</t>
+    <t xml:space="preserve">10.3349170684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1305847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036987304688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3295383453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.425971031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6074914932251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847988128662</t>
   </si>
   <si>
     <t xml:space="preserve">10.4770231246948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2387790679932</t>
+    <t xml:space="preserve">10.2387809753418</t>
   </si>
   <si>
     <t xml:space="preserve">10.2728157043457</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3408842086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2160921096802</t>
+    <t xml:space="preserve">10.3408851623535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2160911560059</t>
   </si>
   <si>
     <t xml:space="preserve">10.0856237411499</t>
@@ -971,13 +971,13 @@
     <t xml:space="preserve">9.90410614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2898302078247</t>
+    <t xml:space="preserve">10.2898330688477</t>
   </si>
   <si>
     <t xml:space="preserve">10.2614698410034</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1083126068115</t>
+    <t xml:space="preserve">10.1083135604858</t>
   </si>
   <si>
     <t xml:space="preserve">10.0062103271484</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">10.1707105636597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1366767883301</t>
+    <t xml:space="preserve">10.1366748809814</t>
   </si>
   <si>
     <t xml:space="preserve">10.0629348754883</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1990728378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3522281646729</t>
+    <t xml:space="preserve">10.1990718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3522291183472</t>
   </si>
   <si>
     <t xml:space="preserve">10.2104167938232</t>
@@ -1007,13 +1007,13 @@
     <t xml:space="preserve">10.1934003829956</t>
   </si>
   <si>
-    <t xml:space="preserve">9.95515727996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1480207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2444524765015</t>
+    <t xml:space="preserve">9.95515823364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1480226516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2444515228271</t>
   </si>
   <si>
     <t xml:space="preserve">10.2841596603394</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">10.0912971496582</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1593656539917</t>
+    <t xml:space="preserve">10.1593647003174</t>
   </si>
   <si>
     <t xml:space="preserve">10.5450925827026</t>
@@ -1037,25 +1037,25 @@
     <t xml:space="preserve">10.3181943893433</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2955045700073</t>
+    <t xml:space="preserve">10.2955055236816</t>
   </si>
   <si>
     <t xml:space="preserve">10.3692455291748</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4316434860229</t>
+    <t xml:space="preserve">10.4316444396973</t>
   </si>
   <si>
     <t xml:space="preserve">10.397608757019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7152662277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6415252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7436294555664</t>
+    <t xml:space="preserve">10.7152652740479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.641526222229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7436285018921</t>
   </si>
   <si>
     <t xml:space="preserve">10.7209386825562</t>
@@ -1064,31 +1064,31 @@
     <t xml:space="preserve">10.669885635376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7776622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7039213180542</t>
+    <t xml:space="preserve">10.777663230896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7039203643799</t>
   </si>
   <si>
     <t xml:space="preserve">10.6585416793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5394201278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3068494796753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5564374923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4826974868774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3352117538452</t>
+    <t xml:space="preserve">10.539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3068504333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5564365386963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4826955795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3352098464966</t>
   </si>
   <si>
     <t xml:space="preserve">10.2331085205078</t>
@@ -1100,52 +1100,52 @@
     <t xml:space="preserve">10.0288991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.040244102478</t>
+    <t xml:space="preserve">10.0402450561523</t>
   </si>
   <si>
     <t xml:space="preserve">10.0969696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.034571647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9835205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96082782745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98919200897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2274341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2557973861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4940404891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5110578536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4146270751953</t>
+    <t xml:space="preserve">10.0345726013184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98351955413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96082973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2274351119995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2557964324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4940385818481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5110569000244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4146280288696</t>
   </si>
   <si>
     <t xml:space="preserve">10.3635740280151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3805904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4600048065186</t>
+    <t xml:space="preserve">10.3805913925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4600057601929</t>
   </si>
   <si>
     <t xml:space="preserve">10.5167303085327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3465566635132</t>
+    <t xml:space="preserve">10.3465576171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.84738159179688</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">9.7282600402832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67720794677734</t>
+    <t xml:space="preserve">9.67720603942871</t>
   </si>
   <si>
     <t xml:space="preserve">9.66018962860107</t>
@@ -1166,10 +1166,10 @@
     <t xml:space="preserve">9.48434352874756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68855285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58644866943359</t>
+    <t xml:space="preserve">9.688551902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58644771575928</t>
   </si>
   <si>
     <t xml:space="preserve">9.71124076843262</t>
@@ -1178,19 +1178,19 @@
     <t xml:space="preserve">9.67153549194336</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61480903625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62048149108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73393249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78498363494873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79633045196533</t>
+    <t xml:space="preserve">9.6148099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62048244476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73393058776855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78498458862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7963285446167</t>
   </si>
   <si>
     <t xml:space="preserve">9.89843273162842</t>
@@ -1199,37 +1199,37 @@
     <t xml:space="preserve">9.16101360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95113277435303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9908390045166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76961326599121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75259780883789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86604499816895</t>
+    <t xml:space="preserve">8.95113372802734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99083995819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76961421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75259685516357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86604595184326</t>
   </si>
   <si>
     <t xml:space="preserve">8.85470104217529</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05891036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24042797088623</t>
+    <t xml:space="preserve">9.05890941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24042701721191</t>
   </si>
   <si>
     <t xml:space="preserve">9.2517728805542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10996246337891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09294414520264</t>
+    <t xml:space="preserve">9.10996150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09294509887695</t>
   </si>
   <si>
     <t xml:space="preserve">8.98516750335693</t>
@@ -1247,25 +1247,25 @@
     <t xml:space="preserve">8.90008068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88306427001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82633972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79230499267578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79797649383545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96815013885498</t>
+    <t xml:space="preserve">8.8830623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82633876800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79230403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79797554016113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9681510925293</t>
   </si>
   <si>
     <t xml:space="preserve">9.00218486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0702543258667</t>
+    <t xml:space="preserve">9.07025623321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.9965124130249</t>
@@ -1274,34 +1274,34 @@
     <t xml:space="preserve">9.01920223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92277050018311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04189205169678</t>
+    <t xml:space="preserve">8.92277145385742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04189300537109</t>
   </si>
   <si>
     <t xml:space="preserve">9.03054714202881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01353073120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04756355285645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03621959686279</t>
+    <t xml:space="preserve">9.01352977752686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04756546020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03622055053711</t>
   </si>
   <si>
     <t xml:space="preserve">9.13832473754883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97382259368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12697792053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16668605804443</t>
+    <t xml:space="preserve">8.97382164001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12697982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16668701171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.19504737854004</t>
@@ -1310,25 +1310,25 @@
     <t xml:space="preserve">9.37089443206787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38223838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34253215789795</t>
+    <t xml:space="preserve">9.38223934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34253120422363</t>
   </si>
   <si>
     <t xml:space="preserve">9.46732616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.67555809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4202976226807</t>
+    <t xml:space="preserve">10.6755599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.420298576355</t>
   </si>
   <si>
     <t xml:space="preserve">10.3919363021851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5961456298828</t>
+    <t xml:space="preserve">10.5961446762085</t>
   </si>
   <si>
     <t xml:space="preserve">10.7549724578857</t>
@@ -1343,10 +1343,10 @@
     <t xml:space="preserve">10.6613779067993</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4543342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032831192017</t>
+    <t xml:space="preserve">10.4543323516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032821655273</t>
   </si>
   <si>
     <t xml:space="preserve">10.4429883956909</t>
@@ -1355,22 +1355,22 @@
     <t xml:space="preserve">10.3777561187744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0742797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1338376998901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0941324234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98635578155518</t>
+    <t xml:space="preserve">10.0742788314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1338396072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0941314697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98635768890381</t>
   </si>
   <si>
     <t xml:space="preserve">10.1565284729004</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1962356567383</t>
+    <t xml:space="preserve">10.1962366104126</t>
   </si>
   <si>
     <t xml:space="preserve">10.2359437942505</t>
@@ -1382,37 +1382,37 @@
     <t xml:space="preserve">10.2416162490845</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2501239776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132530212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.167875289917</t>
+    <t xml:space="preserve">10.2501249313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132539749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1678743362427</t>
   </si>
   <si>
     <t xml:space="preserve">9.90694046020508</t>
   </si>
   <si>
-    <t xml:space="preserve">9.92963123321533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1877279281616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2302722930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0203895568848</t>
+    <t xml:space="preserve">9.92963027954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1877269744873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2302703857422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0203905105591</t>
   </si>
   <si>
     <t xml:space="preserve">10.1905641555786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1820554733276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0317344665527</t>
+    <t xml:space="preserve">10.1820573806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0317354202271</t>
   </si>
   <si>
     <t xml:space="preserve">9.9778470993042</t>
@@ -1433,40 +1433,40 @@
     <t xml:space="preserve">9.97500991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0657691955566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1395130157471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0005369186401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686054229736</t>
+    <t xml:space="preserve">10.065770149231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1395111083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0005350112915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686044692993</t>
   </si>
   <si>
     <t xml:space="preserve">9.73676776885986</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83603572845459</t>
+    <t xml:space="preserve">9.83603668212891</t>
   </si>
   <si>
     <t xml:space="preserve">9.89276027679443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8672342300415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82752704620361</t>
+    <t xml:space="preserve">9.86723518371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8275260925293</t>
   </si>
   <si>
     <t xml:space="preserve">9.77931118011475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83320045471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94948387145996</t>
+    <t xml:space="preserve">9.8331995010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94948577880859</t>
   </si>
   <si>
     <t xml:space="preserve">10.0714416503906</t>
@@ -1475,34 +1475,34 @@
     <t xml:space="preserve">9.93814086914062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71407794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42761898040771</t>
+    <t xml:space="preserve">9.71407699584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42761993408203</t>
   </si>
   <si>
     <t xml:space="preserve">9.10145282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21773910522461</t>
+    <t xml:space="preserve">9.21773815155029</t>
   </si>
   <si>
     <t xml:space="preserve">9.12414264678955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24326419830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20072174072266</t>
+    <t xml:space="preserve">9.24326515197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20072078704834</t>
   </si>
   <si>
     <t xml:space="preserve">9.29274559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51369667053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39841747283936</t>
+    <t xml:space="preserve">9.51369762420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39841842651367</t>
   </si>
   <si>
     <t xml:space="preserve">9.47206783294678</t>
@@ -1511,31 +1511,31 @@
     <t xml:space="preserve">9.44004726409912</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33757591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9853343963623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02696514129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89887714385986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34397983551025</t>
+    <t xml:space="preserve">9.3375768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98533725738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02696418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89887619018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34398078918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.31836318969727</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9373025894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92129135131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.93410110473633</t>
+    <t xml:space="preserve">8.93730354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92129039764404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93410205841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.64590358734131</t>
@@ -1553,13 +1553,13 @@
     <t xml:space="preserve">8.71635150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64270210266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8284273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.80601215362549</t>
+    <t xml:space="preserve">8.64270114898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82842922210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.8060131072998</t>
   </si>
   <si>
     <t xml:space="preserve">8.83163070678711</t>
@@ -1568,10 +1568,10 @@
     <t xml:space="preserve">8.66511726379395</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73556423187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5178165435791</t>
+    <t xml:space="preserve">8.73556613922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51781558990479</t>
   </si>
   <si>
     <t xml:space="preserve">8.48899745941162</t>
@@ -1580,7 +1580,7 @@
     <t xml:space="preserve">8.56905078887939</t>
   </si>
   <si>
-    <t xml:space="preserve">8.45697498321533</t>
+    <t xml:space="preserve">8.45697593688965</t>
   </si>
   <si>
     <t xml:space="preserve">8.39613342285156</t>
@@ -1589,10 +1589,10 @@
     <t xml:space="preserve">8.51141166687012</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53062534332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53702926635742</t>
+    <t xml:space="preserve">8.53062629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53703022003174</t>
   </si>
   <si>
     <t xml:space="preserve">8.54343318939209</t>
@@ -1601,7 +1601,7 @@
     <t xml:space="preserve">8.71315002441406</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40574073791504</t>
+    <t xml:space="preserve">8.40573978424072</t>
   </si>
   <si>
     <t xml:space="preserve">8.36411094665527</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">8.46658134460449</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58186054229736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44096565246582</t>
+    <t xml:space="preserve">8.58185958862305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4409646987915</t>
   </si>
   <si>
     <t xml:space="preserve">9.09421062469482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01735782623291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05578231811523</t>
+    <t xml:space="preserve">9.01735877990723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05578327178955</t>
   </si>
   <si>
     <t xml:space="preserve">9.1998815536499</t>
@@ -1646,34 +1646,34 @@
     <t xml:space="preserve">9.18707370758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91808986663818</t>
+    <t xml:space="preserve">8.9180908203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.87646198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03657150268555</t>
+    <t xml:space="preserve">9.03657054901123</t>
   </si>
   <si>
     <t xml:space="preserve">9.18387126922607</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15505218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1518497467041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23510456085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16465854644775</t>
+    <t xml:space="preserve">9.15505123138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15184879302979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23510646820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16465950012207</t>
   </si>
   <si>
     <t xml:space="preserve">9.1262321472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2607250213623</t>
+    <t xml:space="preserve">9.26072216033936</t>
   </si>
   <si>
     <t xml:space="preserve">9.254319190979</t>
@@ -1682,25 +1682,25 @@
     <t xml:space="preserve">9.20628643035889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20948791503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22550010681152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10701847076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92769622802734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76758766174316</t>
+    <t xml:space="preserve">9.20948886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22549915313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10701942443848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92769718170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76758670806885</t>
   </si>
   <si>
     <t xml:space="preserve">8.65871238708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68112659454346</t>
+    <t xml:space="preserve">8.68112850189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.72595882415771</t>
@@ -1715,28 +1715,28 @@
     <t xml:space="preserve">8.82202529907227</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77719497680664</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78359794616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95331478118896</t>
+    <t xml:space="preserve">8.77719402313232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78359699249268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95331382751465</t>
   </si>
   <si>
     <t xml:space="preserve">8.97252655029297</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96612167358398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86685562133789</t>
+    <t xml:space="preserve">8.9661226272583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86685466766357</t>
   </si>
   <si>
     <t xml:space="preserve">8.86045074462891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.32568454742432</t>
+    <t xml:space="preserve">8.32568550109863</t>
   </si>
   <si>
     <t xml:space="preserve">8.22321510314941</t>
@@ -1751,58 +1751,58 @@
     <t xml:space="preserve">8.48259258270264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.40253639221191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.14956474304199</t>
+    <t xml:space="preserve">8.40253734588623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.14956569671631</t>
   </si>
   <si>
     <t xml:space="preserve">8.06630706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07271194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77490997314453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74929094314575</t>
+    <t xml:space="preserve">8.07271099090576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7749080657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74929141998291</t>
   </si>
   <si>
     <t xml:space="preserve">7.67884302139282</t>
   </si>
   <si>
-    <t xml:space="preserve">7.87417650222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73007917404175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53474473953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42266988754272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25295257568359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21772813796997</t>
+    <t xml:space="preserve">7.87417697906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73007822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53474426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42266941070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25295162200928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21772909164429</t>
   </si>
   <si>
     <t xml:space="preserve">7.08003520965576</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11205673217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84947681427002</t>
+    <t xml:space="preserve">7.11205530166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8494758605957</t>
   </si>
   <si>
     <t xml:space="preserve">6.97116041183472</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04160737991333</t>
+    <t xml:space="preserve">7.04160785675049</t>
   </si>
   <si>
     <t xml:space="preserve">7.03520441055298</t>
@@ -1811,28 +1811,28 @@
     <t xml:space="preserve">7.04801225662231</t>
   </si>
   <si>
-    <t xml:space="preserve">6.94234037399292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95194625854492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0095853805542</t>
+    <t xml:space="preserve">6.94234085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95194673538208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00958728790283</t>
   </si>
   <si>
     <t xml:space="preserve">7.1312689781189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97436141967773</t>
+    <t xml:space="preserve">6.97436189651489</t>
   </si>
   <si>
     <t xml:space="preserve">6.83026361465454</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95515012741089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80144548416138</t>
+    <t xml:space="preserve">6.95514917373657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80144453048706</t>
   </si>
   <si>
     <t xml:space="preserve">6.76622009277344</t>
@@ -1841,31 +1841,31 @@
     <t xml:space="preserve">6.85908317565918</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62852716445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70537853240967</t>
+    <t xml:space="preserve">6.62852573394775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70537948608398</t>
   </si>
   <si>
     <t xml:space="preserve">6.74700736999512</t>
   </si>
   <si>
-    <t xml:space="preserve">6.86548805236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16329193115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09604501724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06722593307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02239608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23053789138794</t>
+    <t xml:space="preserve">6.86548757553101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16329097747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09604549407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06722545623779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02239465713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23053693771362</t>
   </si>
   <si>
     <t xml:space="preserve">7.05761909484863</t>
@@ -1877,10 +1877,10 @@
     <t xml:space="preserve">6.89110517501831</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71818876266479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7374005317688</t>
+    <t xml:space="preserve">6.71818685531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73740100860596</t>
   </si>
   <si>
     <t xml:space="preserve">6.95835161209106</t>
@@ -1889,79 +1889,79 @@
     <t xml:space="preserve">7.01278924942017</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88790416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45881032943726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39796876907349</t>
+    <t xml:space="preserve">6.88790369033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4588098526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39796924591064</t>
   </si>
   <si>
     <t xml:space="preserve">6.1520414352417</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15844535827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96375226974487</t>
+    <t xml:space="preserve">6.15844488143921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96375179290771</t>
   </si>
   <si>
     <t xml:space="preserve">6.10592985153198</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10721015930176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39924955368042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.64453649520874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63172769546509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59010076522827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50043916702271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60290956497192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59650325775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41718196868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52285432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4203839302063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.47802400588989</t>
+    <t xml:space="preserve">6.10721063613892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39925003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64453601837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6317286491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59010028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50043964385986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60290861129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59650564193726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41718101501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52285480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42038440704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.47802305221558</t>
   </si>
   <si>
     <t xml:space="preserve">6.44600105285645</t>
   </si>
   <si>
-    <t xml:space="preserve">6.32624053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.2673192024231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74380540847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09924745559692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30738973617554</t>
+    <t xml:space="preserve">6.32624101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26732015609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74380445480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09924793243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30739068984985</t>
   </si>
   <si>
     <t xml:space="preserve">7.19851589202881</t>
@@ -1976,22 +1976,22 @@
     <t xml:space="preserve">7.15368509292603</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15688800811768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17930173873901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0448112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99357509613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27216577529907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44828605651855</t>
+    <t xml:space="preserve">7.1568865776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17930269241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04481029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99357604980469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27216529846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4482855796814</t>
   </si>
   <si>
     <t xml:space="preserve">7.75889778137207</t>
@@ -2000,55 +2000,55 @@
     <t xml:space="preserve">7.57637310028076</t>
   </si>
   <si>
-    <t xml:space="preserve">7.7268762588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.838951587677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82614374160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84535694122314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89979457855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91260385513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98305082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88058042526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91900730133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23282051086426</t>
+    <t xml:space="preserve">7.72687578201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83895206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82614469528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8453574180603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8997950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9126033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98305177688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88058090209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91900873184204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23282146453857</t>
   </si>
   <si>
     <t xml:space="preserve">8.12074565887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26164150238037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47298622131348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46337985992432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84764194488525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.91168594360352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26392650604248</t>
+    <t xml:space="preserve">8.26164054870605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47298526763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46337890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84764099121094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.91168689727783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2639274597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.33117198944092</t>
@@ -2060,7 +2060,7 @@
     <t xml:space="preserve">9.67700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51049518585205</t>
+    <t xml:space="preserve">9.51049327850342</t>
   </si>
   <si>
     <t xml:space="preserve">9.42083263397217</t>
@@ -2072,22 +2072,22 @@
     <t xml:space="preserve">9.40482330322266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47847270965576</t>
+    <t xml:space="preserve">9.47847366333008</t>
   </si>
   <si>
     <t xml:space="preserve">9.55212306976318</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57133674621582</t>
+    <t xml:space="preserve">9.5713357925415</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026252746582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77627563476562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8147029876709</t>
+    <t xml:space="preserve">9.77627658843994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81470203399658</t>
   </si>
   <si>
     <t xml:space="preserve">10.0836868286133</t>
@@ -2096,31 +2096,31 @@
     <t xml:space="preserve">10.0356521606445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1413259506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2149744033813</t>
+    <t xml:space="preserve">10.1413249969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2149753570557</t>
   </si>
   <si>
     <t xml:space="preserve">10.1957626342773</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2694129943848</t>
+    <t xml:space="preserve">10.2694120407104</t>
   </si>
   <si>
     <t xml:space="preserve">10.2790193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">10.56081199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8490076065063</t>
+    <t xml:space="preserve">10.5608129501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8490085601807</t>
   </si>
   <si>
     <t xml:space="preserve">10.868221282959</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8874349594116</t>
+    <t xml:space="preserve">10.8874340057373</t>
   </si>
   <si>
     <t xml:space="preserve">11.0155220031738</t>
@@ -2132,37 +2132,37 @@
     <t xml:space="preserve">11.281304359436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2909097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5118598937988</t>
+    <t xml:space="preserve">11.2909107208252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5118608474731</t>
   </si>
   <si>
     <t xml:space="preserve">11.5278720855713</t>
   </si>
   <si>
-    <t xml:space="preserve">11.495849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.377368927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3261346817017</t>
+    <t xml:space="preserve">11.4958505630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3773679733276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3261337280273</t>
   </si>
   <si>
     <t xml:space="preserve">11.4926481246948</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8105802536011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9899053573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5992374420166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219249725342</t>
+    <t xml:space="preserve">10.8105812072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9899044036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5992383956909</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219268798828</t>
   </si>
   <si>
     <t xml:space="preserve">11.1404085159302</t>
@@ -2171,58 +2171,58 @@
     <t xml:space="preserve">11.1141204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7917680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7882661819458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4203634262085</t>
+    <t xml:space="preserve">10.79176902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882642745972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4203643798828</t>
   </si>
   <si>
     <t xml:space="preserve">10.5780353546143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3993396759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4273710250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2872180938721</t>
+    <t xml:space="preserve">10.399341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4273719787598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2872190475464</t>
   </si>
   <si>
     <t xml:space="preserve">10.3888292312622</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4238662719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3678064346313</t>
+    <t xml:space="preserve">10.4238681793213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3678073883057</t>
   </si>
   <si>
     <t xml:space="preserve">10.7322034835815</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7742490768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4448900222778</t>
+    <t xml:space="preserve">10.7742500305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4448890686035</t>
   </si>
   <si>
     <t xml:space="preserve">10.5079593658447</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5149669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6305932998657</t>
+    <t xml:space="preserve">10.5149660110474</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6305923461914</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127918243408</t>
   </si>
   <si>
-    <t xml:space="preserve">11.128134727478</t>
+    <t xml:space="preserve">11.1281356811523</t>
   </si>
   <si>
     <t xml:space="preserve">11.1877002716064</t>
@@ -2237,10 +2237,10 @@
     <t xml:space="preserve">11.6151676177979</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7553186416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7342967987061</t>
+    <t xml:space="preserve">11.7553195953369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7342958450317</t>
   </si>
   <si>
     <t xml:space="preserve">11.8429145812988</t>
@@ -2255,22 +2255,22 @@
     <t xml:space="preserve">11.8639373779297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9059820175171</t>
+    <t xml:space="preserve">11.9059829711914</t>
   </si>
   <si>
     <t xml:space="preserve">11.9200000762939</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0496406555176</t>
+    <t xml:space="preserve">12.0496397018433</t>
   </si>
   <si>
     <t xml:space="preserve">12.2318382263184</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2248306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2984113693237</t>
+    <t xml:space="preserve">12.2248315811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2984104156494</t>
   </si>
   <si>
     <t xml:space="preserve">12.214319229126</t>
@@ -2279,34 +2279,34 @@
     <t xml:space="preserve">12.3159303665161</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2773885726929</t>
+    <t xml:space="preserve">12.2773895263672</t>
   </si>
   <si>
     <t xml:space="preserve">12.4175415039062</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684873580933</t>
+    <t xml:space="preserve">12.3684883117676</t>
   </si>
   <si>
     <t xml:space="preserve">12.1267242431641</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0391292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1407384872437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1232204437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1092052459717</t>
+    <t xml:space="preserve">12.0391273498535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464183807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636548995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1407413482666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.123218536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.109206199646</t>
   </si>
   <si>
     <t xml:space="preserve">12.0321216583252</t>
@@ -2318,16 +2318,16 @@
     <t xml:space="preserve">11.9760608673096</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6887474060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4680051803589</t>
+    <t xml:space="preserve">11.6887464523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4680061340332</t>
   </si>
   <si>
     <t xml:space="preserve">11.4890289306641</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4820203781128</t>
+    <t xml:space="preserve">11.4820222854614</t>
   </si>
   <si>
     <t xml:space="preserve">11.6782360076904</t>
@@ -2354,7 +2354,7 @@
     <t xml:space="preserve">11.496036529541</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4469814300537</t>
+    <t xml:space="preserve">11.446982383728</t>
   </si>
   <si>
     <t xml:space="preserve">11.184196472168</t>
@@ -2363,7 +2363,7 @@
     <t xml:space="preserve">11.3243494033813</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2752962112427</t>
+    <t xml:space="preserve">11.275297164917</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
@@ -2372,19 +2372,19 @@
     <t xml:space="preserve">11.4049367904663</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2297458648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4119453430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4995393753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7903575897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8814563751221</t>
+    <t xml:space="preserve">11.2297468185425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4119443893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4995403289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.790358543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8814573287964</t>
   </si>
   <si>
     <t xml:space="preserve">11.8288984298706</t>
@@ -2393,34 +2393,34 @@
     <t xml:space="preserve">11.9550371170044</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6677227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6712284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113794326782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9970846176147</t>
+    <t xml:space="preserve">11.6677236557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6712274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113803863525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9970836639404</t>
   </si>
   <si>
     <t xml:space="preserve">11.9410219192505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9690523147583</t>
+    <t xml:space="preserve">11.969051361084</t>
   </si>
   <si>
     <t xml:space="preserve">12.0671586990356</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2703819274902</t>
+    <t xml:space="preserve">12.2703809738159</t>
   </si>
   <si>
     <t xml:space="preserve">12.2738847732544</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1021976470947</t>
+    <t xml:space="preserve">12.1021966934204</t>
   </si>
   <si>
     <t xml:space="preserve">12.0951900482178</t>
@@ -2429,31 +2429,31 @@
     <t xml:space="preserve">11.9725561141968</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0146017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741672515869</t>
+    <t xml:space="preserve">12.0146026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741662979126</t>
   </si>
   <si>
     <t xml:space="preserve">11.9865713119507</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6011524200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.552098274231</t>
+    <t xml:space="preserve">11.6011514663696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5520992279053</t>
   </si>
   <si>
     <t xml:space="preserve">11.5485935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5941438674927</t>
+    <t xml:space="preserve">11.5941429138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.4259595870972</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5380830764771</t>
+    <t xml:space="preserve">11.5380811691284</t>
   </si>
   <si>
     <t xml:space="preserve">11.6852426528931</t>
@@ -2462,22 +2462,22 @@
     <t xml:space="preserve">11.7693347930908</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7027626037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9480295181274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0846786499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2108144760132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7539072036743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9641370773315</t>
+    <t xml:space="preserve">11.7027616500854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9480285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0846796035767</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2108154296875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7539081573486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9641389846802</t>
   </si>
   <si>
     <t xml:space="preserve">12.7188692092896</t>
@@ -2486,148 +2486,148 @@
     <t xml:space="preserve">12.7889461517334</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7959537506104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9886636734009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1743650436401</t>
+    <t xml:space="preserve">12.795952796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9886646270752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1743669509888</t>
   </si>
   <si>
     <t xml:space="preserve">12.9080781936646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0412216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094058990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6649007797241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8996553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007024765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3656663894653</t>
+    <t xml:space="preserve">13.041223526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094049453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6649017333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8996562957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007034301758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3656673431396</t>
   </si>
   <si>
     <t xml:space="preserve">14.6389636993408</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0173778533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1365060806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5289325714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9493942260742</t>
+    <t xml:space="preserve">15.0173759460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1365070343018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5289335250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9493932723999</t>
   </si>
   <si>
     <t xml:space="preserve">15.7181415557861</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9213638305664</t>
+    <t xml:space="preserve">15.9213619232178</t>
   </si>
   <si>
     <t xml:space="preserve">16.1035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9914379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1245861053467</t>
+    <t xml:space="preserve">15.9914388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.124584197998</t>
   </si>
   <si>
     <t xml:space="preserve">16.4118976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5940971374512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5100021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2086753845215</t>
+    <t xml:space="preserve">16.5940952301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5100040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2086734771729</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474987030029</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8863248825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4868879318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8232555389404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7531776428223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251501083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1575307846069</t>
+    <t xml:space="preserve">15.8863229751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4868869781494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8232545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7531805038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251482009888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1575288772583</t>
   </si>
   <si>
     <t xml:space="preserve">15.3817739486694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2626447677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2976818084717</t>
+    <t xml:space="preserve">15.2626438140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2976837158203</t>
   </si>
   <si>
     <t xml:space="preserve">15.0804452896118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2836656570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2205982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0944595336914</t>
+    <t xml:space="preserve">15.2836666107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2205972671509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0944604873657</t>
   </si>
   <si>
     <t xml:space="preserve">15.0664300918579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0454044342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8561992645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9122619628906</t>
+    <t xml:space="preserve">15.0454063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8562021255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9122629165649</t>
   </si>
   <si>
     <t xml:space="preserve">15.1715450286865</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8702163696289</t>
+    <t xml:space="preserve">14.8702144622803</t>
   </si>
   <si>
     <t xml:space="preserve">14.7721099853516</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3537435531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5029964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5800800323486</t>
+    <t xml:space="preserve">15.3537445068359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5029945373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5800819396973</t>
   </si>
   <si>
     <t xml:space="preserve">16.4189052581787</t>
@@ -2639,16 +2639,16 @@
     <t xml:space="preserve">16.8043251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.622127532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5660648345947</t>
+    <t xml:space="preserve">16.6221256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5660629272461</t>
   </si>
   <si>
     <t xml:space="preserve">16.9865226745605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0075454711914</t>
+    <t xml:space="preserve">17.0075492858887</t>
   </si>
   <si>
     <t xml:space="preserve">16.5380344390869</t>
@@ -2663,40 +2663,40 @@
     <t xml:space="preserve">16.4959888458252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0685234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499572753906</t>
+    <t xml:space="preserve">16.0685253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499582290649</t>
   </si>
   <si>
     <t xml:space="preserve">15.5709781646729</t>
   </si>
   <si>
-    <t xml:space="preserve">16.033483505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9423847198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1666297912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6431522369385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3908729553223</t>
+    <t xml:space="preserve">16.0334854125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9423837661743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1666278839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6431484222412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3908748626709</t>
   </si>
   <si>
     <t xml:space="preserve">16.7622776031494</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7833042144775</t>
+    <t xml:space="preserve">16.7833023071289</t>
   </si>
   <si>
     <t xml:space="preserve">16.6711807250977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272434234619</t>
+    <t xml:space="preserve">16.7272396087646</t>
   </si>
   <si>
     <t xml:space="preserve">16.9514865875244</t>
@@ -2705,13 +2705,13 @@
     <t xml:space="preserve">15.6130266189575</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5198345184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3516511917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5478639602661</t>
+    <t xml:space="preserve">14.5198335647583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3516502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5478658676147</t>
   </si>
   <si>
     <t xml:space="preserve">13.7910394668579</t>
@@ -2723,40 +2723,40 @@
     <t xml:space="preserve">13.0272064208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9956703186035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.347466468811</t>
+    <t xml:space="preserve">12.9956722259521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3474645614624</t>
   </si>
   <si>
     <t xml:space="preserve">11.7202816009521</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3327684402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.688063621521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81069850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25149822235107</t>
+    <t xml:space="preserve">10.3327674865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68806552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81069946289062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25149726867676</t>
   </si>
   <si>
     <t xml:space="preserve">9.51988220214844</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44420909881592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.02024555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70490312576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77497863769531</t>
+    <t xml:space="preserve">8.4442081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.0202465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70490217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77497911453247</t>
   </si>
   <si>
     <t xml:space="preserve">7.49817657470703</t>
@@ -2765,16 +2765,16 @@
     <t xml:space="preserve">7.59978771209717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.28653717041016</t>
+    <t xml:space="preserve">8.28653621673584</t>
   </si>
   <si>
     <t xml:space="preserve">9.06088161468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69507217407227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05036926269531</t>
+    <t xml:space="preserve">9.69507312774658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05037021636963</t>
   </si>
   <si>
     <t xml:space="preserve">8.87167549133301</t>
@@ -2783,49 +2783,49 @@
     <t xml:space="preserve">9.2360725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87517833709717</t>
+    <t xml:space="preserve">8.87517929077148</t>
   </si>
   <si>
     <t xml:space="preserve">9.07489585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68246936798096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0223388671875</t>
+    <t xml:space="preserve">8.68246841430664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02233791351318</t>
   </si>
   <si>
     <t xml:space="preserve">9.48834705352783</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1680879592896</t>
+    <t xml:space="preserve">10.1680889129639</t>
   </si>
   <si>
     <t xml:space="preserve">10.2381649017334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87727165222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29914093017578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44630146026611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51637840270996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58995819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25359153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33417797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4953556060791</t>
+    <t xml:space="preserve">9.87726974487305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29913997650146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4463005065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51637744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58995914459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2535924911499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33417892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49535369873047</t>
   </si>
   <si>
     <t xml:space="preserve">9.47433185577393</t>
@@ -2834,7 +2834,7 @@
     <t xml:space="preserve">10.3713102340698</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8162965774536</t>
+    <t xml:space="preserve">10.816294670105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2122278213501</t>
@@ -2846,13 +2846,13 @@
     <t xml:space="preserve">10.7602338790894</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8618459701538</t>
+    <t xml:space="preserve">10.8618450164795</t>
   </si>
   <si>
     <t xml:space="preserve">10.5324859619141</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6025629043579</t>
+    <t xml:space="preserve">10.6025619506836</t>
   </si>
   <si>
     <t xml:space="preserve">10.6095705032349</t>
@@ -2861,7 +2861,7 @@
     <t xml:space="preserve">10.539493560791</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4133558273315</t>
+    <t xml:space="preserve">10.4133548736572</t>
   </si>
   <si>
     <t xml:space="preserve">11.0058345794678</t>
@@ -2870,10 +2870,10 @@
     <t xml:space="preserve">10.4649343490601</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7654333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6414785385132</t>
+    <t xml:space="preserve">10.7654342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6414775848389</t>
   </si>
   <si>
     <t xml:space="preserve">10.769190788269</t>
@@ -2882,25 +2882,25 @@
     <t xml:space="preserve">10.8743667602539</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9757852554321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9720287322998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.358922958374</t>
+    <t xml:space="preserve">10.9757843017578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9720277786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3589239120483</t>
   </si>
   <si>
     <t xml:space="preserve">11.1936473846436</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3251152038574</t>
+    <t xml:space="preserve">11.3251171112061</t>
   </si>
   <si>
     <t xml:space="preserve">11.5204429626465</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7984056472778</t>
+    <t xml:space="preserve">11.7984046936035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913925170898</t>
@@ -2909,40 +2909,40 @@
     <t xml:space="preserve">12.6923961639404</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9966506958008</t>
+    <t xml:space="preserve">12.9966497421265</t>
   </si>
   <si>
     <t xml:space="preserve">12.4407243728638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3956499099731</t>
+    <t xml:space="preserve">12.3956508636475</t>
   </si>
   <si>
     <t xml:space="preserve">11.6481552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6105928421021</t>
+    <t xml:space="preserve">11.6105918884277</t>
   </si>
   <si>
     <t xml:space="preserve">11.5166854858398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7721118927002</t>
+    <t xml:space="preserve">11.7721109390259</t>
   </si>
   <si>
     <t xml:space="preserve">11.6669359207153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5091733932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7157669067383</t>
+    <t xml:space="preserve">11.5091724395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7157678604126</t>
   </si>
   <si>
     <t xml:space="preserve">11.5730295181274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8284549713135</t>
+    <t xml:space="preserve">11.8284559249878</t>
   </si>
   <si>
     <t xml:space="preserve">11.2687730789185</t>
@@ -2951,61 +2951,61 @@
     <t xml:space="preserve">11.4490728378296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2011594772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4791221618652</t>
+    <t xml:space="preserve">11.2011604309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4791240692139</t>
   </si>
   <si>
     <t xml:space="preserve">11.4265356063843</t>
   </si>
   <si>
-    <t xml:space="preserve">11.366436958313</t>
+    <t xml:space="preserve">11.3664350509644</t>
   </si>
   <si>
     <t xml:space="preserve">11.663179397583</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5429801940918</t>
+    <t xml:space="preserve">11.5429782867432</t>
   </si>
   <si>
     <t xml:space="preserve">11.7796239852905</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7608413696289</t>
+    <t xml:space="preserve">11.7608423233032</t>
   </si>
   <si>
     <t xml:space="preserve">11.4753665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6706924438477</t>
+    <t xml:space="preserve">11.6706914901733</t>
   </si>
   <si>
     <t xml:space="preserve">11.8585042953491</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8434801101685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3580875396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3205242156982</t>
+    <t xml:space="preserve">11.8434820175171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3580884933472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3205251693726</t>
   </si>
   <si>
     <t xml:space="preserve">12.8013257980347</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6999082565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7337141036987</t>
+    <t xml:space="preserve">12.6999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337131500244</t>
   </si>
   <si>
     <t xml:space="preserve">12.8351316452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5684385299683</t>
+    <t xml:space="preserve">12.5684375762939</t>
   </si>
   <si>
     <t xml:space="preserve">12.6097564697266</t>
@@ -3014,13 +3014,13 @@
     <t xml:space="preserve">12.3731117248535</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4369707107544</t>
+    <t xml:space="preserve">12.4369697570801</t>
   </si>
   <si>
     <t xml:space="preserve">12.0763683319092</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0575866699219</t>
+    <t xml:space="preserve">12.0575857162476</t>
   </si>
   <si>
     <t xml:space="preserve">12.3693561553955</t>
@@ -3041,25 +3041,25 @@
     <t xml:space="preserve">12.8276214599609</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7938137054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6585884094238</t>
+    <t xml:space="preserve">12.7938146591187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6585893630981</t>
   </si>
   <si>
     <t xml:space="preserve">12.5984888076782</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4557504653931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.515851020813</t>
+    <t xml:space="preserve">12.4557495117188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5158500671387</t>
   </si>
   <si>
     <t xml:space="preserve">12.3468179702759</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2191047668457</t>
+    <t xml:space="preserve">12.21910572052</t>
   </si>
   <si>
     <t xml:space="preserve">12.6661005020142</t>
@@ -3068,13 +3068,13 @@
     <t xml:space="preserve">12.6247825622559</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5083360671997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3881378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1740303039551</t>
+    <t xml:space="preserve">12.5083379745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3881368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1740322113037</t>
   </si>
   <si>
     <t xml:space="preserve">12.0650997161865</t>
@@ -3083,34 +3083,34 @@
     <t xml:space="preserve">12.264181137085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.974949836731</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1552505493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8847980499268</t>
+    <t xml:space="preserve">11.9749488830566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1552495956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8847990036011</t>
   </si>
   <si>
     <t xml:space="preserve">12.0688562393188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1101760864258</t>
+    <t xml:space="preserve">12.1101751327515</t>
   </si>
   <si>
     <t xml:space="preserve">12.2078380584717</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3843812942505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5120944976807</t>
+    <t xml:space="preserve">12.3843822479248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5120935440063</t>
   </si>
   <si>
     <t xml:space="preserve">12.6285371780396</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4257011413574</t>
+    <t xml:space="preserve">12.4257001876831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8547487258911</t>
@@ -3119,13 +3119,13 @@
     <t xml:space="preserve">11.8322114944458</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8096733093262</t>
+    <t xml:space="preserve">11.8096752166748</t>
   </si>
   <si>
     <t xml:space="preserve">11.6181049346924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3326301574707</t>
+    <t xml:space="preserve">11.3326292037964</t>
   </si>
   <si>
     <t xml:space="preserve">11.7645978927612</t>
@@ -3140,16 +3140,16 @@
     <t xml:space="preserve">11.4640989303589</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3626794815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7120113372803</t>
+    <t xml:space="preserve">11.362678527832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.712010383606</t>
   </si>
   <si>
     <t xml:space="preserve">11.8772869110107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8359680175781</t>
+    <t xml:space="preserve">11.8359670639038</t>
   </si>
   <si>
     <t xml:space="preserve">11.9524116516113</t>
@@ -3158,10 +3158,10 @@
     <t xml:space="preserve">12.2003240585327</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2904758453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1139316558838</t>
+    <t xml:space="preserve">12.2904748916626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1139307022095</t>
   </si>
   <si>
     <t xml:space="preserve">12.4031629562378</t>
@@ -3176,7 +3176,7 @@
     <t xml:space="preserve">12.1514921188354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0801258087158</t>
+    <t xml:space="preserve">12.0801248550415</t>
   </si>
   <si>
     <t xml:space="preserve">11.7007427215576</t>
@@ -3185,13 +3185,13 @@
     <t xml:space="preserve">11.5241985321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8255338668823</t>
+    <t xml:space="preserve">10.8255348205566</t>
   </si>
   <si>
     <t xml:space="preserve">10.6452341079712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8893899917603</t>
+    <t xml:space="preserve">10.8893909454346</t>
   </si>
   <si>
     <t xml:space="preserve">11.2499914169312</t>
@@ -3200,13 +3200,13 @@
     <t xml:space="preserve">11.64439868927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8209428787231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0275373458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8885545730591</t>
+    <t xml:space="preserve">11.8209419250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0275363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8885555267334</t>
   </si>
   <si>
     <t xml:space="preserve">12.5834636688232</t>
@@ -3215,19 +3215,19 @@
     <t xml:space="preserve">12.4332122802734</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106760025024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1393880844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2070016860962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5600891113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2370529174805</t>
+    <t xml:space="preserve">12.4106740951538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1393890380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2070007324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5600900650024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2370519638062</t>
   </si>
   <si>
     <t xml:space="preserve">13.2595891952515</t>
@@ -3239,31 +3239,31 @@
     <t xml:space="preserve">13.6727771759033</t>
   </si>
   <si>
-    <t xml:space="preserve">13.357253074646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.379789352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2746133804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5375537872314</t>
+    <t xml:space="preserve">13.3572521209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3797903060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2746143341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5375509262085</t>
   </si>
   <si>
     <t xml:space="preserve">13.1882209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821283340454</t>
+    <t xml:space="preserve">13.2821273803711</t>
   </si>
   <si>
     <t xml:space="preserve">13.2896404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2295389175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619262695312</t>
+    <t xml:space="preserve">13.2295408248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619272232056</t>
   </si>
   <si>
     <t xml:space="preserve">12.9327945709229</t>
@@ -3275,70 +3275,70 @@
     <t xml:space="preserve">13.1919765472412</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1957321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0154323577881</t>
+    <t xml:space="preserve">13.1957340240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0154342651367</t>
   </si>
   <si>
     <t xml:space="preserve">12.82386302948</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3272018432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361343383789</t>
+    <t xml:space="preserve">13.3271999359131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361333847046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4962339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4323749542236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.349739074707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3384704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1994895935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4135961532593</t>
+    <t xml:space="preserve">13.4323768615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3497409820557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3384695053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1994886398315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4135971069336</t>
   </si>
   <si>
     <t xml:space="preserve">13.4248657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3985691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3910608291626</t>
+    <t xml:space="preserve">13.39857006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.391058921814</t>
   </si>
   <si>
     <t xml:space="preserve">13.6802892684937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2099237442017</t>
+    <t xml:space="preserve">14.2099208831787</t>
   </si>
   <si>
     <t xml:space="preserve">13.9582538604736</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8305397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943977355957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8380537033081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9319581985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7328796386719</t>
+    <t xml:space="preserve">13.8305416107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.89439868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8380546569824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.931960105896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7328786849976</t>
   </si>
   <si>
     <t xml:space="preserve">13.4398899078369</t>
@@ -3350,7 +3350,7 @@
     <t xml:space="preserve">13.1093406677246</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3009090423584</t>
+    <t xml:space="preserve">13.3009080886841</t>
   </si>
   <si>
     <t xml:space="preserve">13.04172706604</t>
@@ -3359,139 +3359,139 @@
     <t xml:space="preserve">13.4887208938599</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5676012039185</t>
+    <t xml:space="preserve">13.5676021575928</t>
   </si>
   <si>
     <t xml:space="preserve">13.7216091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3526611328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5855484008789</t>
+    <t xml:space="preserve">14.3526601791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5855503082275</t>
   </si>
   <si>
     <t xml:space="preserve">15.0550804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">15.092643737793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0250301361084</t>
+    <t xml:space="preserve">15.0926418304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0250291824341</t>
   </si>
   <si>
     <t xml:space="preserve">15.1978178024292</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8447294235229</t>
+    <t xml:space="preserve">14.8447303771973</t>
   </si>
   <si>
     <t xml:space="preserve">14.7207727432251</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9198570251465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.822193145752</t>
+    <t xml:space="preserve">14.9198560714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8221912384033</t>
   </si>
   <si>
     <t xml:space="preserve">14.5329608917236</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6005706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315404891968</t>
+    <t xml:space="preserve">14.6005725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4315414428711</t>
   </si>
   <si>
     <t xml:space="preserve">14.2812919616699</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9499034881592</t>
+    <t xml:space="preserve">14.9499053955078</t>
   </si>
   <si>
     <t xml:space="preserve">14.7846298217773</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7095050811768</t>
+    <t xml:space="preserve">14.7095060348511</t>
   </si>
   <si>
     <t xml:space="preserve">14.6644296646118</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4240293502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7620935440063</t>
+    <t xml:space="preserve">14.4240303039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7958993911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7620916366577</t>
   </si>
   <si>
     <t xml:space="preserve">14.9123439788818</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6606740951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4090032577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.194899559021</t>
+    <t xml:space="preserve">14.6606712341309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4090042114258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1948986053467</t>
   </si>
   <si>
     <t xml:space="preserve">14.1197729110718</t>
   </si>
   <si>
-    <t xml:space="preserve">14.202410697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.277533531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3226099014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714408874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2925577163696</t>
+    <t xml:space="preserve">14.2024097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2775344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3226108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202718734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714399337769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2925605773926</t>
   </si>
   <si>
     <t xml:space="preserve">14.4653472900391</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7470655441284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5930614471436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8898048400879</t>
+    <t xml:space="preserve">14.7470664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5930595397949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8898038864136</t>
   </si>
   <si>
     <t xml:space="preserve">14.848484992981</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2504053115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1001558303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1151809692383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.070107460022</t>
+    <t xml:space="preserve">15.2504062652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.100154876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1151819229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0701055526733</t>
   </si>
   <si>
     <t xml:space="preserve">15.1827926635742</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7245292663574</t>
+    <t xml:space="preserve">14.7245283126831</t>
   </si>
   <si>
     <t xml:space="preserve">14.7508239746094</t>
@@ -3500,61 +3500,61 @@
     <t xml:space="preserve">14.814679145813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8184385299683</t>
+    <t xml:space="preserve">14.8184366226196</t>
   </si>
   <si>
     <t xml:space="preserve">14.9837112426758</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0175170898438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.792142868042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9611730575562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1602563858032</t>
+    <t xml:space="preserve">15.0175180435181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7921419143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9611740112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1602554321289</t>
   </si>
   <si>
     <t xml:space="preserve">14.9724426269531</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0851306915283</t>
+    <t xml:space="preserve">15.085129737854</t>
   </si>
   <si>
     <t xml:space="preserve">15.1377191543579</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3555822372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2579164505005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2804565429688</t>
+    <t xml:space="preserve">15.3555812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2579183578491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2804555892944</t>
   </si>
   <si>
     <t xml:space="preserve">15.2729434967041</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7462329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8664321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8438940048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.641056060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.708667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.671106338501</t>
+    <t xml:space="preserve">15.7462310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.86643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8438949584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6410579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7086696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6711072921753</t>
   </si>
   <si>
     <t xml:space="preserve">16.1603355407715</t>
@@ -3563,37 +3563,37 @@
     <t xml:space="preserve">16.0814266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8841562271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8999404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9551734924316</t>
+    <t xml:space="preserve">15.8841552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.899941444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.955174446106</t>
   </si>
   <si>
     <t xml:space="preserve">16.0419731140137</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0025215148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0972099304199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1445541381836</t>
+    <t xml:space="preserve">16.0025196075439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0972080230713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.144552230835</t>
   </si>
   <si>
     <t xml:space="preserve">16.4601860046387</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4522933959961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4128398895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.326042175293</t>
+    <t xml:space="preserve">16.4522953033447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.412841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3260402679443</t>
   </si>
   <si>
     <t xml:space="preserve">16.3497142791748</t>
@@ -3611,10 +3611,10 @@
     <t xml:space="preserve">16.0183010101318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9472846984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8762683868408</t>
+    <t xml:space="preserve">15.9472827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8762674331665</t>
   </si>
   <si>
     <t xml:space="preserve">16.2392444610596</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">16.5312042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1287746429443</t>
+    <t xml:space="preserve">16.1287727355957</t>
   </si>
   <si>
     <t xml:space="preserve">16.2155704498291</t>
@@ -3641,10 +3641,10 @@
     <t xml:space="preserve">16.5075302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4838562011719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4444026947021</t>
+    <t xml:space="preserve">16.4838581085205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4444046020508</t>
   </si>
   <si>
     <t xml:space="preserve">16.2550258636475</t>
@@ -3656,10 +3656,10 @@
     <t xml:space="preserve">16.8073806762695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1624641418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5254402160645</t>
+    <t xml:space="preserve">17.1624660491943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5254421234131</t>
   </si>
   <si>
     <t xml:space="preserve">17.3281726837158</t>
@@ -3668,46 +3668,46 @@
     <t xml:space="preserve">17.1940288543701</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2492637634277</t>
+    <t xml:space="preserve">17.2492656707764</t>
   </si>
   <si>
     <t xml:space="preserve">17.1387939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4702053070068</t>
+    <t xml:space="preserve">17.4702072143555</t>
   </si>
   <si>
     <t xml:space="preserve">17.4938793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2808284759521</t>
+    <t xml:space="preserve">17.2808265686035</t>
   </si>
   <si>
     <t xml:space="preserve">17.4070796966553</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5727863311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9041996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9120922088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1093616485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1172504425049</t>
+    <t xml:space="preserve">17.5727882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9042015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9120903015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1093597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1172523498535</t>
   </si>
   <si>
     <t xml:space="preserve">18.2592868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3224105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2435054779053</t>
+    <t xml:space="preserve">18.3224124908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2435035705566</t>
   </si>
   <si>
     <t xml:space="preserve">18.4644470214844</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">18.2829570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4249935150146</t>
+    <t xml:space="preserve">18.424991607666</t>
   </si>
   <si>
     <t xml:space="preserve">18.3539752960205</t>
@@ -3731,22 +3731,22 @@
     <t xml:space="preserve">18.5906982421875</t>
   </si>
   <si>
-    <t xml:space="preserve">18.669605255127</t>
+    <t xml:space="preserve">18.6696071624756</t>
   </si>
   <si>
     <t xml:space="preserve">18.748514175415</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7642955780029</t>
+    <t xml:space="preserve">18.7642974853516</t>
   </si>
   <si>
     <t xml:space="preserve">18.8037509918213</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7011699676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7564067840576</t>
+    <t xml:space="preserve">18.701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.756404876709</t>
   </si>
   <si>
     <t xml:space="preserve">18.7406234741211</t>
@@ -3755,40 +3755,40 @@
     <t xml:space="preserve">18.6459331512451</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7169513702393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5749168395996</t>
+    <t xml:space="preserve">18.7169494628906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5749187469482</t>
   </si>
   <si>
     <t xml:space="preserve">18.843204498291</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8984413146973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9536743164062</t>
+    <t xml:space="preserve">18.8984394073486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9536762237549</t>
   </si>
   <si>
     <t xml:space="preserve">19.1903991699219</t>
   </si>
   <si>
-    <t xml:space="preserve">19.087818145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5591354370117</t>
+    <t xml:space="preserve">19.0878200531006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5591373443604</t>
   </si>
   <si>
     <t xml:space="preserve">18.8589859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.937894821167</t>
+    <t xml:space="preserve">18.9378929138184</t>
   </si>
   <si>
     <t xml:space="preserve">19.2614154815674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1430530548096</t>
+    <t xml:space="preserve">19.1430549621582</t>
   </si>
   <si>
     <t xml:space="preserve">18.7327327728271</t>
@@ -3797,10 +3797,10 @@
     <t xml:space="preserve">18.5985889434814</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7721881866455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6538257598877</t>
+    <t xml:space="preserve">18.7721862792969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6538238525391</t>
   </si>
   <si>
     <t xml:space="preserve">18.4013195037842</t>
@@ -3809,37 +3809,37 @@
     <t xml:space="preserve">18.6222629547119</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2356147766113</t>
+    <t xml:space="preserve">18.2356128692627</t>
   </si>
   <si>
     <t xml:space="preserve">18.1409225463867</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4328842163086</t>
+    <t xml:space="preserve">18.43288230896</t>
   </si>
   <si>
     <t xml:space="preserve">18.6380443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8353157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7090606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5375938415527</t>
+    <t xml:space="preserve">18.8353118896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7090587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5375919342041</t>
   </si>
   <si>
     <t xml:space="preserve">19.403450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5297012329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6007194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8374423980713</t>
+    <t xml:space="preserve">19.5297031402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6007175445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8374443054199</t>
   </si>
   <si>
     <t xml:space="preserve">19.6322803497314</t>
@@ -3851,16 +3851,16 @@
     <t xml:space="preserve">19.640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9952602386475</t>
+    <t xml:space="preserve">19.9952583312988</t>
   </si>
   <si>
     <t xml:space="preserve">20.066276550293</t>
   </si>
   <si>
-    <t xml:space="preserve">20.1057281494141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0504932403564</t>
+    <t xml:space="preserve">20.1057300567627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0504951477051</t>
   </si>
   <si>
     <t xml:space="preserve">20.0741672515869</t>
@@ -3878,10 +3878,10 @@
     <t xml:space="preserve">21.1788787841797</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1946601867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9421558380127</t>
+    <t xml:space="preserve">21.1946582794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9421539306641</t>
   </si>
   <si>
     <t xml:space="preserve">20.9816074371338</t>
@@ -3899,7 +3899,7 @@
     <t xml:space="preserve">20.0820579528809</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1035976409912</t>
+    <t xml:space="preserve">19.1035995483398</t>
   </si>
   <si>
     <t xml:space="preserve">19.316650390625</t>
@@ -3908,19 +3908,19 @@
     <t xml:space="preserve">19.3324337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4744663238525</t>
+    <t xml:space="preserve">19.4744682312012</t>
   </si>
   <si>
     <t xml:space="preserve">19.3087596893311</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1746196746826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2377433776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2850875854492</t>
+    <t xml:space="preserve">19.1746158599854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2377414703369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2850894927979</t>
   </si>
   <si>
     <t xml:space="preserve">19.1272716522217</t>
@@ -3929,43 +3929,43 @@
     <t xml:space="preserve">19.024694442749</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8116416931152</t>
+    <t xml:space="preserve">18.8116397857666</t>
   </si>
   <si>
     <t xml:space="preserve">19.0168018341064</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7248401641846</t>
+    <t xml:space="preserve">18.7248420715332</t>
   </si>
   <si>
     <t xml:space="preserve">18.9142208099365</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1667251586914</t>
+    <t xml:space="preserve">19.16672706604</t>
   </si>
   <si>
     <t xml:space="preserve">19.3561058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4113426208496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.7269706726074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9005699157715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9479141235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3403224945068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5770473480225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6165027618408</t>
+    <t xml:space="preserve">19.411340713501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.7269725799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9005680084229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9479160308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3403244018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5770454406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6165008544922</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268211364746</t>
@@ -3980,16 +3980,16 @@
     <t xml:space="preserve">20.5791778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6817569732666</t>
+    <t xml:space="preserve">20.6817588806152</t>
   </si>
   <si>
     <t xml:space="preserve">20.3187828063965</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8847904205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2119388580322</t>
+    <t xml:space="preserve">19.884786605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2119407653809</t>
   </si>
   <si>
     <t xml:space="preserve">18.2671756744385</t>
@@ -4001,22 +4001,22 @@
     <t xml:space="preserve">19.0325832366943</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8747673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.33030128479</t>
+    <t xml:space="preserve">18.8747653961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3303031921387</t>
   </si>
   <si>
     <t xml:space="preserve">18.7958583831787</t>
   </si>
   <si>
-    <t xml:space="preserve">18.369758605957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3145217895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8095092773438</t>
+    <t xml:space="preserve">18.3697566986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3145198822021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8095111846924</t>
   </si>
   <si>
     <t xml:space="preserve">17.7463836669922</t>
@@ -4034,40 +4034,40 @@
     <t xml:space="preserve">16.8862895965576</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6337814331055</t>
+    <t xml:space="preserve">16.6337833404541</t>
   </si>
   <si>
     <t xml:space="preserve">15.4028205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4501647949219</t>
+    <t xml:space="preserve">15.4501638412476</t>
   </si>
   <si>
     <t xml:space="preserve">15.663215637207</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0756683349609</t>
+    <t xml:space="preserve">17.0756664276123</t>
   </si>
   <si>
     <t xml:space="preserve">15.1897687911987</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5093450546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8525943756104</t>
+    <t xml:space="preserve">15.5093460083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.852593421936</t>
   </si>
   <si>
     <t xml:space="preserve">17.0441055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.791597366333</t>
+    <t xml:space="preserve">16.7915992736816</t>
   </si>
   <si>
     <t xml:space="preserve">16.4759674072266</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8152694702148</t>
+    <t xml:space="preserve">16.8152713775635</t>
   </si>
   <si>
     <t xml:space="preserve">16.7837085723877</t>
@@ -4079,79 +4079,79 @@
     <t xml:space="preserve">16.7442531585693</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2413730621338</t>
+    <t xml:space="preserve">17.2413749694824</t>
   </si>
   <si>
     <t xml:space="preserve">16.9415225982666</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6732387542725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7600345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.318151473999</t>
+    <t xml:space="preserve">16.6732349395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7600364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3181533813477</t>
   </si>
   <si>
     <t xml:space="preserve">15.7579050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4107112884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815790176392</t>
+    <t xml:space="preserve">15.4107103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815780639648</t>
   </si>
   <si>
     <t xml:space="preserve">15.9157209396362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8920478820801</t>
+    <t xml:space="preserve">15.8920497894287</t>
   </si>
   <si>
     <t xml:space="preserve">15.8683776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.62770652771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7973594665527</t>
+    <t xml:space="preserve">15.6277074813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7973604202271</t>
   </si>
   <si>
     <t xml:space="preserve">15.7539596557617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8289213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0893173217773</t>
+    <t xml:space="preserve">15.8289222717285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.089319229126</t>
   </si>
   <si>
     <t xml:space="preserve">16.0735378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.176118850708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9236125946045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6395435333252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5132904052734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1660976409912</t>
+    <t xml:space="preserve">16.1761169433594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9236106872559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6395444869995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5132913589478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964437484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1660957336426</t>
   </si>
   <si>
     <t xml:space="preserve">15.6868877410889</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7381792068481</t>
+    <t xml:space="preserve">15.7381782531738</t>
   </si>
   <si>
     <t xml:space="preserve">15.765796661377</t>
@@ -4160,10 +4160,10 @@
     <t xml:space="preserve">16.0261917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">15.805251121521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4583644866943</t>
+    <t xml:space="preserve">15.8052520751953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4583625793457</t>
   </si>
   <si>
     <t xml:space="preserve">16.0873756408691</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">16.7703304290771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305286407471</t>
+    <t xml:space="preserve">16.9305305480957</t>
   </si>
   <si>
     <t xml:space="preserve">16.8209209442139</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">16.7366046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5342483520508</t>
+    <t xml:space="preserve">16.5342464447021</t>
   </si>
   <si>
     <t xml:space="preserve">16.2012023925781</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">14.7298984527588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4390106201172</t>
+    <t xml:space="preserve">14.4390096664429</t>
   </si>
   <si>
     <t xml:space="preserve">14.6287202835083</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">14.506462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2197895050049</t>
+    <t xml:space="preserve">14.2197904586792</t>
   </si>
   <si>
     <t xml:space="preserve">14.6750926971436</t>
@@ -4250,13 +4250,13 @@
     <t xml:space="preserve">13.8277225494385</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289026260376</t>
+    <t xml:space="preserve">13.9289016723633</t>
   </si>
   <si>
     <t xml:space="preserve">13.3724203109741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7771348953247</t>
+    <t xml:space="preserve">13.7771339416504</t>
   </si>
   <si>
     <t xml:space="preserve">14.1523370742798</t>
@@ -4265,19 +4265,19 @@
     <t xml:space="preserve">14.3420476913452</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1354742050171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3546934127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1987113952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6211519241333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6801729202271</t>
+    <t xml:space="preserve">14.1354732513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3546943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.198712348938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.621150970459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6801719665527</t>
   </si>
   <si>
     <t xml:space="preserve">13.8108596801758</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">13.6928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7602710723877</t>
+    <t xml:space="preserve">13.760272026062</t>
   </si>
   <si>
     <t xml:space="preserve">13.7939977645874</t>
@@ -4298,13 +4298,13 @@
     <t xml:space="preserve">13.4609518051147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5494832992554</t>
+    <t xml:space="preserve">13.5494823455811</t>
   </si>
   <si>
     <t xml:space="preserve">14.3631258010864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3926362991333</t>
+    <t xml:space="preserve">14.3926372528076</t>
   </si>
   <si>
     <t xml:space="preserve">14.1312589645386</t>
@@ -4313,22 +4313,22 @@
     <t xml:space="preserve">14.4727363586426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5739154815674</t>
+    <t xml:space="preserve">14.5739145278931</t>
   </si>
   <si>
     <t xml:space="preserve">14.2577314376831</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2956733703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1944952011108</t>
+    <t xml:space="preserve">14.2956743240356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1944942474365</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600877761841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5022468566895</t>
+    <t xml:space="preserve">14.5022459030151</t>
   </si>
   <si>
     <t xml:space="preserve">14.565484046936</t>
@@ -4346,13 +4346,13 @@
     <t xml:space="preserve">13.9794912338257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.768702507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9541959762573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9415493011475</t>
+    <t xml:space="preserve">13.7687034606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9541969299316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9415483474731</t>
   </si>
   <si>
     <t xml:space="preserve">13.8530187606812</t>
@@ -4370,13 +4370,13 @@
     <t xml:space="preserve">13.4356575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1447696685791</t>
+    <t xml:space="preserve">13.1447687149048</t>
   </si>
   <si>
     <t xml:space="preserve">13.6295833587646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4272260665894</t>
+    <t xml:space="preserve">13.427225112915</t>
   </si>
   <si>
     <t xml:space="preserve">13.4946775436401</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">13.5199718475342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1692008972168</t>
+    <t xml:space="preserve">14.1692018508911</t>
   </si>
   <si>
     <t xml:space="preserve">14.0806703567505</t>
@@ -4394,16 +4394,16 @@
     <t xml:space="preserve">14.0722389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9162530899048</t>
+    <t xml:space="preserve">13.9162540435791</t>
   </si>
   <si>
     <t xml:space="preserve">13.7644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8572330474854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4735984802246</t>
+    <t xml:space="preserve">13.8572340011597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4735994338989</t>
   </si>
   <si>
     <t xml:space="preserve">13.1321220397949</t>
@@ -4415,10 +4415,10 @@
     <t xml:space="preserve">12.7527027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5334815979004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4112253189087</t>
+    <t xml:space="preserve">12.5334825515747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.411226272583</t>
   </si>
   <si>
     <t xml:space="preserve">12.0065116882324</t>
@@ -4433,22 +4433,22 @@
     <t xml:space="preserve">13.1532011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9044694900513</t>
+    <t xml:space="preserve">12.9044704437256</t>
   </si>
   <si>
     <t xml:space="preserve">12.7231922149658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5039710998535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5503463745117</t>
+    <t xml:space="preserve">12.5039720535278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5503454208374</t>
   </si>
   <si>
     <t xml:space="preserve">12.4280881881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7324867248535</t>
+    <t xml:space="preserve">11.7324857711792</t>
   </si>
   <si>
     <t xml:space="preserve">12.0908260345459</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">12.5292663574219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7948608398438</t>
+    <t xml:space="preserve">12.7948598861694</t>
   </si>
   <si>
     <t xml:space="preserve">12.8791751861572</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">12.8960380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3007526397705</t>
+    <t xml:space="preserve">13.3007516860962</t>
   </si>
   <si>
     <t xml:space="preserve">13.6843872070312</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">13.532618522644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7897806167603</t>
+    <t xml:space="preserve">13.7897815704346</t>
   </si>
   <si>
     <t xml:space="preserve">13.743408203125</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">13.9963550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.110179901123</t>
+    <t xml:space="preserve">14.1101808547974</t>
   </si>
   <si>
     <t xml:space="preserve">14.3462619781494</t>
@@ -4523,10 +4523,10 @@
     <t xml:space="preserve">16.799840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3740482330322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.441499710083</t>
+    <t xml:space="preserve">16.3740463256836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4415016174316</t>
   </si>
   <si>
     <t xml:space="preserve">16.4035587310791</t>
@@ -4541,10 +4541,10 @@
     <t xml:space="preserve">16.2349281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3993453979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3023796081543</t>
+    <t xml:space="preserve">16.3993434906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3023777008057</t>
   </si>
   <si>
     <t xml:space="preserve">16.6059150695801</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">17.0570030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9558238983154</t>
+    <t xml:space="preserve">16.9558258056641</t>
   </si>
   <si>
     <t xml:space="preserve">16.2855167388916</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">17.2677917480469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2593593597412</t>
+    <t xml:space="preserve">17.2593612670898</t>
   </si>
   <si>
     <t xml:space="preserve">17.2340660095215</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">17.4617156982422</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6893672943115</t>
+    <t xml:space="preserve">17.6893692016602</t>
   </si>
   <si>
     <t xml:space="preserve">17.7146625518799</t>
@@ -4601,7 +4601,7 @@
     <t xml:space="preserve">17.8579998016357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6472110748291</t>
+    <t xml:space="preserve">17.6472129821777</t>
   </si>
   <si>
     <t xml:space="preserve">17.8664302825928</t>
@@ -4619,7 +4619,7 @@
     <t xml:space="preserve">17.9676074981689</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3807544708252</t>
+    <t xml:space="preserve">18.3807525634766</t>
   </si>
   <si>
     <t xml:space="preserve">18.3891849517822</t>
@@ -4637,10 +4637,10 @@
     <t xml:space="preserve">19.1901817321777</t>
   </si>
   <si>
-    <t xml:space="preserve">19.131160736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.164888381958</t>
+    <t xml:space="preserve">19.1311626434326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1648864746094</t>
   </si>
   <si>
     <t xml:space="preserve">18.8444881439209</t>
@@ -4664,16 +4664,16 @@
     <t xml:space="preserve">19.4431266784668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3250865936279</t>
+    <t xml:space="preserve">19.3250885009766</t>
   </si>
   <si>
     <t xml:space="preserve">19.2913608551025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3166561126709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.814115524292</t>
+    <t xml:space="preserve">19.3166542053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8141174316406</t>
   </si>
   <si>
     <t xml:space="preserve">19.8984336853027</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">19.8309783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1564559936523</t>
+    <t xml:space="preserve">19.1564540863037</t>
   </si>
   <si>
     <t xml:space="preserve">19.5358753204346</t>
@@ -4703,7 +4703,7 @@
     <t xml:space="preserve">19.0890026092529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2070446014404</t>
+    <t xml:space="preserve">19.2070465087891</t>
   </si>
   <si>
     <t xml:space="preserve">19.0552787780762</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">18.9456672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9793930053711</t>
+    <t xml:space="preserve">18.9793949127197</t>
   </si>
   <si>
     <t xml:space="preserve">19.1058673858643</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">18.1952590942383</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6134834289551</t>
+    <t xml:space="preserve">17.6134853363037</t>
   </si>
   <si>
     <t xml:space="preserve">16.7745456695557</t>
@@ -4748,16 +4748,16 @@
     <t xml:space="preserve">16.0114936828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4667949676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9052352905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782653808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1126708984375</t>
+    <t xml:space="preserve">16.466796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9052333831787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782634735107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1126689910889</t>
   </si>
   <si>
     <t xml:space="preserve">16.1337490081787</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">16.3487529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6438579559326</t>
+    <t xml:space="preserve">16.643856048584</t>
   </si>
   <si>
     <t xml:space="preserve">16.6101322174072</t>
@@ -4790,16 +4790,16 @@
     <t xml:space="preserve">17.124454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0232791900635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2003383636475</t>
+    <t xml:space="preserve">17.0232772827148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2003402709961</t>
   </si>
   <si>
     <t xml:space="preserve">17.2424983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1075916290283</t>
+    <t xml:space="preserve">17.107593536377</t>
   </si>
   <si>
     <t xml:space="preserve">17.0148468017578</t>
@@ -4811,31 +4811,31 @@
     <t xml:space="preserve">17.0654335021973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8124885559082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5806198120117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9726848602295</t>
+    <t xml:space="preserve">16.8124904632568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5806217193604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9726867675781</t>
   </si>
   <si>
     <t xml:space="preserve">17.0822982788086</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8546447753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9895515441895</t>
+    <t xml:space="preserve">16.8546466827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9895496368408</t>
   </si>
   <si>
     <t xml:space="preserve">17.0738658905029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8504295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2509288787842</t>
+    <t xml:space="preserve">16.8504314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2509269714355</t>
   </si>
   <si>
     <t xml:space="preserve">17.4084911346436</t>
@@ -6387,6 +6387,9 @@
   </si>
   <si>
     <t xml:space="preserve">34.4000015258789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">34.2299995422363</t>
   </si>
 </sst>
 </file>
@@ -71673,7 +71676,7 @@
     </row>
     <row r="2499">
       <c r="A2499" s="1" t="n">
-        <v>45958.6941898148</v>
+        <v>45958.3333333333</v>
       </c>
       <c r="B2499" t="n">
         <v>2400779</v>
@@ -71694,6 +71697,32 @@
         <v>2124</v>
       </c>
       <c r="H2499" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2500">
+      <c r="A2500" s="1" t="n">
+        <v>45959.6910185185</v>
+      </c>
+      <c r="B2500" t="n">
+        <v>674625</v>
+      </c>
+      <c r="C2500" t="n">
+        <v>34.3699989318848</v>
+      </c>
+      <c r="D2500" t="n">
+        <v>33.9199981689453</v>
+      </c>
+      <c r="E2500" t="n">
+        <v>34.2599983215332</v>
+      </c>
+      <c r="F2500" t="n">
+        <v>34.2299995422363</v>
+      </c>
+      <c r="G2500" t="s">
+        <v>2125</v>
+      </c>
+      <c r="H2500" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2130" uniqueCount="2130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2131" uniqueCount="2131">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,61 +38,61 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8295059204102</t>
+    <t xml:space="preserve">10.8295068740845</t>
   </si>
   <si>
     <t xml:space="preserve">AZM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068357467651</t>
+    <t xml:space="preserve">10.7068347930908</t>
   </si>
   <si>
     <t xml:space="preserve">10.4860258102417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1916122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91191959381104</t>
+    <t xml:space="preserve">10.1916131973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91191864013672</t>
   </si>
   <si>
     <t xml:space="preserve">9.9364538192749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.225959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.000244140625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.617506980896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33290767669678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1513500213623</t>
+    <t xml:space="preserve">10.2259607315063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0002431869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61750602722168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33290481567383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15135097503662</t>
   </si>
   <si>
     <t xml:space="preserve">9.37706851959229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85693836212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25930213928223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53899574279785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48992824554443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50955295562744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40160083770752</t>
+    <t xml:space="preserve">8.85693740844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25930118560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53899669647217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48992729187012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50955581665039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40160369873047</t>
   </si>
   <si>
     <t xml:space="preserve">9.12681770324707</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">9.49483394622803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43595123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84712409973145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99433040618896</t>
+    <t xml:space="preserve">9.43595027923584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84712505340576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99433135986328</t>
   </si>
   <si>
     <t xml:space="preserve">8.79805469512939</t>
@@ -116,22 +116,22 @@
     <t xml:space="preserve">8.05711460113525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86574554443359</t>
+    <t xml:space="preserve">7.86574649810791</t>
   </si>
   <si>
     <t xml:space="preserve">8.32699394226074</t>
   </si>
   <si>
-    <t xml:space="preserve">7.61058712005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.679283618927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10127639770508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87065124511719</t>
+    <t xml:space="preserve">7.61058759689331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67928552627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10127735137939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87065172195435</t>
   </si>
   <si>
     <t xml:space="preserve">8.53799152374268</t>
@@ -146,10 +146,10 @@
     <t xml:space="preserve">8.61649990081787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50364112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21413516998291</t>
+    <t xml:space="preserve">8.50364208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21413421630859</t>
   </si>
   <si>
     <t xml:space="preserve">8.69010353088379</t>
@@ -161,67 +161,67 @@
     <t xml:space="preserve">9.29365158081055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.30837059020996</t>
+    <t xml:space="preserve">9.30837154388428</t>
   </si>
   <si>
     <t xml:space="preserve">9.47520637512207</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09737491607666</t>
+    <t xml:space="preserve">9.09737586975098</t>
   </si>
   <si>
     <t xml:space="preserve">9.22004795074463</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41141605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4801139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77943229675293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6616678237915</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79415416717529</t>
+    <t xml:space="preserve">9.41141700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48011302947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77943420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66166687011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79415321350098</t>
   </si>
   <si>
     <t xml:space="preserve">9.77452564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68620204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64694690704346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72545719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2357740402222</t>
+    <t xml:space="preserve">9.68620014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64694786071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7254581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2357730865479</t>
   </si>
   <si>
     <t xml:space="preserve">10.3044710159302</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8383150100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56843566894531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98552322387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93154525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74508666992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3780746459961</t>
+    <t xml:space="preserve">9.83831596374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56843662261963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98552227020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93154621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74508476257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3780736923218</t>
   </si>
   <si>
     <t xml:space="preserve">10.5449085235596</t>
@@ -230,43 +230,43 @@
     <t xml:space="preserve">10.436957359314</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5547208786011</t>
+    <t xml:space="preserve">10.5547227859497</t>
   </si>
   <si>
     <t xml:space="preserve">10.5056533813477</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5498161315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5007467269897</t>
+    <t xml:space="preserve">10.5498151779175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5007448196411</t>
   </si>
   <si>
     <t xml:space="preserve">10.5694427490234</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4173278808594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4811182022095</t>
+    <t xml:space="preserve">10.4173288345337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4811191558838</t>
   </si>
   <si>
     <t xml:space="preserve">10.7411842346191</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8442287445068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7853441238403</t>
+    <t xml:space="preserve">10.8442277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.785346031189</t>
   </si>
   <si>
     <t xml:space="preserve">10.5988836288452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2406806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2897510528564</t>
+    <t xml:space="preserve">10.2406816482544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2897500991821</t>
   </si>
   <si>
     <t xml:space="preserve">9.73036575317383</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">9.57334327697754</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43104457855225</t>
+    <t xml:space="preserve">9.43104362487793</t>
   </si>
   <si>
     <t xml:space="preserve">9.40650939941406</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">9.35253238677979</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47029972076416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.27892971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30346298217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14644432067871</t>
+    <t xml:space="preserve">9.47029876708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2789306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30346488952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14644622802734</t>
   </si>
   <si>
     <t xml:space="preserve">9.52970123291016</t>
@@ -308,31 +308,31 @@
     <t xml:space="preserve">9.79665470123291</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1190137863159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89235401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95279407501221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492347717285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84702396392822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76643371582031</t>
+    <t xml:space="preserve">10.1190128326416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89235496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95279598236084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492328643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84702301025391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76643466949463</t>
   </si>
   <si>
     <t xml:space="preserve">9.42896461486816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42392730712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5246639251709</t>
+    <t xml:space="preserve">9.42392826080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52466487884521</t>
   </si>
   <si>
     <t xml:space="preserve">9.54984855651855</t>
@@ -341,79 +341,79 @@
     <t xml:space="preserve">9.39370632171631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82958030700684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48203945159912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28560161590576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46189117431641</t>
+    <t xml:space="preserve">8.82958126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4820384979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28560256958008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46189212799072</t>
   </si>
   <si>
     <t xml:space="preserve">8.53744411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68351364135742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39874362945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50451755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81680107116699</t>
+    <t xml:space="preserve">8.68351268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39874458312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5045166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81680011749268</t>
   </si>
   <si>
     <t xml:space="preserve">8.46692943572998</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46459770202637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57540845870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49985551834106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34875059127808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43941354751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20268297195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87025117874146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50255966186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62848234176636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8601770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02135467529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38904571533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20771789550781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44948768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66607046127319</t>
+    <t xml:space="preserve">7.46459674835205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540798187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49985504150391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34875011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43941211700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20268106460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87025022506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50256109237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6284818649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86017560958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02135515213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38904476165771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20771932601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44948673248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66607093811035</t>
   </si>
   <si>
     <t xml:space="preserve">7.52503967285156</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">7.64592409133911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79702758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71140336990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94309568405151</t>
+    <t xml:space="preserve">7.79702854156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71140146255493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94309663772583</t>
   </si>
   <si>
     <t xml:space="preserve">7.81717586517334</t>
@@ -437,160 +437,160 @@
     <t xml:space="preserve">7.94813346862793</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08179664611816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92565536499023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71410894393921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.78966045379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.90047121047974</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22786521911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27823352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32860279083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31852865219116</t>
+    <t xml:space="preserve">7.08179807662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92565631866455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71410799026489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7896614074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.90047073364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22786569595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27823495864868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32860136032104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31852912902832</t>
   </si>
   <si>
     <t xml:space="preserve">7.3991174697876</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15734958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94580221176147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19764518737793</t>
+    <t xml:space="preserve">7.15735006332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94580364227295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19764471054077</t>
   </si>
   <si>
     <t xml:space="preserve">6.80477094650269</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02639150619507</t>
+    <t xml:space="preserve">7.02639293670654</t>
   </si>
   <si>
     <t xml:space="preserve">7.08683395385742</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04150247573853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85010290145874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86521339416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22282838821411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31349229812622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23290252685547</t>
+    <t xml:space="preserve">7.04150390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85010385513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8652138710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069124221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22282934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31349277496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23290205001831</t>
   </si>
   <si>
     <t xml:space="preserve">7.29838085174561</t>
   </si>
   <si>
-    <t xml:space="preserve">6.98106098175049</t>
+    <t xml:space="preserve">6.98106050491333</t>
   </si>
   <si>
     <t xml:space="preserve">7.01128149032593</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53781843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79973411560059</t>
+    <t xml:space="preserve">6.53781890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79973459243774</t>
   </si>
   <si>
     <t xml:space="preserve">6.68388748168945</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73929214477539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94076490402222</t>
+    <t xml:space="preserve">6.73929262161255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94076585769653</t>
   </si>
   <si>
     <t xml:space="preserve">6.90550804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66877746582031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46226596832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57307815551758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67381286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.5982608795166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87528705596924</t>
+    <t xml:space="preserve">6.66877603530884</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.46226644515991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57307624816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67381381988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59826040267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8752875328064</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624465942383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15231227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30341911315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62577676773071</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66103363037109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5703706741333</t>
+    <t xml:space="preserve">7.15231323242188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.30341863632202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62577724456787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66103219985962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57037210464478</t>
   </si>
   <si>
     <t xml:space="preserve">7.45452356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.5351128578186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44444990158081</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59555387496948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72147560119629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.605628490448</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70636606216431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48474407196045</t>
+    <t xml:space="preserve">7.53511238098145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44444942474365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59555578231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72147703170776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60562896728516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70636653900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48474502563477</t>
   </si>
   <si>
     <t xml:space="preserve">7.36386013031006</t>
@@ -599,28 +599,28 @@
     <t xml:space="preserve">7.26312351226807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13216495513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17246055603027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69629144668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91791343688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35611820220947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.38633823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51729583740234</t>
+    <t xml:space="preserve">7.13216543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617195129395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17246007919312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69629287719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91791391372681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35611724853516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.38634014129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51729679107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.45181751251221</t>
@@ -629,64 +629,64 @@
     <t xml:space="preserve">8.20501327514648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04887104034424</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.95820760726929</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93132257461548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71623659133911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73236751556396</t>
+    <t xml:space="preserve">8.04887008666992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9582085609436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93132209777832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71623468399048</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73236703872681</t>
   </si>
   <si>
     <t xml:space="preserve">7.63557815551758</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64095401763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45813083648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44199991226196</t>
+    <t xml:space="preserve">7.64095497131348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45813131332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44200038909912</t>
   </si>
   <si>
     <t xml:space="preserve">7.57105207443237</t>
   </si>
   <si>
-    <t xml:space="preserve">7.68935012817383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62482404708862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79689359664917</t>
+    <t xml:space="preserve">7.68934965133667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62482213973999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.7968921661377</t>
   </si>
   <si>
     <t xml:space="preserve">8.20018005371094</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43139934539795</t>
+    <t xml:space="preserve">8.43139839172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.61960029602051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54431915283203</t>
+    <t xml:space="preserve">8.54432010650635</t>
   </si>
   <si>
     <t xml:space="preserve">8.46903896331787</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5873384475708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70025634765625</t>
+    <t xml:space="preserve">8.58733654022217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70025730133057</t>
   </si>
   <si>
     <t xml:space="preserve">8.54969596862793</t>
@@ -695,76 +695,76 @@
     <t xml:space="preserve">8.6034688949585</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53356456756592</t>
+    <t xml:space="preserve">8.53356552124023</t>
   </si>
   <si>
     <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51743316650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5281867980957</t>
+    <t xml:space="preserve">8.51743412017822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52818775177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.67874908447266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11429786682129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15731525421143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2003345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17882442474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05514907836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3347635269165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13043212890625</t>
+    <t xml:space="preserve">9.11429882049561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15731620788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20033359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17882537841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05515003204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33476448059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13043117523193</t>
   </si>
   <si>
     <t xml:space="preserve">9.44768333435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38315773010254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41004276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45843887329102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45306205749512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.37240219116211</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2379732131958</t>
+    <t xml:space="preserve">9.38315868377686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41004371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45843696594238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45306015014648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.37240314483643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23797416687012</t>
   </si>
   <si>
     <t xml:space="preserve">9.32938575744629</t>
   </si>
   <si>
-    <t xml:space="preserve">9.46919250488281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44230556488037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92609882354736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0927906036377</t>
+    <t xml:space="preserve">9.46919345855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44230461120605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92609786987305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09278964996338</t>
   </si>
   <si>
     <t xml:space="preserve">9.07128238677979</t>
@@ -776,28 +776,28 @@
     <t xml:space="preserve">9.16807079315186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25948047637939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28636932373047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24335098266602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26485919952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23259735107422</t>
+    <t xml:space="preserve">9.25948143005371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28636837005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24335193634033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26486015319824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2325963973999</t>
   </si>
   <si>
     <t xml:space="preserve">9.24872875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96373844146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49592399597168</t>
+    <t xml:space="preserve">8.9637393951416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49592590332031</t>
   </si>
   <si>
     <t xml:space="preserve">8.59271430969238</t>
@@ -806,19 +806,19 @@
     <t xml:space="preserve">8.52281093597412</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66799449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73789596557617</t>
+    <t xml:space="preserve">8.66799354553223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7378978729248</t>
   </si>
   <si>
     <t xml:space="preserve">8.71101188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70563507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6357307434082</t>
+    <t xml:space="preserve">8.70563316345215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.63573169708252</t>
   </si>
   <si>
     <t xml:space="preserve">8.53894233703613</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">8.33460998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43677616119385</t>
+    <t xml:space="preserve">8.43677520751953</t>
   </si>
   <si>
     <t xml:space="preserve">8.47441577911377</t>
@@ -845,22 +845,22 @@
     <t xml:space="preserve">8.56582832336426</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47979164123535</t>
+    <t xml:space="preserve">8.47979354858398</t>
   </si>
   <si>
     <t xml:space="preserve">8.66261768341064</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61422252655029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78091526031494</t>
+    <t xml:space="preserve">8.61422157287598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78091430664062</t>
   </si>
   <si>
     <t xml:space="preserve">8.77016067504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79166889190674</t>
+    <t xml:space="preserve">8.79166984558105</t>
   </si>
   <si>
     <t xml:space="preserve">9.18420219421387</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">9.04977321624756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14118480682373</t>
+    <t xml:space="preserve">9.14118385314941</t>
   </si>
   <si>
     <t xml:space="preserve">9.16269397735596</t>
@@ -887,28 +887,28 @@
     <t xml:space="preserve">9.20571041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62513160705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63050746917725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.60899829864502</t>
+    <t xml:space="preserve">9.62513065338135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63050651550293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.60899925231934</t>
   </si>
   <si>
     <t xml:space="preserve">9.63588619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71654224395752</t>
+    <t xml:space="preserve">9.71654319763184</t>
   </si>
   <si>
     <t xml:space="preserve">9.97464656829834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0553045272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.243504524231</t>
+    <t xml:space="preserve">10.0553035736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2435026168823</t>
   </si>
   <si>
     <t xml:space="preserve">10.4155740737915</t>
@@ -917,22 +917,22 @@
     <t xml:space="preserve">10.3456707000732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2327508926392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3994426727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4101963043213</t>
+    <t xml:space="preserve">10.2327499389648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3994417190552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4101972579956</t>
   </si>
   <si>
     <t xml:space="preserve">10.3349151611328</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1305837631226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036987304688</t>
+    <t xml:space="preserve">10.1305828094482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036977767944</t>
   </si>
   <si>
     <t xml:space="preserve">10.3295392990112</t>
@@ -941,22 +941,22 @@
     <t xml:space="preserve">10.425971031189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5507659912109</t>
+    <t xml:space="preserve">10.5507650375366</t>
   </si>
   <si>
     <t xml:space="preserve">10.6074905395508</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5847988128662</t>
+    <t xml:space="preserve">10.5847997665405</t>
   </si>
   <si>
     <t xml:space="preserve">10.4770221710205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2387800216675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2728157043457</t>
+    <t xml:space="preserve">10.2387809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2728147506714</t>
   </si>
   <si>
     <t xml:space="preserve">10.3408842086792</t>
@@ -965,61 +965,61 @@
     <t xml:space="preserve">10.2160902023315</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0856237411499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9041051864624</t>
+    <t xml:space="preserve">10.0856227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90410614013672</t>
   </si>
   <si>
     <t xml:space="preserve">10.2898321151733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2614698410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083116531372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0062103271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94381332397461</t>
+    <t xml:space="preserve">10.2614707946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083135604858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0062084197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94381141662598</t>
   </si>
   <si>
     <t xml:space="preserve">10.1707105636597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1366767883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.062933921814</t>
+    <t xml:space="preserve">10.1366758346558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0629348754883</t>
   </si>
   <si>
     <t xml:space="preserve">10.1990728378296</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3522281646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104177474976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1933994293213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95515727996826</t>
+    <t xml:space="preserve">10.3522272109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1934013366699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95515823364258</t>
   </si>
   <si>
     <t xml:space="preserve">10.1480207443237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2444524765015</t>
+    <t xml:space="preserve">10.2444515228271</t>
   </si>
   <si>
     <t xml:space="preserve">10.2841596603394</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2217636108398</t>
+    <t xml:space="preserve">10.2217626571655</t>
   </si>
   <si>
     <t xml:space="preserve">10.0912971496582</t>
@@ -1028,25 +1028,25 @@
     <t xml:space="preserve">10.1593656539917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5450925827026</t>
+    <t xml:space="preserve">10.5450944900513</t>
   </si>
   <si>
     <t xml:space="preserve">10.408953666687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3181953430176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2955055236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3692464828491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4316425323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.397608757019</t>
+    <t xml:space="preserve">10.3181943893433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2955045700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3692474365234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4316444396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3976097106934</t>
   </si>
   <si>
     <t xml:space="preserve">10.7152662277222</t>
@@ -1058,46 +1058,46 @@
     <t xml:space="preserve">10.7436285018921</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7209377288818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6698875427246</t>
+    <t xml:space="preserve">10.7209386825562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.669885635376</t>
   </si>
   <si>
     <t xml:space="preserve">10.7776622772217</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7039213180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6585426330566</t>
+    <t xml:space="preserve">10.7039203643799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6585416793823</t>
   </si>
   <si>
     <t xml:space="preserve">10.5394201278687</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3068513870239</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5564365386963</t>
+    <t xml:space="preserve">10.3068504333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095947265625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5564374923706</t>
   </si>
   <si>
     <t xml:space="preserve">10.4826955795288</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3352108001709</t>
+    <t xml:space="preserve">10.3352117538452</t>
   </si>
   <si>
     <t xml:space="preserve">10.2331085205078</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2784872055054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0288991928101</t>
+    <t xml:space="preserve">10.2784862518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0288982391357</t>
   </si>
   <si>
     <t xml:space="preserve">10.0402450561523</t>
@@ -1109,13 +1109,13 @@
     <t xml:space="preserve">10.034571647644</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98351955413818</t>
+    <t xml:space="preserve">9.9835205078125</t>
   </si>
   <si>
     <t xml:space="preserve">9.96082878112793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.98919200897217</t>
+    <t xml:space="preserve">9.9891939163208</t>
   </si>
   <si>
     <t xml:space="preserve">10.2274351119995</t>
@@ -1127,106 +1127,106 @@
     <t xml:space="preserve">10.4940395355225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.511058807373</t>
+    <t xml:space="preserve">10.5110578536987</t>
   </si>
   <si>
     <t xml:space="preserve">10.4146270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3295383453369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3635730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3805932998657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4600048065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5167303085327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3465566635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84738159179688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86439800262451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72825908660889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67720794677734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66018867492676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48434448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.688551902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58644866943359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71124076843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67153453826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61480808258057</t>
+    <t xml:space="preserve">10.3295402526855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3635740280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3805913925171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4600067138672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.516731262207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3465576171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84738063812256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.86439895629883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7282600402832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67720699310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66019058227539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48434352874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68855285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58644771575928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71124172210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67153358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.61480903625488</t>
   </si>
   <si>
     <t xml:space="preserve">9.62048149108887</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73393058776855</t>
+    <t xml:space="preserve">9.73393154144287</t>
   </si>
   <si>
     <t xml:space="preserve">9.78498458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7963285446167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89843273162842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16101455688477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.95113182067871</t>
+    <t xml:space="preserve">9.79632949829102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89843368530273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16101360321045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.95113277435303</t>
   </si>
   <si>
     <t xml:space="preserve">8.99084091186523</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76961231231689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75259685516357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86604499816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85470008850098</t>
+    <t xml:space="preserve">8.76961421966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75259780883789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86604595184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85470104217529</t>
   </si>
   <si>
     <t xml:space="preserve">9.05891036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24042797088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2517728805542</t>
+    <t xml:space="preserve">9.24042701721191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25177383422852</t>
   </si>
   <si>
     <t xml:space="preserve">9.10996150970459</t>
@@ -1235,28 +1235,28 @@
     <t xml:space="preserve">9.09294509887695</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98516654968262</t>
+    <t xml:space="preserve">8.98516750335693</t>
   </si>
   <si>
     <t xml:space="preserve">9.075927734375</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13265037536621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05323791503906</t>
+    <t xml:space="preserve">9.13265228271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05323600769043</t>
   </si>
   <si>
     <t xml:space="preserve">8.90008068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.88306331634521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82633972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79230403900146</t>
+    <t xml:space="preserve">8.8830623626709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82633876800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79230308532715</t>
   </si>
   <si>
     <t xml:space="preserve">8.79797744750977</t>
@@ -1268,25 +1268,25 @@
     <t xml:space="preserve">9.00218486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0702543258667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99651145935059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01920223236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92277050018311</t>
+    <t xml:space="preserve">9.07025527954102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.9965124130249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01920127868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92277145385742</t>
   </si>
   <si>
     <t xml:space="preserve">9.04189205169678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03054714202881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01353073120117</t>
+    <t xml:space="preserve">9.03054809570312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01352977752686</t>
   </si>
   <si>
     <t xml:space="preserve">9.04756450653076</t>
@@ -1295,58 +1295,58 @@
     <t xml:space="preserve">9.03621959686279</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13832378387451</t>
+    <t xml:space="preserve">9.13832473754883</t>
   </si>
   <si>
     <t xml:space="preserve">8.97382259368896</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12697982788086</t>
+    <t xml:space="preserve">9.12697887420654</t>
   </si>
   <si>
     <t xml:space="preserve">9.16668605804443</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19504737854004</t>
+    <t xml:space="preserve">9.19504833221436</t>
   </si>
   <si>
     <t xml:space="preserve">9.37089443206787</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38223838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34253311157227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.46732521057129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6755590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.420298576355</t>
+    <t xml:space="preserve">9.38223934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34253215789795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.46732616424561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.67555809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4202966690063</t>
   </si>
   <si>
     <t xml:space="preserve">10.3919363021851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5961456298828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7549724578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7379550933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7606449127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.661376953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4543323516846</t>
+    <t xml:space="preserve">10.5961446762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7549753189087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7379570007324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7606468200684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6613788604736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4543333053589</t>
   </si>
   <si>
     <t xml:space="preserve">10.4032831192017</t>
@@ -1355,7 +1355,7 @@
     <t xml:space="preserve">10.4429883956909</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3777551651001</t>
+    <t xml:space="preserve">10.3777561187744</t>
   </si>
   <si>
     <t xml:space="preserve">10.0742788314819</t>
@@ -1364,19 +1364,19 @@
     <t xml:space="preserve">10.1338396072388</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0941324234009</t>
+    <t xml:space="preserve">10.0941333770752</t>
   </si>
   <si>
     <t xml:space="preserve">9.98635673522949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1565284729004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1962356567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2359437942505</t>
+    <t xml:space="preserve">10.1565294265747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1962366104126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2359447479248</t>
   </si>
   <si>
     <t xml:space="preserve">10.1622009277344</t>
@@ -1385,7 +1385,7 @@
     <t xml:space="preserve">10.2416172027588</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2501249313354</t>
+    <t xml:space="preserve">10.2501258850098</t>
   </si>
   <si>
     <t xml:space="preserve">10.2132530212402</t>
@@ -1394,10 +1394,10 @@
     <t xml:space="preserve">10.1678743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90694046020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92963027954102</t>
+    <t xml:space="preserve">9.90694141387939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92963123321533</t>
   </si>
   <si>
     <t xml:space="preserve">10.1877279281616</t>
@@ -1406,46 +1406,46 @@
     <t xml:space="preserve">10.2302713394165</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0203905105591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1905632019043</t>
+    <t xml:space="preserve">10.0203895568848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1905641555786</t>
   </si>
   <si>
     <t xml:space="preserve">10.1820554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0317344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97784805297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81618213653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88708686828613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89559745788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81334590911865</t>
+    <t xml:space="preserve">10.0317363739014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9778470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81618309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88708782196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89559555053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81334495544434</t>
   </si>
   <si>
     <t xml:space="preserve">9.97501087188721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.065770149231</t>
+    <t xml:space="preserve">10.0657711029053</t>
   </si>
   <si>
     <t xml:space="preserve">10.1395111083984</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0005359649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686054229736</t>
+    <t xml:space="preserve">10.0005369186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686063766479</t>
   </si>
   <si>
     <t xml:space="preserve">9.73676776885986</t>
@@ -1454,40 +1454,40 @@
     <t xml:space="preserve">9.83603572845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89276027679443</t>
+    <t xml:space="preserve">9.89276123046875</t>
   </si>
   <si>
     <t xml:space="preserve">9.86723518371582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8275260925293</t>
+    <t xml:space="preserve">9.82752704620361</t>
   </si>
   <si>
     <t xml:space="preserve">9.77931213378906</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83320045471191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94948482513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714426040649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93814182281494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71407699584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4276180267334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10145282745361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.21773719787598</t>
+    <t xml:space="preserve">9.83319854736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94948577880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714416503906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93813991546631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71407794952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42761898040771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10145378112793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.21773815155029</t>
   </si>
   <si>
     <t xml:space="preserve">9.12414360046387</t>
@@ -1505,13 +1505,13 @@
     <t xml:space="preserve">9.51369667053223</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39841747283936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47206783294678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44004726409912</t>
+    <t xml:space="preserve">9.39841651916504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47206878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44004535675049</t>
   </si>
   <si>
     <t xml:space="preserve">9.3375768661499</t>
@@ -1520,10 +1520,10 @@
     <t xml:space="preserve">8.98533535003662</t>
   </si>
   <si>
-    <t xml:space="preserve">9.02696514129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.89887714385986</t>
+    <t xml:space="preserve">9.02696418762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.89887619018555</t>
   </si>
   <si>
     <t xml:space="preserve">9.34397983551025</t>
@@ -1541,7 +1541,7 @@
     <t xml:space="preserve">8.93410110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64590263366699</t>
+    <t xml:space="preserve">8.64590358734131</t>
   </si>
   <si>
     <t xml:space="preserve">8.83803462982178</t>
@@ -1550,7 +1550,7 @@
     <t xml:space="preserve">8.7547779083252</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72275638580322</t>
+    <t xml:space="preserve">8.72275543212891</t>
   </si>
   <si>
     <t xml:space="preserve">8.71635246276855</t>
@@ -1562,37 +1562,37 @@
     <t xml:space="preserve">8.8284273147583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.80601215362549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83162975311279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66511631011963</t>
+    <t xml:space="preserve">8.8060131072998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83163070678711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66511726379395</t>
   </si>
   <si>
     <t xml:space="preserve">8.73556613922119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5178165435791</t>
+    <t xml:space="preserve">8.51781463623047</t>
   </si>
   <si>
     <t xml:space="preserve">8.4889965057373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56905174255371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.45697402954102</t>
+    <t xml:space="preserve">8.56905078887939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.45697498321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.39613342285156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51141166687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53062534332275</t>
+    <t xml:space="preserve">8.5114107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53062629699707</t>
   </si>
   <si>
     <t xml:space="preserve">8.53702926635742</t>
@@ -1601,52 +1601,52 @@
     <t xml:space="preserve">8.54343318939209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71315002441406</t>
+    <t xml:space="preserve">8.71315097808838</t>
   </si>
   <si>
     <t xml:space="preserve">8.40573978424072</t>
   </si>
   <si>
-    <t xml:space="preserve">8.36411190032959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.3320894241333</t>
+    <t xml:space="preserve">8.36411094665527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.33209037780762</t>
   </si>
   <si>
     <t xml:space="preserve">8.42175102233887</t>
   </si>
   <si>
-    <t xml:space="preserve">8.58506202697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.57225322723389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46017646789551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46658134460449</t>
+    <t xml:space="preserve">8.58506298065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5722541809082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46017742156982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46658229827881</t>
   </si>
   <si>
     <t xml:space="preserve">8.58185958862305</t>
   </si>
   <si>
-    <t xml:space="preserve">8.44096374511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09420967102051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01735687255859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05578231811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1998815536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18707370758057</t>
+    <t xml:space="preserve">8.4409646987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09421062469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01735782623291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05578327178955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19988250732422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18707466125488</t>
   </si>
   <si>
     <t xml:space="preserve">8.91808986663818</t>
@@ -1655,10 +1655,10 @@
     <t xml:space="preserve">8.87646198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03657054901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18387126922607</t>
+    <t xml:space="preserve">9.03657150268555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18387222290039</t>
   </si>
   <si>
     <t xml:space="preserve">9.15505218505859</t>
@@ -1667,37 +1667,37 @@
     <t xml:space="preserve">9.1518497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23510646820068</t>
+    <t xml:space="preserve">9.23510551452637</t>
   </si>
   <si>
     <t xml:space="preserve">9.16465854644775</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12623119354248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26072216033936</t>
+    <t xml:space="preserve">9.1262321472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26072311401367</t>
   </si>
   <si>
     <t xml:space="preserve">9.25432014465332</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2062873840332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2094898223877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22549915313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10701942443848</t>
+    <t xml:space="preserve">9.20628643035889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20948886871338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22550010681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10701847076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.92769622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76758670806885</t>
+    <t xml:space="preserve">8.76758766174316</t>
   </si>
   <si>
     <t xml:space="preserve">8.65871238708496</t>
@@ -1706,28 +1706,28 @@
     <t xml:space="preserve">8.68112754821777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.72595882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61708450317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78039646148682</t>
+    <t xml:space="preserve">8.7259578704834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61708641052246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7803955078125</t>
   </si>
   <si>
     <t xml:space="preserve">8.82202434539795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77719402313232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78359699249268</t>
+    <t xml:space="preserve">8.77719497680664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78359794616699</t>
   </si>
   <si>
     <t xml:space="preserve">8.95331382751465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97252655029297</t>
+    <t xml:space="preserve">8.97252750396729</t>
   </si>
   <si>
     <t xml:space="preserve">8.9661226272583</t>
@@ -1736,10 +1736,10 @@
     <t xml:space="preserve">8.86685562133789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86045074462891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32568454742432</t>
+    <t xml:space="preserve">8.86044979095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32568550109863</t>
   </si>
   <si>
     <t xml:space="preserve">8.22321510314941</t>
@@ -1748,22 +1748,22 @@
     <t xml:space="preserve">8.29366302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53382778167725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48259353637695</t>
+    <t xml:space="preserve">8.53382682800293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48259258270264</t>
   </si>
   <si>
     <t xml:space="preserve">8.40253734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14956474304199</t>
+    <t xml:space="preserve">8.14956569671631</t>
   </si>
   <si>
     <t xml:space="preserve">8.06630802154541</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07271194458008</t>
+    <t xml:space="preserve">8.07271099090576</t>
   </si>
   <si>
     <t xml:space="preserve">7.77490901947021</t>
@@ -1772,25 +1772,25 @@
     <t xml:space="preserve">7.74929094314575</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67884302139282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87417602539062</t>
+    <t xml:space="preserve">7.67884349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8741774559021</t>
   </si>
   <si>
     <t xml:space="preserve">7.73007774353027</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53474569320679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42266988754272</t>
+    <t xml:space="preserve">7.53474521636963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42266941070557</t>
   </si>
   <si>
     <t xml:space="preserve">7.25295305252075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21772861480713</t>
+    <t xml:space="preserve">7.21772956848145</t>
   </si>
   <si>
     <t xml:space="preserve">7.08003520965576</t>
@@ -1799,136 +1799,136 @@
     <t xml:space="preserve">7.11205625534058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84947681427002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9711594581604</t>
+    <t xml:space="preserve">6.84947633743286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97115993499756</t>
   </si>
   <si>
     <t xml:space="preserve">7.0416088104248</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03520393371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04801177978516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94234085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95194673538208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00958681106567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13126850128174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97436237335205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83026361465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95515012741089</t>
+    <t xml:space="preserve">7.03520441055298</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04801225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9423394203186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95194721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00958585739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13126945495605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97436189651489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83026456832886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95514869689941</t>
   </si>
   <si>
     <t xml:space="preserve">6.80144453048706</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7662205696106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85908365249634</t>
+    <t xml:space="preserve">6.76621961593628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8590841293335</t>
   </si>
   <si>
     <t xml:space="preserve">6.62852573394775</t>
   </si>
   <si>
-    <t xml:space="preserve">6.70537853240967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74700736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86548805236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16329193115234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09604501724243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.06722593307495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02239608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23053693771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05761957168579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80464649200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89110565185547</t>
+    <t xml:space="preserve">6.70537900924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74700689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86548900604248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1632924079895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09604692459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.06722640991211</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02239561080933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23053741455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05761909484863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.80464601516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89110612869263</t>
   </si>
   <si>
     <t xml:space="preserve">6.71818733215332</t>
   </si>
   <si>
-    <t xml:space="preserve">6.73740005493164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95835065841675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01278734207153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88790369033813</t>
+    <t xml:space="preserve">6.7374005317688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95835208892822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01278829574585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88790321350098</t>
   </si>
   <si>
     <t xml:space="preserve">6.4588098526001</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39796829223633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15204095840454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15844488143921</t>
+    <t xml:space="preserve">6.39796924591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15204238891602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15844535827637</t>
   </si>
   <si>
     <t xml:space="preserve">5.96375131607056</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10592985153198</t>
+    <t xml:space="preserve">6.10593032836914</t>
   </si>
   <si>
     <t xml:space="preserve">6.10721063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39925003051758</t>
+    <t xml:space="preserve">6.39924907684326</t>
   </si>
   <si>
     <t xml:space="preserve">6.6445369720459</t>
   </si>
   <si>
-    <t xml:space="preserve">6.63172912597656</t>
+    <t xml:space="preserve">6.63172769546509</t>
   </si>
   <si>
     <t xml:space="preserve">6.59010028839111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50043964385986</t>
+    <t xml:space="preserve">6.50043916702271</t>
   </si>
   <si>
     <t xml:space="preserve">6.60290861129761</t>
@@ -1940,100 +1940,100 @@
     <t xml:space="preserve">6.41718149185181</t>
   </si>
   <si>
-    <t xml:space="preserve">6.52285432815552</t>
+    <t xml:space="preserve">6.52285480499268</t>
   </si>
   <si>
     <t xml:space="preserve">6.42038440704346</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47802257537842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44600248336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32624006271362</t>
+    <t xml:space="preserve">6.47802352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4460015296936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32624053955078</t>
   </si>
   <si>
     <t xml:space="preserve">6.26731967926025</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74380540847778</t>
+    <t xml:space="preserve">6.74380493164062</t>
   </si>
   <si>
     <t xml:space="preserve">7.09924840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30739116668701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19851541519165</t>
+    <t xml:space="preserve">7.30739068984985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19851446151733</t>
   </si>
   <si>
     <t xml:space="preserve">7.08964109420776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.11846113204956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15368509292603</t>
+    <t xml:space="preserve">7.1184606552124</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15368461608887</t>
   </si>
   <si>
     <t xml:space="preserve">7.15688610076904</t>
   </si>
   <si>
-    <t xml:space="preserve">7.17930221557617</t>
+    <t xml:space="preserve">7.17930173873901</t>
   </si>
   <si>
     <t xml:space="preserve">7.0448112487793</t>
   </si>
   <si>
-    <t xml:space="preserve">6.99357509613037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27216672897339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44828605651855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.75889825820923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5763726234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7268762588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83895111083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82614374160767</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84535789489746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8997950553894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9126033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98305130004883</t>
+    <t xml:space="preserve">6.99357652664185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27216625213623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.4482855796814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.75889730453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57637357711792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72687578201294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83895349502563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82614421844482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84535646438599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.89979410171509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91260242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98305082321167</t>
   </si>
   <si>
     <t xml:space="preserve">7.88058185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91900730133057</t>
+    <t xml:space="preserve">7.91900825500488</t>
   </si>
   <si>
     <t xml:space="preserve">8.23282241821289</t>
   </si>
   <si>
-    <t xml:space="preserve">8.12074661254883</t>
+    <t xml:space="preserve">8.12074565887451</t>
   </si>
   <si>
     <t xml:space="preserve">8.26164150238037</t>
@@ -2048,22 +2048,22 @@
     <t xml:space="preserve">8.84764194488525</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9116849899292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26392650604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33117294311523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53291034698486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.6770076751709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51049327850342</t>
+    <t xml:space="preserve">8.91168594360352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26392555236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33117198944092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53290939331055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67700862884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51049423217773</t>
   </si>
   <si>
     <t xml:space="preserve">9.42083263397217</t>
@@ -2072,37 +2072,37 @@
     <t xml:space="preserve">9.32796955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40482234954834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47847175598145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55212306976318</t>
+    <t xml:space="preserve">9.40482330322266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47847270965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55212116241455</t>
   </si>
   <si>
     <t xml:space="preserve">9.57133674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7026252746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77627563476562</t>
+    <t xml:space="preserve">9.70262432098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77627658843994</t>
   </si>
   <si>
     <t xml:space="preserve">9.81470203399658</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0836868286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0356531143188</t>
+    <t xml:space="preserve">10.083685874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0356521606445</t>
   </si>
   <si>
     <t xml:space="preserve">10.1413249969482</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2149744033813</t>
+    <t xml:space="preserve">10.2149753570557</t>
   </si>
   <si>
     <t xml:space="preserve">10.1957626342773</t>
@@ -2111,7 +2111,7 @@
     <t xml:space="preserve">10.2694120407104</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2790184020996</t>
+    <t xml:space="preserve">10.2790193557739</t>
   </si>
   <si>
     <t xml:space="preserve">10.5608129501343</t>
@@ -2120,7 +2120,7 @@
     <t xml:space="preserve">10.8490085601807</t>
   </si>
   <si>
-    <t xml:space="preserve">10.868221282959</t>
+    <t xml:space="preserve">10.8682222366333</t>
   </si>
   <si>
     <t xml:space="preserve">10.8874340057373</t>
@@ -2129,25 +2129,25 @@
     <t xml:space="preserve">11.0155210494995</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0603513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.281304359436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2909097671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5118598937988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5278720855713</t>
+    <t xml:space="preserve">11.0603504180908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2813034057617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2909116744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5118608474731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5278730392456</t>
   </si>
   <si>
     <t xml:space="preserve">11.495849609375</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3773679733276</t>
+    <t xml:space="preserve">11.377368927002</t>
   </si>
   <si>
     <t xml:space="preserve">11.3261337280273</t>
@@ -2156,7 +2156,7 @@
     <t xml:space="preserve">11.4926471710205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8105812072754</t>
+    <t xml:space="preserve">10.8105821609497</t>
   </si>
   <si>
     <t xml:space="preserve">10.9899053573608</t>
@@ -2168,10 +2168,10 @@
     <t xml:space="preserve">11.0219259262085</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1404066085815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1141195297241</t>
+    <t xml:space="preserve">11.1404075622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1141204833984</t>
   </si>
   <si>
     <t xml:space="preserve">10.7917680740356</t>
@@ -2186,16 +2186,16 @@
     <t xml:space="preserve">10.5780372619629</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3993396759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4273710250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2872190475464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3888282775879</t>
+    <t xml:space="preserve">10.399341583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4273700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2872180938721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3888292312622</t>
   </si>
   <si>
     <t xml:space="preserve">10.423867225647</t>
@@ -2204,16 +2204,16 @@
     <t xml:space="preserve">10.3678064346313</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7322025299072</t>
+    <t xml:space="preserve">10.7322034835815</t>
   </si>
   <si>
     <t xml:space="preserve">10.7742500305176</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4448900222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079593658447</t>
+    <t xml:space="preserve">10.4448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.507960319519</t>
   </si>
   <si>
     <t xml:space="preserve">10.5149660110474</t>
@@ -2228,7 +2228,7 @@
     <t xml:space="preserve">11.1281356811523</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1876993179321</t>
+    <t xml:space="preserve">11.1877002716064</t>
   </si>
   <si>
     <t xml:space="preserve">11.3523807525635</t>
@@ -2243,37 +2243,37 @@
     <t xml:space="preserve">11.7553195953369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7342977523804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429136276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7097692489624</t>
+    <t xml:space="preserve">11.7342967987061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429145812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7097682952881</t>
   </si>
   <si>
     <t xml:space="preserve">11.6291818618774</t>
   </si>
   <si>
-    <t xml:space="preserve">11.863938331604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.90598487854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9199991226196</t>
+    <t xml:space="preserve">11.8639392852783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9059829711914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9199981689453</t>
   </si>
   <si>
     <t xml:space="preserve">12.0496397018433</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2318382263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2248306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2984104156494</t>
+    <t xml:space="preserve">12.2318391799927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2248315811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2984094619751</t>
   </si>
   <si>
     <t xml:space="preserve">12.2143201828003</t>
@@ -2285,52 +2285,52 @@
     <t xml:space="preserve">12.2773895263672</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4175405502319</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3684883117676</t>
+    <t xml:space="preserve">12.4175415039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3684854507446</t>
   </si>
   <si>
     <t xml:space="preserve">12.1267251968384</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0391283035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464193344116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636539459229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1407403945923</t>
+    <t xml:space="preserve">12.0391292572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636568069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.140739440918</t>
   </si>
   <si>
     <t xml:space="preserve">12.1232194900513</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1092052459717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0321226119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8779525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760599136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6887474060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4680061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4890289306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4820222854614</t>
+    <t xml:space="preserve">12.109206199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0321216583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8779535293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760589599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6887464523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4680070877075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4890279769897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4820213317871</t>
   </si>
   <si>
     <t xml:space="preserve">11.6782360076904</t>
@@ -2339,106 +2339,106 @@
     <t xml:space="preserve">11.2472648620605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0370349884033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1001052856445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7216920852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9284181594849</t>
+    <t xml:space="preserve">11.037036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1001043319702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7216930389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9284172058105</t>
   </si>
   <si>
     <t xml:space="preserve">11.1561651229858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4960374832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4469814300537</t>
+    <t xml:space="preserve">11.496036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.446982383728</t>
   </si>
   <si>
     <t xml:space="preserve">11.1841974258423</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3243503570557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2752962112427</t>
+    <t xml:space="preserve">11.324348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2752952575684</t>
   </si>
   <si>
     <t xml:space="preserve">11.061562538147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.404935836792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2297458648682</t>
+    <t xml:space="preserve">11.4049377441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2297468185425</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119443893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4995403289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.790358543396</t>
+    <t xml:space="preserve">11.4995393753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7903575897217</t>
   </si>
   <si>
     <t xml:space="preserve">11.8814573287964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8288984298706</t>
+    <t xml:space="preserve">11.8288993835449</t>
   </si>
   <si>
     <t xml:space="preserve">11.9550361633301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6677227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6712284088135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113813400269</t>
+    <t xml:space="preserve">11.6677236557007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6712293624878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113803863525</t>
   </si>
   <si>
     <t xml:space="preserve">11.9970836639404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9410228729248</t>
+    <t xml:space="preserve">11.9410219192505</t>
   </si>
   <si>
     <t xml:space="preserve">11.9690523147583</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0671586990356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703809738159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2738838195801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.102198600769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0951890945435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9725561141968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0146026611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741662979126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9865713119507</t>
+    <t xml:space="preserve">12.06715965271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703800201416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2738857269287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1021995544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0951900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9725551605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0146017074585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.986572265625</t>
   </si>
   <si>
     <t xml:space="preserve">11.6011514663696</t>
@@ -2450,7 +2450,7 @@
     <t xml:space="preserve">11.5485935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5941438674927</t>
+    <t xml:space="preserve">11.5941429138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.4259605407715</t>
@@ -2459,13 +2459,13 @@
     <t xml:space="preserve">11.5380830764771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6852416992188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7693338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7027626037598</t>
+    <t xml:space="preserve">11.6852426528931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7693347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7027616500854</t>
   </si>
   <si>
     <t xml:space="preserve">11.9480285644531</t>
@@ -2474,205 +2474,205 @@
     <t xml:space="preserve">12.0846796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2108154296875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7539081573486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9641389846802</t>
+    <t xml:space="preserve">12.2108144760132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7539091110229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9641370773315</t>
   </si>
   <si>
     <t xml:space="preserve">12.7188701629639</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7889471054077</t>
+    <t xml:space="preserve">12.7889461517334</t>
   </si>
   <si>
     <t xml:space="preserve">12.795952796936</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9886655807495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1743659973145</t>
+    <t xml:space="preserve">12.9886636734009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1743669509888</t>
   </si>
   <si>
     <t xml:space="preserve">12.9080772399902</t>
   </si>
   <si>
-    <t xml:space="preserve">13.041223526001</t>
+    <t xml:space="preserve">13.0412216186523</t>
   </si>
   <si>
     <t xml:space="preserve">13.2094049453735</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6649036407471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8996553421021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007034301758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3656673431396</t>
+    <t xml:space="preserve">13.6649017333984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8996572494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007024765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.365665435791</t>
   </si>
   <si>
     <t xml:space="preserve">14.6389627456665</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0173759460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1365051269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5289344787598</t>
+    <t xml:space="preserve">15.0173778533936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1365060806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5289325714111</t>
   </si>
   <si>
     <t xml:space="preserve">15.9493923187256</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7181415557861</t>
+    <t xml:space="preserve">15.7181396484375</t>
   </si>
   <si>
     <t xml:space="preserve">15.9213619232178</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1035633087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9914398193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1245861053467</t>
+    <t xml:space="preserve">16.1035614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9914379119873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1245822906494</t>
   </si>
   <si>
     <t xml:space="preserve">16.4118976593018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5940971374512</t>
+    <t xml:space="preserve">16.5940952301025</t>
   </si>
   <si>
     <t xml:space="preserve">16.5100040435791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2086753845215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0474987030029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.886326789856</t>
+    <t xml:space="preserve">16.2086734771729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0475006103516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.886323928833</t>
   </si>
   <si>
     <t xml:space="preserve">15.486888885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8232564926147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7531785964966</t>
+    <t xml:space="preserve">15.8232536315918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7531766891479</t>
   </si>
   <si>
     <t xml:space="preserve">15.7251482009888</t>
   </si>
   <si>
-    <t xml:space="preserve">15.157527923584</t>
+    <t xml:space="preserve">15.1575298309326</t>
   </si>
   <si>
     <t xml:space="preserve">15.3817739486694</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2626447677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2976818084717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0804452896118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2836675643921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2205963134766</t>
+    <t xml:space="preserve">15.2626428604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.297679901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0804462432861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2836666107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2205982208252</t>
   </si>
   <si>
     <t xml:space="preserve">15.0944623947144</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0664310455322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0454063415527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8562002182007</t>
+    <t xml:space="preserve">15.0664291381836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0454072952271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.856201171875</t>
   </si>
   <si>
     <t xml:space="preserve">14.9122619628906</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1715440750122</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8702144622803</t>
+    <t xml:space="preserve">15.1715450286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8702163696289</t>
   </si>
   <si>
     <t xml:space="preserve">14.7721090316772</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3537435531616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5029964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5800819396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4189052581787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7062206268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8043251037598</t>
+    <t xml:space="preserve">15.353741645813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5029983520508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5800800323486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4189033508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7062168121338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8043231964111</t>
   </si>
   <si>
     <t xml:space="preserve">16.622127532959</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5660667419434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9865245819092</t>
+    <t xml:space="preserve">16.5660629272461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9865226745605</t>
   </si>
   <si>
     <t xml:space="preserve">17.00754737854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5380325317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0545101165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3978805541992</t>
+    <t xml:space="preserve">16.5380344390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0545082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3978824615479</t>
   </si>
   <si>
     <t xml:space="preserve">16.4959888458252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0685234069824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499572753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5709800720215</t>
+    <t xml:space="preserve">16.0685253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499591827393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5709810256958</t>
   </si>
   <si>
     <t xml:space="preserve">16.0334854125977</t>
@@ -2687,7 +2687,7 @@
     <t xml:space="preserve">16.6431503295898</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3908729553223</t>
+    <t xml:space="preserve">16.3908748626709</t>
   </si>
   <si>
     <t xml:space="preserve">16.7622814178467</t>
@@ -2699,25 +2699,25 @@
     <t xml:space="preserve">16.6711807250977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272396087646</t>
+    <t xml:space="preserve">16.7272434234619</t>
   </si>
   <si>
     <t xml:space="preserve">16.9514865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6130247116089</t>
+    <t xml:space="preserve">15.6130275726318</t>
   </si>
   <si>
     <t xml:space="preserve">14.5198335647583</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3516483306885</t>
+    <t xml:space="preserve">14.3516511917114</t>
   </si>
   <si>
     <t xml:space="preserve">14.5478658676147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7910385131836</t>
+    <t xml:space="preserve">13.7910404205322</t>
   </si>
   <si>
     <t xml:space="preserve">13.4546737670898</t>
@@ -2726,16 +2726,16 @@
     <t xml:space="preserve">13.0272054672241</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9956703186035</t>
+    <t xml:space="preserve">12.9956712722778</t>
   </si>
   <si>
     <t xml:space="preserve">12.3474655151367</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7202816009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3327674865723</t>
+    <t xml:space="preserve">11.7202806472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3327684402466</t>
   </si>
   <si>
     <t xml:space="preserve">9.68806457519531</t>
@@ -2744,13 +2744,13 @@
     <t xml:space="preserve">9.81069850921631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25149822235107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51988220214844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4442081451416</t>
+    <t xml:space="preserve">8.25149917602539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51988124847412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.44421005249023</t>
   </si>
   <si>
     <t xml:space="preserve">8.0202465057373</t>
@@ -2759,13 +2759,13 @@
     <t xml:space="preserve">7.70490264892578</t>
   </si>
   <si>
-    <t xml:space="preserve">7.77497863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49817657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59978675842285</t>
+    <t xml:space="preserve">7.77497959136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49817609786987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59978818893433</t>
   </si>
   <si>
     <t xml:space="preserve">8.28653621673584</t>
@@ -2774,31 +2774,31 @@
     <t xml:space="preserve">9.06088066101074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69507217407227</t>
+    <t xml:space="preserve">9.69507312774658</t>
   </si>
   <si>
     <t xml:space="preserve">9.05036926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87167549133301</t>
+    <t xml:space="preserve">8.87167453765869</t>
   </si>
   <si>
     <t xml:space="preserve">9.2360725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87517738342285</t>
+    <t xml:space="preserve">8.87517929077148</t>
   </si>
   <si>
     <t xml:space="preserve">9.07489585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68246841430664</t>
+    <t xml:space="preserve">8.68246936798096</t>
   </si>
   <si>
     <t xml:space="preserve">9.0223388671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48834705352783</t>
+    <t xml:space="preserve">9.48834800720215</t>
   </si>
   <si>
     <t xml:space="preserve">10.1680889129639</t>
@@ -2807,31 +2807,31 @@
     <t xml:space="preserve">10.2381649017334</t>
   </si>
   <si>
-    <t xml:space="preserve">9.87727069854736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29913997650146</t>
+    <t xml:space="preserve">9.87727165222168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29914093017578</t>
   </si>
   <si>
     <t xml:space="preserve">9.4463005065918</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51637744903564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58995819091797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25359153747559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33417987823486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4953556060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47433185577393</t>
+    <t xml:space="preserve">9.51637840270996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58995723724365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25359058380127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33417892456055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49535465240479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47433280944824</t>
   </si>
   <si>
     <t xml:space="preserve">10.3713102340698</t>
@@ -2840,40 +2840,40 @@
     <t xml:space="preserve">10.8162956237793</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2122268676758</t>
+    <t xml:space="preserve">11.2122278213501</t>
   </si>
   <si>
     <t xml:space="preserve">10.8793640136719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7602338790894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8618450164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5324859619141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6025619506836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6095695495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5394926071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4133567810059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0058345794678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4649343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7654342651367</t>
+    <t xml:space="preserve">10.760232925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8618440628052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5324850082397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6025629043579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6095705032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.539493560791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4133548736572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0058336257935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4649333953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.765435218811</t>
   </si>
   <si>
     <t xml:space="preserve">10.6414775848389</t>
@@ -2882,10 +2882,10 @@
     <t xml:space="preserve">10.769190788269</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8743667602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9757852554321</t>
+    <t xml:space="preserve">10.8743658065796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9757843017578</t>
   </si>
   <si>
     <t xml:space="preserve">10.9720277786255</t>
@@ -2894,16 +2894,16 @@
     <t xml:space="preserve">11.358922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1936464309692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3251171112061</t>
+    <t xml:space="preserve">11.1936473846436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3251161575317</t>
   </si>
   <si>
     <t xml:space="preserve">11.5204420089722</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7984046936035</t>
+    <t xml:space="preserve">11.7984056472778</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913925170898</t>
@@ -2915,13 +2915,13 @@
     <t xml:space="preserve">12.9966497421265</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4407253265381</t>
+    <t xml:space="preserve">12.4407243728638</t>
   </si>
   <si>
     <t xml:space="preserve">12.3956499099731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.648154258728</t>
+    <t xml:space="preserve">11.6481552124023</t>
   </si>
   <si>
     <t xml:space="preserve">11.6105918884277</t>
@@ -2930,22 +2930,22 @@
     <t xml:space="preserve">11.5166854858398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7721099853516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6669359207153</t>
+    <t xml:space="preserve">11.7721118927002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6669368743896</t>
   </si>
   <si>
     <t xml:space="preserve">11.5091733932495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7157678604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5730304718018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8284559249878</t>
+    <t xml:space="preserve">11.7157669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5730295181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8284549713135</t>
   </si>
   <si>
     <t xml:space="preserve">11.2687730789185</t>
@@ -2954,25 +2954,25 @@
     <t xml:space="preserve">11.4490728378296</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2011604309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4791240692139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.42653465271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3664350509644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.663179397583</t>
+    <t xml:space="preserve">11.2011594772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4791231155396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4265356063843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3664360046387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6631803512573</t>
   </si>
   <si>
     <t xml:space="preserve">11.5429792404175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7796249389648</t>
+    <t xml:space="preserve">11.7796239852905</t>
   </si>
   <si>
     <t xml:space="preserve">11.7608423233032</t>
@@ -2981,25 +2981,25 @@
     <t xml:space="preserve">11.4753665924072</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6706924438477</t>
+    <t xml:space="preserve">11.6706914901733</t>
   </si>
   <si>
     <t xml:space="preserve">11.8585052490234</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8434801101685</t>
+    <t xml:space="preserve">11.8434810638428</t>
   </si>
   <si>
     <t xml:space="preserve">12.3580884933472</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3205242156982</t>
+    <t xml:space="preserve">12.3205251693726</t>
   </si>
   <si>
     <t xml:space="preserve">12.801326751709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6999073028564</t>
+    <t xml:space="preserve">12.6999082565308</t>
   </si>
   <si>
     <t xml:space="preserve">12.7337131500244</t>
@@ -3008,16 +3008,16 @@
     <t xml:space="preserve">12.8351316452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5684375762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6097574234009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3731126785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4369688034058</t>
+    <t xml:space="preserve">12.5684385299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6097564697266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3731117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4369697570801</t>
   </si>
   <si>
     <t xml:space="preserve">12.0763692855835</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">12.3693571090698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3505744934082</t>
+    <t xml:space="preserve">12.3505754470825</t>
   </si>
   <si>
     <t xml:space="preserve">12.4745311737061</t>
@@ -3041,10 +3041,10 @@
     <t xml:space="preserve">12.470775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8276205062866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938137054443</t>
+    <t xml:space="preserve">12.8276195526123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938146591187</t>
   </si>
   <si>
     <t xml:space="preserve">12.6585884094238</t>
@@ -3056,7 +3056,7 @@
     <t xml:space="preserve">12.4557495117188</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5158500671387</t>
+    <t xml:space="preserve">12.515851020813</t>
   </si>
   <si>
     <t xml:space="preserve">12.3468179702759</t>
@@ -3074,10 +3074,10 @@
     <t xml:space="preserve">12.508337020874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3881378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1740322113037</t>
+    <t xml:space="preserve">12.3881368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1740303039551</t>
   </si>
   <si>
     <t xml:space="preserve">12.0650987625122</t>
@@ -3092,10 +3092,10 @@
     <t xml:space="preserve">12.1552495956421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8847990036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688562393188</t>
+    <t xml:space="preserve">11.8847980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688552856445</t>
   </si>
   <si>
     <t xml:space="preserve">12.1101751327515</t>
@@ -3104,22 +3104,22 @@
     <t xml:space="preserve">12.2078371047974</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3843822479248</t>
+    <t xml:space="preserve">12.3843812942505</t>
   </si>
   <si>
     <t xml:space="preserve">12.5120944976807</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6285371780396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4257011413574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8547496795654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8322105407715</t>
+    <t xml:space="preserve">12.6285381317139</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4257020950317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8547487258911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8322124481201</t>
   </si>
   <si>
     <t xml:space="preserve">11.8096742630005</t>
@@ -3128,58 +3128,58 @@
     <t xml:space="preserve">11.6181049346924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3326282501221</t>
+    <t xml:space="preserve">11.3326301574707</t>
   </si>
   <si>
     <t xml:space="preserve">11.7645988464355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5993232727051</t>
+    <t xml:space="preserve">11.5993223190308</t>
   </si>
   <si>
     <t xml:space="preserve">11.5842990875244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4640989303589</t>
+    <t xml:space="preserve">11.4640979766846</t>
   </si>
   <si>
     <t xml:space="preserve">11.362678527832</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7120113372803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8772859573364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8359670639038</t>
+    <t xml:space="preserve">11.712010383606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8772878646851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8359680175781</t>
   </si>
   <si>
     <t xml:space="preserve">11.9524116516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2003240585327</t>
+    <t xml:space="preserve">12.200325012207</t>
   </si>
   <si>
     <t xml:space="preserve">12.2904758453369</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1139316558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4031620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9448986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0989055633545</t>
+    <t xml:space="preserve">12.1139307022095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4031629562378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.944899559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0989046096802</t>
   </si>
   <si>
     <t xml:space="preserve">12.1514930725098</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0801248550415</t>
+    <t xml:space="preserve">12.0801239013672</t>
   </si>
   <si>
     <t xml:space="preserve">11.7007427215576</t>
@@ -3188,16 +3188,16 @@
     <t xml:space="preserve">11.5241985321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8255348205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6452341079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8893918991089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2499914169312</t>
+    <t xml:space="preserve">10.8255338668823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6452331542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8893909454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2499904632568</t>
   </si>
   <si>
     <t xml:space="preserve">11.64439868927</t>
@@ -3206,13 +3206,13 @@
     <t xml:space="preserve">11.8209419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0275363922119</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8885545730591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5834627151489</t>
+    <t xml:space="preserve">12.0275373458862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8885555267334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5834636688232</t>
   </si>
   <si>
     <t xml:space="preserve">12.4332113265991</t>
@@ -3230,22 +3230,22 @@
     <t xml:space="preserve">13.5600900650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2370519638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2595901489258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2220268249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6727771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3572521209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3797903060913</t>
+    <t xml:space="preserve">13.2370529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2595882415771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2220258712769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.672779083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.357253074646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.379789352417</t>
   </si>
   <si>
     <t xml:space="preserve">13.2746143341064</t>
@@ -3269,13 +3269,13 @@
     <t xml:space="preserve">13.1619272232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9327936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1731939315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1919765472412</t>
+    <t xml:space="preserve">12.9327955245972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1731948852539</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1919775009155</t>
   </si>
   <si>
     <t xml:space="preserve">13.1957340240479</t>
@@ -3287,10 +3287,10 @@
     <t xml:space="preserve">12.8238639831543</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3271999359131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361343383789</t>
+    <t xml:space="preserve">13.3272018432617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361333847046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4962339401245</t>
@@ -3299,7 +3299,7 @@
     <t xml:space="preserve">13.4323759078979</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3497409820557</t>
+    <t xml:space="preserve">13.3497400283813</t>
   </si>
   <si>
     <t xml:space="preserve">13.3384704589844</t>
@@ -3308,34 +3308,34 @@
     <t xml:space="preserve">13.1994895935059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4135971069336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4248657226562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.39857006073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.391058921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.680290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2099237442017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9582538604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8305416107178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.89439868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8380537033081</t>
+    <t xml:space="preserve">13.4135961532593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4248647689819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3985691070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3910579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6802883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2099227905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.958251953125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8305406570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943967819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8380527496338</t>
   </si>
   <si>
     <t xml:space="preserve">13.9319581985474</t>
@@ -3344,37 +3344,37 @@
     <t xml:space="preserve">13.7328786849976</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4398899078369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4060821533203</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1093406677246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3009071350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.04172706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887218475342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676002502441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.721607208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3526592254639</t>
+    <t xml:space="preserve">13.4398908615112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4060840606689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.109338760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3009090423584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0417261123657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887208938599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676012039185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7216091156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3526601791382</t>
   </si>
   <si>
     <t xml:space="preserve">14.5855484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0550804138184</t>
+    <t xml:space="preserve">15.0550813674927</t>
   </si>
   <si>
     <t xml:space="preserve">15.092643737793</t>
@@ -3383,28 +3383,28 @@
     <t xml:space="preserve">15.0250301361084</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1978178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447303771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7207717895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9198560714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.822190284729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5329608917236</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6005706787109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315404891968</t>
+    <t xml:space="preserve">15.1978158950806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447294235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7207736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9198551177979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8221912384033</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.532958984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6005725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4315423965454</t>
   </si>
   <si>
     <t xml:space="preserve">14.2812919616699</t>
@@ -3413,31 +3413,31 @@
     <t xml:space="preserve">14.9499053955078</t>
   </si>
   <si>
-    <t xml:space="preserve">14.784628868103</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7095060348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6644287109375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7620906829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9123411178589</t>
+    <t xml:space="preserve">14.7846307754517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7095031738281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6644296646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240293502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7958993911743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7620916366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9123420715332</t>
   </si>
   <si>
     <t xml:space="preserve">14.6606721878052</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4090051651001</t>
+    <t xml:space="preserve">14.4090042114258</t>
   </si>
   <si>
     <t xml:space="preserve">14.1948976516724</t>
@@ -3449,61 +3449,61 @@
     <t xml:space="preserve">14.202410697937</t>
   </si>
   <si>
-    <t xml:space="preserve">14.277533531189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3226108551025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714408874512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2925596237183</t>
+    <t xml:space="preserve">14.2775344848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3226099014282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202718734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714418411255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2925605773926</t>
   </si>
   <si>
     <t xml:space="preserve">14.4653482437134</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7470674514771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5930614471436</t>
+    <t xml:space="preserve">14.7470664978027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5930595397949</t>
   </si>
   <si>
     <t xml:space="preserve">14.8898057937622</t>
   </si>
   <si>
-    <t xml:space="preserve">14.848484992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2504053115845</t>
+    <t xml:space="preserve">14.8484859466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2504043579102</t>
   </si>
   <si>
     <t xml:space="preserve">15.1001558303833</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1151819229126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.070104598999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7245292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7508230209351</t>
+    <t xml:space="preserve">15.1151809692383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0701065063477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7245311737061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7508249282837</t>
   </si>
   <si>
     <t xml:space="preserve">14.814679145813</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8184366226196</t>
+    <t xml:space="preserve">14.8184375762939</t>
   </si>
   <si>
     <t xml:space="preserve">14.9837112426758</t>
@@ -3512,7 +3512,7 @@
     <t xml:space="preserve">15.0175180435181</t>
   </si>
   <si>
-    <t xml:space="preserve">14.792142868042</t>
+    <t xml:space="preserve">14.7921438217163</t>
   </si>
   <si>
     <t xml:space="preserve">14.9611749649048</t>
@@ -3530,16 +3530,16 @@
     <t xml:space="preserve">15.1377182006836</t>
   </si>
   <si>
-    <t xml:space="preserve">15.3555793762207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2579174041748</t>
+    <t xml:space="preserve">15.3555822372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2579183578491</t>
   </si>
   <si>
     <t xml:space="preserve">15.2804565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2729444503784</t>
+    <t xml:space="preserve">15.2729415893555</t>
   </si>
   <si>
     <t xml:space="preserve">15.7462310791016</t>
@@ -3551,16 +3551,16 @@
     <t xml:space="preserve">15.8438949584961</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6410551071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7086687088013</t>
+    <t xml:space="preserve">15.6410579681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7086696624756</t>
   </si>
   <si>
     <t xml:space="preserve">15.6711072921753</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1603336334229</t>
+    <t xml:space="preserve">16.1603355407715</t>
   </si>
   <si>
     <t xml:space="preserve">16.081428527832</t>
@@ -3572,13 +3572,13 @@
     <t xml:space="preserve">15.8999395370483</t>
   </si>
   <si>
-    <t xml:space="preserve">15.955174446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0419750213623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0025215148926</t>
+    <t xml:space="preserve">15.9551763534546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0419731140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0025196075439</t>
   </si>
   <si>
     <t xml:space="preserve">16.0972080230713</t>
@@ -3587,16 +3587,16 @@
     <t xml:space="preserve">16.1445541381836</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4601860046387</t>
+    <t xml:space="preserve">16.4601879119873</t>
   </si>
   <si>
     <t xml:space="preserve">16.4522953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.412841796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.326042175293</t>
+    <t xml:space="preserve">16.4128398895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3260440826416</t>
   </si>
   <si>
     <t xml:space="preserve">16.3497142791748</t>
@@ -3623,25 +3623,25 @@
     <t xml:space="preserve">16.2392444610596</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2471351623535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5312042236328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1287708282471</t>
+    <t xml:space="preserve">16.2471332550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5312023162842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1287727355957</t>
   </si>
   <si>
     <t xml:space="preserve">16.2155704498291</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3023719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5943279266357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.507532119751</t>
+    <t xml:space="preserve">16.3023700714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5943298339844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5075302124023</t>
   </si>
   <si>
     <t xml:space="preserve">16.4838562011719</t>
@@ -3650,10 +3650,10 @@
     <t xml:space="preserve">16.4444046020508</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2550239562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5233116149902</t>
+    <t xml:space="preserve">16.2550258636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5233135223389</t>
   </si>
   <si>
     <t xml:space="preserve">16.8073806762695</t>
@@ -3662,22 +3662,22 @@
     <t xml:space="preserve">17.1624660491943</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5254421234131</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3281726837158</t>
+    <t xml:space="preserve">17.5254402160645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3281707763672</t>
   </si>
   <si>
     <t xml:space="preserve">17.1940288543701</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2492637634277</t>
+    <t xml:space="preserve">17.2492656707764</t>
   </si>
   <si>
     <t xml:space="preserve">17.1387920379639</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4702053070068</t>
+    <t xml:space="preserve">17.4702072143555</t>
   </si>
   <si>
     <t xml:space="preserve">17.4938793182373</t>
@@ -3689,25 +3689,25 @@
     <t xml:space="preserve">17.4070796966553</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5727882385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9041996002197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9120903015137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1093616485596</t>
+    <t xml:space="preserve">17.5727863311768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9042015075684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9120922088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1093635559082</t>
   </si>
   <si>
     <t xml:space="preserve">18.1172504425049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2592868804932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3224124908447</t>
+    <t xml:space="preserve">18.2592849731445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3224105834961</t>
   </si>
   <si>
     <t xml:space="preserve">18.2435035705566</t>
@@ -3716,16 +3716,16 @@
     <t xml:space="preserve">18.4644451141357</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2513942718506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.282958984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.424991607666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3539772033691</t>
+    <t xml:space="preserve">18.251392364502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2829570770264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4249935150146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3539752960205</t>
   </si>
   <si>
     <t xml:space="preserve">18.4407730102539</t>
@@ -3743,7 +3743,7 @@
     <t xml:space="preserve">18.7642974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8037509918213</t>
+    <t xml:space="preserve">18.8037490844727</t>
   </si>
   <si>
     <t xml:space="preserve">18.7011699676514</t>
@@ -3764,16 +3764,16 @@
     <t xml:space="preserve">18.5749187469482</t>
   </si>
   <si>
-    <t xml:space="preserve">18.843204498291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8984394073486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9536762237549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1903972625732</t>
+    <t xml:space="preserve">18.8432025909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8984413146973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9536743164062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">19.0878200531006</t>
@@ -3785,13 +3785,13 @@
     <t xml:space="preserve">18.8589859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.937894821167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2614135742188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1430549621582</t>
+    <t xml:space="preserve">18.9378929138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2614154815674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1430530548096</t>
   </si>
   <si>
     <t xml:space="preserve">18.7327327728271</t>
@@ -3803,7 +3803,7 @@
     <t xml:space="preserve">18.7721881866455</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6538257598877</t>
+    <t xml:space="preserve">18.6538238525391</t>
   </si>
   <si>
     <t xml:space="preserve">18.4013195037842</t>
@@ -3812,19 +3812,19 @@
     <t xml:space="preserve">18.6222610473633</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2356128692627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1409225463867</t>
+    <t xml:space="preserve">18.2356147766113</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1409244537354</t>
   </si>
   <si>
     <t xml:space="preserve">18.43288230896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6380443572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8353118896484</t>
+    <t xml:space="preserve">18.6380424499512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8353137969971</t>
   </si>
   <si>
     <t xml:space="preserve">18.7090606689453</t>
@@ -3833,10 +3833,10 @@
     <t xml:space="preserve">19.5375938415527</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4034519195557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5297050476074</t>
+    <t xml:space="preserve">19.403450012207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5297012329102</t>
   </si>
   <si>
     <t xml:space="preserve">19.6007194519043</t>
@@ -3848,7 +3848,7 @@
     <t xml:space="preserve">19.6322822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6954097747803</t>
+    <t xml:space="preserve">19.6954078674316</t>
   </si>
   <si>
     <t xml:space="preserve">19.640172958374</t>
@@ -3878,19 +3878,19 @@
     <t xml:space="preserve">20.9027004241943</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1788787841797</t>
+    <t xml:space="preserve">21.1788768768311</t>
   </si>
   <si>
     <t xml:space="preserve">21.1946582794189</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9421520233154</t>
+    <t xml:space="preserve">20.9421539306641</t>
   </si>
   <si>
     <t xml:space="preserve">20.9816074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6659755706787</t>
+    <t xml:space="preserve">20.6659774780273</t>
   </si>
   <si>
     <t xml:space="preserve">20.2161998748779</t>
@@ -3905,19 +3905,19 @@
     <t xml:space="preserve">19.1035995483398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.316650390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3324337005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4744682312012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3087615966797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.174617767334</t>
+    <t xml:space="preserve">19.3166522979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3324317932129</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4744701385498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3087596893311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1746158599854</t>
   </si>
   <si>
     <t xml:space="preserve">19.2377433776855</t>
@@ -3929,7 +3929,7 @@
     <t xml:space="preserve">19.1272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.024694442749</t>
+    <t xml:space="preserve">19.0246925354004</t>
   </si>
   <si>
     <t xml:space="preserve">18.8116416931152</t>
@@ -3944,10 +3944,10 @@
     <t xml:space="preserve">18.9142208099365</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1667251586914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3561038970947</t>
+    <t xml:space="preserve">19.16672706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3561058044434</t>
   </si>
   <si>
     <t xml:space="preserve">19.411340713501</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">19.9479160308838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3403244018555</t>
+    <t xml:space="preserve">19.3403224945068</t>
   </si>
   <si>
     <t xml:space="preserve">19.5770454406738</t>
@@ -3974,7 +3974,7 @@
     <t xml:space="preserve">20.0268211364746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8711376190186</t>
+    <t xml:space="preserve">20.8711395263672</t>
   </si>
   <si>
     <t xml:space="preserve">20.9342651367188</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">20.6817569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3187808990479</t>
+    <t xml:space="preserve">20.3187789916992</t>
   </si>
   <si>
     <t xml:space="preserve">19.8847885131836</t>
@@ -3998,22 +3998,22 @@
     <t xml:space="preserve">18.2671756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3934288024902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0325832366943</t>
+    <t xml:space="preserve">18.3934307098389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.032585144043</t>
   </si>
   <si>
     <t xml:space="preserve">18.8747692108154</t>
   </si>
   <si>
-    <t xml:space="preserve">18.33030128479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7958583831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3697547912598</t>
+    <t xml:space="preserve">18.3303031921387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7958602905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3697566986084</t>
   </si>
   <si>
     <t xml:space="preserve">18.3145198822021</t>
@@ -4025,7 +4025,7 @@
     <t xml:space="preserve">17.7463836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9278717041016</t>
+    <t xml:space="preserve">17.9278697967529</t>
   </si>
   <si>
     <t xml:space="preserve">16.641674041748</t>
@@ -4034,7 +4034,7 @@
     <t xml:space="preserve">17.1782474517822</t>
   </si>
   <si>
-    <t xml:space="preserve">16.886287689209</t>
+    <t xml:space="preserve">16.8862857818604</t>
   </si>
   <si>
     <t xml:space="preserve">16.6337833404541</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">15.4501657485962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6632146835327</t>
+    <t xml:space="preserve">15.6632165908813</t>
   </si>
   <si>
     <t xml:space="preserve">17.0756664276123</t>
@@ -4055,7 +4055,7 @@
     <t xml:space="preserve">15.1897687911987</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5093479156494</t>
+    <t xml:space="preserve">15.5093460083008</t>
   </si>
   <si>
     <t xml:space="preserve">15.8525953292847</t>
@@ -4076,13 +4076,13 @@
     <t xml:space="preserve">16.7837066650391</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4286212921143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7442531585693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2413749694824</t>
+    <t xml:space="preserve">16.4286231994629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.744255065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2413730621338</t>
   </si>
   <si>
     <t xml:space="preserve">16.9415225982666</t>
@@ -4091,16 +4091,16 @@
     <t xml:space="preserve">16.6732368469238</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7600345611572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.318151473999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7579040527344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4107122421265</t>
+    <t xml:space="preserve">16.7600364685059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3181533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7579050064087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4107103347778</t>
   </si>
   <si>
     <t xml:space="preserve">15.7815780639648</t>
@@ -4109,10 +4109,10 @@
     <t xml:space="preserve">15.9157209396362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8920488357544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8683757781982</t>
+    <t xml:space="preserve">15.8920469284058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8683776855469</t>
   </si>
   <si>
     <t xml:space="preserve">15.6277074813843</t>
@@ -4121,10 +4121,10 @@
     <t xml:space="preserve">15.7973604202271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.753960609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8289213180542</t>
+    <t xml:space="preserve">15.7539587020874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8289232254028</t>
   </si>
   <si>
     <t xml:space="preserve">16.0893173217773</t>
@@ -4133,7 +4133,7 @@
     <t xml:space="preserve">16.0735378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.176118850708</t>
+    <t xml:space="preserve">16.1761169433594</t>
   </si>
   <si>
     <t xml:space="preserve">15.9236116409302</t>
@@ -4145,10 +4145,10 @@
     <t xml:space="preserve">15.5132913589478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9964427947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1660966873169</t>
+    <t xml:space="preserve">14.9964447021484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1660947799683</t>
   </si>
   <si>
     <t xml:space="preserve">15.6868877410889</t>
@@ -4163,7 +4163,7 @@
     <t xml:space="preserve">16.0261917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8052501678467</t>
+    <t xml:space="preserve">15.8052492141724</t>
   </si>
   <si>
     <t xml:space="preserve">16.4583625793457</t>
@@ -4211,31 +4211,31 @@
     <t xml:space="preserve">14.7298974990845</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4390106201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6287202835083</t>
+    <t xml:space="preserve">14.4390096664429</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.628719329834</t>
   </si>
   <si>
     <t xml:space="preserve">14.9828443527222</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2830266952515</t>
+    <t xml:space="preserve">14.2830257415771</t>
   </si>
   <si>
     <t xml:space="preserve">14.3715581893921</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4432239532471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.506462097168</t>
+    <t xml:space="preserve">14.4432258605957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5064630508423</t>
   </si>
   <si>
     <t xml:space="preserve">14.2197895050049</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6750936508179</t>
+    <t xml:space="preserve">14.6750946044922</t>
   </si>
   <si>
     <t xml:space="preserve">14.5191087722778</t>
@@ -4247,7 +4247,7 @@
     <t xml:space="preserve">14.2745952606201</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9837055206299</t>
+    <t xml:space="preserve">13.9837064743042</t>
   </si>
   <si>
     <t xml:space="preserve">13.8277225494385</t>
@@ -4259,7 +4259,7 @@
     <t xml:space="preserve">13.3724212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7771339416504</t>
+    <t xml:space="preserve">13.7771348953247</t>
   </si>
   <si>
     <t xml:space="preserve">14.1523380279541</t>
@@ -4268,13 +4268,13 @@
     <t xml:space="preserve">14.3420476913452</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1354742050171</t>
+    <t xml:space="preserve">14.1354732513428</t>
   </si>
   <si>
     <t xml:space="preserve">14.3546943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1987113952637</t>
+    <t xml:space="preserve">14.1987104415894</t>
   </si>
   <si>
     <t xml:space="preserve">13.6211519241333</t>
@@ -4316,13 +4316,13 @@
     <t xml:space="preserve">14.4727363586426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5739154815674</t>
+    <t xml:space="preserve">14.5739145278931</t>
   </si>
   <si>
     <t xml:space="preserve">14.2577314376831</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2956733703613</t>
+    <t xml:space="preserve">14.2956743240356</t>
   </si>
   <si>
     <t xml:space="preserve">14.1944942474365</t>
@@ -4334,16 +4334,16 @@
     <t xml:space="preserve">14.5022468566895</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5654830932617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6371507644653</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3757734298706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643068313599</t>
+    <t xml:space="preserve">14.5654821395874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6371517181396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3757724761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643058776855</t>
   </si>
   <si>
     <t xml:space="preserve">13.9794912338257</t>
@@ -4355,19 +4355,19 @@
     <t xml:space="preserve">13.9541959762573</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9415502548218</t>
+    <t xml:space="preserve">13.9415493011475</t>
   </si>
   <si>
     <t xml:space="preserve">13.8530178070068</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4651679992676</t>
+    <t xml:space="preserve">13.4651670455933</t>
   </si>
   <si>
     <t xml:space="preserve">13.4483041763306</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6380138397217</t>
+    <t xml:space="preserve">13.6380128860474</t>
   </si>
   <si>
     <t xml:space="preserve">13.435658454895</t>
@@ -4376,7 +4376,7 @@
     <t xml:space="preserve">13.1447687149048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6295833587646</t>
+    <t xml:space="preserve">13.6295824050903</t>
   </si>
   <si>
     <t xml:space="preserve">13.4272260665894</t>
@@ -4388,13 +4388,13 @@
     <t xml:space="preserve">13.5199728012085</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1692008972168</t>
+    <t xml:space="preserve">14.1692018508911</t>
   </si>
   <si>
     <t xml:space="preserve">14.0806703567505</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0722389221191</t>
+    <t xml:space="preserve">14.0722379684448</t>
   </si>
   <si>
     <t xml:space="preserve">13.9162540435791</t>
@@ -4406,10 +4406,10 @@
     <t xml:space="preserve">13.8572340011597</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4735994338989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1321220397949</t>
+    <t xml:space="preserve">13.4735984802246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1321210861206</t>
   </si>
   <si>
     <t xml:space="preserve">12.7484865188599</t>
@@ -4418,7 +4418,7 @@
     <t xml:space="preserve">12.7527027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5334815979004</t>
+    <t xml:space="preserve">12.5334825515747</t>
   </si>
   <si>
     <t xml:space="preserve">12.4112253189087</t>
@@ -4466,7 +4466,7 @@
     <t xml:space="preserve">12.8791751861572</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8665294647217</t>
+    <t xml:space="preserve">12.8665285110474</t>
   </si>
   <si>
     <t xml:space="preserve">12.8538808822632</t>
@@ -4487,16 +4487,16 @@
     <t xml:space="preserve">13.7897806167603</t>
   </si>
   <si>
-    <t xml:space="preserve">13.743408203125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9963550567627</t>
+    <t xml:space="preserve">13.7434072494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9963541030884</t>
   </si>
   <si>
     <t xml:space="preserve">14.1101808547974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3462629318237</t>
+    <t xml:space="preserve">14.3462619781494</t>
   </si>
   <si>
     <t xml:space="preserve">14.7214660644531</t>
@@ -4523,16 +4523,16 @@
     <t xml:space="preserve">16.8293514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.799840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3740501403809</t>
+    <t xml:space="preserve">16.7998390197754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3740482330322</t>
   </si>
   <si>
     <t xml:space="preserve">16.441499710083</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4035587310791</t>
+    <t xml:space="preserve">16.4035568237305</t>
   </si>
   <si>
     <t xml:space="preserve">16.3909111022949</t>
@@ -4544,16 +4544,16 @@
     <t xml:space="preserve">16.2349262237549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3993434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3023777008057</t>
+    <t xml:space="preserve">16.3993453979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3023796081543</t>
   </si>
   <si>
     <t xml:space="preserve">16.6059150695801</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5047359466553</t>
+    <t xml:space="preserve">16.5047378540039</t>
   </si>
   <si>
     <t xml:space="preserve">16.5089530944824</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">16.7618980407715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0570030212402</t>
+    <t xml:space="preserve">17.0570011138916</t>
   </si>
   <si>
     <t xml:space="preserve">16.9558258056641</t>
@@ -4583,7 +4583,7 @@
     <t xml:space="preserve">17.2593593597412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2340660095215</t>
+    <t xml:space="preserve">17.2340641021729</t>
   </si>
   <si>
     <t xml:space="preserve">17.5375995635986</t>
@@ -4595,7 +4595,7 @@
     <t xml:space="preserve">17.4617176055908</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6893672943115</t>
+    <t xml:space="preserve">17.6893692016602</t>
   </si>
   <si>
     <t xml:space="preserve">17.7146644592285</t>
@@ -4610,7 +4610,7 @@
     <t xml:space="preserve">17.8664302825928</t>
   </si>
   <si>
-    <t xml:space="preserve">18.043493270874</t>
+    <t xml:space="preserve">18.0434913635254</t>
   </si>
   <si>
     <t xml:space="preserve">18.2542819976807</t>
@@ -4619,19 +4619,19 @@
     <t xml:space="preserve">17.9760398864746</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9676094055176</t>
+    <t xml:space="preserve">17.9676074981689</t>
   </si>
   <si>
     <t xml:space="preserve">18.3807544708252</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3891868591309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8697834014893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9035110473633</t>
+    <t xml:space="preserve">18.3891849517822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8697814941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9035091400146</t>
   </si>
   <si>
     <t xml:space="preserve">18.9625301361084</t>
@@ -4646,16 +4646,16 @@
     <t xml:space="preserve">19.1648864746094</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8444881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.2239074707031</t>
+    <t xml:space="preserve">18.8444900512695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.2239093780518</t>
   </si>
   <si>
     <t xml:space="preserve">19.375675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3588104248047</t>
+    <t xml:space="preserve">19.3588123321533</t>
   </si>
   <si>
     <t xml:space="preserve">19.3419494628906</t>
@@ -4667,7 +4667,7 @@
     <t xml:space="preserve">19.4431285858154</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3250885009766</t>
+    <t xml:space="preserve">19.3250865936279</t>
   </si>
   <si>
     <t xml:space="preserve">19.2913589477539</t>
@@ -4685,10 +4685,10 @@
     <t xml:space="preserve">19.9405899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9321575164795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8899993896484</t>
+    <t xml:space="preserve">19.9321556091309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8900012969971</t>
   </si>
   <si>
     <t xml:space="preserve">19.8309783935547</t>
@@ -4697,7 +4697,7 @@
     <t xml:space="preserve">19.1564540863037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5358753204346</t>
+    <t xml:space="preserve">19.5358734130859</t>
   </si>
   <si>
     <t xml:space="preserve">19.0637092590332</t>
@@ -4721,10 +4721,10 @@
     <t xml:space="preserve">18.9456672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9793949127197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1058673858643</t>
+    <t xml:space="preserve">18.9793930053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1058654785156</t>
   </si>
   <si>
     <t xml:space="preserve">18.895076751709</t>
@@ -4739,10 +4739,10 @@
     <t xml:space="preserve">17.6134834289551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7745456695557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9811191558838</t>
+    <t xml:space="preserve">16.7745475769043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9811172485352</t>
   </si>
   <si>
     <t xml:space="preserve">16.239143371582</t>
@@ -4760,7 +4760,7 @@
     <t xml:space="preserve">16.3782634735107</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1126728057861</t>
+    <t xml:space="preserve">16.1126708984375</t>
   </si>
   <si>
     <t xml:space="preserve">16.1337490081787</t>
@@ -4775,22 +4775,22 @@
     <t xml:space="preserve">16.6101322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.546895980835</t>
+    <t xml:space="preserve">16.5468940734863</t>
   </si>
   <si>
     <t xml:space="preserve">16.3403205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">16.521598815918</t>
+    <t xml:space="preserve">16.5216007232666</t>
   </si>
   <si>
     <t xml:space="preserve">16.7113094329834</t>
   </si>
   <si>
-    <t xml:space="preserve">17.158182144165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1244564056396</t>
+    <t xml:space="preserve">17.1581802368164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.124454498291</t>
   </si>
   <si>
     <t xml:space="preserve">17.0232772827148</t>
@@ -4802,7 +4802,7 @@
     <t xml:space="preserve">17.2424983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.107593536377</t>
+    <t xml:space="preserve">17.1075916290283</t>
   </si>
   <si>
     <t xml:space="preserve">17.0148448944092</t>
@@ -4823,10 +4823,10 @@
     <t xml:space="preserve">16.9726867675781</t>
   </si>
   <si>
-    <t xml:space="preserve">17.08229637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8546466827393</t>
+    <t xml:space="preserve">17.0822982788086</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8546447753906</t>
   </si>
   <si>
     <t xml:space="preserve">16.9895496368408</t>
@@ -4835,10 +4835,10 @@
     <t xml:space="preserve">17.0738658905029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8504295349121</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2509288787842</t>
+    <t xml:space="preserve">16.8504314422607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2509269714355</t>
   </si>
   <si>
     <t xml:space="preserve">17.4084911346436</t>
@@ -6402,6 +6402,9 @@
   </si>
   <si>
     <t xml:space="preserve">33.7299995422363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">33.4199981689453</t>
   </si>
 </sst>
 </file>
@@ -71792,7 +71795,7 @@
     </row>
     <row r="2503">
       <c r="A2503" s="1" t="n">
-        <v>45964.691099537</v>
+        <v>45964.3333333333</v>
       </c>
       <c r="B2503" t="n">
         <v>482149</v>
@@ -71813,6 +71816,32 @@
         <v>2129</v>
       </c>
       <c r="H2503" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2504">
+      <c r="A2504" s="1" t="n">
+        <v>45965.6912384259</v>
+      </c>
+      <c r="B2504" t="n">
+        <v>475017</v>
+      </c>
+      <c r="C2504" t="n">
+        <v>33.6800003051758</v>
+      </c>
+      <c r="D2504" t="n">
+        <v>32.9599990844727</v>
+      </c>
+      <c r="E2504" t="n">
+        <v>33.1800003051758</v>
+      </c>
+      <c r="F2504" t="n">
+        <v>33.4199981689453</v>
+      </c>
+      <c r="G2504" t="s">
+        <v>2130</v>
+      </c>
+      <c r="H2504" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8295068740845</t>
+    <t xml:space="preserve">10.8295078277588</t>
   </si>
   <si>
     <t xml:space="preserve">AZM.MI</t>
@@ -50,49 +50,49 @@
     <t xml:space="preserve">10.4860258102417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1916131973267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.91191864013672</t>
+    <t xml:space="preserve">10.1916122436523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91191959381104</t>
   </si>
   <si>
     <t xml:space="preserve">9.9364538192749</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2259607315063</t>
+    <t xml:space="preserve">10.2259616851807</t>
   </si>
   <si>
     <t xml:space="preserve">10.0002431869507</t>
   </si>
   <si>
-    <t xml:space="preserve">9.61750602722168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33290481567383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15135097503662</t>
+    <t xml:space="preserve">9.61750793457031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33290576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.1513500213623</t>
   </si>
   <si>
     <t xml:space="preserve">9.37706851959229</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85693740844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25930118560791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53899669647217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48992729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50955581665039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40160369873047</t>
+    <t xml:space="preserve">8.85693836212158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25930213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53899574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4899263381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50955390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40160179138184</t>
   </si>
   <si>
     <t xml:space="preserve">9.12681770324707</t>
@@ -101,64 +101,64 @@
     <t xml:space="preserve">9.49483394622803</t>
   </si>
   <si>
-    <t xml:space="preserve">9.43595027923584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.84712505340576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99433135986328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79805469512939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.05711460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86574649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32699394226074</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61058759689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67928552627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10127735137939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87065172195435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53799152374268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78333473205566</t>
+    <t xml:space="preserve">9.43595123291016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.84712314605713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99432945251465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79805660247803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.05711364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86574697494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32699298858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61058855056763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67928504943848</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10127544403076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8706521987915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53798961639404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78333568572998</t>
   </si>
   <si>
     <t xml:space="preserve">8.46929454803467</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61649990081787</t>
+    <t xml:space="preserve">8.61650085449219</t>
   </si>
   <si>
     <t xml:space="preserve">8.50364208221436</t>
   </si>
   <si>
-    <t xml:space="preserve">8.21413421630859</t>
+    <t xml:space="preserve">8.21413516998291</t>
   </si>
   <si>
     <t xml:space="preserve">8.69010353088379</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71954345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29365158081055</t>
+    <t xml:space="preserve">8.71954441070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29365253448486</t>
   </si>
   <si>
     <t xml:space="preserve">9.30837154388428</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">9.09737586975098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22004795074463</t>
+    <t xml:space="preserve">9.22004890441895</t>
   </si>
   <si>
     <t xml:space="preserve">9.41141700744629</t>
@@ -179,46 +179,46 @@
     <t xml:space="preserve">9.48011302947998</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77943420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66166687011719</t>
+    <t xml:space="preserve">9.77943515777588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66166877746582</t>
   </si>
   <si>
     <t xml:space="preserve">9.79415321350098</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77452564239502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68620014190674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64694786071777</t>
+    <t xml:space="preserve">9.77452659606934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68620109558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64694881439209</t>
   </si>
   <si>
     <t xml:space="preserve">9.7254581451416</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357730865479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3044710159302</t>
+    <t xml:space="preserve">10.2357740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3044700622559</t>
   </si>
   <si>
     <t xml:space="preserve">9.83831596374512</t>
   </si>
   <si>
-    <t xml:space="preserve">9.56843662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98552227020264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93154621124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74508476257324</t>
+    <t xml:space="preserve">9.56843757629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98552322387695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93154716491699</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74508571624756</t>
   </si>
   <si>
     <t xml:space="preserve">10.3780736923218</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">10.5449085235596</t>
   </si>
   <si>
-    <t xml:space="preserve">10.436957359314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5547227859497</t>
+    <t xml:space="preserve">10.4369564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5547218322754</t>
   </si>
   <si>
     <t xml:space="preserve">10.5056533813477</t>
@@ -239,28 +239,28 @@
     <t xml:space="preserve">10.5498151779175</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5007448196411</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5694427490234</t>
+    <t xml:space="preserve">10.5007467269897</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5694417953491</t>
   </si>
   <si>
     <t xml:space="preserve">10.4173288345337</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4811191558838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7411842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8442277908325</t>
+    <t xml:space="preserve">10.4811172485352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7411851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8442287445068</t>
   </si>
   <si>
     <t xml:space="preserve">10.785346031189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5988836288452</t>
+    <t xml:space="preserve">10.5988826751709</t>
   </si>
   <si>
     <t xml:space="preserve">10.2406816482544</t>
@@ -272,46 +272,46 @@
     <t xml:space="preserve">9.73036575317383</t>
   </si>
   <si>
-    <t xml:space="preserve">9.57334327697754</t>
+    <t xml:space="preserve">9.57334423065186</t>
   </si>
   <si>
     <t xml:space="preserve">9.43104362487793</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40650939941406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19060611724854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08265590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35253238677979</t>
+    <t xml:space="preserve">9.40650844573975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19060516357422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08265495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3525333404541</t>
   </si>
   <si>
     <t xml:space="preserve">9.47029876708984</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2789306640625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30346488952637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14644622802734</t>
+    <t xml:space="preserve">9.27893161773682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30346584320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14644432067871</t>
   </si>
   <si>
     <t xml:space="preserve">9.52970123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79665470123291</t>
+    <t xml:space="preserve">9.79665565490723</t>
   </si>
   <si>
     <t xml:space="preserve">10.1190128326416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89235496520996</t>
+    <t xml:space="preserve">9.89235401153564</t>
   </si>
   <si>
     <t xml:space="preserve">9.95279598236084</t>
@@ -320,13 +320,13 @@
     <t xml:space="preserve">10.1492328643799</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84702301025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.76643466949463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42896461486816</t>
+    <t xml:space="preserve">9.84702205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76643371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42896556854248</t>
   </si>
   <si>
     <t xml:space="preserve">9.42392826080322</t>
@@ -335,19 +335,19 @@
     <t xml:space="preserve">9.52466487884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.54984855651855</t>
+    <t xml:space="preserve">9.54985046386719</t>
   </si>
   <si>
     <t xml:space="preserve">9.39370632171631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82958126068115</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4820384979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28560256958008</t>
+    <t xml:space="preserve">8.82957935333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48203945159912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28560161590576</t>
   </si>
   <si>
     <t xml:space="preserve">8.46189212799072</t>
@@ -356,97 +356,97 @@
     <t xml:space="preserve">8.53744411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68351268768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39874458312988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5045166015625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81680011749268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692943572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46459674835205</t>
+    <t xml:space="preserve">8.68351173400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39874267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50451755523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81680202484131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46692752838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46459770202637</t>
   </si>
   <si>
     <t xml:space="preserve">7.57540798187256</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49985504150391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34875011444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43941211700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20268106460571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87025022506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50256109237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6284818649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86017560958862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02135515213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38904476165771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20771932601929</t>
+    <t xml:space="preserve">7.49985408782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34875059127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43941354751587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20268249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87024927139282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50256061553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62848281860352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86017799377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02135467529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38904428482056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20771837234497</t>
   </si>
   <si>
     <t xml:space="preserve">7.44948673248291</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66607093811035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52503967285156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64592409133911</t>
+    <t xml:space="preserve">7.66607141494751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52504014968872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64592361450195</t>
   </si>
   <si>
     <t xml:space="preserve">7.79702854156494</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71140146255493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94309663772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.81717586517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94813346862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08179807662964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92565631866455</t>
+    <t xml:space="preserve">7.71140193939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94309711456299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.81717538833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.94813394546509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08179759979248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92565536499023</t>
   </si>
   <si>
     <t xml:space="preserve">6.71410799026489</t>
   </si>
   <si>
-    <t xml:space="preserve">6.7896614074707</t>
+    <t xml:space="preserve">6.78966188430786</t>
   </si>
   <si>
     <t xml:space="preserve">6.90047073364258</t>
@@ -455,76 +455,76 @@
     <t xml:space="preserve">7.22786569595337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27823495864868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32860136032104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31852912902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3991174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15735006332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94580364227295</t>
+    <t xml:space="preserve">7.27823352813721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32860279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31852865219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39911890029907</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15734958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94580221176147</t>
   </si>
   <si>
     <t xml:space="preserve">7.19764471054077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80477094650269</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02639293670654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08683395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04150390625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85010385513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8652138710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069124221802</t>
+    <t xml:space="preserve">6.80477046966553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02639150619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08683443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04150295257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85010194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86521291732788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069171905518</t>
   </si>
   <si>
     <t xml:space="preserve">7.22282934188843</t>
   </si>
   <si>
-    <t xml:space="preserve">7.31349277496338</t>
+    <t xml:space="preserve">7.31349229812622</t>
   </si>
   <si>
     <t xml:space="preserve">7.23290205001831</t>
   </si>
   <si>
-    <t xml:space="preserve">7.29838085174561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98106050491333</t>
+    <t xml:space="preserve">7.29838132858276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98105907440186</t>
   </si>
   <si>
     <t xml:space="preserve">7.01128149032593</t>
   </si>
   <si>
-    <t xml:space="preserve">6.53781890869141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79973459243774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68388748168945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73929262161255</t>
+    <t xml:space="preserve">6.53781938552856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79973411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68388700485229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73929214477539</t>
   </si>
   <si>
     <t xml:space="preserve">6.94076585769653</t>
@@ -533,88 +533,88 @@
     <t xml:space="preserve">6.90550804138184</t>
   </si>
   <si>
-    <t xml:space="preserve">6.66877603530884</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46226644515991</t>
+    <t xml:space="preserve">6.668776512146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4622654914856</t>
   </si>
   <si>
     <t xml:space="preserve">6.57307624816895</t>
   </si>
   <si>
-    <t xml:space="preserve">6.67381381988525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59826040267944</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8752875328064</t>
+    <t xml:space="preserve">6.67381286621094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.5982608795166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87528800964355</t>
   </si>
   <si>
     <t xml:space="preserve">7.00624465942383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15231323242188</t>
+    <t xml:space="preserve">7.15231275558472</t>
   </si>
   <si>
     <t xml:space="preserve">7.30341863632202</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62577724456787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66103219985962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57037210464478</t>
+    <t xml:space="preserve">7.6257758140564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66103410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5703706741333</t>
   </si>
   <si>
     <t xml:space="preserve">7.45452356338501</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53511238098145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44444942474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59555578231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72147703170776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.60562896728516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70636653900146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.48474502563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.36386013031006</t>
+    <t xml:space="preserve">7.53511333465576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44444990158081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59555387496948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72147655487061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.60562801361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70636606216431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.48474407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36386060714722</t>
   </si>
   <si>
     <t xml:space="preserve">7.26312351226807</t>
   </si>
   <si>
-    <t xml:space="preserve">7.13216543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617195129395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17246007919312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69629287719727</t>
+    <t xml:space="preserve">7.13216495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617099761963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17246055603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69629144668579</t>
   </si>
   <si>
     <t xml:space="preserve">7.91791391372681</t>
   </si>
   <si>
-    <t xml:space="preserve">8.35611724853516</t>
+    <t xml:space="preserve">8.35611820220947</t>
   </si>
   <si>
     <t xml:space="preserve">8.38634014129639</t>
@@ -632,58 +632,58 @@
     <t xml:space="preserve">8.04887008666992</t>
   </si>
   <si>
-    <t xml:space="preserve">7.9582085609436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.93132209777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71623468399048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73236703872681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63557815551758</t>
+    <t xml:space="preserve">7.95820760726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.93132162094116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71623563766479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73236751556396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63557767868042</t>
   </si>
   <si>
     <t xml:space="preserve">7.64095497131348</t>
   </si>
   <si>
-    <t xml:space="preserve">7.45813131332397</t>
+    <t xml:space="preserve">7.45813226699829</t>
   </si>
   <si>
     <t xml:space="preserve">7.44200038909912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57105207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68934965133667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62482213973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7968921661377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20018005371094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43139839172363</t>
+    <t xml:space="preserve">7.57105159759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68935060501099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62482309341431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79689311981201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20017910003662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43140029907227</t>
   </si>
   <si>
     <t xml:space="preserve">8.61960029602051</t>
   </si>
   <si>
-    <t xml:space="preserve">8.54432010650635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46903896331787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58733654022217</t>
+    <t xml:space="preserve">8.54431915283203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46903800964355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58733749389648</t>
   </si>
   <si>
     <t xml:space="preserve">8.70025730133057</t>
@@ -692,7 +692,7 @@
     <t xml:space="preserve">8.54969596862793</t>
   </si>
   <si>
-    <t xml:space="preserve">8.6034688949585</t>
+    <t xml:space="preserve">8.60346794128418</t>
   </si>
   <si>
     <t xml:space="preserve">8.53356552124023</t>
@@ -701,13 +701,13 @@
     <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51743412017822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52818775177002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.67874908447266</t>
+    <t xml:space="preserve">8.51743316650391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5281867980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.67874813079834</t>
   </si>
   <si>
     <t xml:space="preserve">9.11429882049561</t>
@@ -722,67 +722,67 @@
     <t xml:space="preserve">9.17882537841797</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05515003204346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33476448059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13043117523193</t>
+    <t xml:space="preserve">9.05515098571777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.33476257324219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13043022155762</t>
   </si>
   <si>
     <t xml:space="preserve">9.44768333435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38315868377686</t>
+    <t xml:space="preserve">9.38315773010254</t>
   </si>
   <si>
     <t xml:space="preserve">9.41004371643066</t>
   </si>
   <si>
-    <t xml:space="preserve">9.45843696594238</t>
+    <t xml:space="preserve">9.4584379196167</t>
   </si>
   <si>
     <t xml:space="preserve">9.45306015014648</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37240314483643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.23797416687012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32938575744629</t>
+    <t xml:space="preserve">9.37240409851074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23797512054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32938671112061</t>
   </si>
   <si>
     <t xml:space="preserve">9.46919345855713</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44230461120605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92609786987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09278964996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07128238677979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76478385925293</t>
+    <t xml:space="preserve">9.44230651855469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92609691619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0927906036377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07128143310547</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76478290557861</t>
   </si>
   <si>
     <t xml:space="preserve">9.16807079315186</t>
   </si>
   <si>
-    <t xml:space="preserve">9.25948143005371</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.28636837005615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24335193634033</t>
+    <t xml:space="preserve">9.25948238372803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.28636932373047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2433500289917</t>
   </si>
   <si>
     <t xml:space="preserve">9.26486015319824</t>
@@ -794,28 +794,28 @@
     <t xml:space="preserve">9.24872875213623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9637393951416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49592590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59271430969238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52281093597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66799354553223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7378978729248</t>
+    <t xml:space="preserve">8.96373844146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.495924949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59271335601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52281188964844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66799449920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73789691925049</t>
   </si>
   <si>
     <t xml:space="preserve">8.71101188659668</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70563316345215</t>
+    <t xml:space="preserve">8.70563411712646</t>
   </si>
   <si>
     <t xml:space="preserve">8.63573169708252</t>
@@ -824,34 +824,34 @@
     <t xml:space="preserve">8.53894233703613</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50130271911621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28621578216553</t>
+    <t xml:space="preserve">8.50130176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28621482849121</t>
   </si>
   <si>
     <t xml:space="preserve">8.33460998535156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.43677520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47441577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62497615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56582832336426</t>
+    <t xml:space="preserve">8.43677616119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4744176864624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62497711181641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56582927703857</t>
   </si>
   <si>
     <t xml:space="preserve">8.47979354858398</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66261768341064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61422157287598</t>
+    <t xml:space="preserve">8.66261672973633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61422252655029</t>
   </si>
   <si>
     <t xml:space="preserve">8.78091430664062</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">8.77016067504883</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79166984558105</t>
+    <t xml:space="preserve">8.79166889190674</t>
   </si>
   <si>
     <t xml:space="preserve">9.18420219421387</t>
@@ -869,22 +869,22 @@
     <t xml:space="preserve">9.04977321624756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14118385314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16269397735596</t>
+    <t xml:space="preserve">9.14118480682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16269302368164</t>
   </si>
   <si>
     <t xml:space="preserve">9.30249977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13580703735352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14656162261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20571041107178</t>
+    <t xml:space="preserve">9.13580799102783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14656257629395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20571136474609</t>
   </si>
   <si>
     <t xml:space="preserve">9.62513065338135</t>
@@ -896,22 +896,22 @@
     <t xml:space="preserve">9.60899925231934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63588619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71654319763184</t>
+    <t xml:space="preserve">9.63588523864746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7165412902832</t>
   </si>
   <si>
     <t xml:space="preserve">9.97464656829834</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0553035736084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2435026168823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4155740737915</t>
+    <t xml:space="preserve">10.0553026199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2435035705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4155731201172</t>
   </si>
   <si>
     <t xml:space="preserve">10.3456707000732</t>
@@ -923,280 +923,280 @@
     <t xml:space="preserve">10.3994417190552</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4101972579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349151611328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1305828094482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1036977767944</t>
+    <t xml:space="preserve">10.410195350647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349161148071</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1305847167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1036996841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3295383453369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4259719848633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6074905395508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5847988128662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4770221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2387800216675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2728157043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3408842086792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2160911560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0856227874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.90410614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2898330688477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2614698410034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0062093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94381237030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1707096099854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1366748809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0629329681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1990728378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3522291183472</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104167938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1933994293213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95515823364258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.148021697998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2444524765015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841596603394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2217626571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0912961959839</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1593647003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.545093536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.408953666687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3181953430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2955055236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3692464828491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4316444396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3976097106934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7152662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6415243148804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7436294555664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7209377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6698865890503</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7776622772217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7039213180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6585426330566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5394201278687</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3068504333496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095937728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5564374923706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4826946258545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3352117538452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2331075668335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2784862518311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0288982391357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.040244102478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0969686508179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.034571647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98351955413818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96082973480225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98919296264648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2274360656738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2557964324951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4940395355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.511058807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4146270751953</t>
   </si>
   <si>
     <t xml:space="preserve">10.3295392990112</t>
   </si>
   <si>
-    <t xml:space="preserve">10.425971031189</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5507650375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6074905395508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5847997665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4770221710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2728147506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3408842086792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2160902023315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0856227874756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.90410614013672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2898321151733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2614707946777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083135604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0062084197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94381141662598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1707105636597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1366758346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0629348754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1990728378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3522272109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104167938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1934013366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95515823364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1480207443237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2444515228271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841596603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2217626571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0912971496582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1593656539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5450944900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.408953666687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3181943893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2955045700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3692474365234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4316444396973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3976097106934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7152662277222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6415252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7436285018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7209386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.669885635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7776622772217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7039203643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6585416793823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5394201278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3068504333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095947265625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5564374923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4826955795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3352117538452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2331085205078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2784862518311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0288982391357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402450561523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0969686508179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.034571647644</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9835205078125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96082878112793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9891939163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2274351119995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2557973861694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4940395355225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5110578536987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4146270751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3295402526855</t>
-  </si>
-  <si>
     <t xml:space="preserve">10.3635740280151</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3805913925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4600067138672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.516731262207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3465576171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84738063812256</t>
+    <t xml:space="preserve">10.3805923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4600057601929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5167303085327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3465566635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84738159179688</t>
   </si>
   <si>
     <t xml:space="preserve">9.86439895629883</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7282600402832</t>
+    <t xml:space="preserve">9.72825908660889</t>
   </si>
   <si>
     <t xml:space="preserve">9.67720699310303</t>
   </si>
   <si>
-    <t xml:space="preserve">9.66019058227539</t>
+    <t xml:space="preserve">9.66018962860107</t>
   </si>
   <si>
     <t xml:space="preserve">9.48434352874756</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68855285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58644771575928</t>
+    <t xml:space="preserve">9.688551902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58644866943359</t>
   </si>
   <si>
     <t xml:space="preserve">9.71124172210693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.67153358459473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61480903625488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.62048149108887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73393154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.78498458862305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79632949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89843368530273</t>
+    <t xml:space="preserve">9.67153453826904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6148099899292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.62048244476318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73393249511719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.78498268127441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7963285446167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89843273162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.16101360321045</t>
@@ -1205,31 +1205,31 @@
     <t xml:space="preserve">8.95113277435303</t>
   </si>
   <si>
-    <t xml:space="preserve">8.99084091186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76961421966553</t>
+    <t xml:space="preserve">8.99083995819092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76961326599121</t>
   </si>
   <si>
     <t xml:space="preserve">8.75259780883789</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86604595184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.85470104217529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05891036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24042701721191</t>
+    <t xml:space="preserve">8.86604499816895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.85470008850098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05890941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24042797088623</t>
   </si>
   <si>
     <t xml:space="preserve">9.25177383422852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10996150970459</t>
+    <t xml:space="preserve">9.10996246337891</t>
   </si>
   <si>
     <t xml:space="preserve">9.09294509887695</t>
@@ -1238,31 +1238,31 @@
     <t xml:space="preserve">8.98516750335693</t>
   </si>
   <si>
-    <t xml:space="preserve">9.075927734375</t>
+    <t xml:space="preserve">9.07592678070068</t>
   </si>
   <si>
     <t xml:space="preserve">9.13265228271484</t>
   </si>
   <si>
-    <t xml:space="preserve">9.05323600769043</t>
+    <t xml:space="preserve">9.05323791503906</t>
   </si>
   <si>
     <t xml:space="preserve">8.90008068084717</t>
   </si>
   <si>
-    <t xml:space="preserve">8.8830623626709</t>
+    <t xml:space="preserve">8.88306331634521</t>
   </si>
   <si>
     <t xml:space="preserve">8.82633876800537</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79230308532715</t>
+    <t xml:space="preserve">8.79230403900146</t>
   </si>
   <si>
     <t xml:space="preserve">8.79797744750977</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9681510925293</t>
+    <t xml:space="preserve">8.96815013885498</t>
   </si>
   <si>
     <t xml:space="preserve">9.00218486785889</t>
@@ -1274,13 +1274,13 @@
     <t xml:space="preserve">8.9965124130249</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01920127868652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92277145385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04189205169678</t>
+    <t xml:space="preserve">9.01920318603516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92277050018311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04189300537109</t>
   </si>
   <si>
     <t xml:space="preserve">9.03054809570312</t>
@@ -1289,19 +1289,19 @@
     <t xml:space="preserve">9.01352977752686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04756450653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03621959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13832473754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97382259368896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12697887420654</t>
+    <t xml:space="preserve">9.04756546020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03622055053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13832378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97382164001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12697792053223</t>
   </si>
   <si>
     <t xml:space="preserve">9.16668605804443</t>
@@ -1310,31 +1310,31 @@
     <t xml:space="preserve">9.19504833221436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37089443206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38223934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34253215789795</t>
+    <t xml:space="preserve">9.37089347839355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34253120422363</t>
   </si>
   <si>
     <t xml:space="preserve">9.46732616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.67555809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4202966690063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3919363021851</t>
+    <t xml:space="preserve">10.6755590438843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4202995300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3919353485107</t>
   </si>
   <si>
     <t xml:space="preserve">10.5961446762085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7549753189087</t>
+    <t xml:space="preserve">10.7549734115601</t>
   </si>
   <si>
     <t xml:space="preserve">10.7379570007324</t>
@@ -1343,61 +1343,61 @@
     <t xml:space="preserve">10.7606468200684</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6613788604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4543333053589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4032831192017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4429883956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3777561187744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0742788314819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1338396072388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0941333770752</t>
+    <t xml:space="preserve">10.6613779067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4543342590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4032821655273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4429893493652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3777551651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0742797851562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1338386535645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0941324234009</t>
   </si>
   <si>
     <t xml:space="preserve">9.98635673522949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1565294265747</t>
+    <t xml:space="preserve">10.1565284729004</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962366104126</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2359447479248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1622009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2416172027588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2501258850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2132530212402</t>
+    <t xml:space="preserve">10.2359437942505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1622018814087</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2416162490845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2501249313354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2132539749146</t>
   </si>
   <si>
     <t xml:space="preserve">10.1678743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90694141387939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.92963123321533</t>
+    <t xml:space="preserve">9.90694046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.92963027954102</t>
   </si>
   <si>
     <t xml:space="preserve">10.1877279281616</t>
@@ -1409,31 +1409,31 @@
     <t xml:space="preserve">10.0203895568848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1905641555786</t>
+    <t xml:space="preserve">10.1905651092529</t>
   </si>
   <si>
     <t xml:space="preserve">10.1820554733276</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0317363739014</t>
+    <t xml:space="preserve">10.0317344665527</t>
   </si>
   <si>
     <t xml:space="preserve">9.9778470993042</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81618309020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88708782196045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89559555053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81334495544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97501087188721</t>
+    <t xml:space="preserve">9.81618213653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88708877563477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89559650421143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81334590911865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97500991821289</t>
   </si>
   <si>
     <t xml:space="preserve">10.0657711029053</t>
@@ -1448,40 +1448,40 @@
     <t xml:space="preserve">10.0686063766479</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73676776885986</t>
+    <t xml:space="preserve">9.73676872253418</t>
   </si>
   <si>
     <t xml:space="preserve">9.83603572845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89276123046875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.86723518371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.82752704620361</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77931213378906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83319854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94948577880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0714416503906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93813991546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71407794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42761898040771</t>
+    <t xml:space="preserve">9.89276027679443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8672342300415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.82752513885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77931118011475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8331995010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94948482513428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0714426040649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93814086914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71407699584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42761993408203</t>
   </si>
   <si>
     <t xml:space="preserve">9.10145378112793</t>
@@ -1490,28 +1490,28 @@
     <t xml:space="preserve">9.21773815155029</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12414360046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24326515197754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20072174072266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29274559020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51369667053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39841651916504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47206878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44004535675049</t>
+    <t xml:space="preserve">9.12414264678955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24326610565186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20072269439697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29274463653564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51369762420654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39841747283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47206783294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4400463104248</t>
   </si>
   <si>
     <t xml:space="preserve">9.3375768661499</t>
@@ -1526,7 +1526,7 @@
     <t xml:space="preserve">8.89887619018555</t>
   </si>
   <si>
-    <t xml:space="preserve">9.34397983551025</t>
+    <t xml:space="preserve">9.34398078918457</t>
   </si>
   <si>
     <t xml:space="preserve">9.31836318969727</t>
@@ -1538,31 +1538,31 @@
     <t xml:space="preserve">8.92129135131836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.93410110473633</t>
+    <t xml:space="preserve">8.93410205841064</t>
   </si>
   <si>
     <t xml:space="preserve">8.64590358734131</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83803462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7547779083252</t>
+    <t xml:space="preserve">8.83803558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75477886199951</t>
   </si>
   <si>
     <t xml:space="preserve">8.72275543212891</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71635246276855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.64270210266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8284273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.8060131072998</t>
+    <t xml:space="preserve">8.71635150909424</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.64270114898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82842826843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.80601406097412</t>
   </si>
   <si>
     <t xml:space="preserve">8.83163070678711</t>
@@ -1574,40 +1574,40 @@
     <t xml:space="preserve">8.73556613922119</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51781463623047</t>
+    <t xml:space="preserve">8.5178165435791</t>
   </si>
   <si>
     <t xml:space="preserve">8.4889965057373</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56905078887939</t>
+    <t xml:space="preserve">8.56905174255371</t>
   </si>
   <si>
     <t xml:space="preserve">8.45697498321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39613342285156</t>
+    <t xml:space="preserve">8.39613246917725</t>
   </si>
   <si>
     <t xml:space="preserve">8.5114107131958</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53062629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53702926635742</t>
+    <t xml:space="preserve">8.53062534332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53703022003174</t>
   </si>
   <si>
     <t xml:space="preserve">8.54343318939209</t>
   </si>
   <si>
-    <t xml:space="preserve">8.71315097808838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40573978424072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.36411094665527</t>
+    <t xml:space="preserve">8.71315002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40574073791504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.36411190032959</t>
   </si>
   <si>
     <t xml:space="preserve">8.33209037780762</t>
@@ -1625,19 +1625,19 @@
     <t xml:space="preserve">8.46017742156982</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46658229827881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.58185958862305</t>
+    <t xml:space="preserve">8.46658134460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.58186054229736</t>
   </si>
   <si>
     <t xml:space="preserve">8.4409646987915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09421062469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.01735782623291</t>
+    <t xml:space="preserve">9.09421157836914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.01735877990723</t>
   </si>
   <si>
     <t xml:space="preserve">9.05578327178955</t>
@@ -1646,40 +1646,40 @@
     <t xml:space="preserve">9.19988250732422</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18707466125488</t>
+    <t xml:space="preserve">9.18707370758057</t>
   </si>
   <si>
     <t xml:space="preserve">8.91808986663818</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87646198272705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03657150268555</t>
+    <t xml:space="preserve">8.87646293640137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03657054901123</t>
   </si>
   <si>
     <t xml:space="preserve">9.18387222290039</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15505218505859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1518497467041</t>
+    <t xml:space="preserve">9.15505123138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15184879302979</t>
   </si>
   <si>
     <t xml:space="preserve">9.23510551452637</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16465854644775</t>
+    <t xml:space="preserve">9.16465950012207</t>
   </si>
   <si>
     <t xml:space="preserve">9.1262321472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26072311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25432014465332</t>
+    <t xml:space="preserve">9.26072216033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.254319190979</t>
   </si>
   <si>
     <t xml:space="preserve">9.20628643035889</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">9.20948886871338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22550010681152</t>
+    <t xml:space="preserve">9.22549915313721</t>
   </si>
   <si>
     <t xml:space="preserve">9.10701847076416</t>
@@ -1697,49 +1697,49 @@
     <t xml:space="preserve">8.92769622802734</t>
   </si>
   <si>
-    <t xml:space="preserve">8.76758766174316</t>
+    <t xml:space="preserve">8.76758670806885</t>
   </si>
   <si>
     <t xml:space="preserve">8.65871238708496</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68112754821777</t>
+    <t xml:space="preserve">8.68112850189209</t>
   </si>
   <si>
     <t xml:space="preserve">8.7259578704834</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61708641052246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7803955078125</t>
+    <t xml:space="preserve">8.61708450317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78039455413818</t>
   </si>
   <si>
     <t xml:space="preserve">8.82202434539795</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77719497680664</t>
+    <t xml:space="preserve">8.77719402313232</t>
   </si>
   <si>
     <t xml:space="preserve">8.78359794616699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95331382751465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97252750396729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9661226272583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86685562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86044979095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32568550109863</t>
+    <t xml:space="preserve">8.95331478118896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97252559661865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96612167358398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86685466766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86045074462891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32568454742432</t>
   </si>
   <si>
     <t xml:space="preserve">8.22321510314941</t>
@@ -1757,40 +1757,40 @@
     <t xml:space="preserve">8.40253734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14956569671631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.06630802154541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.07271099090576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77490901947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74929094314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67884349822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.8741774559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73007774353027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.53474521636963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.42266941070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25295305252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21772956848145</t>
+    <t xml:space="preserve">8.14956665039062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.06630706787109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.07271194458008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77490997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74929237365723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67884254455566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87417697906494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73007822036743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.53474569320679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.42266988754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25295209884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21772861480713</t>
   </si>
   <si>
     <t xml:space="preserve">7.08003520965576</t>
@@ -1799,67 +1799,67 @@
     <t xml:space="preserve">7.11205625534058</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84947633743286</t>
+    <t xml:space="preserve">6.84947729110718</t>
   </si>
   <si>
     <t xml:space="preserve">6.97115993499756</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0416088104248</t>
+    <t xml:space="preserve">7.04160833358765</t>
   </si>
   <si>
     <t xml:space="preserve">7.03520441055298</t>
   </si>
   <si>
-    <t xml:space="preserve">7.04801225662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9423394203186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95194721221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00958585739136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13126945495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.97436189651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83026456832886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95514869689941</t>
+    <t xml:space="preserve">7.04801177978516</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94234132766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9519476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00958633422852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13126993179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97436141967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.83026504516602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95515012741089</t>
   </si>
   <si>
     <t xml:space="preserve">6.80144453048706</t>
   </si>
   <si>
-    <t xml:space="preserve">6.76621961593628</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8590841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62852573394775</t>
+    <t xml:space="preserve">6.7662205696106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85908269882202</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62852621078491</t>
   </si>
   <si>
     <t xml:space="preserve">6.70537900924683</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74700689315796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86548900604248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1632924079895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09604692459106</t>
+    <t xml:space="preserve">6.7470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86548805236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16329097747803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09604644775391</t>
   </si>
   <si>
     <t xml:space="preserve">7.06722640991211</t>
@@ -1874,10 +1874,10 @@
     <t xml:space="preserve">7.05761909484863</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80464601516724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.89110612869263</t>
+    <t xml:space="preserve">6.80464553833008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.89110517501831</t>
   </si>
   <si>
     <t xml:space="preserve">6.71818733215332</t>
@@ -1886,13 +1886,13 @@
     <t xml:space="preserve">6.7374005317688</t>
   </si>
   <si>
-    <t xml:space="preserve">6.95835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01278829574585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88790321350098</t>
+    <t xml:space="preserve">6.95835065841675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01278924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88790225982666</t>
   </si>
   <si>
     <t xml:space="preserve">6.4588098526001</t>
@@ -1904,136 +1904,136 @@
     <t xml:space="preserve">6.15204238891602</t>
   </si>
   <si>
-    <t xml:space="preserve">6.15844535827637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96375131607056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10593032836914</t>
+    <t xml:space="preserve">6.15844440460205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96375274658203</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10592937469482</t>
   </si>
   <si>
     <t xml:space="preserve">6.10721063613892</t>
   </si>
   <si>
-    <t xml:space="preserve">6.39924907684326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6445369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63172769546509</t>
+    <t xml:space="preserve">6.39925003051758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.64453601837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6317286491394</t>
   </si>
   <si>
     <t xml:space="preserve">6.59010028839111</t>
   </si>
   <si>
-    <t xml:space="preserve">6.50043916702271</t>
+    <t xml:space="preserve">6.50043869018555</t>
   </si>
   <si>
     <t xml:space="preserve">6.60290861129761</t>
   </si>
   <si>
-    <t xml:space="preserve">6.59650373458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41718149185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52285480499268</t>
+    <t xml:space="preserve">6.59650421142578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41718101501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52285432815552</t>
   </si>
   <si>
     <t xml:space="preserve">6.42038440704346</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47802352905273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4460015296936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32624053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26731967926025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74380493164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09924840927124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30739068984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.19851446151733</t>
+    <t xml:space="preserve">6.47802305221558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44600200653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32624101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26732015609741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74380445480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09924745559692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3073902130127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.19851493835449</t>
   </si>
   <si>
     <t xml:space="preserve">7.08964109420776</t>
   </si>
   <si>
-    <t xml:space="preserve">7.1184606552124</t>
+    <t xml:space="preserve">7.11845970153809</t>
   </si>
   <si>
     <t xml:space="preserve">7.15368461608887</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15688610076904</t>
+    <t xml:space="preserve">7.1568865776062</t>
   </si>
   <si>
     <t xml:space="preserve">7.17930173873901</t>
   </si>
   <si>
-    <t xml:space="preserve">7.0448112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99357652664185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27216625213623</t>
+    <t xml:space="preserve">7.04481077194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99357557296753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27216672897339</t>
   </si>
   <si>
     <t xml:space="preserve">7.4482855796814</t>
   </si>
   <si>
-    <t xml:space="preserve">7.75889730453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57637357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72687578201294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83895349502563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82614421844482</t>
+    <t xml:space="preserve">7.75889778137207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5763726234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72687673568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83895206451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82614469528198</t>
   </si>
   <si>
     <t xml:space="preserve">7.84535646438599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.89979410171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91260242462158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98305082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88058185577393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91900825500488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23282241821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12074565887451</t>
+    <t xml:space="preserve">7.8997950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9126033782959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98304986953735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88058090209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91900777816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23282051086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1207447052002</t>
   </si>
   <si>
     <t xml:space="preserve">8.26164150238037</t>
@@ -2045,25 +2045,25 @@
     <t xml:space="preserve">8.46337890625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84764194488525</t>
+    <t xml:space="preserve">8.84764099121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.91168594360352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26392555236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33117198944092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53290939331055</t>
+    <t xml:space="preserve">9.2639274597168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3311710357666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53291034698486</t>
   </si>
   <si>
     <t xml:space="preserve">9.67700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51049423217773</t>
+    <t xml:space="preserve">9.51049327850342</t>
   </si>
   <si>
     <t xml:space="preserve">9.42083263397217</t>
@@ -2072,25 +2072,25 @@
     <t xml:space="preserve">9.32796955108643</t>
   </si>
   <si>
-    <t xml:space="preserve">9.40482330322266</t>
+    <t xml:space="preserve">9.40482234954834</t>
   </si>
   <si>
     <t xml:space="preserve">9.47847270965576</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55212116241455</t>
+    <t xml:space="preserve">9.55212306976318</t>
   </si>
   <si>
     <t xml:space="preserve">9.57133674621582</t>
   </si>
   <si>
-    <t xml:space="preserve">9.70262432098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77627658843994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81470203399658</t>
+    <t xml:space="preserve">9.7026252746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77627563476562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8147029876709</t>
   </si>
   <si>
     <t xml:space="preserve">10.083685874939</t>
@@ -2105,7 +2105,7 @@
     <t xml:space="preserve">10.2149753570557</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1957626342773</t>
+    <t xml:space="preserve">10.195761680603</t>
   </si>
   <si>
     <t xml:space="preserve">10.2694120407104</t>
@@ -2114,37 +2114,37 @@
     <t xml:space="preserve">10.2790193557739</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5608129501343</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8490085601807</t>
+    <t xml:space="preserve">10.56081199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8490076065063</t>
   </si>
   <si>
     <t xml:space="preserve">10.8682222366333</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8874340057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0155210494995</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0603504180908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2813034057617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2909116744995</t>
+    <t xml:space="preserve">10.887433052063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0155220031738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0603523254395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2813024520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2909107208252</t>
   </si>
   <si>
     <t xml:space="preserve">11.5118608474731</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5278730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.495849609375</t>
+    <t xml:space="preserve">11.5278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4958505630493</t>
   </si>
   <si>
     <t xml:space="preserve">11.377368927002</t>
@@ -2153,19 +2153,19 @@
     <t xml:space="preserve">11.3261337280273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4926471710205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8105821609497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.9899053573608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5992383956909</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0219259262085</t>
+    <t xml:space="preserve">11.4926481246948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8105812072754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.9899044036865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5992374420166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0219268798828</t>
   </si>
   <si>
     <t xml:space="preserve">11.1404075622559</t>
@@ -2174,28 +2174,28 @@
     <t xml:space="preserve">11.1141204833984</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7917680740356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7882652282715</t>
+    <t xml:space="preserve">10.7917671203613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7882642745972</t>
   </si>
   <si>
     <t xml:space="preserve">10.4203634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5780372619629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.399341583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4273700714111</t>
+    <t xml:space="preserve">10.5780363082886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3993406295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4273710250854</t>
   </si>
   <si>
     <t xml:space="preserve">10.2872180938721</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3888292312622</t>
+    <t xml:space="preserve">10.3888282775879</t>
   </si>
   <si>
     <t xml:space="preserve">10.423867225647</t>
@@ -2213,10 +2213,10 @@
     <t xml:space="preserve">10.4448890686035</t>
   </si>
   <si>
-    <t xml:space="preserve">10.507960319519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5149660110474</t>
+    <t xml:space="preserve">10.5079593658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5149669647217</t>
   </si>
   <si>
     <t xml:space="preserve">10.6305923461914</t>
@@ -2228,40 +2228,40 @@
     <t xml:space="preserve">11.1281356811523</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1877002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3523807525635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5731210708618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6151676177979</t>
+    <t xml:space="preserve">11.1876993179321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3523817062378</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5731191635132</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6151666641235</t>
   </si>
   <si>
     <t xml:space="preserve">11.7553195953369</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7342967987061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8429145812988</t>
+    <t xml:space="preserve">11.7342958450317</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8429136276245</t>
   </si>
   <si>
     <t xml:space="preserve">11.7097682952881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6291818618774</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8639392852783</t>
+    <t xml:space="preserve">11.6291809082031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8639373779297</t>
   </si>
   <si>
     <t xml:space="preserve">11.9059829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9199981689453</t>
+    <t xml:space="preserve">11.9200000762939</t>
   </si>
   <si>
     <t xml:space="preserve">12.0496397018433</t>
@@ -2273,22 +2273,22 @@
     <t xml:space="preserve">12.2248315811157</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2984094619751</t>
+    <t xml:space="preserve">12.2984104156494</t>
   </si>
   <si>
     <t xml:space="preserve">12.2143201828003</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3159303665161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2773895263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4175415039062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3684854507446</t>
+    <t xml:space="preserve">12.3159313201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2773885726929</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4175395965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3684883117676</t>
   </si>
   <si>
     <t xml:space="preserve">12.1267251968384</t>
@@ -2297,37 +2297,37 @@
     <t xml:space="preserve">12.0391292572021</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8464202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636568069458</t>
+    <t xml:space="preserve">11.8464183807373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636558532715</t>
   </si>
   <si>
     <t xml:space="preserve">12.140739440918</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1232194900513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.109206199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0321216583252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8779535293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760589599609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6887464523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4680070877075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4890279769897</t>
+    <t xml:space="preserve">12.1232204437256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1092052459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0321207046509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8779525756836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760599136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6887474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4680061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4890298843384</t>
   </si>
   <si>
     <t xml:space="preserve">11.4820213317871</t>
@@ -2339,13 +2339,13 @@
     <t xml:space="preserve">11.2472648620605</t>
   </si>
   <si>
-    <t xml:space="preserve">11.037036895752</t>
+    <t xml:space="preserve">11.0370359420776</t>
   </si>
   <si>
     <t xml:space="preserve">11.1001043319702</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7216930389404</t>
+    <t xml:space="preserve">10.7216920852661</t>
   </si>
   <si>
     <t xml:space="preserve">10.9284172058105</t>
@@ -2354,10 +2354,10 @@
     <t xml:space="preserve">11.1561651229858</t>
   </si>
   <si>
-    <t xml:space="preserve">11.496036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.446982383728</t>
+    <t xml:space="preserve">11.4960374832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4469833374023</t>
   </si>
   <si>
     <t xml:space="preserve">11.1841974258423</t>
@@ -2372,10 +2372,10 @@
     <t xml:space="preserve">11.061562538147</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4049377441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2297468185425</t>
+    <t xml:space="preserve">11.4049367904663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2297458648682</t>
   </si>
   <si>
     <t xml:space="preserve">11.4119443893433</t>
@@ -2387,7 +2387,7 @@
     <t xml:space="preserve">11.7903575897217</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8814573287964</t>
+    <t xml:space="preserve">11.8814563751221</t>
   </si>
   <si>
     <t xml:space="preserve">11.8288993835449</t>
@@ -2399,7 +2399,7 @@
     <t xml:space="preserve">11.6677236557007</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6712293624878</t>
+    <t xml:space="preserve">11.6712284088135</t>
   </si>
   <si>
     <t xml:space="preserve">11.8113803863525</t>
@@ -2408,37 +2408,37 @@
     <t xml:space="preserve">11.9970836639404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9410219192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9690523147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.06715965271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703800201416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2738857269287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1021995544434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0951900482178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9725551605225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0146017074585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0741672515869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.986572265625</t>
+    <t xml:space="preserve">11.9410228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.969051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0671586990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703819274902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2738847732544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.102198600769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0951910018921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9725561141968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0146026611328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0741662979126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9865713119507</t>
   </si>
   <si>
     <t xml:space="preserve">11.6011514663696</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">11.552098274231</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5485935211182</t>
+    <t xml:space="preserve">11.5485925674438</t>
   </si>
   <si>
     <t xml:space="preserve">11.5941429138184</t>
@@ -2459,7 +2459,7 @@
     <t xml:space="preserve">11.5380830764771</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6852426528931</t>
+    <t xml:space="preserve">11.6852416992188</t>
   </si>
   <si>
     <t xml:space="preserve">11.7693347930908</t>
@@ -2468,16 +2468,16 @@
     <t xml:space="preserve">11.7027616500854</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9480285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0846796035767</t>
+    <t xml:space="preserve">11.9480295181274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0846786499023</t>
   </si>
   <si>
     <t xml:space="preserve">12.2108144760132</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7539091110229</t>
+    <t xml:space="preserve">12.7539081573486</t>
   </si>
   <si>
     <t xml:space="preserve">12.9641370773315</t>
@@ -2495,46 +2495,46 @@
     <t xml:space="preserve">12.9886636734009</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1743669509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9080772399902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0412216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094049453735</t>
+    <t xml:space="preserve">13.1743650436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9080762863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.041223526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094058990479</t>
   </si>
   <si>
     <t xml:space="preserve">13.6649017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8996572494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007024765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.365665435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6389627456665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0173778533936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1365060806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5289325714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9493923187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181396484375</t>
+    <t xml:space="preserve">13.8996562957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007043838501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3656673431396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6389636993408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0173759460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1365079879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5289335250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9493913650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181415557861</t>
   </si>
   <si>
     <t xml:space="preserve">15.9213619232178</t>
@@ -2543,13 +2543,13 @@
     <t xml:space="preserve">16.1035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9914379119873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1245822906494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4118976593018</t>
+    <t xml:space="preserve">15.9914388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1245861053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4118995666504</t>
   </si>
   <si>
     <t xml:space="preserve">16.5940952301025</t>
@@ -2558,49 +2558,49 @@
     <t xml:space="preserve">16.5100040435791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2086734771729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0475006103516</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.886323928833</t>
+    <t xml:space="preserve">16.2086753845215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0474987030029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8863248825073</t>
   </si>
   <si>
     <t xml:space="preserve">15.486888885498</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8232536315918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7531766891479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251482009888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1575298309326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3817739486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2626428604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.297679901123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0804462432861</t>
+    <t xml:space="preserve">15.8232545852661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7531805038452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251462936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1575288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3817749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2626457214355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2976808547974</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0804452896118</t>
   </si>
   <si>
     <t xml:space="preserve">15.2836666107178</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2205982208252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0944623947144</t>
+    <t xml:space="preserve">15.2205991744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.09446144104</t>
   </si>
   <si>
     <t xml:space="preserve">15.0664291381836</t>
@@ -2612,49 +2612,49 @@
     <t xml:space="preserve">14.856201171875</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9122619628906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1715450286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8702163696289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721090316772</t>
+    <t xml:space="preserve">14.9122629165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1715459823608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8702154159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721080780029</t>
   </si>
   <si>
     <t xml:space="preserve">15.353741645813</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5029983520508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5800800323486</t>
+    <t xml:space="preserve">16.5029945373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5800819396973</t>
   </si>
   <si>
     <t xml:space="preserve">16.4189033508301</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7062168121338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8043231964111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.622127532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5660629272461</t>
+    <t xml:space="preserve">16.7062187194824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8043251037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6221256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5660648345947</t>
   </si>
   <si>
     <t xml:space="preserve">16.9865226745605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.00754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5380344390869</t>
+    <t xml:space="preserve">17.0075492858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5380363464355</t>
   </si>
   <si>
     <t xml:space="preserve">16.0545082092285</t>
@@ -2663,106 +2663,106 @@
     <t xml:space="preserve">16.3978824615479</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4959888458252</t>
+    <t xml:space="preserve">16.4959869384766</t>
   </si>
   <si>
     <t xml:space="preserve">16.0685253143311</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5499591827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5709810256958</t>
+    <t xml:space="preserve">15.5499563217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5709819793701</t>
   </si>
   <si>
     <t xml:space="preserve">16.0334854125977</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9423856735229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1666297912598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6431503295898</t>
+    <t xml:space="preserve">15.9423875808716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1666316986084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6431484222412</t>
   </si>
   <si>
     <t xml:space="preserve">16.3908748626709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7622814178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7833023071289</t>
+    <t xml:space="preserve">16.762279510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7833042144775</t>
   </si>
   <si>
     <t xml:space="preserve">16.6711807250977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272434234619</t>
+    <t xml:space="preserve">16.7272415161133</t>
   </si>
   <si>
     <t xml:space="preserve">16.9514865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6130275726318</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5198335647583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3516511917114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5478658676147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7910404205322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4546737670898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0272054672241</t>
+    <t xml:space="preserve">15.6130266189575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.519832611084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3516502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5478649139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7910385131836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4546718597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0272064208984</t>
   </si>
   <si>
     <t xml:space="preserve">12.9956712722778</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3474655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7202806472778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3327684402466</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.68806457519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81069850921631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.25149917602539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.51988124847412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.44421005249023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.0202465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70490264892578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77497959136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49817609786987</t>
+    <t xml:space="preserve">12.3474645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7202825546265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3327674865723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68806552886963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81069755554199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.25149726867676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.51988220214844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4442081451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.02024555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70490217208862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77497816085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49817705154419</t>
   </si>
   <si>
     <t xml:space="preserve">7.59978818893433</t>
@@ -2774,7 +2774,7 @@
     <t xml:space="preserve">9.06088066101074</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69507312774658</t>
+    <t xml:space="preserve">9.69507217407227</t>
   </si>
   <si>
     <t xml:space="preserve">9.05036926269531</t>
@@ -2786,13 +2786,13 @@
     <t xml:space="preserve">9.2360725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87517929077148</t>
+    <t xml:space="preserve">8.87517833709717</t>
   </si>
   <si>
     <t xml:space="preserve">9.07489585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68246936798096</t>
+    <t xml:space="preserve">8.68246746063232</t>
   </si>
   <si>
     <t xml:space="preserve">9.0223388671875</t>
@@ -2813,46 +2813,46 @@
     <t xml:space="preserve">9.29914093017578</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4463005065918</t>
+    <t xml:space="preserve">9.44630146026611</t>
   </si>
   <si>
     <t xml:space="preserve">9.51637840270996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58995723724365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25359058380127</t>
+    <t xml:space="preserve">9.58995914459229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25359153747559</t>
   </si>
   <si>
     <t xml:space="preserve">9.33417892456055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49535465240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47433280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3713102340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8162956237793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2122278213501</t>
+    <t xml:space="preserve">9.49535369873047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47433185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3713111877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.816294670105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2122268676758</t>
   </si>
   <si>
     <t xml:space="preserve">10.8793640136719</t>
   </si>
   <si>
-    <t xml:space="preserve">10.760232925415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8618440628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5324850082397</t>
+    <t xml:space="preserve">10.7602338790894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8618450164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5324859619141</t>
   </si>
   <si>
     <t xml:space="preserve">10.6025629043579</t>
@@ -2867,7 +2867,7 @@
     <t xml:space="preserve">10.4133548736572</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0058336257935</t>
+    <t xml:space="preserve">11.0058355331421</t>
   </si>
   <si>
     <t xml:space="preserve">10.4649333953857</t>
@@ -2888,10 +2888,10 @@
     <t xml:space="preserve">10.9757843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9720277786255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.358922958374</t>
+    <t xml:space="preserve">10.9720287322998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3589239120483</t>
   </si>
   <si>
     <t xml:space="preserve">11.1936473846436</t>
@@ -2900,10 +2900,10 @@
     <t xml:space="preserve">11.3251161575317</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5204420089722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7984056472778</t>
+    <t xml:space="preserve">11.5204429626465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7984046936035</t>
   </si>
   <si>
     <t xml:space="preserve">12.0913925170898</t>
@@ -2912,13 +2912,13 @@
     <t xml:space="preserve">12.6923952102661</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9966497421265</t>
+    <t xml:space="preserve">12.9966506958008</t>
   </si>
   <si>
     <t xml:space="preserve">12.4407243728638</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3956499099731</t>
+    <t xml:space="preserve">12.3956508636475</t>
   </si>
   <si>
     <t xml:space="preserve">11.6481552124023</t>
@@ -2930,46 +2930,46 @@
     <t xml:space="preserve">11.5166854858398</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7721118927002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6669368743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5091733932495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7157669067383</t>
+    <t xml:space="preserve">11.7721109390259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6669359207153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5091724395752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7157678604126</t>
   </si>
   <si>
     <t xml:space="preserve">11.5730295181274</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8284549713135</t>
+    <t xml:space="preserve">11.8284540176392</t>
   </si>
   <si>
     <t xml:space="preserve">11.2687730789185</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4490728378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2011594772339</t>
+    <t xml:space="preserve">11.4490718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2011604309082</t>
   </si>
   <si>
     <t xml:space="preserve">11.4791231155396</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4265356063843</t>
+    <t xml:space="preserve">11.4265365600586</t>
   </si>
   <si>
     <t xml:space="preserve">11.3664360046387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5429792404175</t>
+    <t xml:space="preserve">11.663179397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5429782867432</t>
   </si>
   <si>
     <t xml:space="preserve">11.7796239852905</t>
@@ -2978,28 +2978,28 @@
     <t xml:space="preserve">11.7608423233032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4753665924072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6706914901733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8585052490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8434810638428</t>
+    <t xml:space="preserve">11.4753656387329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6706924438477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8585042953491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8434820175171</t>
   </si>
   <si>
     <t xml:space="preserve">12.3580884933472</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3205251693726</t>
+    <t xml:space="preserve">12.3205242156982</t>
   </si>
   <si>
     <t xml:space="preserve">12.801326751709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6999082565308</t>
+    <t xml:space="preserve">12.6999073028564</t>
   </si>
   <si>
     <t xml:space="preserve">12.7337131500244</t>
@@ -3008,7 +3008,7 @@
     <t xml:space="preserve">12.8351316452026</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5684385299683</t>
+    <t xml:space="preserve">12.5684375762939</t>
   </si>
   <si>
     <t xml:space="preserve">12.6097564697266</t>
@@ -3029,7 +3029,7 @@
     <t xml:space="preserve">12.3693571090698</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3505754470825</t>
+    <t xml:space="preserve">12.3505744934082</t>
   </si>
   <si>
     <t xml:space="preserve">12.4745311737061</t>
@@ -3041,19 +3041,19 @@
     <t xml:space="preserve">12.470775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8276195526123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938146591187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6585884094238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5984878540039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4557495117188</t>
+    <t xml:space="preserve">12.8276205062866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938137054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6585893630981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5984888076782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4557504653931</t>
   </si>
   <si>
     <t xml:space="preserve">12.515851020813</t>
@@ -3062,7 +3062,7 @@
     <t xml:space="preserve">12.3468179702759</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2191066741943</t>
+    <t xml:space="preserve">12.2191047668457</t>
   </si>
   <si>
     <t xml:space="preserve">12.6661005020142</t>
@@ -3071,16 +3071,16 @@
     <t xml:space="preserve">12.6247825622559</t>
   </si>
   <si>
-    <t xml:space="preserve">12.508337020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3881368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1740303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0650987625122</t>
+    <t xml:space="preserve">12.5083379745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3881378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1740312576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0650997161865</t>
   </si>
   <si>
     <t xml:space="preserve">12.2641820907593</t>
@@ -3092,7 +3092,7 @@
     <t xml:space="preserve">12.1552495956421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8847980499268</t>
+    <t xml:space="preserve">11.8847999572754</t>
   </si>
   <si>
     <t xml:space="preserve">12.0688552856445</t>
@@ -3113,13 +3113,13 @@
     <t xml:space="preserve">12.6285381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4257020950317</t>
+    <t xml:space="preserve">12.4257001876831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8547487258911</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8322124481201</t>
+    <t xml:space="preserve">11.8322105407715</t>
   </si>
   <si>
     <t xml:space="preserve">11.8096742630005</t>
@@ -3128,25 +3128,25 @@
     <t xml:space="preserve">11.6181049346924</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3326301574707</t>
+    <t xml:space="preserve">11.3326292037964</t>
   </si>
   <si>
     <t xml:space="preserve">11.7645988464355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5993223190308</t>
+    <t xml:space="preserve">11.5993232727051</t>
   </si>
   <si>
     <t xml:space="preserve">11.5842990875244</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4640979766846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.362678527832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.712010383606</t>
+    <t xml:space="preserve">11.4640989303589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3626794815063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7120113372803</t>
   </si>
   <si>
     <t xml:space="preserve">11.8772878646851</t>
@@ -3161,7 +3161,7 @@
     <t xml:space="preserve">12.200325012207</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2904758453369</t>
+    <t xml:space="preserve">12.2904748916626</t>
   </si>
   <si>
     <t xml:space="preserve">12.1139307022095</t>
@@ -3173,43 +3173,43 @@
     <t xml:space="preserve">11.944899559021</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0989046096802</t>
+    <t xml:space="preserve">12.0989055633545</t>
   </si>
   <si>
     <t xml:space="preserve">12.1514930725098</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0801239013672</t>
+    <t xml:space="preserve">12.0801248550415</t>
   </si>
   <si>
     <t xml:space="preserve">11.7007427215576</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5241985321045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8255338668823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6452331542969</t>
+    <t xml:space="preserve">11.5241994857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8255348205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6452341079712</t>
   </si>
   <si>
     <t xml:space="preserve">10.8893909454346</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2499904632568</t>
+    <t xml:space="preserve">11.2499923706055</t>
   </si>
   <si>
     <t xml:space="preserve">11.64439868927</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8209419250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0275373458862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8885555267334</t>
+    <t xml:space="preserve">11.8209428787231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0275363922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8885545730591</t>
   </si>
   <si>
     <t xml:space="preserve">12.5834636688232</t>
@@ -3224,31 +3224,31 @@
     <t xml:space="preserve">13.1393890380859</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2070016860962</t>
+    <t xml:space="preserve">13.2070026397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.5600900650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2370529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2595882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2220258712769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.672779083252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.357253074646</t>
+    <t xml:space="preserve">13.2370519638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2595891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2220268249512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6727781295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3572521209717</t>
   </si>
   <si>
     <t xml:space="preserve">13.379789352417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2746143341064</t>
+    <t xml:space="preserve">13.2746152877808</t>
   </si>
   <si>
     <t xml:space="preserve">13.5375518798828</t>
@@ -3257,10 +3257,10 @@
     <t xml:space="preserve">13.1882209777832</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2821273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2896404266357</t>
+    <t xml:space="preserve">13.2821264266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2896394729614</t>
   </si>
   <si>
     <t xml:space="preserve">13.2295398712158</t>
@@ -3269,100 +3269,100 @@
     <t xml:space="preserve">13.1619272232056</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9327955245972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1731948852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1919775009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1957340240479</t>
+    <t xml:space="preserve">12.9327945709229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1731958389282</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1919755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1957330703735</t>
   </si>
   <si>
     <t xml:space="preserve">13.0154333114624</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8238639831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3272018432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361333847046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4962339401245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4323759078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3497400283813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3384704589844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1994895935059</t>
+    <t xml:space="preserve">12.82386302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.327202796936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361324310303</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4962329864502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4323768615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.349739074707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3384695053101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1994886398315</t>
   </si>
   <si>
     <t xml:space="preserve">13.4135961532593</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4248647689819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3985691070557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3910579681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6802883148193</t>
+    <t xml:space="preserve">13.4248657226562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.39857006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.391058921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.680290222168</t>
   </si>
   <si>
     <t xml:space="preserve">14.2099227905273</t>
   </si>
   <si>
-    <t xml:space="preserve">13.958251953125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8305406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943967819214</t>
+    <t xml:space="preserve">13.9582529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8305397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.89439868927</t>
   </si>
   <si>
     <t xml:space="preserve">13.8380527496338</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9319581985474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7328786849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4398908615112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4060840606689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.109338760376</t>
+    <t xml:space="preserve">13.9319591522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7328796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4398899078369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4060831069946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1093397140503</t>
   </si>
   <si>
     <t xml:space="preserve">13.3009090423584</t>
   </si>
   <si>
-    <t xml:space="preserve">13.0417261123657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887208938599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5676012039185</t>
+    <t xml:space="preserve">13.04172706604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887218475342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5676031112671</t>
   </si>
   <si>
     <t xml:space="preserve">13.7216091156006</t>
@@ -3380,10 +3380,10 @@
     <t xml:space="preserve">15.092643737793</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0250301361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1978158950806</t>
+    <t xml:space="preserve">15.0250291824341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1978168487549</t>
   </si>
   <si>
     <t xml:space="preserve">14.8447294235229</t>
@@ -3392,34 +3392,34 @@
     <t xml:space="preserve">14.7207736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9198551177979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8221912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.532958984375</t>
+    <t xml:space="preserve">14.9198560714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8221921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5329599380493</t>
   </si>
   <si>
     <t xml:space="preserve">14.6005725860596</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4315423965454</t>
+    <t xml:space="preserve">14.4315404891968</t>
   </si>
   <si>
     <t xml:space="preserve">14.2812919616699</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9499053955078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7846307754517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7095031738281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6644296646118</t>
+    <t xml:space="preserve">14.9499063491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.784628868103</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7095060348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6644287109375</t>
   </si>
   <si>
     <t xml:space="preserve">14.4240293502808</t>
@@ -3428,13 +3428,13 @@
     <t xml:space="preserve">14.7958993911743</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7620916366577</t>
+    <t xml:space="preserve">14.7620935440063</t>
   </si>
   <si>
     <t xml:space="preserve">14.9123420715332</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6606721878052</t>
+    <t xml:space="preserve">14.6606740951538</t>
   </si>
   <si>
     <t xml:space="preserve">14.4090042114258</t>
@@ -3446,37 +3446,37 @@
     <t xml:space="preserve">14.1197729110718</t>
   </si>
   <si>
-    <t xml:space="preserve">14.202410697937</t>
+    <t xml:space="preserve">14.2024097442627</t>
   </si>
   <si>
     <t xml:space="preserve">14.2775344848633</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3226099014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202718734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714418411255</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2925605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4653482437134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7470664978027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5930595397949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8898057937622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8484859466553</t>
+    <t xml:space="preserve">14.3226108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202728271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2925596237183</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4653472900391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7470684051514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5930604934692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8898048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8484869003296</t>
   </si>
   <si>
     <t xml:space="preserve">15.2504043579102</t>
@@ -3488,49 +3488,49 @@
     <t xml:space="preserve">15.1151809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0701065063477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7245311737061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7508249282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.814679145813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8184375762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9837112426758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0175180435181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7921438217163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9611749649048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1602554321289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724426269531</t>
+    <t xml:space="preserve">15.070107460022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827917098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7245292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7508220672607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8146810531616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.818434715271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9837121963501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0175189971924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7921419143677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9611740112305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1602563858032</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724435806274</t>
   </si>
   <si>
     <t xml:space="preserve">15.085129737854</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1377182006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3555822372437</t>
+    <t xml:space="preserve">15.1377201080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3555812835693</t>
   </si>
   <si>
     <t xml:space="preserve">15.2579183578491</t>
@@ -3539,19 +3539,19 @@
     <t xml:space="preserve">15.2804565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2729415893555</t>
+    <t xml:space="preserve">15.2729434967041</t>
   </si>
   <si>
     <t xml:space="preserve">15.7462310791016</t>
   </si>
   <si>
-    <t xml:space="preserve">15.86643409729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8438949584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6410579681396</t>
+    <t xml:space="preserve">15.8664321899414</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8438968658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.641056060791</t>
   </si>
   <si>
     <t xml:space="preserve">15.7086696624756</t>
@@ -3563,16 +3563,16 @@
     <t xml:space="preserve">16.1603355407715</t>
   </si>
   <si>
-    <t xml:space="preserve">16.081428527832</t>
+    <t xml:space="preserve">16.0814266204834</t>
   </si>
   <si>
     <t xml:space="preserve">15.8841571807861</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8999395370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9551763534546</t>
+    <t xml:space="preserve">15.899941444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.955174446106</t>
   </si>
   <si>
     <t xml:space="preserve">16.0419731140137</t>
@@ -3581,10 +3581,10 @@
     <t xml:space="preserve">16.0025196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0972080230713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1445541381836</t>
+    <t xml:space="preserve">16.0972099304199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.144552230835</t>
   </si>
   <si>
     <t xml:space="preserve">16.4601879119873</t>
@@ -3596,34 +3596,34 @@
     <t xml:space="preserve">16.4128398895264</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3260440826416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3497142791748</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.99462890625</t>
+    <t xml:space="preserve">16.326042175293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3497123718262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9946298599243</t>
   </si>
   <si>
     <t xml:space="preserve">16.1208820343018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1918983459473</t>
+    <t xml:space="preserve">16.1919002532959</t>
   </si>
   <si>
     <t xml:space="preserve">16.0183010101318</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9472846984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8762683868408</t>
+    <t xml:space="preserve">15.9472827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8762674331665</t>
   </si>
   <si>
     <t xml:space="preserve">16.2392444610596</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2471332550049</t>
+    <t xml:space="preserve">16.2471351623535</t>
   </si>
   <si>
     <t xml:space="preserve">16.5312023162842</t>
@@ -3632,7 +3632,7 @@
     <t xml:space="preserve">16.1287727355957</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2155704498291</t>
+    <t xml:space="preserve">16.2155723571777</t>
   </si>
   <si>
     <t xml:space="preserve">16.3023700714111</t>
@@ -3644,7 +3644,7 @@
     <t xml:space="preserve">16.5075302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4838562011719</t>
+    <t xml:space="preserve">16.4838581085205</t>
   </si>
   <si>
     <t xml:space="preserve">16.4444046020508</t>
@@ -3659,22 +3659,22 @@
     <t xml:space="preserve">16.8073806762695</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1624660491943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5254402160645</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.3281707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1940288543701</t>
+    <t xml:space="preserve">17.1624641418457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5254421234131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.3281726837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1940307617188</t>
   </si>
   <si>
     <t xml:space="preserve">17.2492656707764</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1387920379639</t>
+    <t xml:space="preserve">17.1387939453125</t>
   </si>
   <si>
     <t xml:space="preserve">17.4702072143555</t>
@@ -3683,28 +3683,28 @@
     <t xml:space="preserve">17.4938793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2808265686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4070796966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.5727863311768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9042015075684</t>
+    <t xml:space="preserve">17.2808284759521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4070816040039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.5727882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9041996002197</t>
   </si>
   <si>
     <t xml:space="preserve">17.9120922088623</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1093635559082</t>
+    <t xml:space="preserve">18.1093597412109</t>
   </si>
   <si>
     <t xml:space="preserve">18.1172504425049</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2592849731445</t>
+    <t xml:space="preserve">18.2592868804932</t>
   </si>
   <si>
     <t xml:space="preserve">18.3224105834961</t>
@@ -3713,7 +3713,7 @@
     <t xml:space="preserve">18.2435035705566</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4644451141357</t>
+    <t xml:space="preserve">18.4644470214844</t>
   </si>
   <si>
     <t xml:space="preserve">18.251392364502</t>
@@ -3722,13 +3722,13 @@
     <t xml:space="preserve">18.2829570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4249935150146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3539752960205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4407730102539</t>
+    <t xml:space="preserve">18.424991607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3539772033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4407749176025</t>
   </si>
   <si>
     <t xml:space="preserve">18.5906982421875</t>
@@ -3737,13 +3737,13 @@
     <t xml:space="preserve">18.6696071624756</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7485160827637</t>
+    <t xml:space="preserve">18.748514175415</t>
   </si>
   <si>
     <t xml:space="preserve">18.7642974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8037490844727</t>
+    <t xml:space="preserve">18.8037509918213</t>
   </si>
   <si>
     <t xml:space="preserve">18.7011699676514</t>
@@ -3755,16 +3755,16 @@
     <t xml:space="preserve">18.7406234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6459331512451</t>
+    <t xml:space="preserve">18.6459350585938</t>
   </si>
   <si>
     <t xml:space="preserve">18.7169513702393</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5749187469482</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8432025909424</t>
+    <t xml:space="preserve">18.5749168395996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.843204498291</t>
   </si>
   <si>
     <t xml:space="preserve">18.8984413146973</t>
@@ -3773,7 +3773,7 @@
     <t xml:space="preserve">18.9536743164062</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1903991699219</t>
+    <t xml:space="preserve">19.1903972625732</t>
   </si>
   <si>
     <t xml:space="preserve">19.0878200531006</t>
@@ -3791,28 +3791,28 @@
     <t xml:space="preserve">19.2614154815674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1430530548096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7327327728271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5985889434814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7721881866455</t>
+    <t xml:space="preserve">19.1430549621582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7327346801758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5985908508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7721862792969</t>
   </si>
   <si>
     <t xml:space="preserve">18.6538238525391</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4013195037842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.6222610473633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2356147766113</t>
+    <t xml:space="preserve">18.4013214111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6222629547119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2356128692627</t>
   </si>
   <si>
     <t xml:space="preserve">18.1409244537354</t>
@@ -3821,43 +3821,43 @@
     <t xml:space="preserve">18.43288230896</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6380424499512</t>
+    <t xml:space="preserve">18.6380443572998</t>
   </si>
   <si>
     <t xml:space="preserve">18.8353137969971</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7090606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5375938415527</t>
+    <t xml:space="preserve">18.7090587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5375919342041</t>
   </si>
   <si>
     <t xml:space="preserve">19.403450012207</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5297012329102</t>
+    <t xml:space="preserve">19.5297031402588</t>
   </si>
   <si>
     <t xml:space="preserve">19.6007194519043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8374423980713</t>
+    <t xml:space="preserve">19.8374443054199</t>
   </si>
   <si>
     <t xml:space="preserve">19.6322822570801</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6954078674316</t>
+    <t xml:space="preserve">19.6954097747803</t>
   </si>
   <si>
     <t xml:space="preserve">19.640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9952602386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.066276550293</t>
+    <t xml:space="preserve">19.9952583312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0662746429443</t>
   </si>
   <si>
     <t xml:space="preserve">20.1057300567627</t>
@@ -3866,19 +3866,19 @@
     <t xml:space="preserve">20.0504951477051</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0741691589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0189323425293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2398738861084</t>
+    <t xml:space="preserve">20.0741672515869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0189342498779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.239875793457</t>
   </si>
   <si>
     <t xml:space="preserve">20.9027004241943</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1788768768311</t>
+    <t xml:space="preserve">21.1788787841797</t>
   </si>
   <si>
     <t xml:space="preserve">21.1946582794189</t>
@@ -3887,16 +3887,16 @@
     <t xml:space="preserve">20.9421539306641</t>
   </si>
   <si>
-    <t xml:space="preserve">20.9816074371338</t>
+    <t xml:space="preserve">20.9816093444824</t>
   </si>
   <si>
     <t xml:space="preserve">20.6659774780273</t>
   </si>
   <si>
-    <t xml:space="preserve">20.2161998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1372947692871</t>
+    <t xml:space="preserve">20.2162017822266</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1372928619385</t>
   </si>
   <si>
     <t xml:space="preserve">20.0820579528809</t>
@@ -3905,13 +3905,13 @@
     <t xml:space="preserve">19.1035995483398</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3166522979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3324317932129</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4744701385498</t>
+    <t xml:space="preserve">19.316650390625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3324337005615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4744682312012</t>
   </si>
   <si>
     <t xml:space="preserve">19.3087596893311</t>
@@ -3929,28 +3929,28 @@
     <t xml:space="preserve">19.1272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0246925354004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8116416931152</t>
+    <t xml:space="preserve">19.024694442749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8116397857666</t>
   </si>
   <si>
     <t xml:space="preserve">19.0168018341064</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7248401641846</t>
+    <t xml:space="preserve">18.7248420715332</t>
   </si>
   <si>
     <t xml:space="preserve">18.9142208099365</t>
   </si>
   <si>
-    <t xml:space="preserve">19.16672706604</t>
+    <t xml:space="preserve">19.1667289733887</t>
   </si>
   <si>
     <t xml:space="preserve">19.3561058044434</t>
   </si>
   <si>
-    <t xml:space="preserve">19.411340713501</t>
+    <t xml:space="preserve">19.4113426208496</t>
   </si>
   <si>
     <t xml:space="preserve">19.7269725799561</t>
@@ -3962,7 +3962,7 @@
     <t xml:space="preserve">19.9479160308838</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3403224945068</t>
+    <t xml:space="preserve">19.3403244018555</t>
   </si>
   <si>
     <t xml:space="preserve">19.5770454406738</t>
@@ -3974,10 +3974,10 @@
     <t xml:space="preserve">20.0268211364746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8711395263672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9342651367188</t>
+    <t xml:space="preserve">20.8711376190186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9342632293701</t>
   </si>
   <si>
     <t xml:space="preserve">20.5791778564453</t>
@@ -3986,7 +3986,7 @@
     <t xml:space="preserve">20.6817569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3187789916992</t>
+    <t xml:space="preserve">20.3187808990479</t>
   </si>
   <si>
     <t xml:space="preserve">19.8847885131836</t>
@@ -3998,19 +3998,19 @@
     <t xml:space="preserve">18.2671756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3934307098389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.032585144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8747692108154</t>
+    <t xml:space="preserve">18.3934288024902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0325832366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8747673034668</t>
   </si>
   <si>
     <t xml:space="preserve">18.3303031921387</t>
   </si>
   <si>
-    <t xml:space="preserve">18.7958602905273</t>
+    <t xml:space="preserve">18.7958583831787</t>
   </si>
   <si>
     <t xml:space="preserve">18.3697566986084</t>
@@ -4019,25 +4019,25 @@
     <t xml:space="preserve">18.3145198822021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8095092773438</t>
+    <t xml:space="preserve">17.8095111846924</t>
   </si>
   <si>
     <t xml:space="preserve">17.7463836669922</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9278697967529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.641674041748</t>
+    <t xml:space="preserve">17.9278717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416759490967</t>
   </si>
   <si>
     <t xml:space="preserve">17.1782474517822</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8862857818604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6337833404541</t>
+    <t xml:space="preserve">16.8862895965576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6337814331055</t>
   </si>
   <si>
     <t xml:space="preserve">15.4028186798096</t>
@@ -4046,7 +4046,7 @@
     <t xml:space="preserve">15.4501657485962</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6632165908813</t>
+    <t xml:space="preserve">15.663215637207</t>
   </si>
   <si>
     <t xml:space="preserve">17.0756664276123</t>
@@ -4055,40 +4055,40 @@
     <t xml:space="preserve">15.1897687911987</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5093460083008</t>
+    <t xml:space="preserve">15.5093441009521</t>
   </si>
   <si>
     <t xml:space="preserve">15.8525953292847</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0441036224365</t>
+    <t xml:space="preserve">17.0441055297852</t>
   </si>
   <si>
     <t xml:space="preserve">16.7915992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4759674072266</t>
+    <t xml:space="preserve">16.4759654998779</t>
   </si>
   <si>
     <t xml:space="preserve">16.8152694702148</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7837066650391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4286231994629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.744255065918</t>
+    <t xml:space="preserve">16.7837085723877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4286212921143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7442531585693</t>
   </si>
   <si>
     <t xml:space="preserve">17.2413730621338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9415225982666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6732368469238</t>
+    <t xml:space="preserve">16.9415245056152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6732349395752</t>
   </si>
   <si>
     <t xml:space="preserve">16.7600364685059</t>
@@ -4103,13 +4103,13 @@
     <t xml:space="preserve">15.4107103347778</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7815780639648</t>
+    <t xml:space="preserve">15.7815771102905</t>
   </si>
   <si>
     <t xml:space="preserve">15.9157209396362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8920469284058</t>
+    <t xml:space="preserve">15.8920478820801</t>
   </si>
   <si>
     <t xml:space="preserve">15.8683776855469</t>
@@ -4121,22 +4121,22 @@
     <t xml:space="preserve">15.7973604202271</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7539587020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8289232254028</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0893173217773</t>
+    <t xml:space="preserve">15.7539596557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8289241790771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.089319229126</t>
   </si>
   <si>
     <t xml:space="preserve">16.0735378265381</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1761169433594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9236116409302</t>
+    <t xml:space="preserve">16.176118850708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9236125946045</t>
   </si>
   <si>
     <t xml:space="preserve">15.6395444869995</t>
@@ -4145,25 +4145,25 @@
     <t xml:space="preserve">15.5132913589478</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9964447021484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1660947799683</t>
+    <t xml:space="preserve">14.9964437484741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1660957336426</t>
   </si>
   <si>
     <t xml:space="preserve">15.6868877410889</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7381782531738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7657957077026</t>
+    <t xml:space="preserve">15.7381801605225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.765796661377</t>
   </si>
   <si>
     <t xml:space="preserve">16.0261917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8052492141724</t>
+    <t xml:space="preserve">15.8052501678467</t>
   </si>
   <si>
     <t xml:space="preserve">16.4583625793457</t>
@@ -4181,7 +4181,7 @@
     <t xml:space="preserve">16.7703304290771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305286407471</t>
+    <t xml:space="preserve">16.9305305480957</t>
   </si>
   <si>
     <t xml:space="preserve">16.8209209442139</t>
@@ -4211,22 +4211,22 @@
     <t xml:space="preserve">14.7298974990845</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4390096664429</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.628719329834</t>
+    <t xml:space="preserve">14.4390106201172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6287212371826</t>
   </si>
   <si>
     <t xml:space="preserve">14.9828443527222</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2830257415771</t>
+    <t xml:space="preserve">14.2830266952515</t>
   </si>
   <si>
     <t xml:space="preserve">14.3715581893921</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4432258605957</t>
+    <t xml:space="preserve">14.4432249069214</t>
   </si>
   <si>
     <t xml:space="preserve">14.5064630508423</t>
@@ -4235,13 +4235,13 @@
     <t xml:space="preserve">14.2197895050049</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6750946044922</t>
+    <t xml:space="preserve">14.6750926971436</t>
   </si>
   <si>
     <t xml:space="preserve">14.5191087722778</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4811668395996</t>
+    <t xml:space="preserve">14.4811658859253</t>
   </si>
   <si>
     <t xml:space="preserve">14.2745952606201</t>
@@ -4259,43 +4259,43 @@
     <t xml:space="preserve">13.3724212646484</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7771348953247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1523380279541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3420476913452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1354732513428</t>
+    <t xml:space="preserve">13.7771339416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1523370742798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3420486450195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1354742050171</t>
   </si>
   <si>
     <t xml:space="preserve">14.3546943664551</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1987104415894</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6211519241333</t>
+    <t xml:space="preserve">14.1987113952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.621150970459</t>
   </si>
   <si>
     <t xml:space="preserve">13.6801719665527</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8108596801758</t>
+    <t xml:space="preserve">13.8108606338501</t>
   </si>
   <si>
     <t xml:space="preserve">14.2493000030518</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6928195953369</t>
+    <t xml:space="preserve">13.6928186416626</t>
   </si>
   <si>
     <t xml:space="preserve">13.7602710723877</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7939987182617</t>
+    <t xml:space="preserve">13.7939977645874</t>
   </si>
   <si>
     <t xml:space="preserve">13.4609518051147</t>
@@ -4322,7 +4322,7 @@
     <t xml:space="preserve">14.2577314376831</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2956743240356</t>
+    <t xml:space="preserve">14.2956733703613</t>
   </si>
   <si>
     <t xml:space="preserve">14.1944942474365</t>
@@ -4331,22 +4331,22 @@
     <t xml:space="preserve">14.4600887298584</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5022468566895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5654821395874</t>
+    <t xml:space="preserve">14.5022459030151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5654830932617</t>
   </si>
   <si>
     <t xml:space="preserve">14.6371517181396</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3757724761963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4643058776855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9794912338257</t>
+    <t xml:space="preserve">14.3757734298706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4643068313599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9794902801514</t>
   </si>
   <si>
     <t xml:space="preserve">13.7687034606934</t>
@@ -4358,25 +4358,25 @@
     <t xml:space="preserve">13.9415493011475</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8530178070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4651670455933</t>
+    <t xml:space="preserve">13.8530187606812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4651679992676</t>
   </si>
   <si>
     <t xml:space="preserve">13.4483041763306</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6380128860474</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.435658454895</t>
+    <t xml:space="preserve">13.6380138397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4356575012207</t>
   </si>
   <si>
     <t xml:space="preserve">13.1447687149048</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6295824050903</t>
+    <t xml:space="preserve">13.6295833587646</t>
   </si>
   <si>
     <t xml:space="preserve">13.4272260665894</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">13.4946775436401</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5199728012085</t>
+    <t xml:space="preserve">13.5199718475342</t>
   </si>
   <si>
     <t xml:space="preserve">14.1692018508911</t>
@@ -4394,19 +4394,19 @@
     <t xml:space="preserve">14.0806703567505</t>
   </si>
   <si>
-    <t xml:space="preserve">14.0722379684448</t>
+    <t xml:space="preserve">14.0722389221191</t>
   </si>
   <si>
     <t xml:space="preserve">13.9162540435791</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7644872665405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8572340011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4735984802246</t>
+    <t xml:space="preserve">13.7644882202148</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8572330474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4735994338989</t>
   </si>
   <si>
     <t xml:space="preserve">13.1321210861206</t>
@@ -4427,13 +4427,13 @@
     <t xml:space="preserve">12.0065107345581</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3985776901245</t>
+    <t xml:space="preserve">12.3985767364502</t>
   </si>
   <si>
     <t xml:space="preserve">12.6009340286255</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1532011032104</t>
+    <t xml:space="preserve">13.1532001495361</t>
   </si>
   <si>
     <t xml:space="preserve">12.9044704437256</t>
@@ -4442,7 +4442,7 @@
     <t xml:space="preserve">12.7231922149658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5039710998535</t>
+    <t xml:space="preserve">12.5039720535278</t>
   </si>
   <si>
     <t xml:space="preserve">12.5503454208374</t>
@@ -4460,7 +4460,7 @@
     <t xml:space="preserve">12.5292663574219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7948608398438</t>
+    <t xml:space="preserve">12.7948598861694</t>
   </si>
   <si>
     <t xml:space="preserve">12.8791751861572</t>
@@ -4478,25 +4478,25 @@
     <t xml:space="preserve">13.3007526397705</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6843872070312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5326194763184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7897806167603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7434072494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9963541030884</t>
+    <t xml:space="preserve">13.6843862533569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.532618522644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7897815704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.743408203125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9963550567627</t>
   </si>
   <si>
     <t xml:space="preserve">14.1101808547974</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3462619781494</t>
+    <t xml:space="preserve">14.3462629318237</t>
   </si>
   <si>
     <t xml:space="preserve">14.7214660644531</t>
@@ -4505,13 +4505,13 @@
     <t xml:space="preserve">14.9449024200439</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0292177200317</t>
+    <t xml:space="preserve">15.0292186737061</t>
   </si>
   <si>
     <t xml:space="preserve">16.1885547637939</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8588638305664</t>
+    <t xml:space="preserve">16.8588619232178</t>
   </si>
   <si>
     <t xml:space="preserve">16.6860160827637</t>
@@ -4523,16 +4523,16 @@
     <t xml:space="preserve">16.8293514251709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7998390197754</t>
+    <t xml:space="preserve">16.799840927124</t>
   </si>
   <si>
     <t xml:space="preserve">16.3740482330322</t>
   </si>
   <si>
-    <t xml:space="preserve">16.441499710083</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4035568237305</t>
+    <t xml:space="preserve">16.4415016174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4035587310791</t>
   </si>
   <si>
     <t xml:space="preserve">16.3909111022949</t>
@@ -4544,10 +4544,10 @@
     <t xml:space="preserve">16.2349262237549</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3993453979492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3023796081543</t>
+    <t xml:space="preserve">16.3993434906006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3023777008057</t>
   </si>
   <si>
     <t xml:space="preserve">16.6059150695801</t>
@@ -4559,7 +4559,7 @@
     <t xml:space="preserve">16.5089530944824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7155265808105</t>
+    <t xml:space="preserve">16.7155246734619</t>
   </si>
   <si>
     <t xml:space="preserve">16.9389610290527</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">16.7618980407715</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0570011138916</t>
+    <t xml:space="preserve">17.0570049285889</t>
   </si>
   <si>
     <t xml:space="preserve">16.9558258056641</t>
@@ -4577,13 +4577,13 @@
     <t xml:space="preserve">16.2855167388916</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2677917480469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2593593597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2340641021729</t>
+    <t xml:space="preserve">17.2677898406982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2593612670898</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2340660095215</t>
   </si>
   <si>
     <t xml:space="preserve">17.5375995635986</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">17.3774013519287</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4617176055908</t>
+    <t xml:space="preserve">17.4617156982422</t>
   </si>
   <si>
     <t xml:space="preserve">17.6893692016602</t>
@@ -4604,31 +4604,31 @@
     <t xml:space="preserve">17.8579998016357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6472110748291</t>
+    <t xml:space="preserve">17.6472129821777</t>
   </si>
   <si>
     <t xml:space="preserve">17.8664302825928</t>
   </si>
   <si>
-    <t xml:space="preserve">18.0434913635254</t>
+    <t xml:space="preserve">18.043493270874</t>
   </si>
   <si>
     <t xml:space="preserve">18.2542819976807</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9760398864746</t>
+    <t xml:space="preserve">17.9760417938232</t>
   </si>
   <si>
     <t xml:space="preserve">17.9676074981689</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3807544708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3891849517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8697814941406</t>
+    <t xml:space="preserve">18.3807525634766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3891868591309</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8697834014893</t>
   </si>
   <si>
     <t xml:space="preserve">18.9035091400146</t>
@@ -4649,13 +4649,13 @@
     <t xml:space="preserve">18.8444900512695</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2239093780518</t>
+    <t xml:space="preserve">19.2239074707031</t>
   </si>
   <si>
     <t xml:space="preserve">19.375675201416</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3588123321533</t>
+    <t xml:space="preserve">19.3588104248047</t>
   </si>
   <si>
     <t xml:space="preserve">19.3419494628906</t>
@@ -4664,10 +4664,10 @@
     <t xml:space="preserve">19.3841075897217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4431285858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3250865936279</t>
+    <t xml:space="preserve">19.4431266784668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3250885009766</t>
   </si>
   <si>
     <t xml:space="preserve">19.2913589477539</t>
@@ -4685,10 +4685,10 @@
     <t xml:space="preserve">19.9405899047852</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9321556091309</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8900012969971</t>
+    <t xml:space="preserve">19.9321575164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8899993896484</t>
   </si>
   <si>
     <t xml:space="preserve">19.8309783935547</t>
@@ -4697,10 +4697,10 @@
     <t xml:space="preserve">19.1564540863037</t>
   </si>
   <si>
-    <t xml:space="preserve">19.5358734130859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0637092590332</t>
+    <t xml:space="preserve">19.5358753204346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0637111663818</t>
   </si>
   <si>
     <t xml:space="preserve">19.0890026092529</t>
@@ -4709,7 +4709,7 @@
     <t xml:space="preserve">19.2070465087891</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0552787780762</t>
+    <t xml:space="preserve">19.0552768707275</t>
   </si>
   <si>
     <t xml:space="preserve">18.9878253936768</t>
@@ -4718,16 +4718,16 @@
     <t xml:space="preserve">18.6168365478516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9456672668457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9793930053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1058654785156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.895076751709</t>
+    <t xml:space="preserve">18.9456653594971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9793949127197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1058673858643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8950786590576</t>
   </si>
   <si>
     <t xml:space="preserve">18.8023319244385</t>
@@ -4739,16 +4739,16 @@
     <t xml:space="preserve">17.6134834289551</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7745475769043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9811172485352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.239143371582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0114917755127</t>
+    <t xml:space="preserve">16.7745456695557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9811191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2391452789307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0114936828613</t>
   </si>
   <si>
     <t xml:space="preserve">16.4667949676514</t>
@@ -4763,7 +4763,7 @@
     <t xml:space="preserve">16.1126708984375</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1337490081787</t>
+    <t xml:space="preserve">16.1337509155273</t>
   </si>
   <si>
     <t xml:space="preserve">16.3487529754639</t>
@@ -4775,22 +4775,22 @@
     <t xml:space="preserve">16.6101322174072</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5468940734863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3403205871582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5216007232666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7113094329834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1581802368164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.124454498291</t>
+    <t xml:space="preserve">16.546895980835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3403224945068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.521598815918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.711311340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.158182144165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1244564056396</t>
   </si>
   <si>
     <t xml:space="preserve">17.0232772827148</t>
@@ -4802,16 +4802,16 @@
     <t xml:space="preserve">17.2424983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1075916290283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.0148448944092</t>
+    <t xml:space="preserve">17.107593536377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.0148468017578</t>
   </si>
   <si>
     <t xml:space="preserve">17.0401401519775</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0654354095459</t>
+    <t xml:space="preserve">17.0654335021973</t>
   </si>
   <si>
     <t xml:space="preserve">16.8124885559082</t>
@@ -4820,13 +4820,13 @@
     <t xml:space="preserve">16.5806217193604</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9726867675781</t>
+    <t xml:space="preserve">16.9726886749268</t>
   </si>
   <si>
     <t xml:space="preserve">17.0822982788086</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8546447753906</t>
+    <t xml:space="preserve">16.8546466827393</t>
   </si>
   <si>
     <t xml:space="preserve">16.9895496368408</t>
@@ -4847,10 +4847,10 @@
     <t xml:space="preserve">17.3769779205322</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0168342590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8097515106201</t>
+    <t xml:space="preserve">17.0168323516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8097496032715</t>
   </si>
   <si>
     <t xml:space="preserve">17.2014083862305</t>
@@ -4859,28 +4859,28 @@
     <t xml:space="preserve">17.1743984222412</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0753574371338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7242183685303</t>
+    <t xml:space="preserve">17.0753593444824</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7242164611816</t>
   </si>
   <si>
     <t xml:space="preserve">17.0213356018066</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4129943847656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4580116271973</t>
+    <t xml:space="preserve">17.412992477417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4580097198486</t>
   </si>
   <si>
     <t xml:space="preserve">17.647087097168</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6425857543945</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.8721790313721</t>
+    <t xml:space="preserve">17.6425838470459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.8721771240234</t>
   </si>
   <si>
     <t xml:space="preserve">17.6020679473877</t>
@@ -4901,7 +4901,7 @@
     <t xml:space="preserve">18.0162353515625</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8496704101562</t>
+    <t xml:space="preserve">17.8496685028076</t>
   </si>
   <si>
     <t xml:space="preserve">17.8136539459229</t>
@@ -4925,7 +4925,7 @@
     <t xml:space="preserve">17.4715175628662</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5750579833984</t>
+    <t xml:space="preserve">17.5750598907471</t>
   </si>
   <si>
     <t xml:space="preserve">17.786642074585</t>
@@ -4952,7 +4952,7 @@
     <t xml:space="preserve">17.8541698455811</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9667148590088</t>
+    <t xml:space="preserve">17.9667167663574</t>
   </si>
   <si>
     <t xml:space="preserve">17.9036903381348</t>
@@ -4964,7 +4964,7 @@
     <t xml:space="preserve">18.1602935791016</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2863445281982</t>
+    <t xml:space="preserve">18.2863426208496</t>
   </si>
   <si>
     <t xml:space="preserve">18.2323226928711</t>
@@ -4973,7 +4973,7 @@
     <t xml:space="preserve">18.2413272857666</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1783008575439</t>
+    <t xml:space="preserve">18.1783027648926</t>
   </si>
   <si>
     <t xml:space="preserve">18.2683372497559</t>
@@ -4994,7 +4994,7 @@
     <t xml:space="preserve">19.0066337585449</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6284809112549</t>
+    <t xml:space="preserve">18.6284828186035</t>
   </si>
   <si>
     <t xml:space="preserve">18.6014709472656</t>
@@ -5006,13 +5006,13 @@
     <t xml:space="preserve">18.6104755401611</t>
   </si>
   <si>
-    <t xml:space="preserve">18.700511932373</t>
+    <t xml:space="preserve">18.7005100250244</t>
   </si>
   <si>
     <t xml:space="preserve">18.7365245819092</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8895874023438</t>
+    <t xml:space="preserve">18.8895854949951</t>
   </si>
   <si>
     <t xml:space="preserve">18.7545318603516</t>
@@ -5024,7 +5024,7 @@
     <t xml:space="preserve">18.8715782165527</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5924663543701</t>
+    <t xml:space="preserve">18.5924682617188</t>
   </si>
   <si>
     <t xml:space="preserve">18.3403663635254</t>
@@ -5036,10 +5036,10 @@
     <t xml:space="preserve">18.5114345550537</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0426464080811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.132682800293</t>
+    <t xml:space="preserve">19.0426483154297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1326847076416</t>
   </si>
   <si>
     <t xml:space="preserve">19.2497310638428</t>
@@ -5051,16 +5051,16 @@
     <t xml:space="preserve">19.1867046356201</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0876655578613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.934606552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9706192016602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0516510009766</t>
+    <t xml:space="preserve">19.08766746521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9346046447754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.9706172943115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0516529083252</t>
   </si>
   <si>
     <t xml:space="preserve">19.0246410369873</t>
@@ -5075,31 +5075,31 @@
     <t xml:space="preserve">19.1957092285156</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8625755310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.790548324585</t>
+    <t xml:space="preserve">18.8625774383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7905464172363</t>
   </si>
   <si>
     <t xml:space="preserve">18.7815437316895</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8535709381104</t>
+    <t xml:space="preserve">18.853572845459</t>
   </si>
   <si>
     <t xml:space="preserve">18.619478225708</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2593326568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.3493690490723</t>
+    <t xml:space="preserve">18.259334564209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3493671417236</t>
   </si>
   <si>
     <t xml:space="preserve">18.538444519043</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3313636779785</t>
+    <t xml:space="preserve">18.3313617706299</t>
   </si>
   <si>
     <t xml:space="preserve">18.0702571868896</t>
@@ -5120,7 +5120,7 @@
     <t xml:space="preserve">17.4670143127441</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4805221557617</t>
+    <t xml:space="preserve">17.4805202484131</t>
   </si>
   <si>
     <t xml:space="preserve">17.6200752258301</t>
@@ -5129,13 +5129,13 @@
     <t xml:space="preserve">17.8991870880127</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8901863098145</t>
+    <t xml:space="preserve">17.8901844024658</t>
   </si>
   <si>
     <t xml:space="preserve">18.1422863006592</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4304027557373</t>
+    <t xml:space="preserve">18.4304008483887</t>
   </si>
   <si>
     <t xml:space="preserve">18.4213981628418</t>
@@ -5150,10 +5150,10 @@
     <t xml:space="preserve">18.7725391387939</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2047138214111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4388084411621</t>
+    <t xml:space="preserve">19.2047119140625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.4388065338135</t>
   </si>
   <si>
     <t xml:space="preserve">19.6278820037842</t>
@@ -5165,19 +5165,19 @@
     <t xml:space="preserve">20.0510520935059</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9069957733154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8439712524414</t>
+    <t xml:space="preserve">19.9069938659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8439693450928</t>
   </si>
   <si>
     <t xml:space="preserve">19.7899475097656</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8979930877686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8079566955566</t>
+    <t xml:space="preserve">19.8979911804199</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.807954788208</t>
   </si>
   <si>
     <t xml:space="preserve">19.6729011535645</t>
@@ -5186,7 +5186,7 @@
     <t xml:space="preserve">19.9520130157471</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0960712432861</t>
+    <t xml:space="preserve">20.0960693359375</t>
   </si>
   <si>
     <t xml:space="preserve">20.0690612792969</t>
@@ -5204,7 +5204,7 @@
     <t xml:space="preserve">20.6542949676514</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5372486114502</t>
+    <t xml:space="preserve">20.5372467041016</t>
   </si>
   <si>
     <t xml:space="preserve">20.996431350708</t>
@@ -5219,7 +5219,7 @@
     <t xml:space="preserve">21.2215213775635</t>
   </si>
   <si>
-    <t xml:space="preserve">21.2755432128906</t>
+    <t xml:space="preserve">21.2755451202393</t>
   </si>
   <si>
     <t xml:space="preserve">21.2935523986816</t>
@@ -5240,22 +5240,22 @@
     <t xml:space="preserve">21.7887516021729</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9598178863525</t>
+    <t xml:space="preserve">21.9598197937012</t>
   </si>
   <si>
     <t xml:space="preserve">22.3199634552002</t>
   </si>
   <si>
-    <t xml:space="preserve">21.671703338623</t>
+    <t xml:space="preserve">21.6717052459717</t>
   </si>
   <si>
     <t xml:space="preserve">22.0948734283447</t>
   </si>
   <si>
-    <t xml:space="preserve">22.2659435272217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.419002532959</t>
+    <t xml:space="preserve">22.265941619873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.4190044403076</t>
   </si>
   <si>
     <t xml:space="preserve">22.5090389251709</t>
@@ -5264,10 +5264,10 @@
     <t xml:space="preserve">22.5900726318359</t>
   </si>
   <si>
-    <t xml:space="preserve">22.563060760498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.905200958252</t>
+    <t xml:space="preserve">22.5630626678467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.9051990509033</t>
   </si>
   <si>
     <t xml:space="preserve">22.797155380249</t>
@@ -5276,7 +5276,7 @@
     <t xml:space="preserve">23.0762672424316</t>
   </si>
   <si>
-    <t xml:space="preserve">23.0222454071045</t>
+    <t xml:space="preserve">23.0222473144531</t>
   </si>
   <si>
     <t xml:space="preserve">23.3103618621826</t>
@@ -5291,10 +5291,10 @@
     <t xml:space="preserve">23.3193645477295</t>
   </si>
   <si>
-    <t xml:space="preserve">23.2293281555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">23.4003982543945</t>
+    <t xml:space="preserve">23.2293300628662</t>
+  </si>
+  <si>
+    <t xml:space="preserve">23.4003963470459</t>
   </si>
   <si>
     <t xml:space="preserve">23.2563400268555</t>
@@ -5303,7 +5303,7 @@
     <t xml:space="preserve">23.6705074310303</t>
   </si>
   <si>
-    <t xml:space="preserve">23.5894756317139</t>
+    <t xml:space="preserve">23.5894737243652</t>
   </si>
   <si>
     <t xml:space="preserve">23.5264472961426</t>
@@ -5315,7 +5315,7 @@
     <t xml:space="preserve">23.8865947723389</t>
   </si>
   <si>
-    <t xml:space="preserve">23.7065200805664</t>
+    <t xml:space="preserve">23.706521987915</t>
   </si>
   <si>
     <t xml:space="preserve">23.6975173950195</t>
@@ -5363,7 +5363,7 @@
     <t xml:space="preserve">21.6987152099609</t>
   </si>
   <si>
-    <t xml:space="preserve">21.9148006439209</t>
+    <t xml:space="preserve">21.9148025512695</t>
   </si>
   <si>
     <t xml:space="preserve">22.5720653533936</t>
@@ -5378,7 +5378,7 @@
     <t xml:space="preserve">22.3559799194336</t>
   </si>
   <si>
-    <t xml:space="preserve">22.310962677002</t>
+    <t xml:space="preserve">22.3109607696533</t>
   </si>
   <si>
     <t xml:space="preserve">22.1218852996826</t>
@@ -5387,19 +5387,19 @@
     <t xml:space="preserve">22.4550189971924</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3289661407471</t>
+    <t xml:space="preserve">22.3289680480957</t>
   </si>
   <si>
     <t xml:space="preserve">22.6260871887207</t>
   </si>
   <si>
-    <t xml:space="preserve">22.671106338501</t>
+    <t xml:space="preserve">22.6711044311523</t>
   </si>
   <si>
     <t xml:space="preserve">21.608678817749</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7977542877197</t>
+    <t xml:space="preserve">21.7977523803711</t>
   </si>
   <si>
     <t xml:space="preserve">21.968822479248</t>
@@ -5417,22 +5417,22 @@
     <t xml:space="preserve">21.5996742248535</t>
   </si>
   <si>
-    <t xml:space="preserve">21.7257232666016</t>
+    <t xml:space="preserve">21.7257251739502</t>
   </si>
   <si>
     <t xml:space="preserve">21.7527370452881</t>
   </si>
   <si>
-    <t xml:space="preserve">21.6176834106445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.8427734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2749443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.1038761138916</t>
+    <t xml:space="preserve">21.6176815032959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.8427715301514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2749462127686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.1038780212402</t>
   </si>
   <si>
     <t xml:space="preserve">22.1578998565674</t>
@@ -5441,16 +5441,16 @@
     <t xml:space="preserve">22.2839488983154</t>
   </si>
   <si>
-    <t xml:space="preserve">22.3019580841064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">22.2569389343262</t>
+    <t xml:space="preserve">22.3019561767578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">22.2569370269775</t>
   </si>
   <si>
     <t xml:space="preserve">22.7341289520264</t>
   </si>
   <si>
-    <t xml:space="preserve">22.9502182006836</t>
+    <t xml:space="preserve">22.950216293335</t>
   </si>
   <si>
     <t xml:space="preserve">23.1843109130859</t>
@@ -5462,13 +5462,13 @@
     <t xml:space="preserve">23.0672645568848</t>
   </si>
   <si>
-    <t xml:space="preserve">23.4364128112793</t>
+    <t xml:space="preserve">23.4364147186279</t>
   </si>
   <si>
     <t xml:space="preserve">23.5084419250488</t>
   </si>
   <si>
-    <t xml:space="preserve">23.8415756225586</t>
+    <t xml:space="preserve">23.84157371521</t>
   </si>
   <si>
     <t xml:space="preserve">23.5945644378662</t>
@@ -6404,7 +6404,7 @@
     <t xml:space="preserve">33.7299995422363</t>
   </si>
   <si>
-    <t xml:space="preserve">33.4199981689453</t>
+    <t xml:space="preserve">33.6699981689453</t>
   </si>
 </sst>
 </file>
@@ -71821,22 +71821,22 @@
     </row>
     <row r="2504">
       <c r="A2504" s="1" t="n">
-        <v>45965.6912384259</v>
+        <v>45966.6912847222</v>
       </c>
       <c r="B2504" t="n">
-        <v>475017</v>
+        <v>534301</v>
       </c>
       <c r="C2504" t="n">
-        <v>33.6800003051758</v>
+        <v>33.8800010681152</v>
       </c>
       <c r="D2504" t="n">
-        <v>32.9599990844727</v>
+        <v>33.0299987792969</v>
       </c>
       <c r="E2504" t="n">
-        <v>33.1800003051758</v>
+        <v>33.1199989318848</v>
       </c>
       <c r="F2504" t="n">
-        <v>33.4199981689453</v>
+        <v>33.6699981689453</v>
       </c>
       <c r="G2504" t="s">
         <v>2130</v>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2134" uniqueCount="2134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="2135">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8295068740845</t>
+    <t xml:space="preserve">10.8295078277588</t>
   </si>
   <si>
     <t xml:space="preserve">AZM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068347930908</t>
+    <t xml:space="preserve">10.7068357467651</t>
   </si>
   <si>
     <t xml:space="preserve">10.4860258102417</t>
   </si>
   <si>
-    <t xml:space="preserve">10.191611289978</t>
+    <t xml:space="preserve">10.1916122436523</t>
   </si>
   <si>
     <t xml:space="preserve">9.9119176864624</t>
@@ -59,16 +59,16 @@
     <t xml:space="preserve">9.93645286560059</t>
   </si>
   <si>
-    <t xml:space="preserve">10.225959777832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0002431869507</t>
+    <t xml:space="preserve">10.2259616851807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.000244140625</t>
   </si>
   <si>
     <t xml:space="preserve">9.61750602722168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33290576934814</t>
+    <t xml:space="preserve">9.33290481567383</t>
   </si>
   <si>
     <t xml:space="preserve">9.1513500213623</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">9.25930309295654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53899478912354</t>
+    <t xml:space="preserve">9.53899765014648</t>
   </si>
   <si>
     <t xml:space="preserve">9.48992729187012</t>
@@ -95,16 +95,16 @@
     <t xml:space="preserve">9.40160274505615</t>
   </si>
   <si>
-    <t xml:space="preserve">9.12681674957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.49483585357666</t>
+    <t xml:space="preserve">9.12681770324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.49483489990234</t>
   </si>
   <si>
     <t xml:space="preserve">9.43595123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84712314605713</t>
+    <t xml:space="preserve">8.84712409973145</t>
   </si>
   <si>
     <t xml:space="preserve">8.99433040618896</t>
@@ -116,34 +116,34 @@
     <t xml:space="preserve">8.05711460113525</t>
   </si>
   <si>
-    <t xml:space="preserve">7.86574602127075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32699394226074</t>
+    <t xml:space="preserve">7.86574649810791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32699298858643</t>
   </si>
   <si>
     <t xml:space="preserve">7.61058759689331</t>
   </si>
   <si>
-    <t xml:space="preserve">7.67928409576416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10127639770508</t>
+    <t xml:space="preserve">7.67928314208984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10127544403076</t>
   </si>
   <si>
     <t xml:space="preserve">7.8706521987915</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53798961639404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.78333473205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46929454803467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61649799346924</t>
+    <t xml:space="preserve">8.53799057006836</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.78333568572998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46929359436035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61649894714355</t>
   </si>
   <si>
     <t xml:space="preserve">8.50364112854004</t>
@@ -152,157 +152,157 @@
     <t xml:space="preserve">8.21413612365723</t>
   </si>
   <si>
-    <t xml:space="preserve">8.69010353088379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71954536437988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29365158081055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30837059020996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47520446777344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09737396240234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.22004795074463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.41141605377197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4801139831543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77943420410156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66166973114014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79415321350098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77452754974365</t>
+    <t xml:space="preserve">8.69010448455811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71954345703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29365062713623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30837154388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47520542144775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09737491607666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.22004890441895</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.41141700744629</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.48011207580566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77943325042725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.66166877746582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79415416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77452659606934</t>
   </si>
   <si>
     <t xml:space="preserve">9.68620204925537</t>
   </si>
   <si>
-    <t xml:space="preserve">9.64694786071777</t>
+    <t xml:space="preserve">9.64694881439209</t>
   </si>
   <si>
     <t xml:space="preserve">9.72545719146729</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2357740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3044719696045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8383150100708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.56843662261963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98552322387695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93154525756836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.74508476257324</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3780736923218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449056625366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4369564056396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5547218322754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5056524276733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5498142242432</t>
+    <t xml:space="preserve">10.2357749938965</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3044700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83831596374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.56843566894531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.98552227020264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93154621124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.74508380889893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3780727386475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449066162109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4369583129883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5547208786011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5056533813477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5498151779175</t>
   </si>
   <si>
     <t xml:space="preserve">10.5007467269897</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5694417953491</t>
+    <t xml:space="preserve">10.5694427490234</t>
   </si>
   <si>
     <t xml:space="preserve">10.4173288345337</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4811201095581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7411842346191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8442306518555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7853450775146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5988836288452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406806945801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2897510528564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7303638458252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57334327697754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43104553222656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40651035308838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19060707092285</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.08265590667725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.3525333404541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47029876708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2789306640625</t>
+    <t xml:space="preserve">10.4811191558838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7411832809448</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8442277908325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.785346031189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5988845825195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406826019287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2897500991821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73036575317383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57334423065186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43104457855225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40650939941406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19060611724854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.08265495300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35253238677979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47029972076416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.27892971038818</t>
   </si>
   <si>
     <t xml:space="preserve">9.30346393585205</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14644432067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52970314025879</t>
+    <t xml:space="preserve">9.14644336700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52970123291016</t>
   </si>
   <si>
     <t xml:space="preserve">9.79665470123291</t>
@@ -311,37 +311,37 @@
     <t xml:space="preserve">10.1190118789673</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89235496520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95279693603516</t>
+    <t xml:space="preserve">9.89235401153564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95279598236084</t>
   </si>
   <si>
     <t xml:space="preserve">10.1492338180542</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84702301025391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.766432762146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42896556854248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42392730712891</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52466583251953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54984951019287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39370536804199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82958126068115</t>
+    <t xml:space="preserve">9.84702205657959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.76643371582031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42896461486816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42392826080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5246639251709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54984855651855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39370632171631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82958030700684</t>
   </si>
   <si>
     <t xml:space="preserve">8.4820384979248</t>
@@ -356,61 +356,61 @@
     <t xml:space="preserve">8.53744411468506</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68351078033447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39874362945557</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50451850891113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81680011749268</t>
+    <t xml:space="preserve">8.68351268768311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39874267578125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50451755523682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81680107116699</t>
   </si>
   <si>
     <t xml:space="preserve">8.46692848205566</t>
   </si>
   <si>
-    <t xml:space="preserve">7.46459817886353</t>
+    <t xml:space="preserve">7.46459722518921</t>
   </si>
   <si>
     <t xml:space="preserve">7.5754075050354</t>
   </si>
   <si>
-    <t xml:space="preserve">7.49985599517822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34875011444092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43941354751587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20268249511719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87025022506714</t>
+    <t xml:space="preserve">7.49985456466675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34874963760376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43941307067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20268154144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8702507019043</t>
   </si>
   <si>
     <t xml:space="preserve">6.50256109237671</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6284818649292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86017656326294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02135610580444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.38904476165771</t>
+    <t xml:space="preserve">6.62848091125488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8601770401001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02135467529297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.38904523849487</t>
   </si>
   <si>
     <t xml:space="preserve">7.20771837234497</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44948720932007</t>
+    <t xml:space="preserve">7.44948530197144</t>
   </si>
   <si>
     <t xml:space="preserve">7.66607189178467</t>
@@ -422,109 +422,109 @@
     <t xml:space="preserve">7.64592409133911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79702854156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71140289306641</t>
+    <t xml:space="preserve">7.79702758789062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71140193939209</t>
   </si>
   <si>
     <t xml:space="preserve">7.94309711456299</t>
   </si>
   <si>
-    <t xml:space="preserve">7.81717586517334</t>
+    <t xml:space="preserve">7.81717491149902</t>
   </si>
   <si>
     <t xml:space="preserve">7.94813394546509</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08179759979248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.92565441131592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71410846710205</t>
+    <t xml:space="preserve">7.08179807662964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.92565488815308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71410942077637</t>
   </si>
   <si>
     <t xml:space="preserve">6.78966045379639</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90047073364258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22786474227905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.27823352813721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32860231399536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31852769851685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.39911890029907</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15735006332397</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94580173492432</t>
+    <t xml:space="preserve">6.90047025680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22786569595337</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.27823305130005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32860374450684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31852865219116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3991174697876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15734958648682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94580268859863</t>
   </si>
   <si>
     <t xml:space="preserve">7.19764471054077</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80476903915405</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02639198303223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08683395385742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04150199890137</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8501033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86521339416504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069267272949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22282886505127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31349182128906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23290252685547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29838132858276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98106098175049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01128101348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53781843185425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.79973554611206</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.68388700485229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.73929309844971</t>
+    <t xml:space="preserve">6.80477094650269</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02639150619507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08683490753174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04150295257568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85010194778442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8652138710022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069219589233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22282934188843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31349277496338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23290348052979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29838180541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98105955123901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01128244400024</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53781890869141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.79973411560059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.68388605117798</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73929262161255</t>
   </si>
   <si>
     <t xml:space="preserve">6.94076585769653</t>
@@ -536,58 +536,58 @@
     <t xml:space="preserve">6.668776512146</t>
   </si>
   <si>
-    <t xml:space="preserve">6.46226596832275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57307624816895</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.67381286621094</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59825992584229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87528705596924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00624513626099</t>
+    <t xml:space="preserve">6.46226501464844</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57307720184326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6738133430481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59826135635376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87528657913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00624370574951</t>
   </si>
   <si>
     <t xml:space="preserve">7.1523118019104</t>
   </si>
   <si>
-    <t xml:space="preserve">7.30341815948486</t>
+    <t xml:space="preserve">7.30341863632202</t>
   </si>
   <si>
     <t xml:space="preserve">7.62577629089355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66103315353394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.57036972045898</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45452308654785</t>
+    <t xml:space="preserve">7.66103410720825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.5703706741333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45452451705933</t>
   </si>
   <si>
     <t xml:space="preserve">7.5351128578186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44445037841797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59555578231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72147560119629</t>
+    <t xml:space="preserve">7.44445085525513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59555625915527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72147607803345</t>
   </si>
   <si>
     <t xml:space="preserve">7.60562944412231</t>
   </si>
   <si>
-    <t xml:space="preserve">7.70636796951294</t>
+    <t xml:space="preserve">7.70636606216431</t>
   </si>
   <si>
     <t xml:space="preserve">7.48474502563477</t>
@@ -596,31 +596,31 @@
     <t xml:space="preserve">7.3638596534729</t>
   </si>
   <si>
-    <t xml:space="preserve">7.26312351226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13216495513916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617052078247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17246007919312</t>
+    <t xml:space="preserve">7.26312398910522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13216543197632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617147445679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17245960235596</t>
   </si>
   <si>
     <t xml:space="preserve">7.69629192352295</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91791343688965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.35611915588379</t>
+    <t xml:space="preserve">7.91791296005249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.35611820220947</t>
   </si>
   <si>
     <t xml:space="preserve">8.38633823394775</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51729679107666</t>
+    <t xml:space="preserve">8.51729488372803</t>
   </si>
   <si>
     <t xml:space="preserve">8.45181751251221</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">8.20501232147217</t>
   </si>
   <si>
-    <t xml:space="preserve">8.04887104034424</t>
+    <t xml:space="preserve">8.04887199401855</t>
   </si>
   <si>
     <t xml:space="preserve">7.95820713043213</t>
@@ -638,40 +638,40 @@
     <t xml:space="preserve">7.93132162094116</t>
   </si>
   <si>
-    <t xml:space="preserve">7.71623420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.73236846923828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.63557720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.64095544815063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45813083648682</t>
+    <t xml:space="preserve">7.71623516082764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.73236799240112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.63557767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.64095401763916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45813274383545</t>
   </si>
   <si>
     <t xml:space="preserve">7.44200038909912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57105159759521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.68935108184814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.62482309341431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.79689264297485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.20017910003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.43139934539795</t>
+    <t xml:space="preserve">7.57105302810669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.68935012817383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.62482404708862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.79689359664917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.20018100738525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.43139839172363</t>
   </si>
   <si>
     <t xml:space="preserve">8.61960029602051</t>
@@ -680,31 +680,31 @@
     <t xml:space="preserve">8.54431915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46903896331787</t>
+    <t xml:space="preserve">8.46903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">8.58733749389648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70025730133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54969692230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.60346698760986</t>
+    <t xml:space="preserve">8.70025634765625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54969596862793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6034688949585</t>
   </si>
   <si>
     <t xml:space="preserve">8.53356552124023</t>
   </si>
   <si>
-    <t xml:space="preserve">8.5980920791626</t>
+    <t xml:space="preserve">8.59809112548828</t>
   </si>
   <si>
     <t xml:space="preserve">8.51743316650391</t>
   </si>
   <si>
-    <t xml:space="preserve">8.52818870544434</t>
+    <t xml:space="preserve">8.52818775177002</t>
   </si>
   <si>
     <t xml:space="preserve">8.67874908447266</t>
@@ -713,13 +713,13 @@
     <t xml:space="preserve">9.11429882049561</t>
   </si>
   <si>
-    <t xml:space="preserve">9.15731620788574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2003345489502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17882633209229</t>
+    <t xml:space="preserve">9.15731716156006</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20033359527588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17882442474365</t>
   </si>
   <si>
     <t xml:space="preserve">9.05515003204346</t>
@@ -734,19 +734,19 @@
     <t xml:space="preserve">9.44768333435059</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38315677642822</t>
+    <t xml:space="preserve">9.38315868377686</t>
   </si>
   <si>
     <t xml:space="preserve">9.41004276275635</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4584379196167</t>
+    <t xml:space="preserve">9.45843696594238</t>
   </si>
   <si>
     <t xml:space="preserve">9.4530611038208</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37240314483643</t>
+    <t xml:space="preserve">9.37240219116211</t>
   </si>
   <si>
     <t xml:space="preserve">9.2379732131958</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">9.44230556488037</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92609882354736</t>
+    <t xml:space="preserve">8.92609786987305</t>
   </si>
   <si>
     <t xml:space="preserve">9.0927906036377</t>
@@ -782,52 +782,52 @@
     <t xml:space="preserve">9.28636932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24335193634033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.26486015319824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2325963973999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2487268447876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.96373844146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.495924949646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59271335601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5228099822998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66799449920654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7378978729248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71100997924805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.70563507080078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.63573169708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53894233703613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50130081176758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28621578216553</t>
+    <t xml:space="preserve">9.24335289001465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.26485919952393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23259830474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24872779846191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96373748779297</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.49592590332031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5927152633667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.52281093597412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66799259185791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73789691925049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71101188659668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.70563411712646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.6357307434082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53894138336182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50130176544189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28621482849121</t>
   </si>
   <si>
     <t xml:space="preserve">8.33460998535156</t>
@@ -836,22 +836,22 @@
     <t xml:space="preserve">8.43677616119385</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47441577911377</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.62497615814209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56582832336426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.47979354858398</t>
+    <t xml:space="preserve">8.47441673278809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.62497520446777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56582736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.47979259490967</t>
   </si>
   <si>
     <t xml:space="preserve">8.66261672973633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.61422348022461</t>
+    <t xml:space="preserve">8.61422157287598</t>
   </si>
   <si>
     <t xml:space="preserve">8.78091526031494</t>
@@ -860,37 +860,37 @@
     <t xml:space="preserve">8.77016162872314</t>
   </si>
   <si>
-    <t xml:space="preserve">8.79166889190674</t>
+    <t xml:space="preserve">8.79166793823242</t>
   </si>
   <si>
     <t xml:space="preserve">9.18420219421387</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04977321624756</t>
+    <t xml:space="preserve">9.04977226257324</t>
   </si>
   <si>
     <t xml:space="preserve">9.14118480682373</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16269302368164</t>
+    <t xml:space="preserve">9.16269493103027</t>
   </si>
   <si>
     <t xml:space="preserve">9.30249977111816</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13580703735352</t>
+    <t xml:space="preserve">9.13580799102783</t>
   </si>
   <si>
     <t xml:space="preserve">9.14656162261963</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20570945739746</t>
+    <t xml:space="preserve">9.20571041107178</t>
   </si>
   <si>
     <t xml:space="preserve">9.62513065338135</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63050651550293</t>
+    <t xml:space="preserve">9.63050746917725</t>
   </si>
   <si>
     <t xml:space="preserve">9.60899829864502</t>
@@ -902,13 +902,13 @@
     <t xml:space="preserve">9.7165412902832</t>
   </si>
   <si>
-    <t xml:space="preserve">9.97464656829834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0553026199341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2435026168823</t>
+    <t xml:space="preserve">9.97464561462402</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0553045272827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2435035705566</t>
   </si>
   <si>
     <t xml:space="preserve">10.4155731201172</t>
@@ -917,7 +917,7 @@
     <t xml:space="preserve">10.3456707000732</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2327508926392</t>
+    <t xml:space="preserve">10.2327489852905</t>
   </si>
   <si>
     <t xml:space="preserve">10.3994426727295</t>
@@ -932,34 +932,34 @@
     <t xml:space="preserve">10.1305847167969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036987304688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3295373916626</t>
+    <t xml:space="preserve">10.1036977767944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3295383453369</t>
   </si>
   <si>
     <t xml:space="preserve">10.425971031189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5507650375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6074914932251</t>
+    <t xml:space="preserve">10.5507659912109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6074905395508</t>
   </si>
   <si>
     <t xml:space="preserve">10.5847997665405</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4770231246948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2387809753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2728157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3408861160278</t>
+    <t xml:space="preserve">10.4770221710205</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2387790679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.27281665802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3408842086792</t>
   </si>
   <si>
     <t xml:space="preserve">10.2160911560059</t>
@@ -974,16 +974,16 @@
     <t xml:space="preserve">10.2898321151733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2614698410034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1083135604858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0062093734741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94381237030029</t>
+    <t xml:space="preserve">10.2614707946777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1083126068115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0062103271484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94381141662598</t>
   </si>
   <si>
     <t xml:space="preserve">10.1707105636597</t>
@@ -992,13 +992,13 @@
     <t xml:space="preserve">10.1366758346558</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0629329681396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1990718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3522291183472</t>
+    <t xml:space="preserve">10.062933921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1990728378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3522272109985</t>
   </si>
   <si>
     <t xml:space="preserve">10.2104177474976</t>
@@ -1013,61 +1013,61 @@
     <t xml:space="preserve">10.1480207443237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2444524765015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2841596603394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2217636108398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0912961959839</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1593647003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.545093536377</t>
+    <t xml:space="preserve">10.2444515228271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2841606140137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2217626571655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0912952423096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1593656539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5450925827026</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089546203613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3181943893433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.295506477356</t>
+    <t xml:space="preserve">10.3181953430176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2955055236816</t>
   </si>
   <si>
     <t xml:space="preserve">10.3692464828491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4316434860229</t>
+    <t xml:space="preserve">10.4316453933716</t>
   </si>
   <si>
     <t xml:space="preserve">10.397608757019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7152671813965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.641526222229</t>
+    <t xml:space="preserve">10.7152662277222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.6415252685547</t>
   </si>
   <si>
     <t xml:space="preserve">10.7436294555664</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7209386825562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.6698875427246</t>
+    <t xml:space="preserve">10.7209377288818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.669885635376</t>
   </si>
   <si>
     <t xml:space="preserve">10.7776613235474</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7039213180542</t>
+    <t xml:space="preserve">10.7039222717285</t>
   </si>
   <si>
     <t xml:space="preserve">10.6585416793823</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">10.5564374923706</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4826965332031</t>
+    <t xml:space="preserve">10.4826946258545</t>
   </si>
   <si>
     <t xml:space="preserve">10.3352117538452</t>
@@ -1094,13 +1094,13 @@
     <t xml:space="preserve">10.2331075668335</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2784872055054</t>
+    <t xml:space="preserve">10.2784881591797</t>
   </si>
   <si>
     <t xml:space="preserve">10.0288991928101</t>
   </si>
   <si>
-    <t xml:space="preserve">10.040244102478</t>
+    <t xml:space="preserve">10.0402450561523</t>
   </si>
   <si>
     <t xml:space="preserve">10.0969696044922</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">10.0345726013184</t>
   </si>
   <si>
-    <t xml:space="preserve">9.9835205078125</t>
+    <t xml:space="preserve">9.98351955413818</t>
   </si>
   <si>
     <t xml:space="preserve">9.96082878112793</t>
@@ -1124,28 +1124,28 @@
     <t xml:space="preserve">10.2557973861694</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4940404891968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.511058807373</t>
+    <t xml:space="preserve">10.4940395355225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5110578536987</t>
   </si>
   <si>
     <t xml:space="preserve">10.4146270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3635730743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3805913925171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4600048065186</t>
+    <t xml:space="preserve">10.3635740280151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3805904388428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4600067138672</t>
   </si>
   <si>
     <t xml:space="preserve">10.5167303085327</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3465576171875</t>
+    <t xml:space="preserve">10.3465566635132</t>
   </si>
   <si>
     <t xml:space="preserve">9.84738063812256</t>
@@ -1154,7 +1154,7 @@
     <t xml:space="preserve">9.86439800262451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.72825908660889</t>
+    <t xml:space="preserve">9.7282600402832</t>
   </si>
   <si>
     <t xml:space="preserve">9.67720794677734</t>
@@ -1163,7 +1163,7 @@
     <t xml:space="preserve">9.66018962860107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48434257507324</t>
+    <t xml:space="preserve">9.48434448242188</t>
   </si>
   <si>
     <t xml:space="preserve">9.688551902771</t>
@@ -1172,13 +1172,13 @@
     <t xml:space="preserve">9.58644771575928</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71124172210693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67153453826904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.61480903625488</t>
+    <t xml:space="preserve">9.71124076843262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67153358459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6148099899292</t>
   </si>
   <si>
     <t xml:space="preserve">9.62048244476318</t>
@@ -1193,52 +1193,52 @@
     <t xml:space="preserve">9.79632949829102</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89843273162842</t>
+    <t xml:space="preserve">9.89843368530273</t>
   </si>
   <si>
     <t xml:space="preserve">9.16101360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95113182067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99083995819092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.76961421966553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75259590148926</t>
+    <t xml:space="preserve">8.95113468170166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99084091186523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.76961326599121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75259685516357</t>
   </si>
   <si>
     <t xml:space="preserve">8.86604499816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85470104217529</t>
+    <t xml:space="preserve">8.85470008850098</t>
   </si>
   <si>
     <t xml:space="preserve">9.05891036987305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24042797088623</t>
+    <t xml:space="preserve">9.24042892456055</t>
   </si>
   <si>
     <t xml:space="preserve">9.25177383422852</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10996246337891</t>
+    <t xml:space="preserve">9.10996150970459</t>
   </si>
   <si>
     <t xml:space="preserve">9.09294414520264</t>
   </si>
   <si>
-    <t xml:space="preserve">8.98516845703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.07592678070068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13265132904053</t>
+    <t xml:space="preserve">8.98516654968262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.075927734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13265228271484</t>
   </si>
   <si>
     <t xml:space="preserve">9.05323600769043</t>
@@ -1250,22 +1250,22 @@
     <t xml:space="preserve">8.88306331634521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82633781433105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79230308532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79797744750977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9681510925293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.00218391418457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0702543258667</t>
+    <t xml:space="preserve">8.82633972167969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79230403900146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79797649383545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.96815013885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.0021858215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07025527954102</t>
   </si>
   <si>
     <t xml:space="preserve">8.9965124130249</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">9.01920223236084</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92277050018311</t>
+    <t xml:space="preserve">8.92277145385742</t>
   </si>
   <si>
     <t xml:space="preserve">9.04189205169678</t>
@@ -1283,67 +1283,67 @@
     <t xml:space="preserve">9.03054714202881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01352977752686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.04756546020508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.03622055053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.1383228302002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97382354736328</t>
+    <t xml:space="preserve">9.01352882385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.04756450653076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.03621959686279</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13832378387451</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97382164001465</t>
   </si>
   <si>
     <t xml:space="preserve">9.12697887420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16668605804443</t>
+    <t xml:space="preserve">9.16668701171875</t>
   </si>
   <si>
     <t xml:space="preserve">9.19504833221436</t>
   </si>
   <si>
-    <t xml:space="preserve">9.37089443206787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.38223934173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34253215789795</t>
+    <t xml:space="preserve">9.37089538574219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.38223838806152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34253120422363</t>
   </si>
   <si>
     <t xml:space="preserve">9.46732616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6755590438843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.420298576355</t>
+    <t xml:space="preserve">10.67555809021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4202976226807</t>
   </si>
   <si>
     <t xml:space="preserve">10.3919363021851</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5961446762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7549734115601</t>
+    <t xml:space="preserve">10.5961437225342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7549724578857</t>
   </si>
   <si>
     <t xml:space="preserve">10.7379560470581</t>
   </si>
   <si>
-    <t xml:space="preserve">10.760645866394</t>
+    <t xml:space="preserve">10.7606468200684</t>
   </si>
   <si>
     <t xml:space="preserve">10.6613779067993</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4543342590332</t>
+    <t xml:space="preserve">10.4543333053589</t>
   </si>
   <si>
     <t xml:space="preserve">10.4032821655273</t>
@@ -1355,19 +1355,19 @@
     <t xml:space="preserve">10.3777561187744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0742788314819</t>
+    <t xml:space="preserve">10.0742797851562</t>
   </si>
   <si>
     <t xml:space="preserve">10.1338386535645</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0941314697266</t>
+    <t xml:space="preserve">10.0941324234009</t>
   </si>
   <si>
     <t xml:space="preserve">9.98635673522949</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1565294265747</t>
+    <t xml:space="preserve">10.1565284729004</t>
   </si>
   <si>
     <t xml:space="preserve">10.1962366104126</t>
@@ -1379,16 +1379,16 @@
     <t xml:space="preserve">10.1622018814087</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2416162490845</t>
+    <t xml:space="preserve">10.2416172027588</t>
   </si>
   <si>
     <t xml:space="preserve">10.2501239776611</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2132530212402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1678733825684</t>
+    <t xml:space="preserve">10.2132539749146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1678743362427</t>
   </si>
   <si>
     <t xml:space="preserve">9.90694046020508</t>
@@ -1397,7 +1397,7 @@
     <t xml:space="preserve">9.92963123321533</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877269744873</t>
+    <t xml:space="preserve">10.1877279281616</t>
   </si>
   <si>
     <t xml:space="preserve">10.2302713394165</t>
@@ -1409,19 +1409,19 @@
     <t xml:space="preserve">10.1905641555786</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1820573806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0317344665527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97784805297852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81618213653564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.88708686828613</t>
+    <t xml:space="preserve">10.182056427002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0317354202271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9778470993042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81618309020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.88708782196045</t>
   </si>
   <si>
     <t xml:space="preserve">9.89559650421143</t>
@@ -1433,49 +1433,49 @@
     <t xml:space="preserve">9.97500991821289</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0657711029053</t>
+    <t xml:space="preserve">10.065770149231</t>
   </si>
   <si>
     <t xml:space="preserve">10.1395120620728</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0005359649658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0686044692993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.73676776885986</t>
+    <t xml:space="preserve">10.0005369186401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0686054229736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.73676681518555</t>
   </si>
   <si>
     <t xml:space="preserve">9.83603572845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89276123046875</t>
+    <t xml:space="preserve">9.89275932312012</t>
   </si>
   <si>
     <t xml:space="preserve">9.8672342300415</t>
   </si>
   <si>
-    <t xml:space="preserve">9.82752704620361</t>
+    <t xml:space="preserve">9.8275260925293</t>
   </si>
   <si>
     <t xml:space="preserve">9.77931118011475</t>
   </si>
   <si>
-    <t xml:space="preserve">9.83319854736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94948577880859</t>
+    <t xml:space="preserve">9.8331995010376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94948482513428</t>
   </si>
   <si>
     <t xml:space="preserve">10.0714426040649</t>
   </si>
   <si>
-    <t xml:space="preserve">9.93813991546631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71407699584961</t>
+    <t xml:space="preserve">9.93814086914062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71407794952393</t>
   </si>
   <si>
     <t xml:space="preserve">9.42761898040771</t>
@@ -1484,10 +1484,10 @@
     <t xml:space="preserve">9.10145282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21773719787598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12414264678955</t>
+    <t xml:space="preserve">9.21773815155029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12414360046387</t>
   </si>
   <si>
     <t xml:space="preserve">9.24326419830322</t>
@@ -1499,16 +1499,16 @@
     <t xml:space="preserve">9.29274559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51369762420654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.39841842651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47206878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4400463104248</t>
+    <t xml:space="preserve">9.51369667053223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.39841747283936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47206783294678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.44004726409912</t>
   </si>
   <si>
     <t xml:space="preserve">9.33757591247559</t>
@@ -1520,19 +1520,19 @@
     <t xml:space="preserve">9.02696514129639</t>
   </si>
   <si>
-    <t xml:space="preserve">8.89887523651123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34398078918457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.31836318969727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.9373025894165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.92129230499268</t>
+    <t xml:space="preserve">8.89887619018555</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34397983551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.31836223602295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.93730354309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.92129039764404</t>
   </si>
   <si>
     <t xml:space="preserve">8.93410110473633</t>
@@ -1541,10 +1541,10 @@
     <t xml:space="preserve">8.64590263366699</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83803462982178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.75477886199951</t>
+    <t xml:space="preserve">8.83803558349609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7547779083252</t>
   </si>
   <si>
     <t xml:space="preserve">8.72275638580322</t>
@@ -1553,55 +1553,55 @@
     <t xml:space="preserve">8.71635150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64270210266113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82842826843262</t>
+    <t xml:space="preserve">8.64270305633545</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82842922210693</t>
   </si>
   <si>
     <t xml:space="preserve">8.8060131072998</t>
   </si>
   <si>
-    <t xml:space="preserve">8.83162975311279</t>
+    <t xml:space="preserve">8.83163070678711</t>
   </si>
   <si>
     <t xml:space="preserve">8.66511631011963</t>
   </si>
   <si>
-    <t xml:space="preserve">8.73556518554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5178165435791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.48899745941162</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56905174255371</t>
+    <t xml:space="preserve">8.73556423187256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51781558990479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4889965057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56905078887939</t>
   </si>
   <si>
     <t xml:space="preserve">8.45697498321533</t>
   </si>
   <si>
-    <t xml:space="preserve">8.39613151550293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5114107131958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53062629699707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53703022003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54343318939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71315002441406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40574073791504</t>
+    <t xml:space="preserve">8.39613342285156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51141262054443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53062534332275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53702831268311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54343414306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71314907073975</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40573978424072</t>
   </si>
   <si>
     <t xml:space="preserve">8.36411190032959</t>
@@ -1616,7 +1616,7 @@
     <t xml:space="preserve">8.58506202697754</t>
   </si>
   <si>
-    <t xml:space="preserve">8.57225513458252</t>
+    <t xml:space="preserve">8.5722541809082</t>
   </si>
   <si>
     <t xml:space="preserve">8.46017646789551</t>
@@ -1631,7 +1631,7 @@
     <t xml:space="preserve">8.4409646987915</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09420967102051</t>
+    <t xml:space="preserve">9.09421062469482</t>
   </si>
   <si>
     <t xml:space="preserve">9.01735782623291</t>
@@ -1640,34 +1640,34 @@
     <t xml:space="preserve">9.05578327178955</t>
   </si>
   <si>
-    <t xml:space="preserve">9.19988250732422</t>
+    <t xml:space="preserve">9.1998815536499</t>
   </si>
   <si>
     <t xml:space="preserve">9.18707370758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.91808986663818</t>
+    <t xml:space="preserve">8.9180908203125</t>
   </si>
   <si>
     <t xml:space="preserve">8.87646198272705</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03657150268555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18387031555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15505123138428</t>
+    <t xml:space="preserve">9.03657054901123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18387126922607</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15505218505859</t>
   </si>
   <si>
     <t xml:space="preserve">9.1518497467041</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23510551452637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16465950012207</t>
+    <t xml:space="preserve">9.23510646820068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16465854644775</t>
   </si>
   <si>
     <t xml:space="preserve">9.1262321472168</t>
@@ -1679,16 +1679,16 @@
     <t xml:space="preserve">9.25431823730469</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2062873840332</t>
+    <t xml:space="preserve">9.20628547668457</t>
   </si>
   <si>
     <t xml:space="preserve">9.20948886871338</t>
   </si>
   <si>
-    <t xml:space="preserve">9.22549915313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.10701942443848</t>
+    <t xml:space="preserve">9.22550010681152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.10701751708984</t>
   </si>
   <si>
     <t xml:space="preserve">8.92769718170166</t>
@@ -1697,10 +1697,10 @@
     <t xml:space="preserve">8.76758670806885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65871238708496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68112754821777</t>
+    <t xml:space="preserve">8.65871334075928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68112659454346</t>
   </si>
   <si>
     <t xml:space="preserve">8.72595882415771</t>
@@ -1712,10 +1712,10 @@
     <t xml:space="preserve">8.7803955078125</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82202339172363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.77719497680664</t>
+    <t xml:space="preserve">8.82202434539795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.77719402313232</t>
   </si>
   <si>
     <t xml:space="preserve">8.78359794616699</t>
@@ -1724,61 +1724,61 @@
     <t xml:space="preserve">8.95331382751465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97252655029297</t>
+    <t xml:space="preserve">8.97252750396729</t>
   </si>
   <si>
     <t xml:space="preserve">8.9661226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86685466766357</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86045169830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32568454742432</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22321510314941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.29366207122803</t>
+    <t xml:space="preserve">8.86685562133789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86044979095459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32568550109863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22321605682373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.29366302490234</t>
   </si>
   <si>
     <t xml:space="preserve">8.53382778167725</t>
   </si>
   <si>
-    <t xml:space="preserve">8.48259449005127</t>
+    <t xml:space="preserve">8.48259258270264</t>
   </si>
   <si>
     <t xml:space="preserve">8.40253734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14956474304199</t>
+    <t xml:space="preserve">8.14956569671631</t>
   </si>
   <si>
     <t xml:space="preserve">8.06630706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07271194458008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77490901947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.74929046630859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67884254455566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87417602539062</t>
+    <t xml:space="preserve">8.07271289825439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77490997314453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.74929094314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67884397506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87417650222778</t>
   </si>
   <si>
     <t xml:space="preserve">7.73007822036743</t>
   </si>
   <si>
-    <t xml:space="preserve">7.53474569320679</t>
+    <t xml:space="preserve">7.53474473953247</t>
   </si>
   <si>
     <t xml:space="preserve">7.42266893386841</t>
@@ -1787,40 +1787,40 @@
     <t xml:space="preserve">7.25295305252075</t>
   </si>
   <si>
-    <t xml:space="preserve">7.21772766113281</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.08003425598145</t>
+    <t xml:space="preserve">7.21772813796997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.0800347328186</t>
   </si>
   <si>
     <t xml:space="preserve">7.11205577850342</t>
   </si>
   <si>
-    <t xml:space="preserve">6.84947729110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.9711594581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0416088104248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.03520441055298</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04801368713379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94234085083008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95194816589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00958633422852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13126993179321</t>
+    <t xml:space="preserve">6.84947776794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.97115993499756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04160833358765</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.03520345687866</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04801225662231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94234132766724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95194721221924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00958585739136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.1312689781189</t>
   </si>
   <si>
     <t xml:space="preserve">6.97436189651489</t>
@@ -1832,52 +1832,52 @@
     <t xml:space="preserve">6.95514869689941</t>
   </si>
   <si>
-    <t xml:space="preserve">6.8014440536499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76622009277344</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8590841293335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62852621078491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70537948608398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74700736999512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86548805236816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16329050064087</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09604597091675</t>
+    <t xml:space="preserve">6.80144453048706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76622152328491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85908365249634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.62852716445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70537805557251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.7470064163208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86548852920532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16329145431519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09604549407959</t>
   </si>
   <si>
     <t xml:space="preserve">7.06722640991211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02239513397217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23053741455078</t>
+    <t xml:space="preserve">7.02239608764648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23053693771362</t>
   </si>
   <si>
     <t xml:space="preserve">7.05762004852295</t>
   </si>
   <si>
-    <t xml:space="preserve">6.80464601516724</t>
+    <t xml:space="preserve">6.80464553833008</t>
   </si>
   <si>
     <t xml:space="preserve">6.89110565185547</t>
   </si>
   <si>
-    <t xml:space="preserve">6.71818733215332</t>
+    <t xml:space="preserve">6.71818780899048</t>
   </si>
   <si>
     <t xml:space="preserve">6.7374005317688</t>
@@ -1889,109 +1889,109 @@
     <t xml:space="preserve">7.01278877258301</t>
   </si>
   <si>
-    <t xml:space="preserve">6.88790273666382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.45880937576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39796924591064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1520414352417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15844488143921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">5.96375226974487</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10593032836914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.10721015930176</t>
+    <t xml:space="preserve">6.88790416717529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4588098526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39796876907349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15204048156738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15844535827637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">5.96375179290771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10592985153198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1072096824646</t>
   </si>
   <si>
     <t xml:space="preserve">6.39925003051758</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6445369720459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.63172817230225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59010028839111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50043869018555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.60290813446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59650421142578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.41718101501465</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52285385131836</t>
+    <t xml:space="preserve">6.64453649520874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6317286491394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59010124206543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50043916702271</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.60290861129761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59650468826294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.41718149185181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52285432815552</t>
   </si>
   <si>
     <t xml:space="preserve">6.4203839302063</t>
   </si>
   <si>
-    <t xml:space="preserve">6.47802400588989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.44600200653076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32624101638794</t>
+    <t xml:space="preserve">6.47802352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.44600248336792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32624006271362</t>
   </si>
   <si>
     <t xml:space="preserve">6.26732015609741</t>
   </si>
   <si>
-    <t xml:space="preserve">6.74380445480347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09924793243408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.30738925933838</t>
+    <t xml:space="preserve">6.74380540847778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09924650192261</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3073902130127</t>
   </si>
   <si>
     <t xml:space="preserve">7.19851493835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08964204788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1184606552124</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15368509292603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15688610076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17930316925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0448112487793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99357652664185</t>
+    <t xml:space="preserve">7.08964157104492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11846017837524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15368556976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15688705444336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17930221557617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04481029510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99357604980469</t>
   </si>
   <si>
     <t xml:space="preserve">7.27216577529907</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44828653335571</t>
+    <t xml:space="preserve">7.4482855796814</t>
   </si>
   <si>
     <t xml:space="preserve">7.75889778137207</t>
@@ -2000,46 +2000,46 @@
     <t xml:space="preserve">7.57637357711792</t>
   </si>
   <si>
-    <t xml:space="preserve">7.72687673568726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.83895206451416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.82614278793335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.84535646438599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.89979410171509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.9126033782959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.98305082321167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.88057994842529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91900777816772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23282146453857</t>
+    <t xml:space="preserve">7.7268762588501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.838951587677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.82614469528198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.84535694122314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.8997950553894</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91260290145874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.98305177688599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.88058042526245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91900730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23282051086426</t>
   </si>
   <si>
     <t xml:space="preserve">8.12074565887451</t>
   </si>
   <si>
-    <t xml:space="preserve">8.26164150238037</t>
+    <t xml:space="preserve">8.26164054870605</t>
   </si>
   <si>
     <t xml:space="preserve">8.47298622131348</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46337985992432</t>
+    <t xml:space="preserve">8.46337890625</t>
   </si>
   <si>
     <t xml:space="preserve">8.84764194488525</t>
@@ -2048,13 +2048,13 @@
     <t xml:space="preserve">8.91168594360352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.2639274597168</t>
+    <t xml:space="preserve">9.26392650604248</t>
   </si>
   <si>
     <t xml:space="preserve">9.33117198944092</t>
   </si>
   <si>
-    <t xml:space="preserve">9.53290939331055</t>
+    <t xml:space="preserve">9.53291034698486</t>
   </si>
   <si>
     <t xml:space="preserve">9.67700862884521</t>
@@ -2063,7 +2063,7 @@
     <t xml:space="preserve">9.51049423217773</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42083263397217</t>
+    <t xml:space="preserve">9.4208345413208</t>
   </si>
   <si>
     <t xml:space="preserve">9.32796859741211</t>
@@ -2072,10 +2072,10 @@
     <t xml:space="preserve">9.40482234954834</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47847270965576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.55212306976318</t>
+    <t xml:space="preserve">9.47847366333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.55212211608887</t>
   </si>
   <si>
     <t xml:space="preserve">9.5713357925415</t>
@@ -2087,16 +2087,16 @@
     <t xml:space="preserve">9.77627563476562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81470203399658</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0836868286133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0356531143188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1413249969482</t>
+    <t xml:space="preserve">9.8147029876709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.083685874939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0356540679932</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1413259506226</t>
   </si>
   <si>
     <t xml:space="preserve">10.21497631073</t>
@@ -2108,19 +2108,19 @@
     <t xml:space="preserve">10.2694129943848</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2790203094482</t>
+    <t xml:space="preserve">10.2790193557739</t>
   </si>
   <si>
     <t xml:space="preserve">10.56081199646</t>
   </si>
   <si>
-    <t xml:space="preserve">10.849009513855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8682222366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8874349594116</t>
+    <t xml:space="preserve">10.8490076065063</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8682203292847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8874340057373</t>
   </si>
   <si>
     <t xml:space="preserve">11.0155220031738</t>
@@ -2135,28 +2135,28 @@
     <t xml:space="preserve">11.2909097671509</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5118618011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5278730392456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.495849609375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.377368927002</t>
+    <t xml:space="preserve">11.5118598937988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5278720855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4958505630493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3773698806763</t>
   </si>
   <si>
     <t xml:space="preserve">11.3261337280273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4926471710205</t>
+    <t xml:space="preserve">11.4926462173462</t>
   </si>
   <si>
     <t xml:space="preserve">10.8105812072754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9899063110352</t>
+    <t xml:space="preserve">10.9899053573608</t>
   </si>
   <si>
     <t xml:space="preserve">10.5992383956909</t>
@@ -2168,19 +2168,19 @@
     <t xml:space="preserve">11.1404075622559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1141204833984</t>
+    <t xml:space="preserve">11.1141195297241</t>
   </si>
   <si>
     <t xml:space="preserve">10.7917680740356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7882642745972</t>
+    <t xml:space="preserve">10.7882652282715</t>
   </si>
   <si>
     <t xml:space="preserve">10.4203634262085</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5780363082886</t>
+    <t xml:space="preserve">10.5780353546143</t>
   </si>
   <si>
     <t xml:space="preserve">10.3993406295776</t>
@@ -2189,46 +2189,46 @@
     <t xml:space="preserve">10.4273710250854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2872180938721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3888282775879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4238681793213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3678064346313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7322034835815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7742500305176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4448890686035</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079593658447</t>
+    <t xml:space="preserve">10.2872190475464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3888292312622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.423867225647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3678073883057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7322025299072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7742490768433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4448900222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079584121704</t>
   </si>
   <si>
     <t xml:space="preserve">10.5149660110474</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6305923461914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8127908706665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1281356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1877002716064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3523817062378</t>
+    <t xml:space="preserve">10.6305932998657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8127918243408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1281366348267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1877012252808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3523797988892</t>
   </si>
   <si>
     <t xml:space="preserve">11.5731191635132</t>
@@ -2243,13 +2243,13 @@
     <t xml:space="preserve">11.7342967987061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429136276245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7097692489624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6291818618774</t>
+    <t xml:space="preserve">11.8429145812988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7097682952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6291809082031</t>
   </si>
   <si>
     <t xml:space="preserve">11.8639373779297</t>
@@ -2258,118 +2258,118 @@
     <t xml:space="preserve">11.9059829711914</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9199991226196</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0496387481689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2318391799927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2248306274414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2984113693237</t>
+    <t xml:space="preserve">11.9200000762939</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0496406555176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2318382263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2248315811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2984104156494</t>
   </si>
   <si>
     <t xml:space="preserve">12.214319229126</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3159322738647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2773895263672</t>
+    <t xml:space="preserve">12.3159313201904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2773885726929</t>
   </si>
   <si>
     <t xml:space="preserve">12.4175405502319</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684873580933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1267251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0391283035278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464183807373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636548995972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1407403945923</t>
+    <t xml:space="preserve">12.3684883117676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1267242431641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0391292572021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464202880859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636558532715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.140739440918</t>
   </si>
   <si>
     <t xml:space="preserve">12.1232204437256</t>
   </si>
   <si>
-    <t xml:space="preserve">12.109206199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0321207046509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8779535293579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760599136353</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6887474060059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4680061340332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4890298843384</t>
+    <t xml:space="preserve">12.1092052459717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0321216583252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8779544830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760608673096</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6887464523315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4680051803589</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4890289306641</t>
   </si>
   <si>
     <t xml:space="preserve">11.4820213317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6782360076904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2472648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0370359420776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1001043319702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7216911315918</t>
+    <t xml:space="preserve">11.6782350540161</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2472639083862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.037036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1001052856445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7216920852661</t>
   </si>
   <si>
     <t xml:space="preserve">10.9284172058105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1561651229858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.496036529541</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4469833374023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1841974258423</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3243474960327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2752952575684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.061562538147</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4049367904663</t>
+    <t xml:space="preserve">11.1561660766602</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4960374832153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4469814300537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.184196472168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3243494033813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2752962112427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0615615844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4049377441406</t>
   </si>
   <si>
     <t xml:space="preserve">11.2297458648682</t>
@@ -2378,16 +2378,16 @@
     <t xml:space="preserve">11.4119443893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4995393753052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.790358543396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8814573287964</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8288993835449</t>
+    <t xml:space="preserve">11.4995403289795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7903575897217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8814563751221</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8288984298706</t>
   </si>
   <si>
     <t xml:space="preserve">11.9550361633301</t>
@@ -2396,10 +2396,10 @@
     <t xml:space="preserve">11.6677227020264</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6712274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8113794326782</t>
+    <t xml:space="preserve">11.6712284088135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8113803863525</t>
   </si>
   <si>
     <t xml:space="preserve">11.9970836639404</t>
@@ -2408,10 +2408,10 @@
     <t xml:space="preserve">11.9410219192505</t>
   </si>
   <si>
-    <t xml:space="preserve">11.969051361084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.06715965271</t>
+    <t xml:space="preserve">11.9690523147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0671577453613</t>
   </si>
   <si>
     <t xml:space="preserve">12.2703819274902</t>
@@ -2423,16 +2423,16 @@
     <t xml:space="preserve">12.1021976470947</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0951910018921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9725551605225</t>
+    <t xml:space="preserve">12.0951900482178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9725570678711</t>
   </si>
   <si>
     <t xml:space="preserve">12.0146017074585</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0741672515869</t>
+    <t xml:space="preserve">12.0741662979126</t>
   </si>
   <si>
     <t xml:space="preserve">11.9865713119507</t>
@@ -2447,7 +2447,7 @@
     <t xml:space="preserve">11.5485935211182</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5941429138184</t>
+    <t xml:space="preserve">11.5941438674927</t>
   </si>
   <si>
     <t xml:space="preserve">11.4259605407715</t>
@@ -2459,58 +2459,58 @@
     <t xml:space="preserve">11.6852426528931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7693347930908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7027616500854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9480295181274</t>
+    <t xml:space="preserve">11.7693338394165</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7027626037598</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9480285644531</t>
   </si>
   <si>
     <t xml:space="preserve">12.0846796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2108144760132</t>
+    <t xml:space="preserve">12.2108154296875</t>
   </si>
   <si>
     <t xml:space="preserve">12.7539081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9641380310059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7188692092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7889471054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.795955657959</t>
+    <t xml:space="preserve">12.9641370773315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7188701629639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7889461517334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.795952796936</t>
   </si>
   <si>
     <t xml:space="preserve">12.9886646270752</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1743669509888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9080753326416</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0412216186523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2094068527222</t>
+    <t xml:space="preserve">13.1743650436401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9080762863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0412225723267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2094058990479</t>
   </si>
   <si>
     <t xml:space="preserve">13.6649017333984</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8996562957764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007034301758</t>
+    <t xml:space="preserve">13.8996572494507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007024765015</t>
   </si>
   <si>
     <t xml:space="preserve">14.365665435791</t>
@@ -2519,112 +2519,112 @@
     <t xml:space="preserve">14.6389646530151</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0173768997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1365079879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5289354324341</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9493913650513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181415557861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9213619232178</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1035594940186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9914388656616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1245861053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4118976593018</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5940952301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5100021362305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2086772918701</t>
+    <t xml:space="preserve">15.0173759460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1365060806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5289325714111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9493942260742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181396484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9213600158691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1035614013672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9914398193359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.124584197998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4118957519531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5940971374512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5100040435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2086734771729</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474987030029</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8863248825073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.486888885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8232545852661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7531805038452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7251462936401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1575288772583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3817749023438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2626438140869</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.297682762146</t>
+    <t xml:space="preserve">15.886326789856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.4868879318237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8232555389404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7531785964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7251501083374</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1575269699097</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3817739486694</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2626447677612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2976818084717</t>
   </si>
   <si>
     <t xml:space="preserve">15.0804452896118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2836647033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2205972671509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.09446144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0664291381836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0454072952271</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8562021255493</t>
+    <t xml:space="preserve">15.2836656570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2205963134766</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0944595336914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0664310455322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0454063415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8561992645264</t>
   </si>
   <si>
     <t xml:space="preserve">14.9122610092163</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1715459823608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8702173233032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721080780029</t>
+    <t xml:space="preserve">15.1715450286865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8702144622803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721090316772</t>
   </si>
   <si>
     <t xml:space="preserve">15.3537435531616</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5029945373535</t>
+    <t xml:space="preserve">16.5029964447021</t>
   </si>
   <si>
     <t xml:space="preserve">16.5800800323486</t>
@@ -2639,10 +2639,10 @@
     <t xml:space="preserve">16.8043251037598</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6221237182617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5660667419434</t>
+    <t xml:space="preserve">16.6221256256104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5660648345947</t>
   </si>
   <si>
     <t xml:space="preserve">16.9865226745605</t>
@@ -2651,34 +2651,34 @@
     <t xml:space="preserve">17.00754737854</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5380363464355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0545063018799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3978824615479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4959869384766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0685253143311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499582290649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5709800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0334854125977</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9423875808716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1666297912598</t>
+    <t xml:space="preserve">16.5380344390869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0545082092285</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3978805541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4959888458252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0685214996338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499572753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5709781646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.033483505249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9423847198486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1666278839111</t>
   </si>
   <si>
     <t xml:space="preserve">16.6431484222412</t>
@@ -2690,7 +2690,7 @@
     <t xml:space="preserve">16.762279510498</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7833023071289</t>
+    <t xml:space="preserve">16.7833003997803</t>
   </si>
   <si>
     <t xml:space="preserve">16.6711807250977</t>
@@ -2702,19 +2702,19 @@
     <t xml:space="preserve">16.9514865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6130285263062</t>
+    <t xml:space="preserve">15.6130266189575</t>
   </si>
   <si>
     <t xml:space="preserve">14.5198345184326</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3516521453857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5478649139404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7910394668579</t>
+    <t xml:space="preserve">14.3516502380371</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5478639602661</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7910404205322</t>
   </si>
   <si>
     <t xml:space="preserve">13.4546728134155</t>
@@ -2723,16 +2723,16 @@
     <t xml:space="preserve">13.0272064208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9956722259521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3474645614624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7202825546265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3327684402466</t>
+    <t xml:space="preserve">12.9956731796265</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3474655151367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7202806472778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3327674865723</t>
   </si>
   <si>
     <t xml:space="preserve">9.68806552886963</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">9.81069850921631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25149726867676</t>
+    <t xml:space="preserve">8.25149822235107</t>
   </si>
   <si>
     <t xml:space="preserve">9.51988220214844</t>
@@ -2750,61 +2750,61 @@
     <t xml:space="preserve">8.4442081451416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.02024555206299</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70490217208862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77497911453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49817705154419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59978723526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28653621673584</t>
+    <t xml:space="preserve">8.0202465057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70490121841431</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77497863769531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49817657470703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59978771209717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28653717041016</t>
   </si>
   <si>
     <t xml:space="preserve">9.06088161468506</t>
   </si>
   <si>
-    <t xml:space="preserve">9.69507217407227</t>
+    <t xml:space="preserve">9.69507312774658</t>
   </si>
   <si>
     <t xml:space="preserve">9.05036926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87167453765869</t>
+    <t xml:space="preserve">8.87167549133301</t>
   </si>
   <si>
     <t xml:space="preserve">9.2360725402832</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87517929077148</t>
+    <t xml:space="preserve">8.87517833709717</t>
   </si>
   <si>
     <t xml:space="preserve">9.07489585876465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.68246746063232</t>
+    <t xml:space="preserve">8.68246841430664</t>
   </si>
   <si>
     <t xml:space="preserve">9.0223388671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48834800720215</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1680889129639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381649017334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87727069854736</t>
+    <t xml:space="preserve">9.48834705352783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1680879592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381639480591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87727165222168</t>
   </si>
   <si>
     <t xml:space="preserve">9.29914093017578</t>
@@ -2813,10 +2813,10 @@
     <t xml:space="preserve">9.44630146026611</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51637649536133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58995914459229</t>
+    <t xml:space="preserve">9.51637744903564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58995819091797</t>
   </si>
   <si>
     <t xml:space="preserve">9.25359153747559</t>
@@ -2825,31 +2825,31 @@
     <t xml:space="preserve">9.33417892456055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49535465240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.47433280944824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3713102340698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.816294670105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2122268676758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8793640136719</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7602348327637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8618440628052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5324869155884</t>
+    <t xml:space="preserve">9.4953556060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.47433185577393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3713092803955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8162956237793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2122278213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8793649673462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.760232925415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8618450164795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5324859619141</t>
   </si>
   <si>
     <t xml:space="preserve">10.6025629043579</t>
@@ -2867,16 +2867,16 @@
     <t xml:space="preserve">11.0058345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4649333953857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.765435218811</t>
+    <t xml:space="preserve">10.4649343490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7654333114624</t>
   </si>
   <si>
     <t xml:space="preserve">10.6414775848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.769190788269</t>
+    <t xml:space="preserve">10.7691898345947</t>
   </si>
   <si>
     <t xml:space="preserve">10.8743658065796</t>
@@ -2891,7 +2891,7 @@
     <t xml:space="preserve">11.358922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1936473846436</t>
+    <t xml:space="preserve">11.1936483383179</t>
   </si>
   <si>
     <t xml:space="preserve">11.3251161575317</t>
@@ -2906,22 +2906,22 @@
     <t xml:space="preserve">12.0913925170898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6923952102661</t>
+    <t xml:space="preserve">12.6923961639404</t>
   </si>
   <si>
     <t xml:space="preserve">12.9966506958008</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4407253265381</t>
+    <t xml:space="preserve">12.4407243728638</t>
   </si>
   <si>
     <t xml:space="preserve">12.3956508636475</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6481552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6105918884277</t>
+    <t xml:space="preserve">11.648154258728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6105928421021</t>
   </si>
   <si>
     <t xml:space="preserve">11.5166854858398</t>
@@ -2933,28 +2933,28 @@
     <t xml:space="preserve">11.6669359207153</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5091724395752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7157678604126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5730295181274</t>
+    <t xml:space="preserve">11.5091733932495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7157669067383</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5730285644531</t>
   </si>
   <si>
     <t xml:space="preserve">11.8284549713135</t>
   </si>
   <si>
-    <t xml:space="preserve">11.2687730789185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4490728378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2011604309082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4791231155396</t>
+    <t xml:space="preserve">11.2687721252441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4490718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2011594772339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4791221618652</t>
   </si>
   <si>
     <t xml:space="preserve">11.4265356063843</t>
@@ -2963,22 +2963,22 @@
     <t xml:space="preserve">11.3664360046387</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6631784439087</t>
+    <t xml:space="preserve">11.6631803512573</t>
   </si>
   <si>
     <t xml:space="preserve">11.5429792404175</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7796230316162</t>
+    <t xml:space="preserve">11.7796239852905</t>
   </si>
   <si>
     <t xml:space="preserve">11.7608423233032</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4753656387329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6706924438477</t>
+    <t xml:space="preserve">11.4753665924072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6706914901733</t>
   </si>
   <si>
     <t xml:space="preserve">11.8585042953491</t>
@@ -2987,43 +2987,43 @@
     <t xml:space="preserve">11.8434810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3580875396729</t>
+    <t xml:space="preserve">12.3580884933472</t>
   </si>
   <si>
     <t xml:space="preserve">12.3205242156982</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8013257980347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6999073028564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7337131500244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8351306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5684375762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6097564697266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3731126785278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4369697570801</t>
+    <t xml:space="preserve">12.801326751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6999082565308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.733715057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.835132598877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5684385299683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6097555160522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3731117248535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4369688034058</t>
   </si>
   <si>
     <t xml:space="preserve">12.0763692855835</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0575866699219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3693571090698</t>
+    <t xml:space="preserve">12.0575857162476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3693561553955</t>
   </si>
   <si>
     <t xml:space="preserve">12.3505754470825</t>
@@ -3038,16 +3038,16 @@
     <t xml:space="preserve">12.470775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8276205062866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7938137054443</t>
+    <t xml:space="preserve">12.8276214599609</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7938146591187</t>
   </si>
   <si>
     <t xml:space="preserve">12.6585893630981</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5984878540039</t>
+    <t xml:space="preserve">12.5984888076782</t>
   </si>
   <si>
     <t xml:space="preserve">12.4557504653931</t>
@@ -3056,13 +3056,13 @@
     <t xml:space="preserve">12.515851020813</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3468189239502</t>
+    <t xml:space="preserve">12.3468179702759</t>
   </si>
   <si>
     <t xml:space="preserve">12.21910572052</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6661005020142</t>
+    <t xml:space="preserve">12.6661014556885</t>
   </si>
   <si>
     <t xml:space="preserve">12.6247825622559</t>
@@ -3071,13 +3071,13 @@
     <t xml:space="preserve">12.508337020874</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3881378173828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1740312576294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0650987625122</t>
+    <t xml:space="preserve">12.3881368637085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1740303039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0650997161865</t>
   </si>
   <si>
     <t xml:space="preserve">12.2641820907593</t>
@@ -3086,13 +3086,13 @@
     <t xml:space="preserve">11.9749488830566</t>
   </si>
   <si>
-    <t xml:space="preserve">12.1552486419678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8847990036011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688552856445</t>
+    <t xml:space="preserve">12.1552495956421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8847980499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688562393188</t>
   </si>
   <si>
     <t xml:space="preserve">12.1101751327515</t>
@@ -3104,19 +3104,19 @@
     <t xml:space="preserve">12.3843812942505</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5120935440063</t>
+    <t xml:space="preserve">12.5120944976807</t>
   </si>
   <si>
     <t xml:space="preserve">12.6285381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4257001876831</t>
+    <t xml:space="preserve">12.4257020950317</t>
   </si>
   <si>
     <t xml:space="preserve">11.8547487258911</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8322105407715</t>
+    <t xml:space="preserve">11.8322124481201</t>
   </si>
   <si>
     <t xml:space="preserve">11.8096742630005</t>
@@ -3128,10 +3128,10 @@
     <t xml:space="preserve">11.3326292037964</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7645978927612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5993232727051</t>
+    <t xml:space="preserve">11.7645988464355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5993242263794</t>
   </si>
   <si>
     <t xml:space="preserve">11.5842990875244</t>
@@ -3149,13 +3149,13 @@
     <t xml:space="preserve">11.8772869110107</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8359680175781</t>
+    <t xml:space="preserve">11.8359670639038</t>
   </si>
   <si>
     <t xml:space="preserve">11.9524116516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.200325012207</t>
+    <t xml:space="preserve">12.2003240585327</t>
   </si>
   <si>
     <t xml:space="preserve">12.2904748916626</t>
@@ -3164,40 +3164,40 @@
     <t xml:space="preserve">12.1139307022095</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4031629562378</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9448986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0989055633545</t>
+    <t xml:space="preserve">12.4031620025635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.944899559021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0989065170288</t>
   </si>
   <si>
     <t xml:space="preserve">12.1514921188354</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0801258087158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7007436752319</t>
+    <t xml:space="preserve">12.0801248550415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7007427215576</t>
   </si>
   <si>
     <t xml:space="preserve">11.5241985321045</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8255338668823</t>
+    <t xml:space="preserve">10.8255348205566</t>
   </si>
   <si>
     <t xml:space="preserve">10.6452341079712</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8893909454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2499923706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6443977355957</t>
+    <t xml:space="preserve">10.8893899917603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2499914169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.64439868927</t>
   </si>
   <si>
     <t xml:space="preserve">11.8209428787231</t>
@@ -3206,7 +3206,7 @@
     <t xml:space="preserve">12.0275363922119</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8885564804077</t>
+    <t xml:space="preserve">11.8885555267334</t>
   </si>
   <si>
     <t xml:space="preserve">12.5834636688232</t>
@@ -3215,10 +3215,10 @@
     <t xml:space="preserve">12.4332122802734</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4106740951538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1393890380859</t>
+    <t xml:space="preserve">12.4106750488281</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1393880844116</t>
   </si>
   <si>
     <t xml:space="preserve">13.2070016860962</t>
@@ -3227,19 +3227,19 @@
     <t xml:space="preserve">13.5600900650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2370519638062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2595882415771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2220268249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6727771759033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.357253074646</t>
+    <t xml:space="preserve">13.2370529174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2595891952515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2220277786255</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6727781295776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3572540283203</t>
   </si>
   <si>
     <t xml:space="preserve">13.379789352417</t>
@@ -3248,100 +3248,100 @@
     <t xml:space="preserve">13.2746133804321</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5375537872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882200241089</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821273803711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2896385192871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2295408248901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619281768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9327936172485</t>
+    <t xml:space="preserve">13.5375528335571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1882219314575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821264266968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2896404266357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2295389175415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619262695312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9327945709229</t>
   </si>
   <si>
     <t xml:space="preserve">13.1731948852539</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1919755935669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1957340240479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0154342651367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8238639831543</t>
+    <t xml:space="preserve">13.1919775009155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1957321166992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0154333114624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8238620758057</t>
   </si>
   <si>
     <t xml:space="preserve">13.3272018432617</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4361333847046</t>
+    <t xml:space="preserve">13.4361343383789</t>
   </si>
   <si>
     <t xml:space="preserve">13.4962339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4323768615723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3497409820557</t>
+    <t xml:space="preserve">13.4323759078979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.349739074707</t>
   </si>
   <si>
     <t xml:space="preserve">13.3384704589844</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1994886398315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.413595199585</t>
+    <t xml:space="preserve">13.1994895935059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4135961532593</t>
   </si>
   <si>
     <t xml:space="preserve">13.4248657226562</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3985710144043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.391058921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.680290222168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.209921836853</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9582538604736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8305406570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.89439868927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8380517959595</t>
+    <t xml:space="preserve">13.39857006073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3910598754883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6802883148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2099227905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9582529067993</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8305397033691</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8943967819214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8380527496338</t>
   </si>
   <si>
     <t xml:space="preserve">13.931960105896</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7328786849976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4398889541626</t>
+    <t xml:space="preserve">13.7328796386719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4398899078369</t>
   </si>
   <si>
     <t xml:space="preserve">13.4060831069946</t>
@@ -3350,13 +3350,13 @@
     <t xml:space="preserve">13.1093397140503</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3009071350098</t>
+    <t xml:space="preserve">13.3009090423584</t>
   </si>
   <si>
     <t xml:space="preserve">13.04172706604</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4887218475342</t>
+    <t xml:space="preserve">13.4887208938599</t>
   </si>
   <si>
     <t xml:space="preserve">13.5676021575928</t>
@@ -3365,49 +3365,49 @@
     <t xml:space="preserve">13.7216091156006</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3526592254639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5855484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0550813674927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0926418304443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0250310897827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1978168487549</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447313308716</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7207717895508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9198560714722</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8221921920776</t>
+    <t xml:space="preserve">14.3526601791382</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5855474472046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0550804138184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0926446914673</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.025032043457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1978178024292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447303771973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7207727432251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9198579788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8221912384033</t>
   </si>
   <si>
     <t xml:space="preserve">14.5329599380493</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6005735397339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4315414428711</t>
+    <t xml:space="preserve">14.6005725860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4315404891968</t>
   </si>
   <si>
     <t xml:space="preserve">14.2812919616699</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9499044418335</t>
+    <t xml:space="preserve">14.9499034881592</t>
   </si>
   <si>
     <t xml:space="preserve">14.7846307754517</t>
@@ -3416,52 +3416,52 @@
     <t xml:space="preserve">14.7095041275024</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6644306182861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7958974838257</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7620897293091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9123420715332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6606721878052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4090051651001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1948976516724</t>
+    <t xml:space="preserve">14.6644296646118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240293502808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7959003448486</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.762092590332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9123430252075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6606731414795</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4090032577515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1948986053467</t>
   </si>
   <si>
     <t xml:space="preserve">14.1197719573975</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2024097442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2775344848633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3226099014282</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4202728271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3714399337769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2925605773926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4653472900391</t>
+    <t xml:space="preserve">14.202410697937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2775354385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3226108551025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4202718734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3714408874512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2925586700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4653482437134</t>
   </si>
   <si>
     <t xml:space="preserve">14.7470664978027</t>
@@ -3470,31 +3470,31 @@
     <t xml:space="preserve">14.5930604934692</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8898029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8484859466553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2504062652588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1001558303833</t>
+    <t xml:space="preserve">14.8898048400879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.848484992981</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2504053115845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1001539230347</t>
   </si>
   <si>
     <t xml:space="preserve">15.1151809692383</t>
   </si>
   <si>
-    <t xml:space="preserve">15.0701036453247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1827936172485</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7245292663574</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7508220672607</t>
+    <t xml:space="preserve">15.0701055526733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1827926635742</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7245283126831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7508249282837</t>
   </si>
   <si>
     <t xml:space="preserve">14.814679145813</t>
@@ -3503,82 +3503,82 @@
     <t xml:space="preserve">14.8184366226196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9837121963501</t>
+    <t xml:space="preserve">14.9837112426758</t>
   </si>
   <si>
     <t xml:space="preserve">15.0175170898438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7921438217163</t>
+    <t xml:space="preserve">14.7921419143677</t>
   </si>
   <si>
     <t xml:space="preserve">14.9611740112305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1602563858032</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724454879761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.085129737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1377182006836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.355583190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2579183578491</t>
+    <t xml:space="preserve">15.1602582931519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724426269531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0851306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1377191543579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3555822372437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2579164505005</t>
   </si>
   <si>
     <t xml:space="preserve">15.2804565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2729415893555</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462310791016</t>
+    <t xml:space="preserve">15.2729454040527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462329864502</t>
   </si>
   <si>
     <t xml:space="preserve">15.8664321899414</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8438949584961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.641056060791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7086696624756</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6711053848267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1603355407715</t>
+    <t xml:space="preserve">15.8438940048218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6410551071167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.708667755127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6711082458496</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1603336334229</t>
   </si>
   <si>
     <t xml:space="preserve">16.0814266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8841571807861</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8999395370483</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.955174446106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.041971206665</t>
+    <t xml:space="preserve">15.8841562271118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8999404907227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9551753997803</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0419731140137</t>
   </si>
   <si>
     <t xml:space="preserve">16.0025196075439</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0972099304199</t>
+    <t xml:space="preserve">16.0972080230713</t>
   </si>
   <si>
     <t xml:space="preserve">16.144552230835</t>
@@ -3590,10 +3590,10 @@
     <t xml:space="preserve">16.4522953033447</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4128398895264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.326042175293</t>
+    <t xml:space="preserve">16.412841796875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3260402679443</t>
   </si>
   <si>
     <t xml:space="preserve">16.3497142791748</t>
@@ -3605,16 +3605,16 @@
     <t xml:space="preserve">16.1208820343018</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1919002532959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0183029174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9472846984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8762674331665</t>
+    <t xml:space="preserve">16.1918983459473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0183010101318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9472827911377</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8762683868408</t>
   </si>
   <si>
     <t xml:space="preserve">16.2392444610596</t>
@@ -3626,7 +3626,7 @@
     <t xml:space="preserve">16.5312042236328</t>
   </si>
   <si>
-    <t xml:space="preserve">16.1287746429443</t>
+    <t xml:space="preserve">16.1287727355957</t>
   </si>
   <si>
     <t xml:space="preserve">16.2155704498291</t>
@@ -3641,19 +3641,19 @@
     <t xml:space="preserve">16.5075302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4838581085205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4444026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.2550239562988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5233135223389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8073806762695</t>
+    <t xml:space="preserve">16.4838562011719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4444046020508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.2550258636475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5233116149902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8073787689209</t>
   </si>
   <si>
     <t xml:space="preserve">17.1624660491943</t>
@@ -3662,25 +3662,25 @@
     <t xml:space="preserve">17.5254421234131</t>
   </si>
   <si>
-    <t xml:space="preserve">17.3281707763672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1940288543701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2492637634277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.1387920379639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.4702072143555</t>
+    <t xml:space="preserve">17.3281726837158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1940307617188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2492656707764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.1387939453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.4702053070068</t>
   </si>
   <si>
     <t xml:space="preserve">17.4938793182373</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2808284759521</t>
+    <t xml:space="preserve">17.2808265686035</t>
   </si>
   <si>
     <t xml:space="preserve">17.4070796966553</t>
@@ -3692,25 +3692,25 @@
     <t xml:space="preserve">17.9042015075684</t>
   </si>
   <si>
-    <t xml:space="preserve">17.9120922088623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1093597412109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1172523498535</t>
+    <t xml:space="preserve">17.9120903015137</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1093616485596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1172504425049</t>
   </si>
   <si>
     <t xml:space="preserve">18.2592868804932</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3224105834961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2435035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4644470214844</t>
+    <t xml:space="preserve">18.3224124908447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2435054779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4644451141357</t>
   </si>
   <si>
     <t xml:space="preserve">18.2513942718506</t>
@@ -3719,70 +3719,70 @@
     <t xml:space="preserve">18.2829570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">18.424991607666</t>
+    <t xml:space="preserve">18.4249935150146</t>
   </si>
   <si>
     <t xml:space="preserve">18.3539752960205</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4407768249512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.5906963348389</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.669605255127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7485122680664</t>
+    <t xml:space="preserve">18.4407749176025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.5906982421875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.6696071624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.748514175415</t>
   </si>
   <si>
     <t xml:space="preserve">18.7642974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8037509918213</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.756404876709</t>
+    <t xml:space="preserve">18.8037490844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7011699676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7564067840576</t>
   </si>
   <si>
     <t xml:space="preserve">18.7406234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6459350585938</t>
+    <t xml:space="preserve">18.6459312438965</t>
   </si>
   <si>
     <t xml:space="preserve">18.7169494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5749168395996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.843204498291</t>
+    <t xml:space="preserve">18.5749206542969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8432025909424</t>
   </si>
   <si>
     <t xml:space="preserve">18.8984394073486</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9536743164062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1904010772705</t>
+    <t xml:space="preserve">18.9536762237549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.1903972625732</t>
   </si>
   <si>
     <t xml:space="preserve">19.0878200531006</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5591354370117</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8589839935303</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.9378929138184</t>
+    <t xml:space="preserve">18.5591373443604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8589859008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.937894821167</t>
   </si>
   <si>
     <t xml:space="preserve">19.2614154815674</t>
@@ -3806,31 +3806,31 @@
     <t xml:space="preserve">18.4013195037842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6222648620605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2356147766113</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1409244537354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4328842163086</t>
+    <t xml:space="preserve">18.6222610473633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2356128692627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1409225463867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.43288230896</t>
   </si>
   <si>
     <t xml:space="preserve">18.6380443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8353157043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7090587615967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5375919342041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4034519195557</t>
+    <t xml:space="preserve">18.8353137969971</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7090606689453</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5375938415527</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.403450012207</t>
   </si>
   <si>
     <t xml:space="preserve">19.5297031402588</t>
@@ -3839,25 +3839,25 @@
     <t xml:space="preserve">19.6007194519043</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8374443054199</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6322822570801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.6954097747803</t>
+    <t xml:space="preserve">19.8374423980713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6322803497314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.6954078674316</t>
   </si>
   <si>
     <t xml:space="preserve">19.640172958374</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9952602386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.0662746429443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1057281494141</t>
+    <t xml:space="preserve">19.9952583312988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.0662784576416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1057300567627</t>
   </si>
   <si>
     <t xml:space="preserve">20.0504951477051</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">20.0741672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0189342498779</t>
+    <t xml:space="preserve">20.0189304351807</t>
   </si>
   <si>
     <t xml:space="preserve">20.2398738861084</t>
@@ -3875,25 +3875,25 @@
     <t xml:space="preserve">20.9027004241943</t>
   </si>
   <si>
-    <t xml:space="preserve">21.1788768768311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">21.1946601867676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9421558380127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.9816093444824</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.6659774780273</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2162017822266</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.1372928619385</t>
+    <t xml:space="preserve">21.1788787841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">21.1946582794189</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9421539306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.9816074371338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.6659755706787</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2162036895752</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.1372947692871</t>
   </si>
   <si>
     <t xml:space="preserve">20.0820579528809</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">19.3324337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4744682312012</t>
+    <t xml:space="preserve">19.4744663238525</t>
   </si>
   <si>
     <t xml:space="preserve">19.3087596893311</t>
@@ -3920,19 +3920,19 @@
     <t xml:space="preserve">19.2377433776855</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2850875854492</t>
+    <t xml:space="preserve">19.2850894927979</t>
   </si>
   <si>
     <t xml:space="preserve">19.1272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.024694442749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8116416931152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.0168018341064</t>
+    <t xml:space="preserve">19.0246925354004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.8116397857666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.0168037414551</t>
   </si>
   <si>
     <t xml:space="preserve">18.7248420715332</t>
@@ -3944,22 +3944,22 @@
     <t xml:space="preserve">19.16672706604</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3561038970947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.4113426208496</t>
+    <t xml:space="preserve">19.3561058044434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.411340713501</t>
   </si>
   <si>
     <t xml:space="preserve">19.7269725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9005680084229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.9479141235352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.3403224945068</t>
+    <t xml:space="preserve">19.9005699157715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.9479160308838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.3403244018555</t>
   </si>
   <si>
     <t xml:space="preserve">19.5770454406738</t>
@@ -3971,31 +3971,31 @@
     <t xml:space="preserve">20.0268211364746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8711357116699</t>
+    <t xml:space="preserve">20.8711395263672</t>
   </si>
   <si>
     <t xml:space="preserve">20.9342632293701</t>
   </si>
   <si>
-    <t xml:space="preserve">20.5791797637939</t>
+    <t xml:space="preserve">20.5791778564453</t>
   </si>
   <si>
     <t xml:space="preserve">20.6817569732666</t>
   </si>
   <si>
-    <t xml:space="preserve">20.3187808990479</t>
+    <t xml:space="preserve">20.3187828063965</t>
   </si>
   <si>
     <t xml:space="preserve">19.8847885131836</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2119388580322</t>
+    <t xml:space="preserve">18.2119426727295</t>
   </si>
   <si>
     <t xml:space="preserve">18.2671756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3934268951416</t>
+    <t xml:space="preserve">18.3934288024902</t>
   </si>
   <si>
     <t xml:space="preserve">19.0325832366943</t>
@@ -4004,10 +4004,10 @@
     <t xml:space="preserve">18.8747673034668</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3303031921387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7958602905273</t>
+    <t xml:space="preserve">18.33030128479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7958583831787</t>
   </si>
   <si>
     <t xml:space="preserve">18.3697566986084</t>
@@ -4016,16 +4016,16 @@
     <t xml:space="preserve">18.3145198822021</t>
   </si>
   <si>
-    <t xml:space="preserve">17.8095092773438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.7463836669922</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9278717041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.641674041748</t>
+    <t xml:space="preserve">17.8095111846924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.7463855743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9278736114502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6416721343994</t>
   </si>
   <si>
     <t xml:space="preserve">17.1782474517822</t>
@@ -4034,13 +4034,13 @@
     <t xml:space="preserve">16.8862895965576</t>
   </si>
   <si>
-    <t xml:space="preserve">16.6337814331055</t>
+    <t xml:space="preserve">16.6337833404541</t>
   </si>
   <si>
     <t xml:space="preserve">15.4028205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4501638412476</t>
+    <t xml:space="preserve">15.4501647949219</t>
   </si>
   <si>
     <t xml:space="preserve">15.663215637207</t>
@@ -4049,25 +4049,25 @@
     <t xml:space="preserve">17.0756664276123</t>
   </si>
   <si>
-    <t xml:space="preserve">15.189769744873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5093441009521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.852593421936</t>
+    <t xml:space="preserve">15.1897687911987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5093469619751</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8525943756104</t>
   </si>
   <si>
     <t xml:space="preserve">17.0441055297852</t>
   </si>
   <si>
-    <t xml:space="preserve">16.791597366333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4759693145752</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8152694702148</t>
+    <t xml:space="preserve">16.7915992736816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4759654998779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8152713775635</t>
   </si>
   <si>
     <t xml:space="preserve">16.7837085723877</t>
@@ -4076,16 +4076,16 @@
     <t xml:space="preserve">16.4286212921143</t>
   </si>
   <si>
-    <t xml:space="preserve">16.744255065918</t>
+    <t xml:space="preserve">16.7442512512207</t>
   </si>
   <si>
     <t xml:space="preserve">17.2413730621338</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9415245056152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6732368469238</t>
+    <t xml:space="preserve">16.9415225982666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6732349395752</t>
   </si>
   <si>
     <t xml:space="preserve">16.7600364685059</t>
@@ -4097,37 +4097,37 @@
     <t xml:space="preserve">15.7579050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4107122421265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815780639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9157228469849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8920478820801</t>
+    <t xml:space="preserve">15.4107112884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815771102905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9157209396362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8920488357544</t>
   </si>
   <si>
     <t xml:space="preserve">15.8683776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6277074813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7973604202271</t>
+    <t xml:space="preserve">15.6277084350586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7973594665527</t>
   </si>
   <si>
     <t xml:space="preserve">15.7539596557617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8289203643799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0893173217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.0735378265381</t>
+    <t xml:space="preserve">15.8289213180542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.089319229126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0735397338867</t>
   </si>
   <si>
     <t xml:space="preserve">16.1761169433594</t>
@@ -4136,13 +4136,13 @@
     <t xml:space="preserve">15.9236125946045</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6395425796509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5132913589478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9964437484741</t>
+    <t xml:space="preserve">15.6395435333252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5132904052734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9964447021484</t>
   </si>
   <si>
     <t xml:space="preserve">15.1660957336426</t>
@@ -4151,7 +4151,7 @@
     <t xml:space="preserve">15.6868877410889</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7381801605225</t>
+    <t xml:space="preserve">15.7381792068481</t>
   </si>
   <si>
     <t xml:space="preserve">15.765796661377</t>
@@ -4160,10 +4160,10 @@
     <t xml:space="preserve">16.0261917114258</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8052520751953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4583625793457</t>
+    <t xml:space="preserve">15.8052530288696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4583644866943</t>
   </si>
   <si>
     <t xml:space="preserve">16.0873756408691</t>
@@ -4178,7 +4178,7 @@
     <t xml:space="preserve">16.7703304290771</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9305305480957</t>
+    <t xml:space="preserve">16.9305286407471</t>
   </si>
   <si>
     <t xml:space="preserve">16.8209209442139</t>
@@ -4199,7 +4199,7 @@
     <t xml:space="preserve">16.7366046905518</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5342464447021</t>
+    <t xml:space="preserve">16.5342483520508</t>
   </si>
   <si>
     <t xml:space="preserve">16.2012023925781</t>
@@ -4208,7 +4208,7 @@
     <t xml:space="preserve">14.7298984527588</t>
   </si>
   <si>
-    <t xml:space="preserve">14.4390096664429</t>
+    <t xml:space="preserve">14.4390106201172</t>
   </si>
   <si>
     <t xml:space="preserve">14.6287202835083</t>
@@ -4229,7 +4229,7 @@
     <t xml:space="preserve">14.506462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2197904586792</t>
+    <t xml:space="preserve">14.2197895050049</t>
   </si>
   <si>
     <t xml:space="preserve">14.6750926971436</t>
@@ -4250,13 +4250,13 @@
     <t xml:space="preserve">13.8277225494385</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9289016723633</t>
+    <t xml:space="preserve">13.9289026260376</t>
   </si>
   <si>
     <t xml:space="preserve">13.3724203109741</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7771339416504</t>
+    <t xml:space="preserve">13.7771348953247</t>
   </si>
   <si>
     <t xml:space="preserve">14.1523370742798</t>
@@ -4265,19 +4265,19 @@
     <t xml:space="preserve">14.3420476913452</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1354732513428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3546943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.198712348938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.621150970459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6801719665527</t>
+    <t xml:space="preserve">14.1354742050171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3546934127808</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1987113952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6211519241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6801729202271</t>
   </si>
   <si>
     <t xml:space="preserve">13.8108596801758</t>
@@ -4289,7 +4289,7 @@
     <t xml:space="preserve">13.6928186416626</t>
   </si>
   <si>
-    <t xml:space="preserve">13.760272026062</t>
+    <t xml:space="preserve">13.7602710723877</t>
   </si>
   <si>
     <t xml:space="preserve">13.7939977645874</t>
@@ -4298,13 +4298,13 @@
     <t xml:space="preserve">13.4609518051147</t>
   </si>
   <si>
-    <t xml:space="preserve">13.5494823455811</t>
+    <t xml:space="preserve">13.5494832992554</t>
   </si>
   <si>
     <t xml:space="preserve">14.3631258010864</t>
   </si>
   <si>
-    <t xml:space="preserve">14.3926372528076</t>
+    <t xml:space="preserve">14.3926362991333</t>
   </si>
   <si>
     <t xml:space="preserve">14.1312589645386</t>
@@ -4313,22 +4313,22 @@
     <t xml:space="preserve">14.4727363586426</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5739145278931</t>
+    <t xml:space="preserve">14.5739154815674</t>
   </si>
   <si>
     <t xml:space="preserve">14.2577314376831</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2956743240356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1944942474365</t>
+    <t xml:space="preserve">14.2956733703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1944952011108</t>
   </si>
   <si>
     <t xml:space="preserve">14.4600877761841</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5022459030151</t>
+    <t xml:space="preserve">14.5022468566895</t>
   </si>
   <si>
     <t xml:space="preserve">14.565484046936</t>
@@ -4346,13 +4346,13 @@
     <t xml:space="preserve">13.9794912338257</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7687034606934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9541969299316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.9415483474731</t>
+    <t xml:space="preserve">13.768702507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9541959762573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9415493011475</t>
   </si>
   <si>
     <t xml:space="preserve">13.8530187606812</t>
@@ -4370,13 +4370,13 @@
     <t xml:space="preserve">13.4356575012207</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1447687149048</t>
+    <t xml:space="preserve">13.1447696685791</t>
   </si>
   <si>
     <t xml:space="preserve">13.6295833587646</t>
   </si>
   <si>
-    <t xml:space="preserve">13.427225112915</t>
+    <t xml:space="preserve">13.4272260665894</t>
   </si>
   <si>
     <t xml:space="preserve">13.4946775436401</t>
@@ -4385,7 +4385,7 @@
     <t xml:space="preserve">13.5199718475342</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1692018508911</t>
+    <t xml:space="preserve">14.1692008972168</t>
   </si>
   <si>
     <t xml:space="preserve">14.0806703567505</t>
@@ -4394,16 +4394,16 @@
     <t xml:space="preserve">14.0722389221191</t>
   </si>
   <si>
-    <t xml:space="preserve">13.9162540435791</t>
+    <t xml:space="preserve">13.9162530899048</t>
   </si>
   <si>
     <t xml:space="preserve">13.7644882202148</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8572340011597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4735994338989</t>
+    <t xml:space="preserve">13.8572330474854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4735984802246</t>
   </si>
   <si>
     <t xml:space="preserve">13.1321220397949</t>
@@ -4415,10 +4415,10 @@
     <t xml:space="preserve">12.7527027130127</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5334825515747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.411226272583</t>
+    <t xml:space="preserve">12.5334815979004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4112253189087</t>
   </si>
   <si>
     <t xml:space="preserve">12.0065116882324</t>
@@ -4433,22 +4433,22 @@
     <t xml:space="preserve">13.1532011032104</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9044704437256</t>
+    <t xml:space="preserve">12.9044694900513</t>
   </si>
   <si>
     <t xml:space="preserve">12.7231922149658</t>
   </si>
   <si>
-    <t xml:space="preserve">12.5039720535278</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5503454208374</t>
+    <t xml:space="preserve">12.5039710998535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5503463745117</t>
   </si>
   <si>
     <t xml:space="preserve">12.4280881881714</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7324857711792</t>
+    <t xml:space="preserve">11.7324867248535</t>
   </si>
   <si>
     <t xml:space="preserve">12.0908260345459</t>
@@ -4457,7 +4457,7 @@
     <t xml:space="preserve">12.5292663574219</t>
   </si>
   <si>
-    <t xml:space="preserve">12.7948598861694</t>
+    <t xml:space="preserve">12.7948608398438</t>
   </si>
   <si>
     <t xml:space="preserve">12.8791751861572</t>
@@ -4472,7 +4472,7 @@
     <t xml:space="preserve">12.8960380554199</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3007516860962</t>
+    <t xml:space="preserve">13.3007526397705</t>
   </si>
   <si>
     <t xml:space="preserve">13.6843872070312</t>
@@ -4481,7 +4481,7 @@
     <t xml:space="preserve">13.532618522644</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7897815704346</t>
+    <t xml:space="preserve">13.7897806167603</t>
   </si>
   <si>
     <t xml:space="preserve">13.743408203125</t>
@@ -4490,7 +4490,7 @@
     <t xml:space="preserve">13.9963550567627</t>
   </si>
   <si>
-    <t xml:space="preserve">14.1101808547974</t>
+    <t xml:space="preserve">14.110179901123</t>
   </si>
   <si>
     <t xml:space="preserve">14.3462619781494</t>
@@ -4523,10 +4523,10 @@
     <t xml:space="preserve">16.799840927124</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3740463256836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4415016174316</t>
+    <t xml:space="preserve">16.3740482330322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.441499710083</t>
   </si>
   <si>
     <t xml:space="preserve">16.4035587310791</t>
@@ -4541,10 +4541,10 @@
     <t xml:space="preserve">16.2349281311035</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3993434906006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3023777008057</t>
+    <t xml:space="preserve">16.3993453979492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3023796081543</t>
   </si>
   <si>
     <t xml:space="preserve">16.6059150695801</t>
@@ -4568,7 +4568,7 @@
     <t xml:space="preserve">17.0570030212402</t>
   </si>
   <si>
-    <t xml:space="preserve">16.9558258056641</t>
+    <t xml:space="preserve">16.9558238983154</t>
   </si>
   <si>
     <t xml:space="preserve">16.2855167388916</t>
@@ -4577,7 +4577,7 @@
     <t xml:space="preserve">17.2677917480469</t>
   </si>
   <si>
-    <t xml:space="preserve">17.2593612670898</t>
+    <t xml:space="preserve">17.2593593597412</t>
   </si>
   <si>
     <t xml:space="preserve">17.2340660095215</t>
@@ -4592,7 +4592,7 @@
     <t xml:space="preserve">17.4617156982422</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6893692016602</t>
+    <t xml:space="preserve">17.6893672943115</t>
   </si>
   <si>
     <t xml:space="preserve">17.7146625518799</t>
@@ -4601,7 +4601,7 @@
     <t xml:space="preserve">17.8579998016357</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6472129821777</t>
+    <t xml:space="preserve">17.6472110748291</t>
   </si>
   <si>
     <t xml:space="preserve">17.8664302825928</t>
@@ -4619,7 +4619,7 @@
     <t xml:space="preserve">17.9676074981689</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3807525634766</t>
+    <t xml:space="preserve">18.3807544708252</t>
   </si>
   <si>
     <t xml:space="preserve">18.3891849517822</t>
@@ -4637,10 +4637,10 @@
     <t xml:space="preserve">19.1901817321777</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1311626434326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.1648864746094</t>
+    <t xml:space="preserve">19.131160736084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.164888381958</t>
   </si>
   <si>
     <t xml:space="preserve">18.8444881439209</t>
@@ -4664,16 +4664,16 @@
     <t xml:space="preserve">19.4431266784668</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3250885009766</t>
+    <t xml:space="preserve">19.3250865936279</t>
   </si>
   <si>
     <t xml:space="preserve">19.2913608551025</t>
   </si>
   <si>
-    <t xml:space="preserve">19.3166542053223</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8141174316406</t>
+    <t xml:space="preserve">19.3166561126709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.814115524292</t>
   </si>
   <si>
     <t xml:space="preserve">19.8984336853027</t>
@@ -4691,7 +4691,7 @@
     <t xml:space="preserve">19.8309783935547</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1564540863037</t>
+    <t xml:space="preserve">19.1564559936523</t>
   </si>
   <si>
     <t xml:space="preserve">19.5358753204346</t>
@@ -4703,7 +4703,7 @@
     <t xml:space="preserve">19.0890026092529</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2070465087891</t>
+    <t xml:space="preserve">19.2070446014404</t>
   </si>
   <si>
     <t xml:space="preserve">19.0552787780762</t>
@@ -4718,7 +4718,7 @@
     <t xml:space="preserve">18.9456672668457</t>
   </si>
   <si>
-    <t xml:space="preserve">18.9793949127197</t>
+    <t xml:space="preserve">18.9793930053711</t>
   </si>
   <si>
     <t xml:space="preserve">19.1058673858643</t>
@@ -4733,7 +4733,7 @@
     <t xml:space="preserve">18.1952590942383</t>
   </si>
   <si>
-    <t xml:space="preserve">17.6134853363037</t>
+    <t xml:space="preserve">17.6134834289551</t>
   </si>
   <si>
     <t xml:space="preserve">16.7745456695557</t>
@@ -4748,16 +4748,16 @@
     <t xml:space="preserve">16.0114936828613</t>
   </si>
   <si>
-    <t xml:space="preserve">16.466796875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9052333831787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.3782634735107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1126689910889</t>
+    <t xml:space="preserve">16.4667949676514</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9052352905273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.3782653808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1126708984375</t>
   </si>
   <si>
     <t xml:space="preserve">16.1337490081787</t>
@@ -4766,7 +4766,7 @@
     <t xml:space="preserve">16.3487529754639</t>
   </si>
   <si>
-    <t xml:space="preserve">16.643856048584</t>
+    <t xml:space="preserve">16.6438579559326</t>
   </si>
   <si>
     <t xml:space="preserve">16.6101322174072</t>
@@ -4790,16 +4790,16 @@
     <t xml:space="preserve">17.124454498291</t>
   </si>
   <si>
-    <t xml:space="preserve">17.0232772827148</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2003402709961</t>
+    <t xml:space="preserve">17.0232791900635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2003383636475</t>
   </si>
   <si>
     <t xml:space="preserve">17.2424983978271</t>
   </si>
   <si>
-    <t xml:space="preserve">17.107593536377</t>
+    <t xml:space="preserve">17.1075916290283</t>
   </si>
   <si>
     <t xml:space="preserve">17.0148468017578</t>
@@ -4811,31 +4811,31 @@
     <t xml:space="preserve">17.0654335021973</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8124904632568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5806217193604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9726867675781</t>
+    <t xml:space="preserve">16.8124885559082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5806198120117</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9726848602295</t>
   </si>
   <si>
     <t xml:space="preserve">17.0822982788086</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8546466827393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.9895496368408</t>
+    <t xml:space="preserve">16.8546447753906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.9895515441895</t>
   </si>
   <si>
     <t xml:space="preserve">17.0738658905029</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8504314422607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2509269714355</t>
+    <t xml:space="preserve">16.8504295349121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2509288787842</t>
   </si>
   <si>
     <t xml:space="preserve">17.4084911346436</t>
@@ -6414,6 +6414,9 @@
   </si>
   <si>
     <t xml:space="preserve">35.810001373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">36.0200004577637</t>
   </si>
 </sst>
 </file>
@@ -71934,7 +71937,7 @@
     </row>
     <row r="2508">
       <c r="A2508" s="1" t="n">
-        <v>45971.6928240741</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2508" t="n">
         <v>1120979</v>
@@ -71955,6 +71958,32 @@
         <v>2133</v>
       </c>
       <c r="H2508" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2509">
+      <c r="A2509" s="1" t="n">
+        <v>45972.6911111111</v>
+      </c>
+      <c r="B2509" t="n">
+        <v>530499</v>
+      </c>
+      <c r="C2509" t="n">
+        <v>36.3800010681152</v>
+      </c>
+      <c r="D2509" t="n">
+        <v>35.8400001525879</v>
+      </c>
+      <c r="E2509" t="n">
+        <v>35.9799995422363</v>
+      </c>
+      <c r="F2509" t="n">
+        <v>36.0200004577637</v>
+      </c>
+      <c r="G2509" t="s">
+        <v>2134</v>
+      </c>
+      <c r="H2509" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/AZM.MI.xlsx
+++ b/data/AZM.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2135" uniqueCount="2135">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2136" uniqueCount="2136">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8295078277588</t>
+    <t xml:space="preserve">10.8295068740845</t>
   </si>
   <si>
     <t xml:space="preserve">AZM.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7068357467651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4860258102417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1916122436523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.9119176864624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.93645286560059</t>
+    <t xml:space="preserve">10.7068347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4860239028931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1916131973267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.91191959381104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.93645191192627</t>
   </si>
   <si>
     <t xml:space="preserve">10.2259616851807</t>
@@ -68,7 +68,7 @@
     <t xml:space="preserve">9.61750602722168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.33290481567383</t>
+    <t xml:space="preserve">9.33290767669678</t>
   </si>
   <si>
     <t xml:space="preserve">9.1513500213623</t>
@@ -77,34 +77,34 @@
     <t xml:space="preserve">9.37706756591797</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85693836212158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25930309295654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.53899765014648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48992729187012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50955486297607</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40160274505615</t>
+    <t xml:space="preserve">8.85693740844727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.25930213928223</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.53899574279785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4899263381958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.50955390930176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40160179138184</t>
   </si>
   <si>
     <t xml:space="preserve">9.12681770324707</t>
   </si>
   <si>
-    <t xml:space="preserve">9.49483489990234</t>
+    <t xml:space="preserve">9.49483394622803</t>
   </si>
   <si>
     <t xml:space="preserve">9.43595123291016</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84712409973145</t>
+    <t xml:space="preserve">8.84712505340576</t>
   </si>
   <si>
     <t xml:space="preserve">8.99433040618896</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">8.79805564880371</t>
   </si>
   <si>
-    <t xml:space="preserve">8.05711460113525</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.86574649810791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32699298858643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.61058759689331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67928314208984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.10127544403076</t>
+    <t xml:space="preserve">8.05711364746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.86574506759644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32699489593506</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.61058664321899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.679283618927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.10127735137939</t>
   </si>
   <si>
     <t xml:space="preserve">7.8706521987915</t>
@@ -137,76 +137,76 @@
     <t xml:space="preserve">8.53799057006836</t>
   </si>
   <si>
-    <t xml:space="preserve">8.78333568572998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46929359436035</t>
+    <t xml:space="preserve">8.78333473205566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.46929454803467</t>
   </si>
   <si>
     <t xml:space="preserve">8.61649894714355</t>
   </si>
   <si>
-    <t xml:space="preserve">8.50364112854004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.21413612365723</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.69010448455811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71954345703125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.29365062713623</t>
+    <t xml:space="preserve">8.50364208221436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.21413516998291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.69010353088379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71954441070557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.29365158081055</t>
   </si>
   <si>
     <t xml:space="preserve">9.30837154388428</t>
   </si>
   <si>
-    <t xml:space="preserve">9.47520542144775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.09737491607666</t>
+    <t xml:space="preserve">9.47520732879639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.09737586975098</t>
   </si>
   <si>
     <t xml:space="preserve">9.22004890441895</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41141700744629</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.48011207580566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.77943325042725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.66166877746582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79415416717529</t>
+    <t xml:space="preserve">9.41141796112061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4801139831543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.77943420410156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.6616678237915</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79415321350098</t>
   </si>
   <si>
     <t xml:space="preserve">9.77452659606934</t>
   </si>
   <si>
-    <t xml:space="preserve">9.68620204925537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.64694881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.72545719146729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2357749938965</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3044700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.83831596374512</t>
+    <t xml:space="preserve">9.68620014190674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.64694690704346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.7254581451416</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2357740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3044710159302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.8383150100708</t>
   </si>
   <si>
     <t xml:space="preserve">9.56843566894531</t>
@@ -218,130 +218,130 @@
     <t xml:space="preserve">9.93154621124268</t>
   </si>
   <si>
-    <t xml:space="preserve">9.74508380889893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3780727386475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5449066162109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4369583129883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5547208786011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5056533813477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5498151779175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5007467269897</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5694427490234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4173288345337</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4811191558838</t>
+    <t xml:space="preserve">9.74508476257324</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3780736923218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5449075698853</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4369564056396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5547218322754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.505654335022</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5498142242432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5007476806641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5694408416748</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4173278808594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4811182022095</t>
   </si>
   <si>
     <t xml:space="preserve">10.7411832809448</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8442277908325</t>
+    <t xml:space="preserve">10.8442296981812</t>
   </si>
   <si>
     <t xml:space="preserve">10.785346031189</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5988845825195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2406826019287</t>
+    <t xml:space="preserve">10.5988826751709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2406816482544</t>
   </si>
   <si>
     <t xml:space="preserve">10.2897500991821</t>
   </si>
   <si>
-    <t xml:space="preserve">9.73036575317383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.57334423065186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.43104457855225</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.40650939941406</t>
+    <t xml:space="preserve">9.73036670684814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57334327697754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.43104267120361</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.40650844573975</t>
   </si>
   <si>
     <t xml:space="preserve">9.19060611724854</t>
   </si>
   <si>
-    <t xml:space="preserve">9.08265495300293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.35253238677979</t>
+    <t xml:space="preserve">9.08265686035156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.35253524780273</t>
   </si>
   <si>
     <t xml:space="preserve">9.47029972076416</t>
   </si>
   <si>
-    <t xml:space="preserve">9.27892971038818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30346393585205</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.14644336700439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.52970123291016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.79665470123291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1190118789673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89235401153564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.95279598236084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1492338180542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.84702205657959</t>
+    <t xml:space="preserve">9.2789306640625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30346488952637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.14644432067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52970218658447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.79665565490723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1190137863159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89235496520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.95279502868652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1492319107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.84702301025391</t>
   </si>
   <si>
     <t xml:space="preserve">9.76643371582031</t>
   </si>
   <si>
-    <t xml:space="preserve">9.42896461486816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42392826080322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5246639251709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.54984855651855</t>
+    <t xml:space="preserve">9.42896556854248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42392730712891</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.52466487884521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.54984951019287</t>
   </si>
   <si>
     <t xml:space="preserve">9.39370632171631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82958030700684</t>
+    <t xml:space="preserve">8.82958221435547</t>
   </si>
   <si>
     <t xml:space="preserve">8.4820384979248</t>
@@ -350,85 +350,85 @@
     <t xml:space="preserve">8.28560161590576</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46189117431641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53744411468506</t>
+    <t xml:space="preserve">8.46189022064209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53744316101074</t>
   </si>
   <si>
     <t xml:space="preserve">8.68351268768311</t>
   </si>
   <si>
-    <t xml:space="preserve">9.39874267578125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.50451755523682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.81680107116699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.46692848205566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.46459722518921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5754075050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49985456466675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.34874963760376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.43941307067871</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.20268154144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8702507019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50256109237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.62848091125488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8601770401001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.02135467529297</t>
+    <t xml:space="preserve">9.39874362945557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.5045166015625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.81680011749268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.4669303894043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.46459770202637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57540655136108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49985551834106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.34875011444092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.43941211700439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.20268106460571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87025022506714</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50256013870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.6284818649292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86017560958862</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.02135562896729</t>
   </si>
   <si>
     <t xml:space="preserve">7.38904523849487</t>
   </si>
   <si>
-    <t xml:space="preserve">7.20771837234497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.44948530197144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.66607189178467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.52503967285156</t>
+    <t xml:space="preserve">7.20771884918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.44948673248291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.66607093811035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.52503871917725</t>
   </si>
   <si>
     <t xml:space="preserve">7.64592409133911</t>
   </si>
   <si>
-    <t xml:space="preserve">7.79702758789062</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.71140193939209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.94309711456299</t>
+    <t xml:space="preserve">7.79702854156494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.71140289306641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.9430980682373</t>
   </si>
   <si>
     <t xml:space="preserve">7.81717491149902</t>
@@ -440,37 +440,37 @@
     <t xml:space="preserve">7.08179807662964</t>
   </si>
   <si>
-    <t xml:space="preserve">6.92565488815308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71410942077637</t>
+    <t xml:space="preserve">6.92565584182739</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71410799026489</t>
   </si>
   <si>
     <t xml:space="preserve">6.78966045379639</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90047025680542</t>
+    <t xml:space="preserve">6.90047073364258</t>
   </si>
   <si>
     <t xml:space="preserve">7.22786569595337</t>
   </si>
   <si>
-    <t xml:space="preserve">7.27823305130005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.32860374450684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31852865219116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3991174697876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.15734958648682</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94580268859863</t>
+    <t xml:space="preserve">7.27823448181152</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.32860279083252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.31852912902832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.39911794662476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15735006332397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94580316543579</t>
   </si>
   <si>
     <t xml:space="preserve">7.19764471054077</t>
@@ -482,40 +482,40 @@
     <t xml:space="preserve">7.02639150619507</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08683490753174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04150295257568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.85010194778442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.8652138710022</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.93069219589233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.22282934188843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.31349277496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23290348052979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.29838180541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.98105955123901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01128244400024</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.53781890869141</t>
+    <t xml:space="preserve">7.08683443069458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04150342941284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.85010242462158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86521339416504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.93069124221802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.22282838821411</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.3134913444519</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23290205001831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.29838228225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.98106098175049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01128101348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.53781795501709</t>
   </si>
   <si>
     <t xml:space="preserve">6.79973411560059</t>
@@ -530,31 +530,31 @@
     <t xml:space="preserve">6.94076585769653</t>
   </si>
   <si>
-    <t xml:space="preserve">6.90550756454468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.668776512146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.46226501464844</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.57307720184326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.6738133430481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59826135635376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.87528657913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00624370574951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.1523118019104</t>
+    <t xml:space="preserve">6.90550851821899</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.66877698898315</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.4622654914856</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.57307767868042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.67381381988525</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59826040267944</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.87528705596924</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00624513626099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.15231227874756</t>
   </si>
   <si>
     <t xml:space="preserve">7.30341863632202</t>
@@ -563,25 +563,25 @@
     <t xml:space="preserve">7.62577629089355</t>
   </si>
   <si>
-    <t xml:space="preserve">7.66103410720825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.5703706741333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45452451705933</t>
+    <t xml:space="preserve">7.66103363037109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.57037115097046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45452404022217</t>
   </si>
   <si>
     <t xml:space="preserve">7.5351128578186</t>
   </si>
   <si>
-    <t xml:space="preserve">7.44445085525513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59555625915527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.72147607803345</t>
+    <t xml:space="preserve">7.44445037841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59555435180664</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72147560119629</t>
   </si>
   <si>
     <t xml:space="preserve">7.60562944412231</t>
@@ -590,37 +590,37 @@
     <t xml:space="preserve">7.70636606216431</t>
   </si>
   <si>
-    <t xml:space="preserve">7.48474502563477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.3638596534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.26312398910522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.13216543197632</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99617147445679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17245960235596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.69629192352295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91791296005249</t>
+    <t xml:space="preserve">7.48474407196045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.36386108398438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.26312494277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.13216495513916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99617290496826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17246055603027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.69629287719727</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91791248321533</t>
   </si>
   <si>
     <t xml:space="preserve">8.35611820220947</t>
   </si>
   <si>
-    <t xml:space="preserve">8.38633823394775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51729488372803</t>
+    <t xml:space="preserve">8.38633918762207</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51729679107666</t>
   </si>
   <si>
     <t xml:space="preserve">8.45181751251221</t>
@@ -635,40 +635,40 @@
     <t xml:space="preserve">7.95820713043213</t>
   </si>
   <si>
-    <t xml:space="preserve">7.93132162094116</t>
+    <t xml:space="preserve">7.93132257461548</t>
   </si>
   <si>
     <t xml:space="preserve">7.71623516082764</t>
   </si>
   <si>
-    <t xml:space="preserve">7.73236799240112</t>
+    <t xml:space="preserve">7.73236656188965</t>
   </si>
   <si>
     <t xml:space="preserve">7.63557767868042</t>
   </si>
   <si>
-    <t xml:space="preserve">7.64095401763916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.45813274383545</t>
+    <t xml:space="preserve">7.64095449447632</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.45813179016113</t>
   </si>
   <si>
     <t xml:space="preserve">7.44200038909912</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57105302810669</t>
+    <t xml:space="preserve">7.57105255126953</t>
   </si>
   <si>
     <t xml:space="preserve">7.68935012817383</t>
   </si>
   <si>
-    <t xml:space="preserve">7.62482404708862</t>
+    <t xml:space="preserve">7.62482309341431</t>
   </si>
   <si>
     <t xml:space="preserve">7.79689359664917</t>
   </si>
   <si>
-    <t xml:space="preserve">8.20018100738525</t>
+    <t xml:space="preserve">8.20017910003662</t>
   </si>
   <si>
     <t xml:space="preserve">8.43139839172363</t>
@@ -680,28 +680,28 @@
     <t xml:space="preserve">8.54431915283203</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46903991699219</t>
+    <t xml:space="preserve">8.46903800964355</t>
   </si>
   <si>
     <t xml:space="preserve">8.58733749389648</t>
   </si>
   <si>
-    <t xml:space="preserve">8.70025634765625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54969596862793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.6034688949585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53356552124023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.59809112548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51743316650391</t>
+    <t xml:space="preserve">8.70025730133057</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54969692230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.60346794128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53356456756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5980920791626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.51743412017822</t>
   </si>
   <si>
     <t xml:space="preserve">8.52818775177002</t>
@@ -710,40 +710,40 @@
     <t xml:space="preserve">8.67874908447266</t>
   </si>
   <si>
-    <t xml:space="preserve">9.11429882049561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.15731716156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20033359527588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.17882442474365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05515003204346</t>
+    <t xml:space="preserve">9.11429977416992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.15731620788574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2003345489502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.17882537841797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05514907836914</t>
   </si>
   <si>
     <t xml:space="preserve">9.33476257324219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.13043022155762</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.44768333435059</t>
+    <t xml:space="preserve">9.13043212890625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4476842880249</t>
   </si>
   <si>
     <t xml:space="preserve">9.38315868377686</t>
   </si>
   <si>
-    <t xml:space="preserve">9.41004276275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.45843696594238</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4530611038208</t>
+    <t xml:space="preserve">9.41004371643066</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.4584379196167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.45306015014648</t>
   </si>
   <si>
     <t xml:space="preserve">9.37240219116211</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">8.92609786987305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.0927906036377</t>
+    <t xml:space="preserve">9.09278964996338</t>
   </si>
   <si>
     <t xml:space="preserve">9.07128238677979</t>
@@ -782,37 +782,37 @@
     <t xml:space="preserve">9.28636932373047</t>
   </si>
   <si>
-    <t xml:space="preserve">9.24335289001465</t>
+    <t xml:space="preserve">9.24335193634033</t>
   </si>
   <si>
     <t xml:space="preserve">9.26485919952393</t>
   </si>
   <si>
-    <t xml:space="preserve">9.23259830474854</t>
+    <t xml:space="preserve">9.23259544372559</t>
   </si>
   <si>
     <t xml:space="preserve">9.24872779846191</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96373748779297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.49592590332031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.5927152633667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.52281093597412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.66799259185791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73789691925049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71101188659668</t>
+    <t xml:space="preserve">8.96373844146729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.495924949646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.59271430969238</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5228099822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.66799449920654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7378978729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71101093292236</t>
   </si>
   <si>
     <t xml:space="preserve">8.70563411712646</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">8.6357307434082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53894138336182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.50130176544189</t>
+    <t xml:space="preserve">8.53894233703613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.50130271911621</t>
   </si>
   <si>
     <t xml:space="preserve">8.28621482849121</t>
   </si>
   <si>
-    <t xml:space="preserve">8.33460998535156</t>
+    <t xml:space="preserve">8.33460903167725</t>
   </si>
   <si>
     <t xml:space="preserve">8.43677616119385</t>
@@ -842,43 +842,43 @@
     <t xml:space="preserve">8.62497520446777</t>
   </si>
   <si>
-    <t xml:space="preserve">8.56582736968994</t>
+    <t xml:space="preserve">8.56582832336426</t>
   </si>
   <si>
     <t xml:space="preserve">8.47979259490967</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66261672973633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.61422157287598</t>
+    <t xml:space="preserve">8.66261577606201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.61422252655029</t>
   </si>
   <si>
     <t xml:space="preserve">8.78091526031494</t>
   </si>
   <si>
-    <t xml:space="preserve">8.77016162872314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79166793823242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.18420219421387</t>
+    <t xml:space="preserve">8.77016067504883</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79166984558105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.18420314788818</t>
   </si>
   <si>
     <t xml:space="preserve">9.04977226257324</t>
   </si>
   <si>
-    <t xml:space="preserve">9.14118480682373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.16269493103027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.30249977111816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13580799102783</t>
+    <t xml:space="preserve">9.14118576049805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.16269397735596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.30249881744385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13580703735352</t>
   </si>
   <si>
     <t xml:space="preserve">9.14656162261963</t>
@@ -887,52 +887,52 @@
     <t xml:space="preserve">9.20571041107178</t>
   </si>
   <si>
-    <t xml:space="preserve">9.62513065338135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.63050746917725</t>
+    <t xml:space="preserve">9.62513160705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.63050651550293</t>
   </si>
   <si>
     <t xml:space="preserve">9.60899829864502</t>
   </si>
   <si>
-    <t xml:space="preserve">9.63588428497314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.7165412902832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97464561462402</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0553045272827</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2435035705566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4155731201172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3456707000732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2327489852905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3994426727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4101972579956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3349170684814</t>
+    <t xml:space="preserve">9.63588619232178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71654033660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97464656829834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0553026199341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.243504524231</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4155750274658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3456697463989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2327518463135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3994436264038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4101963043213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3349161148071</t>
   </si>
   <si>
     <t xml:space="preserve">10.1305847167969</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1036977767944</t>
+    <t xml:space="preserve">10.1036987304688</t>
   </si>
   <si>
     <t xml:space="preserve">10.3295383453369</t>
@@ -947,16 +947,16 @@
     <t xml:space="preserve">10.6074905395508</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5847997665405</t>
+    <t xml:space="preserve">10.5847988128662</t>
   </si>
   <si>
     <t xml:space="preserve">10.4770221710205</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2387790679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.27281665802</t>
+    <t xml:space="preserve">10.2387809753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2728147506714</t>
   </si>
   <si>
     <t xml:space="preserve">10.3408842086792</t>
@@ -968,40 +968,40 @@
     <t xml:space="preserve">10.0856237411499</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90410614013672</t>
+    <t xml:space="preserve">9.9041051864624</t>
   </si>
   <si>
     <t xml:space="preserve">10.2898321151733</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2614707946777</t>
+    <t xml:space="preserve">10.2614698410034</t>
   </si>
   <si>
     <t xml:space="preserve">10.1083126068115</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0062103271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.94381141662598</t>
+    <t xml:space="preserve">10.0062093734741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.94381237030029</t>
   </si>
   <si>
     <t xml:space="preserve">10.1707105636597</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1366758346558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.062933921814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1990728378296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3522272109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2104177474976</t>
+    <t xml:space="preserve">10.1366748809814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0629329681396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1990718841553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3522281646729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2104167938232</t>
   </si>
   <si>
     <t xml:space="preserve">10.1934003829956</t>
@@ -1013,28 +1013,28 @@
     <t xml:space="preserve">10.1480207443237</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2444515228271</t>
+    <t xml:space="preserve">10.2444524765015</t>
   </si>
   <si>
     <t xml:space="preserve">10.2841606140137</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2217626571655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0912952423096</t>
+    <t xml:space="preserve">10.2217636108398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0912971496582</t>
   </si>
   <si>
     <t xml:space="preserve">10.1593656539917</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5450925827026</t>
+    <t xml:space="preserve">10.545093536377</t>
   </si>
   <si>
     <t xml:space="preserve">10.4089546203613</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3181953430176</t>
+    <t xml:space="preserve">10.3181943893433</t>
   </si>
   <si>
     <t xml:space="preserve">10.2955055236816</t>
@@ -1043,13 +1043,13 @@
     <t xml:space="preserve">10.3692464828491</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4316453933716</t>
+    <t xml:space="preserve">10.4316434860229</t>
   </si>
   <si>
     <t xml:space="preserve">10.397608757019</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7152662277222</t>
+    <t xml:space="preserve">10.7152652740479</t>
   </si>
   <si>
     <t xml:space="preserve">10.6415252685547</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">10.669885635376</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7776613235474</t>
+    <t xml:space="preserve">10.777663230896</t>
   </si>
   <si>
     <t xml:space="preserve">10.7039222717285</t>
@@ -1073,46 +1073,46 @@
     <t xml:space="preserve">10.6585416793823</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5394201278687</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3068504333496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7095928192139</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5564374923706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4826946258545</t>
+    <t xml:space="preserve">10.539421081543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3068513870239</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7095937728882</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5564384460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4826955795288</t>
   </si>
   <si>
     <t xml:space="preserve">10.3352117538452</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2331075668335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2784881591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0288991928101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0402450561523</t>
+    <t xml:space="preserve">10.2331085205078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2784872055054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0289011001587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.040244102478</t>
   </si>
   <si>
     <t xml:space="preserve">10.0969696044922</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0345726013184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.98351955413818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.96082878112793</t>
+    <t xml:space="preserve">10.034571647644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.9835205078125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.96082973480225</t>
   </si>
   <si>
     <t xml:space="preserve">9.98919200897217</t>
@@ -1127,19 +1127,19 @@
     <t xml:space="preserve">10.4940395355225</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5110578536987</t>
+    <t xml:space="preserve">10.511058807373</t>
   </si>
   <si>
     <t xml:space="preserve">10.4146270751953</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3635740280151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3805904388428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4600067138672</t>
+    <t xml:space="preserve">10.3635730743408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3805923461914</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4600048065186</t>
   </si>
   <si>
     <t xml:space="preserve">10.5167303085327</t>
@@ -1148,34 +1148,34 @@
     <t xml:space="preserve">10.3465566635132</t>
   </si>
   <si>
-    <t xml:space="preserve">9.84738063812256</t>
+    <t xml:space="preserve">9.84738159179688</t>
   </si>
   <si>
     <t xml:space="preserve">9.86439800262451</t>
   </si>
   <si>
-    <t xml:space="preserve">9.7282600402832</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67720794677734</t>
+    <t xml:space="preserve">9.72825908660889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67720699310303</t>
   </si>
   <si>
     <t xml:space="preserve">9.66018962860107</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48434448242188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.688551902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.58644771575928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.71124076843262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.67153358459473</t>
+    <t xml:space="preserve">9.48434352874756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.68855285644531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.58644866943359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.71124172210693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.67153453826904</t>
   </si>
   <si>
     <t xml:space="preserve">9.6148099899292</t>
@@ -1190,19 +1190,19 @@
     <t xml:space="preserve">9.78498458862305</t>
   </si>
   <si>
-    <t xml:space="preserve">9.79632949829102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.89843368530273</t>
+    <t xml:space="preserve">9.79633045196533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.89843273162842</t>
   </si>
   <si>
     <t xml:space="preserve">9.16101360321045</t>
   </si>
   <si>
-    <t xml:space="preserve">8.95113468170166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.99084091186523</t>
+    <t xml:space="preserve">8.95113182067871</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.99083995819092</t>
   </si>
   <si>
     <t xml:space="preserve">8.76961326599121</t>
@@ -1214,34 +1214,34 @@
     <t xml:space="preserve">8.86604499816895</t>
   </si>
   <si>
-    <t xml:space="preserve">8.85470008850098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05891036987305</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.24042892456055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25177383422852</t>
+    <t xml:space="preserve">8.85470104217529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05891132354736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.24042797088623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.2517728805542</t>
   </si>
   <si>
     <t xml:space="preserve">9.10996150970459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.09294414520264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98516654968262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.075927734375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13265228271484</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.05323600769043</t>
+    <t xml:space="preserve">9.09294319152832</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98516845703125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.07592582702637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13265132904053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.05323696136475</t>
   </si>
   <si>
     <t xml:space="preserve">8.90008068084717</t>
@@ -1250,19 +1250,19 @@
     <t xml:space="preserve">8.88306331634521</t>
   </si>
   <si>
-    <t xml:space="preserve">8.82633972167969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.79230403900146</t>
+    <t xml:space="preserve">8.82633876800537</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.79230308532715</t>
   </si>
   <si>
     <t xml:space="preserve">8.79797649383545</t>
   </si>
   <si>
-    <t xml:space="preserve">8.96815013885498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.0021858215332</t>
+    <t xml:space="preserve">8.9681510925293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.00218391418457</t>
   </si>
   <si>
     <t xml:space="preserve">9.07025527954102</t>
@@ -1277,73 +1277,73 @@
     <t xml:space="preserve">8.92277145385742</t>
   </si>
   <si>
-    <t xml:space="preserve">9.04189205169678</t>
+    <t xml:space="preserve">9.04189300537109</t>
   </si>
   <si>
     <t xml:space="preserve">9.03054714202881</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01352882385254</t>
+    <t xml:space="preserve">9.01352977752686</t>
   </si>
   <si>
     <t xml:space="preserve">9.04756450653076</t>
   </si>
   <si>
-    <t xml:space="preserve">9.03621959686279</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.13832378387451</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.97382164001465</t>
+    <t xml:space="preserve">9.03622055053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.13832187652588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.97382354736328</t>
   </si>
   <si>
     <t xml:space="preserve">9.12697887420654</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16668701171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.19504833221436</t>
+    <t xml:space="preserve">9.16668605804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.19504928588867</t>
   </si>
   <si>
     <t xml:space="preserve">9.37089538574219</t>
   </si>
   <si>
-    <t xml:space="preserve">9.38223838806152</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.34253120422363</t>
+    <t xml:space="preserve">9.38223934173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.34253215789795</t>
   </si>
   <si>
     <t xml:space="preserve">9.46732616424561</t>
   </si>
   <si>
-    <t xml:space="preserve">10.67555809021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4202976226807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.3919363021851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5961437225342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7549724578857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7379560470581</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7606468200684</t>
+    <t xml:space="preserve">10.6755599975586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4202995300293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.3919353485107</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5961446762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7549734115601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7379550933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7606449127197</t>
   </si>
   <si>
     <t xml:space="preserve">10.6613779067993</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4543333053589</t>
+    <t xml:space="preserve">10.4543323516846</t>
   </si>
   <si>
     <t xml:space="preserve">10.4032821655273</t>
@@ -1355,10 +1355,10 @@
     <t xml:space="preserve">10.3777561187744</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0742797851562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1338386535645</t>
+    <t xml:space="preserve">10.0742788314819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1338376998901</t>
   </si>
   <si>
     <t xml:space="preserve">10.0941324234009</t>
@@ -1376,7 +1376,7 @@
     <t xml:space="preserve">10.2359437942505</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1622018814087</t>
+    <t xml:space="preserve">10.1622009277344</t>
   </si>
   <si>
     <t xml:space="preserve">10.2416172027588</t>
@@ -1391,13 +1391,13 @@
     <t xml:space="preserve">10.1678743362427</t>
   </si>
   <si>
-    <t xml:space="preserve">9.90694046020508</t>
+    <t xml:space="preserve">9.90693950653076</t>
   </si>
   <si>
     <t xml:space="preserve">9.92963123321533</t>
   </si>
   <si>
-    <t xml:space="preserve">10.1877279281616</t>
+    <t xml:space="preserve">10.1877269744873</t>
   </si>
   <si>
     <t xml:space="preserve">10.2302713394165</t>
@@ -1412,7 +1412,7 @@
     <t xml:space="preserve">10.182056427002</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0317354202271</t>
+    <t xml:space="preserve">10.0317344665527</t>
   </si>
   <si>
     <t xml:space="preserve">9.9778470993042</t>
@@ -1427,13 +1427,13 @@
     <t xml:space="preserve">9.89559650421143</t>
   </si>
   <si>
-    <t xml:space="preserve">9.81334590911865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.97500991821289</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.065770149231</t>
+    <t xml:space="preserve">9.81334495544434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.97501087188721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0657711029053</t>
   </si>
   <si>
     <t xml:space="preserve">10.1395120620728</t>
@@ -1451,7 +1451,7 @@
     <t xml:space="preserve">9.83603572845459</t>
   </si>
   <si>
-    <t xml:space="preserve">9.89275932312012</t>
+    <t xml:space="preserve">9.89276027679443</t>
   </si>
   <si>
     <t xml:space="preserve">9.8672342300415</t>
@@ -1460,46 +1460,46 @@
     <t xml:space="preserve">9.8275260925293</t>
   </si>
   <si>
-    <t xml:space="preserve">9.77931118011475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.8331995010376</t>
+    <t xml:space="preserve">9.77931213378906</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.83319854736328</t>
   </si>
   <si>
     <t xml:space="preserve">9.94948482513428</t>
   </si>
   <si>
-    <t xml:space="preserve">10.0714426040649</t>
+    <t xml:space="preserve">10.0714416503906</t>
   </si>
   <si>
     <t xml:space="preserve">9.93814086914062</t>
   </si>
   <si>
-    <t xml:space="preserve">9.71407794952393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.42761898040771</t>
+    <t xml:space="preserve">9.71407699584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42761993408203</t>
   </si>
   <si>
     <t xml:space="preserve">9.10145282745361</t>
   </si>
   <si>
-    <t xml:space="preserve">9.21773815155029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.12414360046387</t>
+    <t xml:space="preserve">9.21773910522461</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.12414264678955</t>
   </si>
   <si>
     <t xml:space="preserve">9.24326419830322</t>
   </si>
   <si>
-    <t xml:space="preserve">9.20072174072266</t>
+    <t xml:space="preserve">9.20072078704834</t>
   </si>
   <si>
     <t xml:space="preserve">9.29274559020996</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51369667053223</t>
+    <t xml:space="preserve">9.51369762420654</t>
   </si>
   <si>
     <t xml:space="preserve">9.39841747283936</t>
@@ -1508,16 +1508,16 @@
     <t xml:space="preserve">9.47206783294678</t>
   </si>
   <si>
-    <t xml:space="preserve">9.44004726409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.33757591247559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.98533535003662</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.02696514129639</t>
+    <t xml:space="preserve">9.4400463104248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.3375768661499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.98533630371094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.02696323394775</t>
   </si>
   <si>
     <t xml:space="preserve">8.89887619018555</t>
@@ -1526,25 +1526,25 @@
     <t xml:space="preserve">9.34397983551025</t>
   </si>
   <si>
-    <t xml:space="preserve">9.31836223602295</t>
+    <t xml:space="preserve">9.31836318969727</t>
   </si>
   <si>
     <t xml:space="preserve">8.93730354309082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.92129039764404</t>
+    <t xml:space="preserve">8.92129135131836</t>
   </si>
   <si>
     <t xml:space="preserve">8.93410110473633</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64590263366699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.83803558349609</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.7547779083252</t>
+    <t xml:space="preserve">8.64590358734131</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.83803462982178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.75477695465088</t>
   </si>
   <si>
     <t xml:space="preserve">8.72275638580322</t>
@@ -1553,10 +1553,10 @@
     <t xml:space="preserve">8.71635150909424</t>
   </si>
   <si>
-    <t xml:space="preserve">8.64270305633545</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.82842922210693</t>
+    <t xml:space="preserve">8.64270114898682</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.82842826843262</t>
   </si>
   <si>
     <t xml:space="preserve">8.8060131072998</t>
@@ -1565,19 +1565,19 @@
     <t xml:space="preserve">8.83163070678711</t>
   </si>
   <si>
-    <t xml:space="preserve">8.66511631011963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.73556423187256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.51781558990479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.4889965057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.56905078887939</t>
+    <t xml:space="preserve">8.66511726379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.73556613922119</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.5178165435791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.48899745941162</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.56905174255371</t>
   </si>
   <si>
     <t xml:space="preserve">8.45697498321533</t>
@@ -1586,22 +1586,22 @@
     <t xml:space="preserve">8.39613342285156</t>
   </si>
   <si>
-    <t xml:space="preserve">8.51141262054443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53062534332275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.53702831268311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.54343414306641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.71314907073975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.40573978424072</t>
+    <t xml:space="preserve">8.5114107131958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53062629699707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.53703022003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.54343318939209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.71315002441406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.40574073791504</t>
   </si>
   <si>
     <t xml:space="preserve">8.36411190032959</t>
@@ -1619,7 +1619,7 @@
     <t xml:space="preserve">8.5722541809082</t>
   </si>
   <si>
-    <t xml:space="preserve">8.46017646789551</t>
+    <t xml:space="preserve">8.46017837524414</t>
   </si>
   <si>
     <t xml:space="preserve">8.46658134460449</t>
@@ -1634,7 +1634,7 @@
     <t xml:space="preserve">9.09421062469482</t>
   </si>
   <si>
-    <t xml:space="preserve">9.01735782623291</t>
+    <t xml:space="preserve">9.01735877990723</t>
   </si>
   <si>
     <t xml:space="preserve">9.05578327178955</t>
@@ -1646,7 +1646,7 @@
     <t xml:space="preserve">9.18707370758057</t>
   </si>
   <si>
-    <t xml:space="preserve">8.9180908203125</t>
+    <t xml:space="preserve">8.91808986663818</t>
   </si>
   <si>
     <t xml:space="preserve">8.87646198272705</t>
@@ -1655,31 +1655,31 @@
     <t xml:space="preserve">9.03657054901123</t>
   </si>
   <si>
-    <t xml:space="preserve">9.18387126922607</t>
+    <t xml:space="preserve">9.18387222290039</t>
   </si>
   <si>
     <t xml:space="preserve">9.15505218505859</t>
   </si>
   <si>
-    <t xml:space="preserve">9.1518497467041</t>
+    <t xml:space="preserve">9.15184879302979</t>
   </si>
   <si>
     <t xml:space="preserve">9.23510646820068</t>
   </si>
   <si>
-    <t xml:space="preserve">9.16465854644775</t>
+    <t xml:space="preserve">9.16465950012207</t>
   </si>
   <si>
     <t xml:space="preserve">9.1262321472168</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26072311401367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.25431823730469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.20628547668457</t>
+    <t xml:space="preserve">9.26072216033936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.254319190979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.20628643035889</t>
   </si>
   <si>
     <t xml:space="preserve">9.20948886871338</t>
@@ -1688,7 +1688,7 @@
     <t xml:space="preserve">9.22550010681152</t>
   </si>
   <si>
-    <t xml:space="preserve">9.10701751708984</t>
+    <t xml:space="preserve">9.10701847076416</t>
   </si>
   <si>
     <t xml:space="preserve">8.92769718170166</t>
@@ -1697,13 +1697,13 @@
     <t xml:space="preserve">8.76758670806885</t>
   </si>
   <si>
-    <t xml:space="preserve">8.65871334075928</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.68112659454346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.72595882415771</t>
+    <t xml:space="preserve">8.65871143341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.68112945556641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.7259578704834</t>
   </si>
   <si>
     <t xml:space="preserve">8.61708450317383</t>
@@ -1724,28 +1724,28 @@
     <t xml:space="preserve">8.95331382751465</t>
   </si>
   <si>
-    <t xml:space="preserve">8.97252750396729</t>
+    <t xml:space="preserve">8.97252559661865</t>
   </si>
   <si>
     <t xml:space="preserve">8.9661226272583</t>
   </si>
   <si>
-    <t xml:space="preserve">8.86685562133789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.86044979095459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.32568550109863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.22321605682373</t>
+    <t xml:space="preserve">8.86685466766357</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.86045169830322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.32568454742432</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.22321510314941</t>
   </si>
   <si>
     <t xml:space="preserve">8.29366302490234</t>
   </si>
   <si>
-    <t xml:space="preserve">8.53382778167725</t>
+    <t xml:space="preserve">8.53382682800293</t>
   </si>
   <si>
     <t xml:space="preserve">8.48259258270264</t>
@@ -1754,25 +1754,25 @@
     <t xml:space="preserve">8.40253734588623</t>
   </si>
   <si>
-    <t xml:space="preserve">8.14956569671631</t>
+    <t xml:space="preserve">8.14956474304199</t>
   </si>
   <si>
     <t xml:space="preserve">8.06630706787109</t>
   </si>
   <si>
-    <t xml:space="preserve">8.07271289825439</t>
+    <t xml:space="preserve">8.07271194458008</t>
   </si>
   <si>
     <t xml:space="preserve">7.77490997314453</t>
   </si>
   <si>
-    <t xml:space="preserve">7.74929094314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.67884397506714</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.87417650222778</t>
+    <t xml:space="preserve">7.74929046630859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.67884349822998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.87417602539062</t>
   </si>
   <si>
     <t xml:space="preserve">7.73007822036743</t>
@@ -1781,22 +1781,22 @@
     <t xml:space="preserve">7.53474473953247</t>
   </si>
   <si>
-    <t xml:space="preserve">7.42266893386841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.25295305252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.21772813796997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.0800347328186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11205577850342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.84947776794434</t>
+    <t xml:space="preserve">7.42266988754272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.25295209884644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.21772861480713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.08003616333008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11205530166626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.84947729110718</t>
   </si>
   <si>
     <t xml:space="preserve">6.97115993499756</t>
@@ -1805,112 +1805,112 @@
     <t xml:space="preserve">7.04160833358765</t>
   </si>
   <si>
-    <t xml:space="preserve">7.03520345687866</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04801225662231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.94234132766724</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95194721221924</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.00958585739136</t>
+    <t xml:space="preserve">7.03520393371582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04801273345947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.94234085083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.9519476890564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.00958728790283</t>
   </si>
   <si>
     <t xml:space="preserve">7.1312689781189</t>
   </si>
   <si>
-    <t xml:space="preserve">6.97436189651489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.83026361465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95514869689941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.80144453048706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.76622152328491</t>
+    <t xml:space="preserve">6.97436141967773</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8302640914917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95515012741089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.8014440536499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.76622104644775</t>
   </si>
   <si>
     <t xml:space="preserve">6.85908365249634</t>
   </si>
   <si>
-    <t xml:space="preserve">6.62852716445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.70537805557251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7470064163208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.86548852920532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.16329145431519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09604549407959</t>
+    <t xml:space="preserve">6.6285252571106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.70537900924683</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74700689315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.86548805236816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.16329193115234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09604644775391</t>
   </si>
   <si>
     <t xml:space="preserve">7.06722640991211</t>
   </si>
   <si>
-    <t xml:space="preserve">7.02239608764648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.23053693771362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.05762004852295</t>
+    <t xml:space="preserve">7.02239513397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.23053741455078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.05761909484863</t>
   </si>
   <si>
     <t xml:space="preserve">6.80464553833008</t>
   </si>
   <si>
-    <t xml:space="preserve">6.89110565185547</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.71818780899048</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.7374005317688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.95835208892822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.01278877258301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.88790416717529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4588098526001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.39796876907349</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15204048156738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.15844535827637</t>
+    <t xml:space="preserve">6.89110469818115</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.71818733215332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.73740100860596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.95835161209106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.01278924942017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.88790321350098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.45881032943726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.39796924591064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.1520414352417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.15844488143921</t>
   </si>
   <si>
     <t xml:space="preserve">5.96375179290771</t>
   </si>
   <si>
-    <t xml:space="preserve">6.10592985153198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.1072096824646</t>
+    <t xml:space="preserve">6.10592937469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.10721063613892</t>
   </si>
   <si>
     <t xml:space="preserve">6.39925003051758</t>
@@ -1919,13 +1919,13 @@
     <t xml:space="preserve">6.64453649520874</t>
   </si>
   <si>
-    <t xml:space="preserve">6.6317286491394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.59010124206543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.50043916702271</t>
+    <t xml:space="preserve">6.63172817230225</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.59010028839111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.50043869018555</t>
   </si>
   <si>
     <t xml:space="preserve">6.60290861129761</t>
@@ -1934,31 +1934,31 @@
     <t xml:space="preserve">6.59650468826294</t>
   </si>
   <si>
-    <t xml:space="preserve">6.41718149185181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.52285432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.4203839302063</t>
+    <t xml:space="preserve">6.41718101501465</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.52285480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.42038440704346</t>
   </si>
   <si>
     <t xml:space="preserve">6.47802352905273</t>
   </si>
   <si>
-    <t xml:space="preserve">6.44600248336792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.32624006271362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.26732015609741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.74380540847778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.09924650192261</t>
+    <t xml:space="preserve">6.44600105285645</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.32624101638794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.26731967926025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.74380445480347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.09924840927124</t>
   </si>
   <si>
     <t xml:space="preserve">7.3073902130127</t>
@@ -1967,25 +1967,25 @@
     <t xml:space="preserve">7.19851493835449</t>
   </si>
   <si>
-    <t xml:space="preserve">7.08964157104492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.11846017837524</t>
+    <t xml:space="preserve">7.08964204788208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.11846160888672</t>
   </si>
   <si>
     <t xml:space="preserve">7.15368556976318</t>
   </si>
   <si>
-    <t xml:space="preserve">7.15688705444336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.17930221557617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.04481029510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">6.99357604980469</t>
+    <t xml:space="preserve">7.1568865776062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.17930269241333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.04481077194214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6.99357557296753</t>
   </si>
   <si>
     <t xml:space="preserve">7.27216577529907</t>
@@ -1997,58 +1997,58 @@
     <t xml:space="preserve">7.75889778137207</t>
   </si>
   <si>
-    <t xml:space="preserve">7.57637357711792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.7268762588501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.838951587677</t>
+    <t xml:space="preserve">7.5763726234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.72687673568726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.83895206451416</t>
   </si>
   <si>
     <t xml:space="preserve">7.82614469528198</t>
   </si>
   <si>
-    <t xml:space="preserve">7.84535694122314</t>
+    <t xml:space="preserve">7.84535646438599</t>
   </si>
   <si>
     <t xml:space="preserve">7.8997950553894</t>
   </si>
   <si>
-    <t xml:space="preserve">7.91260290145874</t>
+    <t xml:space="preserve">7.9126033782959</t>
   </si>
   <si>
     <t xml:space="preserve">7.98305177688599</t>
   </si>
   <si>
-    <t xml:space="preserve">7.88058042526245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.91900730133057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.23282051086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.12074565887451</t>
+    <t xml:space="preserve">7.88058090209961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.91900777816772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.23282146453857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.1207447052002</t>
   </si>
   <si>
     <t xml:space="preserve">8.26164054870605</t>
   </si>
   <si>
-    <t xml:space="preserve">8.47298622131348</t>
+    <t xml:space="preserve">8.47298526763916</t>
   </si>
   <si>
     <t xml:space="preserve">8.46337890625</t>
   </si>
   <si>
-    <t xml:space="preserve">8.84764194488525</t>
+    <t xml:space="preserve">8.84764099121094</t>
   </si>
   <si>
     <t xml:space="preserve">8.91168594360352</t>
   </si>
   <si>
-    <t xml:space="preserve">9.26392650604248</t>
+    <t xml:space="preserve">9.2639274597168</t>
   </si>
   <si>
     <t xml:space="preserve">9.33117198944092</t>
@@ -2060,13 +2060,13 @@
     <t xml:space="preserve">9.67700862884521</t>
   </si>
   <si>
-    <t xml:space="preserve">9.51049423217773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.4208345413208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.32796859741211</t>
+    <t xml:space="preserve">9.51049327850342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.42083263397217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.32796955108643</t>
   </si>
   <si>
     <t xml:space="preserve">9.40482234954834</t>
@@ -2075,10 +2075,10 @@
     <t xml:space="preserve">9.47847366333008</t>
   </si>
   <si>
-    <t xml:space="preserve">9.55212211608887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.5713357925415</t>
+    <t xml:space="preserve">9.55212306976318</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.57133674621582</t>
   </si>
   <si>
     <t xml:space="preserve">9.7026252746582</t>
@@ -2087,55 +2087,55 @@
     <t xml:space="preserve">9.77627563476562</t>
   </si>
   <si>
-    <t xml:space="preserve">9.8147029876709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.083685874939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0356540679932</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1413259506226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.21497631073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1957626342773</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2694129943848</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2790193557739</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.56081199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8490076065063</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8682203292847</t>
+    <t xml:space="preserve">9.81470203399658</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0836868286133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0356531143188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1413249969482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2149753570557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.195761680603</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2694120407104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2790184020996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5608129501343</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8490085601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8682222366333</t>
   </si>
   <si>
     <t xml:space="preserve">10.8874340057373</t>
   </si>
   <si>
-    <t xml:space="preserve">11.0155220031738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0603523254395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2813034057617</t>
+    <t xml:space="preserve">11.0155210494995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0603513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.281304359436</t>
   </si>
   <si>
     <t xml:space="preserve">11.2909097671509</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5118598937988</t>
+    <t xml:space="preserve">11.5118608474731</t>
   </si>
   <si>
     <t xml:space="preserve">11.5278720855713</t>
@@ -2144,19 +2144,19 @@
     <t xml:space="preserve">11.4958505630493</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3773698806763</t>
+    <t xml:space="preserve">11.3773679733276</t>
   </si>
   <si>
     <t xml:space="preserve">11.3261337280273</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4926462173462</t>
+    <t xml:space="preserve">11.4926471710205</t>
   </si>
   <si>
     <t xml:space="preserve">10.8105812072754</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9899053573608</t>
+    <t xml:space="preserve">10.9899063110352</t>
   </si>
   <si>
     <t xml:space="preserve">10.5992383956909</t>
@@ -2168,13 +2168,13 @@
     <t xml:space="preserve">11.1404075622559</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1141195297241</t>
+    <t xml:space="preserve">11.1141204833984</t>
   </si>
   <si>
     <t xml:space="preserve">10.7917680740356</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7882652282715</t>
+    <t xml:space="preserve">10.7882642745972</t>
   </si>
   <si>
     <t xml:space="preserve">10.4203634262085</t>
@@ -2183,13 +2183,13 @@
     <t xml:space="preserve">10.5780353546143</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3993406295776</t>
+    <t xml:space="preserve">10.3993396759033</t>
   </si>
   <si>
     <t xml:space="preserve">10.4273710250854</t>
   </si>
   <si>
-    <t xml:space="preserve">10.2872190475464</t>
+    <t xml:space="preserve">10.2872180938721</t>
   </si>
   <si>
     <t xml:space="preserve">10.3888292312622</t>
@@ -2198,43 +2198,43 @@
     <t xml:space="preserve">10.423867225647</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3678073883057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7322025299072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7742490768433</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.4448900222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5079584121704</t>
+    <t xml:space="preserve">10.3678064346313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7322034835815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7742500305176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.4448890686035</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.5079593658447</t>
   </si>
   <si>
     <t xml:space="preserve">10.5149660110474</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6305932998657</t>
+    <t xml:space="preserve">10.6305923461914</t>
   </si>
   <si>
     <t xml:space="preserve">10.8127918243408</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1281366348267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.1877012252808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3523797988892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5731191635132</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6151676177979</t>
+    <t xml:space="preserve">11.1281356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1877002716064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.3523807525635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5731201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6151666641235</t>
   </si>
   <si>
     <t xml:space="preserve">11.7553195953369</t>
@@ -2243,37 +2243,37 @@
     <t xml:space="preserve">11.7342967987061</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8429145812988</t>
+    <t xml:space="preserve">11.8429136276245</t>
   </si>
   <si>
     <t xml:space="preserve">11.7097682952881</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6291809082031</t>
+    <t xml:space="preserve">11.6291818618774</t>
   </si>
   <si>
     <t xml:space="preserve">11.8639373779297</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9059829711914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9200000762939</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0496406555176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2318382263184</t>
+    <t xml:space="preserve">11.9059839248657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9199991226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0496397018433</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2318391799927</t>
   </si>
   <si>
     <t xml:space="preserve">12.2248315811157</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2984104156494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.214319229126</t>
+    <t xml:space="preserve">12.2984113693237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2143201828003</t>
   </si>
   <si>
     <t xml:space="preserve">12.3159313201904</t>
@@ -2285,91 +2285,91 @@
     <t xml:space="preserve">12.4175405502319</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3684883117676</t>
+    <t xml:space="preserve">12.3684873580933</t>
   </si>
   <si>
     <t xml:space="preserve">12.1267242431641</t>
   </si>
   <si>
-    <t xml:space="preserve">12.0391292572021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8464202880859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0636558532715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.140739440918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1232204437256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1092052459717</t>
+    <t xml:space="preserve">12.0391283035278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8464193344116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0636548995972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1407403945923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1232194900513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.109206199646</t>
   </si>
   <si>
     <t xml:space="preserve">12.0321216583252</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8779544830322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9760608673096</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6887464523315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4680051803589</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4890289306641</t>
+    <t xml:space="preserve">11.8779535293579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9760599136353</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6887474060059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4680061340332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4890298843384</t>
   </si>
   <si>
     <t xml:space="preserve">11.4820213317871</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6782350540161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2472639083862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.037036895752</t>
+    <t xml:space="preserve">11.6782360076904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2472658157349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.0370359420776</t>
   </si>
   <si>
     <t xml:space="preserve">11.1001052856445</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7216920852661</t>
+    <t xml:space="preserve">10.7216911315918</t>
   </si>
   <si>
     <t xml:space="preserve">10.9284172058105</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1561660766602</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4960374832153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4469814300537</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.184196472168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.3243494033813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2752962112427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.0615615844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4049377441406</t>
+    <t xml:space="preserve">11.1561651229858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.496036529541</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.446982383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.1841974258423</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.324348449707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2752952575684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.061562538147</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4049367904663</t>
   </si>
   <si>
     <t xml:space="preserve">11.2297458648682</t>
@@ -2378,22 +2378,22 @@
     <t xml:space="preserve">11.4119443893433</t>
   </si>
   <si>
-    <t xml:space="preserve">11.4995403289795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7903575897217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8814563751221</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8288984298706</t>
+    <t xml:space="preserve">11.4995393753052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.790358543396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8814573287964</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8288993835449</t>
   </si>
   <si>
     <t xml:space="preserve">11.9550361633301</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6677227020264</t>
+    <t xml:space="preserve">11.6677236557007</t>
   </si>
   <si>
     <t xml:space="preserve">11.6712284088135</t>
@@ -2405,16 +2405,16 @@
     <t xml:space="preserve">11.9970836639404</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9410219192505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.9690523147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0671577453613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.2703819274902</t>
+    <t xml:space="preserve">11.9410228729248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.969051361084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0671586990356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.2703809738159</t>
   </si>
   <si>
     <t xml:space="preserve">12.2738847732544</t>
@@ -2426,7 +2426,7 @@
     <t xml:space="preserve">12.0951900482178</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9725570678711</t>
+    <t xml:space="preserve">11.9725551605225</t>
   </si>
   <si>
     <t xml:space="preserve">12.0146017074585</t>
@@ -2435,19 +2435,19 @@
     <t xml:space="preserve">12.0741662979126</t>
   </si>
   <si>
-    <t xml:space="preserve">11.9865713119507</t>
+    <t xml:space="preserve">11.986572265625</t>
   </si>
   <si>
     <t xml:space="preserve">11.6011514663696</t>
   </si>
   <si>
-    <t xml:space="preserve">11.552098274231</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5485935211182</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5941438674927</t>
+    <t xml:space="preserve">11.5520992279053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5485925674438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5941429138184</t>
   </si>
   <si>
     <t xml:space="preserve">11.4259605407715</t>
@@ -2459,10 +2459,10 @@
     <t xml:space="preserve">11.6852426528931</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7693338394165</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7027626037598</t>
+    <t xml:space="preserve">11.7693347930908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7027616500854</t>
   </si>
   <si>
     <t xml:space="preserve">11.9480285644531</t>
@@ -2471,31 +2471,31 @@
     <t xml:space="preserve">12.0846796035767</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2108154296875</t>
+    <t xml:space="preserve">12.2108144760132</t>
   </si>
   <si>
     <t xml:space="preserve">12.7539081573486</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9641370773315</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7188701629639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.7889461517334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.795952796936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9886646270752</t>
+    <t xml:space="preserve">12.9641389846802</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7188692092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7889471054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7959537506104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9886636734009</t>
   </si>
   <si>
     <t xml:space="preserve">13.1743650436401</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9080762863159</t>
+    <t xml:space="preserve">12.9080772399902</t>
   </si>
   <si>
     <t xml:space="preserve">13.0412225723267</t>
@@ -2504,142 +2504,142 @@
     <t xml:space="preserve">13.2094058990479</t>
   </si>
   <si>
-    <t xml:space="preserve">13.6649017333984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8996572494507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4007024765015</t>
+    <t xml:space="preserve">13.6649007797241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8996562957764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4007034301758</t>
   </si>
   <si>
     <t xml:space="preserve">14.365665435791</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6389646530151</t>
+    <t xml:space="preserve">14.6389636993408</t>
   </si>
   <si>
     <t xml:space="preserve">15.0173759460449</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1365060806274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5289325714111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9493942260742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7181396484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9213600158691</t>
+    <t xml:space="preserve">15.1365079879761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5289354324341</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9493913650513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7181415557861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9213619232178</t>
   </si>
   <si>
     <t xml:space="preserve">16.1035614013672</t>
   </si>
   <si>
-    <t xml:space="preserve">15.9914398193359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.124584197998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4118957519531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5940971374512</t>
+    <t xml:space="preserve">15.9914388656616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1245861053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4118995666504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5940952301025</t>
   </si>
   <si>
     <t xml:space="preserve">16.5100040435791</t>
   </si>
   <si>
-    <t xml:space="preserve">16.2086734771729</t>
+    <t xml:space="preserve">16.2086772918701</t>
   </si>
   <si>
     <t xml:space="preserve">16.0474987030029</t>
   </si>
   <si>
-    <t xml:space="preserve">15.886326789856</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.4868879318237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8232555389404</t>
+    <t xml:space="preserve">15.8863248825073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.486888885498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8232526779175</t>
   </si>
   <si>
     <t xml:space="preserve">15.7531785964966</t>
   </si>
   <si>
-    <t xml:space="preserve">15.7251501083374</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1575269699097</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3817739486694</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2626447677612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2976818084717</t>
+    <t xml:space="preserve">15.7251462936401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1575288772583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3817749023438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2626438140869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2976808547974</t>
   </si>
   <si>
     <t xml:space="preserve">15.0804452896118</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2836656570435</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2205963134766</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0944595336914</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0664310455322</t>
+    <t xml:space="preserve">15.2836666107178</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2205991744995</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.09446144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0664291381836</t>
   </si>
   <si>
     <t xml:space="preserve">15.0454063415527</t>
   </si>
   <si>
-    <t xml:space="preserve">14.8561992645264</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9122610092163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1715450286865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8702144622803</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7721090316772</t>
+    <t xml:space="preserve">14.856201171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9122629165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1715440750122</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8702154159546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7721099853516</t>
   </si>
   <si>
     <t xml:space="preserve">15.3537435531616</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5029964447021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5800800323486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.4189052581787</t>
+    <t xml:space="preserve">16.5029945373535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5800819396973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.4189033508301</t>
   </si>
   <si>
     <t xml:space="preserve">16.7062187194824</t>
   </si>
   <si>
-    <t xml:space="preserve">16.8043251037598</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6221256256104</t>
+    <t xml:space="preserve">16.8043270111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.6221237182617</t>
   </si>
   <si>
     <t xml:space="preserve">16.5660648345947</t>
@@ -2648,37 +2648,37 @@
     <t xml:space="preserve">16.9865226745605</t>
   </si>
   <si>
-    <t xml:space="preserve">17.00754737854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.5380344390869</t>
+    <t xml:space="preserve">17.0075492858887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.5380363464355</t>
   </si>
   <si>
     <t xml:space="preserve">16.0545082092285</t>
   </si>
   <si>
-    <t xml:space="preserve">16.3978805541992</t>
+    <t xml:space="preserve">16.3978824615479</t>
   </si>
   <si>
     <t xml:space="preserve">16.4959888458252</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0685214996338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5499572753906</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.5709781646729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.033483505249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9423847198486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1666278839111</t>
+    <t xml:space="preserve">16.0685253143311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5499563217163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.5709800720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.0334854125977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.9423856735229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1666297912598</t>
   </si>
   <si>
     <t xml:space="preserve">16.6431484222412</t>
@@ -2687,22 +2687,22 @@
     <t xml:space="preserve">16.3908748626709</t>
   </si>
   <si>
-    <t xml:space="preserve">16.762279510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.7833003997803</t>
+    <t xml:space="preserve">16.7622776031494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.7833023071289</t>
   </si>
   <si>
     <t xml:space="preserve">16.6711807250977</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7272434234619</t>
+    <t xml:space="preserve">16.7272396087646</t>
   </si>
   <si>
     <t xml:space="preserve">16.9514865875244</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6130266189575</t>
+    <t xml:space="preserve">15.6130285263062</t>
   </si>
   <si>
     <t xml:space="preserve">14.5198345184326</t>
@@ -2711,10 +2711,10 @@
     <t xml:space="preserve">14.3516502380371</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5478639602661</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7910404205322</t>
+    <t xml:space="preserve">14.5478649139404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7910394668579</t>
   </si>
   <si>
     <t xml:space="preserve">13.4546728134155</t>
@@ -2723,13 +2723,13 @@
     <t xml:space="preserve">13.0272064208984</t>
   </si>
   <si>
-    <t xml:space="preserve">12.9956731796265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3474655151367</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.7202806472778</t>
+    <t xml:space="preserve">12.9956712722778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3474645614624</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.7202825546265</t>
   </si>
   <si>
     <t xml:space="preserve">10.3327674865723</t>
@@ -2741,7 +2741,7 @@
     <t xml:space="preserve">9.81069850921631</t>
   </si>
   <si>
-    <t xml:space="preserve">8.25149822235107</t>
+    <t xml:space="preserve">8.25149726867676</t>
   </si>
   <si>
     <t xml:space="preserve">9.51988220214844</t>
@@ -2750,43 +2750,43 @@
     <t xml:space="preserve">8.4442081451416</t>
   </si>
   <si>
-    <t xml:space="preserve">8.0202465057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.70490121841431</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.77497863769531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.49817657470703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">7.59978771209717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">8.28653717041016</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.06088161468506</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.69507312774658</t>
+    <t xml:space="preserve">8.02024555206299</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.70490312576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.77497816085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.49817705154419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7.59978723526001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">8.28653621673584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.06088066101074</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.69507217407227</t>
   </si>
   <si>
     <t xml:space="preserve">9.05036926269531</t>
   </si>
   <si>
-    <t xml:space="preserve">8.87167549133301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.2360725402832</t>
+    <t xml:space="preserve">8.87167453765869</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.23607158660889</t>
   </si>
   <si>
     <t xml:space="preserve">8.87517833709717</t>
   </si>
   <si>
-    <t xml:space="preserve">9.07489585876465</t>
+    <t xml:space="preserve">9.07489490509033</t>
   </si>
   <si>
     <t xml:space="preserve">8.68246841430664</t>
@@ -2795,16 +2795,16 @@
     <t xml:space="preserve">9.0223388671875</t>
   </si>
   <si>
-    <t xml:space="preserve">9.48834705352783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.1680879592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.2381639480591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">9.87727165222168</t>
+    <t xml:space="preserve">9.48834800720215</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.1680889129639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.2381649017334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">9.87727069854736</t>
   </si>
   <si>
     <t xml:space="preserve">9.29914093017578</t>
@@ -2816,7 +2816,7 @@
     <t xml:space="preserve">9.51637744903564</t>
   </si>
   <si>
-    <t xml:space="preserve">9.58995819091797</t>
+    <t xml:space="preserve">9.58995914459229</t>
   </si>
   <si>
     <t xml:space="preserve">9.25359153747559</t>
@@ -2825,40 +2825,40 @@
     <t xml:space="preserve">9.33417892456055</t>
   </si>
   <si>
-    <t xml:space="preserve">9.4953556060791</t>
+    <t xml:space="preserve">9.49535369873047</t>
   </si>
   <si>
     <t xml:space="preserve">9.47433185577393</t>
   </si>
   <si>
-    <t xml:space="preserve">10.3713092803955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8162956237793</t>
+    <t xml:space="preserve">10.3713111877441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.816294670105</t>
   </si>
   <si>
     <t xml:space="preserve">11.2122278213501</t>
   </si>
   <si>
-    <t xml:space="preserve">10.8793649673462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.760232925415</t>
+    <t xml:space="preserve">10.8793640136719</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7602348327637</t>
   </si>
   <si>
     <t xml:space="preserve">10.8618450164795</t>
   </si>
   <si>
-    <t xml:space="preserve">10.5324859619141</t>
+    <t xml:space="preserve">10.5324869155884</t>
   </si>
   <si>
     <t xml:space="preserve">10.6025629043579</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6095695495605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.5394926071167</t>
+    <t xml:space="preserve">10.6095705032349</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.539493560791</t>
   </si>
   <si>
     <t xml:space="preserve">10.4133558273315</t>
@@ -2867,16 +2867,16 @@
     <t xml:space="preserve">11.0058345794678</t>
   </si>
   <si>
-    <t xml:space="preserve">10.4649343490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.7654333114624</t>
+    <t xml:space="preserve">10.4649333953857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.7654342651367</t>
   </si>
   <si>
     <t xml:space="preserve">10.6414775848389</t>
   </si>
   <si>
-    <t xml:space="preserve">10.7691898345947</t>
+    <t xml:space="preserve">10.769190788269</t>
   </si>
   <si>
     <t xml:space="preserve">10.8743658065796</t>
@@ -2885,13 +2885,13 @@
     <t xml:space="preserve">10.9757843017578</t>
   </si>
   <si>
-    <t xml:space="preserve">10.9720287322998</t>
+    <t xml:space="preserve">10.9720277786255</t>
   </si>
   <si>
     <t xml:space="preserve">11.358922958374</t>
   </si>
   <si>
-    <t xml:space="preserve">11.1936483383179</t>
+    <t xml:space="preserve">11.1936473846436</t>
   </si>
   <si>
     <t xml:space="preserve">11.3251161575317</t>
@@ -2906,22 +2906,22 @@
     <t xml:space="preserve">12.0913925170898</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6923961639404</t>
+    <t xml:space="preserve">12.6923952102661</t>
   </si>
   <si>
     <t xml:space="preserve">12.9966506958008</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4407243728638</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3956508636475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.648154258728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6105928421021</t>
+    <t xml:space="preserve">12.4407253265381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3956499099731</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6481552124023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.6105918884277</t>
   </si>
   <si>
     <t xml:space="preserve">11.5166854858398</t>
@@ -2930,43 +2930,43 @@
     <t xml:space="preserve">11.7721109390259</t>
   </si>
   <si>
-    <t xml:space="preserve">11.6669359207153</t>
+    <t xml:space="preserve">11.666934967041</t>
   </si>
   <si>
     <t xml:space="preserve">11.5091733932495</t>
   </si>
   <si>
-    <t xml:space="preserve">11.7157669067383</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5730285644531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8284549713135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2687721252441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4490718841553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2011594772339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.4791221618652</t>
+    <t xml:space="preserve">11.7157678604126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5730304718018</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8284559249878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2687730789185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4490728378296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2011604309082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.4791231155396</t>
   </si>
   <si>
     <t xml:space="preserve">11.4265356063843</t>
   </si>
   <si>
-    <t xml:space="preserve">11.3664360046387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.6631803512573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.5429792404175</t>
+    <t xml:space="preserve">11.3664350509644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.663179397583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.5429782867432</t>
   </si>
   <si>
     <t xml:space="preserve">11.7796239852905</t>
@@ -2987,64 +2987,64 @@
     <t xml:space="preserve">11.8434810638428</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3580884933472</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3205242156982</t>
+    <t xml:space="preserve">12.3580875396729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3205251693726</t>
   </si>
   <si>
     <t xml:space="preserve">12.801326751709</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6999082565308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.733715057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.835132598877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.5684385299683</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.6097555160522</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3731117248535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.4369688034058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0763692855835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0575857162476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3693561553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3505754470825</t>
+    <t xml:space="preserve">12.6999073028564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.7337131500244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.8351306915283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5684366226196</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.6097574234009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3731126785278</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.4369697570801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0763683319092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0575876235962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3693571090698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3505744934082</t>
   </si>
   <si>
     <t xml:space="preserve">12.4745311737061</t>
   </si>
   <si>
-    <t xml:space="preserve">12.493311882019</t>
+    <t xml:space="preserve">12.4933128356934</t>
   </si>
   <si>
     <t xml:space="preserve">12.470775604248</t>
   </si>
   <si>
-    <t xml:space="preserve">12.8276214599609</t>
+    <t xml:space="preserve">12.8276205062866</t>
   </si>
   <si>
     <t xml:space="preserve">12.7938146591187</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6585893630981</t>
+    <t xml:space="preserve">12.6585884094238</t>
   </si>
   <si>
     <t xml:space="preserve">12.5984888076782</t>
@@ -3053,7 +3053,7 @@
     <t xml:space="preserve">12.4557504653931</t>
   </si>
   <si>
-    <t xml:space="preserve">12.515851020813</t>
+    <t xml:space="preserve">12.5158500671387</t>
   </si>
   <si>
     <t xml:space="preserve">12.3468179702759</t>
@@ -3065,19 +3065,19 @@
     <t xml:space="preserve">12.6661014556885</t>
   </si>
   <si>
-    <t xml:space="preserve">12.6247825622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.508337020874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.3881368637085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.1740303039551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0650997161865</t>
+    <t xml:space="preserve">12.6247816085815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.5083379745483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.3881378173828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.1740312576294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0650987625122</t>
   </si>
   <si>
     <t xml:space="preserve">12.2641820907593</t>
@@ -3089,10 +3089,10 @@
     <t xml:space="preserve">12.1552495956421</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8847980499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0688562393188</t>
+    <t xml:space="preserve">11.8847999572754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0688552856445</t>
   </si>
   <si>
     <t xml:space="preserve">12.1101751327515</t>
@@ -3101,7 +3101,7 @@
     <t xml:space="preserve">12.2078371047974</t>
   </si>
   <si>
-    <t xml:space="preserve">12.3843812942505</t>
+    <t xml:space="preserve">12.3843822479248</t>
   </si>
   <si>
     <t xml:space="preserve">12.5120944976807</t>
@@ -3110,13 +3110,13 @@
     <t xml:space="preserve">12.6285381317139</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4257020950317</t>
+    <t xml:space="preserve">12.4257001876831</t>
   </si>
   <si>
     <t xml:space="preserve">11.8547487258911</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8322124481201</t>
+    <t xml:space="preserve">11.8322105407715</t>
   </si>
   <si>
     <t xml:space="preserve">11.8096742630005</t>
@@ -3131,7 +3131,7 @@
     <t xml:space="preserve">11.7645988464355</t>
   </si>
   <si>
-    <t xml:space="preserve">11.5993242263794</t>
+    <t xml:space="preserve">11.5993232727051</t>
   </si>
   <si>
     <t xml:space="preserve">11.5842990875244</t>
@@ -3146,16 +3146,16 @@
     <t xml:space="preserve">11.7120113372803</t>
   </si>
   <si>
-    <t xml:space="preserve">11.8772869110107</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.8359670639038</t>
+    <t xml:space="preserve">11.8772859573364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.8359680175781</t>
   </si>
   <si>
     <t xml:space="preserve">11.9524116516113</t>
   </si>
   <si>
-    <t xml:space="preserve">12.2003240585327</t>
+    <t xml:space="preserve">12.200325012207</t>
   </si>
   <si>
     <t xml:space="preserve">12.2904748916626</t>
@@ -3164,13 +3164,13 @@
     <t xml:space="preserve">12.1139307022095</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4031620025635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.944899559021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.0989065170288</t>
+    <t xml:space="preserve">12.4031639099121</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.9448986053467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.0989055633545</t>
   </si>
   <si>
     <t xml:space="preserve">12.1514921188354</t>
@@ -3188,13 +3188,13 @@
     <t xml:space="preserve">10.8255348205566</t>
   </si>
   <si>
-    <t xml:space="preserve">10.6452341079712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.8893899917603</t>
-  </si>
-  <si>
-    <t xml:space="preserve">11.2499914169312</t>
+    <t xml:space="preserve">10.6452350616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.8893909454346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">11.2499923706055</t>
   </si>
   <si>
     <t xml:space="preserve">11.64439868927</t>
@@ -3212,25 +3212,25 @@
     <t xml:space="preserve">12.5834636688232</t>
   </si>
   <si>
-    <t xml:space="preserve">12.4332122802734</t>
+    <t xml:space="preserve">12.4332113265991</t>
   </si>
   <si>
     <t xml:space="preserve">12.4106750488281</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1393880844116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2070016860962</t>
+    <t xml:space="preserve">13.1393890380859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2070007324219</t>
   </si>
   <si>
     <t xml:space="preserve">13.5600900650024</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2370529174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2595891952515</t>
+    <t xml:space="preserve">13.2370519638062</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2595882415771</t>
   </si>
   <si>
     <t xml:space="preserve">13.2220277786255</t>
@@ -3239,64 +3239,64 @@
     <t xml:space="preserve">13.6727781295776</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3572540283203</t>
+    <t xml:space="preserve">13.3572521209717</t>
   </si>
   <si>
     <t xml:space="preserve">13.379789352417</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2746133804321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.5375528335571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1882219314575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.2821264266968</t>
+    <t xml:space="preserve">13.2746143341064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.5375518798828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1882200241089</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.2821273803711</t>
   </si>
   <si>
     <t xml:space="preserve">13.2896404266357</t>
   </si>
   <si>
-    <t xml:space="preserve">13.2295389175415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1619262695312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.9327945709229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1731948852539</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1919775009155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.1957321166992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.0154333114624</t>
-  </si>
-  <si>
-    <t xml:space="preserve">12.8238620758057</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3272018432617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4361343383789</t>
+    <t xml:space="preserve">13.2295408248901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1619272232056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.9327936172485</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1731939315796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1919755935669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.1957330703735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0154342651367</t>
+  </si>
+  <si>
+    <t xml:space="preserve">12.82386302948</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3272008895874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4361333847046</t>
   </si>
   <si>
     <t xml:space="preserve">13.4962339401245</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4323759078979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.349739074707</t>
+    <t xml:space="preserve">13.4323768615723</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3497409820557</t>
   </si>
   <si>
     <t xml:space="preserve">13.3384704589844</t>
@@ -3305,7 +3305,7 @@
     <t xml:space="preserve">13.1994895935059</t>
   </si>
   <si>
-    <t xml:space="preserve">13.4135961532593</t>
+    <t xml:space="preserve">13.4135971069336</t>
   </si>
   <si>
     <t xml:space="preserve">13.4248657226562</t>
@@ -3314,31 +3314,31 @@
     <t xml:space="preserve">13.39857006073</t>
   </si>
   <si>
-    <t xml:space="preserve">13.3910598754883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.6802883148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2099227905273</t>
+    <t xml:space="preserve">13.391058921814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.6802892684937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2099237442017</t>
   </si>
   <si>
     <t xml:space="preserve">13.9582529067993</t>
   </si>
   <si>
-    <t xml:space="preserve">13.8305397033691</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8943967819214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.8380527496338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.931960105896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.7328796386719</t>
+    <t xml:space="preserve">13.8305406570435</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.89439868927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.8380537033081</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.9319591522217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.7328786849976</t>
   </si>
   <si>
     <t xml:space="preserve">13.4398899078369</t>
@@ -3347,67 +3347,67 @@
     <t xml:space="preserve">13.4060831069946</t>
   </si>
   <si>
-    <t xml:space="preserve">13.1093397140503</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.3009090423584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.04172706604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13.4887208938599</t>
+    <t xml:space="preserve">13.1093406677246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.3009080886841</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.0417280197144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13.4887199401855</t>
   </si>
   <si>
     <t xml:space="preserve">13.5676021575928</t>
   </si>
   <si>
-    <t xml:space="preserve">13.7216091156006</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.3526601791382</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5855474472046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0550804138184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0926446914673</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.025032043457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1978178024292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8447303771973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7207727432251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9198579788208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.8221912384033</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.5329599380493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6005725860596</t>
+    <t xml:space="preserve">13.7216081619263</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.3526611328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5855503082275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.055079460144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0926418304443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.0250310897827</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1978168487549</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8447294235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7207736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9198560714722</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8221921920776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.5329608917236</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6005716323853</t>
   </si>
   <si>
     <t xml:space="preserve">14.4315404891968</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2812919616699</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9499034881592</t>
+    <t xml:space="preserve">14.2812929153442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9499044418335</t>
   </si>
   <si>
     <t xml:space="preserve">14.7846307754517</t>
@@ -3416,37 +3416,37 @@
     <t xml:space="preserve">14.7095041275024</t>
   </si>
   <si>
-    <t xml:space="preserve">14.6644296646118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4240293502808</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7959003448486</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.762092590332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9123430252075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.6606731414795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.4090032577515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1948986053467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.1197719573975</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.202410697937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.2775354385376</t>
+    <t xml:space="preserve">14.6644306182861</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4240303039551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7958974838257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7620916366577</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9123420715332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.6606721878052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.4090051651001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1948976516724</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.1197729110718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2024097442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.2775344848633</t>
   </si>
   <si>
     <t xml:space="preserve">14.3226108551025</t>
@@ -3458,7 +3458,7 @@
     <t xml:space="preserve">14.3714408874512</t>
   </si>
   <si>
-    <t xml:space="preserve">14.2925586700439</t>
+    <t xml:space="preserve">14.2925605773926</t>
   </si>
   <si>
     <t xml:space="preserve">14.4653482437134</t>
@@ -3467,19 +3467,19 @@
     <t xml:space="preserve">14.7470664978027</t>
   </si>
   <si>
-    <t xml:space="preserve">14.5930604934692</t>
+    <t xml:space="preserve">14.5930614471436</t>
   </si>
   <si>
     <t xml:space="preserve">14.8898048400879</t>
   </si>
   <si>
-    <t xml:space="preserve">14.848484992981</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2504053115845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1001539230347</t>
+    <t xml:space="preserve">14.8484859466553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2504043579102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1001567840576</t>
   </si>
   <si>
     <t xml:space="preserve">15.1151809692383</t>
@@ -3488,88 +3488,88 @@
     <t xml:space="preserve">15.0701055526733</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1827926635742</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7245283126831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.7508249282837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.814679145813</t>
+    <t xml:space="preserve">15.1827917098999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7245292663574</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.7508239746094</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.8146781921387</t>
   </si>
   <si>
     <t xml:space="preserve">14.8184366226196</t>
   </si>
   <si>
-    <t xml:space="preserve">14.9837112426758</t>
+    <t xml:space="preserve">14.9837102890015</t>
   </si>
   <si>
     <t xml:space="preserve">15.0175170898438</t>
   </si>
   <si>
-    <t xml:space="preserve">14.7921419143677</t>
+    <t xml:space="preserve">14.7921438217163</t>
   </si>
   <si>
     <t xml:space="preserve">14.9611740112305</t>
   </si>
   <si>
-    <t xml:space="preserve">15.1602582931519</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14.9724426269531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.0851306915283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.1377191543579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.3555822372437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.2579164505005</t>
+    <t xml:space="preserve">15.1602544784546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14.9724435806274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.085129737854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.1377201080322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.3555812835693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.2579183578491</t>
   </si>
   <si>
     <t xml:space="preserve">15.2804565429688</t>
   </si>
   <si>
-    <t xml:space="preserve">15.2729454040527</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7462329864502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8664321899414</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8438940048218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6410551071167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.708667755127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.6711082458496</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.1603336334229</t>
+    <t xml:space="preserve">15.2729434967041</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7462310791016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.86643409729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.8438949584961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.641056060791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7086696624756</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.6711053848267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.1603355407715</t>
   </si>
   <si>
     <t xml:space="preserve">16.0814266204834</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8841562271118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8999404907227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.9551753997803</t>
+    <t xml:space="preserve">15.8841552734375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.899941444397</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.955174446106</t>
   </si>
   <si>
     <t xml:space="preserve">16.0419731140137</t>
@@ -3614,7 +3614,7 @@
     <t xml:space="preserve">15.9472827911377</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8762683868408</t>
+    <t xml:space="preserve">15.8762674331665</t>
   </si>
   <si>
     <t xml:space="preserve">16.2392444610596</t>
@@ -3641,7 +3641,7 @@
     <t xml:space="preserve">16.5075302124023</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4838562011719</t>
+    <t xml:space="preserve">16.4838581085205</t>
   </si>
   <si>
     <t xml:space="preserve">16.4444046020508</t>
@@ -3650,10 +3650,10 @@
     <t xml:space="preserve">16.2550258636475</t>
   </si>
   <si>
-    <t xml:space="preserve">16.5233116149902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.8073787689209</t>
+    <t xml:space="preserve">16.5233135223389</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.8073806762695</t>
   </si>
   <si>
     <t xml:space="preserve">17.1624660491943</t>
@@ -3665,7 +3665,7 @@
     <t xml:space="preserve">17.3281726837158</t>
   </si>
   <si>
-    <t xml:space="preserve">17.1940307617188</t>
+    <t xml:space="preserve">17.1940288543701</t>
   </si>
   <si>
     <t xml:space="preserve">17.2492656707764</t>
@@ -3674,7 +3674,7 @@
     <t xml:space="preserve">17.1387939453125</t>
   </si>
   <si>
-    <t xml:space="preserve">17.4702053070068</t>
+    <t xml:space="preserve">17.4702072143555</t>
   </si>
   <si>
     <t xml:space="preserve">17.4938793182373</t>
@@ -3686,7 +3686,7 @@
     <t xml:space="preserve">17.4070796966553</t>
   </si>
   <si>
-    <t xml:space="preserve">17.5727863311768</t>
+    <t xml:space="preserve">17.5727882385254</t>
   </si>
   <si>
     <t xml:space="preserve">17.9042015075684</t>
@@ -3695,10 +3695,10 @@
     <t xml:space="preserve">17.9120903015137</t>
   </si>
   <si>
-    <t xml:space="preserve">18.1093616485596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.1172504425049</t>
+    <t xml:space="preserve">18.1093597412109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.1172523498535</t>
   </si>
   <si>
     <t xml:space="preserve">18.2592868804932</t>
@@ -3707,10 +3707,10 @@
     <t xml:space="preserve">18.3224124908447</t>
   </si>
   <si>
-    <t xml:space="preserve">18.2435054779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.4644451141357</t>
+    <t xml:space="preserve">18.2435035705566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.4644470214844</t>
   </si>
   <si>
     <t xml:space="preserve">18.2513942718506</t>
@@ -3719,7 +3719,7 @@
     <t xml:space="preserve">18.2829570770264</t>
   </si>
   <si>
-    <t xml:space="preserve">18.4249935150146</t>
+    <t xml:space="preserve">18.424991607666</t>
   </si>
   <si>
     <t xml:space="preserve">18.3539752960205</t>
@@ -3740,28 +3740,28 @@
     <t xml:space="preserve">18.7642974853516</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8037490844727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7011699676514</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7564067840576</t>
+    <t xml:space="preserve">18.8037509918213</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.701171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.756404876709</t>
   </si>
   <si>
     <t xml:space="preserve">18.7406234741211</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6459312438965</t>
+    <t xml:space="preserve">18.6459331512451</t>
   </si>
   <si>
     <t xml:space="preserve">18.7169494628906</t>
   </si>
   <si>
-    <t xml:space="preserve">18.5749206542969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.8432025909424</t>
+    <t xml:space="preserve">18.5749187469482</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.843204498291</t>
   </si>
   <si>
     <t xml:space="preserve">18.8984394073486</t>
@@ -3770,7 +3770,7 @@
     <t xml:space="preserve">18.9536762237549</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1903972625732</t>
+    <t xml:space="preserve">19.1903991699219</t>
   </si>
   <si>
     <t xml:space="preserve">19.0878200531006</t>
@@ -3782,13 +3782,13 @@
     <t xml:space="preserve">18.8589859008789</t>
   </si>
   <si>
-    <t xml:space="preserve">18.937894821167</t>
+    <t xml:space="preserve">18.9378929138184</t>
   </si>
   <si>
     <t xml:space="preserve">19.2614154815674</t>
   </si>
   <si>
-    <t xml:space="preserve">19.1430530548096</t>
+    <t xml:space="preserve">19.1430549621582</t>
   </si>
   <si>
     <t xml:space="preserve">18.7327327728271</t>
@@ -3800,13 +3800,13 @@
     <t xml:space="preserve">18.7721862792969</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6538257598877</t>
+    <t xml:space="preserve">18.6538238525391</t>
   </si>
   <si>
     <t xml:space="preserve">18.4013195037842</t>
   </si>
   <si>
-    <t xml:space="preserve">18.6222610473633</t>
+    <t xml:space="preserve">18.6222629547119</t>
   </si>
   <si>
     <t xml:space="preserve">18.2356128692627</t>
@@ -3821,13 +3821,13 @@
     <t xml:space="preserve">18.6380443572998</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8353137969971</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.7090606689453</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.5375938415527</t>
+    <t xml:space="preserve">18.8353118896484</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.7090587615967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.5375919342041</t>
   </si>
   <si>
     <t xml:space="preserve">19.403450012207</t>
@@ -3836,10 +3836,10 @@
     <t xml:space="preserve">19.5297031402588</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6007194519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">19.8374423980713</t>
+    <t xml:space="preserve">19.6007175445557</t>
+  </si>
+  <si>
+    <t xml:space="preserve">19.8374443054199</t>
   </si>
   <si>
     <t xml:space="preserve">19.6322803497314</t>
@@ -3854,7 +3854,7 @@
     <t xml:space="preserve">19.9952583312988</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0662784576416</t>
+    <t xml:space="preserve">20.066276550293</t>
   </si>
   <si>
     <t xml:space="preserve">20.1057300567627</t>
@@ -3866,7 +3866,7 @@
     <t xml:space="preserve">20.0741672515869</t>
   </si>
   <si>
-    <t xml:space="preserve">20.0189304351807</t>
+    <t xml:space="preserve">20.0189323425293</t>
   </si>
   <si>
     <t xml:space="preserve">20.2398738861084</t>
@@ -3887,10 +3887,10 @@
     <t xml:space="preserve">20.9816074371338</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6659755706787</t>
-  </si>
-  <si>
-    <t xml:space="preserve">20.2162036895752</t>
+    <t xml:space="preserve">20.6659774780273</t>
+  </si>
+  <si>
+    <t xml:space="preserve">20.2162017822266</t>
   </si>
   <si>
     <t xml:space="preserve">20.1372947692871</t>
@@ -3908,7 +3908,7 @@
     <t xml:space="preserve">19.3324337005615</t>
   </si>
   <si>
-    <t xml:space="preserve">19.4744663238525</t>
+    <t xml:space="preserve">19.4744682312012</t>
   </si>
   <si>
     <t xml:space="preserve">19.3087596893311</t>
@@ -3917,7 +3917,7 @@
     <t xml:space="preserve">19.1746158599854</t>
   </si>
   <si>
-    <t xml:space="preserve">19.2377433776855</t>
+    <t xml:space="preserve">19.2377414703369</t>
   </si>
   <si>
     <t xml:space="preserve">19.2850894927979</t>
@@ -3926,13 +3926,13 @@
     <t xml:space="preserve">19.1272716522217</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0246925354004</t>
+    <t xml:space="preserve">19.024694442749</t>
   </si>
   <si>
     <t xml:space="preserve">18.8116397857666</t>
   </si>
   <si>
-    <t xml:space="preserve">19.0168037414551</t>
+    <t xml:space="preserve">19.0168018341064</t>
   </si>
   <si>
     <t xml:space="preserve">18.7248420715332</t>
@@ -3953,7 +3953,7 @@
     <t xml:space="preserve">19.7269725799561</t>
   </si>
   <si>
-    <t xml:space="preserve">19.9005699157715</t>
+    <t xml:space="preserve">19.9005680084229</t>
   </si>
   <si>
     <t xml:space="preserve">19.9479160308838</t>
@@ -3965,13 +3965,13 @@
     <t xml:space="preserve">19.5770454406738</t>
   </si>
   <si>
-    <t xml:space="preserve">19.6165027618408</t>
+    <t xml:space="preserve">19.6165008544922</t>
   </si>
   <si>
     <t xml:space="preserve">20.0268211364746</t>
   </si>
   <si>
-    <t xml:space="preserve">20.8711395263672</t>
+    <t xml:space="preserve">20.8711376190186</t>
   </si>
   <si>
     <t xml:space="preserve">20.9342632293701</t>
@@ -3980,31 +3980,31 @@
     <t xml:space="preserve">20.5791778564453</t>
   </si>
   <si>
-    <t xml:space="preserve">20.6817569732666</t>
+    <t xml:space="preserve">20.6817588806152</t>
   </si>
   <si>
     <t xml:space="preserve">20.3187828063965</t>
   </si>
   <si>
-    <t xml:space="preserve">19.8847885131836</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.2119426727295</t>
+    <t xml:space="preserve">19.884786605835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.2119407653809</t>
   </si>
   <si>
     <t xml:space="preserve">18.2671756744385</t>
   </si>
   <si>
-    <t xml:space="preserve">18.3934288024902</t>
+    <t xml:space="preserve">18.3934268951416</t>
   </si>
   <si>
     <t xml:space="preserve">19.0325832366943</t>
   </si>
   <si>
-    <t xml:space="preserve">18.8747673034668</t>
-  </si>
-  <si>
-    <t xml:space="preserve">18.33030128479</t>
+    <t xml:space="preserve">18.8747653961182</t>
+  </si>
+  <si>
+    <t xml:space="preserve">18.3303031921387</t>
   </si>
   <si>
     <t xml:space="preserve">18.7958583831787</t>
@@ -4019,13 +4019,13 @@
     <t xml:space="preserve">17.8095111846924</t>
   </si>
   <si>
-    <t xml:space="preserve">17.7463855743408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.9278736114502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">16.6416721343994</t>
+    <t xml:space="preserve">17.7463836669922</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.9278717041016</t>
+  </si>
+  <si>
+    <t xml:space="preserve">16.641674041748</t>
   </si>
   <si>
     <t xml:space="preserve">17.1782474517822</t>
@@ -4040,7 +4040,7 @@
     <t xml:space="preserve">15.4028205871582</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4501647949219</t>
+    <t xml:space="preserve">15.4501638412476</t>
   </si>
   <si>
     <t xml:space="preserve">15.663215637207</t>
@@ -4052,10 +4052,10 @@
     <t xml:space="preserve">15.1897687911987</t>
   </si>
   <si>
-    <t xml:space="preserve">15.5093469619751</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.8525943756104</t>
+    <t xml:space="preserve">15.5093460083008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.852593421936</t>
   </si>
   <si>
     <t xml:space="preserve">17.0441055297852</t>
@@ -4064,7 +4064,7 @@
     <t xml:space="preserve">16.7915992736816</t>
   </si>
   <si>
-    <t xml:space="preserve">16.4759654998779</t>
+    <t xml:space="preserve">16.4759674072266</t>
   </si>
   <si>
     <t xml:space="preserve">16.8152713775635</t>
@@ -4076,10 +4076,10 @@
     <t xml:space="preserve">16.4286212921143</t>
   </si>
   <si>
-    <t xml:space="preserve">16.7442512512207</t>
-  </si>
-  <si>
-    <t xml:space="preserve">17.2413730621338</t>
+    <t xml:space="preserve">16.7442531585693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">17.2413749694824</t>
   </si>
   <si>
     <t xml:space="preserve">16.9415225982666</t>
@@ -4097,52 +4097,52 @@
     <t xml:space="preserve">15.7579050064087</t>
   </si>
   <si>
-    <t xml:space="preserve">15.4107112884521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7815771102905</t>
+    <t xml:space="preserve">15.4107103347778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7815780639648</t>
   </si>
   <si>
     <t xml:space="preserve">15.9157209396362</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8920488357544</t>
+    <t xml:space="preserve">15.8920497894287</t>
   </si>
   <si>
     <t xml:space="preserve">15.8683776855469</t>
   </si>
   <si>
-    <t xml:space="preserve">15.6277084350586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">15.7973594665527</t>
+    <t xml:space="preserve">15.6277074813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">15.7973604202271</t>
   </si>
   <si>
     <t xml:space="preserve">15.7539596557617</t>
   </si>
   <si>
-    <t xml:space="preserve">15.8289213180542</t>
+    <t xml:space="preserve">15.8289222717285</t>
   </si>
   <si>
     <t xml:space="preserve">16.089319229126</t>
   </si>
   <si>
-    <t xml:space="preserve">16.0735397338867</t>
+    <t xml:space="preserve">16.0735378265381</t>
 